--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18001240-C5C7-4434-A866-CD00CA04AE20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92B022F-4A75-43DE-87CC-24150DF70BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -28002,7 +28002,7 @@
       </c>
       <c r="G321">
         <f>計算表!G321</f>
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="H321">
         <f>計算表!H321</f>
@@ -47881,7 +47881,7 @@
         <v>1004</v>
       </c>
       <c r="G321">
-        <v>0.7</v>
+        <v>0.35</v>
       </c>
       <c r="H321">
         <v>0</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E92B022F-4A75-43DE-87CC-24150DF70BE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EDA8AE0-5682-4FC6-9DF1-EF6416560C31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32475" yWindow="2610" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -3790,6 +3790,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> = 1 + a * (</t>
     </r>
@@ -3806,6 +3807,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>) - b * (</t>
     </r>
@@ -3822,6 +3824,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>)^c</t>
     </r>
@@ -3844,6 +3847,7 @@
       <rPr>
         <sz val="11"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
       </rPr>
       <t>c=</t>
     </r>
@@ -5144,7 +5148,7 @@
       </c>
       <c r="I12">
         <f>計算表!I12</f>
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <f>計算表!J12</f>
@@ -29534,7 +29538,7 @@
         <v>4</v>
       </c>
       <c r="I12">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J12">
         <v>0</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C6209D2-65B5-4236-9CE7-27CD078FC68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639FFC93-2EF7-434B-9933-774675FA223E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -11128,7 +11128,7 @@
       </c>
       <c r="G91">
         <f>計算表!G91</f>
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="H91">
         <f>計算表!H91</f>
@@ -32944,7 +32944,7 @@
         <v>226</v>
       </c>
       <c r="G91">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="H91">
         <v>0</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639FFC93-2EF7-434B-9933-774675FA223E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F48EBE-A495-439B-A630-DB879801E053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -25439,7 +25439,7 @@
       </c>
       <c r="G285">
         <f>計算表!G289</f>
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H285">
         <f>計算表!H289</f>
@@ -44970,7 +44970,7 @@
         <v>826</v>
       </c>
       <c r="G289">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="H289">
         <v>0</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F48EBE-A495-439B-A630-DB879801E053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1608E79-4DB4-4E06-96A0-4ABE11A9FF04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -522,13 +522,7 @@
     <t>吸血 上限</t>
   </si>
   <si>
-    <t>a=吸血上限（%）；0＝無上限。2026-07-30 改版：吸血不再擋上限、也不再以造成的傷害計算，每次回復 = 每秒生命回復 × 吸血%。</t>
-  </si>
-  <si>
     <t>吸魔 上限</t>
-  </si>
-  <si>
-    <t>a=吸魔上限（%）；0＝無上限。2026-07-30 改版：吸魔不再擋上限、也不再以造成的傷害計算，每次回復 = 每秒法力恢復 × 吸魔%。</t>
   </si>
   <si>
     <t>格擋率 上限</t>
@@ -4026,6 +4020,14 @@
   </si>
   <si>
     <t>10.199999999999999</t>
+  </si>
+  <si>
+    <t>a=吸血上限（定值）；0＝無上限。吸血是定值：每次對敵人造成傷害固定回復的生命（舊版百分比以 1%＝1 轉換），單獨計算，與每秒生命回復、造成的傷害皆無關。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a=吸魔上限（定值）；0＝無上限。吸魔是定值：每次對敵人造成傷害固定回復的法力（舊版百分比以 1%＝1 轉換），單獨計算，與每秒法力恢復、造成的傷害皆無關。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -5229,7 +5231,7 @@
         <v>基礎a + 技能熟練度等級 + 潛力天賦加成</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="G11">
         <f>計算表!G11</f>
@@ -5672,7 +5674,7 @@
         <v>（查表）</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G17">
         <f>計算表!G17</f>
@@ -5745,7 +5747,7 @@
         <v>（查表）</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G18">
         <f>計算表!G18</f>
@@ -5818,7 +5820,7 @@
         <v>（查表）</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G19">
         <f>計算表!G19</f>
@@ -5891,7 +5893,7 @@
         <v>（查表）</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G20">
         <f>計算表!G20</f>
@@ -5964,7 +5966,7 @@
         <v>（查表）</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G21">
         <f>計算表!G21</f>
@@ -6037,7 +6039,7 @@
         <v>（查表）</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G22">
         <f>計算表!G22</f>
@@ -6110,7 +6112,7 @@
         <v>（查表）</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G23">
         <f>計算表!G23</f>
@@ -6183,7 +6185,7 @@
         <v>（查表）</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G24">
         <f>計算表!G24</f>
@@ -6256,7 +6258,7 @@
         <v>（查表）</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G25">
         <f>計算表!G25</f>
@@ -6329,7 +6331,7 @@
         <v>（查表）</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G26">
         <f>計算表!G26</f>
@@ -6402,7 +6404,7 @@
         <v>（查表）</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G27">
         <f>計算表!G27</f>
@@ -6475,7 +6477,7 @@
         <v>（查表）</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G28">
         <f>計算表!G28</f>
@@ -6548,7 +6550,7 @@
         <v>（查表）</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G29">
         <f>計算表!G29</f>
@@ -6621,7 +6623,7 @@
         <v>（查表）</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G30">
         <f>計算表!G30</f>
@@ -6694,7 +6696,7 @@
         <v>（查表）</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G31">
         <f>計算表!G31</f>
@@ -6767,7 +6769,7 @@
         <v>（查表）</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G32">
         <f>計算表!G32</f>
@@ -6840,7 +6842,7 @@
         <v>（查表）</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G33">
         <f>計算表!G33</f>
@@ -6913,7 +6915,7 @@
         <v>（查表）</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G34">
         <f>計算表!G34</f>
@@ -6986,7 +6988,7 @@
         <v>（查表）</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G35">
         <f>計算表!G35</f>
@@ -7059,7 +7061,7 @@
         <v>（查表）</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G36">
         <f>計算表!G36</f>
@@ -7132,7 +7134,7 @@
         <v>（查表）</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G37">
         <f>計算表!G37</f>
@@ -7576,7 +7578,7 @@
       </c>
       <c r="F43" t="str">
         <f>計算表!F43</f>
-        <v>a=吸血上限（%）；0＝無上限。2026-07-30 改版：吸血不再擋上限、也不再以造成的傷害計算，每次回復 = 每秒生命回復 × 吸血%。</v>
+        <v>a=吸血上限（定值）；0＝無上限。吸血是定值：每次對敵人造成傷害固定回復的生命（舊版百分比以 1%＝1 轉換），單獨計算，與每秒生命回復、造成的傷害皆無關。</v>
       </c>
       <c r="G43">
         <f>計算表!G43</f>
@@ -7650,7 +7652,7 @@
       </c>
       <c r="F44" t="str">
         <f>計算表!F44</f>
-        <v>a=吸魔上限（%）；0＝無上限。2026-07-30 改版：吸魔不再擋上限、也不再以造成的傷害計算，每次回復 = 每秒法力恢復 × 吸魔%。</v>
+        <v>a=吸魔上限（定值）；0＝無上限。吸魔是定值：每次對敵人造成傷害固定回復的法力（舊版百分比以 1%＝1 轉換），單獨計算，與每秒法力恢復、造成的傷害皆無關。</v>
       </c>
       <c r="G44">
         <f>計算表!G44</f>
@@ -8841,7 +8843,7 @@
         <v>5</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="I60">
         <f>計算表!I60</f>
@@ -9210,7 +9212,7 @@
         <v>5</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="I65">
         <f>計算表!I65</f>
@@ -9283,7 +9285,7 @@
         <v>0.875</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="I66">
         <f>計算表!I66</f>
@@ -9574,7 +9576,7 @@
         <v>a=每點敏捷%。</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="H70">
         <f>計算表!H70</f>
@@ -11493,7 +11495,7 @@
         <v>忽略敵人防禦% = 穿透%/(穿透%+a)</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="G96">
         <f>計算表!G96</f>
@@ -13280,7 +13282,7 @@
         <v>0.5</v>
       </c>
       <c r="I120" s="7" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="J120">
         <f>計算表!J120</f>
@@ -15195,7 +15197,7 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條。</v>
       </c>
       <c r="G146" s="7" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="H146">
         <f>計算表!H146</f>
@@ -15268,13 +15270,13 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條。</v>
       </c>
       <c r="G147" s="7" t="s">
+        <v>1031</v>
+      </c>
+      <c r="H147" s="7" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I147" s="7" t="s">
         <v>1033</v>
-      </c>
-      <c r="H147" s="7" t="s">
-        <v>1034</v>
-      </c>
-      <c r="I147" s="7" t="s">
-        <v>1035</v>
       </c>
       <c r="J147">
         <f>計算表!J147</f>
@@ -15339,20 +15341,20 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條。</v>
       </c>
       <c r="G148" s="7" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="H148" s="7" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="I148">
         <f>計算表!I148</f>
         <v>9.11754</v>
       </c>
       <c r="J148" s="7" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="K148" s="7" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="L148">
         <f>計算表!L148</f>
@@ -15409,22 +15411,22 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條。</v>
       </c>
       <c r="G149" s="7" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H149" s="7" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I149" s="7" t="s">
         <v>1040</v>
       </c>
-      <c r="H149" s="7" t="s">
+      <c r="J149" s="7" t="s">
         <v>1041</v>
       </c>
-      <c r="I149" s="7" t="s">
+      <c r="K149" s="7" t="s">
         <v>1042</v>
       </c>
-      <c r="J149" s="7" t="s">
+      <c r="L149" s="7" t="s">
         <v>1043</v>
-      </c>
-      <c r="K149" s="7" t="s">
-        <v>1044</v>
-      </c>
-      <c r="L149" s="7" t="s">
-        <v>1045</v>
       </c>
       <c r="M149">
         <f>計算表!M149</f>
@@ -15477,28 +15479,28 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條。</v>
       </c>
       <c r="G150" s="7" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H150" s="7" t="s">
+        <v>1045</v>
+      </c>
+      <c r="I150" s="7" t="s">
         <v>1046</v>
       </c>
-      <c r="H150" s="7" t="s">
+      <c r="J150" s="7" t="s">
         <v>1047</v>
       </c>
-      <c r="I150" s="7" t="s">
+      <c r="K150" s="7" t="s">
         <v>1048</v>
       </c>
-      <c r="J150" s="7" t="s">
+      <c r="L150" s="7" t="s">
         <v>1049</v>
       </c>
-      <c r="K150" s="7" t="s">
+      <c r="M150" s="7" t="s">
         <v>1050</v>
       </c>
-      <c r="L150" s="7" t="s">
+      <c r="N150" s="7" t="s">
         <v>1051</v>
-      </c>
-      <c r="M150" s="7" t="s">
-        <v>1052</v>
-      </c>
-      <c r="N150" s="7" t="s">
-        <v>1053</v>
       </c>
       <c r="O150">
         <f>計算表!O150</f>
@@ -15543,28 +15545,28 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條。</v>
       </c>
       <c r="G151" s="7" t="s">
+        <v>1052</v>
+      </c>
+      <c r="H151" s="7" t="s">
+        <v>1053</v>
+      </c>
+      <c r="I151" s="7" t="s">
         <v>1054</v>
       </c>
-      <c r="H151" s="7" t="s">
+      <c r="J151" s="7" t="s">
         <v>1055</v>
       </c>
-      <c r="I151" s="7" t="s">
+      <c r="K151" s="7" t="s">
         <v>1056</v>
       </c>
-      <c r="J151" s="7" t="s">
+      <c r="L151" s="7" t="s">
         <v>1057</v>
       </c>
-      <c r="K151" s="7" t="s">
+      <c r="M151" s="7" t="s">
         <v>1058</v>
       </c>
-      <c r="L151" s="7" t="s">
+      <c r="N151" s="7" t="s">
         <v>1059</v>
-      </c>
-      <c r="M151" s="7" t="s">
-        <v>1060</v>
-      </c>
-      <c r="N151" s="7" t="s">
-        <v>1061</v>
       </c>
       <c r="O151">
         <f>計算表!O151</f>
@@ -15609,31 +15611,31 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條 j=9條。</v>
       </c>
       <c r="G152" s="7" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H152" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="I152" s="7" t="s">
         <v>1062</v>
       </c>
-      <c r="H152" s="7" t="s">
+      <c r="J152" s="7" t="s">
         <v>1063</v>
       </c>
-      <c r="I152" s="7" t="s">
+      <c r="K152" s="7" t="s">
         <v>1064</v>
       </c>
-      <c r="J152" s="7" t="s">
+      <c r="L152" s="7" t="s">
         <v>1065</v>
       </c>
-      <c r="K152" s="7" t="s">
+      <c r="M152" s="7" t="s">
         <v>1066</v>
       </c>
-      <c r="L152" s="7" t="s">
+      <c r="N152" s="7" t="s">
         <v>1067</v>
       </c>
-      <c r="M152" s="7" t="s">
+      <c r="O152" s="7" t="s">
         <v>1068</v>
-      </c>
-      <c r="N152" s="7" t="s">
-        <v>1069</v>
-      </c>
-      <c r="O152" s="7" t="s">
-        <v>1070</v>
       </c>
       <c r="P152">
         <f>計算表!P152</f>
@@ -15674,7 +15676,7 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條 j=9條 k=10條。</v>
       </c>
       <c r="G153" s="7" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="H153">
         <f>計算表!H153</f>
@@ -17157,7 +17159,7 @@
         <v>200</v>
       </c>
       <c r="H173" s="7" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="I173">
         <f>計算表!I173</f>
@@ -17744,7 +17746,7 @@
         <v>a=基礎權重 b=權重加成 c=加成上限 d=出現門檻。普通無加成。神鑄創世不參與此擲骰。(裝備合成才有作用，目前功能關閉中)</v>
       </c>
       <c r="G181" s="7" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="H181" t="str">
         <f>計算表!H181</f>
@@ -20563,7 +20565,7 @@
         <v>1</v>
       </c>
       <c r="I219" s="7" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="J219">
         <f>計算表!J220</f>
@@ -25578,10 +25580,10 @@
         <v>等級上限</v>
       </c>
       <c r="E287" s="7" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="F287" s="7" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="G287">
         <f>計算表!G291</f>
@@ -27212,7 +27214,7 @@
         <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數。</v>
       </c>
       <c r="G309" s="7" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="H309">
         <f>計算表!H325</f>
@@ -27581,7 +27583,7 @@
         <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數。</v>
       </c>
       <c r="G314" s="7" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="H314">
         <f>計算表!H330</f>
@@ -27859,16 +27861,16 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
+        <v>954</v>
+      </c>
+      <c r="D2" t="s">
+        <v>955</v>
+      </c>
+      <c r="E2" t="s">
         <v>956</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>957</v>
-      </c>
-      <c r="E2" t="s">
-        <v>958</v>
-      </c>
-      <c r="F2" t="s">
-        <v>959</v>
       </c>
       <c r="G2">
         <v>50000</v>
@@ -27916,16 +27918,16 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
+        <v>954</v>
+      </c>
+      <c r="D3" t="s">
+        <v>958</v>
+      </c>
+      <c r="E3" t="s">
         <v>956</v>
       </c>
-      <c r="D3" t="s">
-        <v>960</v>
-      </c>
-      <c r="E3" t="s">
-        <v>958</v>
-      </c>
       <c r="F3" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="G3">
         <v>500</v>
@@ -27973,16 +27975,16 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
+        <v>954</v>
+      </c>
+      <c r="D4" t="s">
+        <v>960</v>
+      </c>
+      <c r="E4" t="s">
         <v>956</v>
       </c>
-      <c r="D4" t="s">
-        <v>962</v>
-      </c>
-      <c r="E4" t="s">
-        <v>958</v>
-      </c>
       <c r="F4" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -28030,16 +28032,16 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
+        <v>847</v>
+      </c>
+      <c r="D5" t="s">
+        <v>848</v>
+      </c>
+      <c r="E5" t="s">
         <v>849</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>850</v>
-      </c>
-      <c r="E5" t="s">
-        <v>851</v>
-      </c>
-      <c r="F5" t="s">
-        <v>852</v>
       </c>
       <c r="G5">
         <v>24</v>
@@ -28087,16 +28089,16 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="D6" t="s">
+        <v>851</v>
+      </c>
+      <c r="E6" t="s">
+        <v>852</v>
+      </c>
+      <c r="F6" t="s">
         <v>853</v>
-      </c>
-      <c r="E6" t="s">
-        <v>854</v>
-      </c>
-      <c r="F6" t="s">
-        <v>855</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -28144,16 +28146,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="D7" t="s">
+        <v>854</v>
+      </c>
+      <c r="E7" t="s">
+        <v>855</v>
+      </c>
+      <c r="F7" t="s">
         <v>856</v>
-      </c>
-      <c r="E7" t="s">
-        <v>857</v>
-      </c>
-      <c r="F7" t="s">
-        <v>858</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -28201,16 +28203,16 @@
         <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="D8" t="s">
+        <v>857</v>
+      </c>
+      <c r="E8" t="s">
+        <v>858</v>
+      </c>
+      <c r="F8" t="s">
         <v>859</v>
-      </c>
-      <c r="E8" t="s">
-        <v>860</v>
-      </c>
-      <c r="F8" t="s">
-        <v>861</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -28603,13 +28605,13 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
+        <v>928</v>
+      </c>
+      <c r="E15" t="s">
+        <v>929</v>
+      </c>
+      <c r="F15" t="s">
         <v>930</v>
-      </c>
-      <c r="E15" t="s">
-        <v>931</v>
-      </c>
-      <c r="F15" t="s">
-        <v>932</v>
       </c>
       <c r="G15">
         <v>30</v>
@@ -28660,13 +28662,13 @@
         <v>18</v>
       </c>
       <c r="D16" t="s">
+        <v>931</v>
+      </c>
+      <c r="E16" t="s">
+        <v>932</v>
+      </c>
+      <c r="F16" t="s">
         <v>933</v>
-      </c>
-      <c r="E16" t="s">
-        <v>934</v>
-      </c>
-      <c r="F16" t="s">
-        <v>935</v>
       </c>
       <c r="G16">
         <v>1000</v>
@@ -30204,8 +30206,8 @@
       <c r="E43" t="s">
         <v>151</v>
       </c>
-      <c r="F43" t="s">
-        <v>162</v>
+      <c r="F43" s="7" t="s">
+        <v>1077</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -30256,13 +30258,13 @@
         <v>149</v>
       </c>
       <c r="D44" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E44" t="s">
         <v>151</v>
       </c>
-      <c r="F44" t="s">
-        <v>164</v>
+      <c r="F44" s="7" t="s">
+        <v>1078</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -30313,13 +30315,13 @@
         <v>149</v>
       </c>
       <c r="D45" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E45" t="s">
         <v>151</v>
       </c>
       <c r="F45" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G45">
         <v>50</v>
@@ -30370,13 +30372,13 @@
         <v>149</v>
       </c>
       <c r="D46" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E46" t="s">
         <v>151</v>
       </c>
       <c r="F46" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G46">
         <v>50</v>
@@ -30427,13 +30429,13 @@
         <v>149</v>
       </c>
       <c r="D47" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E47" t="s">
         <v>151</v>
       </c>
       <c r="F47" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -30484,13 +30486,13 @@
         <v>149</v>
       </c>
       <c r="D48" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E48" t="s">
         <v>151</v>
       </c>
       <c r="F48" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G48">
         <v>80</v>
@@ -30541,13 +30543,13 @@
         <v>149</v>
       </c>
       <c r="D49" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E49" t="s">
         <v>151</v>
       </c>
       <c r="F49" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G49">
         <v>80</v>
@@ -30598,13 +30600,13 @@
         <v>149</v>
       </c>
       <c r="D50" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E50" t="s">
         <v>151</v>
       </c>
       <c r="F50" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G50">
         <v>60</v>
@@ -30655,13 +30657,13 @@
         <v>149</v>
       </c>
       <c r="D51" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E51" t="s">
         <v>151</v>
       </c>
       <c r="F51" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G51">
         <v>50</v>
@@ -30712,13 +30714,13 @@
         <v>149</v>
       </c>
       <c r="D52" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E52" t="s">
         <v>151</v>
       </c>
       <c r="F52" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -30769,13 +30771,13 @@
         <v>149</v>
       </c>
       <c r="D53" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E53" t="s">
         <v>151</v>
       </c>
       <c r="F53" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G53">
         <v>60</v>
@@ -30826,13 +30828,13 @@
         <v>149</v>
       </c>
       <c r="D54" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E54" t="s">
         <v>151</v>
       </c>
       <c r="F54" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G54">
         <v>30</v>
@@ -30883,13 +30885,13 @@
         <v>149</v>
       </c>
       <c r="D55" t="s">
+        <v>183</v>
+      </c>
+      <c r="E55" t="s">
+        <v>184</v>
+      </c>
+      <c r="F55" t="s">
         <v>185</v>
-      </c>
-      <c r="E55" t="s">
-        <v>186</v>
-      </c>
-      <c r="F55" t="s">
-        <v>187</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -30940,13 +30942,13 @@
         <v>149</v>
       </c>
       <c r="D56" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E56" t="s">
         <v>151</v>
       </c>
       <c r="F56" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G56">
         <v>45</v>
@@ -30997,13 +30999,13 @@
         <v>149</v>
       </c>
       <c r="D57" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E57" t="s">
         <v>151</v>
       </c>
       <c r="F57" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G57">
         <v>30</v>
@@ -31627,10 +31629,10 @@
         <v>134</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G68">
         <v>0.86</v>
@@ -31963,16 +31965,16 @@
         <v>0</v>
       </c>
       <c r="C74" t="s">
+        <v>237</v>
+      </c>
+      <c r="D74" t="s">
+        <v>238</v>
+      </c>
+      <c r="E74" t="s">
         <v>239</v>
       </c>
-      <c r="D74" t="s">
+      <c r="F74" t="s">
         <v>240</v>
-      </c>
-      <c r="E74" t="s">
-        <v>241</v>
-      </c>
-      <c r="F74" t="s">
-        <v>242</v>
       </c>
       <c r="G74">
         <v>15</v>
@@ -32020,16 +32022,16 @@
         <v>0</v>
       </c>
       <c r="C75" t="s">
+        <v>237</v>
+      </c>
+      <c r="D75" t="s">
+        <v>241</v>
+      </c>
+      <c r="E75" t="s">
         <v>239</v>
       </c>
-      <c r="D75" t="s">
-        <v>243</v>
-      </c>
-      <c r="E75" t="s">
-        <v>241</v>
-      </c>
       <c r="F75" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G75">
         <v>10</v>
@@ -32077,16 +32079,16 @@
         <v>0</v>
       </c>
       <c r="C76" t="s">
+        <v>237</v>
+      </c>
+      <c r="D76" t="s">
+        <v>243</v>
+      </c>
+      <c r="E76" t="s">
         <v>239</v>
       </c>
-      <c r="D76" t="s">
-        <v>245</v>
-      </c>
-      <c r="E76" t="s">
-        <v>241</v>
-      </c>
       <c r="F76" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G76">
         <v>25</v>
@@ -32134,16 +32136,16 @@
         <v>0</v>
       </c>
       <c r="C77" t="s">
+        <v>237</v>
+      </c>
+      <c r="D77" t="s">
+        <v>245</v>
+      </c>
+      <c r="E77" t="s">
         <v>239</v>
       </c>
-      <c r="D77" t="s">
-        <v>247</v>
-      </c>
-      <c r="E77" t="s">
-        <v>241</v>
-      </c>
       <c r="F77" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G77">
         <v>20</v>
@@ -32191,16 +32193,16 @@
         <v>0</v>
       </c>
       <c r="C78" t="s">
+        <v>237</v>
+      </c>
+      <c r="D78" t="s">
+        <v>247</v>
+      </c>
+      <c r="E78" t="s">
         <v>239</v>
       </c>
-      <c r="D78" t="s">
-        <v>249</v>
-      </c>
-      <c r="E78" t="s">
-        <v>241</v>
-      </c>
       <c r="F78" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G78">
         <v>100</v>
@@ -32248,16 +32250,16 @@
         <v>0</v>
       </c>
       <c r="C79" t="s">
+        <v>190</v>
+      </c>
+      <c r="D79" t="s">
+        <v>191</v>
+      </c>
+      <c r="E79" t="s">
         <v>192</v>
       </c>
-      <c r="D79" t="s">
+      <c r="F79" t="s">
         <v>193</v>
-      </c>
-      <c r="E79" t="s">
-        <v>194</v>
-      </c>
-      <c r="F79" t="s">
-        <v>195</v>
       </c>
       <c r="G79">
         <v>10000</v>
@@ -32305,16 +32307,16 @@
         <v>0</v>
       </c>
       <c r="C80" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D80" t="s">
+        <v>194</v>
+      </c>
+      <c r="E80" t="s">
+        <v>195</v>
+      </c>
+      <c r="F80" t="s">
         <v>196</v>
-      </c>
-      <c r="E80" t="s">
-        <v>197</v>
-      </c>
-      <c r="F80" t="s">
-        <v>198</v>
       </c>
       <c r="G80">
         <v>0.95</v>
@@ -32362,16 +32364,16 @@
         <v>0</v>
       </c>
       <c r="C81" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D81" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E81" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F81" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G81">
         <v>0.95</v>
@@ -32419,16 +32421,16 @@
         <v>0</v>
       </c>
       <c r="C82" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D82" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E82" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F82" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G82">
         <v>0.95</v>
@@ -32476,16 +32478,16 @@
         <v>0</v>
       </c>
       <c r="C83" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D83" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E83" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F83" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G83">
         <v>0.95</v>
@@ -32533,16 +32535,16 @@
         <v>0</v>
       </c>
       <c r="C84" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D84" t="s">
+        <v>202</v>
+      </c>
+      <c r="E84" t="s">
+        <v>203</v>
+      </c>
+      <c r="F84" t="s">
         <v>204</v>
-      </c>
-      <c r="E84" t="s">
-        <v>205</v>
-      </c>
-      <c r="F84" t="s">
-        <v>206</v>
       </c>
       <c r="G84">
         <v>0.8</v>
@@ -32590,16 +32592,16 @@
         <v>0</v>
       </c>
       <c r="C85" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D85" t="s">
+        <v>205</v>
+      </c>
+      <c r="E85" t="s">
+        <v>206</v>
+      </c>
+      <c r="F85" t="s">
         <v>207</v>
-      </c>
-      <c r="E85" t="s">
-        <v>208</v>
-      </c>
-      <c r="F85" t="s">
-        <v>209</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -32647,16 +32649,16 @@
         <v>0</v>
       </c>
       <c r="C86" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D86" t="s">
+        <v>208</v>
+      </c>
+      <c r="E86" t="s">
+        <v>209</v>
+      </c>
+      <c r="F86" t="s">
         <v>210</v>
-      </c>
-      <c r="E86" t="s">
-        <v>211</v>
-      </c>
-      <c r="F86" t="s">
-        <v>212</v>
       </c>
       <c r="G86">
         <v>0.7</v>
@@ -32704,16 +32706,16 @@
         <v>0</v>
       </c>
       <c r="C87" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D87" t="s">
+        <v>211</v>
+      </c>
+      <c r="E87" t="s">
+        <v>212</v>
+      </c>
+      <c r="F87" t="s">
         <v>213</v>
-      </c>
-      <c r="E87" t="s">
-        <v>214</v>
-      </c>
-      <c r="F87" t="s">
-        <v>215</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -32761,16 +32763,16 @@
         <v>0</v>
       </c>
       <c r="C88" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D88" t="s">
+        <v>214</v>
+      </c>
+      <c r="E88" t="s">
+        <v>215</v>
+      </c>
+      <c r="F88" t="s">
         <v>216</v>
-      </c>
-      <c r="E88" t="s">
-        <v>217</v>
-      </c>
-      <c r="F88" t="s">
-        <v>218</v>
       </c>
       <c r="G88">
         <v>12</v>
@@ -32818,16 +32820,16 @@
         <v>0</v>
       </c>
       <c r="C89" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D89" t="s">
+        <v>217</v>
+      </c>
+      <c r="E89" t="s">
+        <v>218</v>
+      </c>
+      <c r="F89" t="s">
         <v>219</v>
-      </c>
-      <c r="E89" t="s">
-        <v>220</v>
-      </c>
-      <c r="F89" t="s">
-        <v>221</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -32875,16 +32877,16 @@
         <v>0</v>
       </c>
       <c r="C90" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D90" t="s">
+        <v>220</v>
+      </c>
+      <c r="E90" t="s">
+        <v>221</v>
+      </c>
+      <c r="F90" t="s">
         <v>222</v>
-      </c>
-      <c r="E90" t="s">
-        <v>223</v>
-      </c>
-      <c r="F90" t="s">
-        <v>224</v>
       </c>
       <c r="G90">
         <v>10</v>
@@ -32932,16 +32934,16 @@
         <v>0</v>
       </c>
       <c r="C91" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D91" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E91" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F91" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G91">
         <v>1000</v>
@@ -32989,16 +32991,16 @@
         <v>0</v>
       </c>
       <c r="C92" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D92" t="s">
+        <v>225</v>
+      </c>
+      <c r="E92" t="s">
+        <v>226</v>
+      </c>
+      <c r="F92" t="s">
         <v>227</v>
-      </c>
-      <c r="E92" t="s">
-        <v>228</v>
-      </c>
-      <c r="F92" t="s">
-        <v>229</v>
       </c>
       <c r="G92">
         <v>50</v>
@@ -33046,16 +33048,16 @@
         <v>0</v>
       </c>
       <c r="C93" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D93" t="s">
+        <v>228</v>
+      </c>
+      <c r="E93" t="s">
+        <v>229</v>
+      </c>
+      <c r="F93" t="s">
         <v>230</v>
-      </c>
-      <c r="E93" t="s">
-        <v>231</v>
-      </c>
-      <c r="F93" t="s">
-        <v>232</v>
       </c>
       <c r="G93">
         <v>30</v>
@@ -33103,16 +33105,16 @@
         <v>0</v>
       </c>
       <c r="C94" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D94" t="s">
+        <v>231</v>
+      </c>
+      <c r="E94" t="s">
+        <v>232</v>
+      </c>
+      <c r="F94" t="s">
         <v>233</v>
-      </c>
-      <c r="E94" t="s">
-        <v>234</v>
-      </c>
-      <c r="F94" t="s">
-        <v>235</v>
       </c>
       <c r="G94">
         <v>100</v>
@@ -33160,16 +33162,16 @@
         <v>0</v>
       </c>
       <c r="C95" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D95" t="s">
+        <v>234</v>
+      </c>
+      <c r="E95" t="s">
+        <v>235</v>
+      </c>
+      <c r="F95" t="s">
         <v>236</v>
-      </c>
-      <c r="E95" t="s">
-        <v>237</v>
-      </c>
-      <c r="F95" t="s">
-        <v>238</v>
       </c>
       <c r="G95">
         <v>5</v>
@@ -33217,16 +33219,16 @@
         <v>0</v>
       </c>
       <c r="C96" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D96" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>963</v>
+      </c>
+      <c r="F96" s="2" t="s">
         <v>964</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>965</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>966</v>
       </c>
       <c r="G96">
         <v>0.75</v>
@@ -33274,16 +33276,16 @@
         <v>0</v>
       </c>
       <c r="C97" t="s">
+        <v>318</v>
+      </c>
+      <c r="D97" t="s">
+        <v>319</v>
+      </c>
+      <c r="E97" t="s">
         <v>320</v>
       </c>
-      <c r="D97" t="s">
+      <c r="F97" t="s">
         <v>321</v>
-      </c>
-      <c r="E97" t="s">
-        <v>322</v>
-      </c>
-      <c r="F97" t="s">
-        <v>323</v>
       </c>
       <c r="G97">
         <v>4</v>
@@ -33331,16 +33333,16 @@
         <v>0</v>
       </c>
       <c r="C98" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D98" t="s">
+        <v>322</v>
+      </c>
+      <c r="E98" t="s">
+        <v>323</v>
+      </c>
+      <c r="F98" t="s">
         <v>324</v>
-      </c>
-      <c r="E98" t="s">
-        <v>325</v>
-      </c>
-      <c r="F98" t="s">
-        <v>326</v>
       </c>
       <c r="G98">
         <v>3</v>
@@ -33388,16 +33390,16 @@
         <v>0</v>
       </c>
       <c r="C99" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D99" t="s">
         <v>135</v>
       </c>
       <c r="E99" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F99" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G99">
         <v>200</v>
@@ -33445,25 +33447,25 @@
         <v>0</v>
       </c>
       <c r="C100" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D100" t="s">
+        <v>327</v>
+      </c>
+      <c r="E100" t="s">
+        <v>328</v>
+      </c>
+      <c r="F100" t="s">
         <v>329</v>
       </c>
-      <c r="E100" t="s">
+      <c r="G100" t="s">
         <v>330</v>
       </c>
-      <c r="F100" t="s">
+      <c r="H100" t="s">
         <v>331</v>
       </c>
-      <c r="G100" t="s">
+      <c r="I100" t="s">
         <v>332</v>
-      </c>
-      <c r="H100" t="s">
-        <v>333</v>
-      </c>
-      <c r="I100" t="s">
-        <v>334</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -33502,16 +33504,16 @@
         <v>0</v>
       </c>
       <c r="C101" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D101" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E101" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F101" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G101">
         <v>20</v>
@@ -33559,16 +33561,16 @@
         <v>0</v>
       </c>
       <c r="C102" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D102" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E102" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F102" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="G102">
         <v>3</v>
@@ -33616,16 +33618,16 @@
         <v>0</v>
       </c>
       <c r="C103" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D103" t="s">
+        <v>337</v>
+      </c>
+      <c r="E103" t="s">
+        <v>338</v>
+      </c>
+      <c r="F103" t="s">
         <v>339</v>
-      </c>
-      <c r="E103" t="s">
-        <v>340</v>
-      </c>
-      <c r="F103" t="s">
-        <v>341</v>
       </c>
       <c r="G103">
         <v>10</v>
@@ -33673,16 +33675,16 @@
         <v>0</v>
       </c>
       <c r="C104" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D104" t="s">
+        <v>340</v>
+      </c>
+      <c r="E104" t="s">
+        <v>341</v>
+      </c>
+      <c r="F104" t="s">
         <v>342</v>
-      </c>
-      <c r="E104" t="s">
-        <v>343</v>
-      </c>
-      <c r="F104" t="s">
-        <v>344</v>
       </c>
       <c r="G104">
         <v>3</v>
@@ -33730,16 +33732,16 @@
         <v>0</v>
       </c>
       <c r="C105" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D105" t="s">
         <v>138</v>
       </c>
       <c r="E105" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F105" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G105">
         <v>8</v>
@@ -33787,16 +33789,16 @@
         <v>0</v>
       </c>
       <c r="C106" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D106" t="s">
+        <v>345</v>
+      </c>
+      <c r="E106" t="s">
+        <v>346</v>
+      </c>
+      <c r="F106" t="s">
         <v>347</v>
-      </c>
-      <c r="E106" t="s">
-        <v>348</v>
-      </c>
-      <c r="F106" t="s">
-        <v>349</v>
       </c>
       <c r="G106">
         <v>3</v>
@@ -33844,16 +33846,16 @@
         <v>0</v>
       </c>
       <c r="C107" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D107" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="E107" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F107" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G107">
         <v>2</v>
@@ -33901,16 +33903,16 @@
         <v>0</v>
       </c>
       <c r="C108" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D108" t="s">
+        <v>350</v>
+      </c>
+      <c r="E108" t="s">
+        <v>351</v>
+      </c>
+      <c r="F108" t="s">
         <v>352</v>
-      </c>
-      <c r="E108" t="s">
-        <v>353</v>
-      </c>
-      <c r="F108" t="s">
-        <v>354</v>
       </c>
       <c r="G108">
         <v>60</v>
@@ -33958,16 +33960,16 @@
         <v>0</v>
       </c>
       <c r="C109" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D109" t="s">
+        <v>353</v>
+      </c>
+      <c r="E109" t="s">
+        <v>354</v>
+      </c>
+      <c r="F109" t="s">
         <v>355</v>
-      </c>
-      <c r="E109" t="s">
-        <v>356</v>
-      </c>
-      <c r="F109" t="s">
-        <v>357</v>
       </c>
       <c r="G109">
         <v>51</v>
@@ -34015,16 +34017,16 @@
         <v>0</v>
       </c>
       <c r="C110" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D110" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E110" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F110" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G110">
         <v>1</v>
@@ -34072,16 +34074,16 @@
         <v>0</v>
       </c>
       <c r="C111" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D111" t="s">
+        <v>358</v>
+      </c>
+      <c r="E111" t="s">
+        <v>359</v>
+      </c>
+      <c r="F111" t="s">
         <v>360</v>
-      </c>
-      <c r="E111" t="s">
-        <v>361</v>
-      </c>
-      <c r="F111" t="s">
-        <v>362</v>
       </c>
       <c r="G111">
         <v>5</v>
@@ -34129,16 +34131,16 @@
         <v>0</v>
       </c>
       <c r="C112" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D112" t="s">
+        <v>361</v>
+      </c>
+      <c r="E112" t="s">
+        <v>362</v>
+      </c>
+      <c r="F112" t="s">
         <v>363</v>
-      </c>
-      <c r="E112" t="s">
-        <v>364</v>
-      </c>
-      <c r="F112" t="s">
-        <v>365</v>
       </c>
       <c r="G112">
         <v>100</v>
@@ -34186,16 +34188,16 @@
         <v>0</v>
       </c>
       <c r="C113" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D113" t="s">
+        <v>364</v>
+      </c>
+      <c r="E113" t="s">
+        <v>365</v>
+      </c>
+      <c r="F113" t="s">
         <v>366</v>
-      </c>
-      <c r="E113" t="s">
-        <v>367</v>
-      </c>
-      <c r="F113" t="s">
-        <v>368</v>
       </c>
       <c r="G113">
         <v>30</v>
@@ -34243,25 +34245,25 @@
         <v>0</v>
       </c>
       <c r="C114" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D114" t="s">
+        <v>367</v>
+      </c>
+      <c r="E114" t="s">
+        <v>368</v>
+      </c>
+      <c r="F114" t="s">
+        <v>357</v>
+      </c>
+      <c r="G114" t="s">
         <v>369</v>
       </c>
-      <c r="E114" t="s">
+      <c r="H114" t="s">
         <v>370</v>
       </c>
-      <c r="F114" t="s">
-        <v>359</v>
-      </c>
-      <c r="G114" t="s">
+      <c r="I114" t="s">
         <v>371</v>
-      </c>
-      <c r="H114" t="s">
-        <v>372</v>
-      </c>
-      <c r="I114" t="s">
-        <v>373</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -34300,16 +34302,16 @@
         <v>0</v>
       </c>
       <c r="C115" t="s">
+        <v>308</v>
+      </c>
+      <c r="D115" t="s">
+        <v>309</v>
+      </c>
+      <c r="E115" t="s">
         <v>310</v>
       </c>
-      <c r="D115" t="s">
+      <c r="F115" t="s">
         <v>311</v>
-      </c>
-      <c r="E115" t="s">
-        <v>312</v>
-      </c>
-      <c r="F115" t="s">
-        <v>313</v>
       </c>
       <c r="G115">
         <v>50</v>
@@ -34357,16 +34359,16 @@
         <v>0</v>
       </c>
       <c r="C116" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D116" t="s">
+        <v>312</v>
+      </c>
+      <c r="E116" t="s">
+        <v>313</v>
+      </c>
+      <c r="F116" t="s">
         <v>314</v>
-      </c>
-      <c r="E116" t="s">
-        <v>315</v>
-      </c>
-      <c r="F116" t="s">
-        <v>316</v>
       </c>
       <c r="G116">
         <v>15</v>
@@ -34414,16 +34416,16 @@
         <v>0</v>
       </c>
       <c r="C117" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D117" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="E117" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F117" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G117">
         <v>3</v>
@@ -34471,16 +34473,16 @@
         <v>0</v>
       </c>
       <c r="C118" t="s">
+        <v>249</v>
+      </c>
+      <c r="D118" t="s">
+        <v>250</v>
+      </c>
+      <c r="E118" t="s">
         <v>251</v>
       </c>
-      <c r="D118" t="s">
+      <c r="F118" t="s">
         <v>252</v>
-      </c>
-      <c r="E118" t="s">
-        <v>253</v>
-      </c>
-      <c r="F118" t="s">
-        <v>254</v>
       </c>
       <c r="G118">
         <v>20</v>
@@ -34528,16 +34530,16 @@
         <v>0</v>
       </c>
       <c r="C119" t="s">
+        <v>249</v>
+      </c>
+      <c r="D119" t="s">
+        <v>253</v>
+      </c>
+      <c r="E119" t="s">
         <v>251</v>
       </c>
-      <c r="D119" t="s">
-        <v>255</v>
-      </c>
-      <c r="E119" t="s">
-        <v>253</v>
-      </c>
       <c r="F119" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G119">
         <v>2</v>
@@ -34585,16 +34587,16 @@
         <v>0</v>
       </c>
       <c r="C120" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D120" t="s">
         <v>119</v>
       </c>
       <c r="E120" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="F120" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G120">
         <v>2</v>
@@ -34642,16 +34644,16 @@
         <v>0</v>
       </c>
       <c r="C121" t="s">
+        <v>249</v>
+      </c>
+      <c r="D121" t="s">
+        <v>255</v>
+      </c>
+      <c r="E121" t="s">
         <v>251</v>
       </c>
-      <c r="D121" t="s">
-        <v>257</v>
-      </c>
-      <c r="E121" t="s">
-        <v>253</v>
-      </c>
       <c r="F121" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G121">
         <v>250</v>
@@ -34699,16 +34701,16 @@
         <v>0</v>
       </c>
       <c r="C122" t="s">
+        <v>249</v>
+      </c>
+      <c r="D122" t="s">
+        <v>256</v>
+      </c>
+      <c r="E122" t="s">
         <v>251</v>
       </c>
-      <c r="D122" t="s">
-        <v>258</v>
-      </c>
-      <c r="E122" t="s">
-        <v>253</v>
-      </c>
       <c r="F122" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G122">
         <v>120</v>
@@ -34756,16 +34758,16 @@
         <v>0</v>
       </c>
       <c r="C123" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D123" t="s">
         <v>134</v>
       </c>
       <c r="E123" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F123" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G123">
         <v>1</v>
@@ -34813,37 +34815,37 @@
         <v>0</v>
       </c>
       <c r="C124" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D124" t="s">
         <v>135</v>
       </c>
       <c r="E124" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F124" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G124">
         <v>100</v>
       </c>
       <c r="H124" t="s">
+        <v>261</v>
+      </c>
+      <c r="I124" t="s">
+        <v>262</v>
+      </c>
+      <c r="J124" t="s">
         <v>263</v>
       </c>
-      <c r="I124" t="s">
+      <c r="K124" t="s">
         <v>264</v>
       </c>
-      <c r="J124" t="s">
+      <c r="L124" t="s">
         <v>265</v>
       </c>
-      <c r="K124" t="s">
+      <c r="M124" t="s">
         <v>266</v>
-      </c>
-      <c r="L124" t="s">
-        <v>267</v>
-      </c>
-      <c r="M124" t="s">
-        <v>268</v>
       </c>
       <c r="N124">
         <v>0</v>
@@ -34870,37 +34872,37 @@
         <v>0</v>
       </c>
       <c r="C125" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D125" t="s">
         <v>138</v>
       </c>
       <c r="E125" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F125" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G125">
         <v>5</v>
       </c>
       <c r="H125" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="I125" t="s">
+        <v>268</v>
+      </c>
+      <c r="J125" t="s">
+        <v>269</v>
+      </c>
+      <c r="K125" t="s">
         <v>270</v>
       </c>
-      <c r="J125" t="s">
+      <c r="L125" t="s">
         <v>271</v>
       </c>
-      <c r="K125" t="s">
+      <c r="M125" t="s">
         <v>272</v>
-      </c>
-      <c r="L125" t="s">
-        <v>273</v>
-      </c>
-      <c r="M125" t="s">
-        <v>274</v>
       </c>
       <c r="N125">
         <v>0</v>
@@ -34927,16 +34929,16 @@
         <v>0</v>
       </c>
       <c r="C126" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D126" t="s">
+        <v>273</v>
+      </c>
+      <c r="E126" t="s">
+        <v>274</v>
+      </c>
+      <c r="F126" t="s">
         <v>275</v>
-      </c>
-      <c r="E126" t="s">
-        <v>276</v>
-      </c>
-      <c r="F126" t="s">
-        <v>277</v>
       </c>
       <c r="G126">
         <v>4</v>
@@ -34984,16 +34986,16 @@
         <v>0</v>
       </c>
       <c r="C127" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="E127" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F127" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G127">
         <v>1.5</v>
@@ -35041,22 +35043,22 @@
         <v>0</v>
       </c>
       <c r="C128" t="s">
+        <v>278</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>969</v>
+      </c>
+      <c r="E128" t="s">
+        <v>279</v>
+      </c>
+      <c r="F128" t="s">
         <v>280</v>
       </c>
-      <c r="D128" s="2" t="s">
-        <v>971</v>
-      </c>
-      <c r="E128" t="s">
+      <c r="G128" t="s">
         <v>281</v>
       </c>
-      <c r="F128" t="s">
+      <c r="H128" t="s">
         <v>282</v>
-      </c>
-      <c r="G128" t="s">
-        <v>283</v>
-      </c>
-      <c r="H128" t="s">
-        <v>284</v>
       </c>
       <c r="I128">
         <v>0</v>
@@ -35098,22 +35100,22 @@
         <v>0</v>
       </c>
       <c r="C129" t="s">
+        <v>278</v>
+      </c>
+      <c r="D129" t="s">
+        <v>965</v>
+      </c>
+      <c r="E129" t="s">
+        <v>279</v>
+      </c>
+      <c r="F129" t="s">
         <v>280</v>
       </c>
-      <c r="D129" t="s">
-        <v>967</v>
-      </c>
-      <c r="E129" t="s">
-        <v>281</v>
-      </c>
-      <c r="F129" t="s">
-        <v>282</v>
-      </c>
       <c r="G129" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H129" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="I129">
         <v>0</v>
@@ -35155,25 +35157,25 @@
         <v>0</v>
       </c>
       <c r="C130" t="s">
+        <v>278</v>
+      </c>
+      <c r="D130" t="s">
+        <v>966</v>
+      </c>
+      <c r="E130" t="s">
+        <v>279</v>
+      </c>
+      <c r="F130" t="s">
         <v>280</v>
       </c>
-      <c r="D130" t="s">
-        <v>968</v>
-      </c>
-      <c r="E130" t="s">
-        <v>281</v>
-      </c>
-      <c r="F130" t="s">
-        <v>282</v>
-      </c>
       <c r="G130" t="s">
+        <v>285</v>
+      </c>
+      <c r="H130" t="s">
+        <v>286</v>
+      </c>
+      <c r="I130" t="s">
         <v>287</v>
-      </c>
-      <c r="H130" t="s">
-        <v>288</v>
-      </c>
-      <c r="I130" t="s">
-        <v>289</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -35212,28 +35214,28 @@
         <v>0</v>
       </c>
       <c r="C131" t="s">
+        <v>278</v>
+      </c>
+      <c r="D131" t="s">
+        <v>967</v>
+      </c>
+      <c r="E131" t="s">
+        <v>279</v>
+      </c>
+      <c r="F131" t="s">
         <v>280</v>
       </c>
-      <c r="D131" t="s">
-        <v>969</v>
-      </c>
-      <c r="E131" t="s">
-        <v>281</v>
-      </c>
-      <c r="F131" t="s">
-        <v>282</v>
-      </c>
       <c r="G131" t="s">
+        <v>288</v>
+      </c>
+      <c r="H131" t="s">
+        <v>289</v>
+      </c>
+      <c r="I131" t="s">
         <v>290</v>
       </c>
-      <c r="H131" t="s">
+      <c r="J131" t="s">
         <v>291</v>
-      </c>
-      <c r="I131" t="s">
-        <v>292</v>
-      </c>
-      <c r="J131" t="s">
-        <v>293</v>
       </c>
       <c r="K131">
         <v>0</v>
@@ -35269,28 +35271,28 @@
         <v>0</v>
       </c>
       <c r="C132" t="s">
+        <v>278</v>
+      </c>
+      <c r="D132" t="s">
+        <v>968</v>
+      </c>
+      <c r="E132" t="s">
+        <v>279</v>
+      </c>
+      <c r="F132" t="s">
         <v>280</v>
       </c>
-      <c r="D132" t="s">
-        <v>970</v>
-      </c>
-      <c r="E132" t="s">
-        <v>281</v>
-      </c>
-      <c r="F132" t="s">
-        <v>282</v>
-      </c>
       <c r="G132" s="3" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="H132" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="I132" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="K132">
         <v>0</v>
@@ -35326,31 +35328,31 @@
         <v>0</v>
       </c>
       <c r="C133" t="s">
+        <v>278</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E133" t="s">
+        <v>279</v>
+      </c>
+      <c r="F133" t="s">
         <v>280</v>
       </c>
-      <c r="D133" s="2" t="s">
+      <c r="G133" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="I133" s="3" t="s">
         <v>1009</v>
       </c>
-      <c r="E133" t="s">
-        <v>281</v>
-      </c>
-      <c r="F133" t="s">
-        <v>282</v>
-      </c>
-      <c r="G133" s="3" t="s">
+      <c r="J133" s="3" t="s">
         <v>1012</v>
       </c>
-      <c r="H133" s="3" t="s">
+      <c r="K133" s="3" t="s">
         <v>1013</v>
-      </c>
-      <c r="I133" s="3" t="s">
-        <v>1011</v>
-      </c>
-      <c r="J133" s="3" t="s">
-        <v>1014</v>
-      </c>
-      <c r="K133" s="3" t="s">
-        <v>1015</v>
       </c>
       <c r="L133">
         <v>0</v>
@@ -35383,34 +35385,34 @@
         <v>0</v>
       </c>
       <c r="C134" t="s">
+        <v>278</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E134" t="s">
+        <v>279</v>
+      </c>
+      <c r="F134" t="s">
         <v>280</v>
       </c>
-      <c r="D134" s="2" t="s">
+      <c r="G134" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="J134" s="3" t="s">
         <v>1017</v>
       </c>
-      <c r="E134" t="s">
-        <v>281</v>
-      </c>
-      <c r="F134" t="s">
-        <v>282</v>
-      </c>
-      <c r="G134" s="3" t="s">
-        <v>1008</v>
-      </c>
-      <c r="H134" s="3" t="s">
-        <v>981</v>
-      </c>
-      <c r="I134" s="3" t="s">
-        <v>1018</v>
-      </c>
-      <c r="J134" s="3" t="s">
-        <v>1019</v>
-      </c>
       <c r="K134" s="3" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="M134">
         <v>0</v>
@@ -35440,22 +35442,22 @@
         <v>0</v>
       </c>
       <c r="C135" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="E135" t="s">
+        <v>279</v>
+      </c>
+      <c r="F135" t="s">
+        <v>294</v>
+      </c>
+      <c r="G135" t="s">
         <v>281</v>
       </c>
-      <c r="F135" t="s">
-        <v>296</v>
-      </c>
-      <c r="G135" t="s">
-        <v>283</v>
-      </c>
       <c r="H135" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I135">
         <v>0</v>
@@ -35497,25 +35499,25 @@
         <v>0</v>
       </c>
       <c r="C136" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="E136" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F136" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="J136">
         <v>0</v>
@@ -35554,31 +35556,31 @@
         <v>0</v>
       </c>
       <c r="C137" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="E137" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F137" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G137" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="H137" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="I137" s="3" t="s">
         <v>979</v>
       </c>
-      <c r="H137" s="3" t="s">
+      <c r="J137" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="K137" s="3" t="s">
         <v>980</v>
-      </c>
-      <c r="I137" s="3" t="s">
-        <v>981</v>
-      </c>
-      <c r="J137" s="3" t="s">
-        <v>983</v>
-      </c>
-      <c r="K137" s="3" t="s">
-        <v>982</v>
       </c>
       <c r="L137">
         <v>0</v>
@@ -35611,37 +35613,37 @@
         <v>0</v>
       </c>
       <c r="C138" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="E138" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F138" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="G138" s="3" t="s">
+        <v>992</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="I138" s="3" t="s">
         <v>994</v>
       </c>
-      <c r="H138" s="3" t="s">
+      <c r="J138" s="3" t="s">
         <v>995</v>
       </c>
-      <c r="I138" s="3" t="s">
+      <c r="K138" s="3" t="s">
         <v>996</v>
       </c>
-      <c r="J138" s="3" t="s">
+      <c r="L138" s="3" t="s">
         <v>997</v>
       </c>
-      <c r="K138" s="3" t="s">
+      <c r="M138" s="3" t="s">
         <v>998</v>
-      </c>
-      <c r="L138" s="3" t="s">
-        <v>999</v>
-      </c>
-      <c r="M138" s="3" t="s">
-        <v>1000</v>
       </c>
       <c r="N138">
         <v>0</v>
@@ -35668,37 +35670,37 @@
         <v>0</v>
       </c>
       <c r="C139" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D139" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="E139" t="s">
+        <v>279</v>
+      </c>
+      <c r="F139" t="s">
+        <v>294</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>985</v>
+      </c>
+      <c r="H139" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="I139" s="3" t="s">
         <v>984</v>
       </c>
-      <c r="E139" t="s">
-        <v>281</v>
-      </c>
-      <c r="F139" t="s">
-        <v>296</v>
-      </c>
-      <c r="G139" s="3" t="s">
+      <c r="J139" s="3" t="s">
         <v>987</v>
       </c>
-      <c r="H139" s="3" t="s">
+      <c r="K139" s="3" t="s">
         <v>988</v>
       </c>
-      <c r="I139" s="3" t="s">
-        <v>986</v>
-      </c>
-      <c r="J139" s="3" t="s">
+      <c r="L139" s="3" t="s">
         <v>989</v>
       </c>
-      <c r="K139" s="3" t="s">
+      <c r="M139" s="3" t="s">
         <v>990</v>
-      </c>
-      <c r="L139" s="3" t="s">
-        <v>991</v>
-      </c>
-      <c r="M139" s="3" t="s">
-        <v>992</v>
       </c>
       <c r="N139">
         <v>0</v>
@@ -35725,19 +35727,19 @@
         <v>0</v>
       </c>
       <c r="C140" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D140" t="s">
+        <v>295</v>
+      </c>
+      <c r="E140" t="s">
+        <v>279</v>
+      </c>
+      <c r="F140" t="s">
+        <v>296</v>
+      </c>
+      <c r="G140" t="s">
         <v>297</v>
-      </c>
-      <c r="E140" t="s">
-        <v>281</v>
-      </c>
-      <c r="F140" t="s">
-        <v>298</v>
-      </c>
-      <c r="G140" t="s">
-        <v>299</v>
       </c>
       <c r="H140">
         <v>0</v>
@@ -35782,16 +35784,16 @@
         <v>0</v>
       </c>
       <c r="C141" t="s">
+        <v>298</v>
+      </c>
+      <c r="D141" t="s">
+        <v>299</v>
+      </c>
+      <c r="E141" t="s">
         <v>300</v>
       </c>
-      <c r="D141" t="s">
+      <c r="F141" t="s">
         <v>301</v>
-      </c>
-      <c r="E141" t="s">
-        <v>302</v>
-      </c>
-      <c r="F141" t="s">
-        <v>303</v>
       </c>
       <c r="G141">
         <v>10</v>
@@ -35839,16 +35841,16 @@
         <v>0</v>
       </c>
       <c r="C142" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D142" t="s">
+        <v>302</v>
+      </c>
+      <c r="E142" t="s">
+        <v>303</v>
+      </c>
+      <c r="F142" t="s">
         <v>304</v>
-      </c>
-      <c r="E142" t="s">
-        <v>305</v>
-      </c>
-      <c r="F142" t="s">
-        <v>306</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -35896,16 +35898,16 @@
         <v>0</v>
       </c>
       <c r="C143" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D143" t="s">
+        <v>305</v>
+      </c>
+      <c r="E143" t="s">
+        <v>306</v>
+      </c>
+      <c r="F143" t="s">
         <v>307</v>
-      </c>
-      <c r="E143" t="s">
-        <v>308</v>
-      </c>
-      <c r="F143" t="s">
-        <v>309</v>
       </c>
       <c r="G143">
         <v>2</v>
@@ -35953,16 +35955,16 @@
         <v>0</v>
       </c>
       <c r="C144" t="s">
+        <v>402</v>
+      </c>
+      <c r="D144" t="s">
+        <v>403</v>
+      </c>
+      <c r="E144" t="s">
         <v>404</v>
       </c>
-      <c r="D144" t="s">
+      <c r="F144" t="s">
         <v>405</v>
-      </c>
-      <c r="E144" t="s">
-        <v>406</v>
-      </c>
-      <c r="F144" t="s">
-        <v>407</v>
       </c>
       <c r="G144">
         <v>100</v>
@@ -36010,16 +36012,16 @@
         <v>0</v>
       </c>
       <c r="C145" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D145" t="s">
+        <v>406</v>
+      </c>
+      <c r="E145" t="s">
+        <v>407</v>
+      </c>
+      <c r="F145" t="s">
         <v>408</v>
-      </c>
-      <c r="E145" t="s">
-        <v>409</v>
-      </c>
-      <c r="F145" t="s">
-        <v>410</v>
       </c>
       <c r="G145">
         <v>92</v>
@@ -36067,16 +36069,16 @@
         <v>0</v>
       </c>
       <c r="C146" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D146" t="s">
+        <v>409</v>
+      </c>
+      <c r="E146" t="s">
+        <v>410</v>
+      </c>
+      <c r="F146" t="s">
         <v>411</v>
-      </c>
-      <c r="E146" t="s">
-        <v>412</v>
-      </c>
-      <c r="F146" t="s">
-        <v>413</v>
       </c>
       <c r="G146">
         <v>78.100000000000009</v>
@@ -36124,16 +36126,16 @@
         <v>0</v>
       </c>
       <c r="C147" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D147" t="s">
+        <v>412</v>
+      </c>
+      <c r="E147" t="s">
+        <v>413</v>
+      </c>
+      <c r="F147" t="s">
         <v>414</v>
-      </c>
-      <c r="E147" t="s">
-        <v>415</v>
-      </c>
-      <c r="F147" t="s">
-        <v>416</v>
       </c>
       <c r="G147">
         <v>72.113600000000005</v>
@@ -36181,16 +36183,16 @@
         <v>0</v>
       </c>
       <c r="C148" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D148" t="s">
+        <v>415</v>
+      </c>
+      <c r="E148" t="s">
+        <v>416</v>
+      </c>
+      <c r="F148" t="s">
         <v>417</v>
-      </c>
-      <c r="E148" t="s">
-        <v>418</v>
-      </c>
-      <c r="F148" t="s">
-        <v>419</v>
       </c>
       <c r="G148">
         <v>53.837361999999999</v>
@@ -36238,16 +36240,16 @@
         <v>0</v>
       </c>
       <c r="C149" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D149" t="s">
+        <v>418</v>
+      </c>
+      <c r="E149" t="s">
+        <v>419</v>
+      </c>
+      <c r="F149" t="s">
         <v>420</v>
-      </c>
-      <c r="E149" t="s">
-        <v>421</v>
-      </c>
-      <c r="F149" t="s">
-        <v>422</v>
       </c>
       <c r="G149">
         <v>49.993825599999994</v>
@@ -36295,16 +36297,16 @@
         <v>0</v>
       </c>
       <c r="C150" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D150" t="s">
+        <v>421</v>
+      </c>
+      <c r="E150" t="s">
+        <v>422</v>
+      </c>
+      <c r="F150" t="s">
         <v>423</v>
-      </c>
-      <c r="E150" t="s">
-        <v>424</v>
-      </c>
-      <c r="F150" t="s">
-        <v>425</v>
       </c>
       <c r="G150">
         <v>36.76497232906253</v>
@@ -36352,16 +36354,16 @@
         <v>0</v>
       </c>
       <c r="C151" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D151" t="s">
+        <v>424</v>
+      </c>
+      <c r="E151" t="s">
+        <v>425</v>
+      </c>
+      <c r="F151" t="s">
         <v>426</v>
-      </c>
-      <c r="E151" t="s">
-        <v>427</v>
-      </c>
-      <c r="F151" t="s">
-        <v>428</v>
       </c>
       <c r="G151">
         <v>31.631675870386633</v>
@@ -36409,16 +36411,16 @@
         <v>0</v>
       </c>
       <c r="C152" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D152" t="s">
+        <v>427</v>
+      </c>
+      <c r="E152" t="s">
+        <v>428</v>
+      </c>
+      <c r="F152" t="s">
         <v>429</v>
-      </c>
-      <c r="E152" t="s">
-        <v>430</v>
-      </c>
-      <c r="F152" t="s">
-        <v>431</v>
       </c>
       <c r="G152">
         <v>25.407543428799851</v>
@@ -36466,16 +36468,16 @@
         <v>0</v>
       </c>
       <c r="C153" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D153" t="s">
+        <v>430</v>
+      </c>
+      <c r="E153" t="s">
+        <v>431</v>
+      </c>
+      <c r="F153" t="s">
         <v>432</v>
-      </c>
-      <c r="E153" t="s">
-        <v>433</v>
-      </c>
-      <c r="F153" t="s">
-        <v>434</v>
       </c>
       <c r="G153">
         <v>18.159999999999986</v>
@@ -36523,16 +36525,16 @@
         <v>0</v>
       </c>
       <c r="C154" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D154" t="s">
+        <v>433</v>
+      </c>
+      <c r="E154" t="s">
+        <v>434</v>
+      </c>
+      <c r="F154" t="s">
         <v>435</v>
-      </c>
-      <c r="E154" t="s">
-        <v>436</v>
-      </c>
-      <c r="F154" t="s">
-        <v>437</v>
       </c>
       <c r="G154">
         <v>1.35</v>
@@ -36580,16 +36582,16 @@
         <v>0</v>
       </c>
       <c r="C155" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D155" t="s">
+        <v>436</v>
+      </c>
+      <c r="E155" t="s">
+        <v>437</v>
+      </c>
+      <c r="F155" t="s">
         <v>438</v>
-      </c>
-      <c r="E155" t="s">
-        <v>439</v>
-      </c>
-      <c r="F155" t="s">
-        <v>440</v>
       </c>
       <c r="G155">
         <v>0.5</v>
@@ -36637,16 +36639,16 @@
         <v>0</v>
       </c>
       <c r="C156" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D156" t="s">
+        <v>439</v>
+      </c>
+      <c r="E156" t="s">
+        <v>440</v>
+      </c>
+      <c r="F156" t="s">
         <v>441</v>
-      </c>
-      <c r="E156" t="s">
-        <v>442</v>
-      </c>
-      <c r="F156" t="s">
-        <v>443</v>
       </c>
       <c r="G156">
         <v>4000</v>
@@ -36694,37 +36696,37 @@
         <v>0</v>
       </c>
       <c r="C157" t="s">
+        <v>457</v>
+      </c>
+      <c r="D157" t="s">
+        <v>458</v>
+      </c>
+      <c r="E157" t="s">
         <v>459</v>
       </c>
-      <c r="D157" t="s">
+      <c r="F157" t="s">
         <v>460</v>
       </c>
-      <c r="E157" t="s">
+      <c r="G157" t="s">
         <v>461</v>
       </c>
-      <c r="F157" t="s">
+      <c r="H157" t="s">
         <v>462</v>
       </c>
-      <c r="G157" t="s">
+      <c r="I157" t="s">
         <v>463</v>
       </c>
-      <c r="H157" t="s">
+      <c r="J157" t="s">
         <v>464</v>
       </c>
-      <c r="I157" t="s">
+      <c r="K157" t="s">
         <v>465</v>
       </c>
-      <c r="J157" t="s">
+      <c r="L157" t="s">
         <v>466</v>
       </c>
-      <c r="K157" t="s">
+      <c r="M157" t="s">
         <v>467</v>
-      </c>
-      <c r="L157" t="s">
-        <v>468</v>
-      </c>
-      <c r="M157" t="s">
-        <v>469</v>
       </c>
       <c r="N157">
         <v>0</v>
@@ -36751,37 +36753,37 @@
         <v>0</v>
       </c>
       <c r="C158" t="s">
+        <v>457</v>
+      </c>
+      <c r="D158" t="s">
+        <v>468</v>
+      </c>
+      <c r="E158" t="s">
         <v>459</v>
       </c>
-      <c r="D158" t="s">
-        <v>470</v>
-      </c>
-      <c r="E158" t="s">
+      <c r="F158" t="s">
+        <v>460</v>
+      </c>
+      <c r="G158" t="s">
         <v>461</v>
       </c>
-      <c r="F158" t="s">
+      <c r="H158" t="s">
         <v>462</v>
       </c>
-      <c r="G158" t="s">
+      <c r="I158" t="s">
         <v>463</v>
       </c>
-      <c r="H158" t="s">
+      <c r="J158" t="s">
         <v>464</v>
       </c>
-      <c r="I158" t="s">
+      <c r="K158" t="s">
         <v>465</v>
       </c>
-      <c r="J158" t="s">
+      <c r="L158" t="s">
         <v>466</v>
       </c>
-      <c r="K158" t="s">
+      <c r="M158" t="s">
         <v>467</v>
-      </c>
-      <c r="L158" t="s">
-        <v>468</v>
-      </c>
-      <c r="M158" t="s">
-        <v>469</v>
       </c>
       <c r="N158">
         <v>0</v>
@@ -36808,37 +36810,37 @@
         <v>0</v>
       </c>
       <c r="C159" t="s">
+        <v>457</v>
+      </c>
+      <c r="D159" t="s">
+        <v>469</v>
+      </c>
+      <c r="E159" t="s">
         <v>459</v>
       </c>
-      <c r="D159" t="s">
+      <c r="F159" t="s">
+        <v>460</v>
+      </c>
+      <c r="G159" t="s">
+        <v>470</v>
+      </c>
+      <c r="H159" t="s">
         <v>471</v>
       </c>
-      <c r="E159" t="s">
-        <v>461</v>
-      </c>
-      <c r="F159" t="s">
-        <v>462</v>
-      </c>
-      <c r="G159" t="s">
-        <v>472</v>
-      </c>
-      <c r="H159" t="s">
-        <v>473</v>
-      </c>
       <c r="I159" t="s">
+        <v>463</v>
+      </c>
+      <c r="J159" t="s">
+        <v>464</v>
+      </c>
+      <c r="K159" t="s">
         <v>465</v>
       </c>
-      <c r="J159" t="s">
+      <c r="L159" t="s">
         <v>466</v>
       </c>
-      <c r="K159" t="s">
+      <c r="M159" t="s">
         <v>467</v>
-      </c>
-      <c r="L159" t="s">
-        <v>468</v>
-      </c>
-      <c r="M159" t="s">
-        <v>469</v>
       </c>
       <c r="N159">
         <v>0</v>
@@ -36865,37 +36867,37 @@
         <v>0</v>
       </c>
       <c r="C160" t="s">
+        <v>457</v>
+      </c>
+      <c r="D160" t="s">
+        <v>472</v>
+      </c>
+      <c r="E160" t="s">
         <v>459</v>
       </c>
-      <c r="D160" t="s">
+      <c r="F160" t="s">
+        <v>460</v>
+      </c>
+      <c r="G160" t="s">
+        <v>473</v>
+      </c>
+      <c r="H160" t="s">
+        <v>471</v>
+      </c>
+      <c r="I160" t="s">
         <v>474</v>
       </c>
-      <c r="E160" t="s">
-        <v>461</v>
-      </c>
-      <c r="F160" t="s">
-        <v>462</v>
-      </c>
-      <c r="G160" t="s">
+      <c r="J160" t="s">
         <v>475</v>
       </c>
-      <c r="H160" t="s">
-        <v>473</v>
-      </c>
-      <c r="I160" t="s">
-        <v>476</v>
-      </c>
-      <c r="J160" t="s">
-        <v>477</v>
-      </c>
       <c r="K160" t="s">
+        <v>465</v>
+      </c>
+      <c r="L160" t="s">
+        <v>466</v>
+      </c>
+      <c r="M160" t="s">
         <v>467</v>
-      </c>
-      <c r="L160" t="s">
-        <v>468</v>
-      </c>
-      <c r="M160" t="s">
-        <v>469</v>
       </c>
       <c r="N160">
         <v>0</v>
@@ -36922,37 +36924,37 @@
         <v>0</v>
       </c>
       <c r="C161" t="s">
+        <v>457</v>
+      </c>
+      <c r="D161" t="s">
+        <v>476</v>
+      </c>
+      <c r="E161" t="s">
         <v>459</v>
       </c>
-      <c r="D161" t="s">
+      <c r="F161" t="s">
+        <v>460</v>
+      </c>
+      <c r="G161" t="s">
+        <v>477</v>
+      </c>
+      <c r="H161" t="s">
         <v>478</v>
       </c>
-      <c r="E161" t="s">
-        <v>461</v>
-      </c>
-      <c r="F161" t="s">
-        <v>462</v>
-      </c>
-      <c r="G161" t="s">
+      <c r="I161" t="s">
+        <v>474</v>
+      </c>
+      <c r="J161" t="s">
+        <v>475</v>
+      </c>
+      <c r="K161" t="s">
         <v>479</v>
       </c>
-      <c r="H161" t="s">
+      <c r="L161" t="s">
         <v>480</v>
       </c>
-      <c r="I161" t="s">
-        <v>476</v>
-      </c>
-      <c r="J161" t="s">
-        <v>477</v>
-      </c>
-      <c r="K161" t="s">
+      <c r="M161" t="s">
         <v>481</v>
-      </c>
-      <c r="L161" t="s">
-        <v>482</v>
-      </c>
-      <c r="M161" t="s">
-        <v>483</v>
       </c>
       <c r="N161">
         <v>0</v>
@@ -36979,37 +36981,37 @@
         <v>0</v>
       </c>
       <c r="C162" t="s">
+        <v>457</v>
+      </c>
+      <c r="D162" t="s">
+        <v>482</v>
+      </c>
+      <c r="E162" t="s">
         <v>459</v>
       </c>
-      <c r="D162" t="s">
+      <c r="F162" t="s">
+        <v>460</v>
+      </c>
+      <c r="G162" t="s">
+        <v>483</v>
+      </c>
+      <c r="H162" t="s">
         <v>484</v>
       </c>
-      <c r="E162" t="s">
-        <v>461</v>
-      </c>
-      <c r="F162" t="s">
-        <v>462</v>
-      </c>
-      <c r="G162" t="s">
+      <c r="I162" t="s">
         <v>485</v>
       </c>
-      <c r="H162" t="s">
+      <c r="J162" t="s">
         <v>486</v>
       </c>
-      <c r="I162" t="s">
+      <c r="K162" t="s">
         <v>487</v>
       </c>
-      <c r="J162" t="s">
+      <c r="L162" t="s">
         <v>488</v>
       </c>
-      <c r="K162" t="s">
+      <c r="M162" t="s">
         <v>489</v>
-      </c>
-      <c r="L162" t="s">
-        <v>490</v>
-      </c>
-      <c r="M162" t="s">
-        <v>491</v>
       </c>
       <c r="N162">
         <v>0</v>
@@ -37036,37 +37038,37 @@
         <v>0</v>
       </c>
       <c r="C163" t="s">
+        <v>457</v>
+      </c>
+      <c r="D163" t="s">
+        <v>490</v>
+      </c>
+      <c r="E163" t="s">
         <v>459</v>
       </c>
-      <c r="D163" t="s">
+      <c r="F163" t="s">
+        <v>460</v>
+      </c>
+      <c r="G163" t="s">
+        <v>491</v>
+      </c>
+      <c r="H163" t="s">
         <v>492</v>
       </c>
-      <c r="E163" t="s">
-        <v>461</v>
-      </c>
-      <c r="F163" t="s">
-        <v>462</v>
-      </c>
-      <c r="G163" t="s">
+      <c r="I163" t="s">
         <v>493</v>
       </c>
-      <c r="H163" t="s">
+      <c r="J163" t="s">
         <v>494</v>
       </c>
-      <c r="I163" t="s">
+      <c r="K163" t="s">
         <v>495</v>
       </c>
-      <c r="J163" t="s">
+      <c r="L163" t="s">
         <v>496</v>
       </c>
-      <c r="K163" t="s">
+      <c r="M163" t="s">
         <v>497</v>
-      </c>
-      <c r="L163" t="s">
-        <v>498</v>
-      </c>
-      <c r="M163" t="s">
-        <v>499</v>
       </c>
       <c r="N163">
         <v>0</v>
@@ -37093,37 +37095,37 @@
         <v>0</v>
       </c>
       <c r="C164" t="s">
+        <v>457</v>
+      </c>
+      <c r="D164" t="s">
+        <v>498</v>
+      </c>
+      <c r="E164" t="s">
         <v>459</v>
       </c>
-      <c r="D164" t="s">
+      <c r="F164" t="s">
+        <v>460</v>
+      </c>
+      <c r="G164" t="s">
+        <v>491</v>
+      </c>
+      <c r="H164" t="s">
+        <v>462</v>
+      </c>
+      <c r="I164" t="s">
+        <v>463</v>
+      </c>
+      <c r="J164" t="s">
+        <v>464</v>
+      </c>
+      <c r="K164" t="s">
+        <v>499</v>
+      </c>
+      <c r="L164" t="s">
         <v>500</v>
       </c>
-      <c r="E164" t="s">
-        <v>461</v>
-      </c>
-      <c r="F164" t="s">
-        <v>462</v>
-      </c>
-      <c r="G164" t="s">
-        <v>493</v>
-      </c>
-      <c r="H164" t="s">
-        <v>464</v>
-      </c>
-      <c r="I164" t="s">
-        <v>465</v>
-      </c>
-      <c r="J164" t="s">
-        <v>466</v>
-      </c>
-      <c r="K164" t="s">
+      <c r="M164" t="s">
         <v>501</v>
-      </c>
-      <c r="L164" t="s">
-        <v>502</v>
-      </c>
-      <c r="M164" t="s">
-        <v>503</v>
       </c>
       <c r="N164">
         <v>0</v>
@@ -37150,16 +37152,16 @@
         <v>0</v>
       </c>
       <c r="C165" t="s">
+        <v>442</v>
+      </c>
+      <c r="D165" t="s">
+        <v>443</v>
+      </c>
+      <c r="E165" t="s">
         <v>444</v>
       </c>
-      <c r="D165" t="s">
+      <c r="F165" t="s">
         <v>445</v>
-      </c>
-      <c r="E165" t="s">
-        <v>446</v>
-      </c>
-      <c r="F165" t="s">
-        <v>447</v>
       </c>
       <c r="G165">
         <v>4</v>
@@ -37207,16 +37209,16 @@
         <v>0</v>
       </c>
       <c r="C166" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D166" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E166" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F166" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="G166">
         <v>200</v>
@@ -37264,16 +37266,16 @@
         <v>0</v>
       </c>
       <c r="C167" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D167" t="s">
+        <v>448</v>
+      </c>
+      <c r="E167" t="s">
+        <v>449</v>
+      </c>
+      <c r="F167" t="s">
         <v>450</v>
-      </c>
-      <c r="E167" t="s">
-        <v>451</v>
-      </c>
-      <c r="F167" t="s">
-        <v>452</v>
       </c>
       <c r="G167">
         <v>4</v>
@@ -37321,16 +37323,16 @@
         <v>0</v>
       </c>
       <c r="C168" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D168" t="s">
+        <v>451</v>
+      </c>
+      <c r="E168" t="s">
+        <v>452</v>
+      </c>
+      <c r="F168" t="s">
         <v>453</v>
-      </c>
-      <c r="E168" t="s">
-        <v>454</v>
-      </c>
-      <c r="F168" t="s">
-        <v>455</v>
       </c>
       <c r="G168">
         <v>3</v>
@@ -37378,16 +37380,16 @@
         <v>0</v>
       </c>
       <c r="C169" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="D169" t="s">
+        <v>454</v>
+      </c>
+      <c r="E169" t="s">
+        <v>455</v>
+      </c>
+      <c r="F169" t="s">
         <v>456</v>
-      </c>
-      <c r="E169" t="s">
-        <v>457</v>
-      </c>
-      <c r="F169" t="s">
-        <v>458</v>
       </c>
       <c r="G169">
         <v>4</v>
@@ -37435,16 +37437,16 @@
         <v>0</v>
       </c>
       <c r="C170" t="s">
+        <v>372</v>
+      </c>
+      <c r="D170" t="s">
+        <v>373</v>
+      </c>
+      <c r="E170" t="s">
         <v>374</v>
       </c>
-      <c r="D170" t="s">
+      <c r="F170" t="s">
         <v>375</v>
-      </c>
-      <c r="E170" t="s">
-        <v>376</v>
-      </c>
-      <c r="F170" t="s">
-        <v>377</v>
       </c>
       <c r="G170">
         <v>0.5</v>
@@ -37492,16 +37494,16 @@
         <v>0</v>
       </c>
       <c r="C171" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D171" t="s">
+        <v>376</v>
+      </c>
+      <c r="E171" t="s">
+        <v>377</v>
+      </c>
+      <c r="F171" t="s">
         <v>378</v>
-      </c>
-      <c r="E171" t="s">
-        <v>379</v>
-      </c>
-      <c r="F171" t="s">
-        <v>380</v>
       </c>
       <c r="G171">
         <v>50</v>
@@ -37549,16 +37551,16 @@
         <v>0</v>
       </c>
       <c r="C172" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D172" t="s">
+        <v>379</v>
+      </c>
+      <c r="E172" t="s">
+        <v>380</v>
+      </c>
+      <c r="F172" t="s">
         <v>381</v>
-      </c>
-      <c r="E172" t="s">
-        <v>382</v>
-      </c>
-      <c r="F172" t="s">
-        <v>383</v>
       </c>
       <c r="G172">
         <v>0</v>
@@ -37606,16 +37608,16 @@
         <v>0</v>
       </c>
       <c r="C173" t="s">
+        <v>382</v>
+      </c>
+      <c r="D173" t="s">
+        <v>383</v>
+      </c>
+      <c r="E173" t="s">
         <v>384</v>
       </c>
-      <c r="D173" t="s">
+      <c r="F173" t="s">
         <v>385</v>
-      </c>
-      <c r="E173" t="s">
-        <v>386</v>
-      </c>
-      <c r="F173" t="s">
-        <v>387</v>
       </c>
       <c r="G173">
         <v>200</v>
@@ -37663,28 +37665,28 @@
         <v>0</v>
       </c>
       <c r="C174" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D174" t="s">
+        <v>386</v>
+      </c>
+      <c r="E174" t="s">
+        <v>387</v>
+      </c>
+      <c r="F174" t="s">
         <v>388</v>
-      </c>
-      <c r="E174" t="s">
-        <v>389</v>
-      </c>
-      <c r="F174" t="s">
-        <v>390</v>
       </c>
       <c r="G174">
         <v>55</v>
       </c>
       <c r="H174" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="I174" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="J174" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="K174">
         <v>0</v>
@@ -37720,28 +37722,28 @@
         <v>0</v>
       </c>
       <c r="C175" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D175" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E175" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F175" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G175">
         <v>25</v>
       </c>
       <c r="H175" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="I175">
         <v>2</v>
       </c>
       <c r="J175" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="K175">
         <v>0</v>
@@ -37777,28 +37779,28 @@
         <v>0</v>
       </c>
       <c r="C176" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D176" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E176" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F176" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G176">
         <v>12</v>
       </c>
       <c r="H176" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="I176">
         <v>2.5</v>
       </c>
       <c r="J176" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="K176">
         <v>0</v>
@@ -37834,28 +37836,28 @@
         <v>0</v>
       </c>
       <c r="C177" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D177" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E177" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F177" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G177">
         <v>5.5</v>
       </c>
       <c r="H177" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="I177">
         <v>3</v>
       </c>
       <c r="J177" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="K177">
         <v>0</v>
@@ -37891,28 +37893,28 @@
         <v>0</v>
       </c>
       <c r="C178" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D178" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E178" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F178" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G178">
         <v>1.8</v>
       </c>
       <c r="H178" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="I178">
         <v>3.5</v>
       </c>
       <c r="J178" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="K178">
         <v>0</v>
@@ -37948,28 +37950,28 @@
         <v>0</v>
       </c>
       <c r="C179" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D179" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E179" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F179" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G179">
         <v>0.35</v>
       </c>
       <c r="H179" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="I179">
         <v>4</v>
       </c>
       <c r="J179" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="K179">
         <v>0</v>
@@ -38005,28 +38007,28 @@
         <v>0</v>
       </c>
       <c r="C180" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D180" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E180" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F180" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G180">
         <v>0.08</v>
       </c>
       <c r="H180" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="I180">
         <v>4.5</v>
       </c>
       <c r="J180" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="K180">
         <v>0</v>
@@ -38062,28 +38064,28 @@
         <v>0</v>
       </c>
       <c r="C181" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="D181" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E181" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F181" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="G181">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="H181" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="I181">
         <v>5</v>
       </c>
       <c r="J181" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="K181">
         <v>0</v>
@@ -38119,16 +38121,16 @@
         <v>0</v>
       </c>
       <c r="C182" t="s">
+        <v>536</v>
+      </c>
+      <c r="D182" t="s">
+        <v>537</v>
+      </c>
+      <c r="E182" t="s">
         <v>538</v>
       </c>
-      <c r="D182" t="s">
+      <c r="F182" t="s">
         <v>539</v>
-      </c>
-      <c r="E182" t="s">
-        <v>540</v>
-      </c>
-      <c r="F182" t="s">
-        <v>541</v>
       </c>
       <c r="G182">
         <v>5</v>
@@ -38176,16 +38178,16 @@
         <v>0</v>
       </c>
       <c r="C183" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D183" t="s">
+        <v>540</v>
+      </c>
+      <c r="E183" t="s">
+        <v>541</v>
+      </c>
+      <c r="F183" t="s">
         <v>542</v>
-      </c>
-      <c r="E183" t="s">
-        <v>543</v>
-      </c>
-      <c r="F183" t="s">
-        <v>544</v>
       </c>
       <c r="G183">
         <v>0</v>
@@ -38233,16 +38235,16 @@
         <v>0</v>
       </c>
       <c r="C184" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D184" t="s">
+        <v>951</v>
+      </c>
+      <c r="E184" t="s">
+        <v>952</v>
+      </c>
+      <c r="F184" t="s">
         <v>953</v>
-      </c>
-      <c r="E184" t="s">
-        <v>954</v>
-      </c>
-      <c r="F184" t="s">
-        <v>955</v>
       </c>
       <c r="G184">
         <v>0.1</v>
@@ -38290,16 +38292,16 @@
         <v>0</v>
       </c>
       <c r="C185" t="s">
+        <v>543</v>
+      </c>
+      <c r="D185" t="s">
+        <v>544</v>
+      </c>
+      <c r="E185" t="s">
         <v>545</v>
       </c>
-      <c r="D185" t="s">
+      <c r="F185" t="s">
         <v>546</v>
-      </c>
-      <c r="E185" t="s">
-        <v>547</v>
-      </c>
-      <c r="F185" t="s">
-        <v>548</v>
       </c>
       <c r="G185">
         <v>5</v>
@@ -38347,16 +38349,16 @@
         <v>0</v>
       </c>
       <c r="C186" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D186" t="s">
+        <v>547</v>
+      </c>
+      <c r="E186" t="s">
+        <v>548</v>
+      </c>
+      <c r="F186" t="s">
         <v>549</v>
-      </c>
-      <c r="E186" t="s">
-        <v>550</v>
-      </c>
-      <c r="F186" t="s">
-        <v>551</v>
       </c>
       <c r="G186">
         <v>55</v>
@@ -38404,16 +38406,16 @@
         <v>0</v>
       </c>
       <c r="C187" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D187" t="s">
+        <v>550</v>
+      </c>
+      <c r="E187" t="s">
+        <v>551</v>
+      </c>
+      <c r="F187" t="s">
         <v>552</v>
-      </c>
-      <c r="E187" t="s">
-        <v>553</v>
-      </c>
-      <c r="F187" t="s">
-        <v>554</v>
       </c>
       <c r="G187">
         <v>5000000</v>
@@ -38461,13 +38463,13 @@
         <v>0</v>
       </c>
       <c r="C188" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D188" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E188" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="F188">
         <v>0</v>
@@ -38518,16 +38520,16 @@
         <v>0</v>
       </c>
       <c r="C189" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D189" t="s">
+        <v>554</v>
+      </c>
+      <c r="E189" t="s">
+        <v>555</v>
+      </c>
+      <c r="F189" t="s">
         <v>556</v>
-      </c>
-      <c r="E189" t="s">
-        <v>557</v>
-      </c>
-      <c r="F189" t="s">
-        <v>558</v>
       </c>
       <c r="G189">
         <v>3</v>
@@ -38575,16 +38577,16 @@
         <v>0</v>
       </c>
       <c r="C190" t="s">
+        <v>543</v>
+      </c>
+      <c r="D190" t="s">
+        <v>563</v>
+      </c>
+      <c r="E190" t="s">
         <v>545</v>
       </c>
-      <c r="D190" t="s">
-        <v>565</v>
-      </c>
-      <c r="E190" t="s">
-        <v>547</v>
-      </c>
       <c r="F190" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="G190">
         <v>3</v>
@@ -38632,16 +38634,16 @@
         <v>0</v>
       </c>
       <c r="C191" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D191" t="s">
+        <v>565</v>
+      </c>
+      <c r="E191" t="s">
+        <v>566</v>
+      </c>
+      <c r="F191" t="s">
         <v>567</v>
-      </c>
-      <c r="E191" t="s">
-        <v>568</v>
-      </c>
-      <c r="F191" t="s">
-        <v>569</v>
       </c>
       <c r="G191">
         <v>50</v>
@@ -38689,16 +38691,16 @@
         <v>0</v>
       </c>
       <c r="C192" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D192" t="s">
+        <v>568</v>
+      </c>
+      <c r="E192" t="s">
+        <v>569</v>
+      </c>
+      <c r="F192" t="s">
         <v>570</v>
-      </c>
-      <c r="E192" t="s">
-        <v>571</v>
-      </c>
-      <c r="F192" t="s">
-        <v>572</v>
       </c>
       <c r="G192">
         <v>1000000</v>
@@ -38746,13 +38748,13 @@
         <v>0</v>
       </c>
       <c r="C193" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D193" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E193" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F193">
         <v>0</v>
@@ -38803,16 +38805,16 @@
         <v>0</v>
       </c>
       <c r="C194" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D194" t="s">
+        <v>573</v>
+      </c>
+      <c r="E194" t="s">
+        <v>574</v>
+      </c>
+      <c r="F194" t="s">
         <v>575</v>
-      </c>
-      <c r="E194" t="s">
-        <v>576</v>
-      </c>
-      <c r="F194" t="s">
-        <v>577</v>
       </c>
       <c r="G194">
         <v>3</v>
@@ -38860,16 +38862,16 @@
         <v>0</v>
       </c>
       <c r="C195" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D195" t="s">
+        <v>576</v>
+      </c>
+      <c r="E195" t="s">
+        <v>577</v>
+      </c>
+      <c r="F195" t="s">
         <v>578</v>
-      </c>
-      <c r="E195" t="s">
-        <v>579</v>
-      </c>
-      <c r="F195" t="s">
-        <v>580</v>
       </c>
       <c r="G195">
         <v>6</v>
@@ -38917,16 +38919,16 @@
         <v>0</v>
       </c>
       <c r="C196" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D196" t="s">
+        <v>919</v>
+      </c>
+      <c r="E196" t="s">
+        <v>920</v>
+      </c>
+      <c r="F196" t="s">
         <v>921</v>
-      </c>
-      <c r="E196" t="s">
-        <v>922</v>
-      </c>
-      <c r="F196" t="s">
-        <v>923</v>
       </c>
       <c r="G196">
         <v>20</v>
@@ -38974,16 +38976,16 @@
         <v>0</v>
       </c>
       <c r="C197" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D197" t="s">
+        <v>922</v>
+      </c>
+      <c r="E197" t="s">
+        <v>923</v>
+      </c>
+      <c r="F197" t="s">
         <v>924</v>
-      </c>
-      <c r="E197" t="s">
-        <v>925</v>
-      </c>
-      <c r="F197" t="s">
-        <v>926</v>
       </c>
       <c r="G197">
         <v>500000000</v>
@@ -39031,16 +39033,16 @@
         <v>0</v>
       </c>
       <c r="C198" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="D198" t="s">
+        <v>925</v>
+      </c>
+      <c r="E198" t="s">
+        <v>926</v>
+      </c>
+      <c r="F198" t="s">
         <v>927</v>
-      </c>
-      <c r="E198" t="s">
-        <v>928</v>
-      </c>
-      <c r="F198" t="s">
-        <v>929</v>
       </c>
       <c r="G198">
         <v>13</v>
@@ -39088,16 +39090,16 @@
         <v>0</v>
       </c>
       <c r="C199" t="s">
+        <v>502</v>
+      </c>
+      <c r="D199" t="s">
+        <v>503</v>
+      </c>
+      <c r="E199" t="s">
         <v>504</v>
       </c>
-      <c r="D199" t="s">
+      <c r="F199" t="s">
         <v>505</v>
-      </c>
-      <c r="E199" t="s">
-        <v>506</v>
-      </c>
-      <c r="F199" t="s">
-        <v>507</v>
       </c>
       <c r="G199">
         <v>0</v>
@@ -39145,16 +39147,16 @@
         <v>0</v>
       </c>
       <c r="C200" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D200" t="s">
+        <v>506</v>
+      </c>
+      <c r="E200" t="s">
+        <v>507</v>
+      </c>
+      <c r="F200" t="s">
         <v>508</v>
-      </c>
-      <c r="E200" t="s">
-        <v>509</v>
-      </c>
-      <c r="F200" t="s">
-        <v>510</v>
       </c>
       <c r="G200">
         <v>1.35</v>
@@ -39202,16 +39204,16 @@
         <v>0</v>
       </c>
       <c r="C201" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D201" t="s">
+        <v>509</v>
+      </c>
+      <c r="E201" t="s">
+        <v>510</v>
+      </c>
+      <c r="F201" t="s">
         <v>511</v>
-      </c>
-      <c r="E201" t="s">
-        <v>512</v>
-      </c>
-      <c r="F201" t="s">
-        <v>513</v>
       </c>
       <c r="G201">
         <v>0.05</v>
@@ -39259,16 +39261,16 @@
         <v>0</v>
       </c>
       <c r="C202" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D202" t="s">
+        <v>512</v>
+      </c>
+      <c r="E202" t="s">
+        <v>513</v>
+      </c>
+      <c r="F202" t="s">
         <v>514</v>
-      </c>
-      <c r="E202" t="s">
-        <v>515</v>
-      </c>
-      <c r="F202" t="s">
-        <v>516</v>
       </c>
       <c r="G202">
         <v>2</v>
@@ -39316,16 +39318,16 @@
         <v>0</v>
       </c>
       <c r="C203" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D203" t="s">
+        <v>515</v>
+      </c>
+      <c r="E203" t="s">
+        <v>516</v>
+      </c>
+      <c r="F203" t="s">
         <v>517</v>
-      </c>
-      <c r="E203" t="s">
-        <v>518</v>
-      </c>
-      <c r="F203" t="s">
-        <v>519</v>
       </c>
       <c r="G203">
         <v>0</v>
@@ -39373,16 +39375,16 @@
         <v>0</v>
       </c>
       <c r="C204" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D204" t="s">
+        <v>518</v>
+      </c>
+      <c r="E204" t="s">
+        <v>519</v>
+      </c>
+      <c r="F204" t="s">
         <v>520</v>
-      </c>
-      <c r="E204" t="s">
-        <v>521</v>
-      </c>
-      <c r="F204" t="s">
-        <v>522</v>
       </c>
       <c r="G204">
         <v>5</v>
@@ -39430,16 +39432,16 @@
         <v>0</v>
       </c>
       <c r="C205" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D205" t="s">
+        <v>521</v>
+      </c>
+      <c r="E205" t="s">
+        <v>522</v>
+      </c>
+      <c r="F205" t="s">
         <v>523</v>
-      </c>
-      <c r="E205" t="s">
-        <v>524</v>
-      </c>
-      <c r="F205" t="s">
-        <v>525</v>
       </c>
       <c r="G205">
         <v>8</v>
@@ -39487,16 +39489,16 @@
         <v>0</v>
       </c>
       <c r="C206" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D206" t="s">
+        <v>524</v>
+      </c>
+      <c r="E206" t="s">
+        <v>525</v>
+      </c>
+      <c r="F206" t="s">
         <v>526</v>
-      </c>
-      <c r="E206" t="s">
-        <v>527</v>
-      </c>
-      <c r="F206" t="s">
-        <v>528</v>
       </c>
       <c r="G206">
         <v>1</v>
@@ -39544,16 +39546,16 @@
         <v>0</v>
       </c>
       <c r="C207" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D207" t="s">
+        <v>527</v>
+      </c>
+      <c r="E207" t="s">
+        <v>528</v>
+      </c>
+      <c r="F207" t="s">
         <v>529</v>
-      </c>
-      <c r="E207" t="s">
-        <v>530</v>
-      </c>
-      <c r="F207" t="s">
-        <v>531</v>
       </c>
       <c r="G207">
         <v>0.15</v>
@@ -39601,16 +39603,16 @@
         <v>0</v>
       </c>
       <c r="C208" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D208" t="s">
+        <v>530</v>
+      </c>
+      <c r="E208" t="s">
+        <v>531</v>
+      </c>
+      <c r="F208" t="s">
         <v>532</v>
-      </c>
-      <c r="E208" t="s">
-        <v>533</v>
-      </c>
-      <c r="F208" t="s">
-        <v>534</v>
       </c>
       <c r="G208">
         <v>2</v>
@@ -39658,16 +39660,16 @@
         <v>0</v>
       </c>
       <c r="C209" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D209" t="s">
+        <v>533</v>
+      </c>
+      <c r="E209" t="s">
+        <v>534</v>
+      </c>
+      <c r="F209" t="s">
         <v>535</v>
-      </c>
-      <c r="E209" t="s">
-        <v>536</v>
-      </c>
-      <c r="F209" t="s">
-        <v>537</v>
       </c>
       <c r="G209">
         <v>3</v>
@@ -39715,16 +39717,16 @@
         <v>0</v>
       </c>
       <c r="C210" t="s">
+        <v>608</v>
+      </c>
+      <c r="D210" t="s">
+        <v>609</v>
+      </c>
+      <c r="E210" t="s">
         <v>610</v>
       </c>
-      <c r="D210" t="s">
+      <c r="F210" t="s">
         <v>611</v>
-      </c>
-      <c r="E210" t="s">
-        <v>612</v>
-      </c>
-      <c r="F210" t="s">
-        <v>613</v>
       </c>
       <c r="G210">
         <v>2</v>
@@ -39784,16 +39786,16 @@
         <v>0</v>
       </c>
       <c r="C211" t="s">
+        <v>612</v>
+      </c>
+      <c r="D211" t="s">
+        <v>613</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="F211" t="s">
         <v>614</v>
-      </c>
-      <c r="D211" t="s">
-        <v>615</v>
-      </c>
-      <c r="E211" s="3" t="s">
-        <v>993</v>
-      </c>
-      <c r="F211" t="s">
-        <v>616</v>
       </c>
       <c r="G211">
         <v>10000</v>
@@ -39865,16 +39867,16 @@
         <v>0</v>
       </c>
       <c r="C212" t="s">
+        <v>596</v>
+      </c>
+      <c r="D212" t="s">
+        <v>597</v>
+      </c>
+      <c r="E212" t="s">
         <v>598</v>
       </c>
-      <c r="D212" t="s">
+      <c r="F212" t="s">
         <v>599</v>
-      </c>
-      <c r="E212" t="s">
-        <v>600</v>
-      </c>
-      <c r="F212" t="s">
-        <v>601</v>
       </c>
       <c r="G212">
         <v>5</v>
@@ -39957,16 +39959,16 @@
         <v>0</v>
       </c>
       <c r="C213" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D213" t="s">
+        <v>600</v>
+      </c>
+      <c r="E213" t="s">
+        <v>601</v>
+      </c>
+      <c r="F213" t="s">
         <v>602</v>
-      </c>
-      <c r="E213" t="s">
-        <v>603</v>
-      </c>
-      <c r="F213" t="s">
-        <v>604</v>
       </c>
       <c r="G213">
         <v>0</v>
@@ -40049,16 +40051,16 @@
         <v>0</v>
       </c>
       <c r="C214" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D214" t="s">
+        <v>603</v>
+      </c>
+      <c r="E214" t="s">
+        <v>604</v>
+      </c>
+      <c r="F214" t="s">
         <v>605</v>
-      </c>
-      <c r="E214" t="s">
-        <v>606</v>
-      </c>
-      <c r="F214" t="s">
-        <v>607</v>
       </c>
       <c r="G214">
         <v>0</v>
@@ -40141,16 +40143,16 @@
         <v>0</v>
       </c>
       <c r="C215" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D215" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E215" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="F215" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="G215">
         <v>0</v>
@@ -40233,16 +40235,16 @@
         <v>0</v>
       </c>
       <c r="C216" t="s">
+        <v>557</v>
+      </c>
+      <c r="D216" t="s">
+        <v>558</v>
+      </c>
+      <c r="E216" t="s">
         <v>559</v>
       </c>
-      <c r="D216" t="s">
+      <c r="F216" t="s">
         <v>560</v>
-      </c>
-      <c r="E216" t="s">
-        <v>561</v>
-      </c>
-      <c r="F216" t="s">
-        <v>562</v>
       </c>
       <c r="G216">
         <v>27</v>
@@ -40325,16 +40327,16 @@
         <v>0</v>
       </c>
       <c r="C217" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D217" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E217" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="F217" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G217">
         <v>36</v>
@@ -40417,13 +40419,13 @@
         <v>0</v>
       </c>
       <c r="C218" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D218" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E218" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="F218">
         <v>0</v>
@@ -40509,16 +40511,16 @@
         <v>0</v>
       </c>
       <c r="C219" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D219" t="s">
+        <v>590</v>
+      </c>
+      <c r="E219" t="s">
+        <v>591</v>
+      </c>
+      <c r="F219" t="s">
         <v>592</v>
-      </c>
-      <c r="E219" t="s">
-        <v>593</v>
-      </c>
-      <c r="F219" t="s">
-        <v>594</v>
       </c>
       <c r="G219">
         <v>9</v>
@@ -40601,16 +40603,16 @@
         <v>0</v>
       </c>
       <c r="C220" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D220" t="s">
+        <v>593</v>
+      </c>
+      <c r="E220" t="s">
+        <v>594</v>
+      </c>
+      <c r="F220" t="s">
         <v>595</v>
-      </c>
-      <c r="E220" t="s">
-        <v>596</v>
-      </c>
-      <c r="F220" t="s">
-        <v>597</v>
       </c>
       <c r="G220">
         <v>1</v>
@@ -40693,16 +40695,16 @@
         <v>0</v>
       </c>
       <c r="C221" t="s">
+        <v>615</v>
+      </c>
+      <c r="D221" t="s">
+        <v>616</v>
+      </c>
+      <c r="E221" t="s">
         <v>617</v>
       </c>
-      <c r="D221" t="s">
+      <c r="F221" t="s">
         <v>618</v>
-      </c>
-      <c r="E221" t="s">
-        <v>619</v>
-      </c>
-      <c r="F221" t="s">
-        <v>620</v>
       </c>
       <c r="G221">
         <v>20000</v>
@@ -40785,13 +40787,13 @@
         <v>0</v>
       </c>
       <c r="C222" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D222" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E222" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="F222">
         <v>0</v>
@@ -40877,16 +40879,16 @@
         <v>0</v>
       </c>
       <c r="C223" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D223" t="s">
+        <v>621</v>
+      </c>
+      <c r="E223" t="s">
+        <v>622</v>
+      </c>
+      <c r="F223" t="s">
         <v>623</v>
-      </c>
-      <c r="E223" t="s">
-        <v>624</v>
-      </c>
-      <c r="F223" t="s">
-        <v>625</v>
       </c>
       <c r="G223">
         <v>100</v>
@@ -40969,16 +40971,16 @@
         <v>0</v>
       </c>
       <c r="C224" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D224" t="s">
+        <v>624</v>
+      </c>
+      <c r="E224" t="s">
+        <v>625</v>
+      </c>
+      <c r="F224" t="s">
         <v>626</v>
-      </c>
-      <c r="E224" t="s">
-        <v>627</v>
-      </c>
-      <c r="F224" t="s">
-        <v>628</v>
       </c>
       <c r="G224">
         <v>10000</v>
@@ -41061,13 +41063,13 @@
         <v>0</v>
       </c>
       <c r="C225" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="D225" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E225" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="F225">
         <v>0</v>
@@ -41153,16 +41155,16 @@
         <v>0</v>
       </c>
       <c r="C226" t="s">
+        <v>579</v>
+      </c>
+      <c r="D226" t="s">
+        <v>580</v>
+      </c>
+      <c r="E226" t="s">
         <v>581</v>
       </c>
-      <c r="D226" t="s">
+      <c r="F226" t="s">
         <v>582</v>
-      </c>
-      <c r="E226" t="s">
-        <v>583</v>
-      </c>
-      <c r="F226" t="s">
-        <v>584</v>
       </c>
       <c r="G226">
         <v>30</v>
@@ -41245,13 +41247,13 @@
         <v>0</v>
       </c>
       <c r="C227" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D227" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E227" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="F227">
         <v>0</v>
@@ -41337,13 +41339,13 @@
         <v>0</v>
       </c>
       <c r="C228" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D228" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E228" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="F228">
         <v>0</v>
@@ -41429,16 +41431,16 @@
         <v>0</v>
       </c>
       <c r="C229" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="D229" t="s">
+        <v>586</v>
+      </c>
+      <c r="E229" t="s">
+        <v>587</v>
+      </c>
+      <c r="F229" t="s">
         <v>588</v>
-      </c>
-      <c r="E229" t="s">
-        <v>589</v>
-      </c>
-      <c r="F229" t="s">
-        <v>590</v>
       </c>
       <c r="G229">
         <v>0</v>
@@ -41521,16 +41523,16 @@
         <v>0</v>
       </c>
       <c r="C230" t="s">
+        <v>629</v>
+      </c>
+      <c r="D230" t="s">
+        <v>630</v>
+      </c>
+      <c r="E230" t="s">
         <v>631</v>
       </c>
-      <c r="D230" t="s">
+      <c r="F230" t="s">
         <v>632</v>
-      </c>
-      <c r="E230" t="s">
-        <v>633</v>
-      </c>
-      <c r="F230" t="s">
-        <v>634</v>
       </c>
       <c r="G230">
         <v>0.2</v>
@@ -41613,16 +41615,16 @@
         <v>0</v>
       </c>
       <c r="C231" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D231" t="s">
+        <v>633</v>
+      </c>
+      <c r="E231" t="s">
+        <v>634</v>
+      </c>
+      <c r="F231" t="s">
         <v>635</v>
-      </c>
-      <c r="E231" t="s">
-        <v>636</v>
-      </c>
-      <c r="F231" t="s">
-        <v>637</v>
       </c>
       <c r="G231">
         <v>2</v>
@@ -41705,16 +41707,16 @@
         <v>0</v>
       </c>
       <c r="C232" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D232" t="s">
+        <v>636</v>
+      </c>
+      <c r="E232" t="s">
+        <v>637</v>
+      </c>
+      <c r="F232" t="s">
         <v>638</v>
-      </c>
-      <c r="E232" t="s">
-        <v>639</v>
-      </c>
-      <c r="F232" t="s">
-        <v>640</v>
       </c>
       <c r="G232">
         <v>3</v>
@@ -41766,16 +41768,16 @@
         <v>0</v>
       </c>
       <c r="C233" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D233" t="s">
+        <v>639</v>
+      </c>
+      <c r="E233" t="s">
+        <v>640</v>
+      </c>
+      <c r="F233" t="s">
         <v>641</v>
-      </c>
-      <c r="E233" t="s">
-        <v>642</v>
-      </c>
-      <c r="F233" t="s">
-        <v>643</v>
       </c>
       <c r="G233">
         <v>3</v>
@@ -41823,16 +41825,16 @@
         <v>0</v>
       </c>
       <c r="C234" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D234" t="s">
+        <v>642</v>
+      </c>
+      <c r="E234" t="s">
+        <v>643</v>
+      </c>
+      <c r="F234" t="s">
         <v>644</v>
-      </c>
-      <c r="E234" t="s">
-        <v>645</v>
-      </c>
-      <c r="F234" t="s">
-        <v>646</v>
       </c>
       <c r="G234">
         <v>100</v>
@@ -41880,16 +41882,16 @@
         <v>0</v>
       </c>
       <c r="C235" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D235" t="s">
+        <v>645</v>
+      </c>
+      <c r="E235" t="s">
+        <v>646</v>
+      </c>
+      <c r="F235" t="s">
         <v>647</v>
-      </c>
-      <c r="E235" t="s">
-        <v>648</v>
-      </c>
-      <c r="F235" t="s">
-        <v>649</v>
       </c>
       <c r="G235">
         <v>9</v>
@@ -41937,16 +41939,16 @@
         <v>0</v>
       </c>
       <c r="C236" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D236" t="s">
+        <v>648</v>
+      </c>
+      <c r="E236" t="s">
+        <v>649</v>
+      </c>
+      <c r="F236" t="s">
         <v>650</v>
-      </c>
-      <c r="E236" t="s">
-        <v>651</v>
-      </c>
-      <c r="F236" t="s">
-        <v>652</v>
       </c>
       <c r="G236">
         <v>0.7</v>
@@ -41994,16 +41996,16 @@
         <v>0</v>
       </c>
       <c r="C237" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D237" t="s">
+        <v>651</v>
+      </c>
+      <c r="E237" t="s">
+        <v>652</v>
+      </c>
+      <c r="F237" t="s">
         <v>653</v>
-      </c>
-      <c r="E237" t="s">
-        <v>654</v>
-      </c>
-      <c r="F237" t="s">
-        <v>655</v>
       </c>
       <c r="G237">
         <v>0.7</v>
@@ -42051,16 +42053,16 @@
         <v>0</v>
       </c>
       <c r="C238" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D238" t="s">
+        <v>654</v>
+      </c>
+      <c r="E238" t="s">
+        <v>655</v>
+      </c>
+      <c r="F238" t="s">
         <v>656</v>
-      </c>
-      <c r="E238" t="s">
-        <v>657</v>
-      </c>
-      <c r="F238" t="s">
-        <v>658</v>
       </c>
       <c r="G238">
         <v>10</v>
@@ -42108,16 +42110,16 @@
         <v>0</v>
       </c>
       <c r="C239" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D239" t="s">
+        <v>657</v>
+      </c>
+      <c r="E239" t="s">
+        <v>658</v>
+      </c>
+      <c r="F239" t="s">
         <v>659</v>
-      </c>
-      <c r="E239" t="s">
-        <v>660</v>
-      </c>
-      <c r="F239" t="s">
-        <v>661</v>
       </c>
       <c r="G239">
         <v>0</v>
@@ -42165,16 +42167,16 @@
         <v>0</v>
       </c>
       <c r="C240" t="s">
+        <v>660</v>
+      </c>
+      <c r="D240" t="s">
+        <v>661</v>
+      </c>
+      <c r="E240" t="s">
         <v>662</v>
       </c>
-      <c r="D240" t="s">
+      <c r="F240" t="s">
         <v>663</v>
-      </c>
-      <c r="E240" t="s">
-        <v>664</v>
-      </c>
-      <c r="F240" t="s">
-        <v>665</v>
       </c>
       <c r="G240">
         <v>100000</v>
@@ -42222,16 +42224,16 @@
         <v>0</v>
       </c>
       <c r="C241" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D241" t="s">
+        <v>664</v>
+      </c>
+      <c r="E241" t="s">
+        <v>665</v>
+      </c>
+      <c r="F241" t="s">
         <v>666</v>
-      </c>
-      <c r="E241" t="s">
-        <v>667</v>
-      </c>
-      <c r="F241" t="s">
-        <v>668</v>
       </c>
       <c r="G241">
         <v>5000</v>
@@ -42279,13 +42281,13 @@
         <v>0</v>
       </c>
       <c r="C242" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D242" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="E242" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="F242">
         <v>0</v>
@@ -42336,16 +42338,16 @@
         <v>0</v>
       </c>
       <c r="C243" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D243" t="s">
+        <v>669</v>
+      </c>
+      <c r="E243" t="s">
+        <v>670</v>
+      </c>
+      <c r="F243" t="s">
         <v>671</v>
-      </c>
-      <c r="E243" t="s">
-        <v>672</v>
-      </c>
-      <c r="F243" t="s">
-        <v>673</v>
       </c>
       <c r="G243">
         <v>10000</v>
@@ -42393,28 +42395,28 @@
         <v>0</v>
       </c>
       <c r="C244" t="s">
+        <v>743</v>
+      </c>
+      <c r="D244" t="s">
+        <v>673</v>
+      </c>
+      <c r="E244" t="s">
+        <v>744</v>
+      </c>
+      <c r="F244" t="s">
         <v>745</v>
       </c>
-      <c r="D244" t="s">
-        <v>675</v>
-      </c>
-      <c r="E244" t="s">
+      <c r="G244" t="s">
         <v>746</v>
       </c>
-      <c r="F244" t="s">
+      <c r="H244" t="s">
         <v>747</v>
       </c>
-      <c r="G244" t="s">
+      <c r="I244" t="s">
         <v>748</v>
       </c>
-      <c r="H244" t="s">
+      <c r="J244" t="s">
         <v>749</v>
-      </c>
-      <c r="I244" t="s">
-        <v>750</v>
-      </c>
-      <c r="J244" t="s">
-        <v>751</v>
       </c>
       <c r="K244">
         <v>0</v>
@@ -42450,28 +42452,28 @@
         <v>0</v>
       </c>
       <c r="C245" t="s">
+        <v>743</v>
+      </c>
+      <c r="D245" t="s">
+        <v>678</v>
+      </c>
+      <c r="E245" t="s">
+        <v>744</v>
+      </c>
+      <c r="F245" t="s">
         <v>745</v>
       </c>
-      <c r="D245" t="s">
-        <v>680</v>
-      </c>
-      <c r="E245" t="s">
-        <v>746</v>
-      </c>
-      <c r="F245" t="s">
+      <c r="G245" t="s">
+        <v>750</v>
+      </c>
+      <c r="H245" t="s">
         <v>747</v>
       </c>
-      <c r="G245" t="s">
+      <c r="I245" t="s">
+        <v>751</v>
+      </c>
+      <c r="J245" t="s">
         <v>752</v>
-      </c>
-      <c r="H245" t="s">
-        <v>749</v>
-      </c>
-      <c r="I245" t="s">
-        <v>753</v>
-      </c>
-      <c r="J245" t="s">
-        <v>754</v>
       </c>
       <c r="K245">
         <v>0</v>
@@ -42507,28 +42509,28 @@
         <v>0</v>
       </c>
       <c r="C246" t="s">
+        <v>743</v>
+      </c>
+      <c r="D246" t="s">
+        <v>681</v>
+      </c>
+      <c r="E246" t="s">
+        <v>744</v>
+      </c>
+      <c r="F246" t="s">
         <v>745</v>
       </c>
-      <c r="D246" t="s">
-        <v>683</v>
-      </c>
-      <c r="E246" t="s">
-        <v>746</v>
-      </c>
-      <c r="F246" t="s">
+      <c r="G246" t="s">
+        <v>753</v>
+      </c>
+      <c r="H246" t="s">
         <v>747</v>
       </c>
-      <c r="G246" t="s">
+      <c r="I246" t="s">
+        <v>754</v>
+      </c>
+      <c r="J246" t="s">
         <v>755</v>
-      </c>
-      <c r="H246" t="s">
-        <v>749</v>
-      </c>
-      <c r="I246" t="s">
-        <v>756</v>
-      </c>
-      <c r="J246" t="s">
-        <v>757</v>
       </c>
       <c r="K246">
         <v>0</v>
@@ -42564,31 +42566,31 @@
         <v>0</v>
       </c>
       <c r="C247" t="s">
+        <v>743</v>
+      </c>
+      <c r="D247" t="s">
+        <v>684</v>
+      </c>
+      <c r="E247" t="s">
+        <v>744</v>
+      </c>
+      <c r="F247" t="s">
         <v>745</v>
       </c>
-      <c r="D247" t="s">
-        <v>686</v>
-      </c>
-      <c r="E247" t="s">
-        <v>746</v>
-      </c>
-      <c r="F247" t="s">
+      <c r="G247" t="s">
+        <v>756</v>
+      </c>
+      <c r="H247" t="s">
         <v>747</v>
       </c>
-      <c r="G247" t="s">
-        <v>758</v>
-      </c>
-      <c r="H247" t="s">
-        <v>749</v>
-      </c>
       <c r="I247" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="J247" t="s">
+        <v>755</v>
+      </c>
+      <c r="K247" t="s">
         <v>757</v>
-      </c>
-      <c r="K247" t="s">
-        <v>759</v>
       </c>
       <c r="L247">
         <v>0</v>
@@ -42621,31 +42623,31 @@
         <v>0</v>
       </c>
       <c r="C248" t="s">
+        <v>743</v>
+      </c>
+      <c r="D248" t="s">
+        <v>687</v>
+      </c>
+      <c r="E248" t="s">
+        <v>744</v>
+      </c>
+      <c r="F248" t="s">
         <v>745</v>
       </c>
-      <c r="D248" t="s">
-        <v>689</v>
-      </c>
-      <c r="E248" t="s">
-        <v>746</v>
-      </c>
-      <c r="F248" t="s">
+      <c r="G248" t="s">
+        <v>758</v>
+      </c>
+      <c r="H248" t="s">
         <v>747</v>
       </c>
-      <c r="G248" t="s">
+      <c r="I248" t="s">
+        <v>754</v>
+      </c>
+      <c r="J248" t="s">
+        <v>759</v>
+      </c>
+      <c r="K248" t="s">
         <v>760</v>
-      </c>
-      <c r="H248" t="s">
-        <v>749</v>
-      </c>
-      <c r="I248" t="s">
-        <v>756</v>
-      </c>
-      <c r="J248" t="s">
-        <v>761</v>
-      </c>
-      <c r="K248" t="s">
-        <v>762</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -42678,31 +42680,31 @@
         <v>0</v>
       </c>
       <c r="C249" t="s">
+        <v>743</v>
+      </c>
+      <c r="D249" t="s">
+        <v>690</v>
+      </c>
+      <c r="E249" t="s">
+        <v>744</v>
+      </c>
+      <c r="F249" t="s">
         <v>745</v>
       </c>
-      <c r="D249" t="s">
-        <v>692</v>
-      </c>
-      <c r="E249" t="s">
-        <v>746</v>
-      </c>
-      <c r="F249" t="s">
+      <c r="G249" t="s">
+        <v>761</v>
+      </c>
+      <c r="H249" t="s">
         <v>747</v>
       </c>
-      <c r="G249" t="s">
+      <c r="I249" t="s">
+        <v>754</v>
+      </c>
+      <c r="J249" t="s">
+        <v>762</v>
+      </c>
+      <c r="K249" t="s">
         <v>763</v>
-      </c>
-      <c r="H249" t="s">
-        <v>749</v>
-      </c>
-      <c r="I249" t="s">
-        <v>756</v>
-      </c>
-      <c r="J249" t="s">
-        <v>764</v>
-      </c>
-      <c r="K249" t="s">
-        <v>765</v>
       </c>
       <c r="L249">
         <v>0</v>
@@ -42735,31 +42737,31 @@
         <v>0</v>
       </c>
       <c r="C250" t="s">
+        <v>743</v>
+      </c>
+      <c r="D250" t="s">
+        <v>693</v>
+      </c>
+      <c r="E250" t="s">
+        <v>744</v>
+      </c>
+      <c r="F250" t="s">
         <v>745</v>
       </c>
-      <c r="D250" t="s">
-        <v>695</v>
-      </c>
-      <c r="E250" t="s">
-        <v>746</v>
-      </c>
-      <c r="F250" t="s">
+      <c r="G250" t="s">
+        <v>764</v>
+      </c>
+      <c r="H250" t="s">
         <v>747</v>
       </c>
-      <c r="G250" t="s">
+      <c r="I250" t="s">
+        <v>765</v>
+      </c>
+      <c r="J250" t="s">
         <v>766</v>
       </c>
-      <c r="H250" t="s">
-        <v>749</v>
-      </c>
-      <c r="I250" t="s">
+      <c r="K250" t="s">
         <v>767</v>
-      </c>
-      <c r="J250" t="s">
-        <v>768</v>
-      </c>
-      <c r="K250" t="s">
-        <v>769</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -42792,31 +42794,31 @@
         <v>0</v>
       </c>
       <c r="C251" t="s">
+        <v>743</v>
+      </c>
+      <c r="D251" t="s">
+        <v>698</v>
+      </c>
+      <c r="E251" t="s">
+        <v>744</v>
+      </c>
+      <c r="F251" t="s">
         <v>745</v>
       </c>
-      <c r="D251" t="s">
-        <v>700</v>
-      </c>
-      <c r="E251" t="s">
-        <v>746</v>
-      </c>
-      <c r="F251" t="s">
+      <c r="G251" t="s">
+        <v>768</v>
+      </c>
+      <c r="H251" t="s">
         <v>747</v>
       </c>
-      <c r="G251" t="s">
+      <c r="I251" t="s">
+        <v>769</v>
+      </c>
+      <c r="J251" t="s">
         <v>770</v>
       </c>
-      <c r="H251" t="s">
-        <v>749</v>
-      </c>
-      <c r="I251" t="s">
+      <c r="K251" t="s">
         <v>771</v>
-      </c>
-      <c r="J251" t="s">
-        <v>772</v>
-      </c>
-      <c r="K251" t="s">
-        <v>773</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -42849,31 +42851,31 @@
         <v>0</v>
       </c>
       <c r="C252" t="s">
+        <v>743</v>
+      </c>
+      <c r="D252" t="s">
+        <v>700</v>
+      </c>
+      <c r="E252" t="s">
+        <v>744</v>
+      </c>
+      <c r="F252" t="s">
         <v>745</v>
       </c>
-      <c r="D252" t="s">
-        <v>702</v>
-      </c>
-      <c r="E252" t="s">
-        <v>746</v>
-      </c>
-      <c r="F252" t="s">
+      <c r="G252" t="s">
+        <v>772</v>
+      </c>
+      <c r="H252" t="s">
         <v>747</v>
       </c>
-      <c r="G252" t="s">
+      <c r="I252" t="s">
+        <v>773</v>
+      </c>
+      <c r="J252" t="s">
         <v>774</v>
       </c>
-      <c r="H252" t="s">
-        <v>749</v>
-      </c>
-      <c r="I252" t="s">
+      <c r="K252" t="s">
         <v>775</v>
-      </c>
-      <c r="J252" t="s">
-        <v>776</v>
-      </c>
-      <c r="K252" t="s">
-        <v>777</v>
       </c>
       <c r="L252">
         <v>0</v>
@@ -42906,34 +42908,34 @@
         <v>0</v>
       </c>
       <c r="C253" t="s">
+        <v>743</v>
+      </c>
+      <c r="D253" t="s">
+        <v>704</v>
+      </c>
+      <c r="E253" t="s">
+        <v>744</v>
+      </c>
+      <c r="F253" t="s">
         <v>745</v>
       </c>
-      <c r="D253" t="s">
-        <v>706</v>
-      </c>
-      <c r="E253" t="s">
-        <v>746</v>
-      </c>
-      <c r="F253" t="s">
+      <c r="G253" t="s">
+        <v>776</v>
+      </c>
+      <c r="H253" t="s">
         <v>747</v>
       </c>
-      <c r="G253" t="s">
+      <c r="I253" t="s">
+        <v>773</v>
+      </c>
+      <c r="J253" t="s">
+        <v>774</v>
+      </c>
+      <c r="K253" t="s">
+        <v>777</v>
+      </c>
+      <c r="L253" t="s">
         <v>778</v>
-      </c>
-      <c r="H253" t="s">
-        <v>749</v>
-      </c>
-      <c r="I253" t="s">
-        <v>775</v>
-      </c>
-      <c r="J253" t="s">
-        <v>776</v>
-      </c>
-      <c r="K253" t="s">
-        <v>779</v>
-      </c>
-      <c r="L253" t="s">
-        <v>780</v>
       </c>
       <c r="M253">
         <v>0</v>
@@ -42963,34 +42965,34 @@
         <v>0</v>
       </c>
       <c r="C254" t="s">
+        <v>743</v>
+      </c>
+      <c r="D254" t="s">
+        <v>708</v>
+      </c>
+      <c r="E254" t="s">
+        <v>744</v>
+      </c>
+      <c r="F254" t="s">
         <v>745</v>
       </c>
-      <c r="D254" t="s">
-        <v>710</v>
-      </c>
-      <c r="E254" t="s">
-        <v>746</v>
-      </c>
-      <c r="F254" t="s">
+      <c r="G254" t="s">
+        <v>779</v>
+      </c>
+      <c r="H254" t="s">
         <v>747</v>
       </c>
-      <c r="G254" t="s">
+      <c r="I254" t="s">
+        <v>773</v>
+      </c>
+      <c r="J254" t="s">
+        <v>774</v>
+      </c>
+      <c r="K254" t="s">
+        <v>780</v>
+      </c>
+      <c r="L254" t="s">
         <v>781</v>
-      </c>
-      <c r="H254" t="s">
-        <v>749</v>
-      </c>
-      <c r="I254" t="s">
-        <v>775</v>
-      </c>
-      <c r="J254" t="s">
-        <v>776</v>
-      </c>
-      <c r="K254" t="s">
-        <v>782</v>
-      </c>
-      <c r="L254" t="s">
-        <v>783</v>
       </c>
       <c r="M254">
         <v>0</v>
@@ -43020,34 +43022,34 @@
         <v>0</v>
       </c>
       <c r="C255" t="s">
+        <v>743</v>
+      </c>
+      <c r="D255" t="s">
+        <v>712</v>
+      </c>
+      <c r="E255" t="s">
+        <v>744</v>
+      </c>
+      <c r="F255" t="s">
         <v>745</v>
       </c>
-      <c r="D255" t="s">
-        <v>714</v>
-      </c>
-      <c r="E255" t="s">
-        <v>746</v>
-      </c>
-      <c r="F255" t="s">
+      <c r="G255" t="s">
+        <v>782</v>
+      </c>
+      <c r="H255" t="s">
         <v>747</v>
       </c>
-      <c r="G255" t="s">
+      <c r="I255" t="s">
+        <v>783</v>
+      </c>
+      <c r="J255" t="s">
         <v>784</v>
       </c>
-      <c r="H255" t="s">
-        <v>749</v>
-      </c>
-      <c r="I255" t="s">
+      <c r="K255" t="s">
         <v>785</v>
       </c>
-      <c r="J255" t="s">
+      <c r="L255" t="s">
         <v>786</v>
-      </c>
-      <c r="K255" t="s">
-        <v>787</v>
-      </c>
-      <c r="L255" t="s">
-        <v>788</v>
       </c>
       <c r="M255">
         <v>0</v>
@@ -43077,34 +43079,34 @@
         <v>0</v>
       </c>
       <c r="C256" t="s">
+        <v>743</v>
+      </c>
+      <c r="D256" t="s">
+        <v>716</v>
+      </c>
+      <c r="E256" t="s">
+        <v>744</v>
+      </c>
+      <c r="F256" t="s">
         <v>745</v>
       </c>
-      <c r="D256" t="s">
-        <v>718</v>
-      </c>
-      <c r="E256" t="s">
-        <v>746</v>
-      </c>
-      <c r="F256" t="s">
+      <c r="G256" t="s">
+        <v>787</v>
+      </c>
+      <c r="H256" t="s">
         <v>747</v>
       </c>
-      <c r="G256" t="s">
-        <v>789</v>
-      </c>
-      <c r="H256" t="s">
-        <v>749</v>
-      </c>
       <c r="I256" t="s">
+        <v>783</v>
+      </c>
+      <c r="J256" t="s">
+        <v>784</v>
+      </c>
+      <c r="K256" t="s">
         <v>785</v>
       </c>
-      <c r="J256" t="s">
-        <v>786</v>
-      </c>
-      <c r="K256" t="s">
-        <v>787</v>
-      </c>
       <c r="L256" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="M256">
         <v>0</v>
@@ -43134,34 +43136,34 @@
         <v>0</v>
       </c>
       <c r="C257" t="s">
+        <v>743</v>
+      </c>
+      <c r="D257" t="s">
+        <v>720</v>
+      </c>
+      <c r="E257" t="s">
+        <v>744</v>
+      </c>
+      <c r="F257" t="s">
         <v>745</v>
       </c>
-      <c r="D257" t="s">
-        <v>722</v>
-      </c>
-      <c r="E257" t="s">
-        <v>746</v>
-      </c>
-      <c r="F257" t="s">
+      <c r="G257" t="s">
+        <v>789</v>
+      </c>
+      <c r="H257" t="s">
         <v>747</v>
       </c>
-      <c r="G257" t="s">
-        <v>791</v>
-      </c>
-      <c r="H257" t="s">
-        <v>749</v>
-      </c>
       <c r="I257" t="s">
+        <v>783</v>
+      </c>
+      <c r="J257" t="s">
+        <v>784</v>
+      </c>
+      <c r="K257" t="s">
         <v>785</v>
       </c>
-      <c r="J257" t="s">
-        <v>786</v>
-      </c>
-      <c r="K257" t="s">
-        <v>787</v>
-      </c>
       <c r="L257" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="M257">
         <v>0</v>
@@ -43191,37 +43193,37 @@
         <v>0</v>
       </c>
       <c r="C258" t="s">
+        <v>743</v>
+      </c>
+      <c r="D258" t="s">
+        <v>724</v>
+      </c>
+      <c r="E258" t="s">
+        <v>744</v>
+      </c>
+      <c r="F258" t="s">
         <v>745</v>
       </c>
-      <c r="D258" t="s">
-        <v>726</v>
-      </c>
-      <c r="E258" t="s">
-        <v>746</v>
-      </c>
-      <c r="F258" t="s">
+      <c r="G258" t="s">
+        <v>791</v>
+      </c>
+      <c r="H258" t="s">
         <v>747</v>
       </c>
-      <c r="G258" t="s">
+      <c r="I258" t="s">
+        <v>783</v>
+      </c>
+      <c r="J258" t="s">
+        <v>792</v>
+      </c>
+      <c r="K258" t="s">
         <v>793</v>
       </c>
-      <c r="H258" t="s">
-        <v>749</v>
-      </c>
-      <c r="I258" t="s">
-        <v>785</v>
-      </c>
-      <c r="J258" t="s">
+      <c r="L258" t="s">
+        <v>786</v>
+      </c>
+      <c r="M258" t="s">
         <v>794</v>
-      </c>
-      <c r="K258" t="s">
-        <v>795</v>
-      </c>
-      <c r="L258" t="s">
-        <v>788</v>
-      </c>
-      <c r="M258" t="s">
-        <v>796</v>
       </c>
       <c r="N258">
         <v>0</v>
@@ -43248,37 +43250,37 @@
         <v>0</v>
       </c>
       <c r="C259" t="s">
+        <v>743</v>
+      </c>
+      <c r="D259" t="s">
+        <v>728</v>
+      </c>
+      <c r="E259" t="s">
+        <v>744</v>
+      </c>
+      <c r="F259" t="s">
         <v>745</v>
       </c>
-      <c r="D259" t="s">
-        <v>730</v>
-      </c>
-      <c r="E259" t="s">
-        <v>746</v>
-      </c>
-      <c r="F259" t="s">
+      <c r="G259" t="s">
+        <v>795</v>
+      </c>
+      <c r="H259" t="s">
         <v>747</v>
       </c>
-      <c r="G259" t="s">
-        <v>797</v>
-      </c>
-      <c r="H259" t="s">
-        <v>749</v>
-      </c>
       <c r="I259" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="J259" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="K259" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="L259" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="M259" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="N259">
         <v>0</v>
@@ -43305,37 +43307,37 @@
         <v>0</v>
       </c>
       <c r="C260" t="s">
+        <v>743</v>
+      </c>
+      <c r="D260" t="s">
+        <v>732</v>
+      </c>
+      <c r="E260" t="s">
+        <v>744</v>
+      </c>
+      <c r="F260" t="s">
         <v>745</v>
       </c>
-      <c r="D260" t="s">
-        <v>734</v>
-      </c>
-      <c r="E260" t="s">
-        <v>746</v>
-      </c>
-      <c r="F260" t="s">
+      <c r="G260" t="s">
+        <v>797</v>
+      </c>
+      <c r="H260" t="s">
         <v>747</v>
       </c>
-      <c r="G260" t="s">
-        <v>799</v>
-      </c>
-      <c r="H260" t="s">
-        <v>749</v>
-      </c>
       <c r="I260" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="J260" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="K260" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="L260" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="M260" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="N260">
         <v>0</v>
@@ -43362,40 +43364,40 @@
         <v>0</v>
       </c>
       <c r="C261" t="s">
+        <v>743</v>
+      </c>
+      <c r="D261" t="s">
+        <v>736</v>
+      </c>
+      <c r="E261" t="s">
+        <v>744</v>
+      </c>
+      <c r="F261" t="s">
         <v>745</v>
       </c>
-      <c r="D261" t="s">
-        <v>738</v>
-      </c>
-      <c r="E261" t="s">
-        <v>746</v>
-      </c>
-      <c r="F261" t="s">
+      <c r="G261" t="s">
+        <v>799</v>
+      </c>
+      <c r="H261" t="s">
         <v>747</v>
       </c>
-      <c r="G261" t="s">
-        <v>801</v>
-      </c>
-      <c r="H261" t="s">
-        <v>749</v>
-      </c>
       <c r="I261" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="J261" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="K261" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="L261" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="M261" t="s">
+        <v>798</v>
+      </c>
+      <c r="N261" t="s">
         <v>800</v>
-      </c>
-      <c r="N261" t="s">
-        <v>802</v>
       </c>
       <c r="O261">
         <v>0</v>
@@ -43419,43 +43421,43 @@
         <v>0</v>
       </c>
       <c r="C262" t="s">
+        <v>743</v>
+      </c>
+      <c r="D262" t="s">
+        <v>741</v>
+      </c>
+      <c r="E262" t="s">
+        <v>744</v>
+      </c>
+      <c r="F262" t="s">
         <v>745</v>
       </c>
-      <c r="D262" t="s">
-        <v>743</v>
-      </c>
-      <c r="E262" t="s">
-        <v>746</v>
-      </c>
-      <c r="F262" t="s">
+      <c r="G262" t="s">
+        <v>801</v>
+      </c>
+      <c r="H262" t="s">
         <v>747</v>
       </c>
-      <c r="G262" t="s">
+      <c r="I262" t="s">
+        <v>783</v>
+      </c>
+      <c r="J262" t="s">
+        <v>792</v>
+      </c>
+      <c r="K262" t="s">
+        <v>793</v>
+      </c>
+      <c r="L262" t="s">
+        <v>788</v>
+      </c>
+      <c r="M262" t="s">
+        <v>798</v>
+      </c>
+      <c r="N262" t="s">
+        <v>802</v>
+      </c>
+      <c r="O262" t="s">
         <v>803</v>
-      </c>
-      <c r="H262" t="s">
-        <v>749</v>
-      </c>
-      <c r="I262" t="s">
-        <v>785</v>
-      </c>
-      <c r="J262" t="s">
-        <v>794</v>
-      </c>
-      <c r="K262" t="s">
-        <v>795</v>
-      </c>
-      <c r="L262" t="s">
-        <v>790</v>
-      </c>
-      <c r="M262" t="s">
-        <v>800</v>
-      </c>
-      <c r="N262" t="s">
-        <v>804</v>
-      </c>
-      <c r="O262" t="s">
-        <v>805</v>
       </c>
       <c r="P262">
         <v>0</v>
@@ -43476,46 +43478,46 @@
         <v>0</v>
       </c>
       <c r="C263" t="s">
+        <v>743</v>
+      </c>
+      <c r="D263" t="s">
+        <v>742</v>
+      </c>
+      <c r="E263" t="s">
+        <v>744</v>
+      </c>
+      <c r="F263" t="s">
         <v>745</v>
       </c>
-      <c r="D263" t="s">
-        <v>744</v>
-      </c>
-      <c r="E263" t="s">
-        <v>746</v>
-      </c>
-      <c r="F263" t="s">
+      <c r="G263" t="s">
+        <v>804</v>
+      </c>
+      <c r="H263" t="s">
         <v>747</v>
       </c>
-      <c r="G263" t="s">
+      <c r="I263" t="s">
+        <v>783</v>
+      </c>
+      <c r="J263" t="s">
+        <v>792</v>
+      </c>
+      <c r="K263" t="s">
+        <v>793</v>
+      </c>
+      <c r="L263" t="s">
+        <v>788</v>
+      </c>
+      <c r="M263" t="s">
+        <v>798</v>
+      </c>
+      <c r="N263" t="s">
+        <v>805</v>
+      </c>
+      <c r="O263" t="s">
         <v>806</v>
       </c>
-      <c r="H263" t="s">
-        <v>749</v>
-      </c>
-      <c r="I263" t="s">
-        <v>785</v>
-      </c>
-      <c r="J263" t="s">
-        <v>794</v>
-      </c>
-      <c r="K263" t="s">
-        <v>795</v>
-      </c>
-      <c r="L263" t="s">
-        <v>790</v>
-      </c>
-      <c r="M263" t="s">
-        <v>800</v>
-      </c>
-      <c r="N263" t="s">
+      <c r="P263" t="s">
         <v>807</v>
-      </c>
-      <c r="O263" t="s">
-        <v>808</v>
-      </c>
-      <c r="P263" t="s">
-        <v>809</v>
       </c>
       <c r="Q263">
         <v>0</v>
@@ -43533,22 +43535,22 @@
         <v>0</v>
       </c>
       <c r="C264" t="s">
+        <v>672</v>
+      </c>
+      <c r="D264" t="s">
+        <v>673</v>
+      </c>
+      <c r="E264" t="s">
         <v>674</v>
       </c>
-      <c r="D264" t="s">
+      <c r="F264" t="s">
         <v>675</v>
       </c>
-      <c r="E264" t="s">
+      <c r="G264" t="s">
         <v>676</v>
       </c>
-      <c r="F264" t="s">
+      <c r="H264" t="s">
         <v>677</v>
-      </c>
-      <c r="G264" t="s">
-        <v>678</v>
-      </c>
-      <c r="H264" t="s">
-        <v>679</v>
       </c>
       <c r="I264">
         <v>0</v>
@@ -43590,25 +43592,25 @@
         <v>0</v>
       </c>
       <c r="C265" t="s">
+        <v>672</v>
+      </c>
+      <c r="D265" t="s">
+        <v>678</v>
+      </c>
+      <c r="E265" t="s">
         <v>674</v>
       </c>
-      <c r="D265" t="s">
+      <c r="F265" t="s">
+        <v>675</v>
+      </c>
+      <c r="G265" t="s">
+        <v>676</v>
+      </c>
+      <c r="H265" t="s">
+        <v>679</v>
+      </c>
+      <c r="I265" t="s">
         <v>680</v>
-      </c>
-      <c r="E265" t="s">
-        <v>676</v>
-      </c>
-      <c r="F265" t="s">
-        <v>677</v>
-      </c>
-      <c r="G265" t="s">
-        <v>678</v>
-      </c>
-      <c r="H265" t="s">
-        <v>681</v>
-      </c>
-      <c r="I265" t="s">
-        <v>682</v>
       </c>
       <c r="J265">
         <v>0</v>
@@ -43647,28 +43649,28 @@
         <v>0</v>
       </c>
       <c r="C266" t="s">
+        <v>672</v>
+      </c>
+      <c r="D266" t="s">
+        <v>681</v>
+      </c>
+      <c r="E266" t="s">
         <v>674</v>
       </c>
-      <c r="D266" t="s">
+      <c r="F266" t="s">
+        <v>675</v>
+      </c>
+      <c r="G266" t="s">
+        <v>676</v>
+      </c>
+      <c r="H266" t="s">
+        <v>682</v>
+      </c>
+      <c r="I266" t="s">
+        <v>680</v>
+      </c>
+      <c r="J266" t="s">
         <v>683</v>
-      </c>
-      <c r="E266" t="s">
-        <v>676</v>
-      </c>
-      <c r="F266" t="s">
-        <v>677</v>
-      </c>
-      <c r="G266" t="s">
-        <v>678</v>
-      </c>
-      <c r="H266" t="s">
-        <v>684</v>
-      </c>
-      <c r="I266" t="s">
-        <v>682</v>
-      </c>
-      <c r="J266" t="s">
-        <v>685</v>
       </c>
       <c r="K266">
         <v>0</v>
@@ -43704,28 +43706,28 @@
         <v>0</v>
       </c>
       <c r="C267" t="s">
+        <v>672</v>
+      </c>
+      <c r="D267" t="s">
+        <v>684</v>
+      </c>
+      <c r="E267" t="s">
         <v>674</v>
       </c>
-      <c r="D267" t="s">
+      <c r="F267" t="s">
+        <v>675</v>
+      </c>
+      <c r="G267" t="s">
+        <v>685</v>
+      </c>
+      <c r="H267" t="s">
+        <v>682</v>
+      </c>
+      <c r="I267" t="s">
         <v>686</v>
       </c>
-      <c r="E267" t="s">
-        <v>676</v>
-      </c>
-      <c r="F267" t="s">
-        <v>677</v>
-      </c>
-      <c r="G267" t="s">
-        <v>687</v>
-      </c>
-      <c r="H267" t="s">
-        <v>684</v>
-      </c>
-      <c r="I267" t="s">
-        <v>688</v>
-      </c>
       <c r="J267" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="K267">
         <v>0</v>
@@ -43761,28 +43763,28 @@
         <v>0</v>
       </c>
       <c r="C268" t="s">
+        <v>672</v>
+      </c>
+      <c r="D268" t="s">
+        <v>687</v>
+      </c>
+      <c r="E268" t="s">
         <v>674</v>
       </c>
-      <c r="D268" t="s">
+      <c r="F268" t="s">
+        <v>675</v>
+      </c>
+      <c r="G268" t="s">
+        <v>688</v>
+      </c>
+      <c r="H268" t="s">
+        <v>682</v>
+      </c>
+      <c r="I268" t="s">
+        <v>686</v>
+      </c>
+      <c r="J268" t="s">
         <v>689</v>
-      </c>
-      <c r="E268" t="s">
-        <v>676</v>
-      </c>
-      <c r="F268" t="s">
-        <v>677</v>
-      </c>
-      <c r="G268" t="s">
-        <v>690</v>
-      </c>
-      <c r="H268" t="s">
-        <v>684</v>
-      </c>
-      <c r="I268" t="s">
-        <v>688</v>
-      </c>
-      <c r="J268" t="s">
-        <v>691</v>
       </c>
       <c r="K268">
         <v>0</v>
@@ -43818,31 +43820,31 @@
         <v>0</v>
       </c>
       <c r="C269" t="s">
+        <v>672</v>
+      </c>
+      <c r="D269" t="s">
+        <v>690</v>
+      </c>
+      <c r="E269" t="s">
         <v>674</v>
       </c>
-      <c r="D269" t="s">
+      <c r="F269" t="s">
+        <v>675</v>
+      </c>
+      <c r="G269" t="s">
+        <v>691</v>
+      </c>
+      <c r="H269" t="s">
+        <v>682</v>
+      </c>
+      <c r="I269" t="s">
+        <v>686</v>
+      </c>
+      <c r="J269" t="s">
+        <v>689</v>
+      </c>
+      <c r="K269" t="s">
         <v>692</v>
-      </c>
-      <c r="E269" t="s">
-        <v>676</v>
-      </c>
-      <c r="F269" t="s">
-        <v>677</v>
-      </c>
-      <c r="G269" t="s">
-        <v>693</v>
-      </c>
-      <c r="H269" t="s">
-        <v>684</v>
-      </c>
-      <c r="I269" t="s">
-        <v>688</v>
-      </c>
-      <c r="J269" t="s">
-        <v>691</v>
-      </c>
-      <c r="K269" t="s">
-        <v>694</v>
       </c>
       <c r="L269">
         <v>0</v>
@@ -43875,31 +43877,31 @@
         <v>0</v>
       </c>
       <c r="C270" t="s">
+        <v>672</v>
+      </c>
+      <c r="D270" t="s">
+        <v>693</v>
+      </c>
+      <c r="E270" t="s">
         <v>674</v>
       </c>
-      <c r="D270" t="s">
+      <c r="F270" t="s">
+        <v>675</v>
+      </c>
+      <c r="G270" t="s">
+        <v>694</v>
+      </c>
+      <c r="H270" t="s">
         <v>695</v>
       </c>
-      <c r="E270" t="s">
-        <v>676</v>
-      </c>
-      <c r="F270" t="s">
-        <v>677</v>
-      </c>
-      <c r="G270" t="s">
+      <c r="I270" t="s">
+        <v>689</v>
+      </c>
+      <c r="J270" t="s">
         <v>696</v>
       </c>
-      <c r="H270" t="s">
+      <c r="K270" t="s">
         <v>697</v>
-      </c>
-      <c r="I270" t="s">
-        <v>691</v>
-      </c>
-      <c r="J270" t="s">
-        <v>698</v>
-      </c>
-      <c r="K270" t="s">
-        <v>699</v>
       </c>
       <c r="L270">
         <v>0</v>
@@ -43932,31 +43934,31 @@
         <v>0</v>
       </c>
       <c r="C271" t="s">
+        <v>672</v>
+      </c>
+      <c r="D271" t="s">
+        <v>698</v>
+      </c>
+      <c r="E271" t="s">
         <v>674</v>
       </c>
-      <c r="D271" t="s">
-        <v>700</v>
-      </c>
-      <c r="E271" t="s">
-        <v>676</v>
-      </c>
       <c r="F271" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G271" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="H271" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="I271" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="J271" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="K271" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="L271">
         <v>0</v>
@@ -43989,31 +43991,31 @@
         <v>0</v>
       </c>
       <c r="C272" t="s">
+        <v>672</v>
+      </c>
+      <c r="D272" t="s">
+        <v>700</v>
+      </c>
+      <c r="E272" t="s">
         <v>674</v>
       </c>
-      <c r="D272" t="s">
+      <c r="F272" t="s">
+        <v>675</v>
+      </c>
+      <c r="G272" t="s">
+        <v>695</v>
+      </c>
+      <c r="H272" t="s">
+        <v>701</v>
+      </c>
+      <c r="I272" t="s">
+        <v>696</v>
+      </c>
+      <c r="J272" t="s">
         <v>702</v>
       </c>
-      <c r="E272" t="s">
-        <v>676</v>
-      </c>
-      <c r="F272" t="s">
-        <v>677</v>
-      </c>
-      <c r="G272" t="s">
-        <v>697</v>
-      </c>
-      <c r="H272" t="s">
+      <c r="K272" t="s">
         <v>703</v>
-      </c>
-      <c r="I272" t="s">
-        <v>698</v>
-      </c>
-      <c r="J272" t="s">
-        <v>704</v>
-      </c>
-      <c r="K272" t="s">
-        <v>705</v>
       </c>
       <c r="L272">
         <v>0</v>
@@ -44046,31 +44048,31 @@
         <v>0</v>
       </c>
       <c r="C273" t="s">
+        <v>672</v>
+      </c>
+      <c r="D273" t="s">
+        <v>704</v>
+      </c>
+      <c r="E273" t="s">
         <v>674</v>
       </c>
-      <c r="D273" t="s">
+      <c r="F273" t="s">
+        <v>675</v>
+      </c>
+      <c r="G273" t="s">
+        <v>701</v>
+      </c>
+      <c r="H273" t="s">
+        <v>705</v>
+      </c>
+      <c r="I273" t="s">
+        <v>702</v>
+      </c>
+      <c r="J273" t="s">
         <v>706</v>
       </c>
-      <c r="E273" t="s">
-        <v>676</v>
-      </c>
-      <c r="F273" t="s">
-        <v>677</v>
-      </c>
-      <c r="G273" t="s">
-        <v>703</v>
-      </c>
-      <c r="H273" t="s">
+      <c r="K273" t="s">
         <v>707</v>
-      </c>
-      <c r="I273" t="s">
-        <v>704</v>
-      </c>
-      <c r="J273" t="s">
-        <v>708</v>
-      </c>
-      <c r="K273" t="s">
-        <v>709</v>
       </c>
       <c r="L273">
         <v>0</v>
@@ -44103,31 +44105,31 @@
         <v>0</v>
       </c>
       <c r="C274" t="s">
+        <v>672</v>
+      </c>
+      <c r="D274" t="s">
+        <v>708</v>
+      </c>
+      <c r="E274" t="s">
         <v>674</v>
       </c>
-      <c r="D274" t="s">
+      <c r="F274" t="s">
+        <v>675</v>
+      </c>
+      <c r="G274" t="s">
+        <v>705</v>
+      </c>
+      <c r="H274" t="s">
+        <v>709</v>
+      </c>
+      <c r="I274" t="s">
+        <v>706</v>
+      </c>
+      <c r="J274" t="s">
         <v>710</v>
       </c>
-      <c r="E274" t="s">
-        <v>676</v>
-      </c>
-      <c r="F274" t="s">
-        <v>677</v>
-      </c>
-      <c r="G274" t="s">
-        <v>707</v>
-      </c>
-      <c r="H274" t="s">
+      <c r="K274" t="s">
         <v>711</v>
-      </c>
-      <c r="I274" t="s">
-        <v>708</v>
-      </c>
-      <c r="J274" t="s">
-        <v>712</v>
-      </c>
-      <c r="K274" t="s">
-        <v>713</v>
       </c>
       <c r="L274">
         <v>0</v>
@@ -44160,31 +44162,31 @@
         <v>0</v>
       </c>
       <c r="C275" t="s">
+        <v>672</v>
+      </c>
+      <c r="D275" t="s">
+        <v>712</v>
+      </c>
+      <c r="E275" t="s">
         <v>674</v>
       </c>
-      <c r="D275" t="s">
+      <c r="F275" t="s">
+        <v>675</v>
+      </c>
+      <c r="G275" t="s">
+        <v>709</v>
+      </c>
+      <c r="H275" t="s">
+        <v>713</v>
+      </c>
+      <c r="I275" t="s">
+        <v>710</v>
+      </c>
+      <c r="J275" t="s">
         <v>714</v>
       </c>
-      <c r="E275" t="s">
-        <v>676</v>
-      </c>
-      <c r="F275" t="s">
-        <v>677</v>
-      </c>
-      <c r="G275" t="s">
-        <v>711</v>
-      </c>
-      <c r="H275" t="s">
+      <c r="K275" t="s">
         <v>715</v>
-      </c>
-      <c r="I275" t="s">
-        <v>712</v>
-      </c>
-      <c r="J275" t="s">
-        <v>716</v>
-      </c>
-      <c r="K275" t="s">
-        <v>717</v>
       </c>
       <c r="L275">
         <v>0</v>
@@ -44217,31 +44219,31 @@
         <v>0</v>
       </c>
       <c r="C276" t="s">
+        <v>672</v>
+      </c>
+      <c r="D276" t="s">
+        <v>716</v>
+      </c>
+      <c r="E276" t="s">
         <v>674</v>
       </c>
-      <c r="D276" t="s">
+      <c r="F276" t="s">
+        <v>675</v>
+      </c>
+      <c r="G276" t="s">
+        <v>713</v>
+      </c>
+      <c r="H276" t="s">
+        <v>717</v>
+      </c>
+      <c r="I276" t="s">
+        <v>714</v>
+      </c>
+      <c r="J276" t="s">
         <v>718</v>
       </c>
-      <c r="E276" t="s">
-        <v>676</v>
-      </c>
-      <c r="F276" t="s">
-        <v>677</v>
-      </c>
-      <c r="G276" t="s">
-        <v>715</v>
-      </c>
-      <c r="H276" t="s">
+      <c r="K276" t="s">
         <v>719</v>
-      </c>
-      <c r="I276" t="s">
-        <v>716</v>
-      </c>
-      <c r="J276" t="s">
-        <v>720</v>
-      </c>
-      <c r="K276" t="s">
-        <v>721</v>
       </c>
       <c r="L276">
         <v>0</v>
@@ -44274,31 +44276,31 @@
         <v>0</v>
       </c>
       <c r="C277" t="s">
+        <v>672</v>
+      </c>
+      <c r="D277" t="s">
+        <v>720</v>
+      </c>
+      <c r="E277" t="s">
         <v>674</v>
       </c>
-      <c r="D277" t="s">
+      <c r="F277" t="s">
+        <v>675</v>
+      </c>
+      <c r="G277" t="s">
+        <v>717</v>
+      </c>
+      <c r="H277" t="s">
+        <v>721</v>
+      </c>
+      <c r="I277" t="s">
+        <v>718</v>
+      </c>
+      <c r="J277" t="s">
         <v>722</v>
       </c>
-      <c r="E277" t="s">
-        <v>676</v>
-      </c>
-      <c r="F277" t="s">
-        <v>677</v>
-      </c>
-      <c r="G277" t="s">
-        <v>719</v>
-      </c>
-      <c r="H277" t="s">
+      <c r="K277" t="s">
         <v>723</v>
-      </c>
-      <c r="I277" t="s">
-        <v>720</v>
-      </c>
-      <c r="J277" t="s">
-        <v>724</v>
-      </c>
-      <c r="K277" t="s">
-        <v>725</v>
       </c>
       <c r="L277">
         <v>0</v>
@@ -44331,31 +44333,31 @@
         <v>0</v>
       </c>
       <c r="C278" t="s">
+        <v>672</v>
+      </c>
+      <c r="D278" t="s">
+        <v>724</v>
+      </c>
+      <c r="E278" t="s">
         <v>674</v>
       </c>
-      <c r="D278" t="s">
+      <c r="F278" t="s">
+        <v>675</v>
+      </c>
+      <c r="G278" t="s">
+        <v>721</v>
+      </c>
+      <c r="H278" t="s">
+        <v>725</v>
+      </c>
+      <c r="I278" t="s">
+        <v>722</v>
+      </c>
+      <c r="J278" t="s">
         <v>726</v>
       </c>
-      <c r="E278" t="s">
-        <v>676</v>
-      </c>
-      <c r="F278" t="s">
-        <v>677</v>
-      </c>
-      <c r="G278" t="s">
-        <v>723</v>
-      </c>
-      <c r="H278" t="s">
+      <c r="K278" t="s">
         <v>727</v>
-      </c>
-      <c r="I278" t="s">
-        <v>724</v>
-      </c>
-      <c r="J278" t="s">
-        <v>728</v>
-      </c>
-      <c r="K278" t="s">
-        <v>729</v>
       </c>
       <c r="L278">
         <v>0</v>
@@ -44388,31 +44390,31 @@
         <v>0</v>
       </c>
       <c r="C279" t="s">
+        <v>672</v>
+      </c>
+      <c r="D279" t="s">
+        <v>728</v>
+      </c>
+      <c r="E279" t="s">
         <v>674</v>
       </c>
-      <c r="D279" t="s">
+      <c r="F279" t="s">
+        <v>675</v>
+      </c>
+      <c r="G279" t="s">
+        <v>725</v>
+      </c>
+      <c r="H279" t="s">
+        <v>729</v>
+      </c>
+      <c r="I279" t="s">
+        <v>726</v>
+      </c>
+      <c r="J279" t="s">
         <v>730</v>
       </c>
-      <c r="E279" t="s">
-        <v>676</v>
-      </c>
-      <c r="F279" t="s">
-        <v>677</v>
-      </c>
-      <c r="G279" t="s">
-        <v>727</v>
-      </c>
-      <c r="H279" t="s">
+      <c r="K279" t="s">
         <v>731</v>
-      </c>
-      <c r="I279" t="s">
-        <v>728</v>
-      </c>
-      <c r="J279" t="s">
-        <v>732</v>
-      </c>
-      <c r="K279" t="s">
-        <v>733</v>
       </c>
       <c r="L279">
         <v>0</v>
@@ -44445,31 +44447,31 @@
         <v>0</v>
       </c>
       <c r="C280" t="s">
+        <v>672</v>
+      </c>
+      <c r="D280" t="s">
+        <v>732</v>
+      </c>
+      <c r="E280" t="s">
         <v>674</v>
       </c>
-      <c r="D280" t="s">
+      <c r="F280" t="s">
+        <v>675</v>
+      </c>
+      <c r="G280" t="s">
+        <v>729</v>
+      </c>
+      <c r="H280" t="s">
+        <v>733</v>
+      </c>
+      <c r="I280" t="s">
+        <v>730</v>
+      </c>
+      <c r="J280" t="s">
         <v>734</v>
       </c>
-      <c r="E280" t="s">
-        <v>676</v>
-      </c>
-      <c r="F280" t="s">
-        <v>677</v>
-      </c>
-      <c r="G280" t="s">
-        <v>731</v>
-      </c>
-      <c r="H280" t="s">
+      <c r="K280" t="s">
         <v>735</v>
-      </c>
-      <c r="I280" t="s">
-        <v>732</v>
-      </c>
-      <c r="J280" t="s">
-        <v>736</v>
-      </c>
-      <c r="K280" t="s">
-        <v>737</v>
       </c>
       <c r="L280">
         <v>0</v>
@@ -44502,34 +44504,34 @@
         <v>0</v>
       </c>
       <c r="C281" t="s">
+        <v>672</v>
+      </c>
+      <c r="D281" t="s">
+        <v>736</v>
+      </c>
+      <c r="E281" t="s">
         <v>674</v>
       </c>
-      <c r="D281" t="s">
+      <c r="F281" t="s">
+        <v>675</v>
+      </c>
+      <c r="G281" t="s">
+        <v>719</v>
+      </c>
+      <c r="H281" t="s">
+        <v>737</v>
+      </c>
+      <c r="I281" t="s">
         <v>738</v>
       </c>
-      <c r="E281" t="s">
-        <v>676</v>
-      </c>
-      <c r="F281" t="s">
-        <v>677</v>
-      </c>
-      <c r="G281" t="s">
-        <v>721</v>
-      </c>
-      <c r="H281" t="s">
+      <c r="J281" t="s">
+        <v>734</v>
+      </c>
+      <c r="K281" t="s">
         <v>739</v>
       </c>
-      <c r="I281" t="s">
+      <c r="L281" t="s">
         <v>740</v>
-      </c>
-      <c r="J281" t="s">
-        <v>736</v>
-      </c>
-      <c r="K281" t="s">
-        <v>741</v>
-      </c>
-      <c r="L281" t="s">
-        <v>742</v>
       </c>
       <c r="M281">
         <v>0</v>
@@ -44559,34 +44561,34 @@
         <v>0</v>
       </c>
       <c r="C282" t="s">
+        <v>672</v>
+      </c>
+      <c r="D282" t="s">
+        <v>741</v>
+      </c>
+      <c r="E282" t="s">
         <v>674</v>
       </c>
-      <c r="D282" t="s">
-        <v>743</v>
-      </c>
-      <c r="E282" t="s">
-        <v>676</v>
-      </c>
       <c r="F282" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G282" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="H282" t="s">
+        <v>737</v>
+      </c>
+      <c r="I282" t="s">
+        <v>738</v>
+      </c>
+      <c r="J282" t="s">
+        <v>734</v>
+      </c>
+      <c r="K282" t="s">
         <v>739</v>
       </c>
-      <c r="I282" t="s">
+      <c r="L282" t="s">
         <v>740</v>
-      </c>
-      <c r="J282" t="s">
-        <v>736</v>
-      </c>
-      <c r="K282" t="s">
-        <v>741</v>
-      </c>
-      <c r="L282" t="s">
-        <v>742</v>
       </c>
       <c r="M282">
         <v>0</v>
@@ -44616,34 +44618,34 @@
         <v>0</v>
       </c>
       <c r="C283" t="s">
+        <v>672</v>
+      </c>
+      <c r="D283" t="s">
+        <v>742</v>
+      </c>
+      <c r="E283" t="s">
         <v>674</v>
       </c>
-      <c r="D283" t="s">
-        <v>744</v>
-      </c>
-      <c r="E283" t="s">
-        <v>676</v>
-      </c>
       <c r="F283" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G283" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="H283" t="s">
+        <v>737</v>
+      </c>
+      <c r="I283" t="s">
+        <v>738</v>
+      </c>
+      <c r="J283" t="s">
+        <v>734</v>
+      </c>
+      <c r="K283" t="s">
         <v>739</v>
       </c>
-      <c r="I283" t="s">
+      <c r="L283" t="s">
         <v>740</v>
-      </c>
-      <c r="J283" t="s">
-        <v>736</v>
-      </c>
-      <c r="K283" t="s">
-        <v>741</v>
-      </c>
-      <c r="L283" t="s">
-        <v>742</v>
       </c>
       <c r="M283">
         <v>0</v>
@@ -44673,16 +44675,16 @@
         <v>0</v>
       </c>
       <c r="C284" t="s">
+        <v>808</v>
+      </c>
+      <c r="D284" t="s">
+        <v>809</v>
+      </c>
+      <c r="E284" t="s">
         <v>810</v>
       </c>
-      <c r="D284" t="s">
+      <c r="F284" t="s">
         <v>811</v>
-      </c>
-      <c r="E284" t="s">
-        <v>812</v>
-      </c>
-      <c r="F284" t="s">
-        <v>813</v>
       </c>
       <c r="G284">
         <v>0</v>
@@ -44730,16 +44732,16 @@
         <v>0</v>
       </c>
       <c r="C285" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D285" t="s">
+        <v>812</v>
+      </c>
+      <c r="E285" t="s">
+        <v>813</v>
+      </c>
+      <c r="F285" t="s">
         <v>814</v>
-      </c>
-      <c r="E285" t="s">
-        <v>815</v>
-      </c>
-      <c r="F285" t="s">
-        <v>816</v>
       </c>
       <c r="G285">
         <v>0.1</v>
@@ -44787,16 +44789,16 @@
         <v>0</v>
       </c>
       <c r="C286" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D286" t="s">
+        <v>815</v>
+      </c>
+      <c r="E286" t="s">
+        <v>816</v>
+      </c>
+      <c r="F286" t="s">
         <v>817</v>
-      </c>
-      <c r="E286" t="s">
-        <v>818</v>
-      </c>
-      <c r="F286" t="s">
-        <v>819</v>
       </c>
       <c r="G286">
         <v>0</v>
@@ -44844,16 +44846,16 @@
         <v>0</v>
       </c>
       <c r="C287" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D287" t="s">
+        <v>818</v>
+      </c>
+      <c r="E287" t="s">
+        <v>819</v>
+      </c>
+      <c r="F287" t="s">
         <v>820</v>
-      </c>
-      <c r="E287" t="s">
-        <v>821</v>
-      </c>
-      <c r="F287" t="s">
-        <v>822</v>
       </c>
       <c r="G287">
         <v>0</v>
@@ -44901,16 +44903,16 @@
         <v>0</v>
       </c>
       <c r="C288" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D288" t="s">
+        <v>821</v>
+      </c>
+      <c r="E288" t="s">
+        <v>822</v>
+      </c>
+      <c r="F288" t="s">
         <v>823</v>
-      </c>
-      <c r="E288" t="s">
-        <v>824</v>
-      </c>
-      <c r="F288" t="s">
-        <v>825</v>
       </c>
       <c r="G288">
         <v>0.2</v>
@@ -44958,16 +44960,16 @@
         <v>0</v>
       </c>
       <c r="C289" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="F289" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="G289">
         <v>0.5</v>
@@ -45015,16 +45017,16 @@
         <v>0</v>
       </c>
       <c r="C290" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D290" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E290" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="F290" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="G290">
         <v>1000</v>
@@ -45072,16 +45074,16 @@
         <v>0</v>
       </c>
       <c r="C291" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D291" t="s">
+        <v>827</v>
+      </c>
+      <c r="E291" t="s">
+        <v>828</v>
+      </c>
+      <c r="F291" t="s">
         <v>829</v>
-      </c>
-      <c r="E291" t="s">
-        <v>830</v>
-      </c>
-      <c r="F291" t="s">
-        <v>831</v>
       </c>
       <c r="G291">
         <v>0</v>
@@ -45129,16 +45131,16 @@
         <v>0</v>
       </c>
       <c r="C292" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D292" t="s">
+        <v>830</v>
+      </c>
+      <c r="E292" t="s">
+        <v>831</v>
+      </c>
+      <c r="F292" t="s">
         <v>832</v>
-      </c>
-      <c r="E292" t="s">
-        <v>833</v>
-      </c>
-      <c r="F292" t="s">
-        <v>834</v>
       </c>
       <c r="G292">
         <v>30</v>
@@ -45186,16 +45188,16 @@
         <v>0</v>
       </c>
       <c r="C293" t="s">
+        <v>833</v>
+      </c>
+      <c r="D293" t="s">
+        <v>834</v>
+      </c>
+      <c r="E293" t="s">
         <v>835</v>
       </c>
-      <c r="D293" t="s">
+      <c r="F293" t="s">
         <v>836</v>
-      </c>
-      <c r="E293" t="s">
-        <v>837</v>
-      </c>
-      <c r="F293" t="s">
-        <v>838</v>
       </c>
       <c r="G293">
         <v>0.75</v>
@@ -45243,13 +45245,13 @@
         <v>0</v>
       </c>
       <c r="C294" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D294" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="E294" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="F294">
         <v>0</v>
@@ -45300,16 +45302,16 @@
         <v>0</v>
       </c>
       <c r="C295" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D295" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="E295" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="F295" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="G295">
         <v>45</v>
@@ -45357,16 +45359,16 @@
         <v>0</v>
       </c>
       <c r="C296" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D296" t="s">
+        <v>841</v>
+      </c>
+      <c r="E296" t="s">
+        <v>842</v>
+      </c>
+      <c r="F296" t="s">
         <v>843</v>
-      </c>
-      <c r="E296" t="s">
-        <v>844</v>
-      </c>
-      <c r="F296" t="s">
-        <v>845</v>
       </c>
       <c r="G296">
         <v>0</v>
@@ -45414,16 +45416,16 @@
         <v>0</v>
       </c>
       <c r="C297" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D297" t="s">
+        <v>844</v>
+      </c>
+      <c r="E297" t="s">
+        <v>845</v>
+      </c>
+      <c r="F297" t="s">
         <v>846</v>
-      </c>
-      <c r="E297" t="s">
-        <v>847</v>
-      </c>
-      <c r="F297" t="s">
-        <v>848</v>
       </c>
       <c r="G297">
         <v>0.1</v>
@@ -45471,16 +45473,16 @@
         <v>0</v>
       </c>
       <c r="C298" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D298" t="s">
+        <v>934</v>
+      </c>
+      <c r="E298" t="s">
+        <v>935</v>
+      </c>
+      <c r="F298" t="s">
         <v>936</v>
-      </c>
-      <c r="E298" t="s">
-        <v>937</v>
-      </c>
-      <c r="F298" t="s">
-        <v>938</v>
       </c>
       <c r="G298">
         <v>50000</v>
@@ -45528,16 +45530,16 @@
         <v>0</v>
       </c>
       <c r="C299" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D299" t="s">
+        <v>937</v>
+      </c>
+      <c r="E299" t="s">
+        <v>938</v>
+      </c>
+      <c r="F299" t="s">
         <v>939</v>
-      </c>
-      <c r="E299" t="s">
-        <v>940</v>
-      </c>
-      <c r="F299" t="s">
-        <v>941</v>
       </c>
       <c r="G299">
         <v>10</v>
@@ -45585,16 +45587,16 @@
         <v>0</v>
       </c>
       <c r="C300" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D300" t="s">
+        <v>940</v>
+      </c>
+      <c r="E300" t="s">
+        <v>941</v>
+      </c>
+      <c r="F300" t="s">
         <v>942</v>
-      </c>
-      <c r="E300" t="s">
-        <v>943</v>
-      </c>
-      <c r="F300" t="s">
-        <v>944</v>
       </c>
       <c r="G300">
         <v>75</v>
@@ -45642,16 +45644,16 @@
         <v>0</v>
       </c>
       <c r="C301" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D301" t="s">
+        <v>943</v>
+      </c>
+      <c r="E301" t="s">
+        <v>944</v>
+      </c>
+      <c r="F301" t="s">
         <v>945</v>
-      </c>
-      <c r="E301" t="s">
-        <v>946</v>
-      </c>
-      <c r="F301" t="s">
-        <v>947</v>
       </c>
       <c r="G301">
         <v>25</v>
@@ -45699,16 +45701,16 @@
         <v>0</v>
       </c>
       <c r="C302" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D302" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="E302" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="F302" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="G302">
         <v>5</v>
@@ -45756,16 +45758,16 @@
         <v>0</v>
       </c>
       <c r="C303" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D303" t="s">
+        <v>948</v>
+      </c>
+      <c r="E303" t="s">
+        <v>949</v>
+      </c>
+      <c r="F303" t="s">
         <v>950</v>
-      </c>
-      <c r="E303" t="s">
-        <v>951</v>
-      </c>
-      <c r="F303" t="s">
-        <v>952</v>
       </c>
       <c r="G303">
         <v>0.6</v>
@@ -45813,16 +45815,16 @@
         <v>0</v>
       </c>
       <c r="C304" t="s">
+        <v>871</v>
+      </c>
+      <c r="D304" t="s">
+        <v>872</v>
+      </c>
+      <c r="E304" t="s">
         <v>873</v>
       </c>
-      <c r="D304" t="s">
+      <c r="F304" t="s">
         <v>874</v>
-      </c>
-      <c r="E304" t="s">
-        <v>875</v>
-      </c>
-      <c r="F304" t="s">
-        <v>876</v>
       </c>
       <c r="G304">
         <v>25</v>
@@ -45831,7 +45833,7 @@
         <v>25</v>
       </c>
       <c r="I304" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="J304">
         <v>0</v>
@@ -45870,16 +45872,16 @@
         <v>0</v>
       </c>
       <c r="C305" t="s">
+        <v>871</v>
+      </c>
+      <c r="D305" t="s">
+        <v>876</v>
+      </c>
+      <c r="E305" t="s">
         <v>873</v>
       </c>
-      <c r="D305" t="s">
-        <v>878</v>
-      </c>
-      <c r="E305" t="s">
-        <v>875</v>
-      </c>
       <c r="F305" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="G305">
         <v>20</v>
@@ -45888,7 +45890,7 @@
         <v>20</v>
       </c>
       <c r="I305" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="J305">
         <v>0</v>
@@ -45927,16 +45929,16 @@
         <v>0</v>
       </c>
       <c r="C306" t="s">
+        <v>871</v>
+      </c>
+      <c r="D306" t="s">
+        <v>878</v>
+      </c>
+      <c r="E306" t="s">
         <v>873</v>
       </c>
-      <c r="D306" t="s">
-        <v>880</v>
-      </c>
-      <c r="E306" t="s">
-        <v>875</v>
-      </c>
       <c r="F306" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G306">
         <v>3</v>
@@ -45945,7 +45947,7 @@
         <v>1.5</v>
       </c>
       <c r="I306" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="J306">
         <v>0</v>
@@ -45984,16 +45986,16 @@
         <v>0</v>
       </c>
       <c r="C307" t="s">
+        <v>871</v>
+      </c>
+      <c r="D307" t="s">
+        <v>880</v>
+      </c>
+      <c r="E307" t="s">
         <v>873</v>
       </c>
-      <c r="D307" t="s">
-        <v>882</v>
-      </c>
-      <c r="E307" t="s">
-        <v>875</v>
-      </c>
       <c r="F307" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="G307">
         <v>20</v>
@@ -46002,7 +46004,7 @@
         <v>20</v>
       </c>
       <c r="I307" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="J307">
         <v>0</v>
@@ -46041,16 +46043,16 @@
         <v>0</v>
       </c>
       <c r="C308" t="s">
+        <v>871</v>
+      </c>
+      <c r="D308" t="s">
+        <v>882</v>
+      </c>
+      <c r="E308" t="s">
         <v>873</v>
       </c>
-      <c r="D308" t="s">
-        <v>884</v>
-      </c>
-      <c r="E308" t="s">
-        <v>875</v>
-      </c>
       <c r="F308" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G308">
         <v>3</v>
@@ -46059,7 +46061,7 @@
         <v>1.5</v>
       </c>
       <c r="I308" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="J308">
         <v>0</v>
@@ -46098,16 +46100,16 @@
         <v>0</v>
       </c>
       <c r="C309" t="s">
+        <v>871</v>
+      </c>
+      <c r="D309" t="s">
+        <v>884</v>
+      </c>
+      <c r="E309" t="s">
         <v>873</v>
       </c>
-      <c r="D309" t="s">
-        <v>886</v>
-      </c>
-      <c r="E309" t="s">
-        <v>875</v>
-      </c>
       <c r="F309" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="G309">
         <v>3</v>
@@ -46116,7 +46118,7 @@
         <v>1.5</v>
       </c>
       <c r="I309" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="J309">
         <v>0</v>
@@ -46155,16 +46157,16 @@
         <v>0</v>
       </c>
       <c r="C310" t="s">
+        <v>871</v>
+      </c>
+      <c r="D310" t="s">
+        <v>886</v>
+      </c>
+      <c r="E310" t="s">
         <v>873</v>
       </c>
-      <c r="D310" t="s">
-        <v>888</v>
-      </c>
-      <c r="E310" t="s">
-        <v>875</v>
-      </c>
       <c r="F310" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="G310">
         <v>3</v>
@@ -46173,7 +46175,7 @@
         <v>1.5</v>
       </c>
       <c r="I310" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="J310">
         <v>0</v>
@@ -46212,16 +46214,16 @@
         <v>0</v>
       </c>
       <c r="C311" t="s">
+        <v>871</v>
+      </c>
+      <c r="D311" t="s">
+        <v>888</v>
+      </c>
+      <c r="E311" t="s">
         <v>873</v>
       </c>
-      <c r="D311" t="s">
-        <v>890</v>
-      </c>
-      <c r="E311" t="s">
-        <v>875</v>
-      </c>
       <c r="F311" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G311">
         <v>25</v>
@@ -46230,7 +46232,7 @@
         <v>25</v>
       </c>
       <c r="I311" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="J311">
         <v>0</v>
@@ -46269,16 +46271,16 @@
         <v>0</v>
       </c>
       <c r="C312" t="s">
+        <v>871</v>
+      </c>
+      <c r="D312" t="s">
+        <v>890</v>
+      </c>
+      <c r="E312" t="s">
         <v>873</v>
       </c>
-      <c r="D312" t="s">
-        <v>892</v>
-      </c>
-      <c r="E312" t="s">
-        <v>875</v>
-      </c>
       <c r="F312" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="G312">
         <v>5</v>
@@ -46287,7 +46289,7 @@
         <v>2.5</v>
       </c>
       <c r="I312" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="J312">
         <v>0</v>
@@ -46326,19 +46328,19 @@
         <v>0</v>
       </c>
       <c r="C313" t="s">
+        <v>892</v>
+      </c>
+      <c r="D313" t="s">
+        <v>893</v>
+      </c>
+      <c r="E313" s="3" t="s">
+        <v>999</v>
+      </c>
+      <c r="F313" t="s">
         <v>894</v>
       </c>
-      <c r="D313" t="s">
-        <v>895</v>
-      </c>
-      <c r="E313" s="3" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F313" t="s">
-        <v>896</v>
-      </c>
       <c r="G313" s="3" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="H313">
         <v>3</v>
@@ -46383,16 +46385,16 @@
         <v>0</v>
       </c>
       <c r="C314" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D314" t="s">
+        <v>895</v>
+      </c>
+      <c r="E314" t="s">
+        <v>896</v>
+      </c>
+      <c r="F314" t="s">
         <v>897</v>
-      </c>
-      <c r="E314" t="s">
-        <v>898</v>
-      </c>
-      <c r="F314" t="s">
-        <v>899</v>
       </c>
       <c r="G314">
         <v>5</v>
@@ -46440,16 +46442,16 @@
         <v>0</v>
       </c>
       <c r="C315" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D315" t="s">
+        <v>898</v>
+      </c>
+      <c r="E315" t="s">
+        <v>899</v>
+      </c>
+      <c r="F315" t="s">
         <v>900</v>
-      </c>
-      <c r="E315" t="s">
-        <v>901</v>
-      </c>
-      <c r="F315" t="s">
-        <v>902</v>
       </c>
       <c r="G315">
         <v>10</v>
@@ -46497,16 +46499,16 @@
         <v>0</v>
       </c>
       <c r="C316" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D316" t="s">
+        <v>901</v>
+      </c>
+      <c r="E316" t="s">
+        <v>902</v>
+      </c>
+      <c r="F316" t="s">
         <v>903</v>
-      </c>
-      <c r="E316" t="s">
-        <v>904</v>
-      </c>
-      <c r="F316" t="s">
-        <v>905</v>
       </c>
       <c r="G316">
         <v>10</v>
@@ -46554,16 +46556,16 @@
         <v>0</v>
       </c>
       <c r="C317" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D317" t="s">
+        <v>904</v>
+      </c>
+      <c r="E317" t="s">
+        <v>905</v>
+      </c>
+      <c r="F317" t="s">
         <v>906</v>
-      </c>
-      <c r="E317" t="s">
-        <v>907</v>
-      </c>
-      <c r="F317" t="s">
-        <v>908</v>
       </c>
       <c r="G317">
         <v>2</v>
@@ -46611,16 +46613,16 @@
         <v>0</v>
       </c>
       <c r="C318" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D318" t="s">
+        <v>907</v>
+      </c>
+      <c r="E318" t="s">
+        <v>908</v>
+      </c>
+      <c r="F318" t="s">
         <v>909</v>
-      </c>
-      <c r="E318" t="s">
-        <v>910</v>
-      </c>
-      <c r="F318" t="s">
-        <v>911</v>
       </c>
       <c r="G318">
         <v>5</v>
@@ -46668,16 +46670,16 @@
         <v>0</v>
       </c>
       <c r="C319" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D319" t="s">
+        <v>910</v>
+      </c>
+      <c r="E319" t="s">
+        <v>911</v>
+      </c>
+      <c r="F319" t="s">
         <v>912</v>
-      </c>
-      <c r="E319" t="s">
-        <v>913</v>
-      </c>
-      <c r="F319" t="s">
-        <v>914</v>
       </c>
       <c r="G319">
         <v>10</v>
@@ -46725,16 +46727,16 @@
         <v>0</v>
       </c>
       <c r="C320" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D320" t="s">
+        <v>913</v>
+      </c>
+      <c r="E320" t="s">
+        <v>914</v>
+      </c>
+      <c r="F320" t="s">
         <v>915</v>
-      </c>
-      <c r="E320" t="s">
-        <v>916</v>
-      </c>
-      <c r="F320" t="s">
-        <v>917</v>
       </c>
       <c r="G320">
         <v>20000</v>
@@ -46782,16 +46784,16 @@
         <v>0</v>
       </c>
       <c r="C321" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D321" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E321" t="s">
+        <v>1001</v>
+      </c>
+      <c r="F321" s="5" t="s">
         <v>1002</v>
-      </c>
-      <c r="E321" t="s">
-        <v>1003</v>
-      </c>
-      <c r="F321" s="5" t="s">
-        <v>1004</v>
       </c>
       <c r="G321">
         <v>0.35</v>
@@ -46839,16 +46841,16 @@
         <v>0</v>
       </c>
       <c r="C322" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="D322" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="E322" t="s">
         <v>39</v>
       </c>
       <c r="F322" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="G322">
         <v>1</v>
@@ -46896,16 +46898,16 @@
         <v>0</v>
       </c>
       <c r="C323" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="D323" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="E323" t="s">
         <v>39</v>
       </c>
       <c r="F323" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="G323">
         <v>1.35</v>
@@ -46953,16 +46955,16 @@
         <v>0</v>
       </c>
       <c r="C324" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="D324" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="E324" t="s">
         <v>39</v>
       </c>
       <c r="F324" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="G324">
         <v>1.75</v>
@@ -47010,16 +47012,16 @@
         <v>0</v>
       </c>
       <c r="C325" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="D325" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="E325" t="s">
         <v>39</v>
       </c>
       <c r="F325" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="G325">
         <v>2.2999999999999998</v>
@@ -47067,16 +47069,16 @@
         <v>0</v>
       </c>
       <c r="C326" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="D326" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="E326" t="s">
         <v>39</v>
       </c>
       <c r="F326" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="G326">
         <v>3</v>
@@ -47124,16 +47126,16 @@
         <v>0</v>
       </c>
       <c r="C327" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="D327" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="E327" t="s">
         <v>39</v>
       </c>
       <c r="F327" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="G327">
         <v>4</v>
@@ -47181,16 +47183,16 @@
         <v>0</v>
       </c>
       <c r="C328" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="D328" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="E328" t="s">
         <v>39</v>
       </c>
       <c r="F328" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="G328">
         <v>5.2</v>
@@ -47238,16 +47240,16 @@
         <v>0</v>
       </c>
       <c r="C329" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="D329" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="E329" t="s">
         <v>39</v>
       </c>
       <c r="F329" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="G329">
         <v>6.8</v>
@@ -47295,16 +47297,16 @@
         <v>0</v>
       </c>
       <c r="C330" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="D330" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="E330" t="s">
         <v>39</v>
       </c>
       <c r="F330" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="G330">
         <v>10.199999999999999</v>
@@ -47352,16 +47354,16 @@
         <v>0</v>
       </c>
       <c r="C331" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="D331" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="E331" t="s">
         <v>39</v>
       </c>
       <c r="F331" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="G331">
         <v>15.3</v>
@@ -47409,16 +47411,16 @@
         <v>0</v>
       </c>
       <c r="C332" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="D332" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="E332" t="s">
         <v>39</v>
       </c>
       <c r="F332" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="G332">
         <v>22.95</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1608E79-4DB4-4E06-96A0-4ABE11A9FF04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34CF0D0F-FF55-4381-81C5-78C21FE859FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -466,12 +466,6 @@
   </si>
   <si>
     <t>野外基礎生命恢復</t>
-  </si>
-  <si>
-    <t>(最大生命×a% + b )/秒</t>
-  </si>
-  <si>
-    <t>a=生命加成比例 b=基礎值。</t>
   </si>
   <si>
     <t>全局減傷</t>
@@ -4027,6 +4021,14 @@
   </si>
   <si>
     <t>a=吸魔上限（定值）；0＝無上限。吸魔是定值：每次對敵人造成傷害固定回復的法力（舊版百分比以 1%＝1 轉換），單獨計算，與每秒法力恢復、造成的傷害皆無關。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(a + 加成)/秒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a=基礎生命回復定值。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5231,7 +5233,7 @@
         <v>基礎a + 技能熟練度等級 + 潛力天賦加成</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="G11">
         <f>計算表!G11</f>
@@ -5674,7 +5676,7 @@
         <v>（查表）</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G17">
         <f>計算表!G17</f>
@@ -5747,7 +5749,7 @@
         <v>（查表）</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G18">
         <f>計算表!G18</f>
@@ -5820,7 +5822,7 @@
         <v>（查表）</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G19">
         <f>計算表!G19</f>
@@ -5893,7 +5895,7 @@
         <v>（查表）</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G20">
         <f>計算表!G20</f>
@@ -5966,7 +5968,7 @@
         <v>（查表）</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G21">
         <f>計算表!G21</f>
@@ -6039,7 +6041,7 @@
         <v>（查表）</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G22">
         <f>計算表!G22</f>
@@ -6112,7 +6114,7 @@
         <v>（查表）</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G23">
         <f>計算表!G23</f>
@@ -6185,7 +6187,7 @@
         <v>（查表）</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G24">
         <f>計算表!G24</f>
@@ -6258,7 +6260,7 @@
         <v>（查表）</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G25">
         <f>計算表!G25</f>
@@ -6331,7 +6333,7 @@
         <v>（查表）</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G26">
         <f>計算表!G26</f>
@@ -6404,7 +6406,7 @@
         <v>（查表）</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G27">
         <f>計算表!G27</f>
@@ -6477,7 +6479,7 @@
         <v>（查表）</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G28">
         <f>計算表!G28</f>
@@ -6550,7 +6552,7 @@
         <v>（查表）</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G29">
         <f>計算表!G29</f>
@@ -6623,7 +6625,7 @@
         <v>（查表）</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G30">
         <f>計算表!G30</f>
@@ -6696,7 +6698,7 @@
         <v>（查表）</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G31">
         <f>計算表!G31</f>
@@ -6769,7 +6771,7 @@
         <v>（查表）</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G32">
         <f>計算表!G32</f>
@@ -6842,7 +6844,7 @@
         <v>（查表）</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G33">
         <f>計算表!G33</f>
@@ -6915,7 +6917,7 @@
         <v>（查表）</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G34">
         <f>計算表!G34</f>
@@ -6988,7 +6990,7 @@
         <v>（查表）</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G35">
         <f>計算表!G35</f>
@@ -7061,7 +7063,7 @@
         <v>（查表）</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G36">
         <f>計算表!G36</f>
@@ -7134,7 +7136,7 @@
         <v>（查表）</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="G37">
         <f>計算表!G37</f>
@@ -8840,10 +8842,10 @@
       </c>
       <c r="G60">
         <f>計算表!G60</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="I60">
         <f>計算表!I60</f>
@@ -9212,7 +9214,7 @@
         <v>5</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="I65">
         <f>計算表!I65</f>
@@ -9285,7 +9287,7 @@
         <v>0.875</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="I66">
         <f>計算表!I66</f>
@@ -9576,7 +9578,7 @@
         <v>a=每點敏捷%。</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="H70">
         <f>計算表!H70</f>
@@ -9716,19 +9718,19 @@
       </c>
       <c r="E72" t="str">
         <f>計算表!E72</f>
-        <v>(最大生命×a% + b )/秒</v>
+        <v>(a + 加成)/秒</v>
       </c>
       <c r="F72" t="str">
         <f>計算表!F72</f>
-        <v>a=生命加成比例 b=基礎值。</v>
+        <v>a=基礎生命回復定值。</v>
       </c>
       <c r="G72">
         <f>計算表!G72</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H72">
         <f>計算表!H72</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I72">
         <f>計算表!I72</f>
@@ -11495,7 +11497,7 @@
         <v>忽略敵人防禦% = 穿透%/(穿透%+a)</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="G96">
         <f>計算表!G96</f>
@@ -13282,7 +13284,7 @@
         <v>0.5</v>
       </c>
       <c r="I120" s="7" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="J120">
         <f>計算表!J120</f>
@@ -15197,7 +15199,7 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條。</v>
       </c>
       <c r="G146" s="7" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="H146">
         <f>計算表!H146</f>
@@ -15270,13 +15272,13 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條。</v>
       </c>
       <c r="G147" s="7" t="s">
+        <v>1029</v>
+      </c>
+      <c r="H147" s="7" t="s">
+        <v>1030</v>
+      </c>
+      <c r="I147" s="7" t="s">
         <v>1031</v>
-      </c>
-      <c r="H147" s="7" t="s">
-        <v>1032</v>
-      </c>
-      <c r="I147" s="7" t="s">
-        <v>1033</v>
       </c>
       <c r="J147">
         <f>計算表!J147</f>
@@ -15341,20 +15343,20 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條。</v>
       </c>
       <c r="G148" s="7" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="H148" s="7" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="I148">
         <f>計算表!I148</f>
         <v>9.11754</v>
       </c>
       <c r="J148" s="7" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="K148" s="7" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="L148">
         <f>計算表!L148</f>
@@ -15411,22 +15413,22 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條。</v>
       </c>
       <c r="G149" s="7" t="s">
+        <v>1036</v>
+      </c>
+      <c r="H149" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="I149" s="7" t="s">
         <v>1038</v>
       </c>
-      <c r="H149" s="7" t="s">
+      <c r="J149" s="7" t="s">
         <v>1039</v>
       </c>
-      <c r="I149" s="7" t="s">
+      <c r="K149" s="7" t="s">
         <v>1040</v>
       </c>
-      <c r="J149" s="7" t="s">
+      <c r="L149" s="7" t="s">
         <v>1041</v>
-      </c>
-      <c r="K149" s="7" t="s">
-        <v>1042</v>
-      </c>
-      <c r="L149" s="7" t="s">
-        <v>1043</v>
       </c>
       <c r="M149">
         <f>計算表!M149</f>
@@ -15479,28 +15481,28 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條。</v>
       </c>
       <c r="G150" s="7" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H150" s="7" t="s">
+        <v>1043</v>
+      </c>
+      <c r="I150" s="7" t="s">
         <v>1044</v>
       </c>
-      <c r="H150" s="7" t="s">
+      <c r="J150" s="7" t="s">
         <v>1045</v>
       </c>
-      <c r="I150" s="7" t="s">
+      <c r="K150" s="7" t="s">
         <v>1046</v>
       </c>
-      <c r="J150" s="7" t="s">
+      <c r="L150" s="7" t="s">
         <v>1047</v>
       </c>
-      <c r="K150" s="7" t="s">
+      <c r="M150" s="7" t="s">
         <v>1048</v>
       </c>
-      <c r="L150" s="7" t="s">
+      <c r="N150" s="7" t="s">
         <v>1049</v>
-      </c>
-      <c r="M150" s="7" t="s">
-        <v>1050</v>
-      </c>
-      <c r="N150" s="7" t="s">
-        <v>1051</v>
       </c>
       <c r="O150">
         <f>計算表!O150</f>
@@ -15545,28 +15547,28 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條。</v>
       </c>
       <c r="G151" s="7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H151" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="I151" s="7" t="s">
         <v>1052</v>
       </c>
-      <c r="H151" s="7" t="s">
+      <c r="J151" s="7" t="s">
         <v>1053</v>
       </c>
-      <c r="I151" s="7" t="s">
+      <c r="K151" s="7" t="s">
         <v>1054</v>
       </c>
-      <c r="J151" s="7" t="s">
+      <c r="L151" s="7" t="s">
         <v>1055</v>
       </c>
-      <c r="K151" s="7" t="s">
+      <c r="M151" s="7" t="s">
         <v>1056</v>
       </c>
-      <c r="L151" s="7" t="s">
+      <c r="N151" s="7" t="s">
         <v>1057</v>
-      </c>
-      <c r="M151" s="7" t="s">
-        <v>1058</v>
-      </c>
-      <c r="N151" s="7" t="s">
-        <v>1059</v>
       </c>
       <c r="O151">
         <f>計算表!O151</f>
@@ -15611,31 +15613,31 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條 j=9條。</v>
       </c>
       <c r="G152" s="7" t="s">
+        <v>1058</v>
+      </c>
+      <c r="H152" s="7" t="s">
+        <v>1059</v>
+      </c>
+      <c r="I152" s="7" t="s">
         <v>1060</v>
       </c>
-      <c r="H152" s="7" t="s">
+      <c r="J152" s="7" t="s">
         <v>1061</v>
       </c>
-      <c r="I152" s="7" t="s">
+      <c r="K152" s="7" t="s">
         <v>1062</v>
       </c>
-      <c r="J152" s="7" t="s">
+      <c r="L152" s="7" t="s">
         <v>1063</v>
       </c>
-      <c r="K152" s="7" t="s">
+      <c r="M152" s="7" t="s">
         <v>1064</v>
       </c>
-      <c r="L152" s="7" t="s">
+      <c r="N152" s="7" t="s">
         <v>1065</v>
       </c>
-      <c r="M152" s="7" t="s">
+      <c r="O152" s="7" t="s">
         <v>1066</v>
-      </c>
-      <c r="N152" s="7" t="s">
-        <v>1067</v>
-      </c>
-      <c r="O152" s="7" t="s">
-        <v>1068</v>
       </c>
       <c r="P152">
         <f>計算表!P152</f>
@@ -15676,7 +15678,7 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條 j=9條 k=10條。</v>
       </c>
       <c r="G153" s="7" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="H153">
         <f>計算表!H153</f>
@@ -17159,7 +17161,7 @@
         <v>200</v>
       </c>
       <c r="H173" s="7" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="I173">
         <f>計算表!I173</f>
@@ -17746,7 +17748,7 @@
         <v>a=基礎權重 b=權重加成 c=加成上限 d=出現門檻。普通無加成。神鑄創世不參與此擲骰。(裝備合成才有作用，目前功能關閉中)</v>
       </c>
       <c r="G181" s="7" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="H181" t="str">
         <f>計算表!H181</f>
@@ -20565,7 +20567,7 @@
         <v>1</v>
       </c>
       <c r="I219" s="7" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="J219">
         <f>計算表!J220</f>
@@ -25580,10 +25582,10 @@
         <v>等級上限</v>
       </c>
       <c r="E287" s="7" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="F287" s="7" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="G287">
         <f>計算表!G291</f>
@@ -27214,7 +27216,7 @@
         <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數。</v>
       </c>
       <c r="G309" s="7" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="H309">
         <f>計算表!H325</f>
@@ -27583,7 +27585,7 @@
         <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數。</v>
       </c>
       <c r="G314" s="7" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="H314">
         <f>計算表!H330</f>
@@ -27861,16 +27863,16 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
+        <v>952</v>
+      </c>
+      <c r="D2" t="s">
+        <v>953</v>
+      </c>
+      <c r="E2" t="s">
         <v>954</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>955</v>
-      </c>
-      <c r="E2" t="s">
-        <v>956</v>
-      </c>
-      <c r="F2" t="s">
-        <v>957</v>
       </c>
       <c r="G2">
         <v>50000</v>
@@ -27918,16 +27920,16 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
+        <v>952</v>
+      </c>
+      <c r="D3" t="s">
+        <v>956</v>
+      </c>
+      <c r="E3" t="s">
         <v>954</v>
       </c>
-      <c r="D3" t="s">
-        <v>958</v>
-      </c>
-      <c r="E3" t="s">
-        <v>956</v>
-      </c>
       <c r="F3" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="G3">
         <v>500</v>
@@ -27975,16 +27977,16 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
+        <v>952</v>
+      </c>
+      <c r="D4" t="s">
+        <v>958</v>
+      </c>
+      <c r="E4" t="s">
         <v>954</v>
       </c>
-      <c r="D4" t="s">
-        <v>960</v>
-      </c>
-      <c r="E4" t="s">
-        <v>956</v>
-      </c>
       <c r="F4" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -28032,16 +28034,16 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
+        <v>845</v>
+      </c>
+      <c r="D5" t="s">
+        <v>846</v>
+      </c>
+      <c r="E5" t="s">
         <v>847</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>848</v>
-      </c>
-      <c r="E5" t="s">
-        <v>849</v>
-      </c>
-      <c r="F5" t="s">
-        <v>850</v>
       </c>
       <c r="G5">
         <v>24</v>
@@ -28089,16 +28091,16 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="D6" t="s">
+        <v>849</v>
+      </c>
+      <c r="E6" t="s">
+        <v>850</v>
+      </c>
+      <c r="F6" t="s">
         <v>851</v>
-      </c>
-      <c r="E6" t="s">
-        <v>852</v>
-      </c>
-      <c r="F6" t="s">
-        <v>853</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -28146,16 +28148,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="D7" t="s">
+        <v>852</v>
+      </c>
+      <c r="E7" t="s">
+        <v>853</v>
+      </c>
+      <c r="F7" t="s">
         <v>854</v>
-      </c>
-      <c r="E7" t="s">
-        <v>855</v>
-      </c>
-      <c r="F7" t="s">
-        <v>856</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -28203,16 +28205,16 @@
         <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="D8" t="s">
+        <v>855</v>
+      </c>
+      <c r="E8" t="s">
+        <v>856</v>
+      </c>
+      <c r="F8" t="s">
         <v>857</v>
-      </c>
-      <c r="E8" t="s">
-        <v>858</v>
-      </c>
-      <c r="F8" t="s">
-        <v>859</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -28605,13 +28607,13 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
+        <v>926</v>
+      </c>
+      <c r="E15" t="s">
+        <v>927</v>
+      </c>
+      <c r="F15" t="s">
         <v>928</v>
-      </c>
-      <c r="E15" t="s">
-        <v>929</v>
-      </c>
-      <c r="F15" t="s">
-        <v>930</v>
       </c>
       <c r="G15">
         <v>30</v>
@@ -28662,13 +28664,13 @@
         <v>18</v>
       </c>
       <c r="D16" t="s">
+        <v>929</v>
+      </c>
+      <c r="E16" t="s">
+        <v>930</v>
+      </c>
+      <c r="F16" t="s">
         <v>931</v>
-      </c>
-      <c r="E16" t="s">
-        <v>932</v>
-      </c>
-      <c r="F16" t="s">
-        <v>933</v>
       </c>
       <c r="G16">
         <v>1000</v>
@@ -29913,16 +29915,16 @@
         <v>0</v>
       </c>
       <c r="C38" t="s">
+        <v>147</v>
+      </c>
+      <c r="D38" t="s">
+        <v>148</v>
+      </c>
+      <c r="E38" t="s">
         <v>149</v>
       </c>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
         <v>150</v>
-      </c>
-      <c r="E38" t="s">
-        <v>151</v>
-      </c>
-      <c r="F38" t="s">
-        <v>152</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -29970,16 +29972,16 @@
         <v>0</v>
       </c>
       <c r="C39" t="s">
+        <v>147</v>
+      </c>
+      <c r="D39" t="s">
+        <v>151</v>
+      </c>
+      <c r="E39" t="s">
         <v>149</v>
       </c>
-      <c r="D39" t="s">
-        <v>153</v>
-      </c>
-      <c r="E39" t="s">
-        <v>151</v>
-      </c>
       <c r="F39" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -30027,16 +30029,16 @@
         <v>0</v>
       </c>
       <c r="C40" t="s">
+        <v>147</v>
+      </c>
+      <c r="D40" t="s">
+        <v>153</v>
+      </c>
+      <c r="E40" t="s">
         <v>149</v>
       </c>
-      <c r="D40" t="s">
-        <v>155</v>
-      </c>
-      <c r="E40" t="s">
-        <v>151</v>
-      </c>
       <c r="F40" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -30084,16 +30086,16 @@
         <v>0</v>
       </c>
       <c r="C41" t="s">
+        <v>147</v>
+      </c>
+      <c r="D41" t="s">
+        <v>155</v>
+      </c>
+      <c r="E41" t="s">
         <v>149</v>
       </c>
-      <c r="D41" t="s">
-        <v>157</v>
-      </c>
-      <c r="E41" t="s">
-        <v>151</v>
-      </c>
       <c r="F41" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G41">
         <v>60</v>
@@ -30141,16 +30143,16 @@
         <v>0</v>
       </c>
       <c r="C42" t="s">
+        <v>147</v>
+      </c>
+      <c r="D42" t="s">
+        <v>157</v>
+      </c>
+      <c r="E42" t="s">
         <v>149</v>
       </c>
-      <c r="D42" t="s">
-        <v>159</v>
-      </c>
-      <c r="E42" t="s">
-        <v>151</v>
-      </c>
       <c r="F42" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G42">
         <v>50</v>
@@ -30198,16 +30200,16 @@
         <v>0</v>
       </c>
       <c r="C43" t="s">
+        <v>147</v>
+      </c>
+      <c r="D43" t="s">
+        <v>159</v>
+      </c>
+      <c r="E43" t="s">
         <v>149</v>
       </c>
-      <c r="D43" t="s">
-        <v>161</v>
-      </c>
-      <c r="E43" t="s">
-        <v>151</v>
-      </c>
       <c r="F43" s="7" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -30255,16 +30257,16 @@
         <v>0</v>
       </c>
       <c r="C44" t="s">
+        <v>147</v>
+      </c>
+      <c r="D44" t="s">
+        <v>160</v>
+      </c>
+      <c r="E44" t="s">
         <v>149</v>
       </c>
-      <c r="D44" t="s">
-        <v>162</v>
-      </c>
-      <c r="E44" t="s">
-        <v>151</v>
-      </c>
       <c r="F44" s="7" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -30312,16 +30314,16 @@
         <v>0</v>
       </c>
       <c r="C45" t="s">
+        <v>147</v>
+      </c>
+      <c r="D45" t="s">
+        <v>161</v>
+      </c>
+      <c r="E45" t="s">
         <v>149</v>
       </c>
-      <c r="D45" t="s">
-        <v>163</v>
-      </c>
-      <c r="E45" t="s">
-        <v>151</v>
-      </c>
       <c r="F45" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G45">
         <v>50</v>
@@ -30369,16 +30371,16 @@
         <v>0</v>
       </c>
       <c r="C46" t="s">
+        <v>147</v>
+      </c>
+      <c r="D46" t="s">
+        <v>163</v>
+      </c>
+      <c r="E46" t="s">
         <v>149</v>
       </c>
-      <c r="D46" t="s">
-        <v>165</v>
-      </c>
-      <c r="E46" t="s">
-        <v>151</v>
-      </c>
       <c r="F46" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G46">
         <v>50</v>
@@ -30426,16 +30428,16 @@
         <v>0</v>
       </c>
       <c r="C47" t="s">
+        <v>147</v>
+      </c>
+      <c r="D47" t="s">
+        <v>165</v>
+      </c>
+      <c r="E47" t="s">
         <v>149</v>
       </c>
-      <c r="D47" t="s">
-        <v>167</v>
-      </c>
-      <c r="E47" t="s">
-        <v>151</v>
-      </c>
       <c r="F47" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -30483,16 +30485,16 @@
         <v>0</v>
       </c>
       <c r="C48" t="s">
+        <v>147</v>
+      </c>
+      <c r="D48" t="s">
+        <v>167</v>
+      </c>
+      <c r="E48" t="s">
         <v>149</v>
       </c>
-      <c r="D48" t="s">
-        <v>169</v>
-      </c>
-      <c r="E48" t="s">
-        <v>151</v>
-      </c>
       <c r="F48" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="G48">
         <v>80</v>
@@ -30540,16 +30542,16 @@
         <v>0</v>
       </c>
       <c r="C49" t="s">
+        <v>147</v>
+      </c>
+      <c r="D49" t="s">
+        <v>169</v>
+      </c>
+      <c r="E49" t="s">
         <v>149</v>
       </c>
-      <c r="D49" t="s">
-        <v>171</v>
-      </c>
-      <c r="E49" t="s">
-        <v>151</v>
-      </c>
       <c r="F49" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G49">
         <v>80</v>
@@ -30597,16 +30599,16 @@
         <v>0</v>
       </c>
       <c r="C50" t="s">
+        <v>147</v>
+      </c>
+      <c r="D50" t="s">
+        <v>171</v>
+      </c>
+      <c r="E50" t="s">
         <v>149</v>
       </c>
-      <c r="D50" t="s">
-        <v>173</v>
-      </c>
-      <c r="E50" t="s">
-        <v>151</v>
-      </c>
       <c r="F50" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G50">
         <v>60</v>
@@ -30654,16 +30656,16 @@
         <v>0</v>
       </c>
       <c r="C51" t="s">
+        <v>147</v>
+      </c>
+      <c r="D51" t="s">
+        <v>173</v>
+      </c>
+      <c r="E51" t="s">
         <v>149</v>
       </c>
-      <c r="D51" t="s">
-        <v>175</v>
-      </c>
-      <c r="E51" t="s">
-        <v>151</v>
-      </c>
       <c r="F51" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G51">
         <v>50</v>
@@ -30711,16 +30713,16 @@
         <v>0</v>
       </c>
       <c r="C52" t="s">
+        <v>147</v>
+      </c>
+      <c r="D52" t="s">
+        <v>175</v>
+      </c>
+      <c r="E52" t="s">
         <v>149</v>
       </c>
-      <c r="D52" t="s">
-        <v>177</v>
-      </c>
-      <c r="E52" t="s">
-        <v>151</v>
-      </c>
       <c r="F52" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -30768,16 +30770,16 @@
         <v>0</v>
       </c>
       <c r="C53" t="s">
+        <v>147</v>
+      </c>
+      <c r="D53" t="s">
+        <v>177</v>
+      </c>
+      <c r="E53" t="s">
         <v>149</v>
       </c>
-      <c r="D53" t="s">
-        <v>179</v>
-      </c>
-      <c r="E53" t="s">
-        <v>151</v>
-      </c>
       <c r="F53" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="G53">
         <v>60</v>
@@ -30825,16 +30827,16 @@
         <v>0</v>
       </c>
       <c r="C54" t="s">
+        <v>147</v>
+      </c>
+      <c r="D54" t="s">
+        <v>179</v>
+      </c>
+      <c r="E54" t="s">
         <v>149</v>
       </c>
-      <c r="D54" t="s">
-        <v>181</v>
-      </c>
-      <c r="E54" t="s">
-        <v>151</v>
-      </c>
       <c r="F54" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G54">
         <v>30</v>
@@ -30882,16 +30884,16 @@
         <v>0</v>
       </c>
       <c r="C55" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D55" t="s">
+        <v>181</v>
+      </c>
+      <c r="E55" t="s">
+        <v>182</v>
+      </c>
+      <c r="F55" t="s">
         <v>183</v>
-      </c>
-      <c r="E55" t="s">
-        <v>184</v>
-      </c>
-      <c r="F55" t="s">
-        <v>185</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -30939,16 +30941,16 @@
         <v>0</v>
       </c>
       <c r="C56" t="s">
+        <v>147</v>
+      </c>
+      <c r="D56" t="s">
+        <v>184</v>
+      </c>
+      <c r="E56" t="s">
         <v>149</v>
       </c>
-      <c r="D56" t="s">
-        <v>186</v>
-      </c>
-      <c r="E56" t="s">
-        <v>151</v>
-      </c>
       <c r="F56" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G56">
         <v>45</v>
@@ -30996,16 +30998,16 @@
         <v>0</v>
       </c>
       <c r="C57" t="s">
+        <v>147</v>
+      </c>
+      <c r="D57" t="s">
+        <v>186</v>
+      </c>
+      <c r="E57" t="s">
         <v>149</v>
       </c>
-      <c r="D57" t="s">
-        <v>188</v>
-      </c>
-      <c r="E57" t="s">
-        <v>151</v>
-      </c>
       <c r="F57" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G57">
         <v>30</v>
@@ -31179,7 +31181,7 @@
         <v>112</v>
       </c>
       <c r="G60">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H60">
         <v>4.0000000000000001E-3</v>
@@ -31629,10 +31631,10 @@
         <v>134</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G68">
         <v>0.86</v>
@@ -31857,16 +31859,16 @@
         <v>143</v>
       </c>
       <c r="E72" t="s">
-        <v>144</v>
+        <v>1077</v>
       </c>
       <c r="F72" t="s">
-        <v>145</v>
+        <v>1078</v>
       </c>
       <c r="G72">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H72">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -31911,13 +31913,13 @@
         <v>103</v>
       </c>
       <c r="D73" t="s">
+        <v>144</v>
+      </c>
+      <c r="E73" t="s">
+        <v>145</v>
+      </c>
+      <c r="F73" t="s">
         <v>146</v>
-      </c>
-      <c r="E73" t="s">
-        <v>147</v>
-      </c>
-      <c r="F73" t="s">
-        <v>148</v>
       </c>
       <c r="G73">
         <v>100</v>
@@ -31965,16 +31967,16 @@
         <v>0</v>
       </c>
       <c r="C74" t="s">
+        <v>235</v>
+      </c>
+      <c r="D74" t="s">
+        <v>236</v>
+      </c>
+      <c r="E74" t="s">
         <v>237</v>
       </c>
-      <c r="D74" t="s">
+      <c r="F74" t="s">
         <v>238</v>
-      </c>
-      <c r="E74" t="s">
-        <v>239</v>
-      </c>
-      <c r="F74" t="s">
-        <v>240</v>
       </c>
       <c r="G74">
         <v>15</v>
@@ -32022,16 +32024,16 @@
         <v>0</v>
       </c>
       <c r="C75" t="s">
+        <v>235</v>
+      </c>
+      <c r="D75" t="s">
+        <v>239</v>
+      </c>
+      <c r="E75" t="s">
         <v>237</v>
       </c>
-      <c r="D75" t="s">
-        <v>241</v>
-      </c>
-      <c r="E75" t="s">
-        <v>239</v>
-      </c>
       <c r="F75" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G75">
         <v>10</v>
@@ -32079,16 +32081,16 @@
         <v>0</v>
       </c>
       <c r="C76" t="s">
+        <v>235</v>
+      </c>
+      <c r="D76" t="s">
+        <v>241</v>
+      </c>
+      <c r="E76" t="s">
         <v>237</v>
       </c>
-      <c r="D76" t="s">
-        <v>243</v>
-      </c>
-      <c r="E76" t="s">
-        <v>239</v>
-      </c>
       <c r="F76" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G76">
         <v>25</v>
@@ -32136,16 +32138,16 @@
         <v>0</v>
       </c>
       <c r="C77" t="s">
+        <v>235</v>
+      </c>
+      <c r="D77" t="s">
+        <v>243</v>
+      </c>
+      <c r="E77" t="s">
         <v>237</v>
       </c>
-      <c r="D77" t="s">
-        <v>245</v>
-      </c>
-      <c r="E77" t="s">
-        <v>239</v>
-      </c>
       <c r="F77" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G77">
         <v>20</v>
@@ -32193,16 +32195,16 @@
         <v>0</v>
       </c>
       <c r="C78" t="s">
+        <v>235</v>
+      </c>
+      <c r="D78" t="s">
+        <v>245</v>
+      </c>
+      <c r="E78" t="s">
         <v>237</v>
       </c>
-      <c r="D78" t="s">
-        <v>247</v>
-      </c>
-      <c r="E78" t="s">
-        <v>239</v>
-      </c>
       <c r="F78" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G78">
         <v>100</v>
@@ -32250,16 +32252,16 @@
         <v>0</v>
       </c>
       <c r="C79" t="s">
+        <v>188</v>
+      </c>
+      <c r="D79" t="s">
+        <v>189</v>
+      </c>
+      <c r="E79" t="s">
         <v>190</v>
       </c>
-      <c r="D79" t="s">
+      <c r="F79" t="s">
         <v>191</v>
-      </c>
-      <c r="E79" t="s">
-        <v>192</v>
-      </c>
-      <c r="F79" t="s">
-        <v>193</v>
       </c>
       <c r="G79">
         <v>10000</v>
@@ -32307,16 +32309,16 @@
         <v>0</v>
       </c>
       <c r="C80" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D80" t="s">
+        <v>192</v>
+      </c>
+      <c r="E80" t="s">
+        <v>193</v>
+      </c>
+      <c r="F80" t="s">
         <v>194</v>
-      </c>
-      <c r="E80" t="s">
-        <v>195</v>
-      </c>
-      <c r="F80" t="s">
-        <v>196</v>
       </c>
       <c r="G80">
         <v>0.95</v>
@@ -32364,16 +32366,16 @@
         <v>0</v>
       </c>
       <c r="C81" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D81" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E81" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F81" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G81">
         <v>0.95</v>
@@ -32421,16 +32423,16 @@
         <v>0</v>
       </c>
       <c r="C82" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D82" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="E82" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F82" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G82">
         <v>0.95</v>
@@ -32478,16 +32480,16 @@
         <v>0</v>
       </c>
       <c r="C83" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D83" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E83" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F83" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G83">
         <v>0.95</v>
@@ -32535,16 +32537,16 @@
         <v>0</v>
       </c>
       <c r="C84" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D84" t="s">
+        <v>200</v>
+      </c>
+      <c r="E84" t="s">
+        <v>201</v>
+      </c>
+      <c r="F84" t="s">
         <v>202</v>
-      </c>
-      <c r="E84" t="s">
-        <v>203</v>
-      </c>
-      <c r="F84" t="s">
-        <v>204</v>
       </c>
       <c r="G84">
         <v>0.8</v>
@@ -32592,16 +32594,16 @@
         <v>0</v>
       </c>
       <c r="C85" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D85" t="s">
+        <v>203</v>
+      </c>
+      <c r="E85" t="s">
+        <v>204</v>
+      </c>
+      <c r="F85" t="s">
         <v>205</v>
-      </c>
-      <c r="E85" t="s">
-        <v>206</v>
-      </c>
-      <c r="F85" t="s">
-        <v>207</v>
       </c>
       <c r="G85">
         <v>1</v>
@@ -32649,16 +32651,16 @@
         <v>0</v>
       </c>
       <c r="C86" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D86" t="s">
+        <v>206</v>
+      </c>
+      <c r="E86" t="s">
+        <v>207</v>
+      </c>
+      <c r="F86" t="s">
         <v>208</v>
-      </c>
-      <c r="E86" t="s">
-        <v>209</v>
-      </c>
-      <c r="F86" t="s">
-        <v>210</v>
       </c>
       <c r="G86">
         <v>0.7</v>
@@ -32706,16 +32708,16 @@
         <v>0</v>
       </c>
       <c r="C87" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D87" t="s">
+        <v>209</v>
+      </c>
+      <c r="E87" t="s">
+        <v>210</v>
+      </c>
+      <c r="F87" t="s">
         <v>211</v>
-      </c>
-      <c r="E87" t="s">
-        <v>212</v>
-      </c>
-      <c r="F87" t="s">
-        <v>213</v>
       </c>
       <c r="G87">
         <v>1</v>
@@ -32763,16 +32765,16 @@
         <v>0</v>
       </c>
       <c r="C88" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D88" t="s">
+        <v>212</v>
+      </c>
+      <c r="E88" t="s">
+        <v>213</v>
+      </c>
+      <c r="F88" t="s">
         <v>214</v>
-      </c>
-      <c r="E88" t="s">
-        <v>215</v>
-      </c>
-      <c r="F88" t="s">
-        <v>216</v>
       </c>
       <c r="G88">
         <v>12</v>
@@ -32820,16 +32822,16 @@
         <v>0</v>
       </c>
       <c r="C89" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D89" t="s">
+        <v>215</v>
+      </c>
+      <c r="E89" t="s">
+        <v>216</v>
+      </c>
+      <c r="F89" t="s">
         <v>217</v>
-      </c>
-      <c r="E89" t="s">
-        <v>218</v>
-      </c>
-      <c r="F89" t="s">
-        <v>219</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -32877,16 +32879,16 @@
         <v>0</v>
       </c>
       <c r="C90" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D90" t="s">
+        <v>218</v>
+      </c>
+      <c r="E90" t="s">
+        <v>219</v>
+      </c>
+      <c r="F90" t="s">
         <v>220</v>
-      </c>
-      <c r="E90" t="s">
-        <v>221</v>
-      </c>
-      <c r="F90" t="s">
-        <v>222</v>
       </c>
       <c r="G90">
         <v>10</v>
@@ -32934,16 +32936,16 @@
         <v>0</v>
       </c>
       <c r="C91" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D91" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E91" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="F91" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="G91">
         <v>1000</v>
@@ -32991,16 +32993,16 @@
         <v>0</v>
       </c>
       <c r="C92" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D92" t="s">
+        <v>223</v>
+      </c>
+      <c r="E92" t="s">
+        <v>224</v>
+      </c>
+      <c r="F92" t="s">
         <v>225</v>
-      </c>
-      <c r="E92" t="s">
-        <v>226</v>
-      </c>
-      <c r="F92" t="s">
-        <v>227</v>
       </c>
       <c r="G92">
         <v>50</v>
@@ -33048,16 +33050,16 @@
         <v>0</v>
       </c>
       <c r="C93" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D93" t="s">
+        <v>226</v>
+      </c>
+      <c r="E93" t="s">
+        <v>227</v>
+      </c>
+      <c r="F93" t="s">
         <v>228</v>
-      </c>
-      <c r="E93" t="s">
-        <v>229</v>
-      </c>
-      <c r="F93" t="s">
-        <v>230</v>
       </c>
       <c r="G93">
         <v>30</v>
@@ -33105,16 +33107,16 @@
         <v>0</v>
       </c>
       <c r="C94" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D94" t="s">
+        <v>229</v>
+      </c>
+      <c r="E94" t="s">
+        <v>230</v>
+      </c>
+      <c r="F94" t="s">
         <v>231</v>
-      </c>
-      <c r="E94" t="s">
-        <v>232</v>
-      </c>
-      <c r="F94" t="s">
-        <v>233</v>
       </c>
       <c r="G94">
         <v>100</v>
@@ -33162,16 +33164,16 @@
         <v>0</v>
       </c>
       <c r="C95" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D95" t="s">
+        <v>232</v>
+      </c>
+      <c r="E95" t="s">
+        <v>233</v>
+      </c>
+      <c r="F95" t="s">
         <v>234</v>
-      </c>
-      <c r="E95" t="s">
-        <v>235</v>
-      </c>
-      <c r="F95" t="s">
-        <v>236</v>
       </c>
       <c r="G95">
         <v>5</v>
@@ -33219,16 +33221,16 @@
         <v>0</v>
       </c>
       <c r="C96" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D96" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>961</v>
+      </c>
+      <c r="F96" s="2" t="s">
         <v>962</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>963</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>964</v>
       </c>
       <c r="G96">
         <v>0.75</v>
@@ -33276,16 +33278,16 @@
         <v>0</v>
       </c>
       <c r="C97" t="s">
+        <v>316</v>
+      </c>
+      <c r="D97" t="s">
+        <v>317</v>
+      </c>
+      <c r="E97" t="s">
         <v>318</v>
       </c>
-      <c r="D97" t="s">
+      <c r="F97" t="s">
         <v>319</v>
-      </c>
-      <c r="E97" t="s">
-        <v>320</v>
-      </c>
-      <c r="F97" t="s">
-        <v>321</v>
       </c>
       <c r="G97">
         <v>4</v>
@@ -33333,16 +33335,16 @@
         <v>0</v>
       </c>
       <c r="C98" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D98" t="s">
+        <v>320</v>
+      </c>
+      <c r="E98" t="s">
+        <v>321</v>
+      </c>
+      <c r="F98" t="s">
         <v>322</v>
-      </c>
-      <c r="E98" t="s">
-        <v>323</v>
-      </c>
-      <c r="F98" t="s">
-        <v>324</v>
       </c>
       <c r="G98">
         <v>3</v>
@@ -33390,16 +33392,16 @@
         <v>0</v>
       </c>
       <c r="C99" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D99" t="s">
         <v>135</v>
       </c>
       <c r="E99" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F99" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G99">
         <v>200</v>
@@ -33447,25 +33449,25 @@
         <v>0</v>
       </c>
       <c r="C100" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D100" t="s">
+        <v>325</v>
+      </c>
+      <c r="E100" t="s">
+        <v>326</v>
+      </c>
+      <c r="F100" t="s">
         <v>327</v>
       </c>
-      <c r="E100" t="s">
+      <c r="G100" t="s">
         <v>328</v>
       </c>
-      <c r="F100" t="s">
+      <c r="H100" t="s">
         <v>329</v>
       </c>
-      <c r="G100" t="s">
+      <c r="I100" t="s">
         <v>330</v>
-      </c>
-      <c r="H100" t="s">
-        <v>331</v>
-      </c>
-      <c r="I100" t="s">
-        <v>332</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -33504,16 +33506,16 @@
         <v>0</v>
       </c>
       <c r="C101" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D101" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E101" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F101" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="G101">
         <v>20</v>
@@ -33561,16 +33563,16 @@
         <v>0</v>
       </c>
       <c r="C102" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D102" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E102" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F102" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G102">
         <v>3</v>
@@ -33618,16 +33620,16 @@
         <v>0</v>
       </c>
       <c r="C103" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D103" t="s">
+        <v>335</v>
+      </c>
+      <c r="E103" t="s">
+        <v>336</v>
+      </c>
+      <c r="F103" t="s">
         <v>337</v>
-      </c>
-      <c r="E103" t="s">
-        <v>338</v>
-      </c>
-      <c r="F103" t="s">
-        <v>339</v>
       </c>
       <c r="G103">
         <v>10</v>
@@ -33675,16 +33677,16 @@
         <v>0</v>
       </c>
       <c r="C104" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D104" t="s">
+        <v>338</v>
+      </c>
+      <c r="E104" t="s">
+        <v>339</v>
+      </c>
+      <c r="F104" t="s">
         <v>340</v>
-      </c>
-      <c r="E104" t="s">
-        <v>341</v>
-      </c>
-      <c r="F104" t="s">
-        <v>342</v>
       </c>
       <c r="G104">
         <v>3</v>
@@ -33732,16 +33734,16 @@
         <v>0</v>
       </c>
       <c r="C105" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D105" t="s">
         <v>138</v>
       </c>
       <c r="E105" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F105" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="G105">
         <v>8</v>
@@ -33789,16 +33791,16 @@
         <v>0</v>
       </c>
       <c r="C106" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D106" t="s">
+        <v>343</v>
+      </c>
+      <c r="E106" t="s">
+        <v>344</v>
+      </c>
+      <c r="F106" t="s">
         <v>345</v>
-      </c>
-      <c r="E106" t="s">
-        <v>346</v>
-      </c>
-      <c r="F106" t="s">
-        <v>347</v>
       </c>
       <c r="G106">
         <v>3</v>
@@ -33846,16 +33848,16 @@
         <v>0</v>
       </c>
       <c r="C107" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D107" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E107" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F107" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G107">
         <v>2</v>
@@ -33903,16 +33905,16 @@
         <v>0</v>
       </c>
       <c r="C108" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D108" t="s">
+        <v>348</v>
+      </c>
+      <c r="E108" t="s">
+        <v>349</v>
+      </c>
+      <c r="F108" t="s">
         <v>350</v>
-      </c>
-      <c r="E108" t="s">
-        <v>351</v>
-      </c>
-      <c r="F108" t="s">
-        <v>352</v>
       </c>
       <c r="G108">
         <v>60</v>
@@ -33960,16 +33962,16 @@
         <v>0</v>
       </c>
       <c r="C109" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D109" t="s">
+        <v>351</v>
+      </c>
+      <c r="E109" t="s">
+        <v>352</v>
+      </c>
+      <c r="F109" t="s">
         <v>353</v>
-      </c>
-      <c r="E109" t="s">
-        <v>354</v>
-      </c>
-      <c r="F109" t="s">
-        <v>355</v>
       </c>
       <c r="G109">
         <v>51</v>
@@ -34017,16 +34019,16 @@
         <v>0</v>
       </c>
       <c r="C110" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D110" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E110" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F110" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G110">
         <v>1</v>
@@ -34074,16 +34076,16 @@
         <v>0</v>
       </c>
       <c r="C111" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D111" t="s">
+        <v>356</v>
+      </c>
+      <c r="E111" t="s">
+        <v>357</v>
+      </c>
+      <c r="F111" t="s">
         <v>358</v>
-      </c>
-      <c r="E111" t="s">
-        <v>359</v>
-      </c>
-      <c r="F111" t="s">
-        <v>360</v>
       </c>
       <c r="G111">
         <v>5</v>
@@ -34131,16 +34133,16 @@
         <v>0</v>
       </c>
       <c r="C112" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D112" t="s">
+        <v>359</v>
+      </c>
+      <c r="E112" t="s">
+        <v>360</v>
+      </c>
+      <c r="F112" t="s">
         <v>361</v>
-      </c>
-      <c r="E112" t="s">
-        <v>362</v>
-      </c>
-      <c r="F112" t="s">
-        <v>363</v>
       </c>
       <c r="G112">
         <v>100</v>
@@ -34188,16 +34190,16 @@
         <v>0</v>
       </c>
       <c r="C113" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D113" t="s">
+        <v>362</v>
+      </c>
+      <c r="E113" t="s">
+        <v>363</v>
+      </c>
+      <c r="F113" t="s">
         <v>364</v>
-      </c>
-      <c r="E113" t="s">
-        <v>365</v>
-      </c>
-      <c r="F113" t="s">
-        <v>366</v>
       </c>
       <c r="G113">
         <v>30</v>
@@ -34245,25 +34247,25 @@
         <v>0</v>
       </c>
       <c r="C114" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D114" t="s">
+        <v>365</v>
+      </c>
+      <c r="E114" t="s">
+        <v>366</v>
+      </c>
+      <c r="F114" t="s">
+        <v>355</v>
+      </c>
+      <c r="G114" t="s">
         <v>367</v>
       </c>
-      <c r="E114" t="s">
+      <c r="H114" t="s">
         <v>368</v>
       </c>
-      <c r="F114" t="s">
-        <v>357</v>
-      </c>
-      <c r="G114" t="s">
+      <c r="I114" t="s">
         <v>369</v>
-      </c>
-      <c r="H114" t="s">
-        <v>370</v>
-      </c>
-      <c r="I114" t="s">
-        <v>371</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -34302,16 +34304,16 @@
         <v>0</v>
       </c>
       <c r="C115" t="s">
+        <v>306</v>
+      </c>
+      <c r="D115" t="s">
+        <v>307</v>
+      </c>
+      <c r="E115" t="s">
         <v>308</v>
       </c>
-      <c r="D115" t="s">
+      <c r="F115" t="s">
         <v>309</v>
-      </c>
-      <c r="E115" t="s">
-        <v>310</v>
-      </c>
-      <c r="F115" t="s">
-        <v>311</v>
       </c>
       <c r="G115">
         <v>50</v>
@@ -34359,16 +34361,16 @@
         <v>0</v>
       </c>
       <c r="C116" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D116" t="s">
+        <v>310</v>
+      </c>
+      <c r="E116" t="s">
+        <v>311</v>
+      </c>
+      <c r="F116" t="s">
         <v>312</v>
-      </c>
-      <c r="E116" t="s">
-        <v>313</v>
-      </c>
-      <c r="F116" t="s">
-        <v>314</v>
       </c>
       <c r="G116">
         <v>15</v>
@@ -34416,16 +34418,16 @@
         <v>0</v>
       </c>
       <c r="C117" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="D117" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="E117" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F117" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G117">
         <v>3</v>
@@ -34473,16 +34475,16 @@
         <v>0</v>
       </c>
       <c r="C118" t="s">
+        <v>247</v>
+      </c>
+      <c r="D118" t="s">
+        <v>248</v>
+      </c>
+      <c r="E118" t="s">
         <v>249</v>
       </c>
-      <c r="D118" t="s">
+      <c r="F118" t="s">
         <v>250</v>
-      </c>
-      <c r="E118" t="s">
-        <v>251</v>
-      </c>
-      <c r="F118" t="s">
-        <v>252</v>
       </c>
       <c r="G118">
         <v>20</v>
@@ -34530,16 +34532,16 @@
         <v>0</v>
       </c>
       <c r="C119" t="s">
+        <v>247</v>
+      </c>
+      <c r="D119" t="s">
+        <v>251</v>
+      </c>
+      <c r="E119" t="s">
         <v>249</v>
       </c>
-      <c r="D119" t="s">
-        <v>253</v>
-      </c>
-      <c r="E119" t="s">
-        <v>251</v>
-      </c>
       <c r="F119" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G119">
         <v>2</v>
@@ -34587,16 +34589,16 @@
         <v>0</v>
       </c>
       <c r="C120" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D120" t="s">
         <v>119</v>
       </c>
       <c r="E120" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="F120" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G120">
         <v>2</v>
@@ -34644,16 +34646,16 @@
         <v>0</v>
       </c>
       <c r="C121" t="s">
+        <v>247</v>
+      </c>
+      <c r="D121" t="s">
+        <v>253</v>
+      </c>
+      <c r="E121" t="s">
         <v>249</v>
       </c>
-      <c r="D121" t="s">
-        <v>255</v>
-      </c>
-      <c r="E121" t="s">
-        <v>251</v>
-      </c>
       <c r="F121" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G121">
         <v>250</v>
@@ -34701,16 +34703,16 @@
         <v>0</v>
       </c>
       <c r="C122" t="s">
+        <v>247</v>
+      </c>
+      <c r="D122" t="s">
+        <v>254</v>
+      </c>
+      <c r="E122" t="s">
         <v>249</v>
       </c>
-      <c r="D122" t="s">
-        <v>256</v>
-      </c>
-      <c r="E122" t="s">
-        <v>251</v>
-      </c>
       <c r="F122" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G122">
         <v>120</v>
@@ -34758,16 +34760,16 @@
         <v>0</v>
       </c>
       <c r="C123" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D123" t="s">
         <v>134</v>
       </c>
       <c r="E123" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F123" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G123">
         <v>1</v>
@@ -34815,37 +34817,37 @@
         <v>0</v>
       </c>
       <c r="C124" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D124" t="s">
         <v>135</v>
       </c>
       <c r="E124" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F124" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G124">
         <v>100</v>
       </c>
       <c r="H124" t="s">
+        <v>259</v>
+      </c>
+      <c r="I124" t="s">
+        <v>260</v>
+      </c>
+      <c r="J124" t="s">
         <v>261</v>
       </c>
-      <c r="I124" t="s">
+      <c r="K124" t="s">
         <v>262</v>
       </c>
-      <c r="J124" t="s">
+      <c r="L124" t="s">
         <v>263</v>
       </c>
-      <c r="K124" t="s">
+      <c r="M124" t="s">
         <v>264</v>
-      </c>
-      <c r="L124" t="s">
-        <v>265</v>
-      </c>
-      <c r="M124" t="s">
-        <v>266</v>
       </c>
       <c r="N124">
         <v>0</v>
@@ -34872,37 +34874,37 @@
         <v>0</v>
       </c>
       <c r="C125" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D125" t="s">
         <v>138</v>
       </c>
       <c r="E125" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="F125" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G125">
         <v>5</v>
       </c>
       <c r="H125" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="I125" t="s">
+        <v>266</v>
+      </c>
+      <c r="J125" t="s">
+        <v>267</v>
+      </c>
+      <c r="K125" t="s">
         <v>268</v>
       </c>
-      <c r="J125" t="s">
+      <c r="L125" t="s">
         <v>269</v>
       </c>
-      <c r="K125" t="s">
+      <c r="M125" t="s">
         <v>270</v>
-      </c>
-      <c r="L125" t="s">
-        <v>271</v>
-      </c>
-      <c r="M125" t="s">
-        <v>272</v>
       </c>
       <c r="N125">
         <v>0</v>
@@ -34929,16 +34931,16 @@
         <v>0</v>
       </c>
       <c r="C126" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D126" t="s">
+        <v>271</v>
+      </c>
+      <c r="E126" t="s">
+        <v>272</v>
+      </c>
+      <c r="F126" t="s">
         <v>273</v>
-      </c>
-      <c r="E126" t="s">
-        <v>274</v>
-      </c>
-      <c r="F126" t="s">
-        <v>275</v>
       </c>
       <c r="G126">
         <v>4</v>
@@ -34986,16 +34988,16 @@
         <v>0</v>
       </c>
       <c r="C127" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="E127" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F127" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G127">
         <v>1.5</v>
@@ -35043,22 +35045,22 @@
         <v>0</v>
       </c>
       <c r="C128" t="s">
+        <v>276</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>967</v>
+      </c>
+      <c r="E128" t="s">
+        <v>277</v>
+      </c>
+      <c r="F128" t="s">
         <v>278</v>
       </c>
-      <c r="D128" s="2" t="s">
-        <v>969</v>
-      </c>
-      <c r="E128" t="s">
+      <c r="G128" t="s">
         <v>279</v>
       </c>
-      <c r="F128" t="s">
+      <c r="H128" t="s">
         <v>280</v>
-      </c>
-      <c r="G128" t="s">
-        <v>281</v>
-      </c>
-      <c r="H128" t="s">
-        <v>282</v>
       </c>
       <c r="I128">
         <v>0</v>
@@ -35100,22 +35102,22 @@
         <v>0</v>
       </c>
       <c r="C129" t="s">
+        <v>276</v>
+      </c>
+      <c r="D129" t="s">
+        <v>963</v>
+      </c>
+      <c r="E129" t="s">
+        <v>277</v>
+      </c>
+      <c r="F129" t="s">
         <v>278</v>
       </c>
-      <c r="D129" t="s">
-        <v>965</v>
-      </c>
-      <c r="E129" t="s">
-        <v>279</v>
-      </c>
-      <c r="F129" t="s">
-        <v>280</v>
-      </c>
       <c r="G129" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="H129" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I129">
         <v>0</v>
@@ -35157,25 +35159,25 @@
         <v>0</v>
       </c>
       <c r="C130" t="s">
+        <v>276</v>
+      </c>
+      <c r="D130" t="s">
+        <v>964</v>
+      </c>
+      <c r="E130" t="s">
+        <v>277</v>
+      </c>
+      <c r="F130" t="s">
         <v>278</v>
       </c>
-      <c r="D130" t="s">
-        <v>966</v>
-      </c>
-      <c r="E130" t="s">
-        <v>279</v>
-      </c>
-      <c r="F130" t="s">
-        <v>280</v>
-      </c>
       <c r="G130" t="s">
+        <v>283</v>
+      </c>
+      <c r="H130" t="s">
+        <v>284</v>
+      </c>
+      <c r="I130" t="s">
         <v>285</v>
-      </c>
-      <c r="H130" t="s">
-        <v>286</v>
-      </c>
-      <c r="I130" t="s">
-        <v>287</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -35214,28 +35216,28 @@
         <v>0</v>
       </c>
       <c r="C131" t="s">
+        <v>276</v>
+      </c>
+      <c r="D131" t="s">
+        <v>965</v>
+      </c>
+      <c r="E131" t="s">
+        <v>277</v>
+      </c>
+      <c r="F131" t="s">
         <v>278</v>
       </c>
-      <c r="D131" t="s">
-        <v>967</v>
-      </c>
-      <c r="E131" t="s">
-        <v>279</v>
-      </c>
-      <c r="F131" t="s">
-        <v>280</v>
-      </c>
       <c r="G131" t="s">
+        <v>286</v>
+      </c>
+      <c r="H131" t="s">
+        <v>287</v>
+      </c>
+      <c r="I131" t="s">
         <v>288</v>
       </c>
-      <c r="H131" t="s">
+      <c r="J131" t="s">
         <v>289</v>
-      </c>
-      <c r="I131" t="s">
-        <v>290</v>
-      </c>
-      <c r="J131" t="s">
-        <v>291</v>
       </c>
       <c r="K131">
         <v>0</v>
@@ -35271,28 +35273,28 @@
         <v>0</v>
       </c>
       <c r="C132" t="s">
+        <v>276</v>
+      </c>
+      <c r="D132" t="s">
+        <v>966</v>
+      </c>
+      <c r="E132" t="s">
+        <v>277</v>
+      </c>
+      <c r="F132" t="s">
         <v>278</v>
       </c>
-      <c r="D132" t="s">
-        <v>968</v>
-      </c>
-      <c r="E132" t="s">
-        <v>279</v>
-      </c>
-      <c r="F132" t="s">
-        <v>280</v>
-      </c>
       <c r="G132" s="3" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="H132" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="I132" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="K132">
         <v>0</v>
@@ -35328,31 +35330,31 @@
         <v>0</v>
       </c>
       <c r="C133" t="s">
+        <v>276</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E133" t="s">
+        <v>277</v>
+      </c>
+      <c r="F133" t="s">
         <v>278</v>
       </c>
-      <c r="D133" s="2" t="s">
+      <c r="G133" s="3" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I133" s="3" t="s">
         <v>1007</v>
       </c>
-      <c r="E133" t="s">
-        <v>279</v>
-      </c>
-      <c r="F133" t="s">
-        <v>280</v>
-      </c>
-      <c r="G133" s="3" t="s">
+      <c r="J133" s="3" t="s">
         <v>1010</v>
       </c>
-      <c r="H133" s="3" t="s">
+      <c r="K133" s="3" t="s">
         <v>1011</v>
-      </c>
-      <c r="I133" s="3" t="s">
-        <v>1009</v>
-      </c>
-      <c r="J133" s="3" t="s">
-        <v>1012</v>
-      </c>
-      <c r="K133" s="3" t="s">
-        <v>1013</v>
       </c>
       <c r="L133">
         <v>0</v>
@@ -35385,34 +35387,34 @@
         <v>0</v>
       </c>
       <c r="C134" t="s">
+        <v>276</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E134" t="s">
+        <v>277</v>
+      </c>
+      <c r="F134" t="s">
         <v>278</v>
       </c>
-      <c r="D134" s="2" t="s">
+      <c r="G134" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="J134" s="3" t="s">
         <v>1015</v>
       </c>
-      <c r="E134" t="s">
-        <v>279</v>
-      </c>
-      <c r="F134" t="s">
-        <v>280</v>
-      </c>
-      <c r="G134" s="3" t="s">
-        <v>1006</v>
-      </c>
-      <c r="H134" s="3" t="s">
-        <v>979</v>
-      </c>
-      <c r="I134" s="3" t="s">
-        <v>1016</v>
-      </c>
-      <c r="J134" s="3" t="s">
-        <v>1017</v>
-      </c>
       <c r="K134" s="3" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="M134">
         <v>0</v>
@@ -35442,22 +35444,22 @@
         <v>0</v>
       </c>
       <c r="C135" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="E135" t="s">
+        <v>277</v>
+      </c>
+      <c r="F135" t="s">
+        <v>292</v>
+      </c>
+      <c r="G135" t="s">
         <v>279</v>
       </c>
-      <c r="F135" t="s">
-        <v>294</v>
-      </c>
-      <c r="G135" t="s">
-        <v>281</v>
-      </c>
       <c r="H135" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I135">
         <v>0</v>
@@ -35499,25 +35501,25 @@
         <v>0</v>
       </c>
       <c r="C136" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="E136" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F136" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="J136">
         <v>0</v>
@@ -35556,31 +35558,31 @@
         <v>0</v>
       </c>
       <c r="C137" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="E137" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F137" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G137" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="H137" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="I137" s="3" t="s">
         <v>977</v>
       </c>
-      <c r="H137" s="3" t="s">
+      <c r="J137" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="K137" s="3" t="s">
         <v>978</v>
-      </c>
-      <c r="I137" s="3" t="s">
-        <v>979</v>
-      </c>
-      <c r="J137" s="3" t="s">
-        <v>981</v>
-      </c>
-      <c r="K137" s="3" t="s">
-        <v>980</v>
       </c>
       <c r="L137">
         <v>0</v>
@@ -35613,37 +35615,37 @@
         <v>0</v>
       </c>
       <c r="C138" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="E138" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F138" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G138" s="3" t="s">
+        <v>990</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>991</v>
+      </c>
+      <c r="I138" s="3" t="s">
         <v>992</v>
       </c>
-      <c r="H138" s="3" t="s">
+      <c r="J138" s="3" t="s">
         <v>993</v>
       </c>
-      <c r="I138" s="3" t="s">
+      <c r="K138" s="3" t="s">
         <v>994</v>
       </c>
-      <c r="J138" s="3" t="s">
+      <c r="L138" s="3" t="s">
         <v>995</v>
       </c>
-      <c r="K138" s="3" t="s">
+      <c r="M138" s="3" t="s">
         <v>996</v>
-      </c>
-      <c r="L138" s="3" t="s">
-        <v>997</v>
-      </c>
-      <c r="M138" s="3" t="s">
-        <v>998</v>
       </c>
       <c r="N138">
         <v>0</v>
@@ -35670,37 +35672,37 @@
         <v>0</v>
       </c>
       <c r="C139" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D139" s="2" t="s">
+        <v>980</v>
+      </c>
+      <c r="E139" t="s">
+        <v>277</v>
+      </c>
+      <c r="F139" t="s">
+        <v>292</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="H139" s="3" t="s">
+        <v>984</v>
+      </c>
+      <c r="I139" s="3" t="s">
         <v>982</v>
       </c>
-      <c r="E139" t="s">
-        <v>279</v>
-      </c>
-      <c r="F139" t="s">
-        <v>294</v>
-      </c>
-      <c r="G139" s="3" t="s">
+      <c r="J139" s="3" t="s">
         <v>985</v>
       </c>
-      <c r="H139" s="3" t="s">
+      <c r="K139" s="3" t="s">
         <v>986</v>
       </c>
-      <c r="I139" s="3" t="s">
-        <v>984</v>
-      </c>
-      <c r="J139" s="3" t="s">
+      <c r="L139" s="3" t="s">
         <v>987</v>
       </c>
-      <c r="K139" s="3" t="s">
+      <c r="M139" s="3" t="s">
         <v>988</v>
-      </c>
-      <c r="L139" s="3" t="s">
-        <v>989</v>
-      </c>
-      <c r="M139" s="3" t="s">
-        <v>990</v>
       </c>
       <c r="N139">
         <v>0</v>
@@ -35727,19 +35729,19 @@
         <v>0</v>
       </c>
       <c r="C140" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D140" t="s">
+        <v>293</v>
+      </c>
+      <c r="E140" t="s">
+        <v>277</v>
+      </c>
+      <c r="F140" t="s">
+        <v>294</v>
+      </c>
+      <c r="G140" t="s">
         <v>295</v>
-      </c>
-      <c r="E140" t="s">
-        <v>279</v>
-      </c>
-      <c r="F140" t="s">
-        <v>296</v>
-      </c>
-      <c r="G140" t="s">
-        <v>297</v>
       </c>
       <c r="H140">
         <v>0</v>
@@ -35784,16 +35786,16 @@
         <v>0</v>
       </c>
       <c r="C141" t="s">
+        <v>296</v>
+      </c>
+      <c r="D141" t="s">
+        <v>297</v>
+      </c>
+      <c r="E141" t="s">
         <v>298</v>
       </c>
-      <c r="D141" t="s">
+      <c r="F141" t="s">
         <v>299</v>
-      </c>
-      <c r="E141" t="s">
-        <v>300</v>
-      </c>
-      <c r="F141" t="s">
-        <v>301</v>
       </c>
       <c r="G141">
         <v>10</v>
@@ -35841,16 +35843,16 @@
         <v>0</v>
       </c>
       <c r="C142" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D142" t="s">
+        <v>300</v>
+      </c>
+      <c r="E142" t="s">
+        <v>301</v>
+      </c>
+      <c r="F142" t="s">
         <v>302</v>
-      </c>
-      <c r="E142" t="s">
-        <v>303</v>
-      </c>
-      <c r="F142" t="s">
-        <v>304</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -35898,16 +35900,16 @@
         <v>0</v>
       </c>
       <c r="C143" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="D143" t="s">
+        <v>303</v>
+      </c>
+      <c r="E143" t="s">
+        <v>304</v>
+      </c>
+      <c r="F143" t="s">
         <v>305</v>
-      </c>
-      <c r="E143" t="s">
-        <v>306</v>
-      </c>
-      <c r="F143" t="s">
-        <v>307</v>
       </c>
       <c r="G143">
         <v>2</v>
@@ -35955,16 +35957,16 @@
         <v>0</v>
       </c>
       <c r="C144" t="s">
+        <v>400</v>
+      </c>
+      <c r="D144" t="s">
+        <v>401</v>
+      </c>
+      <c r="E144" t="s">
         <v>402</v>
       </c>
-      <c r="D144" t="s">
+      <c r="F144" t="s">
         <v>403</v>
-      </c>
-      <c r="E144" t="s">
-        <v>404</v>
-      </c>
-      <c r="F144" t="s">
-        <v>405</v>
       </c>
       <c r="G144">
         <v>100</v>
@@ -36012,16 +36014,16 @@
         <v>0</v>
       </c>
       <c r="C145" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D145" t="s">
+        <v>404</v>
+      </c>
+      <c r="E145" t="s">
+        <v>405</v>
+      </c>
+      <c r="F145" t="s">
         <v>406</v>
-      </c>
-      <c r="E145" t="s">
-        <v>407</v>
-      </c>
-      <c r="F145" t="s">
-        <v>408</v>
       </c>
       <c r="G145">
         <v>92</v>
@@ -36069,16 +36071,16 @@
         <v>0</v>
       </c>
       <c r="C146" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D146" t="s">
+        <v>407</v>
+      </c>
+      <c r="E146" t="s">
+        <v>408</v>
+      </c>
+      <c r="F146" t="s">
         <v>409</v>
-      </c>
-      <c r="E146" t="s">
-        <v>410</v>
-      </c>
-      <c r="F146" t="s">
-        <v>411</v>
       </c>
       <c r="G146">
         <v>78.100000000000009</v>
@@ -36126,16 +36128,16 @@
         <v>0</v>
       </c>
       <c r="C147" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D147" t="s">
+        <v>410</v>
+      </c>
+      <c r="E147" t="s">
+        <v>411</v>
+      </c>
+      <c r="F147" t="s">
         <v>412</v>
-      </c>
-      <c r="E147" t="s">
-        <v>413</v>
-      </c>
-      <c r="F147" t="s">
-        <v>414</v>
       </c>
       <c r="G147">
         <v>72.113600000000005</v>
@@ -36183,16 +36185,16 @@
         <v>0</v>
       </c>
       <c r="C148" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D148" t="s">
+        <v>413</v>
+      </c>
+      <c r="E148" t="s">
+        <v>414</v>
+      </c>
+      <c r="F148" t="s">
         <v>415</v>
-      </c>
-      <c r="E148" t="s">
-        <v>416</v>
-      </c>
-      <c r="F148" t="s">
-        <v>417</v>
       </c>
       <c r="G148">
         <v>53.837361999999999</v>
@@ -36240,16 +36242,16 @@
         <v>0</v>
       </c>
       <c r="C149" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D149" t="s">
+        <v>416</v>
+      </c>
+      <c r="E149" t="s">
+        <v>417</v>
+      </c>
+      <c r="F149" t="s">
         <v>418</v>
-      </c>
-      <c r="E149" t="s">
-        <v>419</v>
-      </c>
-      <c r="F149" t="s">
-        <v>420</v>
       </c>
       <c r="G149">
         <v>49.993825599999994</v>
@@ -36297,16 +36299,16 @@
         <v>0</v>
       </c>
       <c r="C150" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D150" t="s">
+        <v>419</v>
+      </c>
+      <c r="E150" t="s">
+        <v>420</v>
+      </c>
+      <c r="F150" t="s">
         <v>421</v>
-      </c>
-      <c r="E150" t="s">
-        <v>422</v>
-      </c>
-      <c r="F150" t="s">
-        <v>423</v>
       </c>
       <c r="G150">
         <v>36.76497232906253</v>
@@ -36354,16 +36356,16 @@
         <v>0</v>
       </c>
       <c r="C151" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D151" t="s">
+        <v>422</v>
+      </c>
+      <c r="E151" t="s">
+        <v>423</v>
+      </c>
+      <c r="F151" t="s">
         <v>424</v>
-      </c>
-      <c r="E151" t="s">
-        <v>425</v>
-      </c>
-      <c r="F151" t="s">
-        <v>426</v>
       </c>
       <c r="G151">
         <v>31.631675870386633</v>
@@ -36411,16 +36413,16 @@
         <v>0</v>
       </c>
       <c r="C152" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D152" t="s">
+        <v>425</v>
+      </c>
+      <c r="E152" t="s">
+        <v>426</v>
+      </c>
+      <c r="F152" t="s">
         <v>427</v>
-      </c>
-      <c r="E152" t="s">
-        <v>428</v>
-      </c>
-      <c r="F152" t="s">
-        <v>429</v>
       </c>
       <c r="G152">
         <v>25.407543428799851</v>
@@ -36468,16 +36470,16 @@
         <v>0</v>
       </c>
       <c r="C153" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D153" t="s">
+        <v>428</v>
+      </c>
+      <c r="E153" t="s">
+        <v>429</v>
+      </c>
+      <c r="F153" t="s">
         <v>430</v>
-      </c>
-      <c r="E153" t="s">
-        <v>431</v>
-      </c>
-      <c r="F153" t="s">
-        <v>432</v>
       </c>
       <c r="G153">
         <v>18.159999999999986</v>
@@ -36525,16 +36527,16 @@
         <v>0</v>
       </c>
       <c r="C154" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D154" t="s">
+        <v>431</v>
+      </c>
+      <c r="E154" t="s">
+        <v>432</v>
+      </c>
+      <c r="F154" t="s">
         <v>433</v>
-      </c>
-      <c r="E154" t="s">
-        <v>434</v>
-      </c>
-      <c r="F154" t="s">
-        <v>435</v>
       </c>
       <c r="G154">
         <v>1.35</v>
@@ -36582,16 +36584,16 @@
         <v>0</v>
       </c>
       <c r="C155" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D155" t="s">
+        <v>434</v>
+      </c>
+      <c r="E155" t="s">
+        <v>435</v>
+      </c>
+      <c r="F155" t="s">
         <v>436</v>
-      </c>
-      <c r="E155" t="s">
-        <v>437</v>
-      </c>
-      <c r="F155" t="s">
-        <v>438</v>
       </c>
       <c r="G155">
         <v>0.5</v>
@@ -36639,16 +36641,16 @@
         <v>0</v>
       </c>
       <c r="C156" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D156" t="s">
+        <v>437</v>
+      </c>
+      <c r="E156" t="s">
+        <v>438</v>
+      </c>
+      <c r="F156" t="s">
         <v>439</v>
-      </c>
-      <c r="E156" t="s">
-        <v>440</v>
-      </c>
-      <c r="F156" t="s">
-        <v>441</v>
       </c>
       <c r="G156">
         <v>4000</v>
@@ -36696,37 +36698,37 @@
         <v>0</v>
       </c>
       <c r="C157" t="s">
+        <v>455</v>
+      </c>
+      <c r="D157" t="s">
+        <v>456</v>
+      </c>
+      <c r="E157" t="s">
         <v>457</v>
       </c>
-      <c r="D157" t="s">
+      <c r="F157" t="s">
         <v>458</v>
       </c>
-      <c r="E157" t="s">
+      <c r="G157" t="s">
         <v>459</v>
       </c>
-      <c r="F157" t="s">
+      <c r="H157" t="s">
         <v>460</v>
       </c>
-      <c r="G157" t="s">
+      <c r="I157" t="s">
         <v>461</v>
       </c>
-      <c r="H157" t="s">
+      <c r="J157" t="s">
         <v>462</v>
       </c>
-      <c r="I157" t="s">
+      <c r="K157" t="s">
         <v>463</v>
       </c>
-      <c r="J157" t="s">
+      <c r="L157" t="s">
         <v>464</v>
       </c>
-      <c r="K157" t="s">
+      <c r="M157" t="s">
         <v>465</v>
-      </c>
-      <c r="L157" t="s">
-        <v>466</v>
-      </c>
-      <c r="M157" t="s">
-        <v>467</v>
       </c>
       <c r="N157">
         <v>0</v>
@@ -36753,37 +36755,37 @@
         <v>0</v>
       </c>
       <c r="C158" t="s">
+        <v>455</v>
+      </c>
+      <c r="D158" t="s">
+        <v>466</v>
+      </c>
+      <c r="E158" t="s">
         <v>457</v>
       </c>
-      <c r="D158" t="s">
-        <v>468</v>
-      </c>
-      <c r="E158" t="s">
+      <c r="F158" t="s">
+        <v>458</v>
+      </c>
+      <c r="G158" t="s">
         <v>459</v>
       </c>
-      <c r="F158" t="s">
+      <c r="H158" t="s">
         <v>460</v>
       </c>
-      <c r="G158" t="s">
+      <c r="I158" t="s">
         <v>461</v>
       </c>
-      <c r="H158" t="s">
+      <c r="J158" t="s">
         <v>462</v>
       </c>
-      <c r="I158" t="s">
+      <c r="K158" t="s">
         <v>463</v>
       </c>
-      <c r="J158" t="s">
+      <c r="L158" t="s">
         <v>464</v>
       </c>
-      <c r="K158" t="s">
+      <c r="M158" t="s">
         <v>465</v>
-      </c>
-      <c r="L158" t="s">
-        <v>466</v>
-      </c>
-      <c r="M158" t="s">
-        <v>467</v>
       </c>
       <c r="N158">
         <v>0</v>
@@ -36810,37 +36812,37 @@
         <v>0</v>
       </c>
       <c r="C159" t="s">
+        <v>455</v>
+      </c>
+      <c r="D159" t="s">
+        <v>467</v>
+      </c>
+      <c r="E159" t="s">
         <v>457</v>
       </c>
-      <c r="D159" t="s">
+      <c r="F159" t="s">
+        <v>458</v>
+      </c>
+      <c r="G159" t="s">
+        <v>468</v>
+      </c>
+      <c r="H159" t="s">
         <v>469</v>
       </c>
-      <c r="E159" t="s">
-        <v>459</v>
-      </c>
-      <c r="F159" t="s">
-        <v>460</v>
-      </c>
-      <c r="G159" t="s">
-        <v>470</v>
-      </c>
-      <c r="H159" t="s">
-        <v>471</v>
-      </c>
       <c r="I159" t="s">
+        <v>461</v>
+      </c>
+      <c r="J159" t="s">
+        <v>462</v>
+      </c>
+      <c r="K159" t="s">
         <v>463</v>
       </c>
-      <c r="J159" t="s">
+      <c r="L159" t="s">
         <v>464</v>
       </c>
-      <c r="K159" t="s">
+      <c r="M159" t="s">
         <v>465</v>
-      </c>
-      <c r="L159" t="s">
-        <v>466</v>
-      </c>
-      <c r="M159" t="s">
-        <v>467</v>
       </c>
       <c r="N159">
         <v>0</v>
@@ -36867,37 +36869,37 @@
         <v>0</v>
       </c>
       <c r="C160" t="s">
+        <v>455</v>
+      </c>
+      <c r="D160" t="s">
+        <v>470</v>
+      </c>
+      <c r="E160" t="s">
         <v>457</v>
       </c>
-      <c r="D160" t="s">
+      <c r="F160" t="s">
+        <v>458</v>
+      </c>
+      <c r="G160" t="s">
+        <v>471</v>
+      </c>
+      <c r="H160" t="s">
+        <v>469</v>
+      </c>
+      <c r="I160" t="s">
         <v>472</v>
       </c>
-      <c r="E160" t="s">
-        <v>459</v>
-      </c>
-      <c r="F160" t="s">
-        <v>460</v>
-      </c>
-      <c r="G160" t="s">
+      <c r="J160" t="s">
         <v>473</v>
       </c>
-      <c r="H160" t="s">
-        <v>471</v>
-      </c>
-      <c r="I160" t="s">
-        <v>474</v>
-      </c>
-      <c r="J160" t="s">
-        <v>475</v>
-      </c>
       <c r="K160" t="s">
+        <v>463</v>
+      </c>
+      <c r="L160" t="s">
+        <v>464</v>
+      </c>
+      <c r="M160" t="s">
         <v>465</v>
-      </c>
-      <c r="L160" t="s">
-        <v>466</v>
-      </c>
-      <c r="M160" t="s">
-        <v>467</v>
       </c>
       <c r="N160">
         <v>0</v>
@@ -36924,37 +36926,37 @@
         <v>0</v>
       </c>
       <c r="C161" t="s">
+        <v>455</v>
+      </c>
+      <c r="D161" t="s">
+        <v>474</v>
+      </c>
+      <c r="E161" t="s">
         <v>457</v>
       </c>
-      <c r="D161" t="s">
+      <c r="F161" t="s">
+        <v>458</v>
+      </c>
+      <c r="G161" t="s">
+        <v>475</v>
+      </c>
+      <c r="H161" t="s">
         <v>476</v>
       </c>
-      <c r="E161" t="s">
-        <v>459</v>
-      </c>
-      <c r="F161" t="s">
-        <v>460</v>
-      </c>
-      <c r="G161" t="s">
+      <c r="I161" t="s">
+        <v>472</v>
+      </c>
+      <c r="J161" t="s">
+        <v>473</v>
+      </c>
+      <c r="K161" t="s">
         <v>477</v>
       </c>
-      <c r="H161" t="s">
+      <c r="L161" t="s">
         <v>478</v>
       </c>
-      <c r="I161" t="s">
-        <v>474</v>
-      </c>
-      <c r="J161" t="s">
-        <v>475</v>
-      </c>
-      <c r="K161" t="s">
+      <c r="M161" t="s">
         <v>479</v>
-      </c>
-      <c r="L161" t="s">
-        <v>480</v>
-      </c>
-      <c r="M161" t="s">
-        <v>481</v>
       </c>
       <c r="N161">
         <v>0</v>
@@ -36981,37 +36983,37 @@
         <v>0</v>
       </c>
       <c r="C162" t="s">
+        <v>455</v>
+      </c>
+      <c r="D162" t="s">
+        <v>480</v>
+      </c>
+      <c r="E162" t="s">
         <v>457</v>
       </c>
-      <c r="D162" t="s">
+      <c r="F162" t="s">
+        <v>458</v>
+      </c>
+      <c r="G162" t="s">
+        <v>481</v>
+      </c>
+      <c r="H162" t="s">
         <v>482</v>
       </c>
-      <c r="E162" t="s">
-        <v>459</v>
-      </c>
-      <c r="F162" t="s">
-        <v>460</v>
-      </c>
-      <c r="G162" t="s">
+      <c r="I162" t="s">
         <v>483</v>
       </c>
-      <c r="H162" t="s">
+      <c r="J162" t="s">
         <v>484</v>
       </c>
-      <c r="I162" t="s">
+      <c r="K162" t="s">
         <v>485</v>
       </c>
-      <c r="J162" t="s">
+      <c r="L162" t="s">
         <v>486</v>
       </c>
-      <c r="K162" t="s">
+      <c r="M162" t="s">
         <v>487</v>
-      </c>
-      <c r="L162" t="s">
-        <v>488</v>
-      </c>
-      <c r="M162" t="s">
-        <v>489</v>
       </c>
       <c r="N162">
         <v>0</v>
@@ -37038,37 +37040,37 @@
         <v>0</v>
       </c>
       <c r="C163" t="s">
+        <v>455</v>
+      </c>
+      <c r="D163" t="s">
+        <v>488</v>
+      </c>
+      <c r="E163" t="s">
         <v>457</v>
       </c>
-      <c r="D163" t="s">
+      <c r="F163" t="s">
+        <v>458</v>
+      </c>
+      <c r="G163" t="s">
+        <v>489</v>
+      </c>
+      <c r="H163" t="s">
         <v>490</v>
       </c>
-      <c r="E163" t="s">
-        <v>459</v>
-      </c>
-      <c r="F163" t="s">
-        <v>460</v>
-      </c>
-      <c r="G163" t="s">
+      <c r="I163" t="s">
         <v>491</v>
       </c>
-      <c r="H163" t="s">
+      <c r="J163" t="s">
         <v>492</v>
       </c>
-      <c r="I163" t="s">
+      <c r="K163" t="s">
         <v>493</v>
       </c>
-      <c r="J163" t="s">
+      <c r="L163" t="s">
         <v>494</v>
       </c>
-      <c r="K163" t="s">
+      <c r="M163" t="s">
         <v>495</v>
-      </c>
-      <c r="L163" t="s">
-        <v>496</v>
-      </c>
-      <c r="M163" t="s">
-        <v>497</v>
       </c>
       <c r="N163">
         <v>0</v>
@@ -37095,37 +37097,37 @@
         <v>0</v>
       </c>
       <c r="C164" t="s">
+        <v>455</v>
+      </c>
+      <c r="D164" t="s">
+        <v>496</v>
+      </c>
+      <c r="E164" t="s">
         <v>457</v>
       </c>
-      <c r="D164" t="s">
+      <c r="F164" t="s">
+        <v>458</v>
+      </c>
+      <c r="G164" t="s">
+        <v>489</v>
+      </c>
+      <c r="H164" t="s">
+        <v>460</v>
+      </c>
+      <c r="I164" t="s">
+        <v>461</v>
+      </c>
+      <c r="J164" t="s">
+        <v>462</v>
+      </c>
+      <c r="K164" t="s">
+        <v>497</v>
+      </c>
+      <c r="L164" t="s">
         <v>498</v>
       </c>
-      <c r="E164" t="s">
-        <v>459</v>
-      </c>
-      <c r="F164" t="s">
-        <v>460</v>
-      </c>
-      <c r="G164" t="s">
-        <v>491</v>
-      </c>
-      <c r="H164" t="s">
-        <v>462</v>
-      </c>
-      <c r="I164" t="s">
-        <v>463</v>
-      </c>
-      <c r="J164" t="s">
-        <v>464</v>
-      </c>
-      <c r="K164" t="s">
+      <c r="M164" t="s">
         <v>499</v>
-      </c>
-      <c r="L164" t="s">
-        <v>500</v>
-      </c>
-      <c r="M164" t="s">
-        <v>501</v>
       </c>
       <c r="N164">
         <v>0</v>
@@ -37152,16 +37154,16 @@
         <v>0</v>
       </c>
       <c r="C165" t="s">
+        <v>440</v>
+      </c>
+      <c r="D165" t="s">
+        <v>441</v>
+      </c>
+      <c r="E165" t="s">
         <v>442</v>
       </c>
-      <c r="D165" t="s">
+      <c r="F165" t="s">
         <v>443</v>
-      </c>
-      <c r="E165" t="s">
-        <v>444</v>
-      </c>
-      <c r="F165" t="s">
-        <v>445</v>
       </c>
       <c r="G165">
         <v>4</v>
@@ -37209,16 +37211,16 @@
         <v>0</v>
       </c>
       <c r="C166" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D166" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E166" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="F166" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="G166">
         <v>200</v>
@@ -37266,16 +37268,16 @@
         <v>0</v>
       </c>
       <c r="C167" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D167" t="s">
+        <v>446</v>
+      </c>
+      <c r="E167" t="s">
+        <v>447</v>
+      </c>
+      <c r="F167" t="s">
         <v>448</v>
-      </c>
-      <c r="E167" t="s">
-        <v>449</v>
-      </c>
-      <c r="F167" t="s">
-        <v>450</v>
       </c>
       <c r="G167">
         <v>4</v>
@@ -37323,16 +37325,16 @@
         <v>0</v>
       </c>
       <c r="C168" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D168" t="s">
+        <v>449</v>
+      </c>
+      <c r="E168" t="s">
+        <v>450</v>
+      </c>
+      <c r="F168" t="s">
         <v>451</v>
-      </c>
-      <c r="E168" t="s">
-        <v>452</v>
-      </c>
-      <c r="F168" t="s">
-        <v>453</v>
       </c>
       <c r="G168">
         <v>3</v>
@@ -37380,16 +37382,16 @@
         <v>0</v>
       </c>
       <c r="C169" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="D169" t="s">
+        <v>452</v>
+      </c>
+      <c r="E169" t="s">
+        <v>453</v>
+      </c>
+      <c r="F169" t="s">
         <v>454</v>
-      </c>
-      <c r="E169" t="s">
-        <v>455</v>
-      </c>
-      <c r="F169" t="s">
-        <v>456</v>
       </c>
       <c r="G169">
         <v>4</v>
@@ -37437,16 +37439,16 @@
         <v>0</v>
       </c>
       <c r="C170" t="s">
+        <v>370</v>
+      </c>
+      <c r="D170" t="s">
+        <v>371</v>
+      </c>
+      <c r="E170" t="s">
         <v>372</v>
       </c>
-      <c r="D170" t="s">
+      <c r="F170" t="s">
         <v>373</v>
-      </c>
-      <c r="E170" t="s">
-        <v>374</v>
-      </c>
-      <c r="F170" t="s">
-        <v>375</v>
       </c>
       <c r="G170">
         <v>0.5</v>
@@ -37494,16 +37496,16 @@
         <v>0</v>
       </c>
       <c r="C171" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D171" t="s">
+        <v>374</v>
+      </c>
+      <c r="E171" t="s">
+        <v>375</v>
+      </c>
+      <c r="F171" t="s">
         <v>376</v>
-      </c>
-      <c r="E171" t="s">
-        <v>377</v>
-      </c>
-      <c r="F171" t="s">
-        <v>378</v>
       </c>
       <c r="G171">
         <v>50</v>
@@ -37551,16 +37553,16 @@
         <v>0</v>
       </c>
       <c r="C172" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D172" t="s">
+        <v>377</v>
+      </c>
+      <c r="E172" t="s">
+        <v>378</v>
+      </c>
+      <c r="F172" t="s">
         <v>379</v>
-      </c>
-      <c r="E172" t="s">
-        <v>380</v>
-      </c>
-      <c r="F172" t="s">
-        <v>381</v>
       </c>
       <c r="G172">
         <v>0</v>
@@ -37608,16 +37610,16 @@
         <v>0</v>
       </c>
       <c r="C173" t="s">
+        <v>380</v>
+      </c>
+      <c r="D173" t="s">
+        <v>381</v>
+      </c>
+      <c r="E173" t="s">
         <v>382</v>
       </c>
-      <c r="D173" t="s">
+      <c r="F173" t="s">
         <v>383</v>
-      </c>
-      <c r="E173" t="s">
-        <v>384</v>
-      </c>
-      <c r="F173" t="s">
-        <v>385</v>
       </c>
       <c r="G173">
         <v>200</v>
@@ -37665,28 +37667,28 @@
         <v>0</v>
       </c>
       <c r="C174" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D174" t="s">
+        <v>384</v>
+      </c>
+      <c r="E174" t="s">
+        <v>385</v>
+      </c>
+      <c r="F174" t="s">
         <v>386</v>
-      </c>
-      <c r="E174" t="s">
-        <v>387</v>
-      </c>
-      <c r="F174" t="s">
-        <v>388</v>
       </c>
       <c r="G174">
         <v>55</v>
       </c>
       <c r="H174" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I174" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="J174" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="K174">
         <v>0</v>
@@ -37722,28 +37724,28 @@
         <v>0</v>
       </c>
       <c r="C175" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D175" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E175" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F175" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G175">
         <v>25</v>
       </c>
       <c r="H175" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I175">
         <v>2</v>
       </c>
       <c r="J175" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="K175">
         <v>0</v>
@@ -37779,28 +37781,28 @@
         <v>0</v>
       </c>
       <c r="C176" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D176" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E176" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F176" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G176">
         <v>12</v>
       </c>
       <c r="H176" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I176">
         <v>2.5</v>
       </c>
       <c r="J176" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="K176">
         <v>0</v>
@@ -37836,28 +37838,28 @@
         <v>0</v>
       </c>
       <c r="C177" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D177" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E177" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F177" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G177">
         <v>5.5</v>
       </c>
       <c r="H177" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I177">
         <v>3</v>
       </c>
       <c r="J177" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="K177">
         <v>0</v>
@@ -37893,28 +37895,28 @@
         <v>0</v>
       </c>
       <c r="C178" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D178" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E178" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F178" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G178">
         <v>1.8</v>
       </c>
       <c r="H178" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I178">
         <v>3.5</v>
       </c>
       <c r="J178" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="K178">
         <v>0</v>
@@ -37950,28 +37952,28 @@
         <v>0</v>
       </c>
       <c r="C179" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D179" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E179" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F179" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G179">
         <v>0.35</v>
       </c>
       <c r="H179" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I179">
         <v>4</v>
       </c>
       <c r="J179" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="K179">
         <v>0</v>
@@ -38007,28 +38009,28 @@
         <v>0</v>
       </c>
       <c r="C180" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D180" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E180" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F180" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G180">
         <v>0.08</v>
       </c>
       <c r="H180" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I180">
         <v>4.5</v>
       </c>
       <c r="J180" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="K180">
         <v>0</v>
@@ -38064,28 +38066,28 @@
         <v>0</v>
       </c>
       <c r="C181" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="D181" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E181" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F181" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="G181">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="H181" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="I181">
         <v>5</v>
       </c>
       <c r="J181" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="K181">
         <v>0</v>
@@ -38121,16 +38123,16 @@
         <v>0</v>
       </c>
       <c r="C182" t="s">
+        <v>534</v>
+      </c>
+      <c r="D182" t="s">
+        <v>535</v>
+      </c>
+      <c r="E182" t="s">
         <v>536</v>
       </c>
-      <c r="D182" t="s">
+      <c r="F182" t="s">
         <v>537</v>
-      </c>
-      <c r="E182" t="s">
-        <v>538</v>
-      </c>
-      <c r="F182" t="s">
-        <v>539</v>
       </c>
       <c r="G182">
         <v>5</v>
@@ -38178,16 +38180,16 @@
         <v>0</v>
       </c>
       <c r="C183" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D183" t="s">
+        <v>538</v>
+      </c>
+      <c r="E183" t="s">
+        <v>539</v>
+      </c>
+      <c r="F183" t="s">
         <v>540</v>
-      </c>
-      <c r="E183" t="s">
-        <v>541</v>
-      </c>
-      <c r="F183" t="s">
-        <v>542</v>
       </c>
       <c r="G183">
         <v>0</v>
@@ -38235,16 +38237,16 @@
         <v>0</v>
       </c>
       <c r="C184" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D184" t="s">
+        <v>949</v>
+      </c>
+      <c r="E184" t="s">
+        <v>950</v>
+      </c>
+      <c r="F184" t="s">
         <v>951</v>
-      </c>
-      <c r="E184" t="s">
-        <v>952</v>
-      </c>
-      <c r="F184" t="s">
-        <v>953</v>
       </c>
       <c r="G184">
         <v>0.1</v>
@@ -38292,16 +38294,16 @@
         <v>0</v>
       </c>
       <c r="C185" t="s">
+        <v>541</v>
+      </c>
+      <c r="D185" t="s">
+        <v>542</v>
+      </c>
+      <c r="E185" t="s">
         <v>543</v>
       </c>
-      <c r="D185" t="s">
+      <c r="F185" t="s">
         <v>544</v>
-      </c>
-      <c r="E185" t="s">
-        <v>545</v>
-      </c>
-      <c r="F185" t="s">
-        <v>546</v>
       </c>
       <c r="G185">
         <v>5</v>
@@ -38349,16 +38351,16 @@
         <v>0</v>
       </c>
       <c r="C186" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D186" t="s">
+        <v>545</v>
+      </c>
+      <c r="E186" t="s">
+        <v>546</v>
+      </c>
+      <c r="F186" t="s">
         <v>547</v>
-      </c>
-      <c r="E186" t="s">
-        <v>548</v>
-      </c>
-      <c r="F186" t="s">
-        <v>549</v>
       </c>
       <c r="G186">
         <v>55</v>
@@ -38406,16 +38408,16 @@
         <v>0</v>
       </c>
       <c r="C187" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D187" t="s">
+        <v>548</v>
+      </c>
+      <c r="E187" t="s">
+        <v>549</v>
+      </c>
+      <c r="F187" t="s">
         <v>550</v>
-      </c>
-      <c r="E187" t="s">
-        <v>551</v>
-      </c>
-      <c r="F187" t="s">
-        <v>552</v>
       </c>
       <c r="G187">
         <v>5000000</v>
@@ -38463,13 +38465,13 @@
         <v>0</v>
       </c>
       <c r="C188" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D188" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E188" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F188">
         <v>0</v>
@@ -38520,16 +38522,16 @@
         <v>0</v>
       </c>
       <c r="C189" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D189" t="s">
+        <v>552</v>
+      </c>
+      <c r="E189" t="s">
+        <v>553</v>
+      </c>
+      <c r="F189" t="s">
         <v>554</v>
-      </c>
-      <c r="E189" t="s">
-        <v>555</v>
-      </c>
-      <c r="F189" t="s">
-        <v>556</v>
       </c>
       <c r="G189">
         <v>3</v>
@@ -38577,16 +38579,16 @@
         <v>0</v>
       </c>
       <c r="C190" t="s">
+        <v>541</v>
+      </c>
+      <c r="D190" t="s">
+        <v>561</v>
+      </c>
+      <c r="E190" t="s">
         <v>543</v>
       </c>
-      <c r="D190" t="s">
-        <v>563</v>
-      </c>
-      <c r="E190" t="s">
-        <v>545</v>
-      </c>
       <c r="F190" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G190">
         <v>3</v>
@@ -38634,16 +38636,16 @@
         <v>0</v>
       </c>
       <c r="C191" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D191" t="s">
+        <v>563</v>
+      </c>
+      <c r="E191" t="s">
+        <v>564</v>
+      </c>
+      <c r="F191" t="s">
         <v>565</v>
-      </c>
-      <c r="E191" t="s">
-        <v>566</v>
-      </c>
-      <c r="F191" t="s">
-        <v>567</v>
       </c>
       <c r="G191">
         <v>50</v>
@@ -38691,16 +38693,16 @@
         <v>0</v>
       </c>
       <c r="C192" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D192" t="s">
+        <v>566</v>
+      </c>
+      <c r="E192" t="s">
+        <v>567</v>
+      </c>
+      <c r="F192" t="s">
         <v>568</v>
-      </c>
-      <c r="E192" t="s">
-        <v>569</v>
-      </c>
-      <c r="F192" t="s">
-        <v>570</v>
       </c>
       <c r="G192">
         <v>1000000</v>
@@ -38748,13 +38750,13 @@
         <v>0</v>
       </c>
       <c r="C193" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D193" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E193" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F193">
         <v>0</v>
@@ -38805,16 +38807,16 @@
         <v>0</v>
       </c>
       <c r="C194" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D194" t="s">
+        <v>571</v>
+      </c>
+      <c r="E194" t="s">
+        <v>572</v>
+      </c>
+      <c r="F194" t="s">
         <v>573</v>
-      </c>
-      <c r="E194" t="s">
-        <v>574</v>
-      </c>
-      <c r="F194" t="s">
-        <v>575</v>
       </c>
       <c r="G194">
         <v>3</v>
@@ -38862,16 +38864,16 @@
         <v>0</v>
       </c>
       <c r="C195" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D195" t="s">
+        <v>574</v>
+      </c>
+      <c r="E195" t="s">
+        <v>575</v>
+      </c>
+      <c r="F195" t="s">
         <v>576</v>
-      </c>
-      <c r="E195" t="s">
-        <v>577</v>
-      </c>
-      <c r="F195" t="s">
-        <v>578</v>
       </c>
       <c r="G195">
         <v>6</v>
@@ -38919,16 +38921,16 @@
         <v>0</v>
       </c>
       <c r="C196" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D196" t="s">
+        <v>917</v>
+      </c>
+      <c r="E196" t="s">
+        <v>918</v>
+      </c>
+      <c r="F196" t="s">
         <v>919</v>
-      </c>
-      <c r="E196" t="s">
-        <v>920</v>
-      </c>
-      <c r="F196" t="s">
-        <v>921</v>
       </c>
       <c r="G196">
         <v>20</v>
@@ -38976,16 +38978,16 @@
         <v>0</v>
       </c>
       <c r="C197" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D197" t="s">
+        <v>920</v>
+      </c>
+      <c r="E197" t="s">
+        <v>921</v>
+      </c>
+      <c r="F197" t="s">
         <v>922</v>
-      </c>
-      <c r="E197" t="s">
-        <v>923</v>
-      </c>
-      <c r="F197" t="s">
-        <v>924</v>
       </c>
       <c r="G197">
         <v>500000000</v>
@@ -39033,16 +39035,16 @@
         <v>0</v>
       </c>
       <c r="C198" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="D198" t="s">
+        <v>923</v>
+      </c>
+      <c r="E198" t="s">
+        <v>924</v>
+      </c>
+      <c r="F198" t="s">
         <v>925</v>
-      </c>
-      <c r="E198" t="s">
-        <v>926</v>
-      </c>
-      <c r="F198" t="s">
-        <v>927</v>
       </c>
       <c r="G198">
         <v>13</v>
@@ -39090,16 +39092,16 @@
         <v>0</v>
       </c>
       <c r="C199" t="s">
+        <v>500</v>
+      </c>
+      <c r="D199" t="s">
+        <v>501</v>
+      </c>
+      <c r="E199" t="s">
         <v>502</v>
       </c>
-      <c r="D199" t="s">
+      <c r="F199" t="s">
         <v>503</v>
-      </c>
-      <c r="E199" t="s">
-        <v>504</v>
-      </c>
-      <c r="F199" t="s">
-        <v>505</v>
       </c>
       <c r="G199">
         <v>0</v>
@@ -39147,16 +39149,16 @@
         <v>0</v>
       </c>
       <c r="C200" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D200" t="s">
+        <v>504</v>
+      </c>
+      <c r="E200" t="s">
+        <v>505</v>
+      </c>
+      <c r="F200" t="s">
         <v>506</v>
-      </c>
-      <c r="E200" t="s">
-        <v>507</v>
-      </c>
-      <c r="F200" t="s">
-        <v>508</v>
       </c>
       <c r="G200">
         <v>1.35</v>
@@ -39204,16 +39206,16 @@
         <v>0</v>
       </c>
       <c r="C201" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D201" t="s">
+        <v>507</v>
+      </c>
+      <c r="E201" t="s">
+        <v>508</v>
+      </c>
+      <c r="F201" t="s">
         <v>509</v>
-      </c>
-      <c r="E201" t="s">
-        <v>510</v>
-      </c>
-      <c r="F201" t="s">
-        <v>511</v>
       </c>
       <c r="G201">
         <v>0.05</v>
@@ -39261,16 +39263,16 @@
         <v>0</v>
       </c>
       <c r="C202" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D202" t="s">
+        <v>510</v>
+      </c>
+      <c r="E202" t="s">
+        <v>511</v>
+      </c>
+      <c r="F202" t="s">
         <v>512</v>
-      </c>
-      <c r="E202" t="s">
-        <v>513</v>
-      </c>
-      <c r="F202" t="s">
-        <v>514</v>
       </c>
       <c r="G202">
         <v>2</v>
@@ -39318,16 +39320,16 @@
         <v>0</v>
       </c>
       <c r="C203" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D203" t="s">
+        <v>513</v>
+      </c>
+      <c r="E203" t="s">
+        <v>514</v>
+      </c>
+      <c r="F203" t="s">
         <v>515</v>
-      </c>
-      <c r="E203" t="s">
-        <v>516</v>
-      </c>
-      <c r="F203" t="s">
-        <v>517</v>
       </c>
       <c r="G203">
         <v>0</v>
@@ -39375,16 +39377,16 @@
         <v>0</v>
       </c>
       <c r="C204" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D204" t="s">
+        <v>516</v>
+      </c>
+      <c r="E204" t="s">
+        <v>517</v>
+      </c>
+      <c r="F204" t="s">
         <v>518</v>
-      </c>
-      <c r="E204" t="s">
-        <v>519</v>
-      </c>
-      <c r="F204" t="s">
-        <v>520</v>
       </c>
       <c r="G204">
         <v>5</v>
@@ -39432,16 +39434,16 @@
         <v>0</v>
       </c>
       <c r="C205" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D205" t="s">
+        <v>519</v>
+      </c>
+      <c r="E205" t="s">
+        <v>520</v>
+      </c>
+      <c r="F205" t="s">
         <v>521</v>
-      </c>
-      <c r="E205" t="s">
-        <v>522</v>
-      </c>
-      <c r="F205" t="s">
-        <v>523</v>
       </c>
       <c r="G205">
         <v>8</v>
@@ -39489,16 +39491,16 @@
         <v>0</v>
       </c>
       <c r="C206" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D206" t="s">
+        <v>522</v>
+      </c>
+      <c r="E206" t="s">
+        <v>523</v>
+      </c>
+      <c r="F206" t="s">
         <v>524</v>
-      </c>
-      <c r="E206" t="s">
-        <v>525</v>
-      </c>
-      <c r="F206" t="s">
-        <v>526</v>
       </c>
       <c r="G206">
         <v>1</v>
@@ -39546,16 +39548,16 @@
         <v>0</v>
       </c>
       <c r="C207" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D207" t="s">
+        <v>525</v>
+      </c>
+      <c r="E207" t="s">
+        <v>526</v>
+      </c>
+      <c r="F207" t="s">
         <v>527</v>
-      </c>
-      <c r="E207" t="s">
-        <v>528</v>
-      </c>
-      <c r="F207" t="s">
-        <v>529</v>
       </c>
       <c r="G207">
         <v>0.15</v>
@@ -39603,16 +39605,16 @@
         <v>0</v>
       </c>
       <c r="C208" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D208" t="s">
+        <v>528</v>
+      </c>
+      <c r="E208" t="s">
+        <v>529</v>
+      </c>
+      <c r="F208" t="s">
         <v>530</v>
-      </c>
-      <c r="E208" t="s">
-        <v>531</v>
-      </c>
-      <c r="F208" t="s">
-        <v>532</v>
       </c>
       <c r="G208">
         <v>2</v>
@@ -39660,16 +39662,16 @@
         <v>0</v>
       </c>
       <c r="C209" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D209" t="s">
+        <v>531</v>
+      </c>
+      <c r="E209" t="s">
+        <v>532</v>
+      </c>
+      <c r="F209" t="s">
         <v>533</v>
-      </c>
-      <c r="E209" t="s">
-        <v>534</v>
-      </c>
-      <c r="F209" t="s">
-        <v>535</v>
       </c>
       <c r="G209">
         <v>3</v>
@@ -39717,16 +39719,16 @@
         <v>0</v>
       </c>
       <c r="C210" t="s">
+        <v>606</v>
+      </c>
+      <c r="D210" t="s">
+        <v>607</v>
+      </c>
+      <c r="E210" t="s">
         <v>608</v>
       </c>
-      <c r="D210" t="s">
+      <c r="F210" t="s">
         <v>609</v>
-      </c>
-      <c r="E210" t="s">
-        <v>610</v>
-      </c>
-      <c r="F210" t="s">
-        <v>611</v>
       </c>
       <c r="G210">
         <v>2</v>
@@ -39786,16 +39788,16 @@
         <v>0</v>
       </c>
       <c r="C211" t="s">
+        <v>610</v>
+      </c>
+      <c r="D211" t="s">
+        <v>611</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="F211" t="s">
         <v>612</v>
-      </c>
-      <c r="D211" t="s">
-        <v>613</v>
-      </c>
-      <c r="E211" s="3" t="s">
-        <v>991</v>
-      </c>
-      <c r="F211" t="s">
-        <v>614</v>
       </c>
       <c r="G211">
         <v>10000</v>
@@ -39867,16 +39869,16 @@
         <v>0</v>
       </c>
       <c r="C212" t="s">
+        <v>594</v>
+      </c>
+      <c r="D212" t="s">
+        <v>595</v>
+      </c>
+      <c r="E212" t="s">
         <v>596</v>
       </c>
-      <c r="D212" t="s">
+      <c r="F212" t="s">
         <v>597</v>
-      </c>
-      <c r="E212" t="s">
-        <v>598</v>
-      </c>
-      <c r="F212" t="s">
-        <v>599</v>
       </c>
       <c r="G212">
         <v>5</v>
@@ -39959,16 +39961,16 @@
         <v>0</v>
       </c>
       <c r="C213" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D213" t="s">
+        <v>598</v>
+      </c>
+      <c r="E213" t="s">
+        <v>599</v>
+      </c>
+      <c r="F213" t="s">
         <v>600</v>
-      </c>
-      <c r="E213" t="s">
-        <v>601</v>
-      </c>
-      <c r="F213" t="s">
-        <v>602</v>
       </c>
       <c r="G213">
         <v>0</v>
@@ -40051,16 +40053,16 @@
         <v>0</v>
       </c>
       <c r="C214" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D214" t="s">
+        <v>601</v>
+      </c>
+      <c r="E214" t="s">
+        <v>602</v>
+      </c>
+      <c r="F214" t="s">
         <v>603</v>
-      </c>
-      <c r="E214" t="s">
-        <v>604</v>
-      </c>
-      <c r="F214" t="s">
-        <v>605</v>
       </c>
       <c r="G214">
         <v>0</v>
@@ -40143,16 +40145,16 @@
         <v>0</v>
       </c>
       <c r="C215" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="D215" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="E215" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="F215" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G215">
         <v>0</v>
@@ -40235,16 +40237,16 @@
         <v>0</v>
       </c>
       <c r="C216" t="s">
+        <v>555</v>
+      </c>
+      <c r="D216" t="s">
+        <v>556</v>
+      </c>
+      <c r="E216" t="s">
         <v>557</v>
       </c>
-      <c r="D216" t="s">
+      <c r="F216" t="s">
         <v>558</v>
-      </c>
-      <c r="E216" t="s">
-        <v>559</v>
-      </c>
-      <c r="F216" t="s">
-        <v>560</v>
       </c>
       <c r="G216">
         <v>27</v>
@@ -40327,16 +40329,16 @@
         <v>0</v>
       </c>
       <c r="C217" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D217" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E217" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F217" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="G217">
         <v>36</v>
@@ -40419,13 +40421,13 @@
         <v>0</v>
       </c>
       <c r="C218" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D218" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E218" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="F218">
         <v>0</v>
@@ -40511,16 +40513,16 @@
         <v>0</v>
       </c>
       <c r="C219" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D219" t="s">
+        <v>588</v>
+      </c>
+      <c r="E219" t="s">
+        <v>589</v>
+      </c>
+      <c r="F219" t="s">
         <v>590</v>
-      </c>
-      <c r="E219" t="s">
-        <v>591</v>
-      </c>
-      <c r="F219" t="s">
-        <v>592</v>
       </c>
       <c r="G219">
         <v>9</v>
@@ -40603,16 +40605,16 @@
         <v>0</v>
       </c>
       <c r="C220" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D220" t="s">
+        <v>591</v>
+      </c>
+      <c r="E220" t="s">
+        <v>592</v>
+      </c>
+      <c r="F220" t="s">
         <v>593</v>
-      </c>
-      <c r="E220" t="s">
-        <v>594</v>
-      </c>
-      <c r="F220" t="s">
-        <v>595</v>
       </c>
       <c r="G220">
         <v>1</v>
@@ -40695,16 +40697,16 @@
         <v>0</v>
       </c>
       <c r="C221" t="s">
+        <v>613</v>
+      </c>
+      <c r="D221" t="s">
+        <v>614</v>
+      </c>
+      <c r="E221" t="s">
         <v>615</v>
       </c>
-      <c r="D221" t="s">
+      <c r="F221" t="s">
         <v>616</v>
-      </c>
-      <c r="E221" t="s">
-        <v>617</v>
-      </c>
-      <c r="F221" t="s">
-        <v>618</v>
       </c>
       <c r="G221">
         <v>20000</v>
@@ -40787,13 +40789,13 @@
         <v>0</v>
       </c>
       <c r="C222" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D222" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E222" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="F222">
         <v>0</v>
@@ -40879,16 +40881,16 @@
         <v>0</v>
       </c>
       <c r="C223" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D223" t="s">
+        <v>619</v>
+      </c>
+      <c r="E223" t="s">
+        <v>620</v>
+      </c>
+      <c r="F223" t="s">
         <v>621</v>
-      </c>
-      <c r="E223" t="s">
-        <v>622</v>
-      </c>
-      <c r="F223" t="s">
-        <v>623</v>
       </c>
       <c r="G223">
         <v>100</v>
@@ -40971,16 +40973,16 @@
         <v>0</v>
       </c>
       <c r="C224" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D224" t="s">
+        <v>622</v>
+      </c>
+      <c r="E224" t="s">
+        <v>623</v>
+      </c>
+      <c r="F224" t="s">
         <v>624</v>
-      </c>
-      <c r="E224" t="s">
-        <v>625</v>
-      </c>
-      <c r="F224" t="s">
-        <v>626</v>
       </c>
       <c r="G224">
         <v>10000</v>
@@ -41063,13 +41065,13 @@
         <v>0</v>
       </c>
       <c r="C225" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="D225" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E225" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="F225">
         <v>0</v>
@@ -41155,16 +41157,16 @@
         <v>0</v>
       </c>
       <c r="C226" t="s">
+        <v>577</v>
+      </c>
+      <c r="D226" t="s">
+        <v>578</v>
+      </c>
+      <c r="E226" t="s">
         <v>579</v>
       </c>
-      <c r="D226" t="s">
+      <c r="F226" t="s">
         <v>580</v>
-      </c>
-      <c r="E226" t="s">
-        <v>581</v>
-      </c>
-      <c r="F226" t="s">
-        <v>582</v>
       </c>
       <c r="G226">
         <v>30</v>
@@ -41247,13 +41249,13 @@
         <v>0</v>
       </c>
       <c r="C227" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D227" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E227" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F227">
         <v>0</v>
@@ -41339,13 +41341,13 @@
         <v>0</v>
       </c>
       <c r="C228" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D228" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E228" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F228">
         <v>0</v>
@@ -41431,16 +41433,16 @@
         <v>0</v>
       </c>
       <c r="C229" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="D229" t="s">
+        <v>584</v>
+      </c>
+      <c r="E229" t="s">
+        <v>585</v>
+      </c>
+      <c r="F229" t="s">
         <v>586</v>
-      </c>
-      <c r="E229" t="s">
-        <v>587</v>
-      </c>
-      <c r="F229" t="s">
-        <v>588</v>
       </c>
       <c r="G229">
         <v>0</v>
@@ -41523,16 +41525,16 @@
         <v>0</v>
       </c>
       <c r="C230" t="s">
+        <v>627</v>
+      </c>
+      <c r="D230" t="s">
+        <v>628</v>
+      </c>
+      <c r="E230" t="s">
         <v>629</v>
       </c>
-      <c r="D230" t="s">
+      <c r="F230" t="s">
         <v>630</v>
-      </c>
-      <c r="E230" t="s">
-        <v>631</v>
-      </c>
-      <c r="F230" t="s">
-        <v>632</v>
       </c>
       <c r="G230">
         <v>0.2</v>
@@ -41615,16 +41617,16 @@
         <v>0</v>
       </c>
       <c r="C231" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D231" t="s">
+        <v>631</v>
+      </c>
+      <c r="E231" t="s">
+        <v>632</v>
+      </c>
+      <c r="F231" t="s">
         <v>633</v>
-      </c>
-      <c r="E231" t="s">
-        <v>634</v>
-      </c>
-      <c r="F231" t="s">
-        <v>635</v>
       </c>
       <c r="G231">
         <v>2</v>
@@ -41707,16 +41709,16 @@
         <v>0</v>
       </c>
       <c r="C232" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D232" t="s">
+        <v>634</v>
+      </c>
+      <c r="E232" t="s">
+        <v>635</v>
+      </c>
+      <c r="F232" t="s">
         <v>636</v>
-      </c>
-      <c r="E232" t="s">
-        <v>637</v>
-      </c>
-      <c r="F232" t="s">
-        <v>638</v>
       </c>
       <c r="G232">
         <v>3</v>
@@ -41768,16 +41770,16 @@
         <v>0</v>
       </c>
       <c r="C233" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D233" t="s">
+        <v>637</v>
+      </c>
+      <c r="E233" t="s">
+        <v>638</v>
+      </c>
+      <c r="F233" t="s">
         <v>639</v>
-      </c>
-      <c r="E233" t="s">
-        <v>640</v>
-      </c>
-      <c r="F233" t="s">
-        <v>641</v>
       </c>
       <c r="G233">
         <v>3</v>
@@ -41825,16 +41827,16 @@
         <v>0</v>
       </c>
       <c r="C234" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D234" t="s">
+        <v>640</v>
+      </c>
+      <c r="E234" t="s">
+        <v>641</v>
+      </c>
+      <c r="F234" t="s">
         <v>642</v>
-      </c>
-      <c r="E234" t="s">
-        <v>643</v>
-      </c>
-      <c r="F234" t="s">
-        <v>644</v>
       </c>
       <c r="G234">
         <v>100</v>
@@ -41882,16 +41884,16 @@
         <v>0</v>
       </c>
       <c r="C235" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D235" t="s">
+        <v>643</v>
+      </c>
+      <c r="E235" t="s">
+        <v>644</v>
+      </c>
+      <c r="F235" t="s">
         <v>645</v>
-      </c>
-      <c r="E235" t="s">
-        <v>646</v>
-      </c>
-      <c r="F235" t="s">
-        <v>647</v>
       </c>
       <c r="G235">
         <v>9</v>
@@ -41939,16 +41941,16 @@
         <v>0</v>
       </c>
       <c r="C236" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D236" t="s">
+        <v>646</v>
+      </c>
+      <c r="E236" t="s">
+        <v>647</v>
+      </c>
+      <c r="F236" t="s">
         <v>648</v>
-      </c>
-      <c r="E236" t="s">
-        <v>649</v>
-      </c>
-      <c r="F236" t="s">
-        <v>650</v>
       </c>
       <c r="G236">
         <v>0.7</v>
@@ -41996,16 +41998,16 @@
         <v>0</v>
       </c>
       <c r="C237" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D237" t="s">
+        <v>649</v>
+      </c>
+      <c r="E237" t="s">
+        <v>650</v>
+      </c>
+      <c r="F237" t="s">
         <v>651</v>
-      </c>
-      <c r="E237" t="s">
-        <v>652</v>
-      </c>
-      <c r="F237" t="s">
-        <v>653</v>
       </c>
       <c r="G237">
         <v>0.7</v>
@@ -42053,16 +42055,16 @@
         <v>0</v>
       </c>
       <c r="C238" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D238" t="s">
+        <v>652</v>
+      </c>
+      <c r="E238" t="s">
+        <v>653</v>
+      </c>
+      <c r="F238" t="s">
         <v>654</v>
-      </c>
-      <c r="E238" t="s">
-        <v>655</v>
-      </c>
-      <c r="F238" t="s">
-        <v>656</v>
       </c>
       <c r="G238">
         <v>10</v>
@@ -42110,16 +42112,16 @@
         <v>0</v>
       </c>
       <c r="C239" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D239" t="s">
+        <v>655</v>
+      </c>
+      <c r="E239" t="s">
+        <v>656</v>
+      </c>
+      <c r="F239" t="s">
         <v>657</v>
-      </c>
-      <c r="E239" t="s">
-        <v>658</v>
-      </c>
-      <c r="F239" t="s">
-        <v>659</v>
       </c>
       <c r="G239">
         <v>0</v>
@@ -42167,16 +42169,16 @@
         <v>0</v>
       </c>
       <c r="C240" t="s">
+        <v>658</v>
+      </c>
+      <c r="D240" t="s">
+        <v>659</v>
+      </c>
+      <c r="E240" t="s">
         <v>660</v>
       </c>
-      <c r="D240" t="s">
+      <c r="F240" t="s">
         <v>661</v>
-      </c>
-      <c r="E240" t="s">
-        <v>662</v>
-      </c>
-      <c r="F240" t="s">
-        <v>663</v>
       </c>
       <c r="G240">
         <v>100000</v>
@@ -42224,16 +42226,16 @@
         <v>0</v>
       </c>
       <c r="C241" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D241" t="s">
+        <v>662</v>
+      </c>
+      <c r="E241" t="s">
+        <v>663</v>
+      </c>
+      <c r="F241" t="s">
         <v>664</v>
-      </c>
-      <c r="E241" t="s">
-        <v>665</v>
-      </c>
-      <c r="F241" t="s">
-        <v>666</v>
       </c>
       <c r="G241">
         <v>5000</v>
@@ -42281,13 +42283,13 @@
         <v>0</v>
       </c>
       <c r="C242" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D242" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="E242" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="F242">
         <v>0</v>
@@ -42338,16 +42340,16 @@
         <v>0</v>
       </c>
       <c r="C243" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D243" t="s">
+        <v>667</v>
+      </c>
+      <c r="E243" t="s">
+        <v>668</v>
+      </c>
+      <c r="F243" t="s">
         <v>669</v>
-      </c>
-      <c r="E243" t="s">
-        <v>670</v>
-      </c>
-      <c r="F243" t="s">
-        <v>671</v>
       </c>
       <c r="G243">
         <v>10000</v>
@@ -42395,28 +42397,28 @@
         <v>0</v>
       </c>
       <c r="C244" t="s">
+        <v>741</v>
+      </c>
+      <c r="D244" t="s">
+        <v>671</v>
+      </c>
+      <c r="E244" t="s">
+        <v>742</v>
+      </c>
+      <c r="F244" t="s">
         <v>743</v>
       </c>
-      <c r="D244" t="s">
-        <v>673</v>
-      </c>
-      <c r="E244" t="s">
+      <c r="G244" t="s">
         <v>744</v>
       </c>
-      <c r="F244" t="s">
+      <c r="H244" t="s">
         <v>745</v>
       </c>
-      <c r="G244" t="s">
+      <c r="I244" t="s">
         <v>746</v>
       </c>
-      <c r="H244" t="s">
+      <c r="J244" t="s">
         <v>747</v>
-      </c>
-      <c r="I244" t="s">
-        <v>748</v>
-      </c>
-      <c r="J244" t="s">
-        <v>749</v>
       </c>
       <c r="K244">
         <v>0</v>
@@ -42452,28 +42454,28 @@
         <v>0</v>
       </c>
       <c r="C245" t="s">
+        <v>741</v>
+      </c>
+      <c r="D245" t="s">
+        <v>676</v>
+      </c>
+      <c r="E245" t="s">
+        <v>742</v>
+      </c>
+      <c r="F245" t="s">
         <v>743</v>
       </c>
-      <c r="D245" t="s">
-        <v>678</v>
-      </c>
-      <c r="E245" t="s">
-        <v>744</v>
-      </c>
-      <c r="F245" t="s">
+      <c r="G245" t="s">
+        <v>748</v>
+      </c>
+      <c r="H245" t="s">
         <v>745</v>
       </c>
-      <c r="G245" t="s">
+      <c r="I245" t="s">
+        <v>749</v>
+      </c>
+      <c r="J245" t="s">
         <v>750</v>
-      </c>
-      <c r="H245" t="s">
-        <v>747</v>
-      </c>
-      <c r="I245" t="s">
-        <v>751</v>
-      </c>
-      <c r="J245" t="s">
-        <v>752</v>
       </c>
       <c r="K245">
         <v>0</v>
@@ -42509,28 +42511,28 @@
         <v>0</v>
       </c>
       <c r="C246" t="s">
+        <v>741</v>
+      </c>
+      <c r="D246" t="s">
+        <v>679</v>
+      </c>
+      <c r="E246" t="s">
+        <v>742</v>
+      </c>
+      <c r="F246" t="s">
         <v>743</v>
       </c>
-      <c r="D246" t="s">
-        <v>681</v>
-      </c>
-      <c r="E246" t="s">
-        <v>744</v>
-      </c>
-      <c r="F246" t="s">
+      <c r="G246" t="s">
+        <v>751</v>
+      </c>
+      <c r="H246" t="s">
         <v>745</v>
       </c>
-      <c r="G246" t="s">
+      <c r="I246" t="s">
+        <v>752</v>
+      </c>
+      <c r="J246" t="s">
         <v>753</v>
-      </c>
-      <c r="H246" t="s">
-        <v>747</v>
-      </c>
-      <c r="I246" t="s">
-        <v>754</v>
-      </c>
-      <c r="J246" t="s">
-        <v>755</v>
       </c>
       <c r="K246">
         <v>0</v>
@@ -42566,31 +42568,31 @@
         <v>0</v>
       </c>
       <c r="C247" t="s">
+        <v>741</v>
+      </c>
+      <c r="D247" t="s">
+        <v>682</v>
+      </c>
+      <c r="E247" t="s">
+        <v>742</v>
+      </c>
+      <c r="F247" t="s">
         <v>743</v>
       </c>
-      <c r="D247" t="s">
-        <v>684</v>
-      </c>
-      <c r="E247" t="s">
-        <v>744</v>
-      </c>
-      <c r="F247" t="s">
+      <c r="G247" t="s">
+        <v>754</v>
+      </c>
+      <c r="H247" t="s">
         <v>745</v>
       </c>
-      <c r="G247" t="s">
-        <v>756</v>
-      </c>
-      <c r="H247" t="s">
-        <v>747</v>
-      </c>
       <c r="I247" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="J247" t="s">
+        <v>753</v>
+      </c>
+      <c r="K247" t="s">
         <v>755</v>
-      </c>
-      <c r="K247" t="s">
-        <v>757</v>
       </c>
       <c r="L247">
         <v>0</v>
@@ -42623,31 +42625,31 @@
         <v>0</v>
       </c>
       <c r="C248" t="s">
+        <v>741</v>
+      </c>
+      <c r="D248" t="s">
+        <v>685</v>
+      </c>
+      <c r="E248" t="s">
+        <v>742</v>
+      </c>
+      <c r="F248" t="s">
         <v>743</v>
       </c>
-      <c r="D248" t="s">
-        <v>687</v>
-      </c>
-      <c r="E248" t="s">
-        <v>744</v>
-      </c>
-      <c r="F248" t="s">
+      <c r="G248" t="s">
+        <v>756</v>
+      </c>
+      <c r="H248" t="s">
         <v>745</v>
       </c>
-      <c r="G248" t="s">
+      <c r="I248" t="s">
+        <v>752</v>
+      </c>
+      <c r="J248" t="s">
+        <v>757</v>
+      </c>
+      <c r="K248" t="s">
         <v>758</v>
-      </c>
-      <c r="H248" t="s">
-        <v>747</v>
-      </c>
-      <c r="I248" t="s">
-        <v>754</v>
-      </c>
-      <c r="J248" t="s">
-        <v>759</v>
-      </c>
-      <c r="K248" t="s">
-        <v>760</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -42680,31 +42682,31 @@
         <v>0</v>
       </c>
       <c r="C249" t="s">
+        <v>741</v>
+      </c>
+      <c r="D249" t="s">
+        <v>688</v>
+      </c>
+      <c r="E249" t="s">
+        <v>742</v>
+      </c>
+      <c r="F249" t="s">
         <v>743</v>
       </c>
-      <c r="D249" t="s">
-        <v>690</v>
-      </c>
-      <c r="E249" t="s">
-        <v>744</v>
-      </c>
-      <c r="F249" t="s">
+      <c r="G249" t="s">
+        <v>759</v>
+      </c>
+      <c r="H249" t="s">
         <v>745</v>
       </c>
-      <c r="G249" t="s">
+      <c r="I249" t="s">
+        <v>752</v>
+      </c>
+      <c r="J249" t="s">
+        <v>760</v>
+      </c>
+      <c r="K249" t="s">
         <v>761</v>
-      </c>
-      <c r="H249" t="s">
-        <v>747</v>
-      </c>
-      <c r="I249" t="s">
-        <v>754</v>
-      </c>
-      <c r="J249" t="s">
-        <v>762</v>
-      </c>
-      <c r="K249" t="s">
-        <v>763</v>
       </c>
       <c r="L249">
         <v>0</v>
@@ -42737,31 +42739,31 @@
         <v>0</v>
       </c>
       <c r="C250" t="s">
+        <v>741</v>
+      </c>
+      <c r="D250" t="s">
+        <v>691</v>
+      </c>
+      <c r="E250" t="s">
+        <v>742</v>
+      </c>
+      <c r="F250" t="s">
         <v>743</v>
       </c>
-      <c r="D250" t="s">
-        <v>693</v>
-      </c>
-      <c r="E250" t="s">
-        <v>744</v>
-      </c>
-      <c r="F250" t="s">
+      <c r="G250" t="s">
+        <v>762</v>
+      </c>
+      <c r="H250" t="s">
         <v>745</v>
       </c>
-      <c r="G250" t="s">
+      <c r="I250" t="s">
+        <v>763</v>
+      </c>
+      <c r="J250" t="s">
         <v>764</v>
       </c>
-      <c r="H250" t="s">
-        <v>747</v>
-      </c>
-      <c r="I250" t="s">
+      <c r="K250" t="s">
         <v>765</v>
-      </c>
-      <c r="J250" t="s">
-        <v>766</v>
-      </c>
-      <c r="K250" t="s">
-        <v>767</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -42794,31 +42796,31 @@
         <v>0</v>
       </c>
       <c r="C251" t="s">
+        <v>741</v>
+      </c>
+      <c r="D251" t="s">
+        <v>696</v>
+      </c>
+      <c r="E251" t="s">
+        <v>742</v>
+      </c>
+      <c r="F251" t="s">
         <v>743</v>
       </c>
-      <c r="D251" t="s">
-        <v>698</v>
-      </c>
-      <c r="E251" t="s">
-        <v>744</v>
-      </c>
-      <c r="F251" t="s">
+      <c r="G251" t="s">
+        <v>766</v>
+      </c>
+      <c r="H251" t="s">
         <v>745</v>
       </c>
-      <c r="G251" t="s">
+      <c r="I251" t="s">
+        <v>767</v>
+      </c>
+      <c r="J251" t="s">
         <v>768</v>
       </c>
-      <c r="H251" t="s">
-        <v>747</v>
-      </c>
-      <c r="I251" t="s">
+      <c r="K251" t="s">
         <v>769</v>
-      </c>
-      <c r="J251" t="s">
-        <v>770</v>
-      </c>
-      <c r="K251" t="s">
-        <v>771</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -42851,31 +42853,31 @@
         <v>0</v>
       </c>
       <c r="C252" t="s">
+        <v>741</v>
+      </c>
+      <c r="D252" t="s">
+        <v>698</v>
+      </c>
+      <c r="E252" t="s">
+        <v>742</v>
+      </c>
+      <c r="F252" t="s">
         <v>743</v>
       </c>
-      <c r="D252" t="s">
-        <v>700</v>
-      </c>
-      <c r="E252" t="s">
-        <v>744</v>
-      </c>
-      <c r="F252" t="s">
+      <c r="G252" t="s">
+        <v>770</v>
+      </c>
+      <c r="H252" t="s">
         <v>745</v>
       </c>
-      <c r="G252" t="s">
+      <c r="I252" t="s">
+        <v>771</v>
+      </c>
+      <c r="J252" t="s">
         <v>772</v>
       </c>
-      <c r="H252" t="s">
-        <v>747</v>
-      </c>
-      <c r="I252" t="s">
+      <c r="K252" t="s">
         <v>773</v>
-      </c>
-      <c r="J252" t="s">
-        <v>774</v>
-      </c>
-      <c r="K252" t="s">
-        <v>775</v>
       </c>
       <c r="L252">
         <v>0</v>
@@ -42908,34 +42910,34 @@
         <v>0</v>
       </c>
       <c r="C253" t="s">
+        <v>741</v>
+      </c>
+      <c r="D253" t="s">
+        <v>702</v>
+      </c>
+      <c r="E253" t="s">
+        <v>742</v>
+      </c>
+      <c r="F253" t="s">
         <v>743</v>
       </c>
-      <c r="D253" t="s">
-        <v>704</v>
-      </c>
-      <c r="E253" t="s">
-        <v>744</v>
-      </c>
-      <c r="F253" t="s">
+      <c r="G253" t="s">
+        <v>774</v>
+      </c>
+      <c r="H253" t="s">
         <v>745</v>
       </c>
-      <c r="G253" t="s">
+      <c r="I253" t="s">
+        <v>771</v>
+      </c>
+      <c r="J253" t="s">
+        <v>772</v>
+      </c>
+      <c r="K253" t="s">
+        <v>775</v>
+      </c>
+      <c r="L253" t="s">
         <v>776</v>
-      </c>
-      <c r="H253" t="s">
-        <v>747</v>
-      </c>
-      <c r="I253" t="s">
-        <v>773</v>
-      </c>
-      <c r="J253" t="s">
-        <v>774</v>
-      </c>
-      <c r="K253" t="s">
-        <v>777</v>
-      </c>
-      <c r="L253" t="s">
-        <v>778</v>
       </c>
       <c r="M253">
         <v>0</v>
@@ -42965,34 +42967,34 @@
         <v>0</v>
       </c>
       <c r="C254" t="s">
+        <v>741</v>
+      </c>
+      <c r="D254" t="s">
+        <v>706</v>
+      </c>
+      <c r="E254" t="s">
+        <v>742</v>
+      </c>
+      <c r="F254" t="s">
         <v>743</v>
       </c>
-      <c r="D254" t="s">
-        <v>708</v>
-      </c>
-      <c r="E254" t="s">
-        <v>744</v>
-      </c>
-      <c r="F254" t="s">
+      <c r="G254" t="s">
+        <v>777</v>
+      </c>
+      <c r="H254" t="s">
         <v>745</v>
       </c>
-      <c r="G254" t="s">
+      <c r="I254" t="s">
+        <v>771</v>
+      </c>
+      <c r="J254" t="s">
+        <v>772</v>
+      </c>
+      <c r="K254" t="s">
+        <v>778</v>
+      </c>
+      <c r="L254" t="s">
         <v>779</v>
-      </c>
-      <c r="H254" t="s">
-        <v>747</v>
-      </c>
-      <c r="I254" t="s">
-        <v>773</v>
-      </c>
-      <c r="J254" t="s">
-        <v>774</v>
-      </c>
-      <c r="K254" t="s">
-        <v>780</v>
-      </c>
-      <c r="L254" t="s">
-        <v>781</v>
       </c>
       <c r="M254">
         <v>0</v>
@@ -43022,34 +43024,34 @@
         <v>0</v>
       </c>
       <c r="C255" t="s">
+        <v>741</v>
+      </c>
+      <c r="D255" t="s">
+        <v>710</v>
+      </c>
+      <c r="E255" t="s">
+        <v>742</v>
+      </c>
+      <c r="F255" t="s">
         <v>743</v>
       </c>
-      <c r="D255" t="s">
-        <v>712</v>
-      </c>
-      <c r="E255" t="s">
-        <v>744</v>
-      </c>
-      <c r="F255" t="s">
+      <c r="G255" t="s">
+        <v>780</v>
+      </c>
+      <c r="H255" t="s">
         <v>745</v>
       </c>
-      <c r="G255" t="s">
+      <c r="I255" t="s">
+        <v>781</v>
+      </c>
+      <c r="J255" t="s">
         <v>782</v>
       </c>
-      <c r="H255" t="s">
-        <v>747</v>
-      </c>
-      <c r="I255" t="s">
+      <c r="K255" t="s">
         <v>783</v>
       </c>
-      <c r="J255" t="s">
+      <c r="L255" t="s">
         <v>784</v>
-      </c>
-      <c r="K255" t="s">
-        <v>785</v>
-      </c>
-      <c r="L255" t="s">
-        <v>786</v>
       </c>
       <c r="M255">
         <v>0</v>
@@ -43079,34 +43081,34 @@
         <v>0</v>
       </c>
       <c r="C256" t="s">
+        <v>741</v>
+      </c>
+      <c r="D256" t="s">
+        <v>714</v>
+      </c>
+      <c r="E256" t="s">
+        <v>742</v>
+      </c>
+      <c r="F256" t="s">
         <v>743</v>
       </c>
-      <c r="D256" t="s">
-        <v>716</v>
-      </c>
-      <c r="E256" t="s">
-        <v>744</v>
-      </c>
-      <c r="F256" t="s">
+      <c r="G256" t="s">
+        <v>785</v>
+      </c>
+      <c r="H256" t="s">
         <v>745</v>
       </c>
-      <c r="G256" t="s">
-        <v>787</v>
-      </c>
-      <c r="H256" t="s">
-        <v>747</v>
-      </c>
       <c r="I256" t="s">
+        <v>781</v>
+      </c>
+      <c r="J256" t="s">
+        <v>782</v>
+      </c>
+      <c r="K256" t="s">
         <v>783</v>
       </c>
-      <c r="J256" t="s">
-        <v>784</v>
-      </c>
-      <c r="K256" t="s">
-        <v>785</v>
-      </c>
       <c r="L256" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="M256">
         <v>0</v>
@@ -43136,34 +43138,34 @@
         <v>0</v>
       </c>
       <c r="C257" t="s">
+        <v>741</v>
+      </c>
+      <c r="D257" t="s">
+        <v>718</v>
+      </c>
+      <c r="E257" t="s">
+        <v>742</v>
+      </c>
+      <c r="F257" t="s">
         <v>743</v>
       </c>
-      <c r="D257" t="s">
-        <v>720</v>
-      </c>
-      <c r="E257" t="s">
-        <v>744</v>
-      </c>
-      <c r="F257" t="s">
+      <c r="G257" t="s">
+        <v>787</v>
+      </c>
+      <c r="H257" t="s">
         <v>745</v>
       </c>
-      <c r="G257" t="s">
-        <v>789</v>
-      </c>
-      <c r="H257" t="s">
-        <v>747</v>
-      </c>
       <c r="I257" t="s">
+        <v>781</v>
+      </c>
+      <c r="J257" t="s">
+        <v>782</v>
+      </c>
+      <c r="K257" t="s">
         <v>783</v>
       </c>
-      <c r="J257" t="s">
-        <v>784</v>
-      </c>
-      <c r="K257" t="s">
-        <v>785</v>
-      </c>
       <c r="L257" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="M257">
         <v>0</v>
@@ -43193,37 +43195,37 @@
         <v>0</v>
       </c>
       <c r="C258" t="s">
+        <v>741</v>
+      </c>
+      <c r="D258" t="s">
+        <v>722</v>
+      </c>
+      <c r="E258" t="s">
+        <v>742</v>
+      </c>
+      <c r="F258" t="s">
         <v>743</v>
       </c>
-      <c r="D258" t="s">
-        <v>724</v>
-      </c>
-      <c r="E258" t="s">
-        <v>744</v>
-      </c>
-      <c r="F258" t="s">
+      <c r="G258" t="s">
+        <v>789</v>
+      </c>
+      <c r="H258" t="s">
         <v>745</v>
       </c>
-      <c r="G258" t="s">
+      <c r="I258" t="s">
+        <v>781</v>
+      </c>
+      <c r="J258" t="s">
+        <v>790</v>
+      </c>
+      <c r="K258" t="s">
         <v>791</v>
       </c>
-      <c r="H258" t="s">
-        <v>747</v>
-      </c>
-      <c r="I258" t="s">
-        <v>783</v>
-      </c>
-      <c r="J258" t="s">
+      <c r="L258" t="s">
+        <v>784</v>
+      </c>
+      <c r="M258" t="s">
         <v>792</v>
-      </c>
-      <c r="K258" t="s">
-        <v>793</v>
-      </c>
-      <c r="L258" t="s">
-        <v>786</v>
-      </c>
-      <c r="M258" t="s">
-        <v>794</v>
       </c>
       <c r="N258">
         <v>0</v>
@@ -43250,37 +43252,37 @@
         <v>0</v>
       </c>
       <c r="C259" t="s">
+        <v>741</v>
+      </c>
+      <c r="D259" t="s">
+        <v>726</v>
+      </c>
+      <c r="E259" t="s">
+        <v>742</v>
+      </c>
+      <c r="F259" t="s">
         <v>743</v>
       </c>
-      <c r="D259" t="s">
-        <v>728</v>
-      </c>
-      <c r="E259" t="s">
-        <v>744</v>
-      </c>
-      <c r="F259" t="s">
+      <c r="G259" t="s">
+        <v>793</v>
+      </c>
+      <c r="H259" t="s">
         <v>745</v>
       </c>
-      <c r="G259" t="s">
-        <v>795</v>
-      </c>
-      <c r="H259" t="s">
-        <v>747</v>
-      </c>
       <c r="I259" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="J259" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="K259" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="L259" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="M259" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="N259">
         <v>0</v>
@@ -43307,37 +43309,37 @@
         <v>0</v>
       </c>
       <c r="C260" t="s">
+        <v>741</v>
+      </c>
+      <c r="D260" t="s">
+        <v>730</v>
+      </c>
+      <c r="E260" t="s">
+        <v>742</v>
+      </c>
+      <c r="F260" t="s">
         <v>743</v>
       </c>
-      <c r="D260" t="s">
-        <v>732</v>
-      </c>
-      <c r="E260" t="s">
-        <v>744</v>
-      </c>
-      <c r="F260" t="s">
+      <c r="G260" t="s">
+        <v>795</v>
+      </c>
+      <c r="H260" t="s">
         <v>745</v>
       </c>
-      <c r="G260" t="s">
-        <v>797</v>
-      </c>
-      <c r="H260" t="s">
-        <v>747</v>
-      </c>
       <c r="I260" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="J260" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="K260" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="L260" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="M260" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="N260">
         <v>0</v>
@@ -43364,40 +43366,40 @@
         <v>0</v>
       </c>
       <c r="C261" t="s">
+        <v>741</v>
+      </c>
+      <c r="D261" t="s">
+        <v>734</v>
+      </c>
+      <c r="E261" t="s">
+        <v>742</v>
+      </c>
+      <c r="F261" t="s">
         <v>743</v>
       </c>
-      <c r="D261" t="s">
-        <v>736</v>
-      </c>
-      <c r="E261" t="s">
-        <v>744</v>
-      </c>
-      <c r="F261" t="s">
+      <c r="G261" t="s">
+        <v>797</v>
+      </c>
+      <c r="H261" t="s">
         <v>745</v>
       </c>
-      <c r="G261" t="s">
-        <v>799</v>
-      </c>
-      <c r="H261" t="s">
-        <v>747</v>
-      </c>
       <c r="I261" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="J261" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="K261" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="L261" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="M261" t="s">
+        <v>796</v>
+      </c>
+      <c r="N261" t="s">
         <v>798</v>
-      </c>
-      <c r="N261" t="s">
-        <v>800</v>
       </c>
       <c r="O261">
         <v>0</v>
@@ -43421,43 +43423,43 @@
         <v>0</v>
       </c>
       <c r="C262" t="s">
+        <v>741</v>
+      </c>
+      <c r="D262" t="s">
+        <v>739</v>
+      </c>
+      <c r="E262" t="s">
+        <v>742</v>
+      </c>
+      <c r="F262" t="s">
         <v>743</v>
       </c>
-      <c r="D262" t="s">
-        <v>741</v>
-      </c>
-      <c r="E262" t="s">
-        <v>744</v>
-      </c>
-      <c r="F262" t="s">
+      <c r="G262" t="s">
+        <v>799</v>
+      </c>
+      <c r="H262" t="s">
         <v>745</v>
       </c>
-      <c r="G262" t="s">
+      <c r="I262" t="s">
+        <v>781</v>
+      </c>
+      <c r="J262" t="s">
+        <v>790</v>
+      </c>
+      <c r="K262" t="s">
+        <v>791</v>
+      </c>
+      <c r="L262" t="s">
+        <v>786</v>
+      </c>
+      <c r="M262" t="s">
+        <v>796</v>
+      </c>
+      <c r="N262" t="s">
+        <v>800</v>
+      </c>
+      <c r="O262" t="s">
         <v>801</v>
-      </c>
-      <c r="H262" t="s">
-        <v>747</v>
-      </c>
-      <c r="I262" t="s">
-        <v>783</v>
-      </c>
-      <c r="J262" t="s">
-        <v>792</v>
-      </c>
-      <c r="K262" t="s">
-        <v>793</v>
-      </c>
-      <c r="L262" t="s">
-        <v>788</v>
-      </c>
-      <c r="M262" t="s">
-        <v>798</v>
-      </c>
-      <c r="N262" t="s">
-        <v>802</v>
-      </c>
-      <c r="O262" t="s">
-        <v>803</v>
       </c>
       <c r="P262">
         <v>0</v>
@@ -43478,46 +43480,46 @@
         <v>0</v>
       </c>
       <c r="C263" t="s">
+        <v>741</v>
+      </c>
+      <c r="D263" t="s">
+        <v>740</v>
+      </c>
+      <c r="E263" t="s">
+        <v>742</v>
+      </c>
+      <c r="F263" t="s">
         <v>743</v>
       </c>
-      <c r="D263" t="s">
-        <v>742</v>
-      </c>
-      <c r="E263" t="s">
-        <v>744</v>
-      </c>
-      <c r="F263" t="s">
+      <c r="G263" t="s">
+        <v>802</v>
+      </c>
+      <c r="H263" t="s">
         <v>745</v>
       </c>
-      <c r="G263" t="s">
+      <c r="I263" t="s">
+        <v>781</v>
+      </c>
+      <c r="J263" t="s">
+        <v>790</v>
+      </c>
+      <c r="K263" t="s">
+        <v>791</v>
+      </c>
+      <c r="L263" t="s">
+        <v>786</v>
+      </c>
+      <c r="M263" t="s">
+        <v>796</v>
+      </c>
+      <c r="N263" t="s">
+        <v>803</v>
+      </c>
+      <c r="O263" t="s">
         <v>804</v>
       </c>
-      <c r="H263" t="s">
-        <v>747</v>
-      </c>
-      <c r="I263" t="s">
-        <v>783</v>
-      </c>
-      <c r="J263" t="s">
-        <v>792</v>
-      </c>
-      <c r="K263" t="s">
-        <v>793</v>
-      </c>
-      <c r="L263" t="s">
-        <v>788</v>
-      </c>
-      <c r="M263" t="s">
-        <v>798</v>
-      </c>
-      <c r="N263" t="s">
+      <c r="P263" t="s">
         <v>805</v>
-      </c>
-      <c r="O263" t="s">
-        <v>806</v>
-      </c>
-      <c r="P263" t="s">
-        <v>807</v>
       </c>
       <c r="Q263">
         <v>0</v>
@@ -43535,22 +43537,22 @@
         <v>0</v>
       </c>
       <c r="C264" t="s">
+        <v>670</v>
+      </c>
+      <c r="D264" t="s">
+        <v>671</v>
+      </c>
+      <c r="E264" t="s">
         <v>672</v>
       </c>
-      <c r="D264" t="s">
+      <c r="F264" t="s">
         <v>673</v>
       </c>
-      <c r="E264" t="s">
+      <c r="G264" t="s">
         <v>674</v>
       </c>
-      <c r="F264" t="s">
+      <c r="H264" t="s">
         <v>675</v>
-      </c>
-      <c r="G264" t="s">
-        <v>676</v>
-      </c>
-      <c r="H264" t="s">
-        <v>677</v>
       </c>
       <c r="I264">
         <v>0</v>
@@ -43592,25 +43594,25 @@
         <v>0</v>
       </c>
       <c r="C265" t="s">
+        <v>670</v>
+      </c>
+      <c r="D265" t="s">
+        <v>676</v>
+      </c>
+      <c r="E265" t="s">
         <v>672</v>
       </c>
-      <c r="D265" t="s">
+      <c r="F265" t="s">
+        <v>673</v>
+      </c>
+      <c r="G265" t="s">
+        <v>674</v>
+      </c>
+      <c r="H265" t="s">
+        <v>677</v>
+      </c>
+      <c r="I265" t="s">
         <v>678</v>
-      </c>
-      <c r="E265" t="s">
-        <v>674</v>
-      </c>
-      <c r="F265" t="s">
-        <v>675</v>
-      </c>
-      <c r="G265" t="s">
-        <v>676</v>
-      </c>
-      <c r="H265" t="s">
-        <v>679</v>
-      </c>
-      <c r="I265" t="s">
-        <v>680</v>
       </c>
       <c r="J265">
         <v>0</v>
@@ -43649,28 +43651,28 @@
         <v>0</v>
       </c>
       <c r="C266" t="s">
+        <v>670</v>
+      </c>
+      <c r="D266" t="s">
+        <v>679</v>
+      </c>
+      <c r="E266" t="s">
         <v>672</v>
       </c>
-      <c r="D266" t="s">
+      <c r="F266" t="s">
+        <v>673</v>
+      </c>
+      <c r="G266" t="s">
+        <v>674</v>
+      </c>
+      <c r="H266" t="s">
+        <v>680</v>
+      </c>
+      <c r="I266" t="s">
+        <v>678</v>
+      </c>
+      <c r="J266" t="s">
         <v>681</v>
-      </c>
-      <c r="E266" t="s">
-        <v>674</v>
-      </c>
-      <c r="F266" t="s">
-        <v>675</v>
-      </c>
-      <c r="G266" t="s">
-        <v>676</v>
-      </c>
-      <c r="H266" t="s">
-        <v>682</v>
-      </c>
-      <c r="I266" t="s">
-        <v>680</v>
-      </c>
-      <c r="J266" t="s">
-        <v>683</v>
       </c>
       <c r="K266">
         <v>0</v>
@@ -43706,28 +43708,28 @@
         <v>0</v>
       </c>
       <c r="C267" t="s">
+        <v>670</v>
+      </c>
+      <c r="D267" t="s">
+        <v>682</v>
+      </c>
+      <c r="E267" t="s">
         <v>672</v>
       </c>
-      <c r="D267" t="s">
+      <c r="F267" t="s">
+        <v>673</v>
+      </c>
+      <c r="G267" t="s">
+        <v>683</v>
+      </c>
+      <c r="H267" t="s">
+        <v>680</v>
+      </c>
+      <c r="I267" t="s">
         <v>684</v>
       </c>
-      <c r="E267" t="s">
-        <v>674</v>
-      </c>
-      <c r="F267" t="s">
-        <v>675</v>
-      </c>
-      <c r="G267" t="s">
-        <v>685</v>
-      </c>
-      <c r="H267" t="s">
-        <v>682</v>
-      </c>
-      <c r="I267" t="s">
-        <v>686</v>
-      </c>
       <c r="J267" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="K267">
         <v>0</v>
@@ -43763,28 +43765,28 @@
         <v>0</v>
       </c>
       <c r="C268" t="s">
+        <v>670</v>
+      </c>
+      <c r="D268" t="s">
+        <v>685</v>
+      </c>
+      <c r="E268" t="s">
         <v>672</v>
       </c>
-      <c r="D268" t="s">
+      <c r="F268" t="s">
+        <v>673</v>
+      </c>
+      <c r="G268" t="s">
+        <v>686</v>
+      </c>
+      <c r="H268" t="s">
+        <v>680</v>
+      </c>
+      <c r="I268" t="s">
+        <v>684</v>
+      </c>
+      <c r="J268" t="s">
         <v>687</v>
-      </c>
-      <c r="E268" t="s">
-        <v>674</v>
-      </c>
-      <c r="F268" t="s">
-        <v>675</v>
-      </c>
-      <c r="G268" t="s">
-        <v>688</v>
-      </c>
-      <c r="H268" t="s">
-        <v>682</v>
-      </c>
-      <c r="I268" t="s">
-        <v>686</v>
-      </c>
-      <c r="J268" t="s">
-        <v>689</v>
       </c>
       <c r="K268">
         <v>0</v>
@@ -43820,31 +43822,31 @@
         <v>0</v>
       </c>
       <c r="C269" t="s">
+        <v>670</v>
+      </c>
+      <c r="D269" t="s">
+        <v>688</v>
+      </c>
+      <c r="E269" t="s">
         <v>672</v>
       </c>
-      <c r="D269" t="s">
+      <c r="F269" t="s">
+        <v>673</v>
+      </c>
+      <c r="G269" t="s">
+        <v>689</v>
+      </c>
+      <c r="H269" t="s">
+        <v>680</v>
+      </c>
+      <c r="I269" t="s">
+        <v>684</v>
+      </c>
+      <c r="J269" t="s">
+        <v>687</v>
+      </c>
+      <c r="K269" t="s">
         <v>690</v>
-      </c>
-      <c r="E269" t="s">
-        <v>674</v>
-      </c>
-      <c r="F269" t="s">
-        <v>675</v>
-      </c>
-      <c r="G269" t="s">
-        <v>691</v>
-      </c>
-      <c r="H269" t="s">
-        <v>682</v>
-      </c>
-      <c r="I269" t="s">
-        <v>686</v>
-      </c>
-      <c r="J269" t="s">
-        <v>689</v>
-      </c>
-      <c r="K269" t="s">
-        <v>692</v>
       </c>
       <c r="L269">
         <v>0</v>
@@ -43877,31 +43879,31 @@
         <v>0</v>
       </c>
       <c r="C270" t="s">
+        <v>670</v>
+      </c>
+      <c r="D270" t="s">
+        <v>691</v>
+      </c>
+      <c r="E270" t="s">
         <v>672</v>
       </c>
-      <c r="D270" t="s">
+      <c r="F270" t="s">
+        <v>673</v>
+      </c>
+      <c r="G270" t="s">
+        <v>692</v>
+      </c>
+      <c r="H270" t="s">
         <v>693</v>
       </c>
-      <c r="E270" t="s">
-        <v>674</v>
-      </c>
-      <c r="F270" t="s">
-        <v>675</v>
-      </c>
-      <c r="G270" t="s">
+      <c r="I270" t="s">
+        <v>687</v>
+      </c>
+      <c r="J270" t="s">
         <v>694</v>
       </c>
-      <c r="H270" t="s">
+      <c r="K270" t="s">
         <v>695</v>
-      </c>
-      <c r="I270" t="s">
-        <v>689</v>
-      </c>
-      <c r="J270" t="s">
-        <v>696</v>
-      </c>
-      <c r="K270" t="s">
-        <v>697</v>
       </c>
       <c r="L270">
         <v>0</v>
@@ -43934,31 +43936,31 @@
         <v>0</v>
       </c>
       <c r="C271" t="s">
+        <v>670</v>
+      </c>
+      <c r="D271" t="s">
+        <v>696</v>
+      </c>
+      <c r="E271" t="s">
         <v>672</v>
       </c>
-      <c r="D271" t="s">
-        <v>698</v>
-      </c>
-      <c r="E271" t="s">
-        <v>674</v>
-      </c>
       <c r="F271" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G271" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="H271" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="I271" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="J271" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="K271" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="L271">
         <v>0</v>
@@ -43991,31 +43993,31 @@
         <v>0</v>
       </c>
       <c r="C272" t="s">
+        <v>670</v>
+      </c>
+      <c r="D272" t="s">
+        <v>698</v>
+      </c>
+      <c r="E272" t="s">
         <v>672</v>
       </c>
-      <c r="D272" t="s">
+      <c r="F272" t="s">
+        <v>673</v>
+      </c>
+      <c r="G272" t="s">
+        <v>693</v>
+      </c>
+      <c r="H272" t="s">
+        <v>699</v>
+      </c>
+      <c r="I272" t="s">
+        <v>694</v>
+      </c>
+      <c r="J272" t="s">
         <v>700</v>
       </c>
-      <c r="E272" t="s">
-        <v>674</v>
-      </c>
-      <c r="F272" t="s">
-        <v>675</v>
-      </c>
-      <c r="G272" t="s">
-        <v>695</v>
-      </c>
-      <c r="H272" t="s">
+      <c r="K272" t="s">
         <v>701</v>
-      </c>
-      <c r="I272" t="s">
-        <v>696</v>
-      </c>
-      <c r="J272" t="s">
-        <v>702</v>
-      </c>
-      <c r="K272" t="s">
-        <v>703</v>
       </c>
       <c r="L272">
         <v>0</v>
@@ -44048,31 +44050,31 @@
         <v>0</v>
       </c>
       <c r="C273" t="s">
+        <v>670</v>
+      </c>
+      <c r="D273" t="s">
+        <v>702</v>
+      </c>
+      <c r="E273" t="s">
         <v>672</v>
       </c>
-      <c r="D273" t="s">
+      <c r="F273" t="s">
+        <v>673</v>
+      </c>
+      <c r="G273" t="s">
+        <v>699</v>
+      </c>
+      <c r="H273" t="s">
+        <v>703</v>
+      </c>
+      <c r="I273" t="s">
+        <v>700</v>
+      </c>
+      <c r="J273" t="s">
         <v>704</v>
       </c>
-      <c r="E273" t="s">
-        <v>674</v>
-      </c>
-      <c r="F273" t="s">
-        <v>675</v>
-      </c>
-      <c r="G273" t="s">
-        <v>701</v>
-      </c>
-      <c r="H273" t="s">
+      <c r="K273" t="s">
         <v>705</v>
-      </c>
-      <c r="I273" t="s">
-        <v>702</v>
-      </c>
-      <c r="J273" t="s">
-        <v>706</v>
-      </c>
-      <c r="K273" t="s">
-        <v>707</v>
       </c>
       <c r="L273">
         <v>0</v>
@@ -44105,31 +44107,31 @@
         <v>0</v>
       </c>
       <c r="C274" t="s">
+        <v>670</v>
+      </c>
+      <c r="D274" t="s">
+        <v>706</v>
+      </c>
+      <c r="E274" t="s">
         <v>672</v>
       </c>
-      <c r="D274" t="s">
+      <c r="F274" t="s">
+        <v>673</v>
+      </c>
+      <c r="G274" t="s">
+        <v>703</v>
+      </c>
+      <c r="H274" t="s">
+        <v>707</v>
+      </c>
+      <c r="I274" t="s">
+        <v>704</v>
+      </c>
+      <c r="J274" t="s">
         <v>708</v>
       </c>
-      <c r="E274" t="s">
-        <v>674</v>
-      </c>
-      <c r="F274" t="s">
-        <v>675</v>
-      </c>
-      <c r="G274" t="s">
-        <v>705</v>
-      </c>
-      <c r="H274" t="s">
+      <c r="K274" t="s">
         <v>709</v>
-      </c>
-      <c r="I274" t="s">
-        <v>706</v>
-      </c>
-      <c r="J274" t="s">
-        <v>710</v>
-      </c>
-      <c r="K274" t="s">
-        <v>711</v>
       </c>
       <c r="L274">
         <v>0</v>
@@ -44162,31 +44164,31 @@
         <v>0</v>
       </c>
       <c r="C275" t="s">
+        <v>670</v>
+      </c>
+      <c r="D275" t="s">
+        <v>710</v>
+      </c>
+      <c r="E275" t="s">
         <v>672</v>
       </c>
-      <c r="D275" t="s">
+      <c r="F275" t="s">
+        <v>673</v>
+      </c>
+      <c r="G275" t="s">
+        <v>707</v>
+      </c>
+      <c r="H275" t="s">
+        <v>711</v>
+      </c>
+      <c r="I275" t="s">
+        <v>708</v>
+      </c>
+      <c r="J275" t="s">
         <v>712</v>
       </c>
-      <c r="E275" t="s">
-        <v>674</v>
-      </c>
-      <c r="F275" t="s">
-        <v>675</v>
-      </c>
-      <c r="G275" t="s">
-        <v>709</v>
-      </c>
-      <c r="H275" t="s">
+      <c r="K275" t="s">
         <v>713</v>
-      </c>
-      <c r="I275" t="s">
-        <v>710</v>
-      </c>
-      <c r="J275" t="s">
-        <v>714</v>
-      </c>
-      <c r="K275" t="s">
-        <v>715</v>
       </c>
       <c r="L275">
         <v>0</v>
@@ -44219,31 +44221,31 @@
         <v>0</v>
       </c>
       <c r="C276" t="s">
+        <v>670</v>
+      </c>
+      <c r="D276" t="s">
+        <v>714</v>
+      </c>
+      <c r="E276" t="s">
         <v>672</v>
       </c>
-      <c r="D276" t="s">
+      <c r="F276" t="s">
+        <v>673</v>
+      </c>
+      <c r="G276" t="s">
+        <v>711</v>
+      </c>
+      <c r="H276" t="s">
+        <v>715</v>
+      </c>
+      <c r="I276" t="s">
+        <v>712</v>
+      </c>
+      <c r="J276" t="s">
         <v>716</v>
       </c>
-      <c r="E276" t="s">
-        <v>674</v>
-      </c>
-      <c r="F276" t="s">
-        <v>675</v>
-      </c>
-      <c r="G276" t="s">
-        <v>713</v>
-      </c>
-      <c r="H276" t="s">
+      <c r="K276" t="s">
         <v>717</v>
-      </c>
-      <c r="I276" t="s">
-        <v>714</v>
-      </c>
-      <c r="J276" t="s">
-        <v>718</v>
-      </c>
-      <c r="K276" t="s">
-        <v>719</v>
       </c>
       <c r="L276">
         <v>0</v>
@@ -44276,31 +44278,31 @@
         <v>0</v>
       </c>
       <c r="C277" t="s">
+        <v>670</v>
+      </c>
+      <c r="D277" t="s">
+        <v>718</v>
+      </c>
+      <c r="E277" t="s">
         <v>672</v>
       </c>
-      <c r="D277" t="s">
+      <c r="F277" t="s">
+        <v>673</v>
+      </c>
+      <c r="G277" t="s">
+        <v>715</v>
+      </c>
+      <c r="H277" t="s">
+        <v>719</v>
+      </c>
+      <c r="I277" t="s">
+        <v>716</v>
+      </c>
+      <c r="J277" t="s">
         <v>720</v>
       </c>
-      <c r="E277" t="s">
-        <v>674</v>
-      </c>
-      <c r="F277" t="s">
-        <v>675</v>
-      </c>
-      <c r="G277" t="s">
-        <v>717</v>
-      </c>
-      <c r="H277" t="s">
+      <c r="K277" t="s">
         <v>721</v>
-      </c>
-      <c r="I277" t="s">
-        <v>718</v>
-      </c>
-      <c r="J277" t="s">
-        <v>722</v>
-      </c>
-      <c r="K277" t="s">
-        <v>723</v>
       </c>
       <c r="L277">
         <v>0</v>
@@ -44333,31 +44335,31 @@
         <v>0</v>
       </c>
       <c r="C278" t="s">
+        <v>670</v>
+      </c>
+      <c r="D278" t="s">
+        <v>722</v>
+      </c>
+      <c r="E278" t="s">
         <v>672</v>
       </c>
-      <c r="D278" t="s">
+      <c r="F278" t="s">
+        <v>673</v>
+      </c>
+      <c r="G278" t="s">
+        <v>719</v>
+      </c>
+      <c r="H278" t="s">
+        <v>723</v>
+      </c>
+      <c r="I278" t="s">
+        <v>720</v>
+      </c>
+      <c r="J278" t="s">
         <v>724</v>
       </c>
-      <c r="E278" t="s">
-        <v>674</v>
-      </c>
-      <c r="F278" t="s">
-        <v>675</v>
-      </c>
-      <c r="G278" t="s">
-        <v>721</v>
-      </c>
-      <c r="H278" t="s">
+      <c r="K278" t="s">
         <v>725</v>
-      </c>
-      <c r="I278" t="s">
-        <v>722</v>
-      </c>
-      <c r="J278" t="s">
-        <v>726</v>
-      </c>
-      <c r="K278" t="s">
-        <v>727</v>
       </c>
       <c r="L278">
         <v>0</v>
@@ -44390,31 +44392,31 @@
         <v>0</v>
       </c>
       <c r="C279" t="s">
+        <v>670</v>
+      </c>
+      <c r="D279" t="s">
+        <v>726</v>
+      </c>
+      <c r="E279" t="s">
         <v>672</v>
       </c>
-      <c r="D279" t="s">
+      <c r="F279" t="s">
+        <v>673</v>
+      </c>
+      <c r="G279" t="s">
+        <v>723</v>
+      </c>
+      <c r="H279" t="s">
+        <v>727</v>
+      </c>
+      <c r="I279" t="s">
+        <v>724</v>
+      </c>
+      <c r="J279" t="s">
         <v>728</v>
       </c>
-      <c r="E279" t="s">
-        <v>674</v>
-      </c>
-      <c r="F279" t="s">
-        <v>675</v>
-      </c>
-      <c r="G279" t="s">
-        <v>725</v>
-      </c>
-      <c r="H279" t="s">
+      <c r="K279" t="s">
         <v>729</v>
-      </c>
-      <c r="I279" t="s">
-        <v>726</v>
-      </c>
-      <c r="J279" t="s">
-        <v>730</v>
-      </c>
-      <c r="K279" t="s">
-        <v>731</v>
       </c>
       <c r="L279">
         <v>0</v>
@@ -44447,31 +44449,31 @@
         <v>0</v>
       </c>
       <c r="C280" t="s">
+        <v>670</v>
+      </c>
+      <c r="D280" t="s">
+        <v>730</v>
+      </c>
+      <c r="E280" t="s">
         <v>672</v>
       </c>
-      <c r="D280" t="s">
+      <c r="F280" t="s">
+        <v>673</v>
+      </c>
+      <c r="G280" t="s">
+        <v>727</v>
+      </c>
+      <c r="H280" t="s">
+        <v>731</v>
+      </c>
+      <c r="I280" t="s">
+        <v>728</v>
+      </c>
+      <c r="J280" t="s">
         <v>732</v>
       </c>
-      <c r="E280" t="s">
-        <v>674</v>
-      </c>
-      <c r="F280" t="s">
-        <v>675</v>
-      </c>
-      <c r="G280" t="s">
-        <v>729</v>
-      </c>
-      <c r="H280" t="s">
+      <c r="K280" t="s">
         <v>733</v>
-      </c>
-      <c r="I280" t="s">
-        <v>730</v>
-      </c>
-      <c r="J280" t="s">
-        <v>734</v>
-      </c>
-      <c r="K280" t="s">
-        <v>735</v>
       </c>
       <c r="L280">
         <v>0</v>
@@ -44504,34 +44506,34 @@
         <v>0</v>
       </c>
       <c r="C281" t="s">
+        <v>670</v>
+      </c>
+      <c r="D281" t="s">
+        <v>734</v>
+      </c>
+      <c r="E281" t="s">
         <v>672</v>
       </c>
-      <c r="D281" t="s">
+      <c r="F281" t="s">
+        <v>673</v>
+      </c>
+      <c r="G281" t="s">
+        <v>717</v>
+      </c>
+      <c r="H281" t="s">
+        <v>735</v>
+      </c>
+      <c r="I281" t="s">
         <v>736</v>
       </c>
-      <c r="E281" t="s">
-        <v>674</v>
-      </c>
-      <c r="F281" t="s">
-        <v>675</v>
-      </c>
-      <c r="G281" t="s">
-        <v>719</v>
-      </c>
-      <c r="H281" t="s">
+      <c r="J281" t="s">
+        <v>732</v>
+      </c>
+      <c r="K281" t="s">
         <v>737</v>
       </c>
-      <c r="I281" t="s">
+      <c r="L281" t="s">
         <v>738</v>
-      </c>
-      <c r="J281" t="s">
-        <v>734</v>
-      </c>
-      <c r="K281" t="s">
-        <v>739</v>
-      </c>
-      <c r="L281" t="s">
-        <v>740</v>
       </c>
       <c r="M281">
         <v>0</v>
@@ -44561,34 +44563,34 @@
         <v>0</v>
       </c>
       <c r="C282" t="s">
+        <v>670</v>
+      </c>
+      <c r="D282" t="s">
+        <v>739</v>
+      </c>
+      <c r="E282" t="s">
         <v>672</v>
       </c>
-      <c r="D282" t="s">
-        <v>741</v>
-      </c>
-      <c r="E282" t="s">
-        <v>674</v>
-      </c>
       <c r="F282" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G282" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="H282" t="s">
+        <v>735</v>
+      </c>
+      <c r="I282" t="s">
+        <v>736</v>
+      </c>
+      <c r="J282" t="s">
+        <v>732</v>
+      </c>
+      <c r="K282" t="s">
         <v>737</v>
       </c>
-      <c r="I282" t="s">
+      <c r="L282" t="s">
         <v>738</v>
-      </c>
-      <c r="J282" t="s">
-        <v>734</v>
-      </c>
-      <c r="K282" t="s">
-        <v>739</v>
-      </c>
-      <c r="L282" t="s">
-        <v>740</v>
       </c>
       <c r="M282">
         <v>0</v>
@@ -44618,34 +44620,34 @@
         <v>0</v>
       </c>
       <c r="C283" t="s">
+        <v>670</v>
+      </c>
+      <c r="D283" t="s">
+        <v>740</v>
+      </c>
+      <c r="E283" t="s">
         <v>672</v>
       </c>
-      <c r="D283" t="s">
-        <v>742</v>
-      </c>
-      <c r="E283" t="s">
-        <v>674</v>
-      </c>
       <c r="F283" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G283" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="H283" t="s">
+        <v>735</v>
+      </c>
+      <c r="I283" t="s">
+        <v>736</v>
+      </c>
+      <c r="J283" t="s">
+        <v>732</v>
+      </c>
+      <c r="K283" t="s">
         <v>737</v>
       </c>
-      <c r="I283" t="s">
+      <c r="L283" t="s">
         <v>738</v>
-      </c>
-      <c r="J283" t="s">
-        <v>734</v>
-      </c>
-      <c r="K283" t="s">
-        <v>739</v>
-      </c>
-      <c r="L283" t="s">
-        <v>740</v>
       </c>
       <c r="M283">
         <v>0</v>
@@ -44675,16 +44677,16 @@
         <v>0</v>
       </c>
       <c r="C284" t="s">
+        <v>806</v>
+      </c>
+      <c r="D284" t="s">
+        <v>807</v>
+      </c>
+      <c r="E284" t="s">
         <v>808</v>
       </c>
-      <c r="D284" t="s">
+      <c r="F284" t="s">
         <v>809</v>
-      </c>
-      <c r="E284" t="s">
-        <v>810</v>
-      </c>
-      <c r="F284" t="s">
-        <v>811</v>
       </c>
       <c r="G284">
         <v>0</v>
@@ -44732,16 +44734,16 @@
         <v>0</v>
       </c>
       <c r="C285" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D285" t="s">
+        <v>810</v>
+      </c>
+      <c r="E285" t="s">
+        <v>811</v>
+      </c>
+      <c r="F285" t="s">
         <v>812</v>
-      </c>
-      <c r="E285" t="s">
-        <v>813</v>
-      </c>
-      <c r="F285" t="s">
-        <v>814</v>
       </c>
       <c r="G285">
         <v>0.1</v>
@@ -44789,16 +44791,16 @@
         <v>0</v>
       </c>
       <c r="C286" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D286" t="s">
+        <v>813</v>
+      </c>
+      <c r="E286" t="s">
+        <v>814</v>
+      </c>
+      <c r="F286" t="s">
         <v>815</v>
-      </c>
-      <c r="E286" t="s">
-        <v>816</v>
-      </c>
-      <c r="F286" t="s">
-        <v>817</v>
       </c>
       <c r="G286">
         <v>0</v>
@@ -44846,16 +44848,16 @@
         <v>0</v>
       </c>
       <c r="C287" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D287" t="s">
+        <v>816</v>
+      </c>
+      <c r="E287" t="s">
+        <v>817</v>
+      </c>
+      <c r="F287" t="s">
         <v>818</v>
-      </c>
-      <c r="E287" t="s">
-        <v>819</v>
-      </c>
-      <c r="F287" t="s">
-        <v>820</v>
       </c>
       <c r="G287">
         <v>0</v>
@@ -44903,16 +44905,16 @@
         <v>0</v>
       </c>
       <c r="C288" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D288" t="s">
+        <v>819</v>
+      </c>
+      <c r="E288" t="s">
+        <v>820</v>
+      </c>
+      <c r="F288" t="s">
         <v>821</v>
-      </c>
-      <c r="E288" t="s">
-        <v>822</v>
-      </c>
-      <c r="F288" t="s">
-        <v>823</v>
       </c>
       <c r="G288">
         <v>0.2</v>
@@ -44960,16 +44962,16 @@
         <v>0</v>
       </c>
       <c r="C289" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="F289" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="G289">
         <v>0.5</v>
@@ -45017,16 +45019,16 @@
         <v>0</v>
       </c>
       <c r="C290" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D290" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E290" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="F290" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="G290">
         <v>1000</v>
@@ -45074,16 +45076,16 @@
         <v>0</v>
       </c>
       <c r="C291" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D291" t="s">
+        <v>825</v>
+      </c>
+      <c r="E291" t="s">
+        <v>826</v>
+      </c>
+      <c r="F291" t="s">
         <v>827</v>
-      </c>
-      <c r="E291" t="s">
-        <v>828</v>
-      </c>
-      <c r="F291" t="s">
-        <v>829</v>
       </c>
       <c r="G291">
         <v>0</v>
@@ -45131,16 +45133,16 @@
         <v>0</v>
       </c>
       <c r="C292" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D292" t="s">
+        <v>828</v>
+      </c>
+      <c r="E292" t="s">
+        <v>829</v>
+      </c>
+      <c r="F292" t="s">
         <v>830</v>
-      </c>
-      <c r="E292" t="s">
-        <v>831</v>
-      </c>
-      <c r="F292" t="s">
-        <v>832</v>
       </c>
       <c r="G292">
         <v>30</v>
@@ -45188,16 +45190,16 @@
         <v>0</v>
       </c>
       <c r="C293" t="s">
+        <v>831</v>
+      </c>
+      <c r="D293" t="s">
+        <v>832</v>
+      </c>
+      <c r="E293" t="s">
         <v>833</v>
       </c>
-      <c r="D293" t="s">
+      <c r="F293" t="s">
         <v>834</v>
-      </c>
-      <c r="E293" t="s">
-        <v>835</v>
-      </c>
-      <c r="F293" t="s">
-        <v>836</v>
       </c>
       <c r="G293">
         <v>0.75</v>
@@ -45245,13 +45247,13 @@
         <v>0</v>
       </c>
       <c r="C294" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D294" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="E294" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="F294">
         <v>0</v>
@@ -45302,16 +45304,16 @@
         <v>0</v>
       </c>
       <c r="C295" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D295" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="E295" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="F295" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="G295">
         <v>45</v>
@@ -45359,16 +45361,16 @@
         <v>0</v>
       </c>
       <c r="C296" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D296" t="s">
+        <v>839</v>
+      </c>
+      <c r="E296" t="s">
+        <v>840</v>
+      </c>
+      <c r="F296" t="s">
         <v>841</v>
-      </c>
-      <c r="E296" t="s">
-        <v>842</v>
-      </c>
-      <c r="F296" t="s">
-        <v>843</v>
       </c>
       <c r="G296">
         <v>0</v>
@@ -45416,16 +45418,16 @@
         <v>0</v>
       </c>
       <c r="C297" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D297" t="s">
+        <v>842</v>
+      </c>
+      <c r="E297" t="s">
+        <v>843</v>
+      </c>
+      <c r="F297" t="s">
         <v>844</v>
-      </c>
-      <c r="E297" t="s">
-        <v>845</v>
-      </c>
-      <c r="F297" t="s">
-        <v>846</v>
       </c>
       <c r="G297">
         <v>0.1</v>
@@ -45473,16 +45475,16 @@
         <v>0</v>
       </c>
       <c r="C298" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D298" t="s">
+        <v>932</v>
+      </c>
+      <c r="E298" t="s">
+        <v>933</v>
+      </c>
+      <c r="F298" t="s">
         <v>934</v>
-      </c>
-      <c r="E298" t="s">
-        <v>935</v>
-      </c>
-      <c r="F298" t="s">
-        <v>936</v>
       </c>
       <c r="G298">
         <v>50000</v>
@@ -45530,16 +45532,16 @@
         <v>0</v>
       </c>
       <c r="C299" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D299" t="s">
+        <v>935</v>
+      </c>
+      <c r="E299" t="s">
+        <v>936</v>
+      </c>
+      <c r="F299" t="s">
         <v>937</v>
-      </c>
-      <c r="E299" t="s">
-        <v>938</v>
-      </c>
-      <c r="F299" t="s">
-        <v>939</v>
       </c>
       <c r="G299">
         <v>10</v>
@@ -45587,16 +45589,16 @@
         <v>0</v>
       </c>
       <c r="C300" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D300" t="s">
+        <v>938</v>
+      </c>
+      <c r="E300" t="s">
+        <v>939</v>
+      </c>
+      <c r="F300" t="s">
         <v>940</v>
-      </c>
-      <c r="E300" t="s">
-        <v>941</v>
-      </c>
-      <c r="F300" t="s">
-        <v>942</v>
       </c>
       <c r="G300">
         <v>75</v>
@@ -45644,16 +45646,16 @@
         <v>0</v>
       </c>
       <c r="C301" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D301" t="s">
+        <v>941</v>
+      </c>
+      <c r="E301" t="s">
+        <v>942</v>
+      </c>
+      <c r="F301" t="s">
         <v>943</v>
-      </c>
-      <c r="E301" t="s">
-        <v>944</v>
-      </c>
-      <c r="F301" t="s">
-        <v>945</v>
       </c>
       <c r="G301">
         <v>25</v>
@@ -45701,16 +45703,16 @@
         <v>0</v>
       </c>
       <c r="C302" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D302" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="E302" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="F302" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="G302">
         <v>5</v>
@@ -45758,16 +45760,16 @@
         <v>0</v>
       </c>
       <c r="C303" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D303" t="s">
+        <v>946</v>
+      </c>
+      <c r="E303" t="s">
+        <v>947</v>
+      </c>
+      <c r="F303" t="s">
         <v>948</v>
-      </c>
-      <c r="E303" t="s">
-        <v>949</v>
-      </c>
-      <c r="F303" t="s">
-        <v>950</v>
       </c>
       <c r="G303">
         <v>0.6</v>
@@ -45815,16 +45817,16 @@
         <v>0</v>
       </c>
       <c r="C304" t="s">
+        <v>869</v>
+      </c>
+      <c r="D304" t="s">
+        <v>870</v>
+      </c>
+      <c r="E304" t="s">
         <v>871</v>
       </c>
-      <c r="D304" t="s">
+      <c r="F304" t="s">
         <v>872</v>
-      </c>
-      <c r="E304" t="s">
-        <v>873</v>
-      </c>
-      <c r="F304" t="s">
-        <v>874</v>
       </c>
       <c r="G304">
         <v>25</v>
@@ -45833,7 +45835,7 @@
         <v>25</v>
       </c>
       <c r="I304" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="J304">
         <v>0</v>
@@ -45872,16 +45874,16 @@
         <v>0</v>
       </c>
       <c r="C305" t="s">
+        <v>869</v>
+      </c>
+      <c r="D305" t="s">
+        <v>874</v>
+      </c>
+      <c r="E305" t="s">
         <v>871</v>
       </c>
-      <c r="D305" t="s">
-        <v>876</v>
-      </c>
-      <c r="E305" t="s">
-        <v>873</v>
-      </c>
       <c r="F305" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G305">
         <v>20</v>
@@ -45890,7 +45892,7 @@
         <v>20</v>
       </c>
       <c r="I305" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="J305">
         <v>0</v>
@@ -45929,16 +45931,16 @@
         <v>0</v>
       </c>
       <c r="C306" t="s">
+        <v>869</v>
+      </c>
+      <c r="D306" t="s">
+        <v>876</v>
+      </c>
+      <c r="E306" t="s">
         <v>871</v>
       </c>
-      <c r="D306" t="s">
-        <v>878</v>
-      </c>
-      <c r="E306" t="s">
-        <v>873</v>
-      </c>
       <c r="F306" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="G306">
         <v>3</v>
@@ -45947,7 +45949,7 @@
         <v>1.5</v>
       </c>
       <c r="I306" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="J306">
         <v>0</v>
@@ -45986,16 +45988,16 @@
         <v>0</v>
       </c>
       <c r="C307" t="s">
+        <v>869</v>
+      </c>
+      <c r="D307" t="s">
+        <v>878</v>
+      </c>
+      <c r="E307" t="s">
         <v>871</v>
       </c>
-      <c r="D307" t="s">
-        <v>880</v>
-      </c>
-      <c r="E307" t="s">
-        <v>873</v>
-      </c>
       <c r="F307" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G307">
         <v>20</v>
@@ -46004,7 +46006,7 @@
         <v>20</v>
       </c>
       <c r="I307" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="J307">
         <v>0</v>
@@ -46043,16 +46045,16 @@
         <v>0</v>
       </c>
       <c r="C308" t="s">
+        <v>869</v>
+      </c>
+      <c r="D308" t="s">
+        <v>880</v>
+      </c>
+      <c r="E308" t="s">
         <v>871</v>
       </c>
-      <c r="D308" t="s">
-        <v>882</v>
-      </c>
-      <c r="E308" t="s">
-        <v>873</v>
-      </c>
       <c r="F308" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="G308">
         <v>3</v>
@@ -46061,7 +46063,7 @@
         <v>1.5</v>
       </c>
       <c r="I308" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="J308">
         <v>0</v>
@@ -46100,16 +46102,16 @@
         <v>0</v>
       </c>
       <c r="C309" t="s">
+        <v>869</v>
+      </c>
+      <c r="D309" t="s">
+        <v>882</v>
+      </c>
+      <c r="E309" t="s">
         <v>871</v>
       </c>
-      <c r="D309" t="s">
-        <v>884</v>
-      </c>
-      <c r="E309" t="s">
-        <v>873</v>
-      </c>
       <c r="F309" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G309">
         <v>3</v>
@@ -46118,7 +46120,7 @@
         <v>1.5</v>
       </c>
       <c r="I309" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="J309">
         <v>0</v>
@@ -46157,16 +46159,16 @@
         <v>0</v>
       </c>
       <c r="C310" t="s">
+        <v>869</v>
+      </c>
+      <c r="D310" t="s">
+        <v>884</v>
+      </c>
+      <c r="E310" t="s">
         <v>871</v>
       </c>
-      <c r="D310" t="s">
-        <v>886</v>
-      </c>
-      <c r="E310" t="s">
-        <v>873</v>
-      </c>
       <c r="F310" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="G310">
         <v>3</v>
@@ -46175,7 +46177,7 @@
         <v>1.5</v>
       </c>
       <c r="I310" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="J310">
         <v>0</v>
@@ -46214,16 +46216,16 @@
         <v>0</v>
       </c>
       <c r="C311" t="s">
+        <v>869</v>
+      </c>
+      <c r="D311" t="s">
+        <v>886</v>
+      </c>
+      <c r="E311" t="s">
         <v>871</v>
       </c>
-      <c r="D311" t="s">
-        <v>888</v>
-      </c>
-      <c r="E311" t="s">
-        <v>873</v>
-      </c>
       <c r="F311" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="G311">
         <v>25</v>
@@ -46232,7 +46234,7 @@
         <v>25</v>
       </c>
       <c r="I311" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="J311">
         <v>0</v>
@@ -46271,16 +46273,16 @@
         <v>0</v>
       </c>
       <c r="C312" t="s">
+        <v>869</v>
+      </c>
+      <c r="D312" t="s">
+        <v>888</v>
+      </c>
+      <c r="E312" t="s">
         <v>871</v>
       </c>
-      <c r="D312" t="s">
-        <v>890</v>
-      </c>
-      <c r="E312" t="s">
-        <v>873</v>
-      </c>
       <c r="F312" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G312">
         <v>5</v>
@@ -46289,7 +46291,7 @@
         <v>2.5</v>
       </c>
       <c r="I312" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="J312">
         <v>0</v>
@@ -46328,19 +46330,19 @@
         <v>0</v>
       </c>
       <c r="C313" t="s">
+        <v>890</v>
+      </c>
+      <c r="D313" t="s">
+        <v>891</v>
+      </c>
+      <c r="E313" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="F313" t="s">
         <v>892</v>
       </c>
-      <c r="D313" t="s">
-        <v>893</v>
-      </c>
-      <c r="E313" s="3" t="s">
-        <v>999</v>
-      </c>
-      <c r="F313" t="s">
-        <v>894</v>
-      </c>
       <c r="G313" s="3" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="H313">
         <v>3</v>
@@ -46385,16 +46387,16 @@
         <v>0</v>
       </c>
       <c r="C314" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D314" t="s">
+        <v>893</v>
+      </c>
+      <c r="E314" t="s">
+        <v>894</v>
+      </c>
+      <c r="F314" t="s">
         <v>895</v>
-      </c>
-      <c r="E314" t="s">
-        <v>896</v>
-      </c>
-      <c r="F314" t="s">
-        <v>897</v>
       </c>
       <c r="G314">
         <v>5</v>
@@ -46442,16 +46444,16 @@
         <v>0</v>
       </c>
       <c r="C315" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D315" t="s">
+        <v>896</v>
+      </c>
+      <c r="E315" t="s">
+        <v>897</v>
+      </c>
+      <c r="F315" t="s">
         <v>898</v>
-      </c>
-      <c r="E315" t="s">
-        <v>899</v>
-      </c>
-      <c r="F315" t="s">
-        <v>900</v>
       </c>
       <c r="G315">
         <v>10</v>
@@ -46499,16 +46501,16 @@
         <v>0</v>
       </c>
       <c r="C316" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D316" t="s">
+        <v>899</v>
+      </c>
+      <c r="E316" t="s">
+        <v>900</v>
+      </c>
+      <c r="F316" t="s">
         <v>901</v>
-      </c>
-      <c r="E316" t="s">
-        <v>902</v>
-      </c>
-      <c r="F316" t="s">
-        <v>903</v>
       </c>
       <c r="G316">
         <v>10</v>
@@ -46556,16 +46558,16 @@
         <v>0</v>
       </c>
       <c r="C317" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D317" t="s">
+        <v>902</v>
+      </c>
+      <c r="E317" t="s">
+        <v>903</v>
+      </c>
+      <c r="F317" t="s">
         <v>904</v>
-      </c>
-      <c r="E317" t="s">
-        <v>905</v>
-      </c>
-      <c r="F317" t="s">
-        <v>906</v>
       </c>
       <c r="G317">
         <v>2</v>
@@ -46613,16 +46615,16 @@
         <v>0</v>
       </c>
       <c r="C318" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D318" t="s">
+        <v>905</v>
+      </c>
+      <c r="E318" t="s">
+        <v>906</v>
+      </c>
+      <c r="F318" t="s">
         <v>907</v>
-      </c>
-      <c r="E318" t="s">
-        <v>908</v>
-      </c>
-      <c r="F318" t="s">
-        <v>909</v>
       </c>
       <c r="G318">
         <v>5</v>
@@ -46670,16 +46672,16 @@
         <v>0</v>
       </c>
       <c r="C319" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D319" t="s">
+        <v>908</v>
+      </c>
+      <c r="E319" t="s">
+        <v>909</v>
+      </c>
+      <c r="F319" t="s">
         <v>910</v>
-      </c>
-      <c r="E319" t="s">
-        <v>911</v>
-      </c>
-      <c r="F319" t="s">
-        <v>912</v>
       </c>
       <c r="G319">
         <v>10</v>
@@ -46727,16 +46729,16 @@
         <v>0</v>
       </c>
       <c r="C320" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D320" t="s">
+        <v>911</v>
+      </c>
+      <c r="E320" t="s">
+        <v>912</v>
+      </c>
+      <c r="F320" t="s">
         <v>913</v>
-      </c>
-      <c r="E320" t="s">
-        <v>914</v>
-      </c>
-      <c r="F320" t="s">
-        <v>915</v>
       </c>
       <c r="G320">
         <v>20000</v>
@@ -46784,16 +46786,16 @@
         <v>0</v>
       </c>
       <c r="C321" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="D321" t="s">
+        <v>998</v>
+      </c>
+      <c r="E321" t="s">
+        <v>999</v>
+      </c>
+      <c r="F321" s="5" t="s">
         <v>1000</v>
-      </c>
-      <c r="E321" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F321" s="5" t="s">
-        <v>1002</v>
       </c>
       <c r="G321">
         <v>0.35</v>
@@ -46841,16 +46843,16 @@
         <v>0</v>
       </c>
       <c r="C322" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D322" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="E322" t="s">
         <v>39</v>
       </c>
       <c r="F322" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="G322">
         <v>1</v>
@@ -46898,16 +46900,16 @@
         <v>0</v>
       </c>
       <c r="C323" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D323" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="E323" t="s">
         <v>39</v>
       </c>
       <c r="F323" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="G323">
         <v>1.35</v>
@@ -46955,16 +46957,16 @@
         <v>0</v>
       </c>
       <c r="C324" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D324" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="E324" t="s">
         <v>39</v>
       </c>
       <c r="F324" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="G324">
         <v>1.75</v>
@@ -47012,16 +47014,16 @@
         <v>0</v>
       </c>
       <c r="C325" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D325" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="E325" t="s">
         <v>39</v>
       </c>
       <c r="F325" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="G325">
         <v>2.2999999999999998</v>
@@ -47069,16 +47071,16 @@
         <v>0</v>
       </c>
       <c r="C326" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D326" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="E326" t="s">
         <v>39</v>
       </c>
       <c r="F326" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="G326">
         <v>3</v>
@@ -47126,16 +47128,16 @@
         <v>0</v>
       </c>
       <c r="C327" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D327" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="E327" t="s">
         <v>39</v>
       </c>
       <c r="F327" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="G327">
         <v>4</v>
@@ -47183,16 +47185,16 @@
         <v>0</v>
       </c>
       <c r="C328" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D328" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="E328" t="s">
         <v>39</v>
       </c>
       <c r="F328" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="G328">
         <v>5.2</v>
@@ -47240,16 +47242,16 @@
         <v>0</v>
       </c>
       <c r="C329" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D329" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="E329" t="s">
         <v>39</v>
       </c>
       <c r="F329" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="G329">
         <v>6.8</v>
@@ -47297,16 +47299,16 @@
         <v>0</v>
       </c>
       <c r="C330" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D330" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="E330" t="s">
         <v>39</v>
       </c>
       <c r="F330" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="G330">
         <v>10.199999999999999</v>
@@ -47354,16 +47356,16 @@
         <v>0</v>
       </c>
       <c r="C331" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D331" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="E331" t="s">
         <v>39</v>
       </c>
       <c r="F331" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="G331">
         <v>15.3</v>
@@ -47411,16 +47413,16 @@
         <v>0</v>
       </c>
       <c r="C332" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="D332" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="E332" t="s">
         <v>39</v>
       </c>
       <c r="F332" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="G332">
         <v>22.95</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1608E79-4DB4-4E06-96A0-4ABE11A9FF04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8AECA76-E756-4F74-B6C9-5D2B04DB3D59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1835" uniqueCount="1079">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1840" uniqueCount="1084">
   <si>
     <t>編號</t>
   </si>
@@ -4028,6 +4028,25 @@
   <si>
     <t>a=吸魔上限（定值）；0＝無上限。吸魔是定值：每次對敵人造成傷害固定回復的法力（舊版百分比以 1%＝1 轉換），單獨計算，與每秒法力恢復、造成的傷害皆無關。</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6-裝備</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>等級前不出現的屬性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>裝備等級（或角色等級）≤ 等級 時，陣列內的詞條不出現</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屬性解鎖門檻（2026-10-05）。成對填寫：a＝等級、b＝該等級（含）以前不出現的詞條陣列；c／d＝第二組、e／f＝第三組…（最多六組，不用的組留空或填 0）。判斷基準：裝備掉落的詞條隨機、洗煉、詞條池提示看「裝備等級」；角色屬性面板看「角色等級」，≤ 等級就不顯示該列。已經在裝備上的詞條不受影響、照常生效。陣列寫法 {詞條鍵,詞條鍵…}，鍵見 Equipment_Affix 表「詞條池」的 id 欄：elemDmgFire／Ice／Lightning／Poison／Light／Dark／Earth／Wind＝火冰雷毒聖暗地風屬性傷害提升；resFire／Ice／Lightning／Poison／Light／Dark／Earth／Wind＝各屬性抗性；resAll＝全屬性抗性。同一個鍵出現在多組時取最高的等級；打錯鍵套用參數會中止並指出是哪一個。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{elemDmgFire,elemDmgIce,elemDmgLightning,elemDmgPoison,elemDmgLight,elemDmgDark,elemDmgEarth,elemDmgWind,resFire,resIce,resLightning,resPoison,resLight,resDark,resEarth,resWind,resAll}</t>
   </si>
 </sst>
 </file>
@@ -4481,7 +4500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R316"/>
+  <dimension ref="A1:R317"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="22.7109375" customWidth="1"/>
@@ -27775,6 +27794,80 @@
       </c>
       <c r="R316">
         <f>計算表!R332</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A317">
+        <f>計算表!A333</f>
+        <v>332</v>
+      </c>
+      <c r="B317">
+        <f>計算表!B333</f>
+        <v>0</v>
+      </c>
+      <c r="C317" t="str">
+        <f>計算表!C333</f>
+        <v>6-裝備</v>
+      </c>
+      <c r="D317" t="str">
+        <f>計算表!D333</f>
+        <v>等級前不出現的屬性</v>
+      </c>
+      <c r="E317" t="str">
+        <f>計算表!E333</f>
+        <v>裝備等級（或角色等級）≤ 等級 時，陣列內的詞條不出現</v>
+      </c>
+      <c r="F317" t="str">
+        <f>計算表!F333</f>
+        <v>屬性解鎖門檻（2026-10-05）。成對填寫：a＝等級、b＝該等級（含）以前不出現的詞條陣列；c／d＝第二組、e／f＝第三組…（最多六組，不用的組留空或填 0）。判斷基準：裝備掉落的詞條隨機、洗煉、詞條池提示看「裝備等級」；角色屬性面板看「角色等級」，≤ 等級就不顯示該列。已經在裝備上的詞條不受影響、照常生效。陣列寫法 {詞條鍵,詞條鍵…}，鍵見 Equipment_Affix 表「詞條池」的 id 欄：elemDmgFire／Ice／Lightning／Poison／Light／Dark／Earth／Wind＝火冰雷毒聖暗地風屬性傷害提升；resFire／Ice／Lightning／Poison／Light／Dark／Earth／Wind＝各屬性抗性；resAll＝全屬性抗性。同一個鍵出現在多組時取最高的等級；打錯鍵套用參數會中止並指出是哪一個。</v>
+      </c>
+      <c r="G317">
+        <f>計算表!G333</f>
+        <v>200</v>
+      </c>
+      <c r="H317" t="str">
+        <f>計算表!H333</f>
+        <v>{elemDmgFire,elemDmgIce,elemDmgLightning,elemDmgPoison,elemDmgLight,elemDmgDark,elemDmgEarth,elemDmgWind,resFire,resIce,resLightning,resPoison,resLight,resDark,resEarth,resWind,resAll}</v>
+      </c>
+      <c r="I317">
+        <f>計算表!I333</f>
+        <v>0</v>
+      </c>
+      <c r="J317">
+        <f>計算表!J333</f>
+        <v>0</v>
+      </c>
+      <c r="K317">
+        <f>計算表!K333</f>
+        <v>0</v>
+      </c>
+      <c r="L317">
+        <f>計算表!L333</f>
+        <v>0</v>
+      </c>
+      <c r="M317">
+        <f>計算表!M333</f>
+        <v>0</v>
+      </c>
+      <c r="N317">
+        <f>計算表!N333</f>
+        <v>0</v>
+      </c>
+      <c r="O317">
+        <f>計算表!O333</f>
+        <v>0</v>
+      </c>
+      <c r="P317">
+        <f>計算表!P333</f>
+        <v>0</v>
+      </c>
+      <c r="Q317">
+        <f>計算表!Q333</f>
+        <v>0</v>
+      </c>
+      <c r="R317">
+        <f>計算表!R333</f>
         <v>0</v>
       </c>
     </row>
@@ -27786,7 +27879,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AB332"/>
+  <dimension ref="A1:AB333"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="23.42578125" customWidth="1"/>
@@ -47005,7 +47098,7 @@
     </row>
     <row r="325" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A325">
-        <f t="shared" ref="A325:A332" si="9">A324+1</f>
+        <f t="shared" ref="A325:A333" si="9">A324+1</f>
         <v>324</v>
       </c>
       <c r="B325">
@@ -47456,6 +47549,63 @@
         <v>0</v>
       </c>
       <c r="R332">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A333">
+        <f t="shared" si="9"/>
+        <v>332</v>
+      </c>
+      <c r="B333">
+        <v>0</v>
+      </c>
+      <c r="C333" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D333" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E333" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F333" t="s">
+        <v>1082</v>
+      </c>
+      <c r="G333">
+        <v>200</v>
+      </c>
+      <c r="H333" t="s">
+        <v>1083</v>
+      </c>
+      <c r="I333">
+        <v>0</v>
+      </c>
+      <c r="J333">
+        <v>0</v>
+      </c>
+      <c r="K333">
+        <v>0</v>
+      </c>
+      <c r="L333">
+        <v>0</v>
+      </c>
+      <c r="M333">
+        <v>0</v>
+      </c>
+      <c r="N333">
+        <v>0</v>
+      </c>
+      <c r="O333">
+        <v>0</v>
+      </c>
+      <c r="P333">
+        <v>0</v>
+      </c>
+      <c r="Q333">
+        <v>0</v>
+      </c>
+      <c r="R333">
         <v>0</v>
       </c>
     </row>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC5A79B4-0527-4002-9CD8-9EA9917D73D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E1302F-45AA-4542-A03A-042A2B0F681F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1840" uniqueCount="1084">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1844" uniqueCount="1086">
   <si>
     <t>編號</t>
   </si>
@@ -664,12 +664,6 @@
   </si>
   <si>
     <t>控場遞減</t>
-  </si>
-  <si>
-    <t>控制持續時間×max(0, 1−每秒遞減率×經過秒數)</t>
-  </si>
-  <si>
-    <t>普通敵人每秒遞減 1%；菁英每秒遞減 3%；BOSS 不受控場遞減。</t>
   </si>
   <si>
     <t>過關回復</t>
@@ -4049,6 +4043,20 @@
   </si>
   <si>
     <t>{elemDmgFire,elemDmgIce,elemDmgLightning,elemDmgPoison,elemDmgLight,elemDmgDark,elemDmgEarth,elemDmgWind,resFire,resIce,resLightning,resPoison,resLight,resDark,resEarth,resWind,resAll}</t>
+  </si>
+  <si>
+    <t>控制持續時間 × max(0, 1 − 該類已被控次數 × 每次遞減%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-10-05 改為依「被控場次數」遞減（取代舊的存活秒數遞減）。控場分三類各自獨立計次與遞減：無法行動（暈眩、凍結、石化等無法普攻／施放技能／行動）、攻速降低、移動速度降低。a=無法行動類每被控 1 次，之後同類控場持續時間遞減 a%；b=攻速降低類每次遞減 b%；c=移動速度降低類每次遞減 c%；d=無法行動類的合併秒數（此秒數內重複施加視為同一次，多段命中不會連扣）。例：a=5，冰凍 2 秒 → 第 1 次 2 秒、第 2 次 1.9 秒、…、第 20 次起完全免疫。遞減只作用在獨立記錄的「控場效果」，狀態本身的數值與持續時間不變（遞減到 0 只是沒有控場效果，狀態仍照常掛上，依賴狀態的判定照常觸發）。攻速／移速類：同類控場還在生效中時不重複計次（場域緩速每 0.5 秒重塗，只算進入場域的那一次）。參數填 0＝該類不遞減。BOSS 對攻擊頻率類控場另有完全免疫，不受本列影響。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>0.5</t>
   </si>
 </sst>
 </file>
@@ -5252,7 +5260,7 @@
         <v>基礎a + 技能熟練度等級 + 潛力天賦加成</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="G11">
         <f>計算表!G11</f>
@@ -5695,7 +5703,7 @@
         <v>（查表）</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G17">
         <f>計算表!G17</f>
@@ -5768,7 +5776,7 @@
         <v>（查表）</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G18">
         <f>計算表!G18</f>
@@ -5841,7 +5849,7 @@
         <v>（查表）</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G19">
         <f>計算表!G19</f>
@@ -5914,7 +5922,7 @@
         <v>（查表）</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G20">
         <f>計算表!G20</f>
@@ -5987,7 +5995,7 @@
         <v>（查表）</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G21">
         <f>計算表!G21</f>
@@ -6060,7 +6068,7 @@
         <v>（查表）</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G22">
         <f>計算表!G22</f>
@@ -6133,7 +6141,7 @@
         <v>（查表）</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G23">
         <f>計算表!G23</f>
@@ -6206,7 +6214,7 @@
         <v>（查表）</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G24">
         <f>計算表!G24</f>
@@ -6279,7 +6287,7 @@
         <v>（查表）</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G25">
         <f>計算表!G25</f>
@@ -6352,7 +6360,7 @@
         <v>（查表）</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G26">
         <f>計算表!G26</f>
@@ -6425,7 +6433,7 @@
         <v>（查表）</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G27">
         <f>計算表!G27</f>
@@ -6498,7 +6506,7 @@
         <v>（查表）</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G28">
         <f>計算表!G28</f>
@@ -6571,7 +6579,7 @@
         <v>（查表）</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G29">
         <f>計算表!G29</f>
@@ -6644,7 +6652,7 @@
         <v>（查表）</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G30">
         <f>計算表!G30</f>
@@ -6717,7 +6725,7 @@
         <v>（查表）</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G31">
         <f>計算表!G31</f>
@@ -6790,7 +6798,7 @@
         <v>（查表）</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G32">
         <f>計算表!G32</f>
@@ -6863,7 +6871,7 @@
         <v>（查表）</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G33">
         <f>計算表!G33</f>
@@ -6936,7 +6944,7 @@
         <v>（查表）</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G34">
         <f>計算表!G34</f>
@@ -7009,7 +7017,7 @@
         <v>（查表）</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G35">
         <f>計算表!G35</f>
@@ -7082,7 +7090,7 @@
         <v>（查表）</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G36">
         <f>計算表!G36</f>
@@ -7155,7 +7163,7 @@
         <v>（查表）</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G37">
         <f>計算表!G37</f>
@@ -8864,7 +8872,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="I60">
         <f>計算表!I60</f>
@@ -9233,7 +9241,7 @@
         <v>5</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="I65">
         <f>計算表!I65</f>
@@ -9306,7 +9314,7 @@
         <v>0.875</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="I66">
         <f>計算表!I66</f>
@@ -9597,7 +9605,7 @@
         <v>a=每點敏捷%。</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="H70">
         <f>計算表!H70</f>
@@ -10847,27 +10855,27 @@
       </c>
       <c r="E87" t="str">
         <f>計算表!E87</f>
-        <v>控制持續時間×max(0, 1−每秒遞減率×經過秒數)</v>
+        <v>控制持續時間 × max(0, 1 − 該類已被控次數 × 每次遞減%)</v>
       </c>
       <c r="F87" t="str">
         <f>計算表!F87</f>
-        <v>普通敵人每秒遞減 1%；菁英每秒遞減 3%；BOSS 不受控場遞減。</v>
-      </c>
-      <c r="G87">
+        <v>2026-10-05 改為依「被控場次數」遞減（取代舊的存活秒數遞減）。控場分三類各自獨立計次與遞減：無法行動（暈眩、凍結、石化等無法普攻／施放技能／行動）、攻速降低、移動速度降低。a=無法行動類每被控 1 次，之後同類控場持續時間遞減 a%；b=攻速降低類每次遞減 b%；c=移動速度降低類每次遞減 c%；d=無法行動類的合併秒數（此秒數內重複施加視為同一次，多段命中不會連扣）。例：a=5，冰凍 2 秒 → 第 1 次 2 秒、第 2 次 1.9 秒、…、第 20 次起完全免疫。遞減只作用在獨立記錄的「控場效果」，狀態本身的數值與持續時間不變（遞減到 0 只是沒有控場效果，狀態仍照常掛上，依賴狀態的判定照常觸發）。攻速／移速類：同類控場還在生效中時不重複計次（場域緩速每 0.5 秒重塗，只算進入場域的那一次）。參數填 0＝該類不遞減。BOSS 對攻擊頻率類控場另有完全免疫，不受本列影響。</v>
+      </c>
+      <c r="G87" t="str">
         <f>計算表!G87</f>
-        <v>1</v>
-      </c>
-      <c r="H87">
+        <v>5</v>
+      </c>
+      <c r="H87" t="str">
         <f>計算表!H87</f>
-        <v>3</v>
-      </c>
-      <c r="I87">
+        <v>5</v>
+      </c>
+      <c r="I87" t="str">
         <f>計算表!I87</f>
-        <v>0</v>
-      </c>
-      <c r="J87">
+        <v>5</v>
+      </c>
+      <c r="J87" t="str">
         <f>計算表!J87</f>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K87">
         <f>計算表!K87</f>
@@ -11516,7 +11524,7 @@
         <v>忽略敵人防禦% = 穿透%/(穿透%+a)</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="G96">
         <f>計算表!G96</f>
@@ -13303,7 +13311,7 @@
         <v>0.5</v>
       </c>
       <c r="I120" s="7" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="J120">
         <f>計算表!J120</f>
@@ -15218,7 +15226,7 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條。</v>
       </c>
       <c r="G146" s="7" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="H146">
         <f>計算表!H146</f>
@@ -15291,13 +15299,13 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條。</v>
       </c>
       <c r="G147" s="7" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H147" s="7" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I147" s="7" t="s">
         <v>1029</v>
-      </c>
-      <c r="H147" s="7" t="s">
-        <v>1030</v>
-      </c>
-      <c r="I147" s="7" t="s">
-        <v>1031</v>
       </c>
       <c r="J147">
         <f>計算表!J147</f>
@@ -15362,20 +15370,20 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條。</v>
       </c>
       <c r="G148" s="7" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="H148" s="7" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="I148">
         <f>計算表!I148</f>
         <v>9.11754</v>
       </c>
       <c r="J148" s="7" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="K148" s="7" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="L148">
         <f>計算表!L148</f>
@@ -15432,22 +15440,22 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條。</v>
       </c>
       <c r="G149" s="7" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H149" s="7" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I149" s="7" t="s">
         <v>1036</v>
       </c>
-      <c r="H149" s="7" t="s">
+      <c r="J149" s="7" t="s">
         <v>1037</v>
       </c>
-      <c r="I149" s="7" t="s">
+      <c r="K149" s="7" t="s">
         <v>1038</v>
       </c>
-      <c r="J149" s="7" t="s">
+      <c r="L149" s="7" t="s">
         <v>1039</v>
-      </c>
-      <c r="K149" s="7" t="s">
-        <v>1040</v>
-      </c>
-      <c r="L149" s="7" t="s">
-        <v>1041</v>
       </c>
       <c r="M149">
         <f>計算表!M149</f>
@@ -15500,28 +15508,28 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條。</v>
       </c>
       <c r="G150" s="7" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H150" s="7" t="s">
+        <v>1041</v>
+      </c>
+      <c r="I150" s="7" t="s">
         <v>1042</v>
       </c>
-      <c r="H150" s="7" t="s">
+      <c r="J150" s="7" t="s">
         <v>1043</v>
       </c>
-      <c r="I150" s="7" t="s">
+      <c r="K150" s="7" t="s">
         <v>1044</v>
       </c>
-      <c r="J150" s="7" t="s">
+      <c r="L150" s="7" t="s">
         <v>1045</v>
       </c>
-      <c r="K150" s="7" t="s">
+      <c r="M150" s="7" t="s">
         <v>1046</v>
       </c>
-      <c r="L150" s="7" t="s">
+      <c r="N150" s="7" t="s">
         <v>1047</v>
-      </c>
-      <c r="M150" s="7" t="s">
-        <v>1048</v>
-      </c>
-      <c r="N150" s="7" t="s">
-        <v>1049</v>
       </c>
       <c r="O150">
         <f>計算表!O150</f>
@@ -15566,28 +15574,28 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條。</v>
       </c>
       <c r="G151" s="7" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H151" s="7" t="s">
+        <v>1049</v>
+      </c>
+      <c r="I151" s="7" t="s">
         <v>1050</v>
       </c>
-      <c r="H151" s="7" t="s">
+      <c r="J151" s="7" t="s">
         <v>1051</v>
       </c>
-      <c r="I151" s="7" t="s">
+      <c r="K151" s="7" t="s">
         <v>1052</v>
       </c>
-      <c r="J151" s="7" t="s">
+      <c r="L151" s="7" t="s">
         <v>1053</v>
       </c>
-      <c r="K151" s="7" t="s">
+      <c r="M151" s="7" t="s">
         <v>1054</v>
       </c>
-      <c r="L151" s="7" t="s">
+      <c r="N151" s="7" t="s">
         <v>1055</v>
-      </c>
-      <c r="M151" s="7" t="s">
-        <v>1056</v>
-      </c>
-      <c r="N151" s="7" t="s">
-        <v>1057</v>
       </c>
       <c r="O151">
         <f>計算表!O151</f>
@@ -15632,31 +15640,31 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條 j=9條。</v>
       </c>
       <c r="G152" s="7" t="s">
+        <v>1056</v>
+      </c>
+      <c r="H152" s="7" t="s">
+        <v>1057</v>
+      </c>
+      <c r="I152" s="7" t="s">
         <v>1058</v>
       </c>
-      <c r="H152" s="7" t="s">
+      <c r="J152" s="7" t="s">
         <v>1059</v>
       </c>
-      <c r="I152" s="7" t="s">
+      <c r="K152" s="7" t="s">
         <v>1060</v>
       </c>
-      <c r="J152" s="7" t="s">
+      <c r="L152" s="7" t="s">
         <v>1061</v>
       </c>
-      <c r="K152" s="7" t="s">
+      <c r="M152" s="7" t="s">
         <v>1062</v>
       </c>
-      <c r="L152" s="7" t="s">
+      <c r="N152" s="7" t="s">
         <v>1063</v>
       </c>
-      <c r="M152" s="7" t="s">
+      <c r="O152" s="7" t="s">
         <v>1064</v>
-      </c>
-      <c r="N152" s="7" t="s">
-        <v>1065</v>
-      </c>
-      <c r="O152" s="7" t="s">
-        <v>1066</v>
       </c>
       <c r="P152">
         <f>計算表!P152</f>
@@ -15697,7 +15705,7 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條 j=9條 k=10條。</v>
       </c>
       <c r="G153" s="7" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="H153">
         <f>計算表!H153</f>
@@ -17180,7 +17188,7 @@
         <v>200</v>
       </c>
       <c r="H173" s="7" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="I173">
         <f>計算表!I173</f>
@@ -17767,7 +17775,7 @@
         <v>a=基礎權重 b=權重加成 c=加成上限 d=出現門檻。普通無加成。神鑄創世不參與此擲骰。(裝備合成才有作用，目前功能關閉中)</v>
       </c>
       <c r="G181" s="7" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="H181" t="str">
         <f>計算表!H181</f>
@@ -20586,7 +20594,7 @@
         <v>1</v>
       </c>
       <c r="I219" s="7" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="J219">
         <f>計算表!J220</f>
@@ -25601,10 +25609,10 @@
         <v>等級上限</v>
       </c>
       <c r="E287" s="7" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="F287" s="7" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="G287">
         <f>計算表!G291</f>
@@ -27235,7 +27243,7 @@
         <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數。</v>
       </c>
       <c r="G309" s="7" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="H309">
         <f>計算表!H325</f>
@@ -27604,7 +27612,7 @@
         <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數。</v>
       </c>
       <c r="G314" s="7" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="H314">
         <f>計算表!H330</f>
@@ -27956,16 +27964,16 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
+        <v>950</v>
+      </c>
+      <c r="D2" t="s">
+        <v>951</v>
+      </c>
+      <c r="E2" t="s">
         <v>952</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>953</v>
-      </c>
-      <c r="E2" t="s">
-        <v>954</v>
-      </c>
-      <c r="F2" t="s">
-        <v>955</v>
       </c>
       <c r="G2">
         <v>50000</v>
@@ -28013,16 +28021,16 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
+        <v>950</v>
+      </c>
+      <c r="D3" t="s">
+        <v>954</v>
+      </c>
+      <c r="E3" t="s">
         <v>952</v>
       </c>
-      <c r="D3" t="s">
-        <v>956</v>
-      </c>
-      <c r="E3" t="s">
-        <v>954</v>
-      </c>
       <c r="F3" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="G3">
         <v>500</v>
@@ -28070,16 +28078,16 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
+        <v>950</v>
+      </c>
+      <c r="D4" t="s">
+        <v>956</v>
+      </c>
+      <c r="E4" t="s">
         <v>952</v>
       </c>
-      <c r="D4" t="s">
-        <v>958</v>
-      </c>
-      <c r="E4" t="s">
-        <v>954</v>
-      </c>
       <c r="F4" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -28127,16 +28135,16 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
+        <v>843</v>
+      </c>
+      <c r="D5" t="s">
+        <v>844</v>
+      </c>
+      <c r="E5" t="s">
         <v>845</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>846</v>
-      </c>
-      <c r="E5" t="s">
-        <v>847</v>
-      </c>
-      <c r="F5" t="s">
-        <v>848</v>
       </c>
       <c r="G5">
         <v>24</v>
@@ -28184,16 +28192,16 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="D6" t="s">
+        <v>847</v>
+      </c>
+      <c r="E6" t="s">
+        <v>848</v>
+      </c>
+      <c r="F6" t="s">
         <v>849</v>
-      </c>
-      <c r="E6" t="s">
-        <v>850</v>
-      </c>
-      <c r="F6" t="s">
-        <v>851</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -28241,16 +28249,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="D7" t="s">
+        <v>850</v>
+      </c>
+      <c r="E7" t="s">
+        <v>851</v>
+      </c>
+      <c r="F7" t="s">
         <v>852</v>
-      </c>
-      <c r="E7" t="s">
-        <v>853</v>
-      </c>
-      <c r="F7" t="s">
-        <v>854</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -28298,16 +28306,16 @@
         <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="D8" t="s">
+        <v>853</v>
+      </c>
+      <c r="E8" t="s">
+        <v>854</v>
+      </c>
+      <c r="F8" t="s">
         <v>855</v>
-      </c>
-      <c r="E8" t="s">
-        <v>856</v>
-      </c>
-      <c r="F8" t="s">
-        <v>857</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -28700,13 +28708,13 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
+        <v>924</v>
+      </c>
+      <c r="E15" t="s">
+        <v>925</v>
+      </c>
+      <c r="F15" t="s">
         <v>926</v>
-      </c>
-      <c r="E15" t="s">
-        <v>927</v>
-      </c>
-      <c r="F15" t="s">
-        <v>928</v>
       </c>
       <c r="G15">
         <v>30</v>
@@ -28757,13 +28765,13 @@
         <v>18</v>
       </c>
       <c r="D16" t="s">
+        <v>927</v>
+      </c>
+      <c r="E16" t="s">
+        <v>928</v>
+      </c>
+      <c r="F16" t="s">
         <v>929</v>
-      </c>
-      <c r="E16" t="s">
-        <v>930</v>
-      </c>
-      <c r="F16" t="s">
-        <v>931</v>
       </c>
       <c r="G16">
         <v>1000</v>
@@ -30302,7 +30310,7 @@
         <v>149</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -30359,7 +30367,7 @@
         <v>149</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -31724,10 +31732,10 @@
         <v>134</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G68">
         <v>0.86</v>
@@ -31952,10 +31960,10 @@
         <v>143</v>
       </c>
       <c r="E72" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="F72" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="G72">
         <v>5</v>
@@ -32060,16 +32068,16 @@
         <v>0</v>
       </c>
       <c r="C74" t="s">
+        <v>233</v>
+      </c>
+      <c r="D74" t="s">
+        <v>234</v>
+      </c>
+      <c r="E74" t="s">
         <v>235</v>
       </c>
-      <c r="D74" t="s">
+      <c r="F74" t="s">
         <v>236</v>
-      </c>
-      <c r="E74" t="s">
-        <v>237</v>
-      </c>
-      <c r="F74" t="s">
-        <v>238</v>
       </c>
       <c r="G74">
         <v>15</v>
@@ -32117,16 +32125,16 @@
         <v>0</v>
       </c>
       <c r="C75" t="s">
+        <v>233</v>
+      </c>
+      <c r="D75" t="s">
+        <v>237</v>
+      </c>
+      <c r="E75" t="s">
         <v>235</v>
       </c>
-      <c r="D75" t="s">
-        <v>239</v>
-      </c>
-      <c r="E75" t="s">
-        <v>237</v>
-      </c>
       <c r="F75" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G75">
         <v>10</v>
@@ -32174,16 +32182,16 @@
         <v>0</v>
       </c>
       <c r="C76" t="s">
+        <v>233</v>
+      </c>
+      <c r="D76" t="s">
+        <v>239</v>
+      </c>
+      <c r="E76" t="s">
         <v>235</v>
       </c>
-      <c r="D76" t="s">
-        <v>241</v>
-      </c>
-      <c r="E76" t="s">
-        <v>237</v>
-      </c>
       <c r="F76" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G76">
         <v>25</v>
@@ -32231,16 +32239,16 @@
         <v>0</v>
       </c>
       <c r="C77" t="s">
+        <v>233</v>
+      </c>
+      <c r="D77" t="s">
+        <v>241</v>
+      </c>
+      <c r="E77" t="s">
         <v>235</v>
       </c>
-      <c r="D77" t="s">
-        <v>243</v>
-      </c>
-      <c r="E77" t="s">
-        <v>237</v>
-      </c>
       <c r="F77" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G77">
         <v>20</v>
@@ -32288,16 +32296,16 @@
         <v>0</v>
       </c>
       <c r="C78" t="s">
+        <v>233</v>
+      </c>
+      <c r="D78" t="s">
+        <v>243</v>
+      </c>
+      <c r="E78" t="s">
         <v>235</v>
       </c>
-      <c r="D78" t="s">
-        <v>245</v>
-      </c>
-      <c r="E78" t="s">
-        <v>237</v>
-      </c>
       <c r="F78" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="G78">
         <v>100</v>
@@ -32806,23 +32814,23 @@
       <c r="D87" t="s">
         <v>209</v>
       </c>
-      <c r="E87" t="s">
-        <v>210</v>
-      </c>
-      <c r="F87" t="s">
-        <v>211</v>
-      </c>
-      <c r="G87">
-        <v>1</v>
-      </c>
-      <c r="H87">
-        <v>3</v>
-      </c>
-      <c r="I87">
-        <v>0</v>
-      </c>
-      <c r="J87">
-        <v>0</v>
+      <c r="E87" s="7" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F87" s="7" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H87" s="7" t="s">
+        <v>1084</v>
+      </c>
+      <c r="I87" s="7" t="s">
+        <v>1084</v>
+      </c>
+      <c r="J87" s="7" t="s">
+        <v>1085</v>
       </c>
       <c r="K87">
         <v>0</v>
@@ -32861,13 +32869,13 @@
         <v>188</v>
       </c>
       <c r="D88" t="s">
+        <v>210</v>
+      </c>
+      <c r="E88" t="s">
+        <v>211</v>
+      </c>
+      <c r="F88" t="s">
         <v>212</v>
-      </c>
-      <c r="E88" t="s">
-        <v>213</v>
-      </c>
-      <c r="F88" t="s">
-        <v>214</v>
       </c>
       <c r="G88">
         <v>12</v>
@@ -32918,13 +32926,13 @@
         <v>188</v>
       </c>
       <c r="D89" t="s">
+        <v>213</v>
+      </c>
+      <c r="E89" t="s">
+        <v>214</v>
+      </c>
+      <c r="F89" t="s">
         <v>215</v>
-      </c>
-      <c r="E89" t="s">
-        <v>216</v>
-      </c>
-      <c r="F89" t="s">
-        <v>217</v>
       </c>
       <c r="G89">
         <v>1</v>
@@ -32975,13 +32983,13 @@
         <v>188</v>
       </c>
       <c r="D90" t="s">
+        <v>216</v>
+      </c>
+      <c r="E90" t="s">
+        <v>217</v>
+      </c>
+      <c r="F90" t="s">
         <v>218</v>
-      </c>
-      <c r="E90" t="s">
-        <v>219</v>
-      </c>
-      <c r="F90" t="s">
-        <v>220</v>
       </c>
       <c r="G90">
         <v>10</v>
@@ -33032,13 +33040,13 @@
         <v>188</v>
       </c>
       <c r="D91" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E91" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F91" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G91">
         <v>1000</v>
@@ -33089,13 +33097,13 @@
         <v>188</v>
       </c>
       <c r="D92" t="s">
+        <v>221</v>
+      </c>
+      <c r="E92" t="s">
+        <v>222</v>
+      </c>
+      <c r="F92" t="s">
         <v>223</v>
-      </c>
-      <c r="E92" t="s">
-        <v>224</v>
-      </c>
-      <c r="F92" t="s">
-        <v>225</v>
       </c>
       <c r="G92">
         <v>50</v>
@@ -33146,13 +33154,13 @@
         <v>188</v>
       </c>
       <c r="D93" t="s">
+        <v>224</v>
+      </c>
+      <c r="E93" t="s">
+        <v>225</v>
+      </c>
+      <c r="F93" t="s">
         <v>226</v>
-      </c>
-      <c r="E93" t="s">
-        <v>227</v>
-      </c>
-      <c r="F93" t="s">
-        <v>228</v>
       </c>
       <c r="G93">
         <v>30</v>
@@ -33203,13 +33211,13 @@
         <v>188</v>
       </c>
       <c r="D94" t="s">
+        <v>227</v>
+      </c>
+      <c r="E94" t="s">
+        <v>228</v>
+      </c>
+      <c r="F94" t="s">
         <v>229</v>
-      </c>
-      <c r="E94" t="s">
-        <v>230</v>
-      </c>
-      <c r="F94" t="s">
-        <v>231</v>
       </c>
       <c r="G94">
         <v>100</v>
@@ -33260,13 +33268,13 @@
         <v>188</v>
       </c>
       <c r="D95" t="s">
+        <v>230</v>
+      </c>
+      <c r="E95" t="s">
+        <v>231</v>
+      </c>
+      <c r="F95" t="s">
         <v>232</v>
-      </c>
-      <c r="E95" t="s">
-        <v>233</v>
-      </c>
-      <c r="F95" t="s">
-        <v>234</v>
       </c>
       <c r="G95">
         <v>5</v>
@@ -33317,13 +33325,13 @@
         <v>188</v>
       </c>
       <c r="D96" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="F96" s="2" t="s">
         <v>960</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>961</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>962</v>
       </c>
       <c r="G96">
         <v>0.75</v>
@@ -33371,16 +33379,16 @@
         <v>0</v>
       </c>
       <c r="C97" t="s">
+        <v>314</v>
+      </c>
+      <c r="D97" t="s">
+        <v>315</v>
+      </c>
+      <c r="E97" t="s">
         <v>316</v>
       </c>
-      <c r="D97" t="s">
+      <c r="F97" t="s">
         <v>317</v>
-      </c>
-      <c r="E97" t="s">
-        <v>318</v>
-      </c>
-      <c r="F97" t="s">
-        <v>319</v>
       </c>
       <c r="G97">
         <v>4</v>
@@ -33428,16 +33436,16 @@
         <v>0</v>
       </c>
       <c r="C98" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D98" t="s">
+        <v>318</v>
+      </c>
+      <c r="E98" t="s">
+        <v>319</v>
+      </c>
+      <c r="F98" t="s">
         <v>320</v>
-      </c>
-      <c r="E98" t="s">
-        <v>321</v>
-      </c>
-      <c r="F98" t="s">
-        <v>322</v>
       </c>
       <c r="G98">
         <v>3</v>
@@ -33485,16 +33493,16 @@
         <v>0</v>
       </c>
       <c r="C99" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D99" t="s">
         <v>135</v>
       </c>
       <c r="E99" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F99" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G99">
         <v>200</v>
@@ -33542,25 +33550,25 @@
         <v>0</v>
       </c>
       <c r="C100" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D100" t="s">
+        <v>323</v>
+      </c>
+      <c r="E100" t="s">
+        <v>324</v>
+      </c>
+      <c r="F100" t="s">
         <v>325</v>
       </c>
-      <c r="E100" t="s">
+      <c r="G100" t="s">
         <v>326</v>
       </c>
-      <c r="F100" t="s">
+      <c r="H100" t="s">
         <v>327</v>
       </c>
-      <c r="G100" t="s">
+      <c r="I100" t="s">
         <v>328</v>
-      </c>
-      <c r="H100" t="s">
-        <v>329</v>
-      </c>
-      <c r="I100" t="s">
-        <v>330</v>
       </c>
       <c r="J100">
         <v>0</v>
@@ -33599,16 +33607,16 @@
         <v>0</v>
       </c>
       <c r="C101" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D101" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E101" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F101" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G101">
         <v>20</v>
@@ -33656,16 +33664,16 @@
         <v>0</v>
       </c>
       <c r="C102" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D102" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E102" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F102" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="G102">
         <v>3</v>
@@ -33713,16 +33721,16 @@
         <v>0</v>
       </c>
       <c r="C103" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D103" t="s">
+        <v>333</v>
+      </c>
+      <c r="E103" t="s">
+        <v>334</v>
+      </c>
+      <c r="F103" t="s">
         <v>335</v>
-      </c>
-      <c r="E103" t="s">
-        <v>336</v>
-      </c>
-      <c r="F103" t="s">
-        <v>337</v>
       </c>
       <c r="G103">
         <v>10</v>
@@ -33770,16 +33778,16 @@
         <v>0</v>
       </c>
       <c r="C104" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D104" t="s">
+        <v>336</v>
+      </c>
+      <c r="E104" t="s">
+        <v>337</v>
+      </c>
+      <c r="F104" t="s">
         <v>338</v>
-      </c>
-      <c r="E104" t="s">
-        <v>339</v>
-      </c>
-      <c r="F104" t="s">
-        <v>340</v>
       </c>
       <c r="G104">
         <v>3</v>
@@ -33827,16 +33835,16 @@
         <v>0</v>
       </c>
       <c r="C105" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D105" t="s">
         <v>138</v>
       </c>
       <c r="E105" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F105" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="G105">
         <v>8</v>
@@ -33884,16 +33892,16 @@
         <v>0</v>
       </c>
       <c r="C106" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D106" t="s">
+        <v>341</v>
+      </c>
+      <c r="E106" t="s">
+        <v>342</v>
+      </c>
+      <c r="F106" t="s">
         <v>343</v>
-      </c>
-      <c r="E106" t="s">
-        <v>344</v>
-      </c>
-      <c r="F106" t="s">
-        <v>345</v>
       </c>
       <c r="G106">
         <v>3</v>
@@ -33941,16 +33949,16 @@
         <v>0</v>
       </c>
       <c r="C107" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D107" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E107" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F107" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="G107">
         <v>2</v>
@@ -33998,16 +34006,16 @@
         <v>0</v>
       </c>
       <c r="C108" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D108" t="s">
+        <v>346</v>
+      </c>
+      <c r="E108" t="s">
+        <v>347</v>
+      </c>
+      <c r="F108" t="s">
         <v>348</v>
-      </c>
-      <c r="E108" t="s">
-        <v>349</v>
-      </c>
-      <c r="F108" t="s">
-        <v>350</v>
       </c>
       <c r="G108">
         <v>60</v>
@@ -34055,16 +34063,16 @@
         <v>0</v>
       </c>
       <c r="C109" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D109" t="s">
+        <v>349</v>
+      </c>
+      <c r="E109" t="s">
+        <v>350</v>
+      </c>
+      <c r="F109" t="s">
         <v>351</v>
-      </c>
-      <c r="E109" t="s">
-        <v>352</v>
-      </c>
-      <c r="F109" t="s">
-        <v>353</v>
       </c>
       <c r="G109">
         <v>51</v>
@@ -34112,16 +34120,16 @@
         <v>0</v>
       </c>
       <c r="C110" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D110" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E110" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F110" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G110">
         <v>1</v>
@@ -34169,16 +34177,16 @@
         <v>0</v>
       </c>
       <c r="C111" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D111" t="s">
+        <v>354</v>
+      </c>
+      <c r="E111" t="s">
+        <v>355</v>
+      </c>
+      <c r="F111" t="s">
         <v>356</v>
-      </c>
-      <c r="E111" t="s">
-        <v>357</v>
-      </c>
-      <c r="F111" t="s">
-        <v>358</v>
       </c>
       <c r="G111">
         <v>5</v>
@@ -34226,16 +34234,16 @@
         <v>0</v>
       </c>
       <c r="C112" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D112" t="s">
+        <v>357</v>
+      </c>
+      <c r="E112" t="s">
+        <v>358</v>
+      </c>
+      <c r="F112" t="s">
         <v>359</v>
-      </c>
-      <c r="E112" t="s">
-        <v>360</v>
-      </c>
-      <c r="F112" t="s">
-        <v>361</v>
       </c>
       <c r="G112">
         <v>100</v>
@@ -34283,16 +34291,16 @@
         <v>0</v>
       </c>
       <c r="C113" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D113" t="s">
+        <v>360</v>
+      </c>
+      <c r="E113" t="s">
+        <v>361</v>
+      </c>
+      <c r="F113" t="s">
         <v>362</v>
-      </c>
-      <c r="E113" t="s">
-        <v>363</v>
-      </c>
-      <c r="F113" t="s">
-        <v>364</v>
       </c>
       <c r="G113">
         <v>30</v>
@@ -34340,25 +34348,25 @@
         <v>0</v>
       </c>
       <c r="C114" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D114" t="s">
+        <v>363</v>
+      </c>
+      <c r="E114" t="s">
+        <v>364</v>
+      </c>
+      <c r="F114" t="s">
+        <v>353</v>
+      </c>
+      <c r="G114" t="s">
         <v>365</v>
       </c>
-      <c r="E114" t="s">
+      <c r="H114" t="s">
         <v>366</v>
       </c>
-      <c r="F114" t="s">
-        <v>355</v>
-      </c>
-      <c r="G114" t="s">
+      <c r="I114" t="s">
         <v>367</v>
-      </c>
-      <c r="H114" t="s">
-        <v>368</v>
-      </c>
-      <c r="I114" t="s">
-        <v>369</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -34397,16 +34405,16 @@
         <v>0</v>
       </c>
       <c r="C115" t="s">
+        <v>304</v>
+      </c>
+      <c r="D115" t="s">
+        <v>305</v>
+      </c>
+      <c r="E115" t="s">
         <v>306</v>
       </c>
-      <c r="D115" t="s">
+      <c r="F115" t="s">
         <v>307</v>
-      </c>
-      <c r="E115" t="s">
-        <v>308</v>
-      </c>
-      <c r="F115" t="s">
-        <v>309</v>
       </c>
       <c r="G115">
         <v>50</v>
@@ -34454,16 +34462,16 @@
         <v>0</v>
       </c>
       <c r="C116" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D116" t="s">
+        <v>308</v>
+      </c>
+      <c r="E116" t="s">
+        <v>309</v>
+      </c>
+      <c r="F116" t="s">
         <v>310</v>
-      </c>
-      <c r="E116" t="s">
-        <v>311</v>
-      </c>
-      <c r="F116" t="s">
-        <v>312</v>
       </c>
       <c r="G116">
         <v>15</v>
@@ -34511,16 +34519,16 @@
         <v>0</v>
       </c>
       <c r="C117" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D117" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="E117" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F117" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G117">
         <v>3</v>
@@ -34568,16 +34576,16 @@
         <v>0</v>
       </c>
       <c r="C118" t="s">
+        <v>245</v>
+      </c>
+      <c r="D118" t="s">
+        <v>246</v>
+      </c>
+      <c r="E118" t="s">
         <v>247</v>
       </c>
-      <c r="D118" t="s">
+      <c r="F118" t="s">
         <v>248</v>
-      </c>
-      <c r="E118" t="s">
-        <v>249</v>
-      </c>
-      <c r="F118" t="s">
-        <v>250</v>
       </c>
       <c r="G118">
         <v>20</v>
@@ -34625,16 +34633,16 @@
         <v>0</v>
       </c>
       <c r="C119" t="s">
+        <v>245</v>
+      </c>
+      <c r="D119" t="s">
+        <v>249</v>
+      </c>
+      <c r="E119" t="s">
         <v>247</v>
       </c>
-      <c r="D119" t="s">
-        <v>251</v>
-      </c>
-      <c r="E119" t="s">
-        <v>249</v>
-      </c>
       <c r="F119" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G119">
         <v>2</v>
@@ -34682,16 +34690,16 @@
         <v>0</v>
       </c>
       <c r="C120" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D120" t="s">
         <v>119</v>
       </c>
       <c r="E120" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="F120" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G120">
         <v>2</v>
@@ -34739,16 +34747,16 @@
         <v>0</v>
       </c>
       <c r="C121" t="s">
+        <v>245</v>
+      </c>
+      <c r="D121" t="s">
+        <v>251</v>
+      </c>
+      <c r="E121" t="s">
         <v>247</v>
       </c>
-      <c r="D121" t="s">
-        <v>253</v>
-      </c>
-      <c r="E121" t="s">
-        <v>249</v>
-      </c>
       <c r="F121" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G121">
         <v>250</v>
@@ -34796,16 +34804,16 @@
         <v>0</v>
       </c>
       <c r="C122" t="s">
+        <v>245</v>
+      </c>
+      <c r="D122" t="s">
+        <v>252</v>
+      </c>
+      <c r="E122" t="s">
         <v>247</v>
       </c>
-      <c r="D122" t="s">
-        <v>254</v>
-      </c>
-      <c r="E122" t="s">
-        <v>249</v>
-      </c>
       <c r="F122" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G122">
         <v>120</v>
@@ -34853,16 +34861,16 @@
         <v>0</v>
       </c>
       <c r="C123" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D123" t="s">
         <v>134</v>
       </c>
       <c r="E123" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F123" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G123">
         <v>1</v>
@@ -34910,37 +34918,37 @@
         <v>0</v>
       </c>
       <c r="C124" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D124" t="s">
         <v>135</v>
       </c>
       <c r="E124" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F124" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G124">
         <v>100</v>
       </c>
       <c r="H124" t="s">
+        <v>257</v>
+      </c>
+      <c r="I124" t="s">
+        <v>258</v>
+      </c>
+      <c r="J124" t="s">
         <v>259</v>
       </c>
-      <c r="I124" t="s">
+      <c r="K124" t="s">
         <v>260</v>
       </c>
-      <c r="J124" t="s">
+      <c r="L124" t="s">
         <v>261</v>
       </c>
-      <c r="K124" t="s">
+      <c r="M124" t="s">
         <v>262</v>
-      </c>
-      <c r="L124" t="s">
-        <v>263</v>
-      </c>
-      <c r="M124" t="s">
-        <v>264</v>
       </c>
       <c r="N124">
         <v>0</v>
@@ -34967,37 +34975,37 @@
         <v>0</v>
       </c>
       <c r="C125" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D125" t="s">
         <v>138</v>
       </c>
       <c r="E125" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F125" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G125">
         <v>5</v>
       </c>
       <c r="H125" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="I125" t="s">
+        <v>264</v>
+      </c>
+      <c r="J125" t="s">
+        <v>265</v>
+      </c>
+      <c r="K125" t="s">
         <v>266</v>
       </c>
-      <c r="J125" t="s">
+      <c r="L125" t="s">
         <v>267</v>
       </c>
-      <c r="K125" t="s">
+      <c r="M125" t="s">
         <v>268</v>
-      </c>
-      <c r="L125" t="s">
-        <v>269</v>
-      </c>
-      <c r="M125" t="s">
-        <v>270</v>
       </c>
       <c r="N125">
         <v>0</v>
@@ -35024,16 +35032,16 @@
         <v>0</v>
       </c>
       <c r="C126" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D126" t="s">
+        <v>269</v>
+      </c>
+      <c r="E126" t="s">
+        <v>270</v>
+      </c>
+      <c r="F126" t="s">
         <v>271</v>
-      </c>
-      <c r="E126" t="s">
-        <v>272</v>
-      </c>
-      <c r="F126" t="s">
-        <v>273</v>
       </c>
       <c r="G126">
         <v>4</v>
@@ -35081,16 +35089,16 @@
         <v>0</v>
       </c>
       <c r="C127" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="E127" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="F127" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G127">
         <v>1.5</v>
@@ -35138,22 +35146,22 @@
         <v>0</v>
       </c>
       <c r="C128" t="s">
+        <v>274</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>965</v>
+      </c>
+      <c r="E128" t="s">
+        <v>275</v>
+      </c>
+      <c r="F128" t="s">
         <v>276</v>
       </c>
-      <c r="D128" s="2" t="s">
-        <v>967</v>
-      </c>
-      <c r="E128" t="s">
+      <c r="G128" t="s">
         <v>277</v>
       </c>
-      <c r="F128" t="s">
+      <c r="H128" t="s">
         <v>278</v>
-      </c>
-      <c r="G128" t="s">
-        <v>279</v>
-      </c>
-      <c r="H128" t="s">
-        <v>280</v>
       </c>
       <c r="I128">
         <v>0</v>
@@ -35195,22 +35203,22 @@
         <v>0</v>
       </c>
       <c r="C129" t="s">
+        <v>274</v>
+      </c>
+      <c r="D129" t="s">
+        <v>961</v>
+      </c>
+      <c r="E129" t="s">
+        <v>275</v>
+      </c>
+      <c r="F129" t="s">
         <v>276</v>
       </c>
-      <c r="D129" t="s">
-        <v>963</v>
-      </c>
-      <c r="E129" t="s">
-        <v>277</v>
-      </c>
-      <c r="F129" t="s">
-        <v>278</v>
-      </c>
       <c r="G129" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H129" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="I129">
         <v>0</v>
@@ -35252,25 +35260,25 @@
         <v>0</v>
       </c>
       <c r="C130" t="s">
+        <v>274</v>
+      </c>
+      <c r="D130" t="s">
+        <v>962</v>
+      </c>
+      <c r="E130" t="s">
+        <v>275</v>
+      </c>
+      <c r="F130" t="s">
         <v>276</v>
       </c>
-      <c r="D130" t="s">
-        <v>964</v>
-      </c>
-      <c r="E130" t="s">
-        <v>277</v>
-      </c>
-      <c r="F130" t="s">
-        <v>278</v>
-      </c>
       <c r="G130" t="s">
+        <v>281</v>
+      </c>
+      <c r="H130" t="s">
+        <v>282</v>
+      </c>
+      <c r="I130" t="s">
         <v>283</v>
-      </c>
-      <c r="H130" t="s">
-        <v>284</v>
-      </c>
-      <c r="I130" t="s">
-        <v>285</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -35309,28 +35317,28 @@
         <v>0</v>
       </c>
       <c r="C131" t="s">
+        <v>274</v>
+      </c>
+      <c r="D131" t="s">
+        <v>963</v>
+      </c>
+      <c r="E131" t="s">
+        <v>275</v>
+      </c>
+      <c r="F131" t="s">
         <v>276</v>
       </c>
-      <c r="D131" t="s">
-        <v>965</v>
-      </c>
-      <c r="E131" t="s">
-        <v>277</v>
-      </c>
-      <c r="F131" t="s">
-        <v>278</v>
-      </c>
       <c r="G131" t="s">
+        <v>284</v>
+      </c>
+      <c r="H131" t="s">
+        <v>285</v>
+      </c>
+      <c r="I131" t="s">
         <v>286</v>
       </c>
-      <c r="H131" t="s">
+      <c r="J131" t="s">
         <v>287</v>
-      </c>
-      <c r="I131" t="s">
-        <v>288</v>
-      </c>
-      <c r="J131" t="s">
-        <v>289</v>
       </c>
       <c r="K131">
         <v>0</v>
@@ -35366,28 +35374,28 @@
         <v>0</v>
       </c>
       <c r="C132" t="s">
+        <v>274</v>
+      </c>
+      <c r="D132" t="s">
+        <v>964</v>
+      </c>
+      <c r="E132" t="s">
+        <v>275</v>
+      </c>
+      <c r="F132" t="s">
         <v>276</v>
       </c>
-      <c r="D132" t="s">
-        <v>966</v>
-      </c>
-      <c r="E132" t="s">
-        <v>277</v>
-      </c>
-      <c r="F132" t="s">
-        <v>278</v>
-      </c>
       <c r="G132" s="3" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="H132" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="I132" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="K132">
         <v>0</v>
@@ -35423,31 +35431,31 @@
         <v>0</v>
       </c>
       <c r="C133" t="s">
+        <v>274</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E133" t="s">
+        <v>275</v>
+      </c>
+      <c r="F133" t="s">
         <v>276</v>
       </c>
-      <c r="D133" s="2" t="s">
+      <c r="G133" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>1007</v>
+      </c>
+      <c r="I133" s="3" t="s">
         <v>1005</v>
       </c>
-      <c r="E133" t="s">
-        <v>277</v>
-      </c>
-      <c r="F133" t="s">
-        <v>278</v>
-      </c>
-      <c r="G133" s="3" t="s">
+      <c r="J133" s="3" t="s">
         <v>1008</v>
       </c>
-      <c r="H133" s="3" t="s">
+      <c r="K133" s="3" t="s">
         <v>1009</v>
-      </c>
-      <c r="I133" s="3" t="s">
-        <v>1007</v>
-      </c>
-      <c r="J133" s="3" t="s">
-        <v>1010</v>
-      </c>
-      <c r="K133" s="3" t="s">
-        <v>1011</v>
       </c>
       <c r="L133">
         <v>0</v>
@@ -35480,34 +35488,34 @@
         <v>0</v>
       </c>
       <c r="C134" t="s">
+        <v>274</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E134" t="s">
+        <v>275</v>
+      </c>
+      <c r="F134" t="s">
         <v>276</v>
       </c>
-      <c r="D134" s="2" t="s">
+      <c r="G134" s="3" t="s">
+        <v>1002</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>1012</v>
+      </c>
+      <c r="J134" s="3" t="s">
         <v>1013</v>
       </c>
-      <c r="E134" t="s">
-        <v>277</v>
-      </c>
-      <c r="F134" t="s">
-        <v>278</v>
-      </c>
-      <c r="G134" s="3" t="s">
-        <v>1004</v>
-      </c>
-      <c r="H134" s="3" t="s">
-        <v>977</v>
-      </c>
-      <c r="I134" s="3" t="s">
-        <v>1014</v>
-      </c>
-      <c r="J134" s="3" t="s">
-        <v>1015</v>
-      </c>
       <c r="K134" s="3" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="M134">
         <v>0</v>
@@ -35537,22 +35545,22 @@
         <v>0</v>
       </c>
       <c r="C135" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="E135" t="s">
+        <v>275</v>
+      </c>
+      <c r="F135" t="s">
+        <v>290</v>
+      </c>
+      <c r="G135" t="s">
         <v>277</v>
       </c>
-      <c r="F135" t="s">
-        <v>292</v>
-      </c>
-      <c r="G135" t="s">
-        <v>279</v>
-      </c>
       <c r="H135" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="I135">
         <v>0</v>
@@ -35594,25 +35602,25 @@
         <v>0</v>
       </c>
       <c r="C136" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="E136" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F136" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="J136">
         <v>0</v>
@@ -35651,31 +35659,31 @@
         <v>0</v>
       </c>
       <c r="C137" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="E137" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F137" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G137" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="H137" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="I137" s="3" t="s">
         <v>975</v>
       </c>
-      <c r="H137" s="3" t="s">
+      <c r="J137" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="K137" s="3" t="s">
         <v>976</v>
-      </c>
-      <c r="I137" s="3" t="s">
-        <v>977</v>
-      </c>
-      <c r="J137" s="3" t="s">
-        <v>979</v>
-      </c>
-      <c r="K137" s="3" t="s">
-        <v>978</v>
       </c>
       <c r="L137">
         <v>0</v>
@@ -35708,37 +35716,37 @@
         <v>0</v>
       </c>
       <c r="C138" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="E138" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F138" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G138" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="I138" s="3" t="s">
         <v>990</v>
       </c>
-      <c r="H138" s="3" t="s">
+      <c r="J138" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="I138" s="3" t="s">
+      <c r="K138" s="3" t="s">
         <v>992</v>
       </c>
-      <c r="J138" s="3" t="s">
+      <c r="L138" s="3" t="s">
         <v>993</v>
       </c>
-      <c r="K138" s="3" t="s">
+      <c r="M138" s="3" t="s">
         <v>994</v>
-      </c>
-      <c r="L138" s="3" t="s">
-        <v>995</v>
-      </c>
-      <c r="M138" s="3" t="s">
-        <v>996</v>
       </c>
       <c r="N138">
         <v>0</v>
@@ -35765,37 +35773,37 @@
         <v>0</v>
       </c>
       <c r="C139" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D139" s="2" t="s">
+        <v>978</v>
+      </c>
+      <c r="E139" t="s">
+        <v>275</v>
+      </c>
+      <c r="F139" t="s">
+        <v>290</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="H139" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="I139" s="3" t="s">
         <v>980</v>
       </c>
-      <c r="E139" t="s">
-        <v>277</v>
-      </c>
-      <c r="F139" t="s">
-        <v>292</v>
-      </c>
-      <c r="G139" s="3" t="s">
+      <c r="J139" s="3" t="s">
         <v>983</v>
       </c>
-      <c r="H139" s="3" t="s">
+      <c r="K139" s="3" t="s">
         <v>984</v>
       </c>
-      <c r="I139" s="3" t="s">
-        <v>982</v>
-      </c>
-      <c r="J139" s="3" t="s">
+      <c r="L139" s="3" t="s">
         <v>985</v>
       </c>
-      <c r="K139" s="3" t="s">
+      <c r="M139" s="3" t="s">
         <v>986</v>
-      </c>
-      <c r="L139" s="3" t="s">
-        <v>987</v>
-      </c>
-      <c r="M139" s="3" t="s">
-        <v>988</v>
       </c>
       <c r="N139">
         <v>0</v>
@@ -35822,19 +35830,19 @@
         <v>0</v>
       </c>
       <c r="C140" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="D140" t="s">
+        <v>291</v>
+      </c>
+      <c r="E140" t="s">
+        <v>275</v>
+      </c>
+      <c r="F140" t="s">
+        <v>292</v>
+      </c>
+      <c r="G140" t="s">
         <v>293</v>
-      </c>
-      <c r="E140" t="s">
-        <v>277</v>
-      </c>
-      <c r="F140" t="s">
-        <v>294</v>
-      </c>
-      <c r="G140" t="s">
-        <v>295</v>
       </c>
       <c r="H140">
         <v>0</v>
@@ -35879,16 +35887,16 @@
         <v>0</v>
       </c>
       <c r="C141" t="s">
+        <v>294</v>
+      </c>
+      <c r="D141" t="s">
+        <v>295</v>
+      </c>
+      <c r="E141" t="s">
         <v>296</v>
       </c>
-      <c r="D141" t="s">
+      <c r="F141" t="s">
         <v>297</v>
-      </c>
-      <c r="E141" t="s">
-        <v>298</v>
-      </c>
-      <c r="F141" t="s">
-        <v>299</v>
       </c>
       <c r="G141">
         <v>10</v>
@@ -35936,16 +35944,16 @@
         <v>0</v>
       </c>
       <c r="C142" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D142" t="s">
+        <v>298</v>
+      </c>
+      <c r="E142" t="s">
+        <v>299</v>
+      </c>
+      <c r="F142" t="s">
         <v>300</v>
-      </c>
-      <c r="E142" t="s">
-        <v>301</v>
-      </c>
-      <c r="F142" t="s">
-        <v>302</v>
       </c>
       <c r="G142">
         <v>1</v>
@@ -35993,16 +36001,16 @@
         <v>0</v>
       </c>
       <c r="C143" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D143" t="s">
+        <v>301</v>
+      </c>
+      <c r="E143" t="s">
+        <v>302</v>
+      </c>
+      <c r="F143" t="s">
         <v>303</v>
-      </c>
-      <c r="E143" t="s">
-        <v>304</v>
-      </c>
-      <c r="F143" t="s">
-        <v>305</v>
       </c>
       <c r="G143">
         <v>2</v>
@@ -36050,16 +36058,16 @@
         <v>0</v>
       </c>
       <c r="C144" t="s">
+        <v>398</v>
+      </c>
+      <c r="D144" t="s">
+        <v>399</v>
+      </c>
+      <c r="E144" t="s">
         <v>400</v>
       </c>
-      <c r="D144" t="s">
+      <c r="F144" t="s">
         <v>401</v>
-      </c>
-      <c r="E144" t="s">
-        <v>402</v>
-      </c>
-      <c r="F144" t="s">
-        <v>403</v>
       </c>
       <c r="G144">
         <v>100</v>
@@ -36107,16 +36115,16 @@
         <v>0</v>
       </c>
       <c r="C145" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D145" t="s">
+        <v>402</v>
+      </c>
+      <c r="E145" t="s">
+        <v>403</v>
+      </c>
+      <c r="F145" t="s">
         <v>404</v>
-      </c>
-      <c r="E145" t="s">
-        <v>405</v>
-      </c>
-      <c r="F145" t="s">
-        <v>406</v>
       </c>
       <c r="G145">
         <v>92</v>
@@ -36164,16 +36172,16 @@
         <v>0</v>
       </c>
       <c r="C146" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D146" t="s">
+        <v>405</v>
+      </c>
+      <c r="E146" t="s">
+        <v>406</v>
+      </c>
+      <c r="F146" t="s">
         <v>407</v>
-      </c>
-      <c r="E146" t="s">
-        <v>408</v>
-      </c>
-      <c r="F146" t="s">
-        <v>409</v>
       </c>
       <c r="G146">
         <v>78.100000000000009</v>
@@ -36221,16 +36229,16 @@
         <v>0</v>
       </c>
       <c r="C147" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D147" t="s">
+        <v>408</v>
+      </c>
+      <c r="E147" t="s">
+        <v>409</v>
+      </c>
+      <c r="F147" t="s">
         <v>410</v>
-      </c>
-      <c r="E147" t="s">
-        <v>411</v>
-      </c>
-      <c r="F147" t="s">
-        <v>412</v>
       </c>
       <c r="G147">
         <v>72.113600000000005</v>
@@ -36278,16 +36286,16 @@
         <v>0</v>
       </c>
       <c r="C148" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D148" t="s">
+        <v>411</v>
+      </c>
+      <c r="E148" t="s">
+        <v>412</v>
+      </c>
+      <c r="F148" t="s">
         <v>413</v>
-      </c>
-      <c r="E148" t="s">
-        <v>414</v>
-      </c>
-      <c r="F148" t="s">
-        <v>415</v>
       </c>
       <c r="G148">
         <v>53.837361999999999</v>
@@ -36335,16 +36343,16 @@
         <v>0</v>
       </c>
       <c r="C149" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D149" t="s">
+        <v>414</v>
+      </c>
+      <c r="E149" t="s">
+        <v>415</v>
+      </c>
+      <c r="F149" t="s">
         <v>416</v>
-      </c>
-      <c r="E149" t="s">
-        <v>417</v>
-      </c>
-      <c r="F149" t="s">
-        <v>418</v>
       </c>
       <c r="G149">
         <v>49.993825599999994</v>
@@ -36392,16 +36400,16 @@
         <v>0</v>
       </c>
       <c r="C150" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D150" t="s">
+        <v>417</v>
+      </c>
+      <c r="E150" t="s">
+        <v>418</v>
+      </c>
+      <c r="F150" t="s">
         <v>419</v>
-      </c>
-      <c r="E150" t="s">
-        <v>420</v>
-      </c>
-      <c r="F150" t="s">
-        <v>421</v>
       </c>
       <c r="G150">
         <v>36.76497232906253</v>
@@ -36449,16 +36457,16 @@
         <v>0</v>
       </c>
       <c r="C151" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D151" t="s">
+        <v>420</v>
+      </c>
+      <c r="E151" t="s">
+        <v>421</v>
+      </c>
+      <c r="F151" t="s">
         <v>422</v>
-      </c>
-      <c r="E151" t="s">
-        <v>423</v>
-      </c>
-      <c r="F151" t="s">
-        <v>424</v>
       </c>
       <c r="G151">
         <v>31.631675870386633</v>
@@ -36506,16 +36514,16 @@
         <v>0</v>
       </c>
       <c r="C152" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D152" t="s">
+        <v>423</v>
+      </c>
+      <c r="E152" t="s">
+        <v>424</v>
+      </c>
+      <c r="F152" t="s">
         <v>425</v>
-      </c>
-      <c r="E152" t="s">
-        <v>426</v>
-      </c>
-      <c r="F152" t="s">
-        <v>427</v>
       </c>
       <c r="G152">
         <v>25.407543428799851</v>
@@ -36563,16 +36571,16 @@
         <v>0</v>
       </c>
       <c r="C153" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D153" t="s">
+        <v>426</v>
+      </c>
+      <c r="E153" t="s">
+        <v>427</v>
+      </c>
+      <c r="F153" t="s">
         <v>428</v>
-      </c>
-      <c r="E153" t="s">
-        <v>429</v>
-      </c>
-      <c r="F153" t="s">
-        <v>430</v>
       </c>
       <c r="G153">
         <v>18.159999999999986</v>
@@ -36620,16 +36628,16 @@
         <v>0</v>
       </c>
       <c r="C154" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D154" t="s">
+        <v>429</v>
+      </c>
+      <c r="E154" t="s">
+        <v>430</v>
+      </c>
+      <c r="F154" t="s">
         <v>431</v>
-      </c>
-      <c r="E154" t="s">
-        <v>432</v>
-      </c>
-      <c r="F154" t="s">
-        <v>433</v>
       </c>
       <c r="G154">
         <v>1.35</v>
@@ -36677,16 +36685,16 @@
         <v>0</v>
       </c>
       <c r="C155" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D155" t="s">
+        <v>432</v>
+      </c>
+      <c r="E155" t="s">
+        <v>433</v>
+      </c>
+      <c r="F155" t="s">
         <v>434</v>
-      </c>
-      <c r="E155" t="s">
-        <v>435</v>
-      </c>
-      <c r="F155" t="s">
-        <v>436</v>
       </c>
       <c r="G155">
         <v>0.5</v>
@@ -36734,16 +36742,16 @@
         <v>0</v>
       </c>
       <c r="C156" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D156" t="s">
+        <v>435</v>
+      </c>
+      <c r="E156" t="s">
+        <v>436</v>
+      </c>
+      <c r="F156" t="s">
         <v>437</v>
-      </c>
-      <c r="E156" t="s">
-        <v>438</v>
-      </c>
-      <c r="F156" t="s">
-        <v>439</v>
       </c>
       <c r="G156">
         <v>4000</v>
@@ -36791,37 +36799,37 @@
         <v>0</v>
       </c>
       <c r="C157" t="s">
+        <v>453</v>
+      </c>
+      <c r="D157" t="s">
+        <v>454</v>
+      </c>
+      <c r="E157" t="s">
         <v>455</v>
       </c>
-      <c r="D157" t="s">
+      <c r="F157" t="s">
         <v>456</v>
       </c>
-      <c r="E157" t="s">
+      <c r="G157" t="s">
         <v>457</v>
       </c>
-      <c r="F157" t="s">
+      <c r="H157" t="s">
         <v>458</v>
       </c>
-      <c r="G157" t="s">
+      <c r="I157" t="s">
         <v>459</v>
       </c>
-      <c r="H157" t="s">
+      <c r="J157" t="s">
         <v>460</v>
       </c>
-      <c r="I157" t="s">
+      <c r="K157" t="s">
         <v>461</v>
       </c>
-      <c r="J157" t="s">
+      <c r="L157" t="s">
         <v>462</v>
       </c>
-      <c r="K157" t="s">
+      <c r="M157" t="s">
         <v>463</v>
-      </c>
-      <c r="L157" t="s">
-        <v>464</v>
-      </c>
-      <c r="M157" t="s">
-        <v>465</v>
       </c>
       <c r="N157">
         <v>0</v>
@@ -36848,37 +36856,37 @@
         <v>0</v>
       </c>
       <c r="C158" t="s">
+        <v>453</v>
+      </c>
+      <c r="D158" t="s">
+        <v>464</v>
+      </c>
+      <c r="E158" t="s">
         <v>455</v>
       </c>
-      <c r="D158" t="s">
-        <v>466</v>
-      </c>
-      <c r="E158" t="s">
+      <c r="F158" t="s">
+        <v>456</v>
+      </c>
+      <c r="G158" t="s">
         <v>457</v>
       </c>
-      <c r="F158" t="s">
+      <c r="H158" t="s">
         <v>458</v>
       </c>
-      <c r="G158" t="s">
+      <c r="I158" t="s">
         <v>459</v>
       </c>
-      <c r="H158" t="s">
+      <c r="J158" t="s">
         <v>460</v>
       </c>
-      <c r="I158" t="s">
+      <c r="K158" t="s">
         <v>461</v>
       </c>
-      <c r="J158" t="s">
+      <c r="L158" t="s">
         <v>462</v>
       </c>
-      <c r="K158" t="s">
+      <c r="M158" t="s">
         <v>463</v>
-      </c>
-      <c r="L158" t="s">
-        <v>464</v>
-      </c>
-      <c r="M158" t="s">
-        <v>465</v>
       </c>
       <c r="N158">
         <v>0</v>
@@ -36905,37 +36913,37 @@
         <v>0</v>
       </c>
       <c r="C159" t="s">
+        <v>453</v>
+      </c>
+      <c r="D159" t="s">
+        <v>465</v>
+      </c>
+      <c r="E159" t="s">
         <v>455</v>
       </c>
-      <c r="D159" t="s">
+      <c r="F159" t="s">
+        <v>456</v>
+      </c>
+      <c r="G159" t="s">
+        <v>466</v>
+      </c>
+      <c r="H159" t="s">
         <v>467</v>
       </c>
-      <c r="E159" t="s">
-        <v>457</v>
-      </c>
-      <c r="F159" t="s">
-        <v>458</v>
-      </c>
-      <c r="G159" t="s">
-        <v>468</v>
-      </c>
-      <c r="H159" t="s">
-        <v>469</v>
-      </c>
       <c r="I159" t="s">
+        <v>459</v>
+      </c>
+      <c r="J159" t="s">
+        <v>460</v>
+      </c>
+      <c r="K159" t="s">
         <v>461</v>
       </c>
-      <c r="J159" t="s">
+      <c r="L159" t="s">
         <v>462</v>
       </c>
-      <c r="K159" t="s">
+      <c r="M159" t="s">
         <v>463</v>
-      </c>
-      <c r="L159" t="s">
-        <v>464</v>
-      </c>
-      <c r="M159" t="s">
-        <v>465</v>
       </c>
       <c r="N159">
         <v>0</v>
@@ -36962,37 +36970,37 @@
         <v>0</v>
       </c>
       <c r="C160" t="s">
+        <v>453</v>
+      </c>
+      <c r="D160" t="s">
+        <v>468</v>
+      </c>
+      <c r="E160" t="s">
         <v>455</v>
       </c>
-      <c r="D160" t="s">
+      <c r="F160" t="s">
+        <v>456</v>
+      </c>
+      <c r="G160" t="s">
+        <v>469</v>
+      </c>
+      <c r="H160" t="s">
+        <v>467</v>
+      </c>
+      <c r="I160" t="s">
         <v>470</v>
       </c>
-      <c r="E160" t="s">
-        <v>457</v>
-      </c>
-      <c r="F160" t="s">
-        <v>458</v>
-      </c>
-      <c r="G160" t="s">
+      <c r="J160" t="s">
         <v>471</v>
       </c>
-      <c r="H160" t="s">
-        <v>469</v>
-      </c>
-      <c r="I160" t="s">
-        <v>472</v>
-      </c>
-      <c r="J160" t="s">
-        <v>473</v>
-      </c>
       <c r="K160" t="s">
+        <v>461</v>
+      </c>
+      <c r="L160" t="s">
+        <v>462</v>
+      </c>
+      <c r="M160" t="s">
         <v>463</v>
-      </c>
-      <c r="L160" t="s">
-        <v>464</v>
-      </c>
-      <c r="M160" t="s">
-        <v>465</v>
       </c>
       <c r="N160">
         <v>0</v>
@@ -37019,37 +37027,37 @@
         <v>0</v>
       </c>
       <c r="C161" t="s">
+        <v>453</v>
+      </c>
+      <c r="D161" t="s">
+        <v>472</v>
+      </c>
+      <c r="E161" t="s">
         <v>455</v>
       </c>
-      <c r="D161" t="s">
+      <c r="F161" t="s">
+        <v>456</v>
+      </c>
+      <c r="G161" t="s">
+        <v>473</v>
+      </c>
+      <c r="H161" t="s">
         <v>474</v>
       </c>
-      <c r="E161" t="s">
-        <v>457</v>
-      </c>
-      <c r="F161" t="s">
-        <v>458</v>
-      </c>
-      <c r="G161" t="s">
+      <c r="I161" t="s">
+        <v>470</v>
+      </c>
+      <c r="J161" t="s">
+        <v>471</v>
+      </c>
+      <c r="K161" t="s">
         <v>475</v>
       </c>
-      <c r="H161" t="s">
+      <c r="L161" t="s">
         <v>476</v>
       </c>
-      <c r="I161" t="s">
-        <v>472</v>
-      </c>
-      <c r="J161" t="s">
-        <v>473</v>
-      </c>
-      <c r="K161" t="s">
+      <c r="M161" t="s">
         <v>477</v>
-      </c>
-      <c r="L161" t="s">
-        <v>478</v>
-      </c>
-      <c r="M161" t="s">
-        <v>479</v>
       </c>
       <c r="N161">
         <v>0</v>
@@ -37076,37 +37084,37 @@
         <v>0</v>
       </c>
       <c r="C162" t="s">
+        <v>453</v>
+      </c>
+      <c r="D162" t="s">
+        <v>478</v>
+      </c>
+      <c r="E162" t="s">
         <v>455</v>
       </c>
-      <c r="D162" t="s">
+      <c r="F162" t="s">
+        <v>456</v>
+      </c>
+      <c r="G162" t="s">
+        <v>479</v>
+      </c>
+      <c r="H162" t="s">
         <v>480</v>
       </c>
-      <c r="E162" t="s">
-        <v>457</v>
-      </c>
-      <c r="F162" t="s">
-        <v>458</v>
-      </c>
-      <c r="G162" t="s">
+      <c r="I162" t="s">
         <v>481</v>
       </c>
-      <c r="H162" t="s">
+      <c r="J162" t="s">
         <v>482</v>
       </c>
-      <c r="I162" t="s">
+      <c r="K162" t="s">
         <v>483</v>
       </c>
-      <c r="J162" t="s">
+      <c r="L162" t="s">
         <v>484</v>
       </c>
-      <c r="K162" t="s">
+      <c r="M162" t="s">
         <v>485</v>
-      </c>
-      <c r="L162" t="s">
-        <v>486</v>
-      </c>
-      <c r="M162" t="s">
-        <v>487</v>
       </c>
       <c r="N162">
         <v>0</v>
@@ -37133,37 +37141,37 @@
         <v>0</v>
       </c>
       <c r="C163" t="s">
+        <v>453</v>
+      </c>
+      <c r="D163" t="s">
+        <v>486</v>
+      </c>
+      <c r="E163" t="s">
         <v>455</v>
       </c>
-      <c r="D163" t="s">
+      <c r="F163" t="s">
+        <v>456</v>
+      </c>
+      <c r="G163" t="s">
+        <v>487</v>
+      </c>
+      <c r="H163" t="s">
         <v>488</v>
       </c>
-      <c r="E163" t="s">
-        <v>457</v>
-      </c>
-      <c r="F163" t="s">
-        <v>458</v>
-      </c>
-      <c r="G163" t="s">
+      <c r="I163" t="s">
         <v>489</v>
       </c>
-      <c r="H163" t="s">
+      <c r="J163" t="s">
         <v>490</v>
       </c>
-      <c r="I163" t="s">
+      <c r="K163" t="s">
         <v>491</v>
       </c>
-      <c r="J163" t="s">
+      <c r="L163" t="s">
         <v>492</v>
       </c>
-      <c r="K163" t="s">
+      <c r="M163" t="s">
         <v>493</v>
-      </c>
-      <c r="L163" t="s">
-        <v>494</v>
-      </c>
-      <c r="M163" t="s">
-        <v>495</v>
       </c>
       <c r="N163">
         <v>0</v>
@@ -37190,37 +37198,37 @@
         <v>0</v>
       </c>
       <c r="C164" t="s">
+        <v>453</v>
+      </c>
+      <c r="D164" t="s">
+        <v>494</v>
+      </c>
+      <c r="E164" t="s">
         <v>455</v>
       </c>
-      <c r="D164" t="s">
+      <c r="F164" t="s">
+        <v>456</v>
+      </c>
+      <c r="G164" t="s">
+        <v>487</v>
+      </c>
+      <c r="H164" t="s">
+        <v>458</v>
+      </c>
+      <c r="I164" t="s">
+        <v>459</v>
+      </c>
+      <c r="J164" t="s">
+        <v>460</v>
+      </c>
+      <c r="K164" t="s">
+        <v>495</v>
+      </c>
+      <c r="L164" t="s">
         <v>496</v>
       </c>
-      <c r="E164" t="s">
-        <v>457</v>
-      </c>
-      <c r="F164" t="s">
-        <v>458</v>
-      </c>
-      <c r="G164" t="s">
-        <v>489</v>
-      </c>
-      <c r="H164" t="s">
-        <v>460</v>
-      </c>
-      <c r="I164" t="s">
-        <v>461</v>
-      </c>
-      <c r="J164" t="s">
-        <v>462</v>
-      </c>
-      <c r="K164" t="s">
+      <c r="M164" t="s">
         <v>497</v>
-      </c>
-      <c r="L164" t="s">
-        <v>498</v>
-      </c>
-      <c r="M164" t="s">
-        <v>499</v>
       </c>
       <c r="N164">
         <v>0</v>
@@ -37247,16 +37255,16 @@
         <v>0</v>
       </c>
       <c r="C165" t="s">
+        <v>438</v>
+      </c>
+      <c r="D165" t="s">
+        <v>439</v>
+      </c>
+      <c r="E165" t="s">
         <v>440</v>
       </c>
-      <c r="D165" t="s">
+      <c r="F165" t="s">
         <v>441</v>
-      </c>
-      <c r="E165" t="s">
-        <v>442</v>
-      </c>
-      <c r="F165" t="s">
-        <v>443</v>
       </c>
       <c r="G165">
         <v>4</v>
@@ -37304,16 +37312,16 @@
         <v>0</v>
       </c>
       <c r="C166" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D166" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E166" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="F166" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="G166">
         <v>200</v>
@@ -37361,16 +37369,16 @@
         <v>0</v>
       </c>
       <c r="C167" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D167" t="s">
+        <v>444</v>
+      </c>
+      <c r="E167" t="s">
+        <v>445</v>
+      </c>
+      <c r="F167" t="s">
         <v>446</v>
-      </c>
-      <c r="E167" t="s">
-        <v>447</v>
-      </c>
-      <c r="F167" t="s">
-        <v>448</v>
       </c>
       <c r="G167">
         <v>4</v>
@@ -37418,16 +37426,16 @@
         <v>0</v>
       </c>
       <c r="C168" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D168" t="s">
+        <v>447</v>
+      </c>
+      <c r="E168" t="s">
+        <v>448</v>
+      </c>
+      <c r="F168" t="s">
         <v>449</v>
-      </c>
-      <c r="E168" t="s">
-        <v>450</v>
-      </c>
-      <c r="F168" t="s">
-        <v>451</v>
       </c>
       <c r="G168">
         <v>3</v>
@@ -37475,16 +37483,16 @@
         <v>0</v>
       </c>
       <c r="C169" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D169" t="s">
+        <v>450</v>
+      </c>
+      <c r="E169" t="s">
+        <v>451</v>
+      </c>
+      <c r="F169" t="s">
         <v>452</v>
-      </c>
-      <c r="E169" t="s">
-        <v>453</v>
-      </c>
-      <c r="F169" t="s">
-        <v>454</v>
       </c>
       <c r="G169">
         <v>4</v>
@@ -37532,16 +37540,16 @@
         <v>0</v>
       </c>
       <c r="C170" t="s">
+        <v>368</v>
+      </c>
+      <c r="D170" t="s">
+        <v>369</v>
+      </c>
+      <c r="E170" t="s">
         <v>370</v>
       </c>
-      <c r="D170" t="s">
+      <c r="F170" t="s">
         <v>371</v>
-      </c>
-      <c r="E170" t="s">
-        <v>372</v>
-      </c>
-      <c r="F170" t="s">
-        <v>373</v>
       </c>
       <c r="G170">
         <v>0.5</v>
@@ -37589,16 +37597,16 @@
         <v>0</v>
       </c>
       <c r="C171" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D171" t="s">
+        <v>372</v>
+      </c>
+      <c r="E171" t="s">
+        <v>373</v>
+      </c>
+      <c r="F171" t="s">
         <v>374</v>
-      </c>
-      <c r="E171" t="s">
-        <v>375</v>
-      </c>
-      <c r="F171" t="s">
-        <v>376</v>
       </c>
       <c r="G171">
         <v>50</v>
@@ -37646,16 +37654,16 @@
         <v>0</v>
       </c>
       <c r="C172" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D172" t="s">
+        <v>375</v>
+      </c>
+      <c r="E172" t="s">
+        <v>376</v>
+      </c>
+      <c r="F172" t="s">
         <v>377</v>
-      </c>
-      <c r="E172" t="s">
-        <v>378</v>
-      </c>
-      <c r="F172" t="s">
-        <v>379</v>
       </c>
       <c r="G172">
         <v>0</v>
@@ -37703,16 +37711,16 @@
         <v>0</v>
       </c>
       <c r="C173" t="s">
+        <v>378</v>
+      </c>
+      <c r="D173" t="s">
+        <v>379</v>
+      </c>
+      <c r="E173" t="s">
         <v>380</v>
       </c>
-      <c r="D173" t="s">
+      <c r="F173" t="s">
         <v>381</v>
-      </c>
-      <c r="E173" t="s">
-        <v>382</v>
-      </c>
-      <c r="F173" t="s">
-        <v>383</v>
       </c>
       <c r="G173">
         <v>200</v>
@@ -37760,28 +37768,28 @@
         <v>0</v>
       </c>
       <c r="C174" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D174" t="s">
+        <v>382</v>
+      </c>
+      <c r="E174" t="s">
+        <v>383</v>
+      </c>
+      <c r="F174" t="s">
         <v>384</v>
-      </c>
-      <c r="E174" t="s">
-        <v>385</v>
-      </c>
-      <c r="F174" t="s">
-        <v>386</v>
       </c>
       <c r="G174">
         <v>55</v>
       </c>
       <c r="H174" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I174" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="J174" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="K174">
         <v>0</v>
@@ -37817,28 +37825,28 @@
         <v>0</v>
       </c>
       <c r="C175" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D175" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="E175" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F175" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G175">
         <v>25</v>
       </c>
       <c r="H175" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I175">
         <v>2</v>
       </c>
       <c r="J175" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="K175">
         <v>0</v>
@@ -37874,28 +37882,28 @@
         <v>0</v>
       </c>
       <c r="C176" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D176" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="E176" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F176" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G176">
         <v>12</v>
       </c>
       <c r="H176" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I176">
         <v>2.5</v>
       </c>
       <c r="J176" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="K176">
         <v>0</v>
@@ -37931,28 +37939,28 @@
         <v>0</v>
       </c>
       <c r="C177" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D177" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E177" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F177" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G177">
         <v>5.5</v>
       </c>
       <c r="H177" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I177">
         <v>3</v>
       </c>
       <c r="J177" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="K177">
         <v>0</v>
@@ -37988,28 +37996,28 @@
         <v>0</v>
       </c>
       <c r="C178" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D178" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="E178" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F178" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G178">
         <v>1.8</v>
       </c>
       <c r="H178" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I178">
         <v>3.5</v>
       </c>
       <c r="J178" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="K178">
         <v>0</v>
@@ -38045,28 +38053,28 @@
         <v>0</v>
       </c>
       <c r="C179" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D179" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="E179" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F179" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G179">
         <v>0.35</v>
       </c>
       <c r="H179" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I179">
         <v>4</v>
       </c>
       <c r="J179" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="K179">
         <v>0</v>
@@ -38102,28 +38110,28 @@
         <v>0</v>
       </c>
       <c r="C180" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D180" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E180" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F180" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G180">
         <v>0.08</v>
       </c>
       <c r="H180" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I180">
         <v>4.5</v>
       </c>
       <c r="J180" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="K180">
         <v>0</v>
@@ -38159,28 +38167,28 @@
         <v>0</v>
       </c>
       <c r="C181" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D181" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E181" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F181" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="G181">
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="H181" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="I181">
         <v>5</v>
       </c>
       <c r="J181" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="K181">
         <v>0</v>
@@ -38216,16 +38224,16 @@
         <v>0</v>
       </c>
       <c r="C182" t="s">
+        <v>532</v>
+      </c>
+      <c r="D182" t="s">
+        <v>533</v>
+      </c>
+      <c r="E182" t="s">
         <v>534</v>
       </c>
-      <c r="D182" t="s">
+      <c r="F182" t="s">
         <v>535</v>
-      </c>
-      <c r="E182" t="s">
-        <v>536</v>
-      </c>
-      <c r="F182" t="s">
-        <v>537</v>
       </c>
       <c r="G182">
         <v>5</v>
@@ -38273,16 +38281,16 @@
         <v>0</v>
       </c>
       <c r="C183" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D183" t="s">
+        <v>536</v>
+      </c>
+      <c r="E183" t="s">
+        <v>537</v>
+      </c>
+      <c r="F183" t="s">
         <v>538</v>
-      </c>
-      <c r="E183" t="s">
-        <v>539</v>
-      </c>
-      <c r="F183" t="s">
-        <v>540</v>
       </c>
       <c r="G183">
         <v>0</v>
@@ -38330,16 +38338,16 @@
         <v>0</v>
       </c>
       <c r="C184" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D184" t="s">
+        <v>947</v>
+      </c>
+      <c r="E184" t="s">
+        <v>948</v>
+      </c>
+      <c r="F184" t="s">
         <v>949</v>
-      </c>
-      <c r="E184" t="s">
-        <v>950</v>
-      </c>
-      <c r="F184" t="s">
-        <v>951</v>
       </c>
       <c r="G184">
         <v>0.1</v>
@@ -38387,16 +38395,16 @@
         <v>0</v>
       </c>
       <c r="C185" t="s">
+        <v>539</v>
+      </c>
+      <c r="D185" t="s">
+        <v>540</v>
+      </c>
+      <c r="E185" t="s">
         <v>541</v>
       </c>
-      <c r="D185" t="s">
+      <c r="F185" t="s">
         <v>542</v>
-      </c>
-      <c r="E185" t="s">
-        <v>543</v>
-      </c>
-      <c r="F185" t="s">
-        <v>544</v>
       </c>
       <c r="G185">
         <v>5</v>
@@ -38444,16 +38452,16 @@
         <v>0</v>
       </c>
       <c r="C186" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D186" t="s">
+        <v>543</v>
+      </c>
+      <c r="E186" t="s">
+        <v>544</v>
+      </c>
+      <c r="F186" t="s">
         <v>545</v>
-      </c>
-      <c r="E186" t="s">
-        <v>546</v>
-      </c>
-      <c r="F186" t="s">
-        <v>547</v>
       </c>
       <c r="G186">
         <v>55</v>
@@ -38501,16 +38509,16 @@
         <v>0</v>
       </c>
       <c r="C187" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D187" t="s">
+        <v>546</v>
+      </c>
+      <c r="E187" t="s">
+        <v>547</v>
+      </c>
+      <c r="F187" t="s">
         <v>548</v>
-      </c>
-      <c r="E187" t="s">
-        <v>549</v>
-      </c>
-      <c r="F187" t="s">
-        <v>550</v>
       </c>
       <c r="G187">
         <v>5000000</v>
@@ -38558,13 +38566,13 @@
         <v>0</v>
       </c>
       <c r="C188" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D188" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E188" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="F188">
         <v>0</v>
@@ -38615,16 +38623,16 @@
         <v>0</v>
       </c>
       <c r="C189" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D189" t="s">
+        <v>550</v>
+      </c>
+      <c r="E189" t="s">
+        <v>551</v>
+      </c>
+      <c r="F189" t="s">
         <v>552</v>
-      </c>
-      <c r="E189" t="s">
-        <v>553</v>
-      </c>
-      <c r="F189" t="s">
-        <v>554</v>
       </c>
       <c r="G189">
         <v>3</v>
@@ -38672,16 +38680,16 @@
         <v>0</v>
       </c>
       <c r="C190" t="s">
+        <v>539</v>
+      </c>
+      <c r="D190" t="s">
+        <v>559</v>
+      </c>
+      <c r="E190" t="s">
         <v>541</v>
       </c>
-      <c r="D190" t="s">
-        <v>561</v>
-      </c>
-      <c r="E190" t="s">
-        <v>543</v>
-      </c>
       <c r="F190" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="G190">
         <v>3</v>
@@ -38729,16 +38737,16 @@
         <v>0</v>
       </c>
       <c r="C191" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D191" t="s">
+        <v>561</v>
+      </c>
+      <c r="E191" t="s">
+        <v>562</v>
+      </c>
+      <c r="F191" t="s">
         <v>563</v>
-      </c>
-      <c r="E191" t="s">
-        <v>564</v>
-      </c>
-      <c r="F191" t="s">
-        <v>565</v>
       </c>
       <c r="G191">
         <v>50</v>
@@ -38786,16 +38794,16 @@
         <v>0</v>
       </c>
       <c r="C192" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D192" t="s">
+        <v>564</v>
+      </c>
+      <c r="E192" t="s">
+        <v>565</v>
+      </c>
+      <c r="F192" t="s">
         <v>566</v>
-      </c>
-      <c r="E192" t="s">
-        <v>567</v>
-      </c>
-      <c r="F192" t="s">
-        <v>568</v>
       </c>
       <c r="G192">
         <v>1000000</v>
@@ -38843,13 +38851,13 @@
         <v>0</v>
       </c>
       <c r="C193" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D193" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E193" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F193">
         <v>0</v>
@@ -38900,16 +38908,16 @@
         <v>0</v>
       </c>
       <c r="C194" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D194" t="s">
+        <v>569</v>
+      </c>
+      <c r="E194" t="s">
+        <v>570</v>
+      </c>
+      <c r="F194" t="s">
         <v>571</v>
-      </c>
-      <c r="E194" t="s">
-        <v>572</v>
-      </c>
-      <c r="F194" t="s">
-        <v>573</v>
       </c>
       <c r="G194">
         <v>3</v>
@@ -38957,16 +38965,16 @@
         <v>0</v>
       </c>
       <c r="C195" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D195" t="s">
+        <v>572</v>
+      </c>
+      <c r="E195" t="s">
+        <v>573</v>
+      </c>
+      <c r="F195" t="s">
         <v>574</v>
-      </c>
-      <c r="E195" t="s">
-        <v>575</v>
-      </c>
-      <c r="F195" t="s">
-        <v>576</v>
       </c>
       <c r="G195">
         <v>6</v>
@@ -39014,16 +39022,16 @@
         <v>0</v>
       </c>
       <c r="C196" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D196" t="s">
+        <v>915</v>
+      </c>
+      <c r="E196" t="s">
+        <v>916</v>
+      </c>
+      <c r="F196" t="s">
         <v>917</v>
-      </c>
-      <c r="E196" t="s">
-        <v>918</v>
-      </c>
-      <c r="F196" t="s">
-        <v>919</v>
       </c>
       <c r="G196">
         <v>20</v>
@@ -39071,16 +39079,16 @@
         <v>0</v>
       </c>
       <c r="C197" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D197" t="s">
+        <v>918</v>
+      </c>
+      <c r="E197" t="s">
+        <v>919</v>
+      </c>
+      <c r="F197" t="s">
         <v>920</v>
-      </c>
-      <c r="E197" t="s">
-        <v>921</v>
-      </c>
-      <c r="F197" t="s">
-        <v>922</v>
       </c>
       <c r="G197">
         <v>500000000</v>
@@ -39128,16 +39136,16 @@
         <v>0</v>
       </c>
       <c r="C198" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D198" t="s">
+        <v>921</v>
+      </c>
+      <c r="E198" t="s">
+        <v>922</v>
+      </c>
+      <c r="F198" t="s">
         <v>923</v>
-      </c>
-      <c r="E198" t="s">
-        <v>924</v>
-      </c>
-      <c r="F198" t="s">
-        <v>925</v>
       </c>
       <c r="G198">
         <v>13</v>
@@ -39185,16 +39193,16 @@
         <v>0</v>
       </c>
       <c r="C199" t="s">
+        <v>498</v>
+      </c>
+      <c r="D199" t="s">
+        <v>499</v>
+      </c>
+      <c r="E199" t="s">
         <v>500</v>
       </c>
-      <c r="D199" t="s">
+      <c r="F199" t="s">
         <v>501</v>
-      </c>
-      <c r="E199" t="s">
-        <v>502</v>
-      </c>
-      <c r="F199" t="s">
-        <v>503</v>
       </c>
       <c r="G199">
         <v>0</v>
@@ -39242,16 +39250,16 @@
         <v>0</v>
       </c>
       <c r="C200" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D200" t="s">
+        <v>502</v>
+      </c>
+      <c r="E200" t="s">
+        <v>503</v>
+      </c>
+      <c r="F200" t="s">
         <v>504</v>
-      </c>
-      <c r="E200" t="s">
-        <v>505</v>
-      </c>
-      <c r="F200" t="s">
-        <v>506</v>
       </c>
       <c r="G200">
         <v>1.35</v>
@@ -39299,16 +39307,16 @@
         <v>0</v>
       </c>
       <c r="C201" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D201" t="s">
+        <v>505</v>
+      </c>
+      <c r="E201" t="s">
+        <v>506</v>
+      </c>
+      <c r="F201" t="s">
         <v>507</v>
-      </c>
-      <c r="E201" t="s">
-        <v>508</v>
-      </c>
-      <c r="F201" t="s">
-        <v>509</v>
       </c>
       <c r="G201">
         <v>0.05</v>
@@ -39356,16 +39364,16 @@
         <v>0</v>
       </c>
       <c r="C202" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D202" t="s">
+        <v>508</v>
+      </c>
+      <c r="E202" t="s">
+        <v>509</v>
+      </c>
+      <c r="F202" t="s">
         <v>510</v>
-      </c>
-      <c r="E202" t="s">
-        <v>511</v>
-      </c>
-      <c r="F202" t="s">
-        <v>512</v>
       </c>
       <c r="G202">
         <v>2</v>
@@ -39413,16 +39421,16 @@
         <v>0</v>
       </c>
       <c r="C203" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D203" t="s">
+        <v>511</v>
+      </c>
+      <c r="E203" t="s">
+        <v>512</v>
+      </c>
+      <c r="F203" t="s">
         <v>513</v>
-      </c>
-      <c r="E203" t="s">
-        <v>514</v>
-      </c>
-      <c r="F203" t="s">
-        <v>515</v>
       </c>
       <c r="G203">
         <v>0</v>
@@ -39470,16 +39478,16 @@
         <v>0</v>
       </c>
       <c r="C204" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D204" t="s">
+        <v>514</v>
+      </c>
+      <c r="E204" t="s">
+        <v>515</v>
+      </c>
+      <c r="F204" t="s">
         <v>516</v>
-      </c>
-      <c r="E204" t="s">
-        <v>517</v>
-      </c>
-      <c r="F204" t="s">
-        <v>518</v>
       </c>
       <c r="G204">
         <v>5</v>
@@ -39527,16 +39535,16 @@
         <v>0</v>
       </c>
       <c r="C205" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D205" t="s">
+        <v>517</v>
+      </c>
+      <c r="E205" t="s">
+        <v>518</v>
+      </c>
+      <c r="F205" t="s">
         <v>519</v>
-      </c>
-      <c r="E205" t="s">
-        <v>520</v>
-      </c>
-      <c r="F205" t="s">
-        <v>521</v>
       </c>
       <c r="G205">
         <v>8</v>
@@ -39584,16 +39592,16 @@
         <v>0</v>
       </c>
       <c r="C206" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D206" t="s">
+        <v>520</v>
+      </c>
+      <c r="E206" t="s">
+        <v>521</v>
+      </c>
+      <c r="F206" t="s">
         <v>522</v>
-      </c>
-      <c r="E206" t="s">
-        <v>523</v>
-      </c>
-      <c r="F206" t="s">
-        <v>524</v>
       </c>
       <c r="G206">
         <v>1</v>
@@ -39641,16 +39649,16 @@
         <v>0</v>
       </c>
       <c r="C207" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D207" t="s">
+        <v>523</v>
+      </c>
+      <c r="E207" t="s">
+        <v>524</v>
+      </c>
+      <c r="F207" t="s">
         <v>525</v>
-      </c>
-      <c r="E207" t="s">
-        <v>526</v>
-      </c>
-      <c r="F207" t="s">
-        <v>527</v>
       </c>
       <c r="G207">
         <v>0.15</v>
@@ -39698,16 +39706,16 @@
         <v>0</v>
       </c>
       <c r="C208" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D208" t="s">
+        <v>526</v>
+      </c>
+      <c r="E208" t="s">
+        <v>527</v>
+      </c>
+      <c r="F208" t="s">
         <v>528</v>
-      </c>
-      <c r="E208" t="s">
-        <v>529</v>
-      </c>
-      <c r="F208" t="s">
-        <v>530</v>
       </c>
       <c r="G208">
         <v>2</v>
@@ -39755,16 +39763,16 @@
         <v>0</v>
       </c>
       <c r="C209" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D209" t="s">
+        <v>529</v>
+      </c>
+      <c r="E209" t="s">
+        <v>530</v>
+      </c>
+      <c r="F209" t="s">
         <v>531</v>
-      </c>
-      <c r="E209" t="s">
-        <v>532</v>
-      </c>
-      <c r="F209" t="s">
-        <v>533</v>
       </c>
       <c r="G209">
         <v>3</v>
@@ -39812,16 +39820,16 @@
         <v>0</v>
       </c>
       <c r="C210" t="s">
+        <v>604</v>
+      </c>
+      <c r="D210" t="s">
+        <v>605</v>
+      </c>
+      <c r="E210" t="s">
         <v>606</v>
       </c>
-      <c r="D210" t="s">
+      <c r="F210" t="s">
         <v>607</v>
-      </c>
-      <c r="E210" t="s">
-        <v>608</v>
-      </c>
-      <c r="F210" t="s">
-        <v>609</v>
       </c>
       <c r="G210">
         <v>2</v>
@@ -39881,16 +39889,16 @@
         <v>0</v>
       </c>
       <c r="C211" t="s">
+        <v>608</v>
+      </c>
+      <c r="D211" t="s">
+        <v>609</v>
+      </c>
+      <c r="E211" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="F211" t="s">
         <v>610</v>
-      </c>
-      <c r="D211" t="s">
-        <v>611</v>
-      </c>
-      <c r="E211" s="3" t="s">
-        <v>989</v>
-      </c>
-      <c r="F211" t="s">
-        <v>612</v>
       </c>
       <c r="G211">
         <v>10000</v>
@@ -39962,16 +39970,16 @@
         <v>0</v>
       </c>
       <c r="C212" t="s">
+        <v>592</v>
+      </c>
+      <c r="D212" t="s">
+        <v>593</v>
+      </c>
+      <c r="E212" t="s">
         <v>594</v>
       </c>
-      <c r="D212" t="s">
+      <c r="F212" t="s">
         <v>595</v>
-      </c>
-      <c r="E212" t="s">
-        <v>596</v>
-      </c>
-      <c r="F212" t="s">
-        <v>597</v>
       </c>
       <c r="G212">
         <v>5</v>
@@ -40054,16 +40062,16 @@
         <v>0</v>
       </c>
       <c r="C213" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D213" t="s">
+        <v>596</v>
+      </c>
+      <c r="E213" t="s">
+        <v>597</v>
+      </c>
+      <c r="F213" t="s">
         <v>598</v>
-      </c>
-      <c r="E213" t="s">
-        <v>599</v>
-      </c>
-      <c r="F213" t="s">
-        <v>600</v>
       </c>
       <c r="G213">
         <v>0</v>
@@ -40146,16 +40154,16 @@
         <v>0</v>
       </c>
       <c r="C214" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D214" t="s">
+        <v>599</v>
+      </c>
+      <c r="E214" t="s">
+        <v>600</v>
+      </c>
+      <c r="F214" t="s">
         <v>601</v>
-      </c>
-      <c r="E214" t="s">
-        <v>602</v>
-      </c>
-      <c r="F214" t="s">
-        <v>603</v>
       </c>
       <c r="G214">
         <v>0</v>
@@ -40238,16 +40246,16 @@
         <v>0</v>
       </c>
       <c r="C215" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="D215" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E215" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="F215" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="G215">
         <v>0</v>
@@ -40330,16 +40338,16 @@
         <v>0</v>
       </c>
       <c r="C216" t="s">
+        <v>553</v>
+      </c>
+      <c r="D216" t="s">
+        <v>554</v>
+      </c>
+      <c r="E216" t="s">
         <v>555</v>
       </c>
-      <c r="D216" t="s">
+      <c r="F216" t="s">
         <v>556</v>
-      </c>
-      <c r="E216" t="s">
-        <v>557</v>
-      </c>
-      <c r="F216" t="s">
-        <v>558</v>
       </c>
       <c r="G216">
         <v>27</v>
@@ -40422,16 +40430,16 @@
         <v>0</v>
       </c>
       <c r="C217" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D217" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E217" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F217" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="G217">
         <v>36</v>
@@ -40514,13 +40522,13 @@
         <v>0</v>
       </c>
       <c r="C218" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D218" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E218" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="F218">
         <v>0</v>
@@ -40606,16 +40614,16 @@
         <v>0</v>
       </c>
       <c r="C219" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D219" t="s">
+        <v>586</v>
+      </c>
+      <c r="E219" t="s">
+        <v>587</v>
+      </c>
+      <c r="F219" t="s">
         <v>588</v>
-      </c>
-      <c r="E219" t="s">
-        <v>589</v>
-      </c>
-      <c r="F219" t="s">
-        <v>590</v>
       </c>
       <c r="G219">
         <v>9</v>
@@ -40698,16 +40706,16 @@
         <v>0</v>
       </c>
       <c r="C220" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D220" t="s">
+        <v>589</v>
+      </c>
+      <c r="E220" t="s">
+        <v>590</v>
+      </c>
+      <c r="F220" t="s">
         <v>591</v>
-      </c>
-      <c r="E220" t="s">
-        <v>592</v>
-      </c>
-      <c r="F220" t="s">
-        <v>593</v>
       </c>
       <c r="G220">
         <v>1</v>
@@ -40790,16 +40798,16 @@
         <v>0</v>
       </c>
       <c r="C221" t="s">
+        <v>611</v>
+      </c>
+      <c r="D221" t="s">
+        <v>612</v>
+      </c>
+      <c r="E221" t="s">
         <v>613</v>
       </c>
-      <c r="D221" t="s">
+      <c r="F221" t="s">
         <v>614</v>
-      </c>
-      <c r="E221" t="s">
-        <v>615</v>
-      </c>
-      <c r="F221" t="s">
-        <v>616</v>
       </c>
       <c r="G221">
         <v>20000</v>
@@ -40882,13 +40890,13 @@
         <v>0</v>
       </c>
       <c r="C222" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D222" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E222" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="F222">
         <v>0</v>
@@ -40974,16 +40982,16 @@
         <v>0</v>
       </c>
       <c r="C223" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D223" t="s">
+        <v>617</v>
+      </c>
+      <c r="E223" t="s">
+        <v>618</v>
+      </c>
+      <c r="F223" t="s">
         <v>619</v>
-      </c>
-      <c r="E223" t="s">
-        <v>620</v>
-      </c>
-      <c r="F223" t="s">
-        <v>621</v>
       </c>
       <c r="G223">
         <v>100</v>
@@ -41066,16 +41074,16 @@
         <v>0</v>
       </c>
       <c r="C224" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D224" t="s">
+        <v>620</v>
+      </c>
+      <c r="E224" t="s">
+        <v>621</v>
+      </c>
+      <c r="F224" t="s">
         <v>622</v>
-      </c>
-      <c r="E224" t="s">
-        <v>623</v>
-      </c>
-      <c r="F224" t="s">
-        <v>624</v>
       </c>
       <c r="G224">
         <v>10000</v>
@@ -41158,13 +41166,13 @@
         <v>0</v>
       </c>
       <c r="C225" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="D225" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E225" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="F225">
         <v>0</v>
@@ -41250,16 +41258,16 @@
         <v>0</v>
       </c>
       <c r="C226" t="s">
+        <v>575</v>
+      </c>
+      <c r="D226" t="s">
+        <v>576</v>
+      </c>
+      <c r="E226" t="s">
         <v>577</v>
       </c>
-      <c r="D226" t="s">
+      <c r="F226" t="s">
         <v>578</v>
-      </c>
-      <c r="E226" t="s">
-        <v>579</v>
-      </c>
-      <c r="F226" t="s">
-        <v>580</v>
       </c>
       <c r="G226">
         <v>30</v>
@@ -41342,13 +41350,13 @@
         <v>0</v>
       </c>
       <c r="C227" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D227" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E227" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="F227">
         <v>0</v>
@@ -41434,13 +41442,13 @@
         <v>0</v>
       </c>
       <c r="C228" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D228" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E228" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="F228">
         <v>0</v>
@@ -41526,16 +41534,16 @@
         <v>0</v>
       </c>
       <c r="C229" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="D229" t="s">
+        <v>582</v>
+      </c>
+      <c r="E229" t="s">
+        <v>583</v>
+      </c>
+      <c r="F229" t="s">
         <v>584</v>
-      </c>
-      <c r="E229" t="s">
-        <v>585</v>
-      </c>
-      <c r="F229" t="s">
-        <v>586</v>
       </c>
       <c r="G229">
         <v>0</v>
@@ -41618,16 +41626,16 @@
         <v>0</v>
       </c>
       <c r="C230" t="s">
+        <v>625</v>
+      </c>
+      <c r="D230" t="s">
+        <v>626</v>
+      </c>
+      <c r="E230" t="s">
         <v>627</v>
       </c>
-      <c r="D230" t="s">
+      <c r="F230" t="s">
         <v>628</v>
-      </c>
-      <c r="E230" t="s">
-        <v>629</v>
-      </c>
-      <c r="F230" t="s">
-        <v>630</v>
       </c>
       <c r="G230">
         <v>0.2</v>
@@ -41710,16 +41718,16 @@
         <v>0</v>
       </c>
       <c r="C231" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D231" t="s">
+        <v>629</v>
+      </c>
+      <c r="E231" t="s">
+        <v>630</v>
+      </c>
+      <c r="F231" t="s">
         <v>631</v>
-      </c>
-      <c r="E231" t="s">
-        <v>632</v>
-      </c>
-      <c r="F231" t="s">
-        <v>633</v>
       </c>
       <c r="G231">
         <v>2</v>
@@ -41802,16 +41810,16 @@
         <v>0</v>
       </c>
       <c r="C232" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D232" t="s">
+        <v>632</v>
+      </c>
+      <c r="E232" t="s">
+        <v>633</v>
+      </c>
+      <c r="F232" t="s">
         <v>634</v>
-      </c>
-      <c r="E232" t="s">
-        <v>635</v>
-      </c>
-      <c r="F232" t="s">
-        <v>636</v>
       </c>
       <c r="G232">
         <v>3</v>
@@ -41863,16 +41871,16 @@
         <v>0</v>
       </c>
       <c r="C233" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D233" t="s">
+        <v>635</v>
+      </c>
+      <c r="E233" t="s">
+        <v>636</v>
+      </c>
+      <c r="F233" t="s">
         <v>637</v>
-      </c>
-      <c r="E233" t="s">
-        <v>638</v>
-      </c>
-      <c r="F233" t="s">
-        <v>639</v>
       </c>
       <c r="G233">
         <v>3</v>
@@ -41920,16 +41928,16 @@
         <v>0</v>
       </c>
       <c r="C234" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D234" t="s">
+        <v>638</v>
+      </c>
+      <c r="E234" t="s">
+        <v>639</v>
+      </c>
+      <c r="F234" t="s">
         <v>640</v>
-      </c>
-      <c r="E234" t="s">
-        <v>641</v>
-      </c>
-      <c r="F234" t="s">
-        <v>642</v>
       </c>
       <c r="G234">
         <v>100</v>
@@ -41977,16 +41985,16 @@
         <v>0</v>
       </c>
       <c r="C235" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D235" t="s">
+        <v>641</v>
+      </c>
+      <c r="E235" t="s">
+        <v>642</v>
+      </c>
+      <c r="F235" t="s">
         <v>643</v>
-      </c>
-      <c r="E235" t="s">
-        <v>644</v>
-      </c>
-      <c r="F235" t="s">
-        <v>645</v>
       </c>
       <c r="G235">
         <v>9</v>
@@ -42034,16 +42042,16 @@
         <v>0</v>
       </c>
       <c r="C236" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D236" t="s">
+        <v>644</v>
+      </c>
+      <c r="E236" t="s">
+        <v>645</v>
+      </c>
+      <c r="F236" t="s">
         <v>646</v>
-      </c>
-      <c r="E236" t="s">
-        <v>647</v>
-      </c>
-      <c r="F236" t="s">
-        <v>648</v>
       </c>
       <c r="G236">
         <v>0.7</v>
@@ -42091,16 +42099,16 @@
         <v>0</v>
       </c>
       <c r="C237" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D237" t="s">
+        <v>647</v>
+      </c>
+      <c r="E237" t="s">
+        <v>648</v>
+      </c>
+      <c r="F237" t="s">
         <v>649</v>
-      </c>
-      <c r="E237" t="s">
-        <v>650</v>
-      </c>
-      <c r="F237" t="s">
-        <v>651</v>
       </c>
       <c r="G237">
         <v>0.7</v>
@@ -42148,16 +42156,16 @@
         <v>0</v>
       </c>
       <c r="C238" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D238" t="s">
+        <v>650</v>
+      </c>
+      <c r="E238" t="s">
+        <v>651</v>
+      </c>
+      <c r="F238" t="s">
         <v>652</v>
-      </c>
-      <c r="E238" t="s">
-        <v>653</v>
-      </c>
-      <c r="F238" t="s">
-        <v>654</v>
       </c>
       <c r="G238">
         <v>10</v>
@@ -42205,16 +42213,16 @@
         <v>0</v>
       </c>
       <c r="C239" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="D239" t="s">
+        <v>653</v>
+      </c>
+      <c r="E239" t="s">
+        <v>654</v>
+      </c>
+      <c r="F239" t="s">
         <v>655</v>
-      </c>
-      <c r="E239" t="s">
-        <v>656</v>
-      </c>
-      <c r="F239" t="s">
-        <v>657</v>
       </c>
       <c r="G239">
         <v>0</v>
@@ -42262,16 +42270,16 @@
         <v>0</v>
       </c>
       <c r="C240" t="s">
+        <v>656</v>
+      </c>
+      <c r="D240" t="s">
+        <v>657</v>
+      </c>
+      <c r="E240" t="s">
         <v>658</v>
       </c>
-      <c r="D240" t="s">
+      <c r="F240" t="s">
         <v>659</v>
-      </c>
-      <c r="E240" t="s">
-        <v>660</v>
-      </c>
-      <c r="F240" t="s">
-        <v>661</v>
       </c>
       <c r="G240">
         <v>100000</v>
@@ -42319,16 +42327,16 @@
         <v>0</v>
       </c>
       <c r="C241" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D241" t="s">
+        <v>660</v>
+      </c>
+      <c r="E241" t="s">
+        <v>661</v>
+      </c>
+      <c r="F241" t="s">
         <v>662</v>
-      </c>
-      <c r="E241" t="s">
-        <v>663</v>
-      </c>
-      <c r="F241" t="s">
-        <v>664</v>
       </c>
       <c r="G241">
         <v>5000</v>
@@ -42376,13 +42384,13 @@
         <v>0</v>
       </c>
       <c r="C242" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D242" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="E242" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="F242">
         <v>0</v>
@@ -42433,16 +42441,16 @@
         <v>0</v>
       </c>
       <c r="C243" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D243" t="s">
+        <v>665</v>
+      </c>
+      <c r="E243" t="s">
+        <v>666</v>
+      </c>
+      <c r="F243" t="s">
         <v>667</v>
-      </c>
-      <c r="E243" t="s">
-        <v>668</v>
-      </c>
-      <c r="F243" t="s">
-        <v>669</v>
       </c>
       <c r="G243">
         <v>10000</v>
@@ -42490,28 +42498,28 @@
         <v>0</v>
       </c>
       <c r="C244" t="s">
+        <v>739</v>
+      </c>
+      <c r="D244" t="s">
+        <v>669</v>
+      </c>
+      <c r="E244" t="s">
+        <v>740</v>
+      </c>
+      <c r="F244" t="s">
         <v>741</v>
       </c>
-      <c r="D244" t="s">
-        <v>671</v>
-      </c>
-      <c r="E244" t="s">
+      <c r="G244" t="s">
         <v>742</v>
       </c>
-      <c r="F244" t="s">
+      <c r="H244" t="s">
         <v>743</v>
       </c>
-      <c r="G244" t="s">
+      <c r="I244" t="s">
         <v>744</v>
       </c>
-      <c r="H244" t="s">
+      <c r="J244" t="s">
         <v>745</v>
-      </c>
-      <c r="I244" t="s">
-        <v>746</v>
-      </c>
-      <c r="J244" t="s">
-        <v>747</v>
       </c>
       <c r="K244">
         <v>0</v>
@@ -42547,28 +42555,28 @@
         <v>0</v>
       </c>
       <c r="C245" t="s">
+        <v>739</v>
+      </c>
+      <c r="D245" t="s">
+        <v>674</v>
+      </c>
+      <c r="E245" t="s">
+        <v>740</v>
+      </c>
+      <c r="F245" t="s">
         <v>741</v>
       </c>
-      <c r="D245" t="s">
-        <v>676</v>
-      </c>
-      <c r="E245" t="s">
-        <v>742</v>
-      </c>
-      <c r="F245" t="s">
+      <c r="G245" t="s">
+        <v>746</v>
+      </c>
+      <c r="H245" t="s">
         <v>743</v>
       </c>
-      <c r="G245" t="s">
+      <c r="I245" t="s">
+        <v>747</v>
+      </c>
+      <c r="J245" t="s">
         <v>748</v>
-      </c>
-      <c r="H245" t="s">
-        <v>745</v>
-      </c>
-      <c r="I245" t="s">
-        <v>749</v>
-      </c>
-      <c r="J245" t="s">
-        <v>750</v>
       </c>
       <c r="K245">
         <v>0</v>
@@ -42604,28 +42612,28 @@
         <v>0</v>
       </c>
       <c r="C246" t="s">
+        <v>739</v>
+      </c>
+      <c r="D246" t="s">
+        <v>677</v>
+      </c>
+      <c r="E246" t="s">
+        <v>740</v>
+      </c>
+      <c r="F246" t="s">
         <v>741</v>
       </c>
-      <c r="D246" t="s">
-        <v>679</v>
-      </c>
-      <c r="E246" t="s">
-        <v>742</v>
-      </c>
-      <c r="F246" t="s">
+      <c r="G246" t="s">
+        <v>749</v>
+      </c>
+      <c r="H246" t="s">
         <v>743</v>
       </c>
-      <c r="G246" t="s">
+      <c r="I246" t="s">
+        <v>750</v>
+      </c>
+      <c r="J246" t="s">
         <v>751</v>
-      </c>
-      <c r="H246" t="s">
-        <v>745</v>
-      </c>
-      <c r="I246" t="s">
-        <v>752</v>
-      </c>
-      <c r="J246" t="s">
-        <v>753</v>
       </c>
       <c r="K246">
         <v>0</v>
@@ -42661,31 +42669,31 @@
         <v>0</v>
       </c>
       <c r="C247" t="s">
+        <v>739</v>
+      </c>
+      <c r="D247" t="s">
+        <v>680</v>
+      </c>
+      <c r="E247" t="s">
+        <v>740</v>
+      </c>
+      <c r="F247" t="s">
         <v>741</v>
       </c>
-      <c r="D247" t="s">
-        <v>682</v>
-      </c>
-      <c r="E247" t="s">
-        <v>742</v>
-      </c>
-      <c r="F247" t="s">
+      <c r="G247" t="s">
+        <v>752</v>
+      </c>
+      <c r="H247" t="s">
         <v>743</v>
       </c>
-      <c r="G247" t="s">
-        <v>754</v>
-      </c>
-      <c r="H247" t="s">
-        <v>745</v>
-      </c>
       <c r="I247" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="J247" t="s">
+        <v>751</v>
+      </c>
+      <c r="K247" t="s">
         <v>753</v>
-      </c>
-      <c r="K247" t="s">
-        <v>755</v>
       </c>
       <c r="L247">
         <v>0</v>
@@ -42718,31 +42726,31 @@
         <v>0</v>
       </c>
       <c r="C248" t="s">
+        <v>739</v>
+      </c>
+      <c r="D248" t="s">
+        <v>683</v>
+      </c>
+      <c r="E248" t="s">
+        <v>740</v>
+      </c>
+      <c r="F248" t="s">
         <v>741</v>
       </c>
-      <c r="D248" t="s">
-        <v>685</v>
-      </c>
-      <c r="E248" t="s">
-        <v>742</v>
-      </c>
-      <c r="F248" t="s">
+      <c r="G248" t="s">
+        <v>754</v>
+      </c>
+      <c r="H248" t="s">
         <v>743</v>
       </c>
-      <c r="G248" t="s">
+      <c r="I248" t="s">
+        <v>750</v>
+      </c>
+      <c r="J248" t="s">
+        <v>755</v>
+      </c>
+      <c r="K248" t="s">
         <v>756</v>
-      </c>
-      <c r="H248" t="s">
-        <v>745</v>
-      </c>
-      <c r="I248" t="s">
-        <v>752</v>
-      </c>
-      <c r="J248" t="s">
-        <v>757</v>
-      </c>
-      <c r="K248" t="s">
-        <v>758</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -42775,31 +42783,31 @@
         <v>0</v>
       </c>
       <c r="C249" t="s">
+        <v>739</v>
+      </c>
+      <c r="D249" t="s">
+        <v>686</v>
+      </c>
+      <c r="E249" t="s">
+        <v>740</v>
+      </c>
+      <c r="F249" t="s">
         <v>741</v>
       </c>
-      <c r="D249" t="s">
-        <v>688</v>
-      </c>
-      <c r="E249" t="s">
-        <v>742</v>
-      </c>
-      <c r="F249" t="s">
+      <c r="G249" t="s">
+        <v>757</v>
+      </c>
+      <c r="H249" t="s">
         <v>743</v>
       </c>
-      <c r="G249" t="s">
+      <c r="I249" t="s">
+        <v>750</v>
+      </c>
+      <c r="J249" t="s">
+        <v>758</v>
+      </c>
+      <c r="K249" t="s">
         <v>759</v>
-      </c>
-      <c r="H249" t="s">
-        <v>745</v>
-      </c>
-      <c r="I249" t="s">
-        <v>752</v>
-      </c>
-      <c r="J249" t="s">
-        <v>760</v>
-      </c>
-      <c r="K249" t="s">
-        <v>761</v>
       </c>
       <c r="L249">
         <v>0</v>
@@ -42832,31 +42840,31 @@
         <v>0</v>
       </c>
       <c r="C250" t="s">
+        <v>739</v>
+      </c>
+      <c r="D250" t="s">
+        <v>689</v>
+      </c>
+      <c r="E250" t="s">
+        <v>740</v>
+      </c>
+      <c r="F250" t="s">
         <v>741</v>
       </c>
-      <c r="D250" t="s">
-        <v>691</v>
-      </c>
-      <c r="E250" t="s">
-        <v>742</v>
-      </c>
-      <c r="F250" t="s">
+      <c r="G250" t="s">
+        <v>760</v>
+      </c>
+      <c r="H250" t="s">
         <v>743</v>
       </c>
-      <c r="G250" t="s">
+      <c r="I250" t="s">
+        <v>761</v>
+      </c>
+      <c r="J250" t="s">
         <v>762</v>
       </c>
-      <c r="H250" t="s">
-        <v>745</v>
-      </c>
-      <c r="I250" t="s">
+      <c r="K250" t="s">
         <v>763</v>
-      </c>
-      <c r="J250" t="s">
-        <v>764</v>
-      </c>
-      <c r="K250" t="s">
-        <v>765</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -42889,31 +42897,31 @@
         <v>0</v>
       </c>
       <c r="C251" t="s">
+        <v>739</v>
+      </c>
+      <c r="D251" t="s">
+        <v>694</v>
+      </c>
+      <c r="E251" t="s">
+        <v>740</v>
+      </c>
+      <c r="F251" t="s">
         <v>741</v>
       </c>
-      <c r="D251" t="s">
-        <v>696</v>
-      </c>
-      <c r="E251" t="s">
-        <v>742</v>
-      </c>
-      <c r="F251" t="s">
+      <c r="G251" t="s">
+        <v>764</v>
+      </c>
+      <c r="H251" t="s">
         <v>743</v>
       </c>
-      <c r="G251" t="s">
+      <c r="I251" t="s">
+        <v>765</v>
+      </c>
+      <c r="J251" t="s">
         <v>766</v>
       </c>
-      <c r="H251" t="s">
-        <v>745</v>
-      </c>
-      <c r="I251" t="s">
+      <c r="K251" t="s">
         <v>767</v>
-      </c>
-      <c r="J251" t="s">
-        <v>768</v>
-      </c>
-      <c r="K251" t="s">
-        <v>769</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -42946,31 +42954,31 @@
         <v>0</v>
       </c>
       <c r="C252" t="s">
+        <v>739</v>
+      </c>
+      <c r="D252" t="s">
+        <v>696</v>
+      </c>
+      <c r="E252" t="s">
+        <v>740</v>
+      </c>
+      <c r="F252" t="s">
         <v>741</v>
       </c>
-      <c r="D252" t="s">
-        <v>698</v>
-      </c>
-      <c r="E252" t="s">
-        <v>742</v>
-      </c>
-      <c r="F252" t="s">
+      <c r="G252" t="s">
+        <v>768</v>
+      </c>
+      <c r="H252" t="s">
         <v>743</v>
       </c>
-      <c r="G252" t="s">
+      <c r="I252" t="s">
+        <v>769</v>
+      </c>
+      <c r="J252" t="s">
         <v>770</v>
       </c>
-      <c r="H252" t="s">
-        <v>745</v>
-      </c>
-      <c r="I252" t="s">
+      <c r="K252" t="s">
         <v>771</v>
-      </c>
-      <c r="J252" t="s">
-        <v>772</v>
-      </c>
-      <c r="K252" t="s">
-        <v>773</v>
       </c>
       <c r="L252">
         <v>0</v>
@@ -43003,34 +43011,34 @@
         <v>0</v>
       </c>
       <c r="C253" t="s">
+        <v>739</v>
+      </c>
+      <c r="D253" t="s">
+        <v>700</v>
+      </c>
+      <c r="E253" t="s">
+        <v>740</v>
+      </c>
+      <c r="F253" t="s">
         <v>741</v>
       </c>
-      <c r="D253" t="s">
-        <v>702</v>
-      </c>
-      <c r="E253" t="s">
-        <v>742</v>
-      </c>
-      <c r="F253" t="s">
+      <c r="G253" t="s">
+        <v>772</v>
+      </c>
+      <c r="H253" t="s">
         <v>743</v>
       </c>
-      <c r="G253" t="s">
+      <c r="I253" t="s">
+        <v>769</v>
+      </c>
+      <c r="J253" t="s">
+        <v>770</v>
+      </c>
+      <c r="K253" t="s">
+        <v>773</v>
+      </c>
+      <c r="L253" t="s">
         <v>774</v>
-      </c>
-      <c r="H253" t="s">
-        <v>745</v>
-      </c>
-      <c r="I253" t="s">
-        <v>771</v>
-      </c>
-      <c r="J253" t="s">
-        <v>772</v>
-      </c>
-      <c r="K253" t="s">
-        <v>775</v>
-      </c>
-      <c r="L253" t="s">
-        <v>776</v>
       </c>
       <c r="M253">
         <v>0</v>
@@ -43060,34 +43068,34 @@
         <v>0</v>
       </c>
       <c r="C254" t="s">
+        <v>739</v>
+      </c>
+      <c r="D254" t="s">
+        <v>704</v>
+      </c>
+      <c r="E254" t="s">
+        <v>740</v>
+      </c>
+      <c r="F254" t="s">
         <v>741</v>
       </c>
-      <c r="D254" t="s">
-        <v>706</v>
-      </c>
-      <c r="E254" t="s">
-        <v>742</v>
-      </c>
-      <c r="F254" t="s">
+      <c r="G254" t="s">
+        <v>775</v>
+      </c>
+      <c r="H254" t="s">
         <v>743</v>
       </c>
-      <c r="G254" t="s">
+      <c r="I254" t="s">
+        <v>769</v>
+      </c>
+      <c r="J254" t="s">
+        <v>770</v>
+      </c>
+      <c r="K254" t="s">
+        <v>776</v>
+      </c>
+      <c r="L254" t="s">
         <v>777</v>
-      </c>
-      <c r="H254" t="s">
-        <v>745</v>
-      </c>
-      <c r="I254" t="s">
-        <v>771</v>
-      </c>
-      <c r="J254" t="s">
-        <v>772</v>
-      </c>
-      <c r="K254" t="s">
-        <v>778</v>
-      </c>
-      <c r="L254" t="s">
-        <v>779</v>
       </c>
       <c r="M254">
         <v>0</v>
@@ -43117,34 +43125,34 @@
         <v>0</v>
       </c>
       <c r="C255" t="s">
+        <v>739</v>
+      </c>
+      <c r="D255" t="s">
+        <v>708</v>
+      </c>
+      <c r="E255" t="s">
+        <v>740</v>
+      </c>
+      <c r="F255" t="s">
         <v>741</v>
       </c>
-      <c r="D255" t="s">
-        <v>710</v>
-      </c>
-      <c r="E255" t="s">
-        <v>742</v>
-      </c>
-      <c r="F255" t="s">
+      <c r="G255" t="s">
+        <v>778</v>
+      </c>
+      <c r="H255" t="s">
         <v>743</v>
       </c>
-      <c r="G255" t="s">
+      <c r="I255" t="s">
+        <v>779</v>
+      </c>
+      <c r="J255" t="s">
         <v>780</v>
       </c>
-      <c r="H255" t="s">
-        <v>745</v>
-      </c>
-      <c r="I255" t="s">
+      <c r="K255" t="s">
         <v>781</v>
       </c>
-      <c r="J255" t="s">
+      <c r="L255" t="s">
         <v>782</v>
-      </c>
-      <c r="K255" t="s">
-        <v>783</v>
-      </c>
-      <c r="L255" t="s">
-        <v>784</v>
       </c>
       <c r="M255">
         <v>0</v>
@@ -43174,34 +43182,34 @@
         <v>0</v>
       </c>
       <c r="C256" t="s">
+        <v>739</v>
+      </c>
+      <c r="D256" t="s">
+        <v>712</v>
+      </c>
+      <c r="E256" t="s">
+        <v>740</v>
+      </c>
+      <c r="F256" t="s">
         <v>741</v>
       </c>
-      <c r="D256" t="s">
-        <v>714</v>
-      </c>
-      <c r="E256" t="s">
-        <v>742</v>
-      </c>
-      <c r="F256" t="s">
+      <c r="G256" t="s">
+        <v>783</v>
+      </c>
+      <c r="H256" t="s">
         <v>743</v>
       </c>
-      <c r="G256" t="s">
-        <v>785</v>
-      </c>
-      <c r="H256" t="s">
-        <v>745</v>
-      </c>
       <c r="I256" t="s">
+        <v>779</v>
+      </c>
+      <c r="J256" t="s">
+        <v>780</v>
+      </c>
+      <c r="K256" t="s">
         <v>781</v>
       </c>
-      <c r="J256" t="s">
-        <v>782</v>
-      </c>
-      <c r="K256" t="s">
-        <v>783</v>
-      </c>
       <c r="L256" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="M256">
         <v>0</v>
@@ -43231,34 +43239,34 @@
         <v>0</v>
       </c>
       <c r="C257" t="s">
+        <v>739</v>
+      </c>
+      <c r="D257" t="s">
+        <v>716</v>
+      </c>
+      <c r="E257" t="s">
+        <v>740</v>
+      </c>
+      <c r="F257" t="s">
         <v>741</v>
       </c>
-      <c r="D257" t="s">
-        <v>718</v>
-      </c>
-      <c r="E257" t="s">
-        <v>742</v>
-      </c>
-      <c r="F257" t="s">
+      <c r="G257" t="s">
+        <v>785</v>
+      </c>
+      <c r="H257" t="s">
         <v>743</v>
       </c>
-      <c r="G257" t="s">
-        <v>787</v>
-      </c>
-      <c r="H257" t="s">
-        <v>745</v>
-      </c>
       <c r="I257" t="s">
+        <v>779</v>
+      </c>
+      <c r="J257" t="s">
+        <v>780</v>
+      </c>
+      <c r="K257" t="s">
         <v>781</v>
       </c>
-      <c r="J257" t="s">
-        <v>782</v>
-      </c>
-      <c r="K257" t="s">
-        <v>783</v>
-      </c>
       <c r="L257" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="M257">
         <v>0</v>
@@ -43288,37 +43296,37 @@
         <v>0</v>
       </c>
       <c r="C258" t="s">
+        <v>739</v>
+      </c>
+      <c r="D258" t="s">
+        <v>720</v>
+      </c>
+      <c r="E258" t="s">
+        <v>740</v>
+      </c>
+      <c r="F258" t="s">
         <v>741</v>
       </c>
-      <c r="D258" t="s">
-        <v>722</v>
-      </c>
-      <c r="E258" t="s">
-        <v>742</v>
-      </c>
-      <c r="F258" t="s">
+      <c r="G258" t="s">
+        <v>787</v>
+      </c>
+      <c r="H258" t="s">
         <v>743</v>
       </c>
-      <c r="G258" t="s">
+      <c r="I258" t="s">
+        <v>779</v>
+      </c>
+      <c r="J258" t="s">
+        <v>788</v>
+      </c>
+      <c r="K258" t="s">
         <v>789</v>
       </c>
-      <c r="H258" t="s">
-        <v>745</v>
-      </c>
-      <c r="I258" t="s">
-        <v>781</v>
-      </c>
-      <c r="J258" t="s">
+      <c r="L258" t="s">
+        <v>782</v>
+      </c>
+      <c r="M258" t="s">
         <v>790</v>
-      </c>
-      <c r="K258" t="s">
-        <v>791</v>
-      </c>
-      <c r="L258" t="s">
-        <v>784</v>
-      </c>
-      <c r="M258" t="s">
-        <v>792</v>
       </c>
       <c r="N258">
         <v>0</v>
@@ -43345,37 +43353,37 @@
         <v>0</v>
       </c>
       <c r="C259" t="s">
+        <v>739</v>
+      </c>
+      <c r="D259" t="s">
+        <v>724</v>
+      </c>
+      <c r="E259" t="s">
+        <v>740</v>
+      </c>
+      <c r="F259" t="s">
         <v>741</v>
       </c>
-      <c r="D259" t="s">
-        <v>726</v>
-      </c>
-      <c r="E259" t="s">
-        <v>742</v>
-      </c>
-      <c r="F259" t="s">
+      <c r="G259" t="s">
+        <v>791</v>
+      </c>
+      <c r="H259" t="s">
         <v>743</v>
       </c>
-      <c r="G259" t="s">
-        <v>793</v>
-      </c>
-      <c r="H259" t="s">
-        <v>745</v>
-      </c>
       <c r="I259" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="J259" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="K259" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="L259" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="M259" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="N259">
         <v>0</v>
@@ -43402,37 +43410,37 @@
         <v>0</v>
       </c>
       <c r="C260" t="s">
+        <v>739</v>
+      </c>
+      <c r="D260" t="s">
+        <v>728</v>
+      </c>
+      <c r="E260" t="s">
+        <v>740</v>
+      </c>
+      <c r="F260" t="s">
         <v>741</v>
       </c>
-      <c r="D260" t="s">
-        <v>730</v>
-      </c>
-      <c r="E260" t="s">
-        <v>742</v>
-      </c>
-      <c r="F260" t="s">
+      <c r="G260" t="s">
+        <v>793</v>
+      </c>
+      <c r="H260" t="s">
         <v>743</v>
       </c>
-      <c r="G260" t="s">
-        <v>795</v>
-      </c>
-      <c r="H260" t="s">
-        <v>745</v>
-      </c>
       <c r="I260" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="J260" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="K260" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="L260" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="M260" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="N260">
         <v>0</v>
@@ -43459,40 +43467,40 @@
         <v>0</v>
       </c>
       <c r="C261" t="s">
+        <v>739</v>
+      </c>
+      <c r="D261" t="s">
+        <v>732</v>
+      </c>
+      <c r="E261" t="s">
+        <v>740</v>
+      </c>
+      <c r="F261" t="s">
         <v>741</v>
       </c>
-      <c r="D261" t="s">
-        <v>734</v>
-      </c>
-      <c r="E261" t="s">
-        <v>742</v>
-      </c>
-      <c r="F261" t="s">
+      <c r="G261" t="s">
+        <v>795</v>
+      </c>
+      <c r="H261" t="s">
         <v>743</v>
       </c>
-      <c r="G261" t="s">
-        <v>797</v>
-      </c>
-      <c r="H261" t="s">
-        <v>745</v>
-      </c>
       <c r="I261" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="J261" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="K261" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="L261" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="M261" t="s">
+        <v>794</v>
+      </c>
+      <c r="N261" t="s">
         <v>796</v>
-      </c>
-      <c r="N261" t="s">
-        <v>798</v>
       </c>
       <c r="O261">
         <v>0</v>
@@ -43516,43 +43524,43 @@
         <v>0</v>
       </c>
       <c r="C262" t="s">
+        <v>739</v>
+      </c>
+      <c r="D262" t="s">
+        <v>737</v>
+      </c>
+      <c r="E262" t="s">
+        <v>740</v>
+      </c>
+      <c r="F262" t="s">
         <v>741</v>
       </c>
-      <c r="D262" t="s">
-        <v>739</v>
-      </c>
-      <c r="E262" t="s">
-        <v>742</v>
-      </c>
-      <c r="F262" t="s">
+      <c r="G262" t="s">
+        <v>797</v>
+      </c>
+      <c r="H262" t="s">
         <v>743</v>
       </c>
-      <c r="G262" t="s">
+      <c r="I262" t="s">
+        <v>779</v>
+      </c>
+      <c r="J262" t="s">
+        <v>788</v>
+      </c>
+      <c r="K262" t="s">
+        <v>789</v>
+      </c>
+      <c r="L262" t="s">
+        <v>784</v>
+      </c>
+      <c r="M262" t="s">
+        <v>794</v>
+      </c>
+      <c r="N262" t="s">
+        <v>798</v>
+      </c>
+      <c r="O262" t="s">
         <v>799</v>
-      </c>
-      <c r="H262" t="s">
-        <v>745</v>
-      </c>
-      <c r="I262" t="s">
-        <v>781</v>
-      </c>
-      <c r="J262" t="s">
-        <v>790</v>
-      </c>
-      <c r="K262" t="s">
-        <v>791</v>
-      </c>
-      <c r="L262" t="s">
-        <v>786</v>
-      </c>
-      <c r="M262" t="s">
-        <v>796</v>
-      </c>
-      <c r="N262" t="s">
-        <v>800</v>
-      </c>
-      <c r="O262" t="s">
-        <v>801</v>
       </c>
       <c r="P262">
         <v>0</v>
@@ -43573,46 +43581,46 @@
         <v>0</v>
       </c>
       <c r="C263" t="s">
+        <v>739</v>
+      </c>
+      <c r="D263" t="s">
+        <v>738</v>
+      </c>
+      <c r="E263" t="s">
+        <v>740</v>
+      </c>
+      <c r="F263" t="s">
         <v>741</v>
       </c>
-      <c r="D263" t="s">
-        <v>740</v>
-      </c>
-      <c r="E263" t="s">
-        <v>742</v>
-      </c>
-      <c r="F263" t="s">
+      <c r="G263" t="s">
+        <v>800</v>
+      </c>
+      <c r="H263" t="s">
         <v>743</v>
       </c>
-      <c r="G263" t="s">
+      <c r="I263" t="s">
+        <v>779</v>
+      </c>
+      <c r="J263" t="s">
+        <v>788</v>
+      </c>
+      <c r="K263" t="s">
+        <v>789</v>
+      </c>
+      <c r="L263" t="s">
+        <v>784</v>
+      </c>
+      <c r="M263" t="s">
+        <v>794</v>
+      </c>
+      <c r="N263" t="s">
+        <v>801</v>
+      </c>
+      <c r="O263" t="s">
         <v>802</v>
       </c>
-      <c r="H263" t="s">
-        <v>745</v>
-      </c>
-      <c r="I263" t="s">
-        <v>781</v>
-      </c>
-      <c r="J263" t="s">
-        <v>790</v>
-      </c>
-      <c r="K263" t="s">
-        <v>791</v>
-      </c>
-      <c r="L263" t="s">
-        <v>786</v>
-      </c>
-      <c r="M263" t="s">
-        <v>796</v>
-      </c>
-      <c r="N263" t="s">
+      <c r="P263" t="s">
         <v>803</v>
-      </c>
-      <c r="O263" t="s">
-        <v>804</v>
-      </c>
-      <c r="P263" t="s">
-        <v>805</v>
       </c>
       <c r="Q263">
         <v>0</v>
@@ -43630,22 +43638,22 @@
         <v>0</v>
       </c>
       <c r="C264" t="s">
+        <v>668</v>
+      </c>
+      <c r="D264" t="s">
+        <v>669</v>
+      </c>
+      <c r="E264" t="s">
         <v>670</v>
       </c>
-      <c r="D264" t="s">
+      <c r="F264" t="s">
         <v>671</v>
       </c>
-      <c r="E264" t="s">
+      <c r="G264" t="s">
         <v>672</v>
       </c>
-      <c r="F264" t="s">
+      <c r="H264" t="s">
         <v>673</v>
-      </c>
-      <c r="G264" t="s">
-        <v>674</v>
-      </c>
-      <c r="H264" t="s">
-        <v>675</v>
       </c>
       <c r="I264">
         <v>0</v>
@@ -43687,25 +43695,25 @@
         <v>0</v>
       </c>
       <c r="C265" t="s">
+        <v>668</v>
+      </c>
+      <c r="D265" t="s">
+        <v>674</v>
+      </c>
+      <c r="E265" t="s">
         <v>670</v>
       </c>
-      <c r="D265" t="s">
+      <c r="F265" t="s">
+        <v>671</v>
+      </c>
+      <c r="G265" t="s">
+        <v>672</v>
+      </c>
+      <c r="H265" t="s">
+        <v>675</v>
+      </c>
+      <c r="I265" t="s">
         <v>676</v>
-      </c>
-      <c r="E265" t="s">
-        <v>672</v>
-      </c>
-      <c r="F265" t="s">
-        <v>673</v>
-      </c>
-      <c r="G265" t="s">
-        <v>674</v>
-      </c>
-      <c r="H265" t="s">
-        <v>677</v>
-      </c>
-      <c r="I265" t="s">
-        <v>678</v>
       </c>
       <c r="J265">
         <v>0</v>
@@ -43744,28 +43752,28 @@
         <v>0</v>
       </c>
       <c r="C266" t="s">
+        <v>668</v>
+      </c>
+      <c r="D266" t="s">
+        <v>677</v>
+      </c>
+      <c r="E266" t="s">
         <v>670</v>
       </c>
-      <c r="D266" t="s">
+      <c r="F266" t="s">
+        <v>671</v>
+      </c>
+      <c r="G266" t="s">
+        <v>672</v>
+      </c>
+      <c r="H266" t="s">
+        <v>678</v>
+      </c>
+      <c r="I266" t="s">
+        <v>676</v>
+      </c>
+      <c r="J266" t="s">
         <v>679</v>
-      </c>
-      <c r="E266" t="s">
-        <v>672</v>
-      </c>
-      <c r="F266" t="s">
-        <v>673</v>
-      </c>
-      <c r="G266" t="s">
-        <v>674</v>
-      </c>
-      <c r="H266" t="s">
-        <v>680</v>
-      </c>
-      <c r="I266" t="s">
-        <v>678</v>
-      </c>
-      <c r="J266" t="s">
-        <v>681</v>
       </c>
       <c r="K266">
         <v>0</v>
@@ -43801,28 +43809,28 @@
         <v>0</v>
       </c>
       <c r="C267" t="s">
+        <v>668</v>
+      </c>
+      <c r="D267" t="s">
+        <v>680</v>
+      </c>
+      <c r="E267" t="s">
         <v>670</v>
       </c>
-      <c r="D267" t="s">
+      <c r="F267" t="s">
+        <v>671</v>
+      </c>
+      <c r="G267" t="s">
+        <v>681</v>
+      </c>
+      <c r="H267" t="s">
+        <v>678</v>
+      </c>
+      <c r="I267" t="s">
         <v>682</v>
       </c>
-      <c r="E267" t="s">
-        <v>672</v>
-      </c>
-      <c r="F267" t="s">
-        <v>673</v>
-      </c>
-      <c r="G267" t="s">
-        <v>683</v>
-      </c>
-      <c r="H267" t="s">
-        <v>680</v>
-      </c>
-      <c r="I267" t="s">
-        <v>684</v>
-      </c>
       <c r="J267" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="K267">
         <v>0</v>
@@ -43858,28 +43866,28 @@
         <v>0</v>
       </c>
       <c r="C268" t="s">
+        <v>668</v>
+      </c>
+      <c r="D268" t="s">
+        <v>683</v>
+      </c>
+      <c r="E268" t="s">
         <v>670</v>
       </c>
-      <c r="D268" t="s">
+      <c r="F268" t="s">
+        <v>671</v>
+      </c>
+      <c r="G268" t="s">
+        <v>684</v>
+      </c>
+      <c r="H268" t="s">
+        <v>678</v>
+      </c>
+      <c r="I268" t="s">
+        <v>682</v>
+      </c>
+      <c r="J268" t="s">
         <v>685</v>
-      </c>
-      <c r="E268" t="s">
-        <v>672</v>
-      </c>
-      <c r="F268" t="s">
-        <v>673</v>
-      </c>
-      <c r="G268" t="s">
-        <v>686</v>
-      </c>
-      <c r="H268" t="s">
-        <v>680</v>
-      </c>
-      <c r="I268" t="s">
-        <v>684</v>
-      </c>
-      <c r="J268" t="s">
-        <v>687</v>
       </c>
       <c r="K268">
         <v>0</v>
@@ -43915,31 +43923,31 @@
         <v>0</v>
       </c>
       <c r="C269" t="s">
+        <v>668</v>
+      </c>
+      <c r="D269" t="s">
+        <v>686</v>
+      </c>
+      <c r="E269" t="s">
         <v>670</v>
       </c>
-      <c r="D269" t="s">
+      <c r="F269" t="s">
+        <v>671</v>
+      </c>
+      <c r="G269" t="s">
+        <v>687</v>
+      </c>
+      <c r="H269" t="s">
+        <v>678</v>
+      </c>
+      <c r="I269" t="s">
+        <v>682</v>
+      </c>
+      <c r="J269" t="s">
+        <v>685</v>
+      </c>
+      <c r="K269" t="s">
         <v>688</v>
-      </c>
-      <c r="E269" t="s">
-        <v>672</v>
-      </c>
-      <c r="F269" t="s">
-        <v>673</v>
-      </c>
-      <c r="G269" t="s">
-        <v>689</v>
-      </c>
-      <c r="H269" t="s">
-        <v>680</v>
-      </c>
-      <c r="I269" t="s">
-        <v>684</v>
-      </c>
-      <c r="J269" t="s">
-        <v>687</v>
-      </c>
-      <c r="K269" t="s">
-        <v>690</v>
       </c>
       <c r="L269">
         <v>0</v>
@@ -43972,31 +43980,31 @@
         <v>0</v>
       </c>
       <c r="C270" t="s">
+        <v>668</v>
+      </c>
+      <c r="D270" t="s">
+        <v>689</v>
+      </c>
+      <c r="E270" t="s">
         <v>670</v>
       </c>
-      <c r="D270" t="s">
+      <c r="F270" t="s">
+        <v>671</v>
+      </c>
+      <c r="G270" t="s">
+        <v>690</v>
+      </c>
+      <c r="H270" t="s">
         <v>691</v>
       </c>
-      <c r="E270" t="s">
-        <v>672</v>
-      </c>
-      <c r="F270" t="s">
-        <v>673</v>
-      </c>
-      <c r="G270" t="s">
+      <c r="I270" t="s">
+        <v>685</v>
+      </c>
+      <c r="J270" t="s">
         <v>692</v>
       </c>
-      <c r="H270" t="s">
+      <c r="K270" t="s">
         <v>693</v>
-      </c>
-      <c r="I270" t="s">
-        <v>687</v>
-      </c>
-      <c r="J270" t="s">
-        <v>694</v>
-      </c>
-      <c r="K270" t="s">
-        <v>695</v>
       </c>
       <c r="L270">
         <v>0</v>
@@ -44029,31 +44037,31 @@
         <v>0</v>
       </c>
       <c r="C271" t="s">
+        <v>668</v>
+      </c>
+      <c r="D271" t="s">
+        <v>694</v>
+      </c>
+      <c r="E271" t="s">
         <v>670</v>
       </c>
-      <c r="D271" t="s">
-        <v>696</v>
-      </c>
-      <c r="E271" t="s">
-        <v>672</v>
-      </c>
       <c r="F271" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="G271" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="H271" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="I271" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="J271" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="K271" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="L271">
         <v>0</v>
@@ -44086,31 +44094,31 @@
         <v>0</v>
       </c>
       <c r="C272" t="s">
+        <v>668</v>
+      </c>
+      <c r="D272" t="s">
+        <v>696</v>
+      </c>
+      <c r="E272" t="s">
         <v>670</v>
       </c>
-      <c r="D272" t="s">
+      <c r="F272" t="s">
+        <v>671</v>
+      </c>
+      <c r="G272" t="s">
+        <v>691</v>
+      </c>
+      <c r="H272" t="s">
+        <v>697</v>
+      </c>
+      <c r="I272" t="s">
+        <v>692</v>
+      </c>
+      <c r="J272" t="s">
         <v>698</v>
       </c>
-      <c r="E272" t="s">
-        <v>672</v>
-      </c>
-      <c r="F272" t="s">
-        <v>673</v>
-      </c>
-      <c r="G272" t="s">
-        <v>693</v>
-      </c>
-      <c r="H272" t="s">
+      <c r="K272" t="s">
         <v>699</v>
-      </c>
-      <c r="I272" t="s">
-        <v>694</v>
-      </c>
-      <c r="J272" t="s">
-        <v>700</v>
-      </c>
-      <c r="K272" t="s">
-        <v>701</v>
       </c>
       <c r="L272">
         <v>0</v>
@@ -44143,31 +44151,31 @@
         <v>0</v>
       </c>
       <c r="C273" t="s">
+        <v>668</v>
+      </c>
+      <c r="D273" t="s">
+        <v>700</v>
+      </c>
+      <c r="E273" t="s">
         <v>670</v>
       </c>
-      <c r="D273" t="s">
+      <c r="F273" t="s">
+        <v>671</v>
+      </c>
+      <c r="G273" t="s">
+        <v>697</v>
+      </c>
+      <c r="H273" t="s">
+        <v>701</v>
+      </c>
+      <c r="I273" t="s">
+        <v>698</v>
+      </c>
+      <c r="J273" t="s">
         <v>702</v>
       </c>
-      <c r="E273" t="s">
-        <v>672</v>
-      </c>
-      <c r="F273" t="s">
-        <v>673</v>
-      </c>
-      <c r="G273" t="s">
-        <v>699</v>
-      </c>
-      <c r="H273" t="s">
+      <c r="K273" t="s">
         <v>703</v>
-      </c>
-      <c r="I273" t="s">
-        <v>700</v>
-      </c>
-      <c r="J273" t="s">
-        <v>704</v>
-      </c>
-      <c r="K273" t="s">
-        <v>705</v>
       </c>
       <c r="L273">
         <v>0</v>
@@ -44200,31 +44208,31 @@
         <v>0</v>
       </c>
       <c r="C274" t="s">
+        <v>668</v>
+      </c>
+      <c r="D274" t="s">
+        <v>704</v>
+      </c>
+      <c r="E274" t="s">
         <v>670</v>
       </c>
-      <c r="D274" t="s">
+      <c r="F274" t="s">
+        <v>671</v>
+      </c>
+      <c r="G274" t="s">
+        <v>701</v>
+      </c>
+      <c r="H274" t="s">
+        <v>705</v>
+      </c>
+      <c r="I274" t="s">
+        <v>702</v>
+      </c>
+      <c r="J274" t="s">
         <v>706</v>
       </c>
-      <c r="E274" t="s">
-        <v>672</v>
-      </c>
-      <c r="F274" t="s">
-        <v>673</v>
-      </c>
-      <c r="G274" t="s">
-        <v>703</v>
-      </c>
-      <c r="H274" t="s">
+      <c r="K274" t="s">
         <v>707</v>
-      </c>
-      <c r="I274" t="s">
-        <v>704</v>
-      </c>
-      <c r="J274" t="s">
-        <v>708</v>
-      </c>
-      <c r="K274" t="s">
-        <v>709</v>
       </c>
       <c r="L274">
         <v>0</v>
@@ -44257,31 +44265,31 @@
         <v>0</v>
       </c>
       <c r="C275" t="s">
+        <v>668</v>
+      </c>
+      <c r="D275" t="s">
+        <v>708</v>
+      </c>
+      <c r="E275" t="s">
         <v>670</v>
       </c>
-      <c r="D275" t="s">
+      <c r="F275" t="s">
+        <v>671</v>
+      </c>
+      <c r="G275" t="s">
+        <v>705</v>
+      </c>
+      <c r="H275" t="s">
+        <v>709</v>
+      </c>
+      <c r="I275" t="s">
+        <v>706</v>
+      </c>
+      <c r="J275" t="s">
         <v>710</v>
       </c>
-      <c r="E275" t="s">
-        <v>672</v>
-      </c>
-      <c r="F275" t="s">
-        <v>673</v>
-      </c>
-      <c r="G275" t="s">
-        <v>707</v>
-      </c>
-      <c r="H275" t="s">
+      <c r="K275" t="s">
         <v>711</v>
-      </c>
-      <c r="I275" t="s">
-        <v>708</v>
-      </c>
-      <c r="J275" t="s">
-        <v>712</v>
-      </c>
-      <c r="K275" t="s">
-        <v>713</v>
       </c>
       <c r="L275">
         <v>0</v>
@@ -44314,31 +44322,31 @@
         <v>0</v>
       </c>
       <c r="C276" t="s">
+        <v>668</v>
+      </c>
+      <c r="D276" t="s">
+        <v>712</v>
+      </c>
+      <c r="E276" t="s">
         <v>670</v>
       </c>
-      <c r="D276" t="s">
+      <c r="F276" t="s">
+        <v>671</v>
+      </c>
+      <c r="G276" t="s">
+        <v>709</v>
+      </c>
+      <c r="H276" t="s">
+        <v>713</v>
+      </c>
+      <c r="I276" t="s">
+        <v>710</v>
+      </c>
+      <c r="J276" t="s">
         <v>714</v>
       </c>
-      <c r="E276" t="s">
-        <v>672</v>
-      </c>
-      <c r="F276" t="s">
-        <v>673</v>
-      </c>
-      <c r="G276" t="s">
-        <v>711</v>
-      </c>
-      <c r="H276" t="s">
+      <c r="K276" t="s">
         <v>715</v>
-      </c>
-      <c r="I276" t="s">
-        <v>712</v>
-      </c>
-      <c r="J276" t="s">
-        <v>716</v>
-      </c>
-      <c r="K276" t="s">
-        <v>717</v>
       </c>
       <c r="L276">
         <v>0</v>
@@ -44371,31 +44379,31 @@
         <v>0</v>
       </c>
       <c r="C277" t="s">
+        <v>668</v>
+      </c>
+      <c r="D277" t="s">
+        <v>716</v>
+      </c>
+      <c r="E277" t="s">
         <v>670</v>
       </c>
-      <c r="D277" t="s">
+      <c r="F277" t="s">
+        <v>671</v>
+      </c>
+      <c r="G277" t="s">
+        <v>713</v>
+      </c>
+      <c r="H277" t="s">
+        <v>717</v>
+      </c>
+      <c r="I277" t="s">
+        <v>714</v>
+      </c>
+      <c r="J277" t="s">
         <v>718</v>
       </c>
-      <c r="E277" t="s">
-        <v>672</v>
-      </c>
-      <c r="F277" t="s">
-        <v>673</v>
-      </c>
-      <c r="G277" t="s">
-        <v>715</v>
-      </c>
-      <c r="H277" t="s">
+      <c r="K277" t="s">
         <v>719</v>
-      </c>
-      <c r="I277" t="s">
-        <v>716</v>
-      </c>
-      <c r="J277" t="s">
-        <v>720</v>
-      </c>
-      <c r="K277" t="s">
-        <v>721</v>
       </c>
       <c r="L277">
         <v>0</v>
@@ -44428,31 +44436,31 @@
         <v>0</v>
       </c>
       <c r="C278" t="s">
+        <v>668</v>
+      </c>
+      <c r="D278" t="s">
+        <v>720</v>
+      </c>
+      <c r="E278" t="s">
         <v>670</v>
       </c>
-      <c r="D278" t="s">
+      <c r="F278" t="s">
+        <v>671</v>
+      </c>
+      <c r="G278" t="s">
+        <v>717</v>
+      </c>
+      <c r="H278" t="s">
+        <v>721</v>
+      </c>
+      <c r="I278" t="s">
+        <v>718</v>
+      </c>
+      <c r="J278" t="s">
         <v>722</v>
       </c>
-      <c r="E278" t="s">
-        <v>672</v>
-      </c>
-      <c r="F278" t="s">
-        <v>673</v>
-      </c>
-      <c r="G278" t="s">
-        <v>719</v>
-      </c>
-      <c r="H278" t="s">
+      <c r="K278" t="s">
         <v>723</v>
-      </c>
-      <c r="I278" t="s">
-        <v>720</v>
-      </c>
-      <c r="J278" t="s">
-        <v>724</v>
-      </c>
-      <c r="K278" t="s">
-        <v>725</v>
       </c>
       <c r="L278">
         <v>0</v>
@@ -44485,31 +44493,31 @@
         <v>0</v>
       </c>
       <c r="C279" t="s">
+        <v>668</v>
+      </c>
+      <c r="D279" t="s">
+        <v>724</v>
+      </c>
+      <c r="E279" t="s">
         <v>670</v>
       </c>
-      <c r="D279" t="s">
+      <c r="F279" t="s">
+        <v>671</v>
+      </c>
+      <c r="G279" t="s">
+        <v>721</v>
+      </c>
+      <c r="H279" t="s">
+        <v>725</v>
+      </c>
+      <c r="I279" t="s">
+        <v>722</v>
+      </c>
+      <c r="J279" t="s">
         <v>726</v>
       </c>
-      <c r="E279" t="s">
-        <v>672</v>
-      </c>
-      <c r="F279" t="s">
-        <v>673</v>
-      </c>
-      <c r="G279" t="s">
-        <v>723</v>
-      </c>
-      <c r="H279" t="s">
+      <c r="K279" t="s">
         <v>727</v>
-      </c>
-      <c r="I279" t="s">
-        <v>724</v>
-      </c>
-      <c r="J279" t="s">
-        <v>728</v>
-      </c>
-      <c r="K279" t="s">
-        <v>729</v>
       </c>
       <c r="L279">
         <v>0</v>
@@ -44542,31 +44550,31 @@
         <v>0</v>
       </c>
       <c r="C280" t="s">
+        <v>668</v>
+      </c>
+      <c r="D280" t="s">
+        <v>728</v>
+      </c>
+      <c r="E280" t="s">
         <v>670</v>
       </c>
-      <c r="D280" t="s">
+      <c r="F280" t="s">
+        <v>671</v>
+      </c>
+      <c r="G280" t="s">
+        <v>725</v>
+      </c>
+      <c r="H280" t="s">
+        <v>729</v>
+      </c>
+      <c r="I280" t="s">
+        <v>726</v>
+      </c>
+      <c r="J280" t="s">
         <v>730</v>
       </c>
-      <c r="E280" t="s">
-        <v>672</v>
-      </c>
-      <c r="F280" t="s">
-        <v>673</v>
-      </c>
-      <c r="G280" t="s">
-        <v>727</v>
-      </c>
-      <c r="H280" t="s">
+      <c r="K280" t="s">
         <v>731</v>
-      </c>
-      <c r="I280" t="s">
-        <v>728</v>
-      </c>
-      <c r="J280" t="s">
-        <v>732</v>
-      </c>
-      <c r="K280" t="s">
-        <v>733</v>
       </c>
       <c r="L280">
         <v>0</v>
@@ -44599,34 +44607,34 @@
         <v>0</v>
       </c>
       <c r="C281" t="s">
+        <v>668</v>
+      </c>
+      <c r="D281" t="s">
+        <v>732</v>
+      </c>
+      <c r="E281" t="s">
         <v>670</v>
       </c>
-      <c r="D281" t="s">
+      <c r="F281" t="s">
+        <v>671</v>
+      </c>
+      <c r="G281" t="s">
+        <v>715</v>
+      </c>
+      <c r="H281" t="s">
+        <v>733</v>
+      </c>
+      <c r="I281" t="s">
         <v>734</v>
       </c>
-      <c r="E281" t="s">
-        <v>672</v>
-      </c>
-      <c r="F281" t="s">
-        <v>673</v>
-      </c>
-      <c r="G281" t="s">
-        <v>717</v>
-      </c>
-      <c r="H281" t="s">
+      <c r="J281" t="s">
+        <v>730</v>
+      </c>
+      <c r="K281" t="s">
         <v>735</v>
       </c>
-      <c r="I281" t="s">
+      <c r="L281" t="s">
         <v>736</v>
-      </c>
-      <c r="J281" t="s">
-        <v>732</v>
-      </c>
-      <c r="K281" t="s">
-        <v>737</v>
-      </c>
-      <c r="L281" t="s">
-        <v>738</v>
       </c>
       <c r="M281">
         <v>0</v>
@@ -44656,34 +44664,34 @@
         <v>0</v>
       </c>
       <c r="C282" t="s">
+        <v>668</v>
+      </c>
+      <c r="D282" t="s">
+        <v>737</v>
+      </c>
+      <c r="E282" t="s">
         <v>670</v>
       </c>
-      <c r="D282" t="s">
-        <v>739</v>
-      </c>
-      <c r="E282" t="s">
-        <v>672</v>
-      </c>
       <c r="F282" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="G282" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="H282" t="s">
+        <v>733</v>
+      </c>
+      <c r="I282" t="s">
+        <v>734</v>
+      </c>
+      <c r="J282" t="s">
+        <v>730</v>
+      </c>
+      <c r="K282" t="s">
         <v>735</v>
       </c>
-      <c r="I282" t="s">
+      <c r="L282" t="s">
         <v>736</v>
-      </c>
-      <c r="J282" t="s">
-        <v>732</v>
-      </c>
-      <c r="K282" t="s">
-        <v>737</v>
-      </c>
-      <c r="L282" t="s">
-        <v>738</v>
       </c>
       <c r="M282">
         <v>0</v>
@@ -44713,34 +44721,34 @@
         <v>0</v>
       </c>
       <c r="C283" t="s">
+        <v>668</v>
+      </c>
+      <c r="D283" t="s">
+        <v>738</v>
+      </c>
+      <c r="E283" t="s">
         <v>670</v>
       </c>
-      <c r="D283" t="s">
-        <v>740</v>
-      </c>
-      <c r="E283" t="s">
-        <v>672</v>
-      </c>
       <c r="F283" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="G283" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="H283" t="s">
+        <v>733</v>
+      </c>
+      <c r="I283" t="s">
+        <v>734</v>
+      </c>
+      <c r="J283" t="s">
+        <v>730</v>
+      </c>
+      <c r="K283" t="s">
         <v>735</v>
       </c>
-      <c r="I283" t="s">
+      <c r="L283" t="s">
         <v>736</v>
-      </c>
-      <c r="J283" t="s">
-        <v>732</v>
-      </c>
-      <c r="K283" t="s">
-        <v>737</v>
-      </c>
-      <c r="L283" t="s">
-        <v>738</v>
       </c>
       <c r="M283">
         <v>0</v>
@@ -44770,16 +44778,16 @@
         <v>0</v>
       </c>
       <c r="C284" t="s">
+        <v>804</v>
+      </c>
+      <c r="D284" t="s">
+        <v>805</v>
+      </c>
+      <c r="E284" t="s">
         <v>806</v>
       </c>
-      <c r="D284" t="s">
+      <c r="F284" t="s">
         <v>807</v>
-      </c>
-      <c r="E284" t="s">
-        <v>808</v>
-      </c>
-      <c r="F284" t="s">
-        <v>809</v>
       </c>
       <c r="G284">
         <v>0</v>
@@ -44827,16 +44835,16 @@
         <v>0</v>
       </c>
       <c r="C285" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D285" t="s">
+        <v>808</v>
+      </c>
+      <c r="E285" t="s">
+        <v>809</v>
+      </c>
+      <c r="F285" t="s">
         <v>810</v>
-      </c>
-      <c r="E285" t="s">
-        <v>811</v>
-      </c>
-      <c r="F285" t="s">
-        <v>812</v>
       </c>
       <c r="G285">
         <v>0.1</v>
@@ -44884,16 +44892,16 @@
         <v>0</v>
       </c>
       <c r="C286" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D286" t="s">
+        <v>811</v>
+      </c>
+      <c r="E286" t="s">
+        <v>812</v>
+      </c>
+      <c r="F286" t="s">
         <v>813</v>
-      </c>
-      <c r="E286" t="s">
-        <v>814</v>
-      </c>
-      <c r="F286" t="s">
-        <v>815</v>
       </c>
       <c r="G286">
         <v>0</v>
@@ -44941,16 +44949,16 @@
         <v>0</v>
       </c>
       <c r="C287" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D287" t="s">
+        <v>814</v>
+      </c>
+      <c r="E287" t="s">
+        <v>815</v>
+      </c>
+      <c r="F287" t="s">
         <v>816</v>
-      </c>
-      <c r="E287" t="s">
-        <v>817</v>
-      </c>
-      <c r="F287" t="s">
-        <v>818</v>
       </c>
       <c r="G287">
         <v>0</v>
@@ -44998,16 +45006,16 @@
         <v>0</v>
       </c>
       <c r="C288" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D288" t="s">
+        <v>817</v>
+      </c>
+      <c r="E288" t="s">
+        <v>818</v>
+      </c>
+      <c r="F288" t="s">
         <v>819</v>
-      </c>
-      <c r="E288" t="s">
-        <v>820</v>
-      </c>
-      <c r="F288" t="s">
-        <v>821</v>
       </c>
       <c r="G288">
         <v>0.2</v>
@@ -45055,16 +45063,16 @@
         <v>0</v>
       </c>
       <c r="C289" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="F289" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="G289">
         <v>0.5</v>
@@ -45112,16 +45120,16 @@
         <v>0</v>
       </c>
       <c r="C290" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D290" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E290" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="F290" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="G290">
         <v>1000</v>
@@ -45169,16 +45177,16 @@
         <v>0</v>
       </c>
       <c r="C291" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D291" t="s">
+        <v>823</v>
+      </c>
+      <c r="E291" t="s">
+        <v>824</v>
+      </c>
+      <c r="F291" t="s">
         <v>825</v>
-      </c>
-      <c r="E291" t="s">
-        <v>826</v>
-      </c>
-      <c r="F291" t="s">
-        <v>827</v>
       </c>
       <c r="G291">
         <v>0</v>
@@ -45226,16 +45234,16 @@
         <v>0</v>
       </c>
       <c r="C292" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D292" t="s">
+        <v>826</v>
+      </c>
+      <c r="E292" t="s">
+        <v>827</v>
+      </c>
+      <c r="F292" t="s">
         <v>828</v>
-      </c>
-      <c r="E292" t="s">
-        <v>829</v>
-      </c>
-      <c r="F292" t="s">
-        <v>830</v>
       </c>
       <c r="G292">
         <v>30</v>
@@ -45283,16 +45291,16 @@
         <v>0</v>
       </c>
       <c r="C293" t="s">
+        <v>829</v>
+      </c>
+      <c r="D293" t="s">
+        <v>830</v>
+      </c>
+      <c r="E293" t="s">
         <v>831</v>
       </c>
-      <c r="D293" t="s">
+      <c r="F293" t="s">
         <v>832</v>
-      </c>
-      <c r="E293" t="s">
-        <v>833</v>
-      </c>
-      <c r="F293" t="s">
-        <v>834</v>
       </c>
       <c r="G293">
         <v>0.75</v>
@@ -45340,13 +45348,13 @@
         <v>0</v>
       </c>
       <c r="C294" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D294" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E294" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="F294">
         <v>0</v>
@@ -45397,16 +45405,16 @@
         <v>0</v>
       </c>
       <c r="C295" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D295" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="E295" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="F295" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="G295">
         <v>45</v>
@@ -45454,16 +45462,16 @@
         <v>0</v>
       </c>
       <c r="C296" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D296" t="s">
+        <v>837</v>
+      </c>
+      <c r="E296" t="s">
+        <v>838</v>
+      </c>
+      <c r="F296" t="s">
         <v>839</v>
-      </c>
-      <c r="E296" t="s">
-        <v>840</v>
-      </c>
-      <c r="F296" t="s">
-        <v>841</v>
       </c>
       <c r="G296">
         <v>0</v>
@@ -45511,16 +45519,16 @@
         <v>0</v>
       </c>
       <c r="C297" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D297" t="s">
+        <v>840</v>
+      </c>
+      <c r="E297" t="s">
+        <v>841</v>
+      </c>
+      <c r="F297" t="s">
         <v>842</v>
-      </c>
-      <c r="E297" t="s">
-        <v>843</v>
-      </c>
-      <c r="F297" t="s">
-        <v>844</v>
       </c>
       <c r="G297">
         <v>0.1</v>
@@ -45568,16 +45576,16 @@
         <v>0</v>
       </c>
       <c r="C298" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D298" t="s">
+        <v>930</v>
+      </c>
+      <c r="E298" t="s">
+        <v>931</v>
+      </c>
+      <c r="F298" t="s">
         <v>932</v>
-      </c>
-      <c r="E298" t="s">
-        <v>933</v>
-      </c>
-      <c r="F298" t="s">
-        <v>934</v>
       </c>
       <c r="G298">
         <v>50000</v>
@@ -45625,16 +45633,16 @@
         <v>0</v>
       </c>
       <c r="C299" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D299" t="s">
+        <v>933</v>
+      </c>
+      <c r="E299" t="s">
+        <v>934</v>
+      </c>
+      <c r="F299" t="s">
         <v>935</v>
-      </c>
-      <c r="E299" t="s">
-        <v>936</v>
-      </c>
-      <c r="F299" t="s">
-        <v>937</v>
       </c>
       <c r="G299">
         <v>10</v>
@@ -45682,16 +45690,16 @@
         <v>0</v>
       </c>
       <c r="C300" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D300" t="s">
+        <v>936</v>
+      </c>
+      <c r="E300" t="s">
+        <v>937</v>
+      </c>
+      <c r="F300" t="s">
         <v>938</v>
-      </c>
-      <c r="E300" t="s">
-        <v>939</v>
-      </c>
-      <c r="F300" t="s">
-        <v>940</v>
       </c>
       <c r="G300">
         <v>75</v>
@@ -45739,16 +45747,16 @@
         <v>0</v>
       </c>
       <c r="C301" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D301" t="s">
+        <v>939</v>
+      </c>
+      <c r="E301" t="s">
+        <v>940</v>
+      </c>
+      <c r="F301" t="s">
         <v>941</v>
-      </c>
-      <c r="E301" t="s">
-        <v>942</v>
-      </c>
-      <c r="F301" t="s">
-        <v>943</v>
       </c>
       <c r="G301">
         <v>25</v>
@@ -45796,16 +45804,16 @@
         <v>0</v>
       </c>
       <c r="C302" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D302" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="E302" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="F302" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="G302">
         <v>5</v>
@@ -45853,16 +45861,16 @@
         <v>0</v>
       </c>
       <c r="C303" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="D303" t="s">
+        <v>944</v>
+      </c>
+      <c r="E303" t="s">
+        <v>945</v>
+      </c>
+      <c r="F303" t="s">
         <v>946</v>
-      </c>
-      <c r="E303" t="s">
-        <v>947</v>
-      </c>
-      <c r="F303" t="s">
-        <v>948</v>
       </c>
       <c r="G303">
         <v>0.6</v>
@@ -45910,16 +45918,16 @@
         <v>0</v>
       </c>
       <c r="C304" t="s">
+        <v>867</v>
+      </c>
+      <c r="D304" t="s">
+        <v>868</v>
+      </c>
+      <c r="E304" t="s">
         <v>869</v>
       </c>
-      <c r="D304" t="s">
+      <c r="F304" t="s">
         <v>870</v>
-      </c>
-      <c r="E304" t="s">
-        <v>871</v>
-      </c>
-      <c r="F304" t="s">
-        <v>872</v>
       </c>
       <c r="G304">
         <v>25</v>
@@ -45928,7 +45936,7 @@
         <v>25</v>
       </c>
       <c r="I304" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="J304">
         <v>0</v>
@@ -45967,16 +45975,16 @@
         <v>0</v>
       </c>
       <c r="C305" t="s">
+        <v>867</v>
+      </c>
+      <c r="D305" t="s">
+        <v>872</v>
+      </c>
+      <c r="E305" t="s">
         <v>869</v>
       </c>
-      <c r="D305" t="s">
-        <v>874</v>
-      </c>
-      <c r="E305" t="s">
-        <v>871</v>
-      </c>
       <c r="F305" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G305">
         <v>20</v>
@@ -45985,7 +45993,7 @@
         <v>20</v>
       </c>
       <c r="I305" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="J305">
         <v>0</v>
@@ -46024,16 +46032,16 @@
         <v>0</v>
       </c>
       <c r="C306" t="s">
+        <v>867</v>
+      </c>
+      <c r="D306" t="s">
+        <v>874</v>
+      </c>
+      <c r="E306" t="s">
         <v>869</v>
       </c>
-      <c r="D306" t="s">
-        <v>876</v>
-      </c>
-      <c r="E306" t="s">
-        <v>871</v>
-      </c>
       <c r="F306" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G306">
         <v>3</v>
@@ -46042,7 +46050,7 @@
         <v>1.5</v>
       </c>
       <c r="I306" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="J306">
         <v>0</v>
@@ -46081,16 +46089,16 @@
         <v>0</v>
       </c>
       <c r="C307" t="s">
+        <v>867</v>
+      </c>
+      <c r="D307" t="s">
+        <v>876</v>
+      </c>
+      <c r="E307" t="s">
         <v>869</v>
       </c>
-      <c r="D307" t="s">
-        <v>878</v>
-      </c>
-      <c r="E307" t="s">
-        <v>871</v>
-      </c>
       <c r="F307" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="G307">
         <v>20</v>
@@ -46099,7 +46107,7 @@
         <v>20</v>
       </c>
       <c r="I307" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="J307">
         <v>0</v>
@@ -46138,16 +46146,16 @@
         <v>0</v>
       </c>
       <c r="C308" t="s">
+        <v>867</v>
+      </c>
+      <c r="D308" t="s">
+        <v>878</v>
+      </c>
+      <c r="E308" t="s">
         <v>869</v>
       </c>
-      <c r="D308" t="s">
-        <v>880</v>
-      </c>
-      <c r="E308" t="s">
-        <v>871</v>
-      </c>
       <c r="F308" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G308">
         <v>3</v>
@@ -46156,7 +46164,7 @@
         <v>1.5</v>
       </c>
       <c r="I308" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="J308">
         <v>0</v>
@@ -46195,16 +46203,16 @@
         <v>0</v>
       </c>
       <c r="C309" t="s">
+        <v>867</v>
+      </c>
+      <c r="D309" t="s">
+        <v>880</v>
+      </c>
+      <c r="E309" t="s">
         <v>869</v>
       </c>
-      <c r="D309" t="s">
-        <v>882</v>
-      </c>
-      <c r="E309" t="s">
-        <v>871</v>
-      </c>
       <c r="F309" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="G309">
         <v>3</v>
@@ -46213,7 +46221,7 @@
         <v>1.5</v>
       </c>
       <c r="I309" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="J309">
         <v>0</v>
@@ -46252,16 +46260,16 @@
         <v>0</v>
       </c>
       <c r="C310" t="s">
+        <v>867</v>
+      </c>
+      <c r="D310" t="s">
+        <v>882</v>
+      </c>
+      <c r="E310" t="s">
         <v>869</v>
       </c>
-      <c r="D310" t="s">
-        <v>884</v>
-      </c>
-      <c r="E310" t="s">
-        <v>871</v>
-      </c>
       <c r="F310" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G310">
         <v>3</v>
@@ -46270,7 +46278,7 @@
         <v>1.5</v>
       </c>
       <c r="I310" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="J310">
         <v>0</v>
@@ -46309,16 +46317,16 @@
         <v>0</v>
       </c>
       <c r="C311" t="s">
+        <v>867</v>
+      </c>
+      <c r="D311" t="s">
+        <v>884</v>
+      </c>
+      <c r="E311" t="s">
         <v>869</v>
       </c>
-      <c r="D311" t="s">
-        <v>886</v>
-      </c>
-      <c r="E311" t="s">
-        <v>871</v>
-      </c>
       <c r="F311" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="G311">
         <v>25</v>
@@ -46327,7 +46335,7 @@
         <v>25</v>
       </c>
       <c r="I311" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="J311">
         <v>0</v>
@@ -46366,16 +46374,16 @@
         <v>0</v>
       </c>
       <c r="C312" t="s">
+        <v>867</v>
+      </c>
+      <c r="D312" t="s">
+        <v>886</v>
+      </c>
+      <c r="E312" t="s">
         <v>869</v>
       </c>
-      <c r="D312" t="s">
-        <v>888</v>
-      </c>
-      <c r="E312" t="s">
-        <v>871</v>
-      </c>
       <c r="F312" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="G312">
         <v>5</v>
@@ -46384,7 +46392,7 @@
         <v>2.5</v>
       </c>
       <c r="I312" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="J312">
         <v>0</v>
@@ -46423,19 +46431,19 @@
         <v>0</v>
       </c>
       <c r="C313" t="s">
+        <v>888</v>
+      </c>
+      <c r="D313" t="s">
+        <v>889</v>
+      </c>
+      <c r="E313" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="F313" t="s">
         <v>890</v>
       </c>
-      <c r="D313" t="s">
-        <v>891</v>
-      </c>
-      <c r="E313" s="3" t="s">
-        <v>997</v>
-      </c>
-      <c r="F313" t="s">
-        <v>892</v>
-      </c>
       <c r="G313" s="3" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="H313">
         <v>3</v>
@@ -46480,16 +46488,16 @@
         <v>0</v>
       </c>
       <c r="C314" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D314" t="s">
+        <v>891</v>
+      </c>
+      <c r="E314" t="s">
+        <v>892</v>
+      </c>
+      <c r="F314" t="s">
         <v>893</v>
-      </c>
-      <c r="E314" t="s">
-        <v>894</v>
-      </c>
-      <c r="F314" t="s">
-        <v>895</v>
       </c>
       <c r="G314">
         <v>5</v>
@@ -46537,16 +46545,16 @@
         <v>0</v>
       </c>
       <c r="C315" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D315" t="s">
+        <v>894</v>
+      </c>
+      <c r="E315" t="s">
+        <v>895</v>
+      </c>
+      <c r="F315" t="s">
         <v>896</v>
-      </c>
-      <c r="E315" t="s">
-        <v>897</v>
-      </c>
-      <c r="F315" t="s">
-        <v>898</v>
       </c>
       <c r="G315">
         <v>10</v>
@@ -46594,16 +46602,16 @@
         <v>0</v>
       </c>
       <c r="C316" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D316" t="s">
+        <v>897</v>
+      </c>
+      <c r="E316" t="s">
+        <v>898</v>
+      </c>
+      <c r="F316" t="s">
         <v>899</v>
-      </c>
-      <c r="E316" t="s">
-        <v>900</v>
-      </c>
-      <c r="F316" t="s">
-        <v>901</v>
       </c>
       <c r="G316">
         <v>10</v>
@@ -46651,16 +46659,16 @@
         <v>0</v>
       </c>
       <c r="C317" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D317" t="s">
+        <v>900</v>
+      </c>
+      <c r="E317" t="s">
+        <v>901</v>
+      </c>
+      <c r="F317" t="s">
         <v>902</v>
-      </c>
-      <c r="E317" t="s">
-        <v>903</v>
-      </c>
-      <c r="F317" t="s">
-        <v>904</v>
       </c>
       <c r="G317">
         <v>2</v>
@@ -46708,16 +46716,16 @@
         <v>0</v>
       </c>
       <c r="C318" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D318" t="s">
+        <v>903</v>
+      </c>
+      <c r="E318" t="s">
+        <v>904</v>
+      </c>
+      <c r="F318" t="s">
         <v>905</v>
-      </c>
-      <c r="E318" t="s">
-        <v>906</v>
-      </c>
-      <c r="F318" t="s">
-        <v>907</v>
       </c>
       <c r="G318">
         <v>5</v>
@@ -46765,16 +46773,16 @@
         <v>0</v>
       </c>
       <c r="C319" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D319" t="s">
+        <v>906</v>
+      </c>
+      <c r="E319" t="s">
+        <v>907</v>
+      </c>
+      <c r="F319" t="s">
         <v>908</v>
-      </c>
-      <c r="E319" t="s">
-        <v>909</v>
-      </c>
-      <c r="F319" t="s">
-        <v>910</v>
       </c>
       <c r="G319">
         <v>10</v>
@@ -46822,16 +46830,16 @@
         <v>0</v>
       </c>
       <c r="C320" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D320" t="s">
+        <v>909</v>
+      </c>
+      <c r="E320" t="s">
+        <v>910</v>
+      </c>
+      <c r="F320" t="s">
         <v>911</v>
-      </c>
-      <c r="E320" t="s">
-        <v>912</v>
-      </c>
-      <c r="F320" t="s">
-        <v>913</v>
       </c>
       <c r="G320">
         <v>20000</v>
@@ -46879,16 +46887,16 @@
         <v>0</v>
       </c>
       <c r="C321" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D321" t="s">
+        <v>996</v>
+      </c>
+      <c r="E321" t="s">
+        <v>997</v>
+      </c>
+      <c r="F321" s="5" t="s">
         <v>998</v>
-      </c>
-      <c r="E321" t="s">
-        <v>999</v>
-      </c>
-      <c r="F321" s="5" t="s">
-        <v>1000</v>
       </c>
       <c r="G321">
         <v>0.35</v>
@@ -46936,16 +46944,16 @@
         <v>0</v>
       </c>
       <c r="C322" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D322" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="E322" t="s">
         <v>39</v>
       </c>
       <c r="F322" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G322">
         <v>1</v>
@@ -46993,16 +47001,16 @@
         <v>0</v>
       </c>
       <c r="C323" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D323" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="E323" t="s">
         <v>39</v>
       </c>
       <c r="F323" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G323">
         <v>1.35</v>
@@ -47050,16 +47058,16 @@
         <v>0</v>
       </c>
       <c r="C324" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D324" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="E324" t="s">
         <v>39</v>
       </c>
       <c r="F324" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G324">
         <v>1.75</v>
@@ -47107,16 +47115,16 @@
         <v>0</v>
       </c>
       <c r="C325" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D325" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="E325" t="s">
         <v>39</v>
       </c>
       <c r="F325" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G325">
         <v>2.2999999999999998</v>
@@ -47164,16 +47172,16 @@
         <v>0</v>
       </c>
       <c r="C326" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D326" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="E326" t="s">
         <v>39</v>
       </c>
       <c r="F326" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G326">
         <v>3</v>
@@ -47221,16 +47229,16 @@
         <v>0</v>
       </c>
       <c r="C327" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D327" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="E327" t="s">
         <v>39</v>
       </c>
       <c r="F327" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G327">
         <v>4</v>
@@ -47278,16 +47286,16 @@
         <v>0</v>
       </c>
       <c r="C328" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D328" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="E328" t="s">
         <v>39</v>
       </c>
       <c r="F328" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G328">
         <v>5.2</v>
@@ -47335,16 +47343,16 @@
         <v>0</v>
       </c>
       <c r="C329" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D329" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="E329" t="s">
         <v>39</v>
       </c>
       <c r="F329" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G329">
         <v>6.8</v>
@@ -47392,16 +47400,16 @@
         <v>0</v>
       </c>
       <c r="C330" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D330" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="E330" t="s">
         <v>39</v>
       </c>
       <c r="F330" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G330">
         <v>10.199999999999999</v>
@@ -47449,16 +47457,16 @@
         <v>0</v>
       </c>
       <c r="C331" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D331" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="E331" t="s">
         <v>39</v>
       </c>
       <c r="F331" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="G331">
         <v>15.3</v>
@@ -47506,16 +47514,16 @@
         <v>0</v>
       </c>
       <c r="C332" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D332" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="E332" t="s">
         <v>39</v>
       </c>
       <c r="F332" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="G332">
         <v>22.95</v>
@@ -47563,22 +47571,22 @@
         <v>0</v>
       </c>
       <c r="C333" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D333" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E333" t="s">
         <v>1079</v>
       </c>
-      <c r="D333" t="s">
+      <c r="F333" t="s">
         <v>1080</v>
-      </c>
-      <c r="E333" t="s">
-        <v>1081</v>
-      </c>
-      <c r="F333" t="s">
-        <v>1082</v>
       </c>
       <c r="G333">
         <v>200</v>
       </c>
       <c r="H333" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="I333">
         <v>0</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63E1302F-45AA-4542-A03A-042A2B0F681F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6EA2E2-9D48-462C-857E-BD9B5F8C3394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1844" uniqueCount="1086">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1840" uniqueCount="1084">
   <si>
     <t>編號</t>
   </si>
@@ -4051,12 +4051,6 @@
   <si>
     <t>2026-10-05 改為依「被控場次數」遞減（取代舊的存活秒數遞減）。控場分三類各自獨立計次與遞減：無法行動（暈眩、凍結、石化等無法普攻／施放技能／行動）、攻速降低、移動速度降低。a=無法行動類每被控 1 次，之後同類控場持續時間遞減 a%；b=攻速降低類每次遞減 b%；c=移動速度降低類每次遞減 c%；d=無法行動類的合併秒數（此秒數內重複施加視為同一次，多段命中不會連扣）。例：a=5，冰凍 2 秒 → 第 1 次 2 秒、第 2 次 1.9 秒、…、第 20 次起完全免疫。遞減只作用在獨立記錄的「控場效果」，狀態本身的數值與持續時間不變（遞減到 0 只是沒有控場效果，狀態仍照常掛上，依賴狀態的判定照常觸發）。攻速／移速類：同類控場還在生效中時不重複計次（場域緩速每 0.5 秒重塗，只算進入場域的那一次）。參數填 0＝該類不遞減。BOSS 對攻擊頻率類控場另有完全免疫，不受本列影響。</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>0.5</t>
   </si>
 </sst>
 </file>
@@ -10861,19 +10855,19 @@
         <f>計算表!F87</f>
         <v>2026-10-05 改為依「被控場次數」遞減（取代舊的存活秒數遞減）。控場分三類各自獨立計次與遞減：無法行動（暈眩、凍結、石化等無法普攻／施放技能／行動）、攻速降低、移動速度降低。a=無法行動類每被控 1 次，之後同類控場持續時間遞減 a%；b=攻速降低類每次遞減 b%；c=移動速度降低類每次遞減 c%；d=無法行動類的合併秒數（此秒數內重複施加視為同一次，多段命中不會連扣）。例：a=5，冰凍 2 秒 → 第 1 次 2 秒、第 2 次 1.9 秒、…、第 20 次起完全免疫。遞減只作用在獨立記錄的「控場效果」，狀態本身的數值與持續時間不變（遞減到 0 只是沒有控場效果，狀態仍照常掛上，依賴狀態的判定照常觸發）。攻速／移速類：同類控場還在生效中時不重複計次（場域緩速每 0.5 秒重塗，只算進入場域的那一次）。參數填 0＝該類不遞減。BOSS 對攻擊頻率類控場另有完全免疫，不受本列影響。</v>
       </c>
-      <c r="G87" t="str">
+      <c r="G87">
         <f>計算表!G87</f>
-        <v>5</v>
-      </c>
-      <c r="H87" t="str">
+        <v>10</v>
+      </c>
+      <c r="H87">
         <f>計算表!H87</f>
-        <v>5</v>
-      </c>
-      <c r="I87" t="str">
+        <v>10</v>
+      </c>
+      <c r="I87">
         <f>計算表!I87</f>
-        <v>5</v>
-      </c>
-      <c r="J87" t="str">
+        <v>10</v>
+      </c>
+      <c r="J87">
         <f>計算表!J87</f>
         <v>0.5</v>
       </c>
@@ -32820,17 +32814,17 @@
       <c r="F87" s="7" t="s">
         <v>1083</v>
       </c>
-      <c r="G87" s="7" t="s">
-        <v>1084</v>
-      </c>
-      <c r="H87" s="7" t="s">
-        <v>1084</v>
-      </c>
-      <c r="I87" s="7" t="s">
-        <v>1084</v>
-      </c>
-      <c r="J87" s="7" t="s">
-        <v>1085</v>
+      <c r="G87">
+        <v>10</v>
+      </c>
+      <c r="H87">
+        <v>10</v>
+      </c>
+      <c r="I87">
+        <v>10</v>
+      </c>
+      <c r="J87">
+        <v>0.5</v>
       </c>
       <c r="K87">
         <v>0</v>
@@ -47625,5 +47619,6 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6EA2E2-9D48-462C-857E-BD9B5F8C3394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630FFE6B-30B5-406E-89C9-947ECD374EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -4042,14 +4042,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{elemDmgFire,elemDmgIce,elemDmgLightning,elemDmgPoison,elemDmgLight,elemDmgDark,elemDmgEarth,elemDmgWind,resFire,resIce,resLightning,resPoison,resLight,resDark,resEarth,resWind,resAll}</t>
-  </si>
-  <si>
     <t>控制持續時間 × max(0, 1 − 該類已被控次數 × 每次遞減%)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>2026-10-05 改為依「被控場次數」遞減（取代舊的存活秒數遞減）。控場分三類各自獨立計次與遞減：無法行動（暈眩、凍結、石化等無法普攻／施放技能／行動）、攻速降低、移動速度降低。a=無法行動類每被控 1 次，之後同類控場持續時間遞減 a%；b=攻速降低類每次遞減 b%；c=移動速度降低類每次遞減 c%；d=無法行動類的合併秒數（此秒數內重複施加視為同一次，多段命中不會連扣）。例：a=5，冰凍 2 秒 → 第 1 次 2 秒、第 2 次 1.9 秒、…、第 20 次起完全免疫。遞減只作用在獨立記錄的「控場效果」，狀態本身的數值與持續時間不變（遞減到 0 只是沒有控場效果，狀態仍照常掛上，依賴狀態的判定照常觸發）。攻速／移速類：同類控場還在生效中時不重複計次（場域緩速每 0.5 秒重塗，只算進入場域的那一次）。參數填 0＝該類不遞減。BOSS 對攻擊頻率類控場另有完全免疫，不受本列影響。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{elemDmgFire,elemDmgIce,elemDmgLightning,elemDmgPoison,elemDmgLight,elemDmgDark,elemDmgEarth,elemDmgWind,resFire,resIce,resLightning,resPoison,resLight,resDark,resEarth,resWind,resAll}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -27028,7 +27029,7 @@
       </c>
       <c r="J306">
         <f>計算表!J322</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K306">
         <f>計算表!K322</f>
@@ -27249,7 +27250,7 @@
       </c>
       <c r="J309">
         <f>計算表!J325</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K309">
         <f>計算表!K325</f>
@@ -27323,7 +27324,7 @@
       </c>
       <c r="J310">
         <f>計算表!J326</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K310">
         <f>計算表!K326</f>
@@ -27397,7 +27398,7 @@
       </c>
       <c r="J311">
         <f>計算表!J327</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K311">
         <f>計算表!K327</f>
@@ -27471,7 +27472,7 @@
       </c>
       <c r="J312">
         <f>計算表!J328</f>
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K312">
         <f>計算表!K328</f>
@@ -27545,7 +27546,7 @@
       </c>
       <c r="J313">
         <f>計算表!J329</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K313">
         <f>計算表!K329</f>
@@ -27618,7 +27619,7 @@
       </c>
       <c r="J314">
         <f>計算表!J330</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K314">
         <f>計算表!K330</f>
@@ -27692,7 +27693,7 @@
       </c>
       <c r="J315">
         <f>計算表!J331</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K315">
         <f>計算表!K331</f>
@@ -27766,7 +27767,7 @@
       </c>
       <c r="J316">
         <f>計算表!J332</f>
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K316">
         <f>計算表!K332</f>
@@ -32809,10 +32810,10 @@
         <v>209</v>
       </c>
       <c r="E87" s="7" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F87" s="7" t="s">
         <v>1082</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>1083</v>
       </c>
       <c r="G87">
         <v>10</v>
@@ -46959,7 +46960,7 @@
         <v>1</v>
       </c>
       <c r="J322">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K322">
         <v>0</v>
@@ -47130,7 +47131,7 @@
         <v>3</v>
       </c>
       <c r="J325">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K325">
         <v>1</v>
@@ -47187,7 +47188,7 @@
         <v>4</v>
       </c>
       <c r="J326">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K326">
         <v>2</v>
@@ -47244,7 +47245,7 @@
         <v>5</v>
       </c>
       <c r="J327">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K327">
         <v>2</v>
@@ -47301,7 +47302,7 @@
         <v>6</v>
       </c>
       <c r="J328">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K328">
         <v>2</v>
@@ -47358,7 +47359,7 @@
         <v>7</v>
       </c>
       <c r="J329">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K329">
         <v>3</v>
@@ -47415,7 +47416,7 @@
         <v>8</v>
       </c>
       <c r="J330">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K330">
         <v>3</v>
@@ -47472,7 +47473,7 @@
         <v>9</v>
       </c>
       <c r="J331">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K331">
         <v>3</v>
@@ -47529,7 +47530,7 @@
         <v>10</v>
       </c>
       <c r="J332">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K332">
         <v>3</v>
@@ -47579,8 +47580,8 @@
       <c r="G333">
         <v>200</v>
       </c>
-      <c r="H333" t="s">
-        <v>1081</v>
+      <c r="H333" s="3" t="s">
+        <v>1083</v>
       </c>
       <c r="I333">
         <v>0</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{630FFE6B-30B5-406E-89C9-947ECD374EFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D019DBC-4C57-4A3E-AC33-BC7CED289242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1840" uniqueCount="1084">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1850" uniqueCount="1088">
   <si>
     <t>編號</t>
   </si>
@@ -2610,9 +2610,6 @@
     <t>普通</t>
   </si>
   <si>
-    <t>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數。</t>
-  </si>
-  <si>
     <t>精良</t>
   </si>
   <si>
@@ -2773,9 +2770,6 @@
   </si>
   <si>
     <t>混沌</t>
-  </si>
-  <si>
-    <t>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數；倍率與分解係數為暫定值，可調整。</t>
   </si>
   <si>
     <t>神鑄混沌</t>
@@ -4051,6 +4045,26 @@
   </si>
   <si>
     <t>{elemDmgFire,elemDmgIce,elemDmgLightning,elemDmgPoison,elemDmgLight,elemDmgDark,elemDmgEarth,elemDmgWind,resFire,resIce,resLightning,resPoison,resLight,resDark,resEarth,resWind,resAll}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）；倍率與分解係數為暫定值，可調整。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5255,7 +5269,7 @@
         <v>基礎a + 技能熟練度等級 + 潛力天賦加成</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="G11">
         <f>計算表!G11</f>
@@ -5698,7 +5712,7 @@
         <v>（查表）</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G17">
         <f>計算表!G17</f>
@@ -5771,7 +5785,7 @@
         <v>（查表）</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G18">
         <f>計算表!G18</f>
@@ -5844,7 +5858,7 @@
         <v>（查表）</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G19">
         <f>計算表!G19</f>
@@ -5917,7 +5931,7 @@
         <v>（查表）</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G20">
         <f>計算表!G20</f>
@@ -5990,7 +6004,7 @@
         <v>（查表）</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G21">
         <f>計算表!G21</f>
@@ -6063,7 +6077,7 @@
         <v>（查表）</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G22">
         <f>計算表!G22</f>
@@ -6136,7 +6150,7 @@
         <v>（查表）</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G23">
         <f>計算表!G23</f>
@@ -6209,7 +6223,7 @@
         <v>（查表）</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G24">
         <f>計算表!G24</f>
@@ -6282,7 +6296,7 @@
         <v>（查表）</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G25">
         <f>計算表!G25</f>
@@ -6355,7 +6369,7 @@
         <v>（查表）</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G26">
         <f>計算表!G26</f>
@@ -6428,7 +6442,7 @@
         <v>（查表）</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G27">
         <f>計算表!G27</f>
@@ -6501,7 +6515,7 @@
         <v>（查表）</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G28">
         <f>計算表!G28</f>
@@ -6574,7 +6588,7 @@
         <v>（查表）</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G29">
         <f>計算表!G29</f>
@@ -6647,7 +6661,7 @@
         <v>（查表）</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G30">
         <f>計算表!G30</f>
@@ -6720,7 +6734,7 @@
         <v>（查表）</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G31">
         <f>計算表!G31</f>
@@ -6793,7 +6807,7 @@
         <v>（查表）</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G32">
         <f>計算表!G32</f>
@@ -6866,7 +6880,7 @@
         <v>（查表）</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G33">
         <f>計算表!G33</f>
@@ -6939,7 +6953,7 @@
         <v>（查表）</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G34">
         <f>計算表!G34</f>
@@ -7012,7 +7026,7 @@
         <v>（查表）</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G35">
         <f>計算表!G35</f>
@@ -7085,7 +7099,7 @@
         <v>（查表）</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G36">
         <f>計算表!G36</f>
@@ -7158,7 +7172,7 @@
         <v>（查表）</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="G37">
         <f>計算表!G37</f>
@@ -8867,7 +8881,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="I60">
         <f>計算表!I60</f>
@@ -9236,7 +9250,7 @@
         <v>5</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="I65">
         <f>計算表!I65</f>
@@ -9309,7 +9323,7 @@
         <v>0.875</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="I66">
         <f>計算表!I66</f>
@@ -9600,7 +9614,7 @@
         <v>a=每點敏捷%。</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="H70">
         <f>計算表!H70</f>
@@ -11519,7 +11533,7 @@
         <v>忽略敵人防禦% = 穿透%/(穿透%+a)</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="G96">
         <f>計算表!G96</f>
@@ -13306,7 +13320,7 @@
         <v>0.5</v>
       </c>
       <c r="I120" s="7" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="J120">
         <f>計算表!J120</f>
@@ -15221,7 +15235,7 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條。</v>
       </c>
       <c r="G146" s="7" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="H146">
         <f>計算表!H146</f>
@@ -15294,13 +15308,13 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條。</v>
       </c>
       <c r="G147" s="7" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H147" s="7" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I147" s="7" t="s">
         <v>1027</v>
-      </c>
-      <c r="H147" s="7" t="s">
-        <v>1028</v>
-      </c>
-      <c r="I147" s="7" t="s">
-        <v>1029</v>
       </c>
       <c r="J147">
         <f>計算表!J147</f>
@@ -15365,20 +15379,20 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條。</v>
       </c>
       <c r="G148" s="7" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="H148" s="7" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="I148">
         <f>計算表!I148</f>
         <v>9.11754</v>
       </c>
       <c r="J148" s="7" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="K148" s="7" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
       <c r="L148">
         <f>計算表!L148</f>
@@ -15435,22 +15449,22 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條。</v>
       </c>
       <c r="G149" s="7" t="s">
+        <v>1032</v>
+      </c>
+      <c r="H149" s="7" t="s">
+        <v>1033</v>
+      </c>
+      <c r="I149" s="7" t="s">
         <v>1034</v>
       </c>
-      <c r="H149" s="7" t="s">
+      <c r="J149" s="7" t="s">
         <v>1035</v>
       </c>
-      <c r="I149" s="7" t="s">
+      <c r="K149" s="7" t="s">
         <v>1036</v>
       </c>
-      <c r="J149" s="7" t="s">
+      <c r="L149" s="7" t="s">
         <v>1037</v>
-      </c>
-      <c r="K149" s="7" t="s">
-        <v>1038</v>
-      </c>
-      <c r="L149" s="7" t="s">
-        <v>1039</v>
       </c>
       <c r="M149">
         <f>計算表!M149</f>
@@ -15503,28 +15517,28 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條。</v>
       </c>
       <c r="G150" s="7" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H150" s="7" t="s">
+        <v>1039</v>
+      </c>
+      <c r="I150" s="7" t="s">
         <v>1040</v>
       </c>
-      <c r="H150" s="7" t="s">
+      <c r="J150" s="7" t="s">
         <v>1041</v>
       </c>
-      <c r="I150" s="7" t="s">
+      <c r="K150" s="7" t="s">
         <v>1042</v>
       </c>
-      <c r="J150" s="7" t="s">
+      <c r="L150" s="7" t="s">
         <v>1043</v>
       </c>
-      <c r="K150" s="7" t="s">
+      <c r="M150" s="7" t="s">
         <v>1044</v>
       </c>
-      <c r="L150" s="7" t="s">
+      <c r="N150" s="7" t="s">
         <v>1045</v>
-      </c>
-      <c r="M150" s="7" t="s">
-        <v>1046</v>
-      </c>
-      <c r="N150" s="7" t="s">
-        <v>1047</v>
       </c>
       <c r="O150">
         <f>計算表!O150</f>
@@ -15569,28 +15583,28 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條。</v>
       </c>
       <c r="G151" s="7" t="s">
+        <v>1046</v>
+      </c>
+      <c r="H151" s="7" t="s">
+        <v>1047</v>
+      </c>
+      <c r="I151" s="7" t="s">
         <v>1048</v>
       </c>
-      <c r="H151" s="7" t="s">
+      <c r="J151" s="7" t="s">
         <v>1049</v>
       </c>
-      <c r="I151" s="7" t="s">
+      <c r="K151" s="7" t="s">
         <v>1050</v>
       </c>
-      <c r="J151" s="7" t="s">
+      <c r="L151" s="7" t="s">
         <v>1051</v>
       </c>
-      <c r="K151" s="7" t="s">
+      <c r="M151" s="7" t="s">
         <v>1052</v>
       </c>
-      <c r="L151" s="7" t="s">
+      <c r="N151" s="7" t="s">
         <v>1053</v>
-      </c>
-      <c r="M151" s="7" t="s">
-        <v>1054</v>
-      </c>
-      <c r="N151" s="7" t="s">
-        <v>1055</v>
       </c>
       <c r="O151">
         <f>計算表!O151</f>
@@ -15635,31 +15649,31 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條 j=9條。</v>
       </c>
       <c r="G152" s="7" t="s">
+        <v>1054</v>
+      </c>
+      <c r="H152" s="7" t="s">
+        <v>1055</v>
+      </c>
+      <c r="I152" s="7" t="s">
         <v>1056</v>
       </c>
-      <c r="H152" s="7" t="s">
+      <c r="J152" s="7" t="s">
         <v>1057</v>
       </c>
-      <c r="I152" s="7" t="s">
+      <c r="K152" s="7" t="s">
         <v>1058</v>
       </c>
-      <c r="J152" s="7" t="s">
+      <c r="L152" s="7" t="s">
         <v>1059</v>
       </c>
-      <c r="K152" s="7" t="s">
+      <c r="M152" s="7" t="s">
         <v>1060</v>
       </c>
-      <c r="L152" s="7" t="s">
+      <c r="N152" s="7" t="s">
         <v>1061</v>
       </c>
-      <c r="M152" s="7" t="s">
+      <c r="O152" s="7" t="s">
         <v>1062</v>
-      </c>
-      <c r="N152" s="7" t="s">
-        <v>1063</v>
-      </c>
-      <c r="O152" s="7" t="s">
-        <v>1064</v>
       </c>
       <c r="P152">
         <f>計算表!P152</f>
@@ -15700,7 +15714,7 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條 j=9條 k=10條。</v>
       </c>
       <c r="G153" s="7" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="H153">
         <f>計算表!H153</f>
@@ -17183,7 +17197,7 @@
         <v>200</v>
       </c>
       <c r="H173" s="7" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="I173">
         <f>計算表!I173</f>
@@ -17770,7 +17784,7 @@
         <v>a=基礎權重 b=權重加成 c=加成上限 d=出現門檻。普通無加成。神鑄創世不參與此擲骰。(裝備合成才有作用，目前功能關閉中)</v>
       </c>
       <c r="G181" s="7" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="H181" t="str">
         <f>計算表!H181</f>
@@ -20589,7 +20603,7 @@
         <v>1</v>
       </c>
       <c r="I219" s="7" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="J219">
         <f>計算表!J220</f>
@@ -25604,10 +25618,10 @@
         <v>等級上限</v>
       </c>
       <c r="E287" s="7" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="F287" s="7" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G287">
         <f>計算表!G291</f>
@@ -27013,7 +27027,7 @@
       </c>
       <c r="F306" t="str">
         <f>計算表!F322</f>
-        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數。</v>
+        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）。</v>
       </c>
       <c r="G306">
         <f>計算表!G322</f>
@@ -27087,7 +27101,7 @@
       </c>
       <c r="F307" t="str">
         <f>計算表!F323</f>
-        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數。</v>
+        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）。</v>
       </c>
       <c r="G307">
         <f>計算表!G323</f>
@@ -27113,9 +27127,9 @@
         <f>計算表!L323</f>
         <v>1.7</v>
       </c>
-      <c r="M307">
+      <c r="M307" t="str">
         <f>計算表!M323</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N307">
         <f>計算表!N323</f>
@@ -27161,7 +27175,7 @@
       </c>
       <c r="F308" t="str">
         <f>計算表!F324</f>
-        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數。</v>
+        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）。</v>
       </c>
       <c r="G308">
         <f>計算表!G324</f>
@@ -27187,9 +27201,9 @@
         <f>計算表!L324</f>
         <v>2.8</v>
       </c>
-      <c r="M308">
+      <c r="M308" t="str">
         <f>計算表!M324</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N308">
         <f>計算表!N324</f>
@@ -27235,10 +27249,10 @@
       </c>
       <c r="F309" t="str">
         <f>計算表!F325</f>
-        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數。</v>
+        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）。</v>
       </c>
       <c r="G309" s="7" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="H309">
         <f>計算表!H325</f>
@@ -27260,9 +27274,9 @@
         <f>計算表!L325</f>
         <v>4.5</v>
       </c>
-      <c r="M309">
+      <c r="M309" t="str">
         <f>計算表!M325</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N309">
         <f>計算表!N325</f>
@@ -27308,7 +27322,7 @@
       </c>
       <c r="F310" t="str">
         <f>計算表!F326</f>
-        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數。</v>
+        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）。</v>
       </c>
       <c r="G310">
         <f>計算表!G326</f>
@@ -27334,9 +27348,9 @@
         <f>計算表!L326</f>
         <v>7.5</v>
       </c>
-      <c r="M310">
+      <c r="M310" t="str">
         <f>計算表!M326</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N310">
         <f>計算表!N326</f>
@@ -27382,7 +27396,7 @@
       </c>
       <c r="F311" t="str">
         <f>計算表!F327</f>
-        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數。</v>
+        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）。</v>
       </c>
       <c r="G311">
         <f>計算表!G327</f>
@@ -27408,9 +27422,9 @@
         <f>計算表!L327</f>
         <v>12</v>
       </c>
-      <c r="M311">
+      <c r="M311" t="str">
         <f>計算表!M327</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N311">
         <f>計算表!N327</f>
@@ -27456,7 +27470,7 @@
       </c>
       <c r="F312" t="str">
         <f>計算表!F328</f>
-        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數。</v>
+        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）。</v>
       </c>
       <c r="G312">
         <f>計算表!G328</f>
@@ -27482,9 +27496,9 @@
         <f>計算表!L328</f>
         <v>19</v>
       </c>
-      <c r="M312">
+      <c r="M312" t="str">
         <f>計算表!M328</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N312">
         <f>計算表!N328</f>
@@ -27530,7 +27544,7 @@
       </c>
       <c r="F313" t="str">
         <f>計算表!F329</f>
-        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數。</v>
+        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）。</v>
       </c>
       <c r="G313">
         <f>計算表!G329</f>
@@ -27556,9 +27570,9 @@
         <f>計算表!L329</f>
         <v>30</v>
       </c>
-      <c r="M313">
+      <c r="M313" t="str">
         <f>計算表!M329</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N313">
         <f>計算表!N329</f>
@@ -27604,10 +27618,10 @@
       </c>
       <c r="F314" t="str">
         <f>計算表!F330</f>
-        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數。</v>
+        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）。</v>
       </c>
       <c r="G314" s="7" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="H314">
         <f>計算表!H330</f>
@@ -27629,9 +27643,9 @@
         <f>計算表!L330</f>
         <v>45</v>
       </c>
-      <c r="M314">
+      <c r="M314" t="str">
         <f>計算表!M330</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N314">
         <f>計算表!N330</f>
@@ -27677,7 +27691,7 @@
       </c>
       <c r="F315" t="str">
         <f>計算表!F331</f>
-        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數；倍率與分解係數為暫定值，可調整。</v>
+        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）；倍率與分解係數為暫定值，可調整。</v>
       </c>
       <c r="G315">
         <f>計算表!G331</f>
@@ -27703,9 +27717,9 @@
         <f>計算表!L331</f>
         <v>67.5</v>
       </c>
-      <c r="M315">
+      <c r="M315" t="str">
         <f>計算表!M331</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N315">
         <f>計算表!N331</f>
@@ -27751,7 +27765,7 @@
       </c>
       <c r="F316" t="str">
         <f>計算表!F332</f>
-        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數；倍率與分解係數為暫定值，可調整。</v>
+        <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）；倍率與分解係數為暫定值，可調整。</v>
       </c>
       <c r="G316">
         <f>計算表!G332</f>
@@ -27777,9 +27791,9 @@
         <f>計算表!L332</f>
         <v>101.25</v>
       </c>
-      <c r="M316">
+      <c r="M316" t="str">
         <f>計算表!M332</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N316">
         <f>計算表!N332</f>
@@ -27959,16 +27973,16 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
+        <v>948</v>
+      </c>
+      <c r="D2" t="s">
+        <v>949</v>
+      </c>
+      <c r="E2" t="s">
         <v>950</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>951</v>
-      </c>
-      <c r="E2" t="s">
-        <v>952</v>
-      </c>
-      <c r="F2" t="s">
-        <v>953</v>
       </c>
       <c r="G2">
         <v>50000</v>
@@ -28016,16 +28030,16 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
+        <v>948</v>
+      </c>
+      <c r="D3" t="s">
+        <v>952</v>
+      </c>
+      <c r="E3" t="s">
         <v>950</v>
       </c>
-      <c r="D3" t="s">
-        <v>954</v>
-      </c>
-      <c r="E3" t="s">
-        <v>952</v>
-      </c>
       <c r="F3" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="G3">
         <v>500</v>
@@ -28073,16 +28087,16 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
+        <v>948</v>
+      </c>
+      <c r="D4" t="s">
+        <v>954</v>
+      </c>
+      <c r="E4" t="s">
         <v>950</v>
       </c>
-      <c r="D4" t="s">
-        <v>956</v>
-      </c>
-      <c r="E4" t="s">
-        <v>952</v>
-      </c>
       <c r="F4" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -28703,13 +28717,13 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
+        <v>922</v>
+      </c>
+      <c r="E15" t="s">
+        <v>923</v>
+      </c>
+      <c r="F15" t="s">
         <v>924</v>
-      </c>
-      <c r="E15" t="s">
-        <v>925</v>
-      </c>
-      <c r="F15" t="s">
-        <v>926</v>
       </c>
       <c r="G15">
         <v>30</v>
@@ -28760,13 +28774,13 @@
         <v>18</v>
       </c>
       <c r="D16" t="s">
+        <v>925</v>
+      </c>
+      <c r="E16" t="s">
+        <v>926</v>
+      </c>
+      <c r="F16" t="s">
         <v>927</v>
-      </c>
-      <c r="E16" t="s">
-        <v>928</v>
-      </c>
-      <c r="F16" t="s">
-        <v>929</v>
       </c>
       <c r="G16">
         <v>1000</v>
@@ -30305,7 +30319,7 @@
         <v>149</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -30362,7 +30376,7 @@
         <v>149</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -31727,10 +31741,10 @@
         <v>134</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="G68">
         <v>0.86</v>
@@ -31955,10 +31969,10 @@
         <v>143</v>
       </c>
       <c r="E72" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="F72" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="G72">
         <v>5</v>
@@ -32810,10 +32824,10 @@
         <v>209</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="G87">
         <v>10</v>
@@ -33320,13 +33334,13 @@
         <v>188</v>
       </c>
       <c r="D96" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>957</v>
+      </c>
+      <c r="F96" s="2" t="s">
         <v>958</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>959</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>960</v>
       </c>
       <c r="G96">
         <v>0.75</v>
@@ -35087,7 +35101,7 @@
         <v>245</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="E127" t="s">
         <v>272</v>
@@ -35144,7 +35158,7 @@
         <v>274</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="E128" t="s">
         <v>275</v>
@@ -35201,7 +35215,7 @@
         <v>274</v>
       </c>
       <c r="D129" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="E129" t="s">
         <v>275</v>
@@ -35258,7 +35272,7 @@
         <v>274</v>
       </c>
       <c r="D130" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="E130" t="s">
         <v>275</v>
@@ -35315,7 +35329,7 @@
         <v>274</v>
       </c>
       <c r="D131" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="E131" t="s">
         <v>275</v>
@@ -35372,7 +35386,7 @@
         <v>274</v>
       </c>
       <c r="D132" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="E132" t="s">
         <v>275</v>
@@ -35381,7 +35395,7 @@
         <v>276</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="H132" t="s">
         <v>288</v>
@@ -35390,7 +35404,7 @@
         <v>289</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="K132">
         <v>0</v>
@@ -35429,7 +35443,7 @@
         <v>274</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="E133" t="s">
         <v>275</v>
@@ -35438,19 +35452,19 @@
         <v>276</v>
       </c>
       <c r="G133" s="3" t="s">
+        <v>1004</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I133" s="3" t="s">
+        <v>1003</v>
+      </c>
+      <c r="J133" s="3" t="s">
         <v>1006</v>
       </c>
-      <c r="H133" s="3" t="s">
+      <c r="K133" s="3" t="s">
         <v>1007</v>
-      </c>
-      <c r="I133" s="3" t="s">
-        <v>1005</v>
-      </c>
-      <c r="J133" s="3" t="s">
-        <v>1008</v>
-      </c>
-      <c r="K133" s="3" t="s">
-        <v>1009</v>
       </c>
       <c r="L133">
         <v>0</v>
@@ -35486,7 +35500,7 @@
         <v>274</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="E134" t="s">
         <v>275</v>
@@ -35495,22 +35509,22 @@
         <v>276</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="K134" s="3" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="M134">
         <v>0</v>
@@ -35543,7 +35557,7 @@
         <v>274</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="E135" t="s">
         <v>275</v>
@@ -35600,7 +35614,7 @@
         <v>274</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="E136" t="s">
         <v>275</v>
@@ -35609,13 +35623,13 @@
         <v>290</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="J136">
         <v>0</v>
@@ -35657,7 +35671,7 @@
         <v>274</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="E137" t="s">
         <v>275</v>
@@ -35666,19 +35680,19 @@
         <v>290</v>
       </c>
       <c r="G137" s="3" t="s">
+        <v>971</v>
+      </c>
+      <c r="H137" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="I137" s="3" t="s">
         <v>973</v>
       </c>
-      <c r="H137" s="3" t="s">
+      <c r="J137" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="K137" s="3" t="s">
         <v>974</v>
-      </c>
-      <c r="I137" s="3" t="s">
-        <v>975</v>
-      </c>
-      <c r="J137" s="3" t="s">
-        <v>977</v>
-      </c>
-      <c r="K137" s="3" t="s">
-        <v>976</v>
       </c>
       <c r="L137">
         <v>0</v>
@@ -35714,7 +35728,7 @@
         <v>274</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="E138" t="s">
         <v>275</v>
@@ -35723,25 +35737,25 @@
         <v>290</v>
       </c>
       <c r="G138" s="3" t="s">
+        <v>986</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>987</v>
+      </c>
+      <c r="I138" s="3" t="s">
         <v>988</v>
       </c>
-      <c r="H138" s="3" t="s">
+      <c r="J138" s="3" t="s">
         <v>989</v>
       </c>
-      <c r="I138" s="3" t="s">
+      <c r="K138" s="3" t="s">
         <v>990</v>
       </c>
-      <c r="J138" s="3" t="s">
+      <c r="L138" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="K138" s="3" t="s">
+      <c r="M138" s="3" t="s">
         <v>992</v>
-      </c>
-      <c r="L138" s="3" t="s">
-        <v>993</v>
-      </c>
-      <c r="M138" s="3" t="s">
-        <v>994</v>
       </c>
       <c r="N138">
         <v>0</v>
@@ -35771,7 +35785,7 @@
         <v>274</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="E139" t="s">
         <v>275</v>
@@ -35780,25 +35794,25 @@
         <v>290</v>
       </c>
       <c r="G139" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="H139" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="I139" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="J139" s="3" t="s">
         <v>981</v>
       </c>
-      <c r="H139" s="3" t="s">
+      <c r="K139" s="3" t="s">
         <v>982</v>
       </c>
-      <c r="I139" s="3" t="s">
-        <v>980</v>
-      </c>
-      <c r="J139" s="3" t="s">
+      <c r="L139" s="3" t="s">
         <v>983</v>
       </c>
-      <c r="K139" s="3" t="s">
+      <c r="M139" s="3" t="s">
         <v>984</v>
-      </c>
-      <c r="L139" s="3" t="s">
-        <v>985</v>
-      </c>
-      <c r="M139" s="3" t="s">
-        <v>986</v>
       </c>
       <c r="N139">
         <v>0</v>
@@ -38336,13 +38350,13 @@
         <v>532</v>
       </c>
       <c r="D184" t="s">
+        <v>945</v>
+      </c>
+      <c r="E184" t="s">
+        <v>946</v>
+      </c>
+      <c r="F184" t="s">
         <v>947</v>
-      </c>
-      <c r="E184" t="s">
-        <v>948</v>
-      </c>
-      <c r="F184" t="s">
-        <v>949</v>
       </c>
       <c r="G184">
         <v>0.1</v>
@@ -39020,13 +39034,13 @@
         <v>539</v>
       </c>
       <c r="D196" t="s">
+        <v>913</v>
+      </c>
+      <c r="E196" t="s">
+        <v>914</v>
+      </c>
+      <c r="F196" t="s">
         <v>915</v>
-      </c>
-      <c r="E196" t="s">
-        <v>916</v>
-      </c>
-      <c r="F196" t="s">
-        <v>917</v>
       </c>
       <c r="G196">
         <v>20</v>
@@ -39077,13 +39091,13 @@
         <v>539</v>
       </c>
       <c r="D197" t="s">
+        <v>916</v>
+      </c>
+      <c r="E197" t="s">
+        <v>917</v>
+      </c>
+      <c r="F197" t="s">
         <v>918</v>
-      </c>
-      <c r="E197" t="s">
-        <v>919</v>
-      </c>
-      <c r="F197" t="s">
-        <v>920</v>
       </c>
       <c r="G197">
         <v>500000000</v>
@@ -39134,13 +39148,13 @@
         <v>539</v>
       </c>
       <c r="D198" t="s">
+        <v>919</v>
+      </c>
+      <c r="E198" t="s">
+        <v>920</v>
+      </c>
+      <c r="F198" t="s">
         <v>921</v>
-      </c>
-      <c r="E198" t="s">
-        <v>922</v>
-      </c>
-      <c r="F198" t="s">
-        <v>923</v>
       </c>
       <c r="G198">
         <v>13</v>
@@ -39890,7 +39904,7 @@
         <v>609</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="F211" t="s">
         <v>610</v>
@@ -45061,10 +45075,10 @@
         <v>804</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="F289" t="s">
         <v>820</v>
@@ -45574,13 +45588,13 @@
         <v>829</v>
       </c>
       <c r="D298" t="s">
+        <v>928</v>
+      </c>
+      <c r="E298" t="s">
+        <v>929</v>
+      </c>
+      <c r="F298" t="s">
         <v>930</v>
-      </c>
-      <c r="E298" t="s">
-        <v>931</v>
-      </c>
-      <c r="F298" t="s">
-        <v>932</v>
       </c>
       <c r="G298">
         <v>50000</v>
@@ -45631,13 +45645,13 @@
         <v>829</v>
       </c>
       <c r="D299" t="s">
+        <v>931</v>
+      </c>
+      <c r="E299" t="s">
+        <v>932</v>
+      </c>
+      <c r="F299" t="s">
         <v>933</v>
-      </c>
-      <c r="E299" t="s">
-        <v>934</v>
-      </c>
-      <c r="F299" t="s">
-        <v>935</v>
       </c>
       <c r="G299">
         <v>10</v>
@@ -45688,13 +45702,13 @@
         <v>829</v>
       </c>
       <c r="D300" t="s">
+        <v>934</v>
+      </c>
+      <c r="E300" t="s">
+        <v>935</v>
+      </c>
+      <c r="F300" t="s">
         <v>936</v>
-      </c>
-      <c r="E300" t="s">
-        <v>937</v>
-      </c>
-      <c r="F300" t="s">
-        <v>938</v>
       </c>
       <c r="G300">
         <v>75</v>
@@ -45745,13 +45759,13 @@
         <v>829</v>
       </c>
       <c r="D301" t="s">
+        <v>937</v>
+      </c>
+      <c r="E301" t="s">
+        <v>938</v>
+      </c>
+      <c r="F301" t="s">
         <v>939</v>
-      </c>
-      <c r="E301" t="s">
-        <v>940</v>
-      </c>
-      <c r="F301" t="s">
-        <v>941</v>
       </c>
       <c r="G301">
         <v>25</v>
@@ -45802,13 +45816,13 @@
         <v>829</v>
       </c>
       <c r="D302" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="E302" t="s">
         <v>594</v>
       </c>
       <c r="F302" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="G302">
         <v>5</v>
@@ -45859,13 +45873,13 @@
         <v>829</v>
       </c>
       <c r="D303" t="s">
+        <v>942</v>
+      </c>
+      <c r="E303" t="s">
+        <v>943</v>
+      </c>
+      <c r="F303" t="s">
         <v>944</v>
-      </c>
-      <c r="E303" t="s">
-        <v>945</v>
-      </c>
-      <c r="F303" t="s">
-        <v>946</v>
       </c>
       <c r="G303">
         <v>0.6</v>
@@ -45913,16 +45927,16 @@
         <v>0</v>
       </c>
       <c r="C304" t="s">
+        <v>866</v>
+      </c>
+      <c r="D304" t="s">
         <v>867</v>
       </c>
-      <c r="D304" t="s">
+      <c r="E304" t="s">
         <v>868</v>
       </c>
-      <c r="E304" t="s">
+      <c r="F304" t="s">
         <v>869</v>
-      </c>
-      <c r="F304" t="s">
-        <v>870</v>
       </c>
       <c r="G304">
         <v>25</v>
@@ -45931,7 +45945,7 @@
         <v>25</v>
       </c>
       <c r="I304" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="J304">
         <v>0</v>
@@ -45970,16 +45984,16 @@
         <v>0</v>
       </c>
       <c r="C305" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D305" t="s">
+        <v>871</v>
+      </c>
+      <c r="E305" t="s">
+        <v>868</v>
+      </c>
+      <c r="F305" t="s">
         <v>872</v>
-      </c>
-      <c r="E305" t="s">
-        <v>869</v>
-      </c>
-      <c r="F305" t="s">
-        <v>873</v>
       </c>
       <c r="G305">
         <v>20</v>
@@ -45988,7 +46002,7 @@
         <v>20</v>
       </c>
       <c r="I305" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="J305">
         <v>0</v>
@@ -46027,16 +46041,16 @@
         <v>0</v>
       </c>
       <c r="C306" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D306" t="s">
+        <v>873</v>
+      </c>
+      <c r="E306" t="s">
+        <v>868</v>
+      </c>
+      <c r="F306" t="s">
         <v>874</v>
-      </c>
-      <c r="E306" t="s">
-        <v>869</v>
-      </c>
-      <c r="F306" t="s">
-        <v>875</v>
       </c>
       <c r="G306">
         <v>3</v>
@@ -46045,7 +46059,7 @@
         <v>1.5</v>
       </c>
       <c r="I306" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="J306">
         <v>0</v>
@@ -46084,16 +46098,16 @@
         <v>0</v>
       </c>
       <c r="C307" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D307" t="s">
+        <v>875</v>
+      </c>
+      <c r="E307" t="s">
+        <v>868</v>
+      </c>
+      <c r="F307" t="s">
         <v>876</v>
-      </c>
-      <c r="E307" t="s">
-        <v>869</v>
-      </c>
-      <c r="F307" t="s">
-        <v>877</v>
       </c>
       <c r="G307">
         <v>20</v>
@@ -46102,7 +46116,7 @@
         <v>20</v>
       </c>
       <c r="I307" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="J307">
         <v>0</v>
@@ -46141,16 +46155,16 @@
         <v>0</v>
       </c>
       <c r="C308" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D308" t="s">
+        <v>877</v>
+      </c>
+      <c r="E308" t="s">
+        <v>868</v>
+      </c>
+      <c r="F308" t="s">
         <v>878</v>
-      </c>
-      <c r="E308" t="s">
-        <v>869</v>
-      </c>
-      <c r="F308" t="s">
-        <v>879</v>
       </c>
       <c r="G308">
         <v>3</v>
@@ -46159,7 +46173,7 @@
         <v>1.5</v>
       </c>
       <c r="I308" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="J308">
         <v>0</v>
@@ -46198,16 +46212,16 @@
         <v>0</v>
       </c>
       <c r="C309" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D309" t="s">
+        <v>879</v>
+      </c>
+      <c r="E309" t="s">
+        <v>868</v>
+      </c>
+      <c r="F309" t="s">
         <v>880</v>
-      </c>
-      <c r="E309" t="s">
-        <v>869</v>
-      </c>
-      <c r="F309" t="s">
-        <v>881</v>
       </c>
       <c r="G309">
         <v>3</v>
@@ -46216,7 +46230,7 @@
         <v>1.5</v>
       </c>
       <c r="I309" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="J309">
         <v>0</v>
@@ -46255,16 +46269,16 @@
         <v>0</v>
       </c>
       <c r="C310" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D310" t="s">
+        <v>881</v>
+      </c>
+      <c r="E310" t="s">
+        <v>868</v>
+      </c>
+      <c r="F310" t="s">
         <v>882</v>
-      </c>
-      <c r="E310" t="s">
-        <v>869</v>
-      </c>
-      <c r="F310" t="s">
-        <v>883</v>
       </c>
       <c r="G310">
         <v>3</v>
@@ -46273,7 +46287,7 @@
         <v>1.5</v>
       </c>
       <c r="I310" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="J310">
         <v>0</v>
@@ -46312,16 +46326,16 @@
         <v>0</v>
       </c>
       <c r="C311" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D311" t="s">
+        <v>883</v>
+      </c>
+      <c r="E311" t="s">
+        <v>868</v>
+      </c>
+      <c r="F311" t="s">
         <v>884</v>
-      </c>
-      <c r="E311" t="s">
-        <v>869</v>
-      </c>
-      <c r="F311" t="s">
-        <v>885</v>
       </c>
       <c r="G311">
         <v>25</v>
@@ -46330,7 +46344,7 @@
         <v>25</v>
       </c>
       <c r="I311" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="J311">
         <v>0</v>
@@ -46369,16 +46383,16 @@
         <v>0</v>
       </c>
       <c r="C312" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D312" t="s">
+        <v>885</v>
+      </c>
+      <c r="E312" t="s">
+        <v>868</v>
+      </c>
+      <c r="F312" t="s">
         <v>886</v>
-      </c>
-      <c r="E312" t="s">
-        <v>869</v>
-      </c>
-      <c r="F312" t="s">
-        <v>887</v>
       </c>
       <c r="G312">
         <v>5</v>
@@ -46387,7 +46401,7 @@
         <v>2.5</v>
       </c>
       <c r="I312" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="J312">
         <v>0</v>
@@ -46426,19 +46440,19 @@
         <v>0</v>
       </c>
       <c r="C313" t="s">
+        <v>887</v>
+      </c>
+      <c r="D313" t="s">
         <v>888</v>
       </c>
-      <c r="D313" t="s">
+      <c r="E313" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="F313" t="s">
         <v>889</v>
       </c>
-      <c r="E313" s="3" t="s">
-        <v>995</v>
-      </c>
-      <c r="F313" t="s">
-        <v>890</v>
-      </c>
       <c r="G313" s="3" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="H313">
         <v>3</v>
@@ -46483,16 +46497,16 @@
         <v>0</v>
       </c>
       <c r="C314" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D314" t="s">
+        <v>890</v>
+      </c>
+      <c r="E314" t="s">
         <v>891</v>
       </c>
-      <c r="E314" t="s">
+      <c r="F314" t="s">
         <v>892</v>
-      </c>
-      <c r="F314" t="s">
-        <v>893</v>
       </c>
       <c r="G314">
         <v>5</v>
@@ -46540,16 +46554,16 @@
         <v>0</v>
       </c>
       <c r="C315" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D315" t="s">
+        <v>893</v>
+      </c>
+      <c r="E315" t="s">
         <v>894</v>
       </c>
-      <c r="E315" t="s">
+      <c r="F315" t="s">
         <v>895</v>
-      </c>
-      <c r="F315" t="s">
-        <v>896</v>
       </c>
       <c r="G315">
         <v>10</v>
@@ -46597,16 +46611,16 @@
         <v>0</v>
       </c>
       <c r="C316" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D316" t="s">
+        <v>896</v>
+      </c>
+      <c r="E316" t="s">
         <v>897</v>
       </c>
-      <c r="E316" t="s">
+      <c r="F316" t="s">
         <v>898</v>
-      </c>
-      <c r="F316" t="s">
-        <v>899</v>
       </c>
       <c r="G316">
         <v>10</v>
@@ -46654,16 +46668,16 @@
         <v>0</v>
       </c>
       <c r="C317" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D317" t="s">
+        <v>899</v>
+      </c>
+      <c r="E317" t="s">
         <v>900</v>
       </c>
-      <c r="E317" t="s">
+      <c r="F317" t="s">
         <v>901</v>
-      </c>
-      <c r="F317" t="s">
-        <v>902</v>
       </c>
       <c r="G317">
         <v>2</v>
@@ -46711,16 +46725,16 @@
         <v>0</v>
       </c>
       <c r="C318" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D318" t="s">
+        <v>902</v>
+      </c>
+      <c r="E318" t="s">
         <v>903</v>
       </c>
-      <c r="E318" t="s">
+      <c r="F318" t="s">
         <v>904</v>
-      </c>
-      <c r="F318" t="s">
-        <v>905</v>
       </c>
       <c r="G318">
         <v>5</v>
@@ -46768,16 +46782,16 @@
         <v>0</v>
       </c>
       <c r="C319" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D319" t="s">
+        <v>905</v>
+      </c>
+      <c r="E319" t="s">
         <v>906</v>
       </c>
-      <c r="E319" t="s">
+      <c r="F319" t="s">
         <v>907</v>
-      </c>
-      <c r="F319" t="s">
-        <v>908</v>
       </c>
       <c r="G319">
         <v>10</v>
@@ -46825,16 +46839,16 @@
         <v>0</v>
       </c>
       <c r="C320" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D320" t="s">
+        <v>908</v>
+      </c>
+      <c r="E320" t="s">
         <v>909</v>
       </c>
-      <c r="E320" t="s">
+      <c r="F320" t="s">
         <v>910</v>
-      </c>
-      <c r="F320" t="s">
-        <v>911</v>
       </c>
       <c r="G320">
         <v>20000</v>
@@ -46882,16 +46896,16 @@
         <v>0</v>
       </c>
       <c r="C321" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D321" t="s">
+        <v>994</v>
+      </c>
+      <c r="E321" t="s">
+        <v>995</v>
+      </c>
+      <c r="F321" s="5" t="s">
         <v>996</v>
-      </c>
-      <c r="E321" t="s">
-        <v>997</v>
-      </c>
-      <c r="F321" s="5" t="s">
-        <v>998</v>
       </c>
       <c r="G321">
         <v>0.35</v>
@@ -46947,8 +46961,8 @@
       <c r="E322" t="s">
         <v>39</v>
       </c>
-      <c r="F322" t="s">
-        <v>858</v>
+      <c r="F322" s="7" t="s">
+        <v>1082</v>
       </c>
       <c r="G322">
         <v>1</v>
@@ -46999,13 +47013,13 @@
         <v>856</v>
       </c>
       <c r="D323" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="E323" t="s">
         <v>39</v>
       </c>
-      <c r="F323" t="s">
-        <v>858</v>
+      <c r="F323" s="7" t="s">
+        <v>1082</v>
       </c>
       <c r="G323">
         <v>1.35</v>
@@ -47025,8 +47039,8 @@
       <c r="L323">
         <v>1.7</v>
       </c>
-      <c r="M323">
-        <v>0</v>
+      <c r="M323" s="7" t="s">
+        <v>1083</v>
       </c>
       <c r="N323">
         <v>0</v>
@@ -47056,13 +47070,13 @@
         <v>856</v>
       </c>
       <c r="D324" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="E324" t="s">
         <v>39</v>
       </c>
-      <c r="F324" t="s">
-        <v>858</v>
+      <c r="F324" s="7" t="s">
+        <v>1082</v>
       </c>
       <c r="G324">
         <v>1.75</v>
@@ -47082,8 +47096,8 @@
       <c r="L324">
         <v>2.8</v>
       </c>
-      <c r="M324">
-        <v>0</v>
+      <c r="M324" s="7" t="s">
+        <v>1083</v>
       </c>
       <c r="N324">
         <v>0</v>
@@ -47113,13 +47127,13 @@
         <v>856</v>
       </c>
       <c r="D325" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="E325" t="s">
         <v>39</v>
       </c>
-      <c r="F325" t="s">
-        <v>858</v>
+      <c r="F325" s="7" t="s">
+        <v>1082</v>
       </c>
       <c r="G325">
         <v>2.2999999999999998</v>
@@ -47139,8 +47153,8 @@
       <c r="L325">
         <v>4.5</v>
       </c>
-      <c r="M325">
-        <v>0</v>
+      <c r="M325" s="7" t="s">
+        <v>1084</v>
       </c>
       <c r="N325">
         <v>0</v>
@@ -47170,13 +47184,13 @@
         <v>856</v>
       </c>
       <c r="D326" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E326" t="s">
         <v>39</v>
       </c>
-      <c r="F326" t="s">
-        <v>858</v>
+      <c r="F326" s="7" t="s">
+        <v>1082</v>
       </c>
       <c r="G326">
         <v>3</v>
@@ -47196,8 +47210,8 @@
       <c r="L326">
         <v>7.5</v>
       </c>
-      <c r="M326">
-        <v>0</v>
+      <c r="M326" s="7" t="s">
+        <v>1085</v>
       </c>
       <c r="N326">
         <v>0</v>
@@ -47227,13 +47241,13 @@
         <v>856</v>
       </c>
       <c r="D327" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E327" t="s">
         <v>39</v>
       </c>
-      <c r="F327" t="s">
-        <v>858</v>
+      <c r="F327" s="7" t="s">
+        <v>1082</v>
       </c>
       <c r="G327">
         <v>4</v>
@@ -47253,8 +47267,8 @@
       <c r="L327">
         <v>12</v>
       </c>
-      <c r="M327">
-        <v>0</v>
+      <c r="M327" s="7" t="s">
+        <v>1086</v>
       </c>
       <c r="N327">
         <v>0</v>
@@ -47284,13 +47298,13 @@
         <v>856</v>
       </c>
       <c r="D328" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="E328" t="s">
         <v>39</v>
       </c>
-      <c r="F328" t="s">
-        <v>858</v>
+      <c r="F328" s="7" t="s">
+        <v>1082</v>
       </c>
       <c r="G328">
         <v>5.2</v>
@@ -47310,8 +47324,8 @@
       <c r="L328">
         <v>19</v>
       </c>
-      <c r="M328">
-        <v>0</v>
+      <c r="M328" s="7" t="s">
+        <v>1086</v>
       </c>
       <c r="N328">
         <v>0</v>
@@ -47341,13 +47355,13 @@
         <v>856</v>
       </c>
       <c r="D329" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E329" t="s">
         <v>39</v>
       </c>
-      <c r="F329" t="s">
-        <v>858</v>
+      <c r="F329" s="7" t="s">
+        <v>1082</v>
       </c>
       <c r="G329">
         <v>6.8</v>
@@ -47367,8 +47381,8 @@
       <c r="L329">
         <v>30</v>
       </c>
-      <c r="M329">
-        <v>0</v>
+      <c r="M329" s="7" t="s">
+        <v>1086</v>
       </c>
       <c r="N329">
         <v>0</v>
@@ -47398,13 +47412,13 @@
         <v>856</v>
       </c>
       <c r="D330" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="E330" t="s">
         <v>39</v>
       </c>
-      <c r="F330" t="s">
-        <v>858</v>
+      <c r="F330" s="7" t="s">
+        <v>1082</v>
       </c>
       <c r="G330">
         <v>10.199999999999999</v>
@@ -47424,8 +47438,8 @@
       <c r="L330">
         <v>45</v>
       </c>
-      <c r="M330">
-        <v>0</v>
+      <c r="M330" s="7" t="s">
+        <v>1086</v>
       </c>
       <c r="N330">
         <v>0</v>
@@ -47455,13 +47469,13 @@
         <v>856</v>
       </c>
       <c r="D331" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E331" t="s">
         <v>39</v>
       </c>
-      <c r="F331" t="s">
-        <v>913</v>
+      <c r="F331" s="7" t="s">
+        <v>1087</v>
       </c>
       <c r="G331">
         <v>15.3</v>
@@ -47481,8 +47495,8 @@
       <c r="L331">
         <v>67.5</v>
       </c>
-      <c r="M331">
-        <v>0</v>
+      <c r="M331" s="7" t="s">
+        <v>1086</v>
       </c>
       <c r="N331">
         <v>0</v>
@@ -47512,13 +47526,13 @@
         <v>856</v>
       </c>
       <c r="D332" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="E332" t="s">
         <v>39</v>
       </c>
-      <c r="F332" t="s">
-        <v>913</v>
+      <c r="F332" s="7" t="s">
+        <v>1087</v>
       </c>
       <c r="G332">
         <v>22.95</v>
@@ -47538,8 +47552,8 @@
       <c r="L332">
         <v>101.25</v>
       </c>
-      <c r="M332">
-        <v>0</v>
+      <c r="M332" s="7" t="s">
+        <v>1086</v>
       </c>
       <c r="N332">
         <v>0</v>
@@ -47566,22 +47580,22 @@
         <v>0</v>
       </c>
       <c r="C333" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D333" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E333" t="s">
         <v>1077</v>
       </c>
-      <c r="D333" t="s">
+      <c r="F333" t="s">
         <v>1078</v>
-      </c>
-      <c r="E333" t="s">
-        <v>1079</v>
-      </c>
-      <c r="F333" t="s">
-        <v>1080</v>
       </c>
       <c r="G333">
         <v>200</v>
       </c>
       <c r="H333" s="3" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="I333">
         <v>0</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\codex-battle-camera-20261008\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6184CB83-15C5-4240-84A8-FE3AD7D88D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEEF74BD-7426-42F7-AC23-8E37417CB467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1968" uniqueCount="1162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1972" uniqueCount="1166">
   <si>
     <t>編號</t>
   </si>
@@ -4289,6 +4289,22 @@
   </si>
   <si>
     <t>菁英出現於階段為 10 的倍數，敵人數量與普通怪一致。〔菁英現在成群出現（可能帶小兵），普通關也會遇到；群的設定見「4-菁英群組」。小兵不吃這一列的倍率。〕</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8-戰鬥畫面</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>戰鬥鏡頭距離</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鏡頭距離=a%；畫面縮放=100÷a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a＝相對原鏡頭距離（%）。100＝原距離；125＝拉遠25%；數值越大視野越廣。套用後重載遊戲，影響野外與BOSS畫面。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4743,7 +4759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R336"/>
+  <dimension ref="A1:R337"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="22.7109375" customWidth="1"/>
@@ -29517,6 +29533,80 @@
       </c>
       <c r="R336">
         <f>計算表!R352</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="337" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A337">
+        <f>計算表!A353</f>
+        <v>352</v>
+      </c>
+      <c r="B337">
+        <f>計算表!B353</f>
+        <v>0</v>
+      </c>
+      <c r="C337" t="str">
+        <f>計算表!C353</f>
+        <v>8-戰鬥畫面</v>
+      </c>
+      <c r="D337" t="str">
+        <f>計算表!D353</f>
+        <v>戰鬥鏡頭距離</v>
+      </c>
+      <c r="E337" t="str">
+        <f>計算表!E353</f>
+        <v>鏡頭距離=a%；畫面縮放=100÷a</v>
+      </c>
+      <c r="F337" t="str">
+        <f>計算表!F353</f>
+        <v>a＝相對原鏡頭距離（%）。100＝原距離；125＝拉遠25%；數值越大視野越廣。套用後重載遊戲，影響野外與BOSS畫面。</v>
+      </c>
+      <c r="G337">
+        <f>計算表!G353</f>
+        <v>125</v>
+      </c>
+      <c r="H337">
+        <f>計算表!H353</f>
+        <v>0</v>
+      </c>
+      <c r="I337">
+        <f>計算表!I353</f>
+        <v>0</v>
+      </c>
+      <c r="J337">
+        <f>計算表!J353</f>
+        <v>0</v>
+      </c>
+      <c r="K337">
+        <f>計算表!K353</f>
+        <v>0</v>
+      </c>
+      <c r="L337">
+        <f>計算表!L353</f>
+        <v>0</v>
+      </c>
+      <c r="M337">
+        <f>計算表!M353</f>
+        <v>0</v>
+      </c>
+      <c r="N337">
+        <f>計算表!N353</f>
+        <v>0</v>
+      </c>
+      <c r="O337">
+        <f>計算表!O353</f>
+        <v>0</v>
+      </c>
+      <c r="P337">
+        <f>計算表!P353</f>
+        <v>0</v>
+      </c>
+      <c r="Q337">
+        <f>計算表!Q353</f>
+        <v>0</v>
+      </c>
+      <c r="R337">
+        <f>計算表!R353</f>
         <v>0</v>
       </c>
     </row>
@@ -29528,7 +29618,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AB352"/>
+  <dimension ref="A1:AB353"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="23.42578125" customWidth="1"/>
@@ -50341,6 +50431,62 @@
         <v>0</v>
       </c>
     </row>
+    <row r="353" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A353">
+        <v>352</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353" t="s">
+        <v>1162</v>
+      </c>
+      <c r="D353" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E353" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F353" t="s">
+        <v>1165</v>
+      </c>
+      <c r="G353">
+        <v>125</v>
+      </c>
+      <c r="H353">
+        <v>0</v>
+      </c>
+      <c r="I353">
+        <v>0</v>
+      </c>
+      <c r="J353">
+        <v>0</v>
+      </c>
+      <c r="K353">
+        <v>0</v>
+      </c>
+      <c r="L353">
+        <v>0</v>
+      </c>
+      <c r="M353">
+        <v>0</v>
+      </c>
+      <c r="N353">
+        <v>0</v>
+      </c>
+      <c r="O353">
+        <v>0</v>
+      </c>
+      <c r="P353">
+        <v>0</v>
+      </c>
+      <c r="Q353">
+        <v>0</v>
+      </c>
+      <c r="R353">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:R332">
     <sortCondition ref="C2:C332"/>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\codex-battle-camera-20261008\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEEF74BD-7426-42F7-AC23-8E37417CB467}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5DA5C8-48A1-40C9-9606-8A07E5F16AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33420" yWindow="2730" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1972" uniqueCount="1166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1962" uniqueCount="1162">
   <si>
     <t>編號</t>
   </si>
@@ -4044,18 +4044,6 @@
   <si>
     <t>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）。</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>4</t>
   </si>
   <si>
     <t>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）；倍率與分解係數為暫定值，可調整。</t>
@@ -27367,7 +27355,7 @@
         <f>計算表!L323</f>
         <v>1.7</v>
       </c>
-      <c r="M307" t="str">
+      <c r="M307">
         <f>計算表!M323</f>
         <v>1</v>
       </c>
@@ -27441,7 +27429,7 @@
         <f>計算表!L324</f>
         <v>2.8</v>
       </c>
-      <c r="M308" t="str">
+      <c r="M308">
         <f>計算表!M324</f>
         <v>1</v>
       </c>
@@ -27514,9 +27502,9 @@
         <f>計算表!L325</f>
         <v>4.5</v>
       </c>
-      <c r="M309" t="str">
+      <c r="M309">
         <f>計算表!M325</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N309">
         <f>計算表!N325</f>
@@ -27588,9 +27576,9 @@
         <f>計算表!L326</f>
         <v>7.5</v>
       </c>
-      <c r="M310" t="str">
+      <c r="M310">
         <f>計算表!M326</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N310">
         <f>計算表!N326</f>
@@ -27662,9 +27650,9 @@
         <f>計算表!L327</f>
         <v>12</v>
       </c>
-      <c r="M311" t="str">
+      <c r="M311">
         <f>計算表!M327</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N311">
         <f>計算表!N327</f>
@@ -27736,9 +27724,9 @@
         <f>計算表!L328</f>
         <v>19</v>
       </c>
-      <c r="M312" t="str">
+      <c r="M312">
         <f>計算表!M328</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N312">
         <f>計算表!N328</f>
@@ -27810,9 +27798,9 @@
         <f>計算表!L329</f>
         <v>30</v>
       </c>
-      <c r="M313" t="str">
+      <c r="M313">
         <f>計算表!M329</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N313">
         <f>計算表!N329</f>
@@ -27883,9 +27871,9 @@
         <f>計算表!L330</f>
         <v>45</v>
       </c>
-      <c r="M314" t="str">
+      <c r="M314">
         <f>計算表!M330</f>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="N314">
         <f>計算表!N330</f>
@@ -27957,7 +27945,7 @@
         <f>計算表!L331</f>
         <v>67.5</v>
       </c>
-      <c r="M315" t="str">
+      <c r="M315">
         <f>計算表!M331</f>
         <v>4</v>
       </c>
@@ -28031,7 +28019,7 @@
         <f>計算表!L332</f>
         <v>101.25</v>
       </c>
-      <c r="M316" t="str">
+      <c r="M316">
         <f>計算表!M332</f>
         <v>4</v>
       </c>
@@ -36770,7 +36758,7 @@
         <v>270</v>
       </c>
       <c r="F126" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="G126">
         <v>4</v>
@@ -37283,7 +37271,7 @@
         <v>274</v>
       </c>
       <c r="F135" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="G135" t="s">
         <v>276</v>
@@ -37340,7 +37328,7 @@
         <v>274</v>
       </c>
       <c r="F136" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>968</v>
@@ -37397,7 +37385,7 @@
         <v>274</v>
       </c>
       <c r="F137" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>969</v>
@@ -37454,7 +37442,7 @@
         <v>274</v>
       </c>
       <c r="F138" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>984</v>
@@ -37511,7 +37499,7 @@
         <v>274</v>
       </c>
       <c r="F139" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>977</v>
@@ -48759,8 +48747,8 @@
       <c r="L323">
         <v>1.7</v>
       </c>
-      <c r="M323" s="7" t="s">
-        <v>1081</v>
+      <c r="M323">
+        <v>1</v>
       </c>
       <c r="N323">
         <v>0</v>
@@ -48816,8 +48804,8 @@
       <c r="L324">
         <v>2.8</v>
       </c>
-      <c r="M324" s="7" t="s">
-        <v>1081</v>
+      <c r="M324">
+        <v>1</v>
       </c>
       <c r="N324">
         <v>0</v>
@@ -48873,8 +48861,8 @@
       <c r="L325">
         <v>4.5</v>
       </c>
-      <c r="M325" s="7" t="s">
-        <v>1082</v>
+      <c r="M325">
+        <v>1</v>
       </c>
       <c r="N325">
         <v>0</v>
@@ -48930,8 +48918,8 @@
       <c r="L326">
         <v>7.5</v>
       </c>
-      <c r="M326" s="7" t="s">
-        <v>1083</v>
+      <c r="M326">
+        <v>2</v>
       </c>
       <c r="N326">
         <v>0</v>
@@ -48987,8 +48975,8 @@
       <c r="L327">
         <v>12</v>
       </c>
-      <c r="M327" s="7" t="s">
-        <v>1084</v>
+      <c r="M327">
+        <v>2</v>
       </c>
       <c r="N327">
         <v>0</v>
@@ -49044,8 +49032,8 @@
       <c r="L328">
         <v>19</v>
       </c>
-      <c r="M328" s="7" t="s">
-        <v>1084</v>
+      <c r="M328">
+        <v>2</v>
       </c>
       <c r="N328">
         <v>0</v>
@@ -49101,8 +49089,8 @@
       <c r="L329">
         <v>30</v>
       </c>
-      <c r="M329" s="7" t="s">
-        <v>1084</v>
+      <c r="M329">
+        <v>3</v>
       </c>
       <c r="N329">
         <v>0</v>
@@ -49158,8 +49146,8 @@
       <c r="L330">
         <v>45</v>
       </c>
-      <c r="M330" s="7" t="s">
-        <v>1084</v>
+      <c r="M330">
+        <v>3</v>
       </c>
       <c r="N330">
         <v>0</v>
@@ -49195,7 +49183,7 @@
         <v>39</v>
       </c>
       <c r="F331" s="7" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="G331">
         <v>15.3</v>
@@ -49215,8 +49203,8 @@
       <c r="L331">
         <v>67.5</v>
       </c>
-      <c r="M331" s="7" t="s">
-        <v>1084</v>
+      <c r="M331">
+        <v>4</v>
       </c>
       <c r="N331">
         <v>0</v>
@@ -49252,7 +49240,7 @@
         <v>39</v>
       </c>
       <c r="F332" s="7" t="s">
-        <v>1085</v>
+        <v>1081</v>
       </c>
       <c r="G332">
         <v>22.95</v>
@@ -49272,8 +49260,8 @@
       <c r="L332">
         <v>101.25</v>
       </c>
-      <c r="M332" s="7" t="s">
-        <v>1084</v>
+      <c r="M332">
+        <v>4</v>
       </c>
       <c r="N332">
         <v>0</v>
@@ -49357,28 +49345,28 @@
         <v>0</v>
       </c>
       <c r="C334" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D334" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E334" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F334" t="s">
+        <v>1085</v>
+      </c>
+      <c r="G334" s="7" t="s">
         <v>1086</v>
       </c>
-      <c r="D334" s="2" t="s">
+      <c r="H334" s="7" t="s">
         <v>1087</v>
       </c>
-      <c r="E334" t="s">
+      <c r="I334" s="7" t="s">
         <v>1088</v>
       </c>
-      <c r="F334" t="s">
+      <c r="J334" s="7" t="s">
         <v>1089</v>
-      </c>
-      <c r="G334" s="7" t="s">
-        <v>1090</v>
-      </c>
-      <c r="H334" s="7" t="s">
-        <v>1091</v>
-      </c>
-      <c r="I334" s="7" t="s">
-        <v>1092</v>
-      </c>
-      <c r="J334" s="7" t="s">
-        <v>1093</v>
       </c>
       <c r="K334">
         <v>0</v>
@@ -49414,22 +49402,22 @@
         <v>0</v>
       </c>
       <c r="C335" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="E335" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="F335" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="G335" s="7" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="H335" s="7" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="I335">
         <v>0</v>
@@ -49471,22 +49459,22 @@
         <v>0</v>
       </c>
       <c r="C336" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>1097</v>
+        <v>1093</v>
       </c>
       <c r="E336" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="F336" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="G336" s="7" t="s">
-        <v>1098</v>
+        <v>1094</v>
       </c>
       <c r="H336" s="7" t="s">
-        <v>1099</v>
+        <v>1095</v>
       </c>
       <c r="I336">
         <v>0</v>
@@ -49528,22 +49516,22 @@
         <v>0</v>
       </c>
       <c r="C337" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>1100</v>
+        <v>1096</v>
       </c>
       <c r="E337" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="F337" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="G337" s="7" t="s">
-        <v>1101</v>
+        <v>1097</v>
       </c>
       <c r="H337" s="7" t="s">
-        <v>1102</v>
+        <v>1098</v>
       </c>
       <c r="I337">
         <v>0</v>
@@ -49585,19 +49573,19 @@
         <v>0</v>
       </c>
       <c r="C338" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>1103</v>
+        <v>1099</v>
       </c>
       <c r="E338" t="s">
-        <v>1088</v>
+        <v>1084</v>
       </c>
       <c r="F338" t="s">
-        <v>1089</v>
+        <v>1085</v>
       </c>
       <c r="G338" s="7" t="s">
-        <v>1104</v>
+        <v>1100</v>
       </c>
       <c r="H338">
         <v>0</v>
@@ -49642,34 +49630,34 @@
         <v>0</v>
       </c>
       <c r="C339" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="D339" s="2" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E339" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F339" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G339" s="7" t="s">
+        <v>1104</v>
+      </c>
+      <c r="H339" s="7" t="s">
         <v>1105</v>
       </c>
-      <c r="E339" t="s">
+      <c r="I339" s="7" t="s">
         <v>1106</v>
       </c>
-      <c r="F339" t="s">
+      <c r="J339" s="7" t="s">
         <v>1107</v>
       </c>
-      <c r="G339" s="7" t="s">
+      <c r="K339" s="7" t="s">
         <v>1108</v>
       </c>
-      <c r="H339" s="7" t="s">
+      <c r="L339" s="7" t="s">
         <v>1109</v>
-      </c>
-      <c r="I339" s="7" t="s">
-        <v>1110</v>
-      </c>
-      <c r="J339" s="7" t="s">
-        <v>1111</v>
-      </c>
-      <c r="K339" s="7" t="s">
-        <v>1112</v>
-      </c>
-      <c r="L339" s="7" t="s">
-        <v>1113</v>
       </c>
       <c r="M339">
         <v>0</v>
@@ -49699,25 +49687,25 @@
         <v>0</v>
       </c>
       <c r="C340" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>1114</v>
+        <v>1110</v>
       </c>
       <c r="E340" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="F340" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="G340" s="7" t="s">
-        <v>1115</v>
+        <v>1111</v>
       </c>
       <c r="H340" s="7" t="s">
-        <v>1116</v>
+        <v>1112</v>
       </c>
       <c r="I340" s="7" t="s">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="J340">
         <v>0</v>
@@ -49756,25 +49744,25 @@
         <v>0</v>
       </c>
       <c r="C341" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>1118</v>
+        <v>1114</v>
       </c>
       <c r="E341" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="F341" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="G341" s="7" t="s">
-        <v>1119</v>
+        <v>1115</v>
       </c>
       <c r="H341" s="7" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="I341" s="7" t="s">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="J341">
         <v>0</v>
@@ -49813,25 +49801,25 @@
         <v>0</v>
       </c>
       <c r="C342" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="E342" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="F342" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="G342" s="7" t="s">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="H342" s="7" t="s">
+        <v>1116</v>
+      </c>
+      <c r="I342" s="7" t="s">
         <v>1120</v>
-      </c>
-      <c r="I342" s="7" t="s">
-        <v>1124</v>
       </c>
       <c r="J342">
         <v>0</v>
@@ -49870,25 +49858,25 @@
         <v>0</v>
       </c>
       <c r="C343" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>1125</v>
+        <v>1121</v>
       </c>
       <c r="E343" t="s">
-        <v>1106</v>
+        <v>1102</v>
       </c>
       <c r="F343" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="G343" s="7" t="s">
-        <v>1126</v>
+        <v>1122</v>
       </c>
       <c r="H343" s="7" t="s">
-        <v>1120</v>
+        <v>1116</v>
       </c>
       <c r="I343" s="7" t="s">
-        <v>1127</v>
+        <v>1123</v>
       </c>
       <c r="J343">
         <v>0</v>
@@ -49927,22 +49915,22 @@
         <v>0</v>
       </c>
       <c r="C344" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="D344" s="2" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E344" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F344" t="s">
+        <v>1126</v>
+      </c>
+      <c r="G344" s="7" t="s">
+        <v>1127</v>
+      </c>
+      <c r="H344" s="7" t="s">
         <v>1128</v>
-      </c>
-      <c r="E344" t="s">
-        <v>1129</v>
-      </c>
-      <c r="F344" t="s">
-        <v>1130</v>
-      </c>
-      <c r="G344" s="7" t="s">
-        <v>1131</v>
-      </c>
-      <c r="H344" s="7" t="s">
-        <v>1132</v>
       </c>
       <c r="I344">
         <v>0</v>
@@ -49984,22 +49972,22 @@
         <v>0</v>
       </c>
       <c r="C345" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>1133</v>
+        <v>1129</v>
       </c>
       <c r="E345" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="F345" t="s">
+        <v>1126</v>
+      </c>
+      <c r="G345" s="7" t="s">
         <v>1130</v>
       </c>
-      <c r="G345" s="7" t="s">
-        <v>1134</v>
-      </c>
       <c r="H345" s="7" t="s">
-        <v>1135</v>
+        <v>1131</v>
       </c>
       <c r="I345">
         <v>0</v>
@@ -50041,19 +50029,19 @@
         <v>0</v>
       </c>
       <c r="C346" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>1136</v>
+        <v>1132</v>
       </c>
       <c r="E346" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="F346" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="G346" s="7" t="s">
-        <v>1137</v>
+        <v>1133</v>
       </c>
       <c r="H346">
         <v>0</v>
@@ -50098,19 +50086,19 @@
         <v>0</v>
       </c>
       <c r="C347" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="E347" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="F347" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="G347" s="7" t="s">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="H347">
         <v>0</v>
@@ -50155,19 +50143,19 @@
         <v>0</v>
       </c>
       <c r="C348" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="E348" t="s">
-        <v>1129</v>
+        <v>1125</v>
       </c>
       <c r="F348" t="s">
-        <v>1130</v>
+        <v>1126</v>
       </c>
       <c r="G348" s="7" t="s">
-        <v>1141</v>
+        <v>1137</v>
       </c>
       <c r="H348">
         <v>0</v>
@@ -50212,25 +50200,25 @@
         <v>0</v>
       </c>
       <c r="C349" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="D349" s="2" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E349" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F349" t="s">
+        <v>1140</v>
+      </c>
+      <c r="G349" s="7" t="s">
+        <v>1141</v>
+      </c>
+      <c r="H349" s="7" t="s">
         <v>1142</v>
       </c>
-      <c r="E349" t="s">
+      <c r="I349" s="7" t="s">
         <v>1143</v>
-      </c>
-      <c r="F349" t="s">
-        <v>1144</v>
-      </c>
-      <c r="G349" s="7" t="s">
-        <v>1145</v>
-      </c>
-      <c r="H349" s="7" t="s">
-        <v>1146</v>
-      </c>
-      <c r="I349" s="7" t="s">
-        <v>1147</v>
       </c>
       <c r="J349">
         <v>0</v>
@@ -50269,25 +50257,25 @@
         <v>0</v>
       </c>
       <c r="C350" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="D350" s="2" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E350" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F350" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G350" s="7" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H350" s="7" t="s">
         <v>1148</v>
       </c>
-      <c r="E350" t="s">
+      <c r="I350" s="7" t="s">
         <v>1149</v>
-      </c>
-      <c r="F350" t="s">
-        <v>1150</v>
-      </c>
-      <c r="G350" s="7" t="s">
-        <v>1151</v>
-      </c>
-      <c r="H350" s="7" t="s">
-        <v>1152</v>
-      </c>
-      <c r="I350" s="7" t="s">
-        <v>1153</v>
       </c>
       <c r="J350">
         <v>0</v>
@@ -50326,16 +50314,16 @@
         <v>0</v>
       </c>
       <c r="C351" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="E351" t="s">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="F351" t="s">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="G351">
         <v>1</v>
@@ -50383,16 +50371,16 @@
         <v>0</v>
       </c>
       <c r="C352" t="s">
-        <v>1086</v>
+        <v>1082</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>1157</v>
+        <v>1153</v>
       </c>
       <c r="E352" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="F352" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="G352">
         <v>100</v>
@@ -50439,16 +50427,16 @@
         <v>0</v>
       </c>
       <c r="C353" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="E353" t="s">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="F353" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="G353">
         <v>125</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC5DA5C8-48A1-40C9-9606-8A07E5F16AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179DF6A5-DA32-4114-8DA0-EF02F32F2C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1962" uniqueCount="1162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="1174">
   <si>
     <t>編號</t>
   </si>
@@ -4242,9 +4242,6 @@
     <t>權重表：{關卡下限~上限,1個,2個,3個}</t>
   </si>
   <si>
-    <t>每隻菁英身上帶幾個技能（詞條）。寫法 {最低關~最高關,1個的權重,2個的權重,3個的權重}；權重只看相對大小，同一群的菁英共用同一組技能。每一格寫一個關卡區間；同一關落在多格時取最前面那一格；留空或 0 的格子略過，關卡沒被任何區間涵蓋就視為 0。「其他地圖」是神界三圖（沒有專屬一列的地圖）共用的一列。</t>
-  </si>
-  <si>
     <t>{1~100,70,28,2}</t>
   </si>
   <si>
@@ -4267,9 +4264,6 @@
   </si>
   <si>
     <t>傷害×a% 冷卻×b%；首次施放≤c 秒；場域上限 d；召喚上限 e；鏈結連線 f</t>
-  </si>
-  <si>
-    <t>a＝所有菁英技能傷害的總倍率（%）；b＝所有菁英技能冷卻的總倍率（%，數字越大施放越慢）；c＝菁英進場後第一次施放技能最久等幾秒；d＝場上同時存在的菁英場域（毒雲、火牆…）上限；e＝每隻菁英一生最多能召喚幾隻小兵；f＝是否畫「生命鏈結」的連線（1＝畫、0＝不畫）。每個技能自己的冷卻、半徑、傷害倍率寫在 js/elite_data.js 的 ELITE_AFFIXES。</t>
   </si>
   <si>
     <t>菁英與小怪分開擲骰——菁英一次出太多根本打不動，預設集中在 1~2 隻。每波獨立擲骰。權重只看相對大小，總和不必湊 100；填 0 或留空＝不會被抽中。數量上限為棋盤總格數（見 4-戰場站位/棋盤格數）。〔菁英群組改版：菁英現在成「群」出現，這一列的數量代表「群數」；每群幾隻、全員菁英或帶小兵、技能數量見「4-菁英群組」各列。〕</t>
@@ -4293,6 +4287,50 @@
   </si>
   <si>
     <t>a＝相對原鏡頭距離（%）。100＝原距離；125＝拉遠25%；數值越大視野越廣。套用後重載遊戲，影響野外與BOSS畫面。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>高級菁英機率</t>
+  </si>
+  <si>
+    <t>每隻菁英有 a% 機率升級成高級菁英（普通關）；菁英關 b%</t>
+  </si>
+  <si>
+    <t>每一隻要出場的菁英，先擲一次骰決定要不要升級成「高級菁英」（體型 2.2 倍、黃色光暈、3 個隨機技能，數值倍率見「高級菁英倍率」）。a＝普通關的機率（%），b＝菁英關（階段為 10 的倍數）的機率（%）。0＝不會出現高級菁英。同一群內每一隻各自擲骰，所以一群裡可能同時有菁英與高級菁英。</t>
+  </si>
+  <si>
+    <t>高級菁英倍率</t>
+  </si>
+  <si>
+    <t>生命×a 攻擊×b 金幣經驗×c（相對同階段普通怪）</t>
+  </si>
+  <si>
+    <t>高級菁英的數值倍率，基準是「同階段普通怪」，與「4-野外怪物/菁英倍率」同一個算法（那一列是一般菁英：生命×4 攻擊×2）。a＝生命倍率，b＝攻擊倍率，c＝金幣與經驗倍率；防禦、閃避、攻速沿用一般菁英。</t>
+  </si>
+  <si>
+    <t>敵人體型倍率</t>
+  </si>
+  <si>
+    <t>菁英×a 高級菁英×b 野外BOSS×c 封魔塔BOSS d~e（相對普通敵人）</t>
+  </si>
+  <si>
+    <t>畫面上各種高級敵人相對普通敵人的大小：a＝菁英（泛淡藍色光暈）、b＝高級菁英（黃色光暈）、c＝野外 BOSS（光暈顏色隨屬性）、d~e＝封魔塔 BOSS（依 BOSS 順序從 d 線性長到 e）。體型同時影響碰撞半徑（大隻的邊緣先碰到你），不影響技能傷害範圍。</t>
+  </si>
+  <si>
+    <t>跑位設定</t>
+  </si>
+  <si>
+    <t>菁英、高級菁英、野外 BOSS、封魔塔 BOSS 每 a~b 秒換一次位置</t>
+  </si>
+  <si>
+    <t>這四種高級敵人不再從頭到尾站在原地：每隔 a~b 秒（隨機）會跑到新的位置，目標點以「跑位結束後仍可直接攻擊到玩家」為主（近戰貼在你身邊繞一個角度，遠程在射程內換一個方位）。跑位期間仍會攻擊。個別技能（火鏈、瘟疫、秘法加持…）有自己的跑位節奏，寫在 Skills2 敵人技能的效果參數裡。</t>
+  </si>
+  <si>
+    <t>a＝所有敵人技能傷害的總倍率（%）；b＝所有敵人技能冷卻的總倍率（%，數字越大施放越慢）；c＝進場後第一次施放技能最久等幾秒；d＝場上同時存在的敵人場域（毒窪、火徑、毒十字、冰球…）上限；e＝每隻怪物一生最多能召喚幾隻小兵；f＝是否畫「生命鏈結」的連線（1＝畫、0＝不畫）。每個技能自己的冷卻、半徑、傷害倍率寫在 Skills2 表（類別＝enemy）；每種敵人帶哪些技能寫在 NPC 表。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>【已停用】敵人的技能數量改由 NPC 表決定（專屬技能＋隨機技能數量上下限，依敵人類型：菁英、高級菁英、野外BOSS、封魔塔BOSS 各一列）；這一列的數值不再被讀取，保留僅供對照舊設定。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4747,7 +4785,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R337"/>
+  <dimension ref="A1:R341"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="22.7109375" customWidth="1"/>
@@ -29325,7 +29363,7 @@
       </c>
       <c r="F334" t="str">
         <f>計算表!F350</f>
-        <v>每隻菁英身上帶幾個技能（詞條）。寫法 {最低關~最高關,1個的權重,2個的權重,3個的權重}；權重只看相對大小，同一群的菁英共用同一組技能。每一格寫一個關卡區間；同一關落在多格時取最前面那一格；留空或 0 的格子略過，關卡沒被任何區間涵蓋就視為 0。「其他地圖」是神界三圖（沒有專屬一列的地圖）共用的一列。</v>
+        <v>【已停用】敵人的技能數量改由 NPC 表決定（專屬技能＋隨機技能數量上下限，依敵人類型：菁英、高級菁英、野外BOSS、封魔塔BOSS 各一列）；這一列的數值不再被讀取，保留僅供對照舊設定。</v>
       </c>
       <c r="G334" s="7" t="str">
         <f>計算表!G350</f>
@@ -29473,7 +29511,7 @@
       </c>
       <c r="F336" t="str">
         <f>計算表!F352</f>
-        <v>a＝所有菁英技能傷害的總倍率（%）；b＝所有菁英技能冷卻的總倍率（%，數字越大施放越慢）；c＝菁英進場後第一次施放技能最久等幾秒；d＝場上同時存在的菁英場域（毒雲、火牆…）上限；e＝每隻菁英一生最多能召喚幾隻小兵；f＝是否畫「生命鏈結」的連線（1＝畫、0＝不畫）。每個技能自己的冷卻、半徑、傷害倍率寫在 js/elite_data.js 的 ELITE_AFFIXES。</v>
+        <v>a＝所有敵人技能傷害的總倍率（%）；b＝所有敵人技能冷卻的總倍率（%，數字越大施放越慢）；c＝進場後第一次施放技能最久等幾秒；d＝場上同時存在的敵人場域（毒窪、火徑、毒十字、冰球…）上限；e＝每隻怪物一生最多能召喚幾隻小兵；f＝是否畫「生命鏈結」的連線（1＝畫、0＝不畫）。每個技能自己的冷卻、半徑、傷害倍率寫在 Skills2 表（類別＝enemy）；每種敵人帶哪些技能寫在 NPC 表。</v>
       </c>
       <c r="G336">
         <f>計算表!G352</f>
@@ -29489,11 +29527,11 @@
       </c>
       <c r="J336">
         <f>計算表!J352</f>
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="K336">
         <f>計算表!K352</f>
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L336">
         <f>計算表!L352</f>
@@ -29595,6 +29633,302 @@
       </c>
       <c r="R337">
         <f>計算表!R353</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="338" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A338">
+        <f>計算表!A354</f>
+        <v>353</v>
+      </c>
+      <c r="B338">
+        <f>計算表!B354</f>
+        <v>0</v>
+      </c>
+      <c r="C338" t="str">
+        <f>計算表!C354</f>
+        <v>4-菁英群組</v>
+      </c>
+      <c r="D338" t="str">
+        <f>計算表!D354</f>
+        <v>高級菁英機率</v>
+      </c>
+      <c r="E338" t="str">
+        <f>計算表!E354</f>
+        <v>每隻菁英有 a% 機率升級成高級菁英（普通關）；菁英關 b%</v>
+      </c>
+      <c r="F338" t="str">
+        <f>計算表!F354</f>
+        <v>每一隻要出場的菁英，先擲一次骰決定要不要升級成「高級菁英」（體型 2.2 倍、黃色光暈、3 個隨機技能，數值倍率見「高級菁英倍率」）。a＝普通關的機率（%），b＝菁英關（階段為 10 的倍數）的機率（%）。0＝不會出現高級菁英。同一群內每一隻各自擲骰，所以一群裡可能同時有菁英與高級菁英。</v>
+      </c>
+      <c r="G338">
+        <f>計算表!G354</f>
+        <v>6</v>
+      </c>
+      <c r="H338">
+        <f>計算表!H354</f>
+        <v>20</v>
+      </c>
+      <c r="I338">
+        <f>計算表!I354</f>
+        <v>0</v>
+      </c>
+      <c r="J338">
+        <f>計算表!J354</f>
+        <v>0</v>
+      </c>
+      <c r="K338">
+        <f>計算表!K354</f>
+        <v>0</v>
+      </c>
+      <c r="L338">
+        <f>計算表!L354</f>
+        <v>0</v>
+      </c>
+      <c r="M338">
+        <f>計算表!M354</f>
+        <v>0</v>
+      </c>
+      <c r="N338">
+        <f>計算表!N354</f>
+        <v>0</v>
+      </c>
+      <c r="O338">
+        <f>計算表!O354</f>
+        <v>0</v>
+      </c>
+      <c r="P338">
+        <f>計算表!P354</f>
+        <v>0</v>
+      </c>
+      <c r="Q338">
+        <f>計算表!Q354</f>
+        <v>0</v>
+      </c>
+      <c r="R338">
+        <f>計算表!R354</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A339">
+        <f>計算表!A355</f>
+        <v>354</v>
+      </c>
+      <c r="B339">
+        <f>計算表!B355</f>
+        <v>0</v>
+      </c>
+      <c r="C339" t="str">
+        <f>計算表!C355</f>
+        <v>4-菁英群組</v>
+      </c>
+      <c r="D339" t="str">
+        <f>計算表!D355</f>
+        <v>高級菁英倍率</v>
+      </c>
+      <c r="E339" t="str">
+        <f>計算表!E355</f>
+        <v>生命×a 攻擊×b 金幣經驗×c（相對同階段普通怪）</v>
+      </c>
+      <c r="F339" t="str">
+        <f>計算表!F355</f>
+        <v>高級菁英的數值倍率，基準是「同階段普通怪」，與「4-野外怪物/菁英倍率」同一個算法（那一列是一般菁英：生命×4 攻擊×2）。a＝生命倍率，b＝攻擊倍率，c＝金幣與經驗倍率；防禦、閃避、攻速沿用一般菁英。</v>
+      </c>
+      <c r="G339">
+        <f>計算表!G355</f>
+        <v>8</v>
+      </c>
+      <c r="H339">
+        <f>計算表!H355</f>
+        <v>3</v>
+      </c>
+      <c r="I339">
+        <f>計算表!I355</f>
+        <v>4</v>
+      </c>
+      <c r="J339">
+        <f>計算表!J355</f>
+        <v>0</v>
+      </c>
+      <c r="K339">
+        <f>計算表!K355</f>
+        <v>0</v>
+      </c>
+      <c r="L339">
+        <f>計算表!L355</f>
+        <v>0</v>
+      </c>
+      <c r="M339">
+        <f>計算表!M355</f>
+        <v>0</v>
+      </c>
+      <c r="N339">
+        <f>計算表!N355</f>
+        <v>0</v>
+      </c>
+      <c r="O339">
+        <f>計算表!O355</f>
+        <v>0</v>
+      </c>
+      <c r="P339">
+        <f>計算表!P355</f>
+        <v>0</v>
+      </c>
+      <c r="Q339">
+        <f>計算表!Q355</f>
+        <v>0</v>
+      </c>
+      <c r="R339">
+        <f>計算表!R355</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A340">
+        <f>計算表!A356</f>
+        <v>355</v>
+      </c>
+      <c r="B340">
+        <f>計算表!B356</f>
+        <v>0</v>
+      </c>
+      <c r="C340" t="str">
+        <f>計算表!C356</f>
+        <v>4-菁英群組</v>
+      </c>
+      <c r="D340" t="str">
+        <f>計算表!D356</f>
+        <v>敵人體型倍率</v>
+      </c>
+      <c r="E340" t="str">
+        <f>計算表!E356</f>
+        <v>菁英×a 高級菁英×b 野外BOSS×c 封魔塔BOSS d~e（相對普通敵人）</v>
+      </c>
+      <c r="F340" t="str">
+        <f>計算表!F356</f>
+        <v>畫面上各種高級敵人相對普通敵人的大小：a＝菁英（泛淡藍色光暈）、b＝高級菁英（黃色光暈）、c＝野外 BOSS（光暈顏色隨屬性）、d~e＝封魔塔 BOSS（依 BOSS 順序從 d 線性長到 e）。體型同時影響碰撞半徑（大隻的邊緣先碰到你），不影響技能傷害範圍。</v>
+      </c>
+      <c r="G340">
+        <f>計算表!G356</f>
+        <v>1.6</v>
+      </c>
+      <c r="H340">
+        <f>計算表!H356</f>
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="I340">
+        <f>計算表!I356</f>
+        <v>3.4</v>
+      </c>
+      <c r="J340">
+        <f>計算表!J356</f>
+        <v>5</v>
+      </c>
+      <c r="K340">
+        <f>計算表!K356</f>
+        <v>7</v>
+      </c>
+      <c r="L340">
+        <f>計算表!L356</f>
+        <v>0</v>
+      </c>
+      <c r="M340">
+        <f>計算表!M356</f>
+        <v>0</v>
+      </c>
+      <c r="N340">
+        <f>計算表!N356</f>
+        <v>0</v>
+      </c>
+      <c r="O340">
+        <f>計算表!O356</f>
+        <v>0</v>
+      </c>
+      <c r="P340">
+        <f>計算表!P356</f>
+        <v>0</v>
+      </c>
+      <c r="Q340">
+        <f>計算表!Q356</f>
+        <v>0</v>
+      </c>
+      <c r="R340">
+        <f>計算表!R356</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A341">
+        <f>計算表!A357</f>
+        <v>356</v>
+      </c>
+      <c r="B341">
+        <f>計算表!B357</f>
+        <v>0</v>
+      </c>
+      <c r="C341" t="str">
+        <f>計算表!C357</f>
+        <v>4-菁英群組</v>
+      </c>
+      <c r="D341" t="str">
+        <f>計算表!D357</f>
+        <v>跑位設定</v>
+      </c>
+      <c r="E341" t="str">
+        <f>計算表!E357</f>
+        <v>菁英、高級菁英、野外 BOSS、封魔塔 BOSS 每 a~b 秒換一次位置</v>
+      </c>
+      <c r="F341" t="str">
+        <f>計算表!F357</f>
+        <v>這四種高級敵人不再從頭到尾站在原地：每隔 a~b 秒（隨機）會跑到新的位置，目標點以「跑位結束後仍可直接攻擊到玩家」為主（近戰貼在你身邊繞一個角度，遠程在射程內換一個方位）。跑位期間仍會攻擊。個別技能（火鏈、瘟疫、秘法加持…）有自己的跑位節奏，寫在 Skills2 敵人技能的效果參數裡。</v>
+      </c>
+      <c r="G341">
+        <f>計算表!G357</f>
+        <v>4</v>
+      </c>
+      <c r="H341">
+        <f>計算表!H357</f>
+        <v>8</v>
+      </c>
+      <c r="I341">
+        <f>計算表!I357</f>
+        <v>0</v>
+      </c>
+      <c r="J341">
+        <f>計算表!J357</f>
+        <v>0</v>
+      </c>
+      <c r="K341">
+        <f>計算表!K357</f>
+        <v>0</v>
+      </c>
+      <c r="L341">
+        <f>計算表!L357</f>
+        <v>0</v>
+      </c>
+      <c r="M341">
+        <f>計算表!M357</f>
+        <v>0</v>
+      </c>
+      <c r="N341">
+        <f>計算表!N357</f>
+        <v>0</v>
+      </c>
+      <c r="O341">
+        <f>計算表!O357</f>
+        <v>0</v>
+      </c>
+      <c r="P341">
+        <f>計算表!P357</f>
+        <v>0</v>
+      </c>
+      <c r="Q341">
+        <f>計算表!Q357</f>
+        <v>0</v>
+      </c>
+      <c r="R341">
+        <f>計算表!R357</f>
         <v>0</v>
       </c>
     </row>
@@ -29606,7 +29940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AB353"/>
+  <dimension ref="A1:AB357"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="23.42578125" customWidth="1"/>
@@ -36758,7 +37092,7 @@
         <v>270</v>
       </c>
       <c r="F126" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="G126">
         <v>4</v>
@@ -37271,7 +37605,7 @@
         <v>274</v>
       </c>
       <c r="F135" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="G135" t="s">
         <v>276</v>
@@ -37328,7 +37662,7 @@
         <v>274</v>
       </c>
       <c r="F136" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>968</v>
@@ -37385,7 +37719,7 @@
         <v>274</v>
       </c>
       <c r="F137" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>969</v>
@@ -37442,7 +37776,7 @@
         <v>274</v>
       </c>
       <c r="F138" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>984</v>
@@ -37499,7 +37833,7 @@
         <v>274</v>
       </c>
       <c r="F139" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>977</v>
@@ -50266,16 +50600,16 @@
         <v>1145</v>
       </c>
       <c r="F350" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G350" s="7" t="s">
         <v>1146</v>
       </c>
-      <c r="G350" s="7" t="s">
+      <c r="H350" s="7" t="s">
         <v>1147</v>
       </c>
-      <c r="H350" s="7" t="s">
+      <c r="I350" s="7" t="s">
         <v>1148</v>
-      </c>
-      <c r="I350" s="7" t="s">
-        <v>1149</v>
       </c>
       <c r="J350">
         <v>0</v>
@@ -50317,13 +50651,13 @@
         <v>1082</v>
       </c>
       <c r="D351" s="2" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E351" t="s">
         <v>1150</v>
       </c>
-      <c r="E351" t="s">
+      <c r="F351" t="s">
         <v>1151</v>
-      </c>
-      <c r="F351" t="s">
-        <v>1152</v>
       </c>
       <c r="G351">
         <v>1</v>
@@ -50374,13 +50708,13 @@
         <v>1082</v>
       </c>
       <c r="D352" s="2" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E352" t="s">
         <v>1153</v>
       </c>
-      <c r="E352" t="s">
-        <v>1154</v>
-      </c>
       <c r="F352" t="s">
-        <v>1155</v>
+        <v>1172</v>
       </c>
       <c r="G352">
         <v>100</v>
@@ -50392,10 +50726,10 @@
         <v>3.5</v>
       </c>
       <c r="J352">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="K352">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L352">
         <v>1</v>
@@ -50427,16 +50761,16 @@
         <v>0</v>
       </c>
       <c r="C353" t="s">
+        <v>1156</v>
+      </c>
+      <c r="D353" s="2" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E353" t="s">
         <v>1158</v>
       </c>
-      <c r="D353" s="2" t="s">
+      <c r="F353" t="s">
         <v>1159</v>
-      </c>
-      <c r="E353" t="s">
-        <v>1160</v>
-      </c>
-      <c r="F353" t="s">
-        <v>1161</v>
       </c>
       <c r="G353">
         <v>125</v>
@@ -50472,6 +50806,234 @@
         <v>0</v>
       </c>
       <c r="R353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A354">
+        <f>A353+1</f>
+        <v>353</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D354" s="2" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E354" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F354" t="s">
+        <v>1162</v>
+      </c>
+      <c r="G354">
+        <v>6</v>
+      </c>
+      <c r="H354">
+        <v>20</v>
+      </c>
+      <c r="I354">
+        <v>0</v>
+      </c>
+      <c r="J354">
+        <v>0</v>
+      </c>
+      <c r="K354">
+        <v>0</v>
+      </c>
+      <c r="L354">
+        <v>0</v>
+      </c>
+      <c r="M354">
+        <v>0</v>
+      </c>
+      <c r="N354">
+        <v>0</v>
+      </c>
+      <c r="O354">
+        <v>0</v>
+      </c>
+      <c r="P354">
+        <v>0</v>
+      </c>
+      <c r="Q354">
+        <v>0</v>
+      </c>
+      <c r="R354">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A355">
+        <f>A354+1</f>
+        <v>354</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D355" s="2" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E355" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F355" t="s">
+        <v>1165</v>
+      </c>
+      <c r="G355">
+        <v>8</v>
+      </c>
+      <c r="H355">
+        <v>3</v>
+      </c>
+      <c r="I355">
+        <v>4</v>
+      </c>
+      <c r="J355">
+        <v>0</v>
+      </c>
+      <c r="K355">
+        <v>0</v>
+      </c>
+      <c r="L355">
+        <v>0</v>
+      </c>
+      <c r="M355">
+        <v>0</v>
+      </c>
+      <c r="N355">
+        <v>0</v>
+      </c>
+      <c r="O355">
+        <v>0</v>
+      </c>
+      <c r="P355">
+        <v>0</v>
+      </c>
+      <c r="Q355">
+        <v>0</v>
+      </c>
+      <c r="R355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A356">
+        <f>A355+1</f>
+        <v>355</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D356" s="2" t="s">
+        <v>1166</v>
+      </c>
+      <c r="E356" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F356" t="s">
+        <v>1168</v>
+      </c>
+      <c r="G356">
+        <v>1.6</v>
+      </c>
+      <c r="H356">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="I356">
+        <v>3.4</v>
+      </c>
+      <c r="J356">
+        <v>5</v>
+      </c>
+      <c r="K356">
+        <v>7</v>
+      </c>
+      <c r="L356">
+        <v>0</v>
+      </c>
+      <c r="M356">
+        <v>0</v>
+      </c>
+      <c r="N356">
+        <v>0</v>
+      </c>
+      <c r="O356">
+        <v>0</v>
+      </c>
+      <c r="P356">
+        <v>0</v>
+      </c>
+      <c r="Q356">
+        <v>0</v>
+      </c>
+      <c r="R356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A357">
+        <f>A356+1</f>
+        <v>356</v>
+      </c>
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357" t="s">
+        <v>1082</v>
+      </c>
+      <c r="D357" s="2" t="s">
+        <v>1169</v>
+      </c>
+      <c r="E357" t="s">
+        <v>1170</v>
+      </c>
+      <c r="F357" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G357">
+        <v>4</v>
+      </c>
+      <c r="H357">
+        <v>8</v>
+      </c>
+      <c r="I357">
+        <v>0</v>
+      </c>
+      <c r="J357">
+        <v>0</v>
+      </c>
+      <c r="K357">
+        <v>0</v>
+      </c>
+      <c r="L357">
+        <v>0</v>
+      </c>
+      <c r="M357">
+        <v>0</v>
+      </c>
+      <c r="N357">
+        <v>0</v>
+      </c>
+      <c r="O357">
+        <v>0</v>
+      </c>
+      <c r="P357">
+        <v>0</v>
+      </c>
+      <c r="Q357">
+        <v>0</v>
+      </c>
+      <c r="R357">
         <v>0</v>
       </c>
     </row>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{179DF6A5-DA32-4114-8DA0-EF02F32F2C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A2C7366-2865-4DAC-BBE8-DF42FE716CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1978" uniqueCount="1174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="1193">
   <si>
     <t>編號</t>
   </si>
@@ -3839,16 +3839,7 @@
     <t>a=生命與四維最終倍率 b=升級經驗倍率  c=升級經驗基礎增加值 d=階級名稱 e=潛力技能等級上限（查表）。 f=已停用（舊融合技上限增加值，2026-09-29 移除）。</t>
   </si>
   <si>
-    <t>4.0000000000000001E-3</t>
-  </si>
-  <si>
-    <t>1.0000000000000001E-5</t>
-  </si>
-  <si>
     <t>2.5000000000000001E-3</t>
-  </si>
-  <si>
-    <t>3.4999999999999999E-6</t>
   </si>
   <si>
     <t/>
@@ -4332,6 +4323,75 @@
   <si>
     <t>【已停用】敵人的技能數量改由 NPC 表決定（專屬技能＋隨機技能數量上下限，依敵人類型：菁英、高級菁英、野外BOSS、封魔塔BOSS 各一列）；這一列的數值不再被讀取，保留僅供對照舊設定。</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>(a+(等級-1)×b+體質×c+生命定值)×(1+生命%)</t>
+  </si>
+  <si>
+    <t>a=基礎 b=每級 c=每點體質。再乘轉生倍率。</t>
+  </si>
+  <si>
+    <t>a+智力×b+體質×c+加成</t>
+  </si>
+  <si>
+    <t>a=基礎 b=每點智力 c=每點體質。</t>
+  </si>
+  <si>
+    <t>0.01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.02</t>
+  </si>
+  <si>
+    <t>(a+物防定值+b×物防定值*c^轉生次數+力量×d+體質*e)×(1+物防%)</t>
+  </si>
+  <si>
+    <t>a=基礎 b=定值加成 c=轉生加成指數底 d=每點力量 e=每點體質。</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>(a+魔防定值+b×魔防定值*c^轉生次數+智力×d+體質*e)×(1+魔防%)</t>
+  </si>
+  <si>
+    <t>a=基礎 b=定值加成 c=轉生加成指數底 d=每點智力 e=每點體質。</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a=基礎%（無上限）b=每點敏捷%。</t>
+  </si>
+  <si>
+    <t>0.02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命恢復/秒</t>
+  </si>
+  <si>
+    <t>力量×a+體質×b+詞條</t>
+  </si>
+  <si>
+    <t>a=每點力量 b=每點體質。</t>
+  </si>
+  <si>
+    <t>0.03</t>
+  </si>
+  <si>
+    <t>0.06</t>
+  </si>
+  <si>
+    <t>不再受負重影響。</t>
   </si>
 </sst>
 </file>
@@ -8986,13 +9046,11 @@
         <f>計算表!D58</f>
         <v>生命上限</v>
       </c>
-      <c r="E58" t="str">
-        <f>計算表!E58</f>
-        <v>(a+(等級-1)×b+耐力×c+生命定值)×(1+生命%)</v>
-      </c>
-      <c r="F58" t="str">
-        <f>計算表!F58</f>
-        <v>a=基礎 b=每級 c=每點耐力。再乘轉生倍率。</v>
+      <c r="E58" s="7" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>1172</v>
       </c>
       <c r="G58">
         <f>計算表!G58</f>
@@ -9134,24 +9192,21 @@
         <f>計算表!D60</f>
         <v>法力恢復/秒</v>
       </c>
-      <c r="E60" t="str">
-        <f>計算表!E60</f>
-        <v>a+智力×b+加成</v>
-      </c>
-      <c r="F60" t="str">
-        <f>計算表!F60</f>
-        <v>a=基礎 b=每點智力。</v>
+      <c r="E60" s="7" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>1174</v>
       </c>
       <c r="G60">
         <f>計算表!G60</f>
         <v>1</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I60">
-        <f>計算表!I60</f>
-        <v>0</v>
+        <v>1175</v>
+      </c>
+      <c r="I60" s="7" t="s">
+        <v>1176</v>
       </c>
       <c r="J60">
         <f>計算表!J60</f>
@@ -9355,13 +9410,11 @@
         <f>計算表!D63</f>
         <v>物理防禦</v>
       </c>
-      <c r="E63" t="str">
-        <f>計算表!E63</f>
-        <v>(a+物防定值+b×物防定值*c^轉生次數+力量×d+耐力*e)×(1+物防%)</v>
-      </c>
-      <c r="F63" t="str">
-        <f>計算表!F63</f>
-        <v>a=基礎 b=定值加成 c=轉生加成指數底 d=每點力量 e=每點耐力。</v>
+      <c r="E63" s="7" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>1178</v>
       </c>
       <c r="G63">
         <f>計算表!G63</f>
@@ -9375,13 +9428,11 @@
         <f>計算表!I63</f>
         <v>2.4</v>
       </c>
-      <c r="J63">
-        <f>計算表!J63</f>
-        <v>0.35</v>
-      </c>
-      <c r="K63">
-        <f>計算表!K63</f>
-        <v>0.65</v>
+      <c r="J63" s="7" t="s">
+        <v>1179</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>1180</v>
       </c>
       <c r="L63">
         <f>計算表!L63</f>
@@ -9429,13 +9480,11 @@
         <f>計算表!D64</f>
         <v>魔法防禦</v>
       </c>
-      <c r="E64" t="str">
-        <f>計算表!E64</f>
-        <v>(a+魔防定值+b×魔防定值*c^轉生次數+智力×d+耐力*e)×(1+魔防%)</v>
-      </c>
-      <c r="F64" t="str">
-        <f>計算表!F64</f>
-        <v>a=基礎 b=定值加成 c=轉生加成指數底 d=每點智力 e=每點耐力。</v>
+      <c r="E64" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>1182</v>
       </c>
       <c r="G64">
         <f>計算表!G64</f>
@@ -9449,13 +9498,11 @@
         <f>計算表!I64</f>
         <v>2.4</v>
       </c>
-      <c r="J64">
-        <f>計算表!J64</f>
-        <v>0.35</v>
-      </c>
-      <c r="K64">
-        <f>計算表!K64</f>
-        <v>0.65</v>
+      <c r="J64" s="7" t="s">
+        <v>1183</v>
+      </c>
+      <c r="K64" s="7" t="s">
+        <v>1180</v>
       </c>
       <c r="L64">
         <f>計算表!L64</f>
@@ -9516,7 +9563,7 @@
         <v>5</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>1017</v>
+        <v>1184</v>
       </c>
       <c r="I65">
         <f>計算表!I65</f>
@@ -9589,7 +9636,7 @@
         <v>0.875</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="I66">
         <f>計算表!I66</f>
@@ -9649,21 +9696,18 @@
         <f>計算表!D67</f>
         <v>暴擊傷害</v>
       </c>
-      <c r="E67" t="str">
-        <f>計算表!E67</f>
-        <v>a+加成</v>
-      </c>
-      <c r="F67" t="str">
-        <f>計算表!F67</f>
-        <v>a=基礎%（無上限）。</v>
+      <c r="E67" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>1185</v>
       </c>
       <c r="G67">
         <f>計算表!G67</f>
         <v>150</v>
       </c>
-      <c r="H67">
-        <f>計算表!H67</f>
-        <v>0</v>
+      <c r="H67" s="7" t="s">
+        <v>1180</v>
       </c>
       <c r="I67">
         <f>計算表!I67</f>
@@ -9735,9 +9779,8 @@
         <f>計算表!G68</f>
         <v>0.86</v>
       </c>
-      <c r="H68">
-        <f>計算表!H68</f>
-        <v>0.2</v>
+      <c r="H68" s="7" t="s">
+        <v>1183</v>
       </c>
       <c r="I68">
         <f>計算表!I68</f>
@@ -9805,9 +9848,8 @@
         <f>計算表!F69</f>
         <v>a=每點敏捷%（減去敵方閃避後最低 5%）。</v>
       </c>
-      <c r="G69">
-        <f>計算表!G69</f>
-        <v>0</v>
+      <c r="G69" s="7" t="s">
+        <v>1176</v>
       </c>
       <c r="H69">
         <f>計算表!H69</f>
@@ -9880,7 +9922,7 @@
         <v>a=每點敏捷%。</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>1019</v>
+        <v>1186</v>
       </c>
       <c r="H70">
         <f>計算表!H70</f>
@@ -9940,25 +9982,20 @@
         <f>計算表!C71</f>
         <v>2-屬性派生</v>
       </c>
-      <c r="D71" t="str">
-        <f>計算表!D71</f>
-        <v>負重上限</v>
-      </c>
-      <c r="E71" t="str">
-        <f>計算表!E71</f>
-        <v>力量×a+詞條</v>
-      </c>
-      <c r="F71" t="str">
-        <f>計算表!F71</f>
-        <v>a=每點力量。</v>
-      </c>
-      <c r="G71">
-        <f>計算表!G71</f>
-        <v>0.5</v>
-      </c>
-      <c r="H71">
-        <f>計算表!H71</f>
-        <v>0</v>
+      <c r="D71" s="7" t="s">
+        <v>1187</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>1188</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>1190</v>
+      </c>
+      <c r="H71" s="7" t="s">
+        <v>1191</v>
       </c>
       <c r="I71">
         <f>計算表!I71</f>
@@ -11799,7 +11836,7 @@
         <v>忽略敵人防禦% = 穿透%/(穿透%+a)</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="G96">
         <f>計算表!G96</f>
@@ -13586,7 +13623,7 @@
         <v>0.5</v>
       </c>
       <c r="I120" s="7" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="J120">
         <f>計算表!J120</f>
@@ -15501,7 +15538,7 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條。</v>
       </c>
       <c r="G146" s="7" t="s">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="H146">
         <f>計算表!H146</f>
@@ -15574,13 +15611,13 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條。</v>
       </c>
       <c r="G147" s="7" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="H147" s="7" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="J147">
         <f>計算表!J147</f>
@@ -15645,20 +15682,20 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條。</v>
       </c>
       <c r="G148" s="7" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="H148" s="7" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="I148">
         <f>計算表!I148</f>
         <v>9.11754</v>
       </c>
       <c r="J148" s="7" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="K148" s="7" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="L148">
         <f>計算表!L148</f>
@@ -15715,22 +15752,22 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條。</v>
       </c>
       <c r="G149" s="7" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H149" s="7" t="s">
+        <v>1028</v>
+      </c>
+      <c r="I149" s="7" t="s">
+        <v>1029</v>
+      </c>
+      <c r="J149" s="7" t="s">
         <v>1030</v>
       </c>
-      <c r="H149" s="7" t="s">
+      <c r="K149" s="7" t="s">
         <v>1031</v>
       </c>
-      <c r="I149" s="7" t="s">
+      <c r="L149" s="7" t="s">
         <v>1032</v>
-      </c>
-      <c r="J149" s="7" t="s">
-        <v>1033</v>
-      </c>
-      <c r="K149" s="7" t="s">
-        <v>1034</v>
-      </c>
-      <c r="L149" s="7" t="s">
-        <v>1035</v>
       </c>
       <c r="M149">
         <f>計算表!M149</f>
@@ -15783,28 +15820,28 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條。</v>
       </c>
       <c r="G150" s="7" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H150" s="7" t="s">
+        <v>1034</v>
+      </c>
+      <c r="I150" s="7" t="s">
+        <v>1035</v>
+      </c>
+      <c r="J150" s="7" t="s">
         <v>1036</v>
       </c>
-      <c r="H150" s="7" t="s">
+      <c r="K150" s="7" t="s">
         <v>1037</v>
       </c>
-      <c r="I150" s="7" t="s">
+      <c r="L150" s="7" t="s">
         <v>1038</v>
       </c>
-      <c r="J150" s="7" t="s">
+      <c r="M150" s="7" t="s">
         <v>1039</v>
       </c>
-      <c r="K150" s="7" t="s">
+      <c r="N150" s="7" t="s">
         <v>1040</v>
-      </c>
-      <c r="L150" s="7" t="s">
-        <v>1041</v>
-      </c>
-      <c r="M150" s="7" t="s">
-        <v>1042</v>
-      </c>
-      <c r="N150" s="7" t="s">
-        <v>1043</v>
       </c>
       <c r="O150">
         <f>計算表!O150</f>
@@ -15849,28 +15886,28 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條。</v>
       </c>
       <c r="G151" s="7" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H151" s="7" t="s">
+        <v>1042</v>
+      </c>
+      <c r="I151" s="7" t="s">
+        <v>1043</v>
+      </c>
+      <c r="J151" s="7" t="s">
         <v>1044</v>
       </c>
-      <c r="H151" s="7" t="s">
+      <c r="K151" s="7" t="s">
         <v>1045</v>
       </c>
-      <c r="I151" s="7" t="s">
+      <c r="L151" s="7" t="s">
         <v>1046</v>
       </c>
-      <c r="J151" s="7" t="s">
+      <c r="M151" s="7" t="s">
         <v>1047</v>
       </c>
-      <c r="K151" s="7" t="s">
+      <c r="N151" s="7" t="s">
         <v>1048</v>
-      </c>
-      <c r="L151" s="7" t="s">
-        <v>1049</v>
-      </c>
-      <c r="M151" s="7" t="s">
-        <v>1050</v>
-      </c>
-      <c r="N151" s="7" t="s">
-        <v>1051</v>
       </c>
       <c r="O151">
         <f>計算表!O151</f>
@@ -15915,31 +15952,31 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條 j=9條。</v>
       </c>
       <c r="G152" s="7" t="s">
+        <v>1049</v>
+      </c>
+      <c r="H152" s="7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="I152" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="J152" s="7" t="s">
         <v>1052</v>
       </c>
-      <c r="H152" s="7" t="s">
+      <c r="K152" s="7" t="s">
         <v>1053</v>
       </c>
-      <c r="I152" s="7" t="s">
+      <c r="L152" s="7" t="s">
         <v>1054</v>
       </c>
-      <c r="J152" s="7" t="s">
+      <c r="M152" s="7" t="s">
         <v>1055</v>
       </c>
-      <c r="K152" s="7" t="s">
+      <c r="N152" s="7" t="s">
         <v>1056</v>
       </c>
-      <c r="L152" s="7" t="s">
+      <c r="O152" s="7" t="s">
         <v>1057</v>
-      </c>
-      <c r="M152" s="7" t="s">
-        <v>1058</v>
-      </c>
-      <c r="N152" s="7" t="s">
-        <v>1059</v>
-      </c>
-      <c r="O152" s="7" t="s">
-        <v>1060</v>
       </c>
       <c r="P152">
         <f>計算表!P152</f>
@@ -15980,7 +16017,7 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條 j=9條 k=10條。</v>
       </c>
       <c r="G153" s="7" t="s">
-        <v>1061</v>
+        <v>1058</v>
       </c>
       <c r="H153">
         <f>計算表!H153</f>
@@ -17463,7 +17500,7 @@
         <v>200</v>
       </c>
       <c r="H173" s="7" t="s">
-        <v>1062</v>
+        <v>1059</v>
       </c>
       <c r="I173">
         <f>計算表!I173</f>
@@ -18050,7 +18087,7 @@
         <v>a=基礎權重 b=權重加成 c=加成上限 d=出現門檻。普通無加成。神鑄創世不參與此擲骰。(裝備合成才有作用，目前功能關閉中)</v>
       </c>
       <c r="G181" s="7" t="s">
-        <v>1063</v>
+        <v>1060</v>
       </c>
       <c r="H181" t="str">
         <f>計算表!H181</f>
@@ -20869,7 +20906,7 @@
         <v>1</v>
       </c>
       <c r="I219" s="7" t="s">
-        <v>1064</v>
+        <v>1061</v>
       </c>
       <c r="J219">
         <f>計算表!J220</f>
@@ -20999,13 +21036,11 @@
         <f>計算表!D222</f>
         <v>合成暫存區</v>
       </c>
-      <c r="E221" t="str">
-        <f>計算表!E222</f>
-        <v>a + ⌊負重上限/b⌋</v>
-      </c>
-      <c r="F221">
-        <f>計算表!F222</f>
-        <v>0</v>
+      <c r="E221" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="F221" s="7" t="s">
+        <v>1192</v>
       </c>
       <c r="G221">
         <f>計算表!G222</f>
@@ -25884,10 +25919,10 @@
         <v>等級上限</v>
       </c>
       <c r="E287" s="7" t="s">
-        <v>1065</v>
+        <v>1062</v>
       </c>
       <c r="F287" s="7" t="s">
-        <v>1066</v>
+        <v>1063</v>
       </c>
       <c r="G287">
         <f>計算表!G291</f>
@@ -27518,7 +27553,7 @@
         <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）。</v>
       </c>
       <c r="G309" s="7" t="s">
-        <v>1067</v>
+        <v>1064</v>
       </c>
       <c r="H309">
         <f>計算表!H325</f>
@@ -27887,7 +27922,7 @@
         <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）。</v>
       </c>
       <c r="G314" s="7" t="s">
-        <v>1068</v>
+        <v>1065</v>
       </c>
       <c r="H314">
         <f>計算表!H330</f>
@@ -32361,7 +32396,7 @@
         <v>149</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>1069</v>
+        <v>1066</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -32418,7 +32453,7 @@
         <v>149</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>1070</v>
+        <v>1067</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -34011,10 +34046,10 @@
         <v>143</v>
       </c>
       <c r="E72" t="s">
-        <v>1071</v>
+        <v>1068</v>
       </c>
       <c r="F72" t="s">
-        <v>1072</v>
+        <v>1069</v>
       </c>
       <c r="G72">
         <v>5</v>
@@ -34866,10 +34901,10 @@
         <v>209</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>1077</v>
+        <v>1074</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>1078</v>
+        <v>1075</v>
       </c>
       <c r="G87">
         <v>10</v>
@@ -37092,7 +37127,7 @@
         <v>270</v>
       </c>
       <c r="F126" t="s">
-        <v>1155</v>
+        <v>1152</v>
       </c>
       <c r="G126">
         <v>4</v>
@@ -37605,7 +37640,7 @@
         <v>274</v>
       </c>
       <c r="F135" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="G135" t="s">
         <v>276</v>
@@ -37662,7 +37697,7 @@
         <v>274</v>
       </c>
       <c r="F136" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>968</v>
@@ -37719,7 +37754,7 @@
         <v>274</v>
       </c>
       <c r="F137" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>969</v>
@@ -37776,7 +37811,7 @@
         <v>274</v>
       </c>
       <c r="F138" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>984</v>
@@ -37833,7 +37868,7 @@
         <v>274</v>
       </c>
       <c r="F139" t="s">
-        <v>1154</v>
+        <v>1151</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>977</v>
@@ -49004,7 +49039,7 @@
         <v>39</v>
       </c>
       <c r="F322" s="7" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="G322">
         <v>1</v>
@@ -49061,7 +49096,7 @@
         <v>39</v>
       </c>
       <c r="F323" s="7" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="G323">
         <v>1.35</v>
@@ -49118,7 +49153,7 @@
         <v>39</v>
       </c>
       <c r="F324" s="7" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="G324">
         <v>1.75</v>
@@ -49175,7 +49210,7 @@
         <v>39</v>
       </c>
       <c r="F325" s="7" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="G325">
         <v>2.2999999999999998</v>
@@ -49232,7 +49267,7 @@
         <v>39</v>
       </c>
       <c r="F326" s="7" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="G326">
         <v>3</v>
@@ -49289,7 +49324,7 @@
         <v>39</v>
       </c>
       <c r="F327" s="7" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="G327">
         <v>4</v>
@@ -49346,7 +49381,7 @@
         <v>39</v>
       </c>
       <c r="F328" s="7" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="G328">
         <v>5.2</v>
@@ -49403,7 +49438,7 @@
         <v>39</v>
       </c>
       <c r="F329" s="7" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="G329">
         <v>6.8</v>
@@ -49460,7 +49495,7 @@
         <v>39</v>
       </c>
       <c r="F330" s="7" t="s">
-        <v>1080</v>
+        <v>1077</v>
       </c>
       <c r="G330">
         <v>10.199999999999999</v>
@@ -49517,7 +49552,7 @@
         <v>39</v>
       </c>
       <c r="F331" s="7" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="G331">
         <v>15.3</v>
@@ -49574,7 +49609,7 @@
         <v>39</v>
       </c>
       <c r="F332" s="7" t="s">
-        <v>1081</v>
+        <v>1078</v>
       </c>
       <c r="G332">
         <v>22.95</v>
@@ -49622,22 +49657,22 @@
         <v>0</v>
       </c>
       <c r="C333" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D333" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E333" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F333" t="s">
         <v>1073</v>
-      </c>
-      <c r="D333" t="s">
-        <v>1074</v>
-      </c>
-      <c r="E333" t="s">
-        <v>1075</v>
-      </c>
-      <c r="F333" t="s">
-        <v>1076</v>
       </c>
       <c r="G333">
         <v>200</v>
       </c>
       <c r="H333" s="3" t="s">
-        <v>1079</v>
+        <v>1076</v>
       </c>
       <c r="I333">
         <v>0</v>
@@ -49679,28 +49714,28 @@
         <v>0</v>
       </c>
       <c r="C334" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D334" s="2" t="s">
+        <v>1080</v>
+      </c>
+      <c r="E334" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F334" t="s">
         <v>1082</v>
       </c>
-      <c r="D334" s="2" t="s">
+      <c r="G334" s="7" t="s">
         <v>1083</v>
       </c>
-      <c r="E334" t="s">
+      <c r="H334" s="7" t="s">
         <v>1084</v>
       </c>
-      <c r="F334" t="s">
+      <c r="I334" s="7" t="s">
         <v>1085</v>
       </c>
-      <c r="G334" s="7" t="s">
+      <c r="J334" s="7" t="s">
         <v>1086</v>
-      </c>
-      <c r="H334" s="7" t="s">
-        <v>1087</v>
-      </c>
-      <c r="I334" s="7" t="s">
-        <v>1088</v>
-      </c>
-      <c r="J334" s="7" t="s">
-        <v>1089</v>
       </c>
       <c r="K334">
         <v>0</v>
@@ -49736,22 +49771,22 @@
         <v>0</v>
       </c>
       <c r="C335" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D335" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E335" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F335" t="s">
         <v>1082</v>
       </c>
-      <c r="D335" s="2" t="s">
-        <v>1090</v>
-      </c>
-      <c r="E335" t="s">
-        <v>1084</v>
-      </c>
-      <c r="F335" t="s">
-        <v>1085</v>
-      </c>
       <c r="G335" s="7" t="s">
-        <v>1091</v>
+        <v>1088</v>
       </c>
       <c r="H335" s="7" t="s">
-        <v>1092</v>
+        <v>1089</v>
       </c>
       <c r="I335">
         <v>0</v>
@@ -49793,22 +49828,22 @@
         <v>0</v>
       </c>
       <c r="C336" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D336" s="2" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E336" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F336" t="s">
         <v>1082</v>
       </c>
-      <c r="D336" s="2" t="s">
-        <v>1093</v>
-      </c>
-      <c r="E336" t="s">
-        <v>1084</v>
-      </c>
-      <c r="F336" t="s">
-        <v>1085</v>
-      </c>
       <c r="G336" s="7" t="s">
-        <v>1094</v>
+        <v>1091</v>
       </c>
       <c r="H336" s="7" t="s">
-        <v>1095</v>
+        <v>1092</v>
       </c>
       <c r="I336">
         <v>0</v>
@@ -49850,22 +49885,22 @@
         <v>0</v>
       </c>
       <c r="C337" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D337" s="2" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E337" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F337" t="s">
         <v>1082</v>
       </c>
-      <c r="D337" s="2" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E337" t="s">
-        <v>1084</v>
-      </c>
-      <c r="F337" t="s">
-        <v>1085</v>
-      </c>
       <c r="G337" s="7" t="s">
-        <v>1097</v>
+        <v>1094</v>
       </c>
       <c r="H337" s="7" t="s">
-        <v>1098</v>
+        <v>1095</v>
       </c>
       <c r="I337">
         <v>0</v>
@@ -49907,19 +49942,19 @@
         <v>0</v>
       </c>
       <c r="C338" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D338" s="2" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E338" t="s">
+        <v>1081</v>
+      </c>
+      <c r="F338" t="s">
         <v>1082</v>
       </c>
-      <c r="D338" s="2" t="s">
-        <v>1099</v>
-      </c>
-      <c r="E338" t="s">
-        <v>1084</v>
-      </c>
-      <c r="F338" t="s">
-        <v>1085</v>
-      </c>
       <c r="G338" s="7" t="s">
-        <v>1100</v>
+        <v>1097</v>
       </c>
       <c r="H338">
         <v>0</v>
@@ -49964,34 +49999,34 @@
         <v>0</v>
       </c>
       <c r="C339" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D339" s="2" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E339" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F339" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G339" s="7" t="s">
         <v>1101</v>
       </c>
-      <c r="E339" t="s">
+      <c r="H339" s="7" t="s">
         <v>1102</v>
       </c>
-      <c r="F339" t="s">
+      <c r="I339" s="7" t="s">
         <v>1103</v>
       </c>
-      <c r="G339" s="7" t="s">
+      <c r="J339" s="7" t="s">
         <v>1104</v>
       </c>
-      <c r="H339" s="7" t="s">
+      <c r="K339" s="7" t="s">
         <v>1105</v>
       </c>
-      <c r="I339" s="7" t="s">
+      <c r="L339" s="7" t="s">
         <v>1106</v>
-      </c>
-      <c r="J339" s="7" t="s">
-        <v>1107</v>
-      </c>
-      <c r="K339" s="7" t="s">
-        <v>1108</v>
-      </c>
-      <c r="L339" s="7" t="s">
-        <v>1109</v>
       </c>
       <c r="M339">
         <v>0</v>
@@ -50021,25 +50056,25 @@
         <v>0</v>
       </c>
       <c r="C340" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D340" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E340" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F340" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G340" s="7" t="s">
+        <v>1108</v>
+      </c>
+      <c r="H340" s="7" t="s">
+        <v>1109</v>
+      </c>
+      <c r="I340" s="7" t="s">
         <v>1110</v>
-      </c>
-      <c r="E340" t="s">
-        <v>1102</v>
-      </c>
-      <c r="F340" t="s">
-        <v>1103</v>
-      </c>
-      <c r="G340" s="7" t="s">
-        <v>1111</v>
-      </c>
-      <c r="H340" s="7" t="s">
-        <v>1112</v>
-      </c>
-      <c r="I340" s="7" t="s">
-        <v>1113</v>
       </c>
       <c r="J340">
         <v>0</v>
@@ -50078,25 +50113,25 @@
         <v>0</v>
       </c>
       <c r="C341" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D341" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E341" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F341" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G341" s="7" t="s">
+        <v>1112</v>
+      </c>
+      <c r="H341" s="7" t="s">
+        <v>1113</v>
+      </c>
+      <c r="I341" s="7" t="s">
         <v>1114</v>
-      </c>
-      <c r="E341" t="s">
-        <v>1102</v>
-      </c>
-      <c r="F341" t="s">
-        <v>1103</v>
-      </c>
-      <c r="G341" s="7" t="s">
-        <v>1115</v>
-      </c>
-      <c r="H341" s="7" t="s">
-        <v>1116</v>
-      </c>
-      <c r="I341" s="7" t="s">
-        <v>1117</v>
       </c>
       <c r="J341">
         <v>0</v>
@@ -50135,25 +50170,25 @@
         <v>0</v>
       </c>
       <c r="C342" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="E342" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="F342" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="G342" s="7" t="s">
-        <v>1119</v>
+        <v>1116</v>
       </c>
       <c r="H342" s="7" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="I342" s="7" t="s">
-        <v>1120</v>
+        <v>1117</v>
       </c>
       <c r="J342">
         <v>0</v>
@@ -50192,25 +50227,25 @@
         <v>0</v>
       </c>
       <c r="C343" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>1121</v>
+        <v>1118</v>
       </c>
       <c r="E343" t="s">
-        <v>1102</v>
+        <v>1099</v>
       </c>
       <c r="F343" t="s">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="G343" s="7" t="s">
-        <v>1122</v>
+        <v>1119</v>
       </c>
       <c r="H343" s="7" t="s">
-        <v>1116</v>
+        <v>1113</v>
       </c>
       <c r="I343" s="7" t="s">
-        <v>1123</v>
+        <v>1120</v>
       </c>
       <c r="J343">
         <v>0</v>
@@ -50249,22 +50284,22 @@
         <v>0</v>
       </c>
       <c r="C344" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D344" s="2" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E344" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F344" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G344" s="7" t="s">
         <v>1124</v>
       </c>
-      <c r="E344" t="s">
+      <c r="H344" s="7" t="s">
         <v>1125</v>
-      </c>
-      <c r="F344" t="s">
-        <v>1126</v>
-      </c>
-      <c r="G344" s="7" t="s">
-        <v>1127</v>
-      </c>
-      <c r="H344" s="7" t="s">
-        <v>1128</v>
       </c>
       <c r="I344">
         <v>0</v>
@@ -50306,22 +50341,22 @@
         <v>0</v>
       </c>
       <c r="C345" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>1129</v>
+        <v>1126</v>
       </c>
       <c r="E345" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="F345" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="G345" s="7" t="s">
-        <v>1130</v>
+        <v>1127</v>
       </c>
       <c r="H345" s="7" t="s">
-        <v>1131</v>
+        <v>1128</v>
       </c>
       <c r="I345">
         <v>0</v>
@@ -50363,19 +50398,19 @@
         <v>0</v>
       </c>
       <c r="C346" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>1132</v>
+        <v>1129</v>
       </c>
       <c r="E346" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="F346" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="G346" s="7" t="s">
-        <v>1133</v>
+        <v>1130</v>
       </c>
       <c r="H346">
         <v>0</v>
@@ -50420,19 +50455,19 @@
         <v>0</v>
       </c>
       <c r="C347" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>1134</v>
+        <v>1131</v>
       </c>
       <c r="E347" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="F347" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="G347" s="7" t="s">
-        <v>1135</v>
+        <v>1132</v>
       </c>
       <c r="H347">
         <v>0</v>
@@ -50477,19 +50512,19 @@
         <v>0</v>
       </c>
       <c r="C348" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>1136</v>
+        <v>1133</v>
       </c>
       <c r="E348" t="s">
-        <v>1125</v>
+        <v>1122</v>
       </c>
       <c r="F348" t="s">
-        <v>1126</v>
+        <v>1123</v>
       </c>
       <c r="G348" s="7" t="s">
-        <v>1137</v>
+        <v>1134</v>
       </c>
       <c r="H348">
         <v>0</v>
@@ -50534,25 +50569,25 @@
         <v>0</v>
       </c>
       <c r="C349" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D349" s="2" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E349" t="s">
+        <v>1136</v>
+      </c>
+      <c r="F349" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G349" s="7" t="s">
         <v>1138</v>
       </c>
-      <c r="E349" t="s">
+      <c r="H349" s="7" t="s">
         <v>1139</v>
       </c>
-      <c r="F349" t="s">
+      <c r="I349" s="7" t="s">
         <v>1140</v>
-      </c>
-      <c r="G349" s="7" t="s">
-        <v>1141</v>
-      </c>
-      <c r="H349" s="7" t="s">
-        <v>1142</v>
-      </c>
-      <c r="I349" s="7" t="s">
-        <v>1143</v>
       </c>
       <c r="J349">
         <v>0</v>
@@ -50591,25 +50626,25 @@
         <v>0</v>
       </c>
       <c r="C350" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D350" s="2" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E350" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F350" t="s">
+        <v>1170</v>
+      </c>
+      <c r="G350" s="7" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H350" s="7" t="s">
         <v>1144</v>
       </c>
-      <c r="E350" t="s">
+      <c r="I350" s="7" t="s">
         <v>1145</v>
-      </c>
-      <c r="F350" t="s">
-        <v>1173</v>
-      </c>
-      <c r="G350" s="7" t="s">
-        <v>1146</v>
-      </c>
-      <c r="H350" s="7" t="s">
-        <v>1147</v>
-      </c>
-      <c r="I350" s="7" t="s">
-        <v>1148</v>
       </c>
       <c r="J350">
         <v>0</v>
@@ -50648,16 +50683,16 @@
         <v>0</v>
       </c>
       <c r="C351" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>1149</v>
+        <v>1146</v>
       </c>
       <c r="E351" t="s">
-        <v>1150</v>
+        <v>1147</v>
       </c>
       <c r="F351" t="s">
-        <v>1151</v>
+        <v>1148</v>
       </c>
       <c r="G351">
         <v>1</v>
@@ -50705,16 +50740,16 @@
         <v>0</v>
       </c>
       <c r="C352" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>1152</v>
+        <v>1149</v>
       </c>
       <c r="E352" t="s">
-        <v>1153</v>
+        <v>1150</v>
       </c>
       <c r="F352" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="G352">
         <v>100</v>
@@ -50761,16 +50796,16 @@
         <v>0</v>
       </c>
       <c r="C353" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D353" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E353" t="s">
+        <v>1155</v>
+      </c>
+      <c r="F353" t="s">
         <v>1156</v>
-      </c>
-      <c r="D353" s="2" t="s">
-        <v>1157</v>
-      </c>
-      <c r="E353" t="s">
-        <v>1158</v>
-      </c>
-      <c r="F353" t="s">
-        <v>1159</v>
       </c>
       <c r="G353">
         <v>125</v>
@@ -50818,16 +50853,16 @@
         <v>0</v>
       </c>
       <c r="C354" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>1160</v>
+        <v>1157</v>
       </c>
       <c r="E354" t="s">
-        <v>1161</v>
+        <v>1158</v>
       </c>
       <c r="F354" t="s">
-        <v>1162</v>
+        <v>1159</v>
       </c>
       <c r="G354">
         <v>6</v>
@@ -50875,16 +50910,16 @@
         <v>0</v>
       </c>
       <c r="C355" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>1163</v>
+        <v>1160</v>
       </c>
       <c r="E355" t="s">
-        <v>1164</v>
+        <v>1161</v>
       </c>
       <c r="F355" t="s">
-        <v>1165</v>
+        <v>1162</v>
       </c>
       <c r="G355">
         <v>8</v>
@@ -50932,16 +50967,16 @@
         <v>0</v>
       </c>
       <c r="C356" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>1166</v>
+        <v>1163</v>
       </c>
       <c r="E356" t="s">
-        <v>1167</v>
+        <v>1164</v>
       </c>
       <c r="F356" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="G356">
         <v>1.6</v>
@@ -50989,16 +51024,16 @@
         <v>0</v>
       </c>
       <c r="C357" t="s">
-        <v>1082</v>
+        <v>1079</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="E357" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
       <c r="F357" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="G357">
         <v>4</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A2C7366-2865-4DAC-BBE8-DF42FE716CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89938B76-0144-4163-9663-1C77FAF80B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2003" uniqueCount="1193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2008" uniqueCount="1198">
   <si>
     <t>編號</t>
   </si>
@@ -3839,9 +3839,6 @@
     <t>a=生命與四維最終倍率 b=升級經驗倍率  c=升級經驗基礎增加值 d=階級名稱 e=潛力技能等級上限（查表）。 f=已停用（舊融合技上限增加值，2026-09-29 移除）。</t>
   </si>
   <si>
-    <t>2.5000000000000001E-3</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -4392,6 +4389,25 @@
   </si>
   <si>
     <t>不再受負重影響。</t>
+  </si>
+  <si>
+    <t>每次攻擊命中有 a% 機率追加「連擊數」次攻擊；連擊數 = b×LN(暴擊率÷100) + c×LN(攻速÷5) + d×LN(冷卻縮減÷60)</t>
+  </si>
+  <si>
+    <t>a=命中時觸發連擊的機率% b=暴擊率溢出的自然對數乘數（暴擊率超過 100% 才有） c=攻速溢出的乘數（原始攻速超過 5 次/秒才有） d=冷卻縮減溢出的乘數（原始冷卻縮減超過 60% 才有）。各項低於門檻時為 0。</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.65</t>
+  </si>
+  <si>
+    <t>0.8</t>
   </si>
 </sst>
 </file>
@@ -9047,10 +9063,10 @@
         <v>生命上限</v>
       </c>
       <c r="E58" s="7" t="s">
+        <v>1170</v>
+      </c>
+      <c r="F58" s="7" t="s">
         <v>1171</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>1172</v>
       </c>
       <c r="G58">
         <f>計算表!G58</f>
@@ -9193,20 +9209,20 @@
         <v>法力恢復/秒</v>
       </c>
       <c r="E60" s="7" t="s">
+        <v>1172</v>
+      </c>
+      <c r="F60" s="7" t="s">
         <v>1173</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>1174</v>
       </c>
       <c r="G60">
         <f>計算表!G60</f>
         <v>1</v>
       </c>
       <c r="H60" s="7" t="s">
+        <v>1174</v>
+      </c>
+      <c r="I60" s="7" t="s">
         <v>1175</v>
-      </c>
-      <c r="I60" s="7" t="s">
-        <v>1176</v>
       </c>
       <c r="J60">
         <f>計算表!J60</f>
@@ -9411,10 +9427,10 @@
         <v>物理防禦</v>
       </c>
       <c r="E63" s="7" t="s">
+        <v>1176</v>
+      </c>
+      <c r="F63" s="7" t="s">
         <v>1177</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>1178</v>
       </c>
       <c r="G63">
         <f>計算表!G63</f>
@@ -9429,10 +9445,10 @@
         <v>2.4</v>
       </c>
       <c r="J63" s="7" t="s">
+        <v>1178</v>
+      </c>
+      <c r="K63" s="7" t="s">
         <v>1179</v>
-      </c>
-      <c r="K63" s="7" t="s">
-        <v>1180</v>
       </c>
       <c r="L63">
         <f>計算表!L63</f>
@@ -9481,10 +9497,10 @@
         <v>魔法防禦</v>
       </c>
       <c r="E64" s="7" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F64" s="7" t="s">
         <v>1181</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>1182</v>
       </c>
       <c r="G64">
         <f>計算表!G64</f>
@@ -9499,10 +9515,10 @@
         <v>2.4</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="L64">
         <f>計算表!L64</f>
@@ -9563,7 +9579,7 @@
         <v>5</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="I65">
         <f>計算表!I65</f>
@@ -9623,28 +9639,23 @@
         <f>計算表!D66</f>
         <v>連擊數</v>
       </c>
-      <c r="E66" t="str">
-        <f>計算表!E66</f>
-        <v>a* LN(暴擊率%) + b * 暴擊率% + c</v>
-      </c>
-      <c r="F66" t="str">
-        <f>計算表!F66</f>
-        <v>a=自然對數乘數 b=爆擊乘數 c=常數 。</v>
-      </c>
-      <c r="G66">
-        <f>計算表!G66</f>
-        <v>0.875</v>
+      <c r="E66" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>1194</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>1016</v>
-      </c>
-      <c r="I66">
-        <f>計算表!I66</f>
-        <v>0.05</v>
-      </c>
-      <c r="J66">
-        <f>計算表!J66</f>
-        <v>0</v>
+        <v>1195</v>
+      </c>
+      <c r="I66" s="7" t="s">
+        <v>1196</v>
+      </c>
+      <c r="J66" s="7" t="s">
+        <v>1197</v>
       </c>
       <c r="K66">
         <f>計算表!K66</f>
@@ -9700,14 +9711,14 @@
         <v>126</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="G67">
         <f>計算表!G67</f>
         <v>150</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="I67">
         <f>計算表!I67</f>
@@ -9780,7 +9791,7 @@
         <v>0.86</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I68">
         <f>計算表!I68</f>
@@ -9849,7 +9860,7 @@
         <v>a=每點敏捷%（減去敵方閃避後最低 5%）。</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H69">
         <f>計算表!H69</f>
@@ -9922,7 +9933,7 @@
         <v>a=每點敏捷%。</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H70">
         <f>計算表!H70</f>
@@ -9983,19 +9994,19 @@
         <v>2-屬性派生</v>
       </c>
       <c r="D71" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="E71" s="7" t="s">
         <v>1187</v>
       </c>
-      <c r="E71" s="7" t="s">
+      <c r="F71" s="7" t="s">
         <v>1188</v>
       </c>
-      <c r="F71" s="7" t="s">
+      <c r="G71" s="7" t="s">
         <v>1189</v>
       </c>
-      <c r="G71" s="7" t="s">
+      <c r="H71" s="7" t="s">
         <v>1190</v>
-      </c>
-      <c r="H71" s="7" t="s">
-        <v>1191</v>
       </c>
       <c r="I71">
         <f>計算表!I71</f>
@@ -11836,7 +11847,7 @@
         <v>忽略敵人防禦% = 穿透%/(穿透%+a)</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="G96">
         <f>計算表!G96</f>
@@ -13623,7 +13634,7 @@
         <v>0.5</v>
       </c>
       <c r="I120" s="7" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="J120">
         <f>計算表!J120</f>
@@ -15538,7 +15549,7 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條。</v>
       </c>
       <c r="G146" s="7" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="H146">
         <f>計算表!H146</f>
@@ -15611,13 +15622,13 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條。</v>
       </c>
       <c r="G147" s="7" t="s">
+        <v>1019</v>
+      </c>
+      <c r="H147" s="7" t="s">
         <v>1020</v>
       </c>
-      <c r="H147" s="7" t="s">
+      <c r="I147" s="7" t="s">
         <v>1021</v>
-      </c>
-      <c r="I147" s="7" t="s">
-        <v>1022</v>
       </c>
       <c r="J147">
         <f>計算表!J147</f>
@@ -15682,20 +15693,20 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條。</v>
       </c>
       <c r="G148" s="7" t="s">
+        <v>1022</v>
+      </c>
+      <c r="H148" s="7" t="s">
         <v>1023</v>
-      </c>
-      <c r="H148" s="7" t="s">
-        <v>1024</v>
       </c>
       <c r="I148">
         <f>計算表!I148</f>
         <v>9.11754</v>
       </c>
       <c r="J148" s="7" t="s">
+        <v>1024</v>
+      </c>
+      <c r="K148" s="7" t="s">
         <v>1025</v>
-      </c>
-      <c r="K148" s="7" t="s">
-        <v>1026</v>
       </c>
       <c r="L148">
         <f>計算表!L148</f>
@@ -15752,22 +15763,22 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條。</v>
       </c>
       <c r="G149" s="7" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H149" s="7" t="s">
         <v>1027</v>
       </c>
-      <c r="H149" s="7" t="s">
+      <c r="I149" s="7" t="s">
         <v>1028</v>
       </c>
-      <c r="I149" s="7" t="s">
+      <c r="J149" s="7" t="s">
         <v>1029</v>
       </c>
-      <c r="J149" s="7" t="s">
+      <c r="K149" s="7" t="s">
         <v>1030</v>
       </c>
-      <c r="K149" s="7" t="s">
+      <c r="L149" s="7" t="s">
         <v>1031</v>
-      </c>
-      <c r="L149" s="7" t="s">
-        <v>1032</v>
       </c>
       <c r="M149">
         <f>計算表!M149</f>
@@ -15820,28 +15831,28 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條。</v>
       </c>
       <c r="G150" s="7" t="s">
+        <v>1032</v>
+      </c>
+      <c r="H150" s="7" t="s">
         <v>1033</v>
       </c>
-      <c r="H150" s="7" t="s">
+      <c r="I150" s="7" t="s">
         <v>1034</v>
       </c>
-      <c r="I150" s="7" t="s">
+      <c r="J150" s="7" t="s">
         <v>1035</v>
       </c>
-      <c r="J150" s="7" t="s">
+      <c r="K150" s="7" t="s">
         <v>1036</v>
       </c>
-      <c r="K150" s="7" t="s">
+      <c r="L150" s="7" t="s">
         <v>1037</v>
       </c>
-      <c r="L150" s="7" t="s">
+      <c r="M150" s="7" t="s">
         <v>1038</v>
       </c>
-      <c r="M150" s="7" t="s">
+      <c r="N150" s="7" t="s">
         <v>1039</v>
-      </c>
-      <c r="N150" s="7" t="s">
-        <v>1040</v>
       </c>
       <c r="O150">
         <f>計算表!O150</f>
@@ -15886,28 +15897,28 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條。</v>
       </c>
       <c r="G151" s="7" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H151" s="7" t="s">
         <v>1041</v>
       </c>
-      <c r="H151" s="7" t="s">
+      <c r="I151" s="7" t="s">
         <v>1042</v>
       </c>
-      <c r="I151" s="7" t="s">
+      <c r="J151" s="7" t="s">
         <v>1043</v>
       </c>
-      <c r="J151" s="7" t="s">
+      <c r="K151" s="7" t="s">
         <v>1044</v>
       </c>
-      <c r="K151" s="7" t="s">
+      <c r="L151" s="7" t="s">
         <v>1045</v>
       </c>
-      <c r="L151" s="7" t="s">
+      <c r="M151" s="7" t="s">
         <v>1046</v>
       </c>
-      <c r="M151" s="7" t="s">
+      <c r="N151" s="7" t="s">
         <v>1047</v>
-      </c>
-      <c r="N151" s="7" t="s">
-        <v>1048</v>
       </c>
       <c r="O151">
         <f>計算表!O151</f>
@@ -15952,31 +15963,31 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條 j=9條。</v>
       </c>
       <c r="G152" s="7" t="s">
+        <v>1048</v>
+      </c>
+      <c r="H152" s="7" t="s">
         <v>1049</v>
       </c>
-      <c r="H152" s="7" t="s">
+      <c r="I152" s="7" t="s">
         <v>1050</v>
       </c>
-      <c r="I152" s="7" t="s">
+      <c r="J152" s="7" t="s">
         <v>1051</v>
       </c>
-      <c r="J152" s="7" t="s">
+      <c r="K152" s="7" t="s">
         <v>1052</v>
       </c>
-      <c r="K152" s="7" t="s">
+      <c r="L152" s="7" t="s">
         <v>1053</v>
       </c>
-      <c r="L152" s="7" t="s">
+      <c r="M152" s="7" t="s">
         <v>1054</v>
       </c>
-      <c r="M152" s="7" t="s">
+      <c r="N152" s="7" t="s">
         <v>1055</v>
       </c>
-      <c r="N152" s="7" t="s">
+      <c r="O152" s="7" t="s">
         <v>1056</v>
-      </c>
-      <c r="O152" s="7" t="s">
-        <v>1057</v>
       </c>
       <c r="P152">
         <f>計算表!P152</f>
@@ -16017,7 +16028,7 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條 j=9條 k=10條。</v>
       </c>
       <c r="G153" s="7" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="H153">
         <f>計算表!H153</f>
@@ -17500,7 +17511,7 @@
         <v>200</v>
       </c>
       <c r="H173" s="7" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="I173">
         <f>計算表!I173</f>
@@ -18087,7 +18098,7 @@
         <v>a=基礎權重 b=權重加成 c=加成上限 d=出現門檻。普通無加成。神鑄創世不參與此擲骰。(裝備合成才有作用，目前功能關閉中)</v>
       </c>
       <c r="G181" s="7" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="H181" t="str">
         <f>計算表!H181</f>
@@ -20906,7 +20917,7 @@
         <v>1</v>
       </c>
       <c r="I219" s="7" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="J219">
         <f>計算表!J220</f>
@@ -21040,7 +21051,7 @@
         <v>611</v>
       </c>
       <c r="F221" s="7" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="G221">
         <f>計算表!G222</f>
@@ -25919,10 +25930,10 @@
         <v>等級上限</v>
       </c>
       <c r="E287" s="7" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F287" s="7" t="s">
         <v>1062</v>
-      </c>
-      <c r="F287" s="7" t="s">
-        <v>1063</v>
       </c>
       <c r="G287">
         <f>計算表!G291</f>
@@ -27553,7 +27564,7 @@
         <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）。</v>
       </c>
       <c r="G309" s="7" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="H309">
         <f>計算表!H325</f>
@@ -27922,7 +27933,7 @@
         <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）。</v>
       </c>
       <c r="G314" s="7" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="H314">
         <f>計算表!H330</f>
@@ -32396,7 +32407,7 @@
         <v>149</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -32453,7 +32464,7 @@
         <v>149</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -34046,10 +34057,10 @@
         <v>143</v>
       </c>
       <c r="E72" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F72" t="s">
         <v>1068</v>
-      </c>
-      <c r="F72" t="s">
-        <v>1069</v>
       </c>
       <c r="G72">
         <v>5</v>
@@ -34901,10 +34912,10 @@
         <v>209</v>
       </c>
       <c r="E87" s="7" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F87" s="7" t="s">
         <v>1074</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>1075</v>
       </c>
       <c r="G87">
         <v>10</v>
@@ -37127,7 +37138,7 @@
         <v>270</v>
       </c>
       <c r="F126" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="G126">
         <v>4</v>
@@ -37640,7 +37651,7 @@
         <v>274</v>
       </c>
       <c r="F135" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="G135" t="s">
         <v>276</v>
@@ -37697,7 +37708,7 @@
         <v>274</v>
       </c>
       <c r="F136" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="G136" s="3" t="s">
         <v>968</v>
@@ -37754,7 +37765,7 @@
         <v>274</v>
       </c>
       <c r="F137" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="G137" s="3" t="s">
         <v>969</v>
@@ -37811,7 +37822,7 @@
         <v>274</v>
       </c>
       <c r="F138" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="G138" s="3" t="s">
         <v>984</v>
@@ -37868,7 +37879,7 @@
         <v>274</v>
       </c>
       <c r="F139" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="G139" s="3" t="s">
         <v>977</v>
@@ -49039,7 +49050,7 @@
         <v>39</v>
       </c>
       <c r="F322" s="7" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G322">
         <v>1</v>
@@ -49096,7 +49107,7 @@
         <v>39</v>
       </c>
       <c r="F323" s="7" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G323">
         <v>1.35</v>
@@ -49153,7 +49164,7 @@
         <v>39</v>
       </c>
       <c r="F324" s="7" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G324">
         <v>1.75</v>
@@ -49210,7 +49221,7 @@
         <v>39</v>
       </c>
       <c r="F325" s="7" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G325">
         <v>2.2999999999999998</v>
@@ -49267,7 +49278,7 @@
         <v>39</v>
       </c>
       <c r="F326" s="7" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G326">
         <v>3</v>
@@ -49324,7 +49335,7 @@
         <v>39</v>
       </c>
       <c r="F327" s="7" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G327">
         <v>4</v>
@@ -49381,7 +49392,7 @@
         <v>39</v>
       </c>
       <c r="F328" s="7" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G328">
         <v>5.2</v>
@@ -49438,7 +49449,7 @@
         <v>39</v>
       </c>
       <c r="F329" s="7" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G329">
         <v>6.8</v>
@@ -49495,7 +49506,7 @@
         <v>39</v>
       </c>
       <c r="F330" s="7" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="G330">
         <v>10.199999999999999</v>
@@ -49552,7 +49563,7 @@
         <v>39</v>
       </c>
       <c r="F331" s="7" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="G331">
         <v>15.3</v>
@@ -49609,7 +49620,7 @@
         <v>39</v>
       </c>
       <c r="F332" s="7" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="G332">
         <v>22.95</v>
@@ -49657,22 +49668,22 @@
         <v>0</v>
       </c>
       <c r="C333" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D333" t="s">
         <v>1070</v>
       </c>
-      <c r="D333" t="s">
+      <c r="E333" t="s">
         <v>1071</v>
       </c>
-      <c r="E333" t="s">
+      <c r="F333" t="s">
         <v>1072</v>
-      </c>
-      <c r="F333" t="s">
-        <v>1073</v>
       </c>
       <c r="G333">
         <v>200</v>
       </c>
       <c r="H333" s="3" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="I333">
         <v>0</v>
@@ -49714,28 +49725,28 @@
         <v>0</v>
       </c>
       <c r="C334" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D334" s="2" t="s">
         <v>1079</v>
       </c>
-      <c r="D334" s="2" t="s">
+      <c r="E334" t="s">
         <v>1080</v>
       </c>
-      <c r="E334" t="s">
+      <c r="F334" t="s">
         <v>1081</v>
       </c>
-      <c r="F334" t="s">
+      <c r="G334" s="7" t="s">
         <v>1082</v>
       </c>
-      <c r="G334" s="7" t="s">
+      <c r="H334" s="7" t="s">
         <v>1083</v>
       </c>
-      <c r="H334" s="7" t="s">
+      <c r="I334" s="7" t="s">
         <v>1084</v>
       </c>
-      <c r="I334" s="7" t="s">
+      <c r="J334" s="7" t="s">
         <v>1085</v>
-      </c>
-      <c r="J334" s="7" t="s">
-        <v>1086</v>
       </c>
       <c r="K334">
         <v>0</v>
@@ -49771,22 +49782,22 @@
         <v>0</v>
       </c>
       <c r="C335" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D335" s="2" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E335" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F335" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G335" s="7" t="s">
         <v>1087</v>
       </c>
-      <c r="E335" t="s">
-        <v>1081</v>
-      </c>
-      <c r="F335" t="s">
-        <v>1082</v>
-      </c>
-      <c r="G335" s="7" t="s">
+      <c r="H335" s="7" t="s">
         <v>1088</v>
-      </c>
-      <c r="H335" s="7" t="s">
-        <v>1089</v>
       </c>
       <c r="I335">
         <v>0</v>
@@ -49828,22 +49839,22 @@
         <v>0</v>
       </c>
       <c r="C336" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D336" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E336" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F336" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G336" s="7" t="s">
         <v>1090</v>
       </c>
-      <c r="E336" t="s">
-        <v>1081</v>
-      </c>
-      <c r="F336" t="s">
-        <v>1082</v>
-      </c>
-      <c r="G336" s="7" t="s">
+      <c r="H336" s="7" t="s">
         <v>1091</v>
-      </c>
-      <c r="H336" s="7" t="s">
-        <v>1092</v>
       </c>
       <c r="I336">
         <v>0</v>
@@ -49885,22 +49896,22 @@
         <v>0</v>
       </c>
       <c r="C337" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D337" s="2" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E337" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F337" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G337" s="7" t="s">
         <v>1093</v>
       </c>
-      <c r="E337" t="s">
-        <v>1081</v>
-      </c>
-      <c r="F337" t="s">
-        <v>1082</v>
-      </c>
-      <c r="G337" s="7" t="s">
+      <c r="H337" s="7" t="s">
         <v>1094</v>
-      </c>
-      <c r="H337" s="7" t="s">
-        <v>1095</v>
       </c>
       <c r="I337">
         <v>0</v>
@@ -49942,19 +49953,19 @@
         <v>0</v>
       </c>
       <c r="C338" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D338" s="2" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E338" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F338" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G338" s="7" t="s">
         <v>1096</v>
-      </c>
-      <c r="E338" t="s">
-        <v>1081</v>
-      </c>
-      <c r="F338" t="s">
-        <v>1082</v>
-      </c>
-      <c r="G338" s="7" t="s">
-        <v>1097</v>
       </c>
       <c r="H338">
         <v>0</v>
@@ -49999,34 +50010,34 @@
         <v>0</v>
       </c>
       <c r="C339" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D339" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E339" t="s">
         <v>1098</v>
       </c>
-      <c r="E339" t="s">
+      <c r="F339" t="s">
         <v>1099</v>
       </c>
-      <c r="F339" t="s">
+      <c r="G339" s="7" t="s">
         <v>1100</v>
       </c>
-      <c r="G339" s="7" t="s">
+      <c r="H339" s="7" t="s">
         <v>1101</v>
       </c>
-      <c r="H339" s="7" t="s">
+      <c r="I339" s="7" t="s">
         <v>1102</v>
       </c>
-      <c r="I339" s="7" t="s">
+      <c r="J339" s="7" t="s">
         <v>1103</v>
       </c>
-      <c r="J339" s="7" t="s">
+      <c r="K339" s="7" t="s">
         <v>1104</v>
       </c>
-      <c r="K339" s="7" t="s">
+      <c r="L339" s="7" t="s">
         <v>1105</v>
-      </c>
-      <c r="L339" s="7" t="s">
-        <v>1106</v>
       </c>
       <c r="M339">
         <v>0</v>
@@ -50056,25 +50067,25 @@
         <v>0</v>
       </c>
       <c r="C340" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D340" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E340" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F340" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G340" s="7" t="s">
         <v>1107</v>
       </c>
-      <c r="E340" t="s">
-        <v>1099</v>
-      </c>
-      <c r="F340" t="s">
-        <v>1100</v>
-      </c>
-      <c r="G340" s="7" t="s">
+      <c r="H340" s="7" t="s">
         <v>1108</v>
       </c>
-      <c r="H340" s="7" t="s">
+      <c r="I340" s="7" t="s">
         <v>1109</v>
-      </c>
-      <c r="I340" s="7" t="s">
-        <v>1110</v>
       </c>
       <c r="J340">
         <v>0</v>
@@ -50113,25 +50124,25 @@
         <v>0</v>
       </c>
       <c r="C341" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D341" s="2" t="s">
+        <v>1110</v>
+      </c>
+      <c r="E341" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F341" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G341" s="7" t="s">
         <v>1111</v>
       </c>
-      <c r="E341" t="s">
-        <v>1099</v>
-      </c>
-      <c r="F341" t="s">
-        <v>1100</v>
-      </c>
-      <c r="G341" s="7" t="s">
+      <c r="H341" s="7" t="s">
         <v>1112</v>
       </c>
-      <c r="H341" s="7" t="s">
+      <c r="I341" s="7" t="s">
         <v>1113</v>
-      </c>
-      <c r="I341" s="7" t="s">
-        <v>1114</v>
       </c>
       <c r="J341">
         <v>0</v>
@@ -50170,25 +50181,25 @@
         <v>0</v>
       </c>
       <c r="C342" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D342" s="2" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E342" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F342" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G342" s="7" t="s">
         <v>1115</v>
       </c>
-      <c r="E342" t="s">
-        <v>1099</v>
-      </c>
-      <c r="F342" t="s">
-        <v>1100</v>
-      </c>
-      <c r="G342" s="7" t="s">
+      <c r="H342" s="7" t="s">
+        <v>1112</v>
+      </c>
+      <c r="I342" s="7" t="s">
         <v>1116</v>
-      </c>
-      <c r="H342" s="7" t="s">
-        <v>1113</v>
-      </c>
-      <c r="I342" s="7" t="s">
-        <v>1117</v>
       </c>
       <c r="J342">
         <v>0</v>
@@ -50227,25 +50238,25 @@
         <v>0</v>
       </c>
       <c r="C343" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D343" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E343" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F343" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G343" s="7" t="s">
         <v>1118</v>
       </c>
-      <c r="E343" t="s">
-        <v>1099</v>
-      </c>
-      <c r="F343" t="s">
-        <v>1100</v>
-      </c>
-      <c r="G343" s="7" t="s">
+      <c r="H343" s="7" t="s">
+        <v>1112</v>
+      </c>
+      <c r="I343" s="7" t="s">
         <v>1119</v>
-      </c>
-      <c r="H343" s="7" t="s">
-        <v>1113</v>
-      </c>
-      <c r="I343" s="7" t="s">
-        <v>1120</v>
       </c>
       <c r="J343">
         <v>0</v>
@@ -50284,22 +50295,22 @@
         <v>0</v>
       </c>
       <c r="C344" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D344" s="2" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E344" t="s">
         <v>1121</v>
       </c>
-      <c r="E344" t="s">
+      <c r="F344" t="s">
         <v>1122</v>
       </c>
-      <c r="F344" t="s">
+      <c r="G344" s="7" t="s">
         <v>1123</v>
       </c>
-      <c r="G344" s="7" t="s">
+      <c r="H344" s="7" t="s">
         <v>1124</v>
-      </c>
-      <c r="H344" s="7" t="s">
-        <v>1125</v>
       </c>
       <c r="I344">
         <v>0</v>
@@ -50341,22 +50352,22 @@
         <v>0</v>
       </c>
       <c r="C345" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D345" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E345" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F345" t="s">
+        <v>1122</v>
+      </c>
+      <c r="G345" s="7" t="s">
         <v>1126</v>
       </c>
-      <c r="E345" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F345" t="s">
-        <v>1123</v>
-      </c>
-      <c r="G345" s="7" t="s">
+      <c r="H345" s="7" t="s">
         <v>1127</v>
-      </c>
-      <c r="H345" s="7" t="s">
-        <v>1128</v>
       </c>
       <c r="I345">
         <v>0</v>
@@ -50398,19 +50409,19 @@
         <v>0</v>
       </c>
       <c r="C346" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D346" s="2" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E346" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F346" t="s">
+        <v>1122</v>
+      </c>
+      <c r="G346" s="7" t="s">
         <v>1129</v>
-      </c>
-      <c r="E346" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F346" t="s">
-        <v>1123</v>
-      </c>
-      <c r="G346" s="7" t="s">
-        <v>1130</v>
       </c>
       <c r="H346">
         <v>0</v>
@@ -50455,19 +50466,19 @@
         <v>0</v>
       </c>
       <c r="C347" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D347" s="2" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E347" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F347" t="s">
+        <v>1122</v>
+      </c>
+      <c r="G347" s="7" t="s">
         <v>1131</v>
-      </c>
-      <c r="E347" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F347" t="s">
-        <v>1123</v>
-      </c>
-      <c r="G347" s="7" t="s">
-        <v>1132</v>
       </c>
       <c r="H347">
         <v>0</v>
@@ -50512,19 +50523,19 @@
         <v>0</v>
       </c>
       <c r="C348" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D348" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E348" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F348" t="s">
+        <v>1122</v>
+      </c>
+      <c r="G348" s="7" t="s">
         <v>1133</v>
-      </c>
-      <c r="E348" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F348" t="s">
-        <v>1123</v>
-      </c>
-      <c r="G348" s="7" t="s">
-        <v>1134</v>
       </c>
       <c r="H348">
         <v>0</v>
@@ -50569,25 +50580,25 @@
         <v>0</v>
       </c>
       <c r="C349" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D349" s="2" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E349" t="s">
         <v>1135</v>
       </c>
-      <c r="E349" t="s">
+      <c r="F349" t="s">
         <v>1136</v>
       </c>
-      <c r="F349" t="s">
+      <c r="G349" s="7" t="s">
         <v>1137</v>
       </c>
-      <c r="G349" s="7" t="s">
+      <c r="H349" s="7" t="s">
         <v>1138</v>
       </c>
-      <c r="H349" s="7" t="s">
+      <c r="I349" s="7" t="s">
         <v>1139</v>
-      </c>
-      <c r="I349" s="7" t="s">
-        <v>1140</v>
       </c>
       <c r="J349">
         <v>0</v>
@@ -50626,25 +50637,25 @@
         <v>0</v>
       </c>
       <c r="C350" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D350" s="2" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E350" t="s">
         <v>1141</v>
       </c>
-      <c r="E350" t="s">
+      <c r="F350" t="s">
+        <v>1169</v>
+      </c>
+      <c r="G350" s="7" t="s">
         <v>1142</v>
       </c>
-      <c r="F350" t="s">
-        <v>1170</v>
-      </c>
-      <c r="G350" s="7" t="s">
+      <c r="H350" s="7" t="s">
         <v>1143</v>
       </c>
-      <c r="H350" s="7" t="s">
+      <c r="I350" s="7" t="s">
         <v>1144</v>
-      </c>
-      <c r="I350" s="7" t="s">
-        <v>1145</v>
       </c>
       <c r="J350">
         <v>0</v>
@@ -50683,16 +50694,16 @@
         <v>0</v>
       </c>
       <c r="C351" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D351" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E351" t="s">
         <v>1146</v>
       </c>
-      <c r="E351" t="s">
+      <c r="F351" t="s">
         <v>1147</v>
-      </c>
-      <c r="F351" t="s">
-        <v>1148</v>
       </c>
       <c r="G351">
         <v>1</v>
@@ -50740,16 +50751,16 @@
         <v>0</v>
       </c>
       <c r="C352" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D352" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E352" t="s">
         <v>1149</v>
       </c>
-      <c r="E352" t="s">
-        <v>1150</v>
-      </c>
       <c r="F352" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G352">
         <v>100</v>
@@ -50796,16 +50807,16 @@
         <v>0</v>
       </c>
       <c r="C353" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D353" s="2" t="s">
         <v>1153</v>
       </c>
-      <c r="D353" s="2" t="s">
+      <c r="E353" t="s">
         <v>1154</v>
       </c>
-      <c r="E353" t="s">
+      <c r="F353" t="s">
         <v>1155</v>
-      </c>
-      <c r="F353" t="s">
-        <v>1156</v>
       </c>
       <c r="G353">
         <v>125</v>
@@ -50853,16 +50864,16 @@
         <v>0</v>
       </c>
       <c r="C354" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D354" s="2" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E354" t="s">
         <v>1157</v>
       </c>
-      <c r="E354" t="s">
+      <c r="F354" t="s">
         <v>1158</v>
-      </c>
-      <c r="F354" t="s">
-        <v>1159</v>
       </c>
       <c r="G354">
         <v>6</v>
@@ -50910,16 +50921,16 @@
         <v>0</v>
       </c>
       <c r="C355" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D355" s="2" t="s">
+        <v>1159</v>
+      </c>
+      <c r="E355" t="s">
         <v>1160</v>
       </c>
-      <c r="E355" t="s">
+      <c r="F355" t="s">
         <v>1161</v>
-      </c>
-      <c r="F355" t="s">
-        <v>1162</v>
       </c>
       <c r="G355">
         <v>8</v>
@@ -50967,16 +50978,16 @@
         <v>0</v>
       </c>
       <c r="C356" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D356" s="2" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E356" t="s">
         <v>1163</v>
       </c>
-      <c r="E356" t="s">
+      <c r="F356" t="s">
         <v>1164</v>
-      </c>
-      <c r="F356" t="s">
-        <v>1165</v>
       </c>
       <c r="G356">
         <v>1.6</v>
@@ -51024,16 +51035,16 @@
         <v>0</v>
       </c>
       <c r="C357" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="D357" s="2" t="s">
+        <v>1165</v>
+      </c>
+      <c r="E357" t="s">
         <v>1166</v>
       </c>
-      <c r="E357" t="s">
+      <c r="F357" t="s">
         <v>1167</v>
-      </c>
-      <c r="F357" t="s">
-        <v>1168</v>
       </c>
       <c r="G357">
         <v>4</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89938B76-0144-4163-9663-1C77FAF80B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63790264-F0AD-4CE6-9A67-4150603B8E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4391,12 +4391,6 @@
     <t>不再受負重影響。</t>
   </si>
   <si>
-    <t>每次攻擊命中有 a% 機率追加「連擊數」次攻擊；連擊數 = b×LN(暴擊率÷100) + c×LN(攻速÷5) + d×LN(冷卻縮減÷60)</t>
-  </si>
-  <si>
-    <t>a=命中時觸發連擊的機率% b=暴擊率溢出的自然對數乘數（暴擊率超過 100% 才有） c=攻速溢出的乘數（原始攻速超過 5 次/秒才有） d=冷卻縮減溢出的乘數（原始冷卻縮減超過 60% 才有）。各項低於門檻時為 0。</t>
-  </si>
-  <si>
     <t>25</t>
   </si>
   <si>
@@ -4408,6 +4402,14 @@
   </si>
   <si>
     <t>0.8</t>
+  </si>
+  <si>
+    <t>每次攻擊命中有 a% 機率追加「連擊數」次攻擊；連擊數 = b×LN(暴擊溢出%) + c×LN(攻速溢出%) + d×LN(冷卻縮減溢出%)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a=命中時觸發連擊的機率% b=暴擊乘數 c=攻速乘數 d=冷卻縮減乘數。溢出% = 超出門檻的部分（暴擊門檻 100%：暴擊率 250% → 溢出 150% → LN(1.5)；攻速門檻 5 次/秒：溢出% = (攻速−5)÷5，用未夾上限的原始攻速；冷卻縮減門檻 = 冷卻縮減上限 60%：溢出% = 冷卻縮減−60，用未夾上限的原始值）。溢出% 不超過 100%（LN ≤ 0）時該項為 0。門檻本身不在此表（暴擊 100% 為程式常數，攻速／冷卻縮減跟著各自上限）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -9640,22 +9642,22 @@
         <v>連擊數</v>
       </c>
       <c r="E66" s="7" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>1197</v>
+      </c>
+      <c r="G66" s="7" t="s">
         <v>1192</v>
       </c>
-      <c r="F66" s="7" t="s">
+      <c r="H66" s="7" t="s">
         <v>1193</v>
       </c>
-      <c r="G66" s="7" t="s">
+      <c r="I66" s="7" t="s">
         <v>1194</v>
       </c>
-      <c r="H66" s="7" t="s">
+      <c r="J66" s="7" t="s">
         <v>1195</v>
-      </c>
-      <c r="I66" s="7" t="s">
-        <v>1196</v>
-      </c>
-      <c r="J66" s="7" t="s">
-        <v>1197</v>
       </c>
       <c r="K66">
         <f>計算表!K66</f>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63790264-F0AD-4CE6-9A67-4150603B8E5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42A0C06-94DF-4E40-95CF-3D2F937CF32C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4408,7 +4408,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>a=命中時觸發連擊的機率% b=暴擊乘數 c=攻速乘數 d=冷卻縮減乘數。溢出% = 超出門檻的部分（暴擊門檻 100%：暴擊率 250% → 溢出 150% → LN(1.5)；攻速門檻 5 次/秒：溢出% = (攻速−5)÷5，用未夾上限的原始攻速；冷卻縮減門檻 = 冷卻縮減上限 60%：溢出% = 冷卻縮減−60，用未夾上限的原始值）。溢出% 不超過 100%（LN ≤ 0）時該項為 0。門檻本身不在此表（暴擊 100% 為程式常數，攻速／冷卻縮減跟著各自上限）。</t>
+    <t>a=命中時觸發連擊的機率% b=暴擊乘數 c=攻速乘數 d=冷卻縮減乘數。溢出% = 超出門檻的部分（暴擊門檻 100%：暴擊率 250% → 溢出 150% → LN(1.5)；攻速用攻速加成%（裝備詞條上的值，未夾上限），門檻 = 攻速剛好到 5 次/秒所需的加成%（約 481.4%）：溢出% = 攻速加成% − 門檻；冷卻縮減門檻 = 冷卻縮減上限 60%：溢出% = 冷卻縮減−60，用未夾上限的原始值）。溢出% 不超過 100%（LN ≤ 0）時該項為 0。門檻本身不在此表（暴擊 100% 為程式常數，攻速／冷卻縮減跟著各自上限）。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42A0C06-94DF-4E40-95CF-3D2F937CF32C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE779FF1-6225-41D6-B61B-3C25BBE2EE57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4311,9 +4311,6 @@
     <t>菁英、高級菁英、野外 BOSS、封魔塔 BOSS 每 a~b 秒換一次位置</t>
   </si>
   <si>
-    <t>這四種高級敵人不再從頭到尾站在原地：每隔 a~b 秒（隨機）會跑到新的位置，目標點以「跑位結束後仍可直接攻擊到玩家」為主（近戰貼在你身邊繞一個角度，遠程在射程內換一個方位）。跑位期間仍會攻擊。個別技能（火鏈、瘟疫、秘法加持…）有自己的跑位節奏，寫在 Skills2 敵人技能的效果參數裡。</t>
-  </si>
-  <si>
     <t>a＝所有敵人技能傷害的總倍率（%）；b＝所有敵人技能冷卻的總倍率（%，數字越大施放越慢）；c＝進場後第一次施放技能最久等幾秒；d＝場上同時存在的敵人場域（毒窪、火徑、毒十字、冰球…）上限；e＝每隻怪物一生最多能召喚幾隻小兵；f＝是否畫「生命鏈結」的連線（1＝畫、0＝不畫）。每個技能自己的冷卻、半徑、傷害倍率寫在 Skills2 表（類別＝enemy）；每種敵人帶哪些技能寫在 NPC 表。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4409,6 +4406,10 @@
   </si>
   <si>
     <t>a=命中時觸發連擊的機率% b=暴擊乘數 c=攻速乘數 d=冷卻縮減乘數。溢出% = 超出門檻的部分（暴擊門檻 100%：暴擊率 250% → 溢出 150% → LN(1.5)；攻速用攻速加成%（裝備詞條上的值，未夾上限），門檻 = 攻速剛好到 5 次/秒所需的加成%（約 481.4%）：溢出% = 攻速加成% − 門檻；冷卻縮減門檻 = 冷卻縮減上限 60%：溢出% = 冷卻縮減−60，用未夾上限的原始值）。溢出% 不超過 100%（LN ≤ 0）時該項為 0。門檻本身不在此表（暴擊 100% 為程式常數，攻速／冷卻縮減跟著各自上限）。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>這四種高級敵人不再從頭到尾站在原地：每隔 a~b 秒（隨機）會跑到新的位置，目標點以「跑位結束後仍可直接攻擊到玩家」為主（近戰貼在你身邊繞一個角度，遠程在射程內換一個方位）。跑位期間仍會攻擊。c＝跑位時的移動速度倍率（乘上該敵人的跑速；預設 1.6：玩家一直在動，敵人要跑得比平常快才追得上目標點，不會跑到一半被甩開而放棄）。個別技能（火鏈、瘟疫、秘法加持…）有自己的跑位節奏，寫在 Skills2 敵人技能的效果參數裡。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -9065,10 +9066,10 @@
         <v>生命上限</v>
       </c>
       <c r="E58" s="7" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F58" s="7" t="s">
         <v>1170</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>1171</v>
       </c>
       <c r="G58">
         <f>計算表!G58</f>
@@ -9211,20 +9212,20 @@
         <v>法力恢復/秒</v>
       </c>
       <c r="E60" s="7" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F60" s="7" t="s">
         <v>1172</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>1173</v>
       </c>
       <c r="G60">
         <f>計算表!G60</f>
         <v>1</v>
       </c>
       <c r="H60" s="7" t="s">
+        <v>1173</v>
+      </c>
+      <c r="I60" s="7" t="s">
         <v>1174</v>
-      </c>
-      <c r="I60" s="7" t="s">
-        <v>1175</v>
       </c>
       <c r="J60">
         <f>計算表!J60</f>
@@ -9429,10 +9430,10 @@
         <v>物理防禦</v>
       </c>
       <c r="E63" s="7" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F63" s="7" t="s">
         <v>1176</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>1177</v>
       </c>
       <c r="G63">
         <f>計算表!G63</f>
@@ -9447,10 +9448,10 @@
         <v>2.4</v>
       </c>
       <c r="J63" s="7" t="s">
+        <v>1177</v>
+      </c>
+      <c r="K63" s="7" t="s">
         <v>1178</v>
-      </c>
-      <c r="K63" s="7" t="s">
-        <v>1179</v>
       </c>
       <c r="L63">
         <f>計算表!L63</f>
@@ -9499,10 +9500,10 @@
         <v>魔法防禦</v>
       </c>
       <c r="E64" s="7" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F64" s="7" t="s">
         <v>1180</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>1181</v>
       </c>
       <c r="G64">
         <f>計算表!G64</f>
@@ -9517,10 +9518,10 @@
         <v>2.4</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="L64">
         <f>計算表!L64</f>
@@ -9581,7 +9582,7 @@
         <v>5</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="I65">
         <f>計算表!I65</f>
@@ -9642,22 +9643,22 @@
         <v>連擊數</v>
       </c>
       <c r="E66" s="7" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F66" s="7" t="s">
         <v>1196</v>
       </c>
-      <c r="F66" s="7" t="s">
-        <v>1197</v>
-      </c>
       <c r="G66" s="7" t="s">
+        <v>1191</v>
+      </c>
+      <c r="H66" s="7" t="s">
         <v>1192</v>
       </c>
-      <c r="H66" s="7" t="s">
+      <c r="I66" s="7" t="s">
         <v>1193</v>
       </c>
-      <c r="I66" s="7" t="s">
+      <c r="J66" s="7" t="s">
         <v>1194</v>
-      </c>
-      <c r="J66" s="7" t="s">
-        <v>1195</v>
       </c>
       <c r="K66">
         <f>計算表!K66</f>
@@ -9713,14 +9714,14 @@
         <v>126</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="G67">
         <f>計算表!G67</f>
         <v>150</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="I67">
         <f>計算表!I67</f>
@@ -9793,7 +9794,7 @@
         <v>0.86</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="I68">
         <f>計算表!I68</f>
@@ -9862,7 +9863,7 @@
         <v>a=每點敏捷%（減去敵方閃避後最低 5%）。</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H69">
         <f>計算表!H69</f>
@@ -9935,7 +9936,7 @@
         <v>a=每點敏捷%。</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H70">
         <f>計算表!H70</f>
@@ -9996,19 +9997,19 @@
         <v>2-屬性派生</v>
       </c>
       <c r="D71" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E71" s="7" t="s">
         <v>1186</v>
       </c>
-      <c r="E71" s="7" t="s">
+      <c r="F71" s="7" t="s">
         <v>1187</v>
       </c>
-      <c r="F71" s="7" t="s">
+      <c r="G71" s="7" t="s">
         <v>1188</v>
       </c>
-      <c r="G71" s="7" t="s">
+      <c r="H71" s="7" t="s">
         <v>1189</v>
-      </c>
-      <c r="H71" s="7" t="s">
-        <v>1190</v>
       </c>
       <c r="I71">
         <f>計算表!I71</f>
@@ -21053,7 +21054,7 @@
         <v>611</v>
       </c>
       <c r="F221" s="7" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="G221">
         <f>計算表!G222</f>
@@ -29929,7 +29930,7 @@
       </c>
       <c r="F341" t="str">
         <f>計算表!F357</f>
-        <v>這四種高級敵人不再從頭到尾站在原地：每隔 a~b 秒（隨機）會跑到新的位置，目標點以「跑位結束後仍可直接攻擊到玩家」為主（近戰貼在你身邊繞一個角度，遠程在射程內換一個方位）。跑位期間仍會攻擊。個別技能（火鏈、瘟疫、秘法加持…）有自己的跑位節奏，寫在 Skills2 敵人技能的效果參數裡。</v>
+        <v>這四種高級敵人不再從頭到尾站在原地：每隔 a~b 秒（隨機）會跑到新的位置，目標點以「跑位結束後仍可直接攻擊到玩家」為主（近戰貼在你身邊繞一個角度，遠程在射程內換一個方位）。跑位期間仍會攻擊。c＝跑位時的移動速度倍率（乘上該敵人的跑速；預設 1.6：玩家一直在動，敵人要跑得比平常快才追得上目標點，不會跑到一半被甩開而放棄）。個別技能（火鏈、瘟疫、秘法加持…）有自己的跑位節奏，寫在 Skills2 敵人技能的效果參數裡。</v>
       </c>
       <c r="G341">
         <f>計算表!G357</f>
@@ -29941,7 +29942,7 @@
       </c>
       <c r="I341">
         <f>計算表!I357</f>
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="J341">
         <f>計算表!J357</f>
@@ -50648,7 +50649,7 @@
         <v>1141</v>
       </c>
       <c r="F350" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="G350" s="7" t="s">
         <v>1142</v>
@@ -50762,7 +50763,7 @@
         <v>1149</v>
       </c>
       <c r="F352" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G352">
         <v>100</v>
@@ -51046,7 +51047,7 @@
         <v>1166</v>
       </c>
       <c r="F357" t="s">
-        <v>1167</v>
+        <v>1197</v>
       </c>
       <c r="G357">
         <v>4</v>
@@ -51055,7 +51056,7 @@
         <v>8</v>
       </c>
       <c r="I357">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="J357">
         <v>0</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE779FF1-6225-41D6-B61B-3C25BBE2EE57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B4F3A1-D940-4199-BBAE-57ECE910ED5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2008" uniqueCount="1198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2026" uniqueCount="1208">
   <si>
     <t>編號</t>
   </si>
@@ -4411,6 +4411,36 @@
   <si>
     <t>這四種高級敵人不再從頭到尾站在原地：每隔 a~b 秒（隨機）會跑到新的位置，目標點以「跑位結束後仍可直接攻擊到玩家」為主（近戰貼在你身邊繞一個角度，遠程在射程內換一個方位）。跑位期間仍會攻擊。c＝跑位時的移動速度倍率（乘上該敵人的跑速；預設 1.6：玩家一直在動，敵人要跑得比平常快才追得上目標點，不會跑到一半被甩開而放棄）。個別技能（火鏈、瘟疫、秘法加持…）有自己的跑位節奏，寫在 Skills2 敵人技能的效果參數裡。</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>357</t>
+  </si>
+  <si>
+    <t>封魔塔BOSS玩家技能</t>
+  </si>
+  <si>
+    <t>傷害×a% 跳動×b% 範圍×c% 增益×d% 控場×e% 護盾×f% 復活生命×g%；被動最短間隔 h 秒</t>
+  </si>
+  <si>
+    <t>封魔塔 BOSS 施放的玩家超神進化技能（Skills2 超神列的封魔塔層級＝該層 BOSS 固定使用；規則與對照表見 docs/BOSS_PLAYER_SKILLS.md）的整體強度。a＝技能傷害倍率（%）：技能 pct% 乘 a% 就是 BOSS 攻擊力的倍數；b＝持續場域與領域每次跳動的再折扣（%）；c＝範圍半徑倍率（%，玩家技能的範圍是為打一群怪設計的）；d＝玩家式增益（攻擊提高％、疊層）轉成 BOSS 增益的強度（%）；e＝控場（暈眩、緩速）秒數倍率（%）；f＝護盾量倍率（%）；g＝復活類技能復活後的生命倍率（%）；h＝被動反應技能（神聖之體、天穹崩裂）兩次觸發的最短間隔（秒）。單一技能要個別調整時，在 Skills2 該列的效果參數(JSON) 補 bossMul（傷害倍率）、bossCd 與 bossCdMax（冷卻秒數）。</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
 </sst>
 </file>
@@ -4864,7 +4894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R341"/>
+  <dimension ref="A1:R342"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="22.7109375" customWidth="1"/>
@@ -29979,6 +30009,62 @@
       <c r="R341">
         <f>計算表!R357</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="342" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A342" s="7" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B342" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C342" s="7" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D342" s="7" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E342" s="7" t="s">
+        <v>1200</v>
+      </c>
+      <c r="F342" s="7" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G342" s="7" t="s">
+        <v>1191</v>
+      </c>
+      <c r="H342" s="7" t="s">
+        <v>1202</v>
+      </c>
+      <c r="I342" s="7" t="s">
+        <v>1203</v>
+      </c>
+      <c r="J342" s="7" t="s">
+        <v>1191</v>
+      </c>
+      <c r="K342" s="7" t="s">
+        <v>1204</v>
+      </c>
+      <c r="L342" s="7" t="s">
+        <v>1205</v>
+      </c>
+      <c r="M342" s="7" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N342" s="7" t="s">
+        <v>1207</v>
+      </c>
+      <c r="O342" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="P342" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="Q342" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="R342" s="7" t="s">
+        <v>1181</v>
       </c>
     </row>
   </sheetData>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B4F3A1-D940-4199-BBAE-57ECE910ED5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8573C070-5FFA-49BB-8F64-3BA8CA573F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2026" uniqueCount="1208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2062" uniqueCount="1223">
   <si>
     <t>編號</t>
   </si>
@@ -4441,6 +4441,51 @@
   </si>
   <si>
     <t>4</t>
+  </si>
+  <si>
+    <t>358</t>
+  </si>
+  <si>
+    <t>4-遠方怪群</t>
+  </si>
+  <si>
+    <t>預先生成</t>
+  </si>
+  <si>
+    <t>格點間距a米；預載b米內／c米外；同時最多d群，每群最多e隻</t>
+  </si>
+  <si>
+    <t>固定世界格點在玩家抵達前預置；同區域只配置一次，玩家站著、清掉怪群或往返都不補生。移動到新格區才預載新地點；近身原有波次刷怪維持，遠方群不占波次數量上限，共用戰場總容量。</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>70</t>
+  </si>
+  <si>
+    <t>359</t>
+  </si>
+  <si>
+    <t>未警戒遊走</t>
+  </si>
+  <si>
+    <t>出生點半徑a米內；跑速×b；到點停留c~d秒</t>
+  </si>
+  <si>
+    <t>僅遠方預置怪群未發現玩家時生效。以各隻出生世界座標為固定中心，隨機走走停停，不跟玩家平移；發現玩家後依NPC表視野切換追擊，不再回到遊走。</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>0.25</t>
+  </si>
+  <si>
+    <t>2.5</t>
   </si>
 </sst>
 </file>
@@ -4894,7 +4939,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R342"/>
+  <dimension ref="A1:R344"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="22.7109375" customWidth="1"/>
@@ -30013,46 +30058,46 @@
     </row>
     <row r="342" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A342" s="7" t="s">
-        <v>1198</v>
+        <v>1208</v>
       </c>
       <c r="B342" s="7" t="s">
         <v>1181</v>
       </c>
       <c r="C342" s="7" t="s">
-        <v>1078</v>
+        <v>1209</v>
       </c>
       <c r="D342" s="7" t="s">
-        <v>1199</v>
+        <v>1210</v>
       </c>
       <c r="E342" s="7" t="s">
-        <v>1200</v>
+        <v>1211</v>
       </c>
       <c r="F342" s="7" t="s">
-        <v>1201</v>
+        <v>1212</v>
       </c>
       <c r="G342" s="7" t="s">
-        <v>1191</v>
+        <v>1213</v>
       </c>
       <c r="H342" s="7" t="s">
-        <v>1202</v>
+        <v>1214</v>
       </c>
       <c r="I342" s="7" t="s">
-        <v>1203</v>
+        <v>1215</v>
       </c>
       <c r="J342" s="7" t="s">
-        <v>1191</v>
+        <v>1207</v>
       </c>
       <c r="K342" s="7" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
       <c r="L342" s="7" t="s">
-        <v>1205</v>
+        <v>1181</v>
       </c>
       <c r="M342" s="7" t="s">
-        <v>1206</v>
+        <v>1181</v>
       </c>
       <c r="N342" s="7" t="s">
-        <v>1207</v>
+        <v>1181</v>
       </c>
       <c r="O342" s="7" t="s">
         <v>1181</v>
@@ -30064,6 +30109,118 @@
         <v>1181</v>
       </c>
       <c r="R342" s="7" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="343" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A343" s="7" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B343" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C343" s="7" t="s">
+        <v>1209</v>
+      </c>
+      <c r="D343" s="7" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E343" s="7" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F343" s="7" t="s">
+        <v>1219</v>
+      </c>
+      <c r="G343" s="7" t="s">
+        <v>1220</v>
+      </c>
+      <c r="H343" s="7" t="s">
+        <v>1221</v>
+      </c>
+      <c r="I343" s="7" t="s">
+        <v>1194</v>
+      </c>
+      <c r="J343" s="7" t="s">
+        <v>1222</v>
+      </c>
+      <c r="K343" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="L343" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="M343" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="N343" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="O343" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="P343" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="Q343" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="R343" s="7" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="344" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A344" s="7" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B344" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C344" s="7" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D344" s="7" t="s">
+        <v>1199</v>
+      </c>
+      <c r="E344" s="7" t="s">
+        <v>1200</v>
+      </c>
+      <c r="F344" s="7" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G344" s="7" t="s">
+        <v>1191</v>
+      </c>
+      <c r="H344" s="7" t="s">
+        <v>1202</v>
+      </c>
+      <c r="I344" s="7" t="s">
+        <v>1203</v>
+      </c>
+      <c r="J344" s="7" t="s">
+        <v>1191</v>
+      </c>
+      <c r="K344" s="7" t="s">
+        <v>1204</v>
+      </c>
+      <c r="L344" s="7" t="s">
+        <v>1205</v>
+      </c>
+      <c r="M344" s="7" t="s">
+        <v>1206</v>
+      </c>
+      <c r="N344" s="7" t="s">
+        <v>1207</v>
+      </c>
+      <c r="O344" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="P344" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="Q344" s="7" t="s">
+        <v>1181</v>
+      </c>
+      <c r="R344" s="7" t="s">
         <v>1181</v>
       </c>
     </row>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8573C070-5FFA-49BB-8F64-3BA8CA573F5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639D0C48-C490-4D0B-88DB-AD4730435FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2062" uniqueCount="1223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2062" uniqueCount="1225">
   <si>
     <t>編號</t>
   </si>
@@ -4452,12 +4452,6 @@
     <t>預先生成</t>
   </si>
   <si>
-    <t>格點間距a米；預載b米內／c米外；同時最多d群，每群最多e隻</t>
-  </si>
-  <si>
-    <t>固定世界格點在玩家抵達前預置；同區域只配置一次，玩家站著、清掉怪群或往返都不補生。移動到新格區才預載新地點；近身原有波次刷怪維持，遠方群不占波次數量上限，共用戰場總容量。</t>
-  </si>
-  <si>
     <t>100</t>
   </si>
   <si>
@@ -4476,9 +4470,6 @@
     <t>出生點半徑a米內；跑速×b；到點停留c~d秒</t>
   </si>
   <si>
-    <t>僅遠方預置怪群未發現玩家時生效。以各隻出生世界座標為固定中心，隨機走走停停，不跟玩家平移；發現玩家後依NPC表視野切換追擊，不再回到遊走。</t>
-  </si>
-  <si>
     <t>8</t>
   </si>
   <si>
@@ -4486,6 +4477,26 @@
   </si>
   <si>
     <t>2.5</t>
+  </si>
+  <si>
+    <t>格點間距a米；預載b米內／c米外；隨機f～d群，每群最多e隻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>初次隨機抽定群數，整群死亡後在遠方隨機空位補回。存活群保留，部分死亡不補單隻；與近身波次獨立，共用戰場總容量。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>僅遠方預置怪群未發現玩家時生效。以各隻出生世界座標為固定中心隨機走停；玩家進入NPC視野或怪物受擊後停止遊走並追擊。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -30070,28 +30081,28 @@
         <v>1210</v>
       </c>
       <c r="E342" s="7" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F342" s="7" t="s">
+        <v>1221</v>
+      </c>
+      <c r="G342" s="7" t="s">
         <v>1211</v>
       </c>
-      <c r="F342" s="7" t="s">
+      <c r="H342" s="7" t="s">
         <v>1212</v>
       </c>
-      <c r="G342" s="7" t="s">
+      <c r="I342" s="7" t="s">
         <v>1213</v>
       </c>
-      <c r="H342" s="7" t="s">
-        <v>1214</v>
-      </c>
-      <c r="I342" s="7" t="s">
-        <v>1215</v>
-      </c>
       <c r="J342" s="7" t="s">
-        <v>1207</v>
+        <v>1222</v>
       </c>
       <c r="K342" s="7" t="s">
         <v>1207</v>
       </c>
       <c r="L342" s="7" t="s">
-        <v>1181</v>
+        <v>1223</v>
       </c>
       <c r="M342" s="7" t="s">
         <v>1181</v>
@@ -30114,7 +30125,7 @@
     </row>
     <row r="343" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A343" s="7" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="B343" s="7" t="s">
         <v>1181</v>
@@ -30123,25 +30134,25 @@
         <v>1209</v>
       </c>
       <c r="D343" s="7" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E343" s="7" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F343" s="7" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G343" s="7" t="s">
         <v>1217</v>
       </c>
-      <c r="E343" s="7" t="s">
+      <c r="H343" s="7" t="s">
         <v>1218</v>
-      </c>
-      <c r="F343" s="7" t="s">
-        <v>1219</v>
-      </c>
-      <c r="G343" s="7" t="s">
-        <v>1220</v>
-      </c>
-      <c r="H343" s="7" t="s">
-        <v>1221</v>
       </c>
       <c r="I343" s="7" t="s">
         <v>1194</v>
       </c>
       <c r="J343" s="7" t="s">
-        <v>1222</v>
+        <v>1219</v>
       </c>
       <c r="K343" s="7" t="s">
         <v>1181</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{639D0C48-C490-4D0B-88DB-AD4730435FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039C0A24-2512-4EE5-8615-4FD698B7E847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1938,21 +1938,9 @@
     <t>寶石合成(手動)</t>
   </si>
   <si>
-    <t>a 顆同種同級 → 1 顆同種下一階</t>
-  </si>
-  <si>
-    <t>a=3；手動合成素材數量（3 合 1）；金幣另見「寶石合成金幣」。</t>
-  </si>
-  <si>
     <t>寶石合成金幣</t>
   </si>
   <si>
-    <t>依素材等級 a/b/c/d/e</t>
-  </si>
-  <si>
-    <t>1級→2級 a、2級→3級 b …。</t>
-  </si>
-  <si>
     <t>寶石轉換(九宮格)</t>
   </si>
   <si>
@@ -1963,12 +1951,6 @@
   </si>
   <si>
     <t>寶石拆解(一般)</t>
-  </si>
-  <si>
-    <t>⌊3^(N-1) × a⌋ 顆同種 1 級</t>
-  </si>
-  <si>
-    <t>a=保留比例（損失 30%）。2級→2 3級→6 4級→18 5級→56。</t>
   </si>
   <si>
     <t>寶石拆解(融合)</t>
@@ -4496,6 +4478,30 @@
   </si>
   <si>
     <t>僅遠方預置怪群未發現玩家時生效。以各隻出生世界座標為固定中心隨機走停；玩家進入NPC視野或怪物受擊後停止遊走並追擊。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依成品階級消耗 a/b/c 顆同種同級寶石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成品2～5級用a顆、6～9級用b顆、10級用c顆前一階寶石；金幣另見「寶石合成金幣」。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>依素材等級 a/b/c/d/e/f/g/h/i</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1級→2級用a、2級→3級用b、依序至9級→10級用i；高階沿既有逐階遞增趨勢延伸。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>⌊逐階合成成本連乘 × a⌋ 顆同種 1 級</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a=保留比例；合成素材數見「寶石合成(手動)」，拆解依新合成成本換算。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5700,7 +5706,7 @@
         <v>基礎a + 技能熟練度等級 + 潛力天賦加成</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="G11">
         <f>計算表!G11</f>
@@ -6143,7 +6149,7 @@
         <v>（查表）</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G17">
         <f>計算表!G17</f>
@@ -6216,7 +6222,7 @@
         <v>（查表）</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G18">
         <f>計算表!G18</f>
@@ -6289,7 +6295,7 @@
         <v>（查表）</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G19">
         <f>計算表!G19</f>
@@ -6362,7 +6368,7 @@
         <v>（查表）</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G20">
         <f>計算表!G20</f>
@@ -6435,7 +6441,7 @@
         <v>（查表）</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G21">
         <f>計算表!G21</f>
@@ -6508,7 +6514,7 @@
         <v>（查表）</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G22">
         <f>計算表!G22</f>
@@ -6581,7 +6587,7 @@
         <v>（查表）</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G23">
         <f>計算表!G23</f>
@@ -6654,7 +6660,7 @@
         <v>（查表）</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G24">
         <f>計算表!G24</f>
@@ -6727,7 +6733,7 @@
         <v>（查表）</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G25">
         <f>計算表!G25</f>
@@ -6800,7 +6806,7 @@
         <v>（查表）</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G26">
         <f>計算表!G26</f>
@@ -6873,7 +6879,7 @@
         <v>（查表）</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G27">
         <f>計算表!G27</f>
@@ -6946,7 +6952,7 @@
         <v>（查表）</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G28">
         <f>計算表!G28</f>
@@ -7019,7 +7025,7 @@
         <v>（查表）</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G29">
         <f>計算表!G29</f>
@@ -7092,7 +7098,7 @@
         <v>（查表）</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G30">
         <f>計算表!G30</f>
@@ -7165,7 +7171,7 @@
         <v>（查表）</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G31">
         <f>計算表!G31</f>
@@ -7238,7 +7244,7 @@
         <v>（查表）</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G32">
         <f>計算表!G32</f>
@@ -7311,7 +7317,7 @@
         <v>（查表）</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G33">
         <f>計算表!G33</f>
@@ -7384,7 +7390,7 @@
         <v>（查表）</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G34">
         <f>計算表!G34</f>
@@ -7457,7 +7463,7 @@
         <v>（查表）</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G35">
         <f>計算表!G35</f>
@@ -7530,7 +7536,7 @@
         <v>（查表）</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G36">
         <f>計算表!G36</f>
@@ -7603,7 +7609,7 @@
         <v>（查表）</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
       <c r="G37">
         <f>計算表!G37</f>
@@ -9152,10 +9158,10 @@
         <v>生命上限</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>1169</v>
+        <v>1163</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>1170</v>
+        <v>1164</v>
       </c>
       <c r="G58">
         <f>計算表!G58</f>
@@ -9298,20 +9304,20 @@
         <v>法力恢復/秒</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>1172</v>
+        <v>1166</v>
       </c>
       <c r="G60">
         <f>計算表!G60</f>
         <v>1</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>1173</v>
+        <v>1167</v>
       </c>
       <c r="I60" s="7" t="s">
-        <v>1174</v>
+        <v>1168</v>
       </c>
       <c r="J60">
         <f>計算表!J60</f>
@@ -9516,10 +9522,10 @@
         <v>物理防禦</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>1175</v>
+        <v>1169</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
       <c r="G63">
         <f>計算表!G63</f>
@@ -9534,10 +9540,10 @@
         <v>2.4</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>1177</v>
+        <v>1171</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>1178</v>
+        <v>1172</v>
       </c>
       <c r="L63">
         <f>計算表!L63</f>
@@ -9586,10 +9592,10 @@
         <v>魔法防禦</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>1179</v>
+        <v>1173</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>1180</v>
+        <v>1174</v>
       </c>
       <c r="G64">
         <f>計算表!G64</f>
@@ -9604,10 +9610,10 @@
         <v>2.4</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>1178</v>
+        <v>1172</v>
       </c>
       <c r="L64">
         <f>計算表!L64</f>
@@ -9668,7 +9674,7 @@
         <v>5</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>1182</v>
+        <v>1176</v>
       </c>
       <c r="I65">
         <f>計算表!I65</f>
@@ -9729,22 +9735,22 @@
         <v>連擊數</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>1191</v>
+        <v>1185</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>1192</v>
+        <v>1186</v>
       </c>
       <c r="I66" s="7" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
       <c r="J66" s="7" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="K66">
         <f>計算表!K66</f>
@@ -9800,14 +9806,14 @@
         <v>126</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>1183</v>
+        <v>1177</v>
       </c>
       <c r="G67">
         <f>計算表!G67</f>
         <v>150</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>1178</v>
+        <v>1172</v>
       </c>
       <c r="I67">
         <f>計算表!I67</f>
@@ -9880,7 +9886,7 @@
         <v>0.86</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="I68">
         <f>計算表!I68</f>
@@ -9949,7 +9955,7 @@
         <v>a=每點敏捷%（減去敵方閃避後最低 5%）。</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>1174</v>
+        <v>1168</v>
       </c>
       <c r="H69">
         <f>計算表!H69</f>
@@ -10022,7 +10028,7 @@
         <v>a=每點敏捷%。</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
       <c r="H70">
         <f>計算表!H70</f>
@@ -10083,19 +10089,19 @@
         <v>2-屬性派生</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
       <c r="H71" s="7" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
       <c r="I71">
         <f>計算表!I71</f>
@@ -11936,7 +11942,7 @@
         <v>忽略敵人防禦% = 穿透%/(穿透%+a)</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="G96">
         <f>計算表!G96</f>
@@ -13723,7 +13729,7 @@
         <v>0.5</v>
       </c>
       <c r="I120" s="7" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
       <c r="J120">
         <f>計算表!J120</f>
@@ -15638,7 +15644,7 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條。</v>
       </c>
       <c r="G146" s="7" t="s">
-        <v>1018</v>
+        <v>1012</v>
       </c>
       <c r="H146">
         <f>計算表!H146</f>
@@ -15711,13 +15717,13 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條。</v>
       </c>
       <c r="G147" s="7" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
       <c r="H147" s="7" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="J147">
         <f>計算表!J147</f>
@@ -15782,20 +15788,20 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條。</v>
       </c>
       <c r="G148" s="7" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="H148" s="7" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="I148">
         <f>計算表!I148</f>
         <v>9.11754</v>
       </c>
       <c r="J148" s="7" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
       <c r="K148" s="7" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="L148">
         <f>計算表!L148</f>
@@ -15852,22 +15858,22 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條。</v>
       </c>
       <c r="G149" s="7" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="H149" s="7" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="J149" s="7" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
       <c r="K149" s="7" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
       <c r="L149" s="7" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
       <c r="M149">
         <f>計算表!M149</f>
@@ -15920,28 +15926,28 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條。</v>
       </c>
       <c r="G150" s="7" t="s">
+        <v>1026</v>
+      </c>
+      <c r="H150" s="7" t="s">
+        <v>1027</v>
+      </c>
+      <c r="I150" s="7" t="s">
+        <v>1028</v>
+      </c>
+      <c r="J150" s="7" t="s">
+        <v>1029</v>
+      </c>
+      <c r="K150" s="7" t="s">
+        <v>1030</v>
+      </c>
+      <c r="L150" s="7" t="s">
+        <v>1031</v>
+      </c>
+      <c r="M150" s="7" t="s">
         <v>1032</v>
       </c>
-      <c r="H150" s="7" t="s">
+      <c r="N150" s="7" t="s">
         <v>1033</v>
-      </c>
-      <c r="I150" s="7" t="s">
-        <v>1034</v>
-      </c>
-      <c r="J150" s="7" t="s">
-        <v>1035</v>
-      </c>
-      <c r="K150" s="7" t="s">
-        <v>1036</v>
-      </c>
-      <c r="L150" s="7" t="s">
-        <v>1037</v>
-      </c>
-      <c r="M150" s="7" t="s">
-        <v>1038</v>
-      </c>
-      <c r="N150" s="7" t="s">
-        <v>1039</v>
       </c>
       <c r="O150">
         <f>計算表!O150</f>
@@ -15986,28 +15992,28 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條。</v>
       </c>
       <c r="G151" s="7" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H151" s="7" t="s">
+        <v>1035</v>
+      </c>
+      <c r="I151" s="7" t="s">
+        <v>1036</v>
+      </c>
+      <c r="J151" s="7" t="s">
+        <v>1037</v>
+      </c>
+      <c r="K151" s="7" t="s">
+        <v>1038</v>
+      </c>
+      <c r="L151" s="7" t="s">
+        <v>1039</v>
+      </c>
+      <c r="M151" s="7" t="s">
         <v>1040</v>
       </c>
-      <c r="H151" s="7" t="s">
+      <c r="N151" s="7" t="s">
         <v>1041</v>
-      </c>
-      <c r="I151" s="7" t="s">
-        <v>1042</v>
-      </c>
-      <c r="J151" s="7" t="s">
-        <v>1043</v>
-      </c>
-      <c r="K151" s="7" t="s">
-        <v>1044</v>
-      </c>
-      <c r="L151" s="7" t="s">
-        <v>1045</v>
-      </c>
-      <c r="M151" s="7" t="s">
-        <v>1046</v>
-      </c>
-      <c r="N151" s="7" t="s">
-        <v>1047</v>
       </c>
       <c r="O151">
         <f>計算表!O151</f>
@@ -16052,31 +16058,31 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條 j=9條。</v>
       </c>
       <c r="G152" s="7" t="s">
+        <v>1042</v>
+      </c>
+      <c r="H152" s="7" t="s">
+        <v>1043</v>
+      </c>
+      <c r="I152" s="7" t="s">
+        <v>1044</v>
+      </c>
+      <c r="J152" s="7" t="s">
+        <v>1045</v>
+      </c>
+      <c r="K152" s="7" t="s">
+        <v>1046</v>
+      </c>
+      <c r="L152" s="7" t="s">
+        <v>1047</v>
+      </c>
+      <c r="M152" s="7" t="s">
         <v>1048</v>
       </c>
-      <c r="H152" s="7" t="s">
+      <c r="N152" s="7" t="s">
         <v>1049</v>
       </c>
-      <c r="I152" s="7" t="s">
+      <c r="O152" s="7" t="s">
         <v>1050</v>
-      </c>
-      <c r="J152" s="7" t="s">
-        <v>1051</v>
-      </c>
-      <c r="K152" s="7" t="s">
-        <v>1052</v>
-      </c>
-      <c r="L152" s="7" t="s">
-        <v>1053</v>
-      </c>
-      <c r="M152" s="7" t="s">
-        <v>1054</v>
-      </c>
-      <c r="N152" s="7" t="s">
-        <v>1055</v>
-      </c>
-      <c r="O152" s="7" t="s">
-        <v>1056</v>
       </c>
       <c r="P152">
         <f>計算表!P152</f>
@@ -16117,7 +16123,7 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條 j=9條 k=10條。</v>
       </c>
       <c r="G153" s="7" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="H153">
         <f>計算表!H153</f>
@@ -17600,7 +17606,7 @@
         <v>200</v>
       </c>
       <c r="H173" s="7" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="I173">
         <f>計算表!I173</f>
@@ -18187,7 +18193,7 @@
         <v>a=基礎權重 b=權重加成 c=加成上限 d=出現門檻。普通無加成。神鑄創世不參與此擲骰。(裝備合成才有作用，目前功能關閉中)</v>
       </c>
       <c r="G181" s="7" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="H181" t="str">
         <f>計算表!H181</f>
@@ -21006,7 +21012,7 @@
         <v>1</v>
       </c>
       <c r="I219" s="7" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
       <c r="J219">
         <f>計算表!J220</f>
@@ -21140,7 +21146,7 @@
         <v>611</v>
       </c>
       <c r="F221" s="7" t="s">
-        <v>1190</v>
+        <v>1184</v>
       </c>
       <c r="G221">
         <f>計算表!G222</f>
@@ -21950,11 +21956,11 @@
       </c>
       <c r="E232" t="str">
         <f>計算表!E233</f>
-        <v>a 顆同種同級 → 1 顆同種下一階</v>
+        <v>依成品階級消耗 a/b/c 顆同種同級寶石</v>
       </c>
       <c r="F232" t="str">
         <f>計算表!F233</f>
-        <v>a=3；手動合成素材數量（3 合 1）；金幣另見「寶石合成金幣」。</v>
+        <v>成品2～5級用a顆、6～9級用b顆、10級用c顆前一階寶石；金幣另見「寶石合成金幣」。</v>
       </c>
       <c r="G232">
         <f>計算表!G233</f>
@@ -21962,11 +21968,11 @@
       </c>
       <c r="H232">
         <f>計算表!H233</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I232">
         <f>計算表!I233</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J232">
         <f>計算表!J233</f>
@@ -22024,11 +22030,11 @@
       </c>
       <c r="E233" t="str">
         <f>計算表!E234</f>
-        <v>依素材等級 a/b/c/d/e</v>
+        <v>依素材等級 a/b/c/d/e/f/g/h/i</v>
       </c>
       <c r="F233" t="str">
         <f>計算表!F234</f>
-        <v>1級→2級 a、2級→3級 b …。</v>
+        <v>1級→2級用a、2級→3級用b、依序至9級→10級用i；高階沿既有逐階遞增趨勢延伸。</v>
       </c>
       <c r="G233">
         <f>計算表!G234</f>
@@ -22052,19 +22058,19 @@
       </c>
       <c r="L233">
         <f>計算表!L234</f>
-        <v>0</v>
+        <v>24300</v>
       </c>
       <c r="M233">
         <f>計算表!M234</f>
-        <v>0</v>
+        <v>72900</v>
       </c>
       <c r="N233">
         <f>計算表!N234</f>
-        <v>0</v>
+        <v>218700</v>
       </c>
       <c r="O233">
         <f>計算表!O234</f>
-        <v>0</v>
+        <v>656100</v>
       </c>
       <c r="P233">
         <f>計算表!P234</f>
@@ -22172,11 +22178,11 @@
       </c>
       <c r="E235" t="str">
         <f>計算表!E236</f>
-        <v>⌊3^(N-1) × a⌋ 顆同種 1 級</v>
+        <v>⌊逐階合成成本連乘 × a⌋ 顆同種 1 級</v>
       </c>
       <c r="F235" t="str">
         <f>計算表!F236</f>
-        <v>a=保留比例（損失 30%）。2級→2 3級→6 4級→18 5級→56。</v>
+        <v>a=保留比例；合成素材數見「寶石合成(手動)」，拆解依新合成成本換算。</v>
       </c>
       <c r="G235">
         <f>計算表!G236</f>
@@ -26019,10 +26025,10 @@
         <v>等級上限</v>
       </c>
       <c r="E287" s="7" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="F287" s="7" t="s">
-        <v>1062</v>
+        <v>1056</v>
       </c>
       <c r="G287">
         <f>計算表!G291</f>
@@ -27653,7 +27659,7 @@
         <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）。</v>
       </c>
       <c r="G309" s="7" t="s">
-        <v>1063</v>
+        <v>1057</v>
       </c>
       <c r="H309">
         <f>計算表!H325</f>
@@ -28022,7 +28028,7 @@
         <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）。</v>
       </c>
       <c r="G314" s="7" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
       <c r="H314">
         <f>計算表!H330</f>
@@ -30069,170 +30075,170 @@
     </row>
     <row r="342" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A342" s="7" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
       <c r="B342" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="C342" s="7" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
       <c r="D342" s="7" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="E342" s="7" t="s">
-        <v>1220</v>
+        <v>1214</v>
       </c>
       <c r="F342" s="7" t="s">
-        <v>1221</v>
+        <v>1215</v>
       </c>
       <c r="G342" s="7" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="H342" s="7" t="s">
-        <v>1212</v>
+        <v>1206</v>
       </c>
       <c r="I342" s="7" t="s">
-        <v>1213</v>
+        <v>1207</v>
       </c>
       <c r="J342" s="7" t="s">
-        <v>1222</v>
+        <v>1216</v>
       </c>
       <c r="K342" s="7" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
       <c r="L342" s="7" t="s">
-        <v>1223</v>
+        <v>1217</v>
       </c>
       <c r="M342" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="N342" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="O342" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="P342" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="Q342" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="R342" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="343" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A343" s="7" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="B343" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="C343" s="7" t="s">
+        <v>1203</v>
+      </c>
+      <c r="D343" s="7" t="s">
         <v>1209</v>
       </c>
-      <c r="D343" s="7" t="s">
-        <v>1215</v>
-      </c>
       <c r="E343" s="7" t="s">
-        <v>1216</v>
+        <v>1210</v>
       </c>
       <c r="F343" s="7" t="s">
-        <v>1224</v>
+        <v>1218</v>
       </c>
       <c r="G343" s="7" t="s">
-        <v>1217</v>
+        <v>1211</v>
       </c>
       <c r="H343" s="7" t="s">
-        <v>1218</v>
+        <v>1212</v>
       </c>
       <c r="I343" s="7" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="J343" s="7" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
       <c r="K343" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="L343" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="M343" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="N343" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="O343" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="P343" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="Q343" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="R343" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="344" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A344" s="7" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B344" s="7" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C344" s="7" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D344" s="7" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E344" s="7" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F344" s="7" t="s">
+        <v>1195</v>
+      </c>
+      <c r="G344" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="H344" s="7" t="s">
+        <v>1196</v>
+      </c>
+      <c r="I344" s="7" t="s">
+        <v>1197</v>
+      </c>
+      <c r="J344" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="K344" s="7" t="s">
         <v>1198</v>
       </c>
-      <c r="B344" s="7" t="s">
-        <v>1181</v>
-      </c>
-      <c r="C344" s="7" t="s">
-        <v>1078</v>
-      </c>
-      <c r="D344" s="7" t="s">
+      <c r="L344" s="7" t="s">
         <v>1199</v>
       </c>
-      <c r="E344" s="7" t="s">
+      <c r="M344" s="7" t="s">
         <v>1200</v>
       </c>
-      <c r="F344" s="7" t="s">
+      <c r="N344" s="7" t="s">
         <v>1201</v>
       </c>
-      <c r="G344" s="7" t="s">
-        <v>1191</v>
-      </c>
-      <c r="H344" s="7" t="s">
-        <v>1202</v>
-      </c>
-      <c r="I344" s="7" t="s">
-        <v>1203</v>
-      </c>
-      <c r="J344" s="7" t="s">
-        <v>1191</v>
-      </c>
-      <c r="K344" s="7" t="s">
-        <v>1204</v>
-      </c>
-      <c r="L344" s="7" t="s">
-        <v>1205</v>
-      </c>
-      <c r="M344" s="7" t="s">
-        <v>1206</v>
-      </c>
-      <c r="N344" s="7" t="s">
-        <v>1207</v>
-      </c>
       <c r="O344" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="P344" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="Q344" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
       <c r="R344" s="7" t="s">
-        <v>1181</v>
+        <v>1175</v>
       </c>
     </row>
   </sheetData>
@@ -30318,16 +30324,16 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="D2" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
       <c r="E2" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="F2" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="G2">
         <v>50000</v>
@@ -30375,16 +30381,16 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>946</v>
+        <v>940</v>
       </c>
       <c r="D3" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
       <c r="E3" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="F3" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="G3">
         <v>500</v>
@@ -30432,16 +30438,16 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
+        <v>940</v>
+      </c>
+      <c r="D4" t="s">
         <v>946</v>
       </c>
-      <c r="D4" t="s">
-        <v>952</v>
-      </c>
       <c r="E4" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="F4" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -30489,16 +30495,16 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="D5" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="E5" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="F5" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="G5">
         <v>24</v>
@@ -30546,16 +30552,16 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
+        <v>835</v>
+      </c>
+      <c r="D6" t="s">
+        <v>839</v>
+      </c>
+      <c r="E6" t="s">
+        <v>840</v>
+      </c>
+      <c r="F6" t="s">
         <v>841</v>
-      </c>
-      <c r="D6" t="s">
-        <v>845</v>
-      </c>
-      <c r="E6" t="s">
-        <v>846</v>
-      </c>
-      <c r="F6" t="s">
-        <v>847</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -30603,16 +30609,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="D7" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="E7" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
       <c r="F7" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -30660,16 +30666,16 @@
         <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="D8" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="E8" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="F8" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -31062,13 +31068,13 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="E15" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="F15" t="s">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="G15">
         <v>30</v>
@@ -31119,13 +31125,13 @@
         <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>923</v>
+        <v>917</v>
       </c>
       <c r="E16" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
       <c r="F16" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="G16">
         <v>1000</v>
@@ -32664,7 +32670,7 @@
         <v>149</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -32721,7 +32727,7 @@
         <v>149</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -34086,10 +34092,10 @@
         <v>134</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="G68">
         <v>0.86</v>
@@ -34314,10 +34320,10 @@
         <v>143</v>
       </c>
       <c r="E72" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
       <c r="F72" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
       <c r="G72">
         <v>5</v>
@@ -35169,10 +35175,10 @@
         <v>209</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="G87">
         <v>10</v>
@@ -35679,13 +35685,13 @@
         <v>188</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="G96">
         <v>0.75</v>
@@ -37395,7 +37401,7 @@
         <v>270</v>
       </c>
       <c r="F126" t="s">
-        <v>1151</v>
+        <v>1145</v>
       </c>
       <c r="G126">
         <v>4</v>
@@ -37446,7 +37452,7 @@
         <v>245</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="E127" t="s">
         <v>271</v>
@@ -37503,7 +37509,7 @@
         <v>273</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="E128" t="s">
         <v>274</v>
@@ -37560,7 +37566,7 @@
         <v>273</v>
       </c>
       <c r="D129" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="E129" t="s">
         <v>274</v>
@@ -37617,7 +37623,7 @@
         <v>273</v>
       </c>
       <c r="D130" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="E130" t="s">
         <v>274</v>
@@ -37674,7 +37680,7 @@
         <v>273</v>
       </c>
       <c r="D131" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="E131" t="s">
         <v>274</v>
@@ -37731,7 +37737,7 @@
         <v>273</v>
       </c>
       <c r="D132" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="E132" t="s">
         <v>274</v>
@@ -37740,7 +37746,7 @@
         <v>275</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
       <c r="H132" t="s">
         <v>287</v>
@@ -37749,7 +37755,7 @@
         <v>288</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="K132">
         <v>0</v>
@@ -37788,7 +37794,7 @@
         <v>273</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="E133" t="s">
         <v>274</v>
@@ -37797,19 +37803,19 @@
         <v>275</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>1003</v>
+        <v>997</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="J133" s="3" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
       <c r="K133" s="3" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
       <c r="L133">
         <v>0</v>
@@ -37845,7 +37851,7 @@
         <v>273</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="E134" t="s">
         <v>274</v>
@@ -37854,22 +37860,22 @@
         <v>275</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="K134" s="3" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="M134">
         <v>0</v>
@@ -37902,13 +37908,13 @@
         <v>273</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="E135" t="s">
         <v>274</v>
       </c>
       <c r="F135" t="s">
-        <v>1150</v>
+        <v>1144</v>
       </c>
       <c r="G135" t="s">
         <v>276</v>
@@ -37959,22 +37965,22 @@
         <v>273</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="E136" t="s">
         <v>274</v>
       </c>
       <c r="F136" t="s">
-        <v>1150</v>
+        <v>1144</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="J136">
         <v>0</v>
@@ -38016,28 +38022,28 @@
         <v>273</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="E137" t="s">
         <v>274</v>
       </c>
       <c r="F137" t="s">
-        <v>1150</v>
+        <v>1144</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
       <c r="J137" s="3" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="K137" s="3" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
       <c r="L137">
         <v>0</v>
@@ -38073,34 +38079,34 @@
         <v>273</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
       <c r="E138" t="s">
         <v>274</v>
       </c>
       <c r="F138" t="s">
-        <v>1150</v>
+        <v>1144</v>
       </c>
       <c r="G138" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="J138" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="K138" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="L138" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="M138" s="3" t="s">
         <v>984</v>
-      </c>
-      <c r="H138" s="3" t="s">
-        <v>985</v>
-      </c>
-      <c r="I138" s="3" t="s">
-        <v>986</v>
-      </c>
-      <c r="J138" s="3" t="s">
-        <v>987</v>
-      </c>
-      <c r="K138" s="3" t="s">
-        <v>988</v>
-      </c>
-      <c r="L138" s="3" t="s">
-        <v>989</v>
-      </c>
-      <c r="M138" s="3" t="s">
-        <v>990</v>
       </c>
       <c r="N138">
         <v>0</v>
@@ -38130,34 +38136,34 @@
         <v>273</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="E139" t="s">
         <v>274</v>
       </c>
       <c r="F139" t="s">
-        <v>1150</v>
+        <v>1144</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
       <c r="I139" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="J139" s="3" t="s">
+        <v>973</v>
+      </c>
+      <c r="K139" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="L139" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="M139" s="3" t="s">
         <v>976</v>
-      </c>
-      <c r="J139" s="3" t="s">
-        <v>979</v>
-      </c>
-      <c r="K139" s="3" t="s">
-        <v>980</v>
-      </c>
-      <c r="L139" s="3" t="s">
-        <v>981</v>
-      </c>
-      <c r="M139" s="3" t="s">
-        <v>982</v>
       </c>
       <c r="N139">
         <v>0</v>
@@ -40695,13 +40701,13 @@
         <v>530</v>
       </c>
       <c r="D184" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
       <c r="E184" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
       <c r="F184" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
       <c r="G184">
         <v>0.1</v>
@@ -41379,13 +41385,13 @@
         <v>537</v>
       </c>
       <c r="D196" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
       <c r="E196" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
       <c r="F196" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
       <c r="G196">
         <v>20</v>
@@ -41436,13 +41442,13 @@
         <v>537</v>
       </c>
       <c r="D197" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="E197" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
       <c r="F197" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="G197">
         <v>500000000</v>
@@ -41493,13 +41499,13 @@
         <v>537</v>
       </c>
       <c r="D198" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="E198" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="F198" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="G198">
         <v>13</v>
@@ -42249,7 +42255,7 @@
         <v>607</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="F211" t="s">
         <v>608</v>
@@ -44231,19 +44237,19 @@
         <v>633</v>
       </c>
       <c r="E233" t="s">
-        <v>634</v>
+        <v>1219</v>
       </c>
       <c r="F233" t="s">
-        <v>635</v>
+        <v>1220</v>
       </c>
       <c r="G233">
         <v>3</v>
       </c>
       <c r="H233">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I233">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J233">
         <v>0</v>
@@ -44285,13 +44291,13 @@
         <v>623</v>
       </c>
       <c r="D234" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="E234" t="s">
-        <v>637</v>
+        <v>1221</v>
       </c>
       <c r="F234" t="s">
-        <v>638</v>
+        <v>1222</v>
       </c>
       <c r="G234">
         <v>100</v>
@@ -44309,16 +44315,16 @@
         <v>8100</v>
       </c>
       <c r="L234">
-        <v>0</v>
+        <v>24300</v>
       </c>
       <c r="M234">
-        <v>0</v>
+        <v>72900</v>
       </c>
       <c r="N234">
-        <v>0</v>
+        <v>218700</v>
       </c>
       <c r="O234">
-        <v>0</v>
+        <v>656100</v>
       </c>
       <c r="P234">
         <v>0</v>
@@ -44342,13 +44348,13 @@
         <v>623</v>
       </c>
       <c r="D235" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="E235" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="F235" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="G235">
         <v>9</v>
@@ -44399,13 +44405,13 @@
         <v>623</v>
       </c>
       <c r="D236" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="E236" t="s">
-        <v>643</v>
+        <v>1223</v>
       </c>
       <c r="F236" t="s">
-        <v>644</v>
+        <v>1224</v>
       </c>
       <c r="G236">
         <v>0.7</v>
@@ -44456,13 +44462,13 @@
         <v>623</v>
       </c>
       <c r="D237" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="E237" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="F237" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="G237">
         <v>0.7</v>
@@ -44513,13 +44519,13 @@
         <v>623</v>
       </c>
       <c r="D238" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="E238" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="F238" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="G238">
         <v>10</v>
@@ -44570,13 +44576,13 @@
         <v>623</v>
       </c>
       <c r="D239" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="E239" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="F239" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="G239">
         <v>0</v>
@@ -44624,16 +44630,16 @@
         <v>0</v>
       </c>
       <c r="C240" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="D240" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="E240" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="F240" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="G240">
         <v>100000</v>
@@ -44681,16 +44687,16 @@
         <v>0</v>
       </c>
       <c r="C241" t="s">
+        <v>648</v>
+      </c>
+      <c r="D241" t="s">
+        <v>652</v>
+      </c>
+      <c r="E241" t="s">
+        <v>653</v>
+      </c>
+      <c r="F241" t="s">
         <v>654</v>
-      </c>
-      <c r="D241" t="s">
-        <v>658</v>
-      </c>
-      <c r="E241" t="s">
-        <v>659</v>
-      </c>
-      <c r="F241" t="s">
-        <v>660</v>
       </c>
       <c r="G241">
         <v>5000</v>
@@ -44738,13 +44744,13 @@
         <v>0</v>
       </c>
       <c r="C242" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="D242" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
       <c r="E242" t="s">
-        <v>662</v>
+        <v>656</v>
       </c>
       <c r="F242">
         <v>0</v>
@@ -44795,16 +44801,16 @@
         <v>0</v>
       </c>
       <c r="C243" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="D243" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="E243" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="F243" t="s">
-        <v>665</v>
+        <v>659</v>
       </c>
       <c r="G243">
         <v>10000</v>
@@ -44852,28 +44858,28 @@
         <v>0</v>
       </c>
       <c r="C244" t="s">
+        <v>731</v>
+      </c>
+      <c r="D244" t="s">
+        <v>661</v>
+      </c>
+      <c r="E244" t="s">
+        <v>732</v>
+      </c>
+      <c r="F244" t="s">
+        <v>733</v>
+      </c>
+      <c r="G244" t="s">
+        <v>734</v>
+      </c>
+      <c r="H244" t="s">
+        <v>735</v>
+      </c>
+      <c r="I244" t="s">
+        <v>736</v>
+      </c>
+      <c r="J244" t="s">
         <v>737</v>
-      </c>
-      <c r="D244" t="s">
-        <v>667</v>
-      </c>
-      <c r="E244" t="s">
-        <v>738</v>
-      </c>
-      <c r="F244" t="s">
-        <v>739</v>
-      </c>
-      <c r="G244" t="s">
-        <v>740</v>
-      </c>
-      <c r="H244" t="s">
-        <v>741</v>
-      </c>
-      <c r="I244" t="s">
-        <v>742</v>
-      </c>
-      <c r="J244" t="s">
-        <v>743</v>
       </c>
       <c r="K244">
         <v>0</v>
@@ -44909,28 +44915,28 @@
         <v>0</v>
       </c>
       <c r="C245" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D245" t="s">
-        <v>672</v>
+        <v>666</v>
       </c>
       <c r="E245" t="s">
+        <v>732</v>
+      </c>
+      <c r="F245" t="s">
+        <v>733</v>
+      </c>
+      <c r="G245" t="s">
         <v>738</v>
       </c>
-      <c r="F245" t="s">
+      <c r="H245" t="s">
+        <v>735</v>
+      </c>
+      <c r="I245" t="s">
         <v>739</v>
       </c>
-      <c r="G245" t="s">
-        <v>744</v>
-      </c>
-      <c r="H245" t="s">
-        <v>741</v>
-      </c>
-      <c r="I245" t="s">
-        <v>745</v>
-      </c>
       <c r="J245" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="K245">
         <v>0</v>
@@ -44966,28 +44972,28 @@
         <v>0</v>
       </c>
       <c r="C246" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D246" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="E246" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="F246" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="G246" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
       <c r="H246" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="I246" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="J246" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="K246">
         <v>0</v>
@@ -45023,31 +45029,31 @@
         <v>0</v>
       </c>
       <c r="C247" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D247" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="E247" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="F247" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="G247" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
       <c r="H247" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="I247" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="J247" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="K247" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="L247">
         <v>0</v>
@@ -45080,31 +45086,31 @@
         <v>0</v>
       </c>
       <c r="C248" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D248" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="E248" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="F248" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="G248" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="H248" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="I248" t="s">
+        <v>742</v>
+      </c>
+      <c r="J248" t="s">
+        <v>747</v>
+      </c>
+      <c r="K248" t="s">
         <v>748</v>
-      </c>
-      <c r="J248" t="s">
-        <v>753</v>
-      </c>
-      <c r="K248" t="s">
-        <v>754</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -45137,31 +45143,31 @@
         <v>0</v>
       </c>
       <c r="C249" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D249" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="E249" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="F249" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="G249" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="H249" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="I249" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="J249" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
       <c r="K249" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="L249">
         <v>0</v>
@@ -45194,31 +45200,31 @@
         <v>0</v>
       </c>
       <c r="C250" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D250" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="E250" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="F250" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="G250" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="H250" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="I250" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="J250" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="K250" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -45251,31 +45257,31 @@
         <v>0</v>
       </c>
       <c r="C251" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D251" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="E251" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="F251" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="G251" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
       <c r="H251" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="I251" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="J251" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="K251" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -45308,31 +45314,31 @@
         <v>0</v>
       </c>
       <c r="C252" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D252" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="E252" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="F252" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="G252" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="H252" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="I252" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="J252" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="K252" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="L252">
         <v>0</v>
@@ -45365,34 +45371,34 @@
         <v>0</v>
       </c>
       <c r="C253" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D253" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="E253" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="F253" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="G253" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="H253" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="I253" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="J253" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="K253" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="L253" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="M253">
         <v>0</v>
@@ -45422,34 +45428,34 @@
         <v>0</v>
       </c>
       <c r="C254" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D254" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="E254" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="F254" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="G254" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="H254" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="I254" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="J254" t="s">
+        <v>762</v>
+      </c>
+      <c r="K254" t="s">
         <v>768</v>
       </c>
-      <c r="K254" t="s">
-        <v>774</v>
-      </c>
       <c r="L254" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="M254">
         <v>0</v>
@@ -45479,34 +45485,34 @@
         <v>0</v>
       </c>
       <c r="C255" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D255" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="E255" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="F255" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="G255" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="H255" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="I255" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="J255" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="K255" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="L255" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="M255">
         <v>0</v>
@@ -45536,34 +45542,34 @@
         <v>0</v>
       </c>
       <c r="C256" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D256" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="E256" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="F256" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="G256" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="H256" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="I256" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="J256" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="K256" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="L256" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="M256">
         <v>0</v>
@@ -45593,34 +45599,34 @@
         <v>0</v>
       </c>
       <c r="C257" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D257" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="E257" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="F257" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="G257" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="H257" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="I257" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="J257" t="s">
+        <v>772</v>
+      </c>
+      <c r="K257" t="s">
+        <v>773</v>
+      </c>
+      <c r="L257" t="s">
         <v>778</v>
-      </c>
-      <c r="K257" t="s">
-        <v>779</v>
-      </c>
-      <c r="L257" t="s">
-        <v>784</v>
       </c>
       <c r="M257">
         <v>0</v>
@@ -45650,37 +45656,37 @@
         <v>0</v>
       </c>
       <c r="C258" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D258" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="E258" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="F258" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="G258" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="H258" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="I258" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="J258" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="K258" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="L258" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="M258" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="N258">
         <v>0</v>
@@ -45707,37 +45713,37 @@
         <v>0</v>
       </c>
       <c r="C259" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D259" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="E259" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="F259" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="G259" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
       <c r="H259" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="I259" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="J259" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="K259" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="L259" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="M259" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="N259">
         <v>0</v>
@@ -45764,37 +45770,37 @@
         <v>0</v>
       </c>
       <c r="C260" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D260" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="E260" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="F260" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="G260" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="H260" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="I260" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="J260" t="s">
+        <v>780</v>
+      </c>
+      <c r="K260" t="s">
+        <v>781</v>
+      </c>
+      <c r="L260" t="s">
+        <v>776</v>
+      </c>
+      <c r="M260" t="s">
         <v>786</v>
-      </c>
-      <c r="K260" t="s">
-        <v>787</v>
-      </c>
-      <c r="L260" t="s">
-        <v>782</v>
-      </c>
-      <c r="M260" t="s">
-        <v>792</v>
       </c>
       <c r="N260">
         <v>0</v>
@@ -45821,40 +45827,40 @@
         <v>0</v>
       </c>
       <c r="C261" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D261" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="E261" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="F261" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="G261" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="H261" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="I261" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="J261" t="s">
+        <v>780</v>
+      </c>
+      <c r="K261" t="s">
+        <v>781</v>
+      </c>
+      <c r="L261" t="s">
+        <v>776</v>
+      </c>
+      <c r="M261" t="s">
         <v>786</v>
       </c>
-      <c r="K261" t="s">
-        <v>787</v>
-      </c>
-      <c r="L261" t="s">
-        <v>782</v>
-      </c>
-      <c r="M261" t="s">
-        <v>792</v>
-      </c>
       <c r="N261" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="O261">
         <v>0</v>
@@ -45878,43 +45884,43 @@
         <v>0</v>
       </c>
       <c r="C262" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D262" t="s">
+        <v>729</v>
+      </c>
+      <c r="E262" t="s">
+        <v>732</v>
+      </c>
+      <c r="F262" t="s">
+        <v>733</v>
+      </c>
+      <c r="G262" t="s">
+        <v>789</v>
+      </c>
+      <c r="H262" t="s">
         <v>735</v>
       </c>
-      <c r="E262" t="s">
-        <v>738</v>
-      </c>
-      <c r="F262" t="s">
-        <v>739</v>
-      </c>
-      <c r="G262" t="s">
-        <v>795</v>
-      </c>
-      <c r="H262" t="s">
-        <v>741</v>
-      </c>
       <c r="I262" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="J262" t="s">
+        <v>780</v>
+      </c>
+      <c r="K262" t="s">
+        <v>781</v>
+      </c>
+      <c r="L262" t="s">
+        <v>776</v>
+      </c>
+      <c r="M262" t="s">
         <v>786</v>
       </c>
-      <c r="K262" t="s">
-        <v>787</v>
-      </c>
-      <c r="L262" t="s">
-        <v>782</v>
-      </c>
-      <c r="M262" t="s">
-        <v>792</v>
-      </c>
       <c r="N262" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="O262" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
       <c r="P262">
         <v>0</v>
@@ -45935,46 +45941,46 @@
         <v>0</v>
       </c>
       <c r="C263" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D263" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="E263" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="F263" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="G263" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="H263" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="I263" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="J263" t="s">
+        <v>780</v>
+      </c>
+      <c r="K263" t="s">
+        <v>781</v>
+      </c>
+      <c r="L263" t="s">
+        <v>776</v>
+      </c>
+      <c r="M263" t="s">
         <v>786</v>
       </c>
-      <c r="K263" t="s">
-        <v>787</v>
-      </c>
-      <c r="L263" t="s">
-        <v>782</v>
-      </c>
-      <c r="M263" t="s">
-        <v>792</v>
-      </c>
       <c r="N263" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="O263" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="P263" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
       <c r="Q263">
         <v>0</v>
@@ -45992,22 +45998,22 @@
         <v>0</v>
       </c>
       <c r="C264" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D264" t="s">
-        <v>667</v>
+        <v>661</v>
       </c>
       <c r="E264" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F264" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="G264" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="H264" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="I264">
         <v>0</v>
@@ -46049,25 +46055,25 @@
         <v>0</v>
       </c>
       <c r="C265" t="s">
+        <v>660</v>
+      </c>
+      <c r="D265" t="s">
         <v>666</v>
       </c>
-      <c r="D265" t="s">
-        <v>672</v>
-      </c>
       <c r="E265" t="s">
+        <v>662</v>
+      </c>
+      <c r="F265" t="s">
+        <v>663</v>
+      </c>
+      <c r="G265" t="s">
+        <v>664</v>
+      </c>
+      <c r="H265" t="s">
+        <v>667</v>
+      </c>
+      <c r="I265" t="s">
         <v>668</v>
-      </c>
-      <c r="F265" t="s">
-        <v>669</v>
-      </c>
-      <c r="G265" t="s">
-        <v>670</v>
-      </c>
-      <c r="H265" t="s">
-        <v>673</v>
-      </c>
-      <c r="I265" t="s">
-        <v>674</v>
       </c>
       <c r="J265">
         <v>0</v>
@@ -46106,28 +46112,28 @@
         <v>0</v>
       </c>
       <c r="C266" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D266" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
       <c r="E266" t="s">
+        <v>662</v>
+      </c>
+      <c r="F266" t="s">
+        <v>663</v>
+      </c>
+      <c r="G266" t="s">
+        <v>664</v>
+      </c>
+      <c r="H266" t="s">
+        <v>670</v>
+      </c>
+      <c r="I266" t="s">
         <v>668</v>
       </c>
-      <c r="F266" t="s">
-        <v>669</v>
-      </c>
-      <c r="G266" t="s">
-        <v>670</v>
-      </c>
-      <c r="H266" t="s">
-        <v>676</v>
-      </c>
-      <c r="I266" t="s">
-        <v>674</v>
-      </c>
       <c r="J266" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="K266">
         <v>0</v>
@@ -46163,28 +46169,28 @@
         <v>0</v>
       </c>
       <c r="C267" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D267" t="s">
-        <v>678</v>
+        <v>672</v>
       </c>
       <c r="E267" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F267" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="G267" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="H267" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="I267" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="J267" t="s">
-        <v>677</v>
+        <v>671</v>
       </c>
       <c r="K267">
         <v>0</v>
@@ -46220,28 +46226,28 @@
         <v>0</v>
       </c>
       <c r="C268" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D268" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="E268" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F268" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="G268" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="H268" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="I268" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="J268" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="K268">
         <v>0</v>
@@ -46277,31 +46283,31 @@
         <v>0</v>
       </c>
       <c r="C269" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D269" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="E269" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F269" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="G269" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="H269" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="I269" t="s">
+        <v>674</v>
+      </c>
+      <c r="J269" t="s">
+        <v>677</v>
+      </c>
+      <c r="K269" t="s">
         <v>680</v>
-      </c>
-      <c r="J269" t="s">
-        <v>683</v>
-      </c>
-      <c r="K269" t="s">
-        <v>686</v>
       </c>
       <c r="L269">
         <v>0</v>
@@ -46334,31 +46340,31 @@
         <v>0</v>
       </c>
       <c r="C270" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D270" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="E270" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F270" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="G270" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="H270" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="I270" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="J270" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="K270" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="L270">
         <v>0</v>
@@ -46391,31 +46397,31 @@
         <v>0</v>
       </c>
       <c r="C271" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D271" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="E271" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F271" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="G271" t="s">
-        <v>676</v>
+        <v>670</v>
       </c>
       <c r="H271" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="I271" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="J271" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="K271" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="L271">
         <v>0</v>
@@ -46448,31 +46454,31 @@
         <v>0</v>
       </c>
       <c r="C272" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D272" t="s">
-        <v>694</v>
+        <v>688</v>
       </c>
       <c r="E272" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F272" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="G272" t="s">
+        <v>683</v>
+      </c>
+      <c r="H272" t="s">
         <v>689</v>
       </c>
-      <c r="H272" t="s">
-        <v>695</v>
-      </c>
       <c r="I272" t="s">
+        <v>684</v>
+      </c>
+      <c r="J272" t="s">
         <v>690</v>
       </c>
-      <c r="J272" t="s">
-        <v>696</v>
-      </c>
       <c r="K272" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="L272">
         <v>0</v>
@@ -46505,31 +46511,31 @@
         <v>0</v>
       </c>
       <c r="C273" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D273" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="E273" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F273" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="G273" t="s">
+        <v>689</v>
+      </c>
+      <c r="H273" t="s">
+        <v>693</v>
+      </c>
+      <c r="I273" t="s">
+        <v>690</v>
+      </c>
+      <c r="J273" t="s">
+        <v>694</v>
+      </c>
+      <c r="K273" t="s">
         <v>695</v>
-      </c>
-      <c r="H273" t="s">
-        <v>699</v>
-      </c>
-      <c r="I273" t="s">
-        <v>696</v>
-      </c>
-      <c r="J273" t="s">
-        <v>700</v>
-      </c>
-      <c r="K273" t="s">
-        <v>701</v>
       </c>
       <c r="L273">
         <v>0</v>
@@ -46562,31 +46568,31 @@
         <v>0</v>
       </c>
       <c r="C274" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D274" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="E274" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F274" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="G274" t="s">
+        <v>693</v>
+      </c>
+      <c r="H274" t="s">
+        <v>697</v>
+      </c>
+      <c r="I274" t="s">
+        <v>694</v>
+      </c>
+      <c r="J274" t="s">
+        <v>698</v>
+      </c>
+      <c r="K274" t="s">
         <v>699</v>
-      </c>
-      <c r="H274" t="s">
-        <v>703</v>
-      </c>
-      <c r="I274" t="s">
-        <v>700</v>
-      </c>
-      <c r="J274" t="s">
-        <v>704</v>
-      </c>
-      <c r="K274" t="s">
-        <v>705</v>
       </c>
       <c r="L274">
         <v>0</v>
@@ -46619,31 +46625,31 @@
         <v>0</v>
       </c>
       <c r="C275" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D275" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="E275" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F275" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="G275" t="s">
+        <v>697</v>
+      </c>
+      <c r="H275" t="s">
+        <v>701</v>
+      </c>
+      <c r="I275" t="s">
+        <v>698</v>
+      </c>
+      <c r="J275" t="s">
+        <v>702</v>
+      </c>
+      <c r="K275" t="s">
         <v>703</v>
-      </c>
-      <c r="H275" t="s">
-        <v>707</v>
-      </c>
-      <c r="I275" t="s">
-        <v>704</v>
-      </c>
-      <c r="J275" t="s">
-        <v>708</v>
-      </c>
-      <c r="K275" t="s">
-        <v>709</v>
       </c>
       <c r="L275">
         <v>0</v>
@@ -46676,31 +46682,31 @@
         <v>0</v>
       </c>
       <c r="C276" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D276" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="E276" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F276" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="G276" t="s">
+        <v>701</v>
+      </c>
+      <c r="H276" t="s">
+        <v>705</v>
+      </c>
+      <c r="I276" t="s">
+        <v>702</v>
+      </c>
+      <c r="J276" t="s">
+        <v>706</v>
+      </c>
+      <c r="K276" t="s">
         <v>707</v>
-      </c>
-      <c r="H276" t="s">
-        <v>711</v>
-      </c>
-      <c r="I276" t="s">
-        <v>708</v>
-      </c>
-      <c r="J276" t="s">
-        <v>712</v>
-      </c>
-      <c r="K276" t="s">
-        <v>713</v>
       </c>
       <c r="L276">
         <v>0</v>
@@ -46733,31 +46739,31 @@
         <v>0</v>
       </c>
       <c r="C277" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D277" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="E277" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F277" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="G277" t="s">
+        <v>705</v>
+      </c>
+      <c r="H277" t="s">
+        <v>709</v>
+      </c>
+      <c r="I277" t="s">
+        <v>706</v>
+      </c>
+      <c r="J277" t="s">
+        <v>710</v>
+      </c>
+      <c r="K277" t="s">
         <v>711</v>
-      </c>
-      <c r="H277" t="s">
-        <v>715</v>
-      </c>
-      <c r="I277" t="s">
-        <v>712</v>
-      </c>
-      <c r="J277" t="s">
-        <v>716</v>
-      </c>
-      <c r="K277" t="s">
-        <v>717</v>
       </c>
       <c r="L277">
         <v>0</v>
@@ -46790,31 +46796,31 @@
         <v>0</v>
       </c>
       <c r="C278" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D278" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="E278" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F278" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="G278" t="s">
+        <v>709</v>
+      </c>
+      <c r="H278" t="s">
+        <v>713</v>
+      </c>
+      <c r="I278" t="s">
+        <v>710</v>
+      </c>
+      <c r="J278" t="s">
+        <v>714</v>
+      </c>
+      <c r="K278" t="s">
         <v>715</v>
-      </c>
-      <c r="H278" t="s">
-        <v>719</v>
-      </c>
-      <c r="I278" t="s">
-        <v>716</v>
-      </c>
-      <c r="J278" t="s">
-        <v>720</v>
-      </c>
-      <c r="K278" t="s">
-        <v>721</v>
       </c>
       <c r="L278">
         <v>0</v>
@@ -46847,31 +46853,31 @@
         <v>0</v>
       </c>
       <c r="C279" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D279" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="E279" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F279" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="G279" t="s">
+        <v>713</v>
+      </c>
+      <c r="H279" t="s">
+        <v>717</v>
+      </c>
+      <c r="I279" t="s">
+        <v>714</v>
+      </c>
+      <c r="J279" t="s">
+        <v>718</v>
+      </c>
+      <c r="K279" t="s">
         <v>719</v>
-      </c>
-      <c r="H279" t="s">
-        <v>723</v>
-      </c>
-      <c r="I279" t="s">
-        <v>720</v>
-      </c>
-      <c r="J279" t="s">
-        <v>724</v>
-      </c>
-      <c r="K279" t="s">
-        <v>725</v>
       </c>
       <c r="L279">
         <v>0</v>
@@ -46904,31 +46910,31 @@
         <v>0</v>
       </c>
       <c r="C280" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D280" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="E280" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F280" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="G280" t="s">
+        <v>717</v>
+      </c>
+      <c r="H280" t="s">
+        <v>721</v>
+      </c>
+      <c r="I280" t="s">
+        <v>718</v>
+      </c>
+      <c r="J280" t="s">
+        <v>722</v>
+      </c>
+      <c r="K280" t="s">
         <v>723</v>
-      </c>
-      <c r="H280" t="s">
-        <v>727</v>
-      </c>
-      <c r="I280" t="s">
-        <v>724</v>
-      </c>
-      <c r="J280" t="s">
-        <v>728</v>
-      </c>
-      <c r="K280" t="s">
-        <v>729</v>
       </c>
       <c r="L280">
         <v>0</v>
@@ -46961,34 +46967,34 @@
         <v>0</v>
       </c>
       <c r="C281" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D281" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="E281" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F281" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="G281" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H281" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="I281" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J281" t="s">
+        <v>722</v>
+      </c>
+      <c r="K281" t="s">
+        <v>727</v>
+      </c>
+      <c r="L281" t="s">
         <v>728</v>
-      </c>
-      <c r="K281" t="s">
-        <v>733</v>
-      </c>
-      <c r="L281" t="s">
-        <v>734</v>
       </c>
       <c r="M281">
         <v>0</v>
@@ -47018,34 +47024,34 @@
         <v>0</v>
       </c>
       <c r="C282" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D282" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="E282" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F282" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="G282" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H282" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="I282" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J282" t="s">
+        <v>722</v>
+      </c>
+      <c r="K282" t="s">
+        <v>727</v>
+      </c>
+      <c r="L282" t="s">
         <v>728</v>
-      </c>
-      <c r="K282" t="s">
-        <v>733</v>
-      </c>
-      <c r="L282" t="s">
-        <v>734</v>
       </c>
       <c r="M282">
         <v>0</v>
@@ -47075,34 +47081,34 @@
         <v>0</v>
       </c>
       <c r="C283" t="s">
-        <v>666</v>
+        <v>660</v>
       </c>
       <c r="D283" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
       <c r="E283" t="s">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="F283" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="G283" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="H283" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="I283" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
       <c r="J283" t="s">
+        <v>722</v>
+      </c>
+      <c r="K283" t="s">
+        <v>727</v>
+      </c>
+      <c r="L283" t="s">
         <v>728</v>
-      </c>
-      <c r="K283" t="s">
-        <v>733</v>
-      </c>
-      <c r="L283" t="s">
-        <v>734</v>
       </c>
       <c r="M283">
         <v>0</v>
@@ -47132,16 +47138,16 @@
         <v>0</v>
       </c>
       <c r="C284" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="D284" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="E284" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="F284" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="G284">
         <v>0</v>
@@ -47189,16 +47195,16 @@
         <v>0</v>
       </c>
       <c r="C285" t="s">
+        <v>796</v>
+      </c>
+      <c r="D285" t="s">
+        <v>800</v>
+      </c>
+      <c r="E285" t="s">
+        <v>801</v>
+      </c>
+      <c r="F285" t="s">
         <v>802</v>
-      </c>
-      <c r="D285" t="s">
-        <v>806</v>
-      </c>
-      <c r="E285" t="s">
-        <v>807</v>
-      </c>
-      <c r="F285" t="s">
-        <v>808</v>
       </c>
       <c r="G285">
         <v>0.1</v>
@@ -47246,16 +47252,16 @@
         <v>0</v>
       </c>
       <c r="C286" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="D286" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="E286" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="F286" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="G286">
         <v>0</v>
@@ -47303,16 +47309,16 @@
         <v>0</v>
       </c>
       <c r="C287" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="D287" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="E287" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="F287" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="G287">
         <v>0</v>
@@ -47360,16 +47366,16 @@
         <v>0</v>
       </c>
       <c r="C288" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="D288" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="E288" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="F288" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
       <c r="G288">
         <v>0.2</v>
@@ -47417,16 +47423,16 @@
         <v>0</v>
       </c>
       <c r="C289" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
       <c r="F289" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="G289">
         <v>0.5</v>
@@ -47474,16 +47480,16 @@
         <v>0</v>
       </c>
       <c r="C290" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="D290" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="E290" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="F290" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="G290">
         <v>1000</v>
@@ -47531,16 +47537,16 @@
         <v>0</v>
       </c>
       <c r="C291" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="D291" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
       <c r="E291" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="F291" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="G291">
         <v>0</v>
@@ -47588,16 +47594,16 @@
         <v>0</v>
       </c>
       <c r="C292" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="D292" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="E292" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
       <c r="F292" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="G292">
         <v>30</v>
@@ -47645,16 +47651,16 @@
         <v>0</v>
       </c>
       <c r="C293" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="D293" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="E293" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
       <c r="F293" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="G293">
         <v>0.75</v>
@@ -47702,13 +47708,13 @@
         <v>0</v>
       </c>
       <c r="C294" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="D294" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="E294" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="F294">
         <v>0</v>
@@ -47759,16 +47765,16 @@
         <v>0</v>
       </c>
       <c r="C295" t="s">
+        <v>821</v>
+      </c>
+      <c r="D295" t="s">
         <v>827</v>
-      </c>
-      <c r="D295" t="s">
-        <v>833</v>
       </c>
       <c r="E295" t="s">
         <v>592</v>
       </c>
       <c r="F295" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="G295">
         <v>45</v>
@@ -47816,16 +47822,16 @@
         <v>0</v>
       </c>
       <c r="C296" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="D296" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="E296" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="F296" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="G296">
         <v>0</v>
@@ -47873,16 +47879,16 @@
         <v>0</v>
       </c>
       <c r="C297" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="D297" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="E297" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="F297" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="G297">
         <v>0.1</v>
@@ -47930,16 +47936,16 @@
         <v>0</v>
       </c>
       <c r="C298" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="D298" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="E298" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="F298" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
       <c r="G298">
         <v>50000</v>
@@ -47987,16 +47993,16 @@
         <v>0</v>
       </c>
       <c r="C299" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="D299" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
       <c r="E299" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
       <c r="F299" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
       <c r="G299">
         <v>10</v>
@@ -48044,16 +48050,16 @@
         <v>0</v>
       </c>
       <c r="C300" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="D300" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="E300" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
       <c r="F300" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
       <c r="G300">
         <v>75</v>
@@ -48101,16 +48107,16 @@
         <v>0</v>
       </c>
       <c r="C301" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="D301" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
       <c r="E301" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
       <c r="F301" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
       <c r="G301">
         <v>25</v>
@@ -48158,16 +48164,16 @@
         <v>0</v>
       </c>
       <c r="C302" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="D302" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="E302" t="s">
         <v>592</v>
       </c>
       <c r="F302" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="G302">
         <v>5</v>
@@ -48215,16 +48221,16 @@
         <v>0</v>
       </c>
       <c r="C303" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="D303" t="s">
-        <v>940</v>
+        <v>934</v>
       </c>
       <c r="E303" t="s">
-        <v>941</v>
+        <v>935</v>
       </c>
       <c r="F303" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
       <c r="G303">
         <v>0.6</v>
@@ -48272,16 +48278,16 @@
         <v>0</v>
       </c>
       <c r="C304" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="D304" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
       <c r="E304" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="F304" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="G304">
         <v>25</v>
@@ -48290,7 +48296,7 @@
         <v>25</v>
       </c>
       <c r="I304" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="J304">
         <v>0</v>
@@ -48329,16 +48335,16 @@
         <v>0</v>
       </c>
       <c r="C305" t="s">
+        <v>858</v>
+      </c>
+      <c r="D305" t="s">
+        <v>863</v>
+      </c>
+      <c r="E305" t="s">
+        <v>860</v>
+      </c>
+      <c r="F305" t="s">
         <v>864</v>
-      </c>
-      <c r="D305" t="s">
-        <v>869</v>
-      </c>
-      <c r="E305" t="s">
-        <v>866</v>
-      </c>
-      <c r="F305" t="s">
-        <v>870</v>
       </c>
       <c r="G305">
         <v>20</v>
@@ -48347,7 +48353,7 @@
         <v>20</v>
       </c>
       <c r="I305" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="J305">
         <v>0</v>
@@ -48386,16 +48392,16 @@
         <v>0</v>
       </c>
       <c r="C306" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="D306" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="E306" t="s">
+        <v>860</v>
+      </c>
+      <c r="F306" t="s">
         <v>866</v>
-      </c>
-      <c r="F306" t="s">
-        <v>872</v>
       </c>
       <c r="G306">
         <v>3</v>
@@ -48404,7 +48410,7 @@
         <v>1.5</v>
       </c>
       <c r="I306" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="J306">
         <v>0</v>
@@ -48443,16 +48449,16 @@
         <v>0</v>
       </c>
       <c r="C307" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="D307" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="E307" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="F307" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="G307">
         <v>20</v>
@@ -48461,7 +48467,7 @@
         <v>20</v>
       </c>
       <c r="I307" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="J307">
         <v>0</v>
@@ -48500,16 +48506,16 @@
         <v>0</v>
       </c>
       <c r="C308" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="D308" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="E308" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="F308" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="G308">
         <v>3</v>
@@ -48518,7 +48524,7 @@
         <v>1.5</v>
       </c>
       <c r="I308" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="J308">
         <v>0</v>
@@ -48557,16 +48563,16 @@
         <v>0</v>
       </c>
       <c r="C309" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="D309" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="E309" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="F309" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="G309">
         <v>3</v>
@@ -48575,7 +48581,7 @@
         <v>1.5</v>
       </c>
       <c r="I309" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="J309">
         <v>0</v>
@@ -48614,16 +48620,16 @@
         <v>0</v>
       </c>
       <c r="C310" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="D310" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="E310" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="F310" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
       <c r="G310">
         <v>3</v>
@@ -48632,7 +48638,7 @@
         <v>1.5</v>
       </c>
       <c r="I310" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="J310">
         <v>0</v>
@@ -48671,16 +48677,16 @@
         <v>0</v>
       </c>
       <c r="C311" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="D311" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
       <c r="E311" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="F311" t="s">
-        <v>882</v>
+        <v>876</v>
       </c>
       <c r="G311">
         <v>25</v>
@@ -48689,7 +48695,7 @@
         <v>25</v>
       </c>
       <c r="I311" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="J311">
         <v>0</v>
@@ -48728,16 +48734,16 @@
         <v>0</v>
       </c>
       <c r="C312" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="D312" t="s">
-        <v>883</v>
+        <v>877</v>
       </c>
       <c r="E312" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="F312" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="G312">
         <v>5</v>
@@ -48746,7 +48752,7 @@
         <v>2.5</v>
       </c>
       <c r="I312" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="J312">
         <v>0</v>
@@ -48785,19 +48791,19 @@
         <v>0</v>
       </c>
       <c r="C313" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="D313" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="E313" s="3" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="F313" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="G313" s="3" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
       <c r="H313">
         <v>3</v>
@@ -48842,16 +48848,16 @@
         <v>0</v>
       </c>
       <c r="C314" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="D314" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="E314" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="F314" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="G314">
         <v>5</v>
@@ -48899,16 +48905,16 @@
         <v>0</v>
       </c>
       <c r="C315" t="s">
+        <v>879</v>
+      </c>
+      <c r="D315" t="s">
         <v>885</v>
       </c>
-      <c r="D315" t="s">
-        <v>891</v>
-      </c>
       <c r="E315" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="F315" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="G315">
         <v>10</v>
@@ -48956,16 +48962,16 @@
         <v>0</v>
       </c>
       <c r="C316" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="D316" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="E316" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
       <c r="F316" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="G316">
         <v>10</v>
@@ -49013,16 +49019,16 @@
         <v>0</v>
       </c>
       <c r="C317" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="D317" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="E317" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
       <c r="F317" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="G317">
         <v>2</v>
@@ -49070,16 +49076,16 @@
         <v>0</v>
       </c>
       <c r="C318" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="D318" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="E318" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
       <c r="F318" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="G318">
         <v>5</v>
@@ -49127,16 +49133,16 @@
         <v>0</v>
       </c>
       <c r="C319" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="D319" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="E319" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="F319" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="G319">
         <v>10</v>
@@ -49184,16 +49190,16 @@
         <v>0</v>
       </c>
       <c r="C320" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="D320" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
       <c r="E320" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="F320" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="G320">
         <v>20000</v>
@@ -49241,16 +49247,16 @@
         <v>0</v>
       </c>
       <c r="C321" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="D321" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
       <c r="E321" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
       <c r="F321" s="5" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
       <c r="G321">
         <v>0.35</v>
@@ -49298,16 +49304,16 @@
         <v>0</v>
       </c>
       <c r="C322" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="D322" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="E322" t="s">
         <v>39</v>
       </c>
       <c r="F322" s="7" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="G322">
         <v>1</v>
@@ -49355,16 +49361,16 @@
         <v>0</v>
       </c>
       <c r="C323" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="D323" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="E323" t="s">
         <v>39</v>
       </c>
       <c r="F323" s="7" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="G323">
         <v>1.35</v>
@@ -49412,16 +49418,16 @@
         <v>0</v>
       </c>
       <c r="C324" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="D324" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="E324" t="s">
         <v>39</v>
       </c>
       <c r="F324" s="7" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="G324">
         <v>1.75</v>
@@ -49469,16 +49475,16 @@
         <v>0</v>
       </c>
       <c r="C325" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="D325" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="E325" t="s">
         <v>39</v>
       </c>
       <c r="F325" s="7" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="G325">
         <v>2.2999999999999998</v>
@@ -49526,16 +49532,16 @@
         <v>0</v>
       </c>
       <c r="C326" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="D326" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="E326" t="s">
         <v>39</v>
       </c>
       <c r="F326" s="7" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="G326">
         <v>3</v>
@@ -49583,16 +49589,16 @@
         <v>0</v>
       </c>
       <c r="C327" t="s">
+        <v>848</v>
+      </c>
+      <c r="D327" t="s">
         <v>854</v>
-      </c>
-      <c r="D327" t="s">
-        <v>860</v>
       </c>
       <c r="E327" t="s">
         <v>39</v>
       </c>
       <c r="F327" s="7" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="G327">
         <v>4</v>
@@ -49640,16 +49646,16 @@
         <v>0</v>
       </c>
       <c r="C328" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="D328" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
       <c r="E328" t="s">
         <v>39</v>
       </c>
       <c r="F328" s="7" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="G328">
         <v>5.2</v>
@@ -49697,16 +49703,16 @@
         <v>0</v>
       </c>
       <c r="C329" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="D329" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="E329" t="s">
         <v>39</v>
       </c>
       <c r="F329" s="7" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="G329">
         <v>6.8</v>
@@ -49754,16 +49760,16 @@
         <v>0</v>
       </c>
       <c r="C330" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="D330" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="E330" t="s">
         <v>39</v>
       </c>
       <c r="F330" s="7" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="G330">
         <v>10.199999999999999</v>
@@ -49811,16 +49817,16 @@
         <v>0</v>
       </c>
       <c r="C331" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="D331" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="E331" t="s">
         <v>39</v>
       </c>
       <c r="F331" s="7" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="G331">
         <v>15.3</v>
@@ -49868,16 +49874,16 @@
         <v>0</v>
       </c>
       <c r="C332" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="D332" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
       <c r="E332" t="s">
         <v>39</v>
       </c>
       <c r="F332" s="7" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
       <c r="G332">
         <v>22.95</v>
@@ -49925,22 +49931,22 @@
         <v>0</v>
       </c>
       <c r="C333" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
       <c r="D333" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
       <c r="E333" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
       <c r="F333" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
       <c r="G333">
         <v>200</v>
       </c>
       <c r="H333" s="3" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="I333">
         <v>0</v>
@@ -49982,28 +49988,28 @@
         <v>0</v>
       </c>
       <c r="C334" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D334" s="2" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E334" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F334" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G334" s="7" t="s">
+        <v>1076</v>
+      </c>
+      <c r="H334" s="7" t="s">
+        <v>1077</v>
+      </c>
+      <c r="I334" s="7" t="s">
         <v>1078</v>
       </c>
-      <c r="D334" s="2" t="s">
+      <c r="J334" s="7" t="s">
         <v>1079</v>
-      </c>
-      <c r="E334" t="s">
-        <v>1080</v>
-      </c>
-      <c r="F334" t="s">
-        <v>1081</v>
-      </c>
-      <c r="G334" s="7" t="s">
-        <v>1082</v>
-      </c>
-      <c r="H334" s="7" t="s">
-        <v>1083</v>
-      </c>
-      <c r="I334" s="7" t="s">
-        <v>1084</v>
-      </c>
-      <c r="J334" s="7" t="s">
-        <v>1085</v>
       </c>
       <c r="K334">
         <v>0</v>
@@ -50039,22 +50045,22 @@
         <v>0</v>
       </c>
       <c r="C335" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D335" s="2" t="s">
-        <v>1086</v>
+        <v>1080</v>
       </c>
       <c r="E335" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="F335" t="s">
+        <v>1075</v>
+      </c>
+      <c r="G335" s="7" t="s">
         <v>1081</v>
       </c>
-      <c r="G335" s="7" t="s">
-        <v>1087</v>
-      </c>
       <c r="H335" s="7" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
       <c r="I335">
         <v>0</v>
@@ -50096,22 +50102,22 @@
         <v>0</v>
       </c>
       <c r="C336" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D336" s="2" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="E336" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="F336" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="G336" s="7" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="H336" s="7" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="I336">
         <v>0</v>
@@ -50153,22 +50159,22 @@
         <v>0</v>
       </c>
       <c r="C337" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D337" s="2" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="E337" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="F337" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="G337" s="7" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="H337" s="7" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="I337">
         <v>0</v>
@@ -50210,19 +50216,19 @@
         <v>0</v>
       </c>
       <c r="C338" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D338" s="2" t="s">
-        <v>1095</v>
+        <v>1089</v>
       </c>
       <c r="E338" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
       <c r="F338" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="G338" s="7" t="s">
-        <v>1096</v>
+        <v>1090</v>
       </c>
       <c r="H338">
         <v>0</v>
@@ -50267,34 +50273,34 @@
         <v>0</v>
       </c>
       <c r="C339" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D339" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E339" t="s">
+        <v>1092</v>
+      </c>
+      <c r="F339" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G339" s="7" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H339" s="7" t="s">
+        <v>1095</v>
+      </c>
+      <c r="I339" s="7" t="s">
+        <v>1096</v>
+      </c>
+      <c r="J339" s="7" t="s">
         <v>1097</v>
       </c>
-      <c r="E339" t="s">
+      <c r="K339" s="7" t="s">
         <v>1098</v>
       </c>
-      <c r="F339" t="s">
+      <c r="L339" s="7" t="s">
         <v>1099</v>
-      </c>
-      <c r="G339" s="7" t="s">
-        <v>1100</v>
-      </c>
-      <c r="H339" s="7" t="s">
-        <v>1101</v>
-      </c>
-      <c r="I339" s="7" t="s">
-        <v>1102</v>
-      </c>
-      <c r="J339" s="7" t="s">
-        <v>1103</v>
-      </c>
-      <c r="K339" s="7" t="s">
-        <v>1104</v>
-      </c>
-      <c r="L339" s="7" t="s">
-        <v>1105</v>
       </c>
       <c r="M339">
         <v>0</v>
@@ -50324,25 +50330,25 @@
         <v>0</v>
       </c>
       <c r="C340" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D340" s="2" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
       <c r="E340" t="s">
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="F340" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="G340" s="7" t="s">
-        <v>1107</v>
+        <v>1101</v>
       </c>
       <c r="H340" s="7" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
       <c r="I340" s="7" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
       <c r="J340">
         <v>0</v>
@@ -50381,25 +50387,25 @@
         <v>0</v>
       </c>
       <c r="C341" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D341" s="2" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
       <c r="E341" t="s">
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="F341" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="G341" s="7" t="s">
-        <v>1111</v>
+        <v>1105</v>
       </c>
       <c r="H341" s="7" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="I341" s="7" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="J341">
         <v>0</v>
@@ -50438,25 +50444,25 @@
         <v>0</v>
       </c>
       <c r="C342" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D342" s="2" t="s">
-        <v>1114</v>
+        <v>1108</v>
       </c>
       <c r="E342" t="s">
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="F342" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="G342" s="7" t="s">
-        <v>1115</v>
+        <v>1109</v>
       </c>
       <c r="H342" s="7" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="I342" s="7" t="s">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="J342">
         <v>0</v>
@@ -50495,25 +50501,25 @@
         <v>0</v>
       </c>
       <c r="C343" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D343" s="2" t="s">
-        <v>1117</v>
+        <v>1111</v>
       </c>
       <c r="E343" t="s">
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="F343" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="G343" s="7" t="s">
-        <v>1118</v>
+        <v>1112</v>
       </c>
       <c r="H343" s="7" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="I343" s="7" t="s">
-        <v>1119</v>
+        <v>1113</v>
       </c>
       <c r="J343">
         <v>0</v>
@@ -50552,22 +50558,22 @@
         <v>0</v>
       </c>
       <c r="C344" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D344" s="2" t="s">
-        <v>1120</v>
+        <v>1114</v>
       </c>
       <c r="E344" t="s">
-        <v>1121</v>
+        <v>1115</v>
       </c>
       <c r="F344" t="s">
-        <v>1122</v>
+        <v>1116</v>
       </c>
       <c r="G344" s="7" t="s">
-        <v>1123</v>
+        <v>1117</v>
       </c>
       <c r="H344" s="7" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
       <c r="I344">
         <v>0</v>
@@ -50609,22 +50615,22 @@
         <v>0</v>
       </c>
       <c r="C345" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D345" s="2" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="E345" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F345" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G345" s="7" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H345" s="7" t="s">
         <v>1121</v>
-      </c>
-      <c r="F345" t="s">
-        <v>1122</v>
-      </c>
-      <c r="G345" s="7" t="s">
-        <v>1126</v>
-      </c>
-      <c r="H345" s="7" t="s">
-        <v>1127</v>
       </c>
       <c r="I345">
         <v>0</v>
@@ -50666,19 +50672,19 @@
         <v>0</v>
       </c>
       <c r="C346" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>1128</v>
+        <v>1122</v>
       </c>
       <c r="E346" t="s">
-        <v>1121</v>
+        <v>1115</v>
       </c>
       <c r="F346" t="s">
-        <v>1122</v>
+        <v>1116</v>
       </c>
       <c r="G346" s="7" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="H346">
         <v>0</v>
@@ -50723,19 +50729,19 @@
         <v>0</v>
       </c>
       <c r="C347" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
       <c r="E347" t="s">
-        <v>1121</v>
+        <v>1115</v>
       </c>
       <c r="F347" t="s">
-        <v>1122</v>
+        <v>1116</v>
       </c>
       <c r="G347" s="7" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
       <c r="H347">
         <v>0</v>
@@ -50780,19 +50786,19 @@
         <v>0</v>
       </c>
       <c r="C348" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
       <c r="E348" t="s">
-        <v>1121</v>
+        <v>1115</v>
       </c>
       <c r="F348" t="s">
-        <v>1122</v>
+        <v>1116</v>
       </c>
       <c r="G348" s="7" t="s">
-        <v>1133</v>
+        <v>1127</v>
       </c>
       <c r="H348">
         <v>0</v>
@@ -50837,25 +50843,25 @@
         <v>0</v>
       </c>
       <c r="C349" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>1134</v>
+        <v>1128</v>
       </c>
       <c r="E349" t="s">
-        <v>1135</v>
+        <v>1129</v>
       </c>
       <c r="F349" t="s">
-        <v>1136</v>
+        <v>1130</v>
       </c>
       <c r="G349" s="7" t="s">
-        <v>1137</v>
+        <v>1131</v>
       </c>
       <c r="H349" s="7" t="s">
-        <v>1138</v>
+        <v>1132</v>
       </c>
       <c r="I349" s="7" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="J349">
         <v>0</v>
@@ -50894,25 +50900,25 @@
         <v>0</v>
       </c>
       <c r="C350" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>1140</v>
+        <v>1134</v>
       </c>
       <c r="E350" t="s">
-        <v>1141</v>
+        <v>1135</v>
       </c>
       <c r="F350" t="s">
-        <v>1168</v>
+        <v>1162</v>
       </c>
       <c r="G350" s="7" t="s">
-        <v>1142</v>
+        <v>1136</v>
       </c>
       <c r="H350" s="7" t="s">
-        <v>1143</v>
+        <v>1137</v>
       </c>
       <c r="I350" s="7" t="s">
-        <v>1144</v>
+        <v>1138</v>
       </c>
       <c r="J350">
         <v>0</v>
@@ -50951,16 +50957,16 @@
         <v>0</v>
       </c>
       <c r="C351" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>1145</v>
+        <v>1139</v>
       </c>
       <c r="E351" t="s">
-        <v>1146</v>
+        <v>1140</v>
       </c>
       <c r="F351" t="s">
-        <v>1147</v>
+        <v>1141</v>
       </c>
       <c r="G351">
         <v>1</v>
@@ -51008,16 +51014,16 @@
         <v>0</v>
       </c>
       <c r="C352" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>1148</v>
+        <v>1142</v>
       </c>
       <c r="E352" t="s">
-        <v>1149</v>
+        <v>1143</v>
       </c>
       <c r="F352" t="s">
-        <v>1167</v>
+        <v>1161</v>
       </c>
       <c r="G352">
         <v>100</v>
@@ -51064,16 +51070,16 @@
         <v>0</v>
       </c>
       <c r="C353" t="s">
-        <v>1152</v>
+        <v>1146</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="E353" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="F353" t="s">
-        <v>1155</v>
+        <v>1149</v>
       </c>
       <c r="G353">
         <v>125</v>
@@ -51121,16 +51127,16 @@
         <v>0</v>
       </c>
       <c r="C354" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>1156</v>
+        <v>1150</v>
       </c>
       <c r="E354" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="F354" t="s">
-        <v>1158</v>
+        <v>1152</v>
       </c>
       <c r="G354">
         <v>6</v>
@@ -51178,16 +51184,16 @@
         <v>0</v>
       </c>
       <c r="C355" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>1159</v>
+        <v>1153</v>
       </c>
       <c r="E355" t="s">
-        <v>1160</v>
+        <v>1154</v>
       </c>
       <c r="F355" t="s">
-        <v>1161</v>
+        <v>1155</v>
       </c>
       <c r="G355">
         <v>8</v>
@@ -51235,16 +51241,16 @@
         <v>0</v>
       </c>
       <c r="C356" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>1162</v>
+        <v>1156</v>
       </c>
       <c r="E356" t="s">
-        <v>1163</v>
+        <v>1157</v>
       </c>
       <c r="F356" t="s">
-        <v>1164</v>
+        <v>1158</v>
       </c>
       <c r="G356">
         <v>1.6</v>
@@ -51292,16 +51298,16 @@
         <v>0</v>
       </c>
       <c r="C357" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>1165</v>
+        <v>1159</v>
       </c>
       <c r="E357" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="F357" t="s">
-        <v>1197</v>
+        <v>1191</v>
       </c>
       <c r="G357">
         <v>4</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039C0A24-2512-4EE5-8615-4FD698B7E847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD91BFFD-D12A-4431-A465-54ACA05480B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1942,12 +1942,6 @@
   </si>
   <si>
     <t>寶石轉換(九宮格)</t>
-  </si>
-  <si>
-    <t>a 格；每格上限 b 顆；同階轉換數量不變（免費）</t>
-  </si>
-  <si>
-    <t>融合寶石無法轉換。</t>
   </si>
   <si>
     <t>寶石拆解(一般)</t>
@@ -4502,6 +4496,14 @@
   </si>
   <si>
     <t>a=保留比例；合成素材數見「寶石合成(手動)」，拆解依新合成成本換算。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>a 格；每格上限 b 顆；同階任意2顆換1顆指定寶石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>融合寶石無法轉換；各階分開湊組；奇數餘1顆保留庫存；不收金幣。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5706,7 +5708,7 @@
         <v>基礎a + 技能熟練度等級 + 潛力天賦加成</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="G11">
         <f>計算表!G11</f>
@@ -6149,7 +6151,7 @@
         <v>（查表）</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G17">
         <f>計算表!G17</f>
@@ -6222,7 +6224,7 @@
         <v>（查表）</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G18">
         <f>計算表!G18</f>
@@ -6295,7 +6297,7 @@
         <v>（查表）</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G19">
         <f>計算表!G19</f>
@@ -6368,7 +6370,7 @@
         <v>（查表）</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G20">
         <f>計算表!G20</f>
@@ -6441,7 +6443,7 @@
         <v>（查表）</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G21">
         <f>計算表!G21</f>
@@ -6514,7 +6516,7 @@
         <v>（查表）</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G22">
         <f>計算表!G22</f>
@@ -6587,7 +6589,7 @@
         <v>（查表）</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G23">
         <f>計算表!G23</f>
@@ -6660,7 +6662,7 @@
         <v>（查表）</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G24">
         <f>計算表!G24</f>
@@ -6733,7 +6735,7 @@
         <v>（查表）</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G25">
         <f>計算表!G25</f>
@@ -6806,7 +6808,7 @@
         <v>（查表）</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G26">
         <f>計算表!G26</f>
@@ -6879,7 +6881,7 @@
         <v>（查表）</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G27">
         <f>計算表!G27</f>
@@ -6952,7 +6954,7 @@
         <v>（查表）</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G28">
         <f>計算表!G28</f>
@@ -7025,7 +7027,7 @@
         <v>（查表）</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G29">
         <f>計算表!G29</f>
@@ -7098,7 +7100,7 @@
         <v>（查表）</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G30">
         <f>計算表!G30</f>
@@ -7171,7 +7173,7 @@
         <v>（查表）</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G31">
         <f>計算表!G31</f>
@@ -7244,7 +7246,7 @@
         <v>（查表）</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G32">
         <f>計算表!G32</f>
@@ -7317,7 +7319,7 @@
         <v>（查表）</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G33">
         <f>計算表!G33</f>
@@ -7390,7 +7392,7 @@
         <v>（查表）</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G34">
         <f>計算表!G34</f>
@@ -7463,7 +7465,7 @@
         <v>（查表）</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G35">
         <f>計算表!G35</f>
@@ -7536,7 +7538,7 @@
         <v>（查表）</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G36">
         <f>計算表!G36</f>
@@ -7609,7 +7611,7 @@
         <v>（查表）</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="G37">
         <f>計算表!G37</f>
@@ -9158,10 +9160,10 @@
         <v>生命上限</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="G58">
         <f>計算表!G58</f>
@@ -9304,20 +9306,20 @@
         <v>法力恢復/秒</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="G60">
         <f>計算表!G60</f>
         <v>1</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="I60" s="7" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="J60">
         <f>計算表!J60</f>
@@ -9522,10 +9524,10 @@
         <v>物理防禦</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="G63">
         <f>計算表!G63</f>
@@ -9540,10 +9542,10 @@
         <v>2.4</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="L63">
         <f>計算表!L63</f>
@@ -9592,10 +9594,10 @@
         <v>魔法防禦</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="G64">
         <f>計算表!G64</f>
@@ -9610,10 +9612,10 @@
         <v>2.4</v>
       </c>
       <c r="J64" s="7" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="K64" s="7" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="L64">
         <f>計算表!L64</f>
@@ -9674,7 +9676,7 @@
         <v>5</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="I65">
         <f>計算表!I65</f>
@@ -9735,22 +9737,22 @@
         <v>連擊數</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="G66" s="7" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H66" s="7" t="s">
+        <v>1184</v>
+      </c>
+      <c r="I66" s="7" t="s">
         <v>1185</v>
       </c>
-      <c r="H66" s="7" t="s">
+      <c r="J66" s="7" t="s">
         <v>1186</v>
-      </c>
-      <c r="I66" s="7" t="s">
-        <v>1187</v>
-      </c>
-      <c r="J66" s="7" t="s">
-        <v>1188</v>
       </c>
       <c r="K66">
         <f>計算表!K66</f>
@@ -9806,14 +9808,14 @@
         <v>126</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="G67">
         <f>計算表!G67</f>
         <v>150</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="I67">
         <f>計算表!I67</f>
@@ -9886,7 +9888,7 @@
         <v>0.86</v>
       </c>
       <c r="H68" s="7" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="I68">
         <f>計算表!I68</f>
@@ -9955,7 +9957,7 @@
         <v>a=每點敏捷%（減去敵方閃避後最低 5%）。</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="H69">
         <f>計算表!H69</f>
@@ -10028,7 +10030,7 @@
         <v>a=每點敏捷%。</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="H70">
         <f>計算表!H70</f>
@@ -10089,19 +10091,19 @@
         <v>2-屬性派生</v>
       </c>
       <c r="D71" s="7" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>1178</v>
+      </c>
+      <c r="F71" s="7" t="s">
         <v>1179</v>
       </c>
-      <c r="E71" s="7" t="s">
+      <c r="G71" s="7" t="s">
         <v>1180</v>
       </c>
-      <c r="F71" s="7" t="s">
+      <c r="H71" s="7" t="s">
         <v>1181</v>
-      </c>
-      <c r="G71" s="7" t="s">
-        <v>1182</v>
-      </c>
-      <c r="H71" s="7" t="s">
-        <v>1183</v>
       </c>
       <c r="I71">
         <f>計算表!I71</f>
@@ -11942,7 +11944,7 @@
         <v>忽略敵人防禦% = 穿透%/(穿透%+a)</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="G96">
         <f>計算表!G96</f>
@@ -13729,7 +13731,7 @@
         <v>0.5</v>
       </c>
       <c r="I120" s="7" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="J120">
         <f>計算表!J120</f>
@@ -15644,7 +15646,7 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條。</v>
       </c>
       <c r="G146" s="7" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="H146">
         <f>計算表!H146</f>
@@ -15717,13 +15719,13 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條。</v>
       </c>
       <c r="G147" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H147" s="7" t="s">
+        <v>1012</v>
+      </c>
+      <c r="I147" s="7" t="s">
         <v>1013</v>
-      </c>
-      <c r="H147" s="7" t="s">
-        <v>1014</v>
-      </c>
-      <c r="I147" s="7" t="s">
-        <v>1015</v>
       </c>
       <c r="J147">
         <f>計算表!J147</f>
@@ -15788,20 +15790,20 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條。</v>
       </c>
       <c r="G148" s="7" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="H148" s="7" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="I148">
         <f>計算表!I148</f>
         <v>9.11754</v>
       </c>
       <c r="J148" s="7" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="K148" s="7" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="L148">
         <f>計算表!L148</f>
@@ -15858,22 +15860,22 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條。</v>
       </c>
       <c r="G149" s="7" t="s">
+        <v>1018</v>
+      </c>
+      <c r="H149" s="7" t="s">
+        <v>1019</v>
+      </c>
+      <c r="I149" s="7" t="s">
         <v>1020</v>
       </c>
-      <c r="H149" s="7" t="s">
+      <c r="J149" s="7" t="s">
         <v>1021</v>
       </c>
-      <c r="I149" s="7" t="s">
+      <c r="K149" s="7" t="s">
         <v>1022</v>
       </c>
-      <c r="J149" s="7" t="s">
+      <c r="L149" s="7" t="s">
         <v>1023</v>
-      </c>
-      <c r="K149" s="7" t="s">
-        <v>1024</v>
-      </c>
-      <c r="L149" s="7" t="s">
-        <v>1025</v>
       </c>
       <c r="M149">
         <f>計算表!M149</f>
@@ -15926,28 +15928,28 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條。</v>
       </c>
       <c r="G150" s="7" t="s">
+        <v>1024</v>
+      </c>
+      <c r="H150" s="7" t="s">
+        <v>1025</v>
+      </c>
+      <c r="I150" s="7" t="s">
         <v>1026</v>
       </c>
-      <c r="H150" s="7" t="s">
+      <c r="J150" s="7" t="s">
         <v>1027</v>
       </c>
-      <c r="I150" s="7" t="s">
+      <c r="K150" s="7" t="s">
         <v>1028</v>
       </c>
-      <c r="J150" s="7" t="s">
+      <c r="L150" s="7" t="s">
         <v>1029</v>
       </c>
-      <c r="K150" s="7" t="s">
+      <c r="M150" s="7" t="s">
         <v>1030</v>
       </c>
-      <c r="L150" s="7" t="s">
+      <c r="N150" s="7" t="s">
         <v>1031</v>
-      </c>
-      <c r="M150" s="7" t="s">
-        <v>1032</v>
-      </c>
-      <c r="N150" s="7" t="s">
-        <v>1033</v>
       </c>
       <c r="O150">
         <f>計算表!O150</f>
@@ -15992,28 +15994,28 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條。</v>
       </c>
       <c r="G151" s="7" t="s">
+        <v>1032</v>
+      </c>
+      <c r="H151" s="7" t="s">
+        <v>1033</v>
+      </c>
+      <c r="I151" s="7" t="s">
         <v>1034</v>
       </c>
-      <c r="H151" s="7" t="s">
+      <c r="J151" s="7" t="s">
         <v>1035</v>
       </c>
-      <c r="I151" s="7" t="s">
+      <c r="K151" s="7" t="s">
         <v>1036</v>
       </c>
-      <c r="J151" s="7" t="s">
+      <c r="L151" s="7" t="s">
         <v>1037</v>
       </c>
-      <c r="K151" s="7" t="s">
+      <c r="M151" s="7" t="s">
         <v>1038</v>
       </c>
-      <c r="L151" s="7" t="s">
+      <c r="N151" s="7" t="s">
         <v>1039</v>
-      </c>
-      <c r="M151" s="7" t="s">
-        <v>1040</v>
-      </c>
-      <c r="N151" s="7" t="s">
-        <v>1041</v>
       </c>
       <c r="O151">
         <f>計算表!O151</f>
@@ -16058,31 +16060,31 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條 j=9條。</v>
       </c>
       <c r="G152" s="7" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H152" s="7" t="s">
+        <v>1041</v>
+      </c>
+      <c r="I152" s="7" t="s">
         <v>1042</v>
       </c>
-      <c r="H152" s="7" t="s">
+      <c r="J152" s="7" t="s">
         <v>1043</v>
       </c>
-      <c r="I152" s="7" t="s">
+      <c r="K152" s="7" t="s">
         <v>1044</v>
       </c>
-      <c r="J152" s="7" t="s">
+      <c r="L152" s="7" t="s">
         <v>1045</v>
       </c>
-      <c r="K152" s="7" t="s">
+      <c r="M152" s="7" t="s">
         <v>1046</v>
       </c>
-      <c r="L152" s="7" t="s">
+      <c r="N152" s="7" t="s">
         <v>1047</v>
       </c>
-      <c r="M152" s="7" t="s">
+      <c r="O152" s="7" t="s">
         <v>1048</v>
-      </c>
-      <c r="N152" s="7" t="s">
-        <v>1049</v>
-      </c>
-      <c r="O152" s="7" t="s">
-        <v>1050</v>
       </c>
       <c r="P152">
         <f>計算表!P152</f>
@@ -16123,7 +16125,7 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條 j=9條 k=10條。</v>
       </c>
       <c r="G153" s="7" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="H153">
         <f>計算表!H153</f>
@@ -17606,7 +17608,7 @@
         <v>200</v>
       </c>
       <c r="H173" s="7" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="I173">
         <f>計算表!I173</f>
@@ -18193,7 +18195,7 @@
         <v>a=基礎權重 b=權重加成 c=加成上限 d=出現門檻。普通無加成。神鑄創世不參與此擲骰。(裝備合成才有作用，目前功能關閉中)</v>
       </c>
       <c r="G181" s="7" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="H181" t="str">
         <f>計算表!H181</f>
@@ -21012,7 +21014,7 @@
         <v>1</v>
       </c>
       <c r="I219" s="7" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="J219">
         <f>計算表!J220</f>
@@ -21146,7 +21148,7 @@
         <v>611</v>
       </c>
       <c r="F221" s="7" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="G221">
         <f>計算表!G222</f>
@@ -22104,11 +22106,11 @@
       </c>
       <c r="E234" t="str">
         <f>計算表!E235</f>
-        <v>a 格；每格上限 b 顆；同階轉換數量不變（免費）</v>
+        <v>a 格；每格上限 b 顆；同階任意2顆換1顆指定寶石</v>
       </c>
       <c r="F234" t="str">
         <f>計算表!F235</f>
-        <v>融合寶石無法轉換。</v>
+        <v>融合寶石無法轉換；各階分開湊組；奇數餘1顆保留庫存；不收金幣。</v>
       </c>
       <c r="G234">
         <f>計算表!G235</f>
@@ -26025,10 +26027,10 @@
         <v>等級上限</v>
       </c>
       <c r="E287" s="7" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="F287" s="7" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="G287">
         <f>計算表!G291</f>
@@ -27659,7 +27661,7 @@
         <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）。</v>
       </c>
       <c r="G309" s="7" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="H309">
         <f>計算表!H325</f>
@@ -28028,7 +28030,7 @@
         <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）。</v>
       </c>
       <c r="G314" s="7" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="H314">
         <f>計算表!H330</f>
@@ -30075,170 +30077,170 @@
     </row>
     <row r="342" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A342" s="7" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B342" s="7" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C342" s="7" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D342" s="7" t="s">
         <v>1202</v>
       </c>
-      <c r="B342" s="7" t="s">
-        <v>1175</v>
-      </c>
-      <c r="C342" s="7" t="s">
+      <c r="E342" s="7" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F342" s="7" t="s">
+        <v>1213</v>
+      </c>
+      <c r="G342" s="7" t="s">
         <v>1203</v>
       </c>
-      <c r="D342" s="7" t="s">
+      <c r="H342" s="7" t="s">
         <v>1204</v>
       </c>
-      <c r="E342" s="7" t="s">
+      <c r="I342" s="7" t="s">
+        <v>1205</v>
+      </c>
+      <c r="J342" s="7" t="s">
         <v>1214</v>
       </c>
-      <c r="F342" s="7" t="s">
+      <c r="K342" s="7" t="s">
+        <v>1199</v>
+      </c>
+      <c r="L342" s="7" t="s">
         <v>1215</v>
       </c>
-      <c r="G342" s="7" t="s">
-        <v>1205</v>
-      </c>
-      <c r="H342" s="7" t="s">
-        <v>1206</v>
-      </c>
-      <c r="I342" s="7" t="s">
-        <v>1207</v>
-      </c>
-      <c r="J342" s="7" t="s">
-        <v>1216</v>
-      </c>
-      <c r="K342" s="7" t="s">
-        <v>1201</v>
-      </c>
-      <c r="L342" s="7" t="s">
-        <v>1217</v>
-      </c>
       <c r="M342" s="7" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="N342" s="7" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="O342" s="7" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="P342" s="7" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="Q342" s="7" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="R342" s="7" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="343" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A343" s="7" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B343" s="7" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C343" s="7" t="s">
+        <v>1201</v>
+      </c>
+      <c r="D343" s="7" t="s">
+        <v>1207</v>
+      </c>
+      <c r="E343" s="7" t="s">
         <v>1208</v>
       </c>
-      <c r="B343" s="7" t="s">
-        <v>1175</v>
-      </c>
-      <c r="C343" s="7" t="s">
-        <v>1203</v>
-      </c>
-      <c r="D343" s="7" t="s">
+      <c r="F343" s="7" t="s">
+        <v>1216</v>
+      </c>
+      <c r="G343" s="7" t="s">
         <v>1209</v>
       </c>
-      <c r="E343" s="7" t="s">
+      <c r="H343" s="7" t="s">
         <v>1210</v>
       </c>
-      <c r="F343" s="7" t="s">
-        <v>1218</v>
-      </c>
-      <c r="G343" s="7" t="s">
+      <c r="I343" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="J343" s="7" t="s">
         <v>1211</v>
       </c>
-      <c r="H343" s="7" t="s">
-        <v>1212</v>
-      </c>
-      <c r="I343" s="7" t="s">
-        <v>1188</v>
-      </c>
-      <c r="J343" s="7" t="s">
-        <v>1213</v>
-      </c>
       <c r="K343" s="7" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="L343" s="7" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="M343" s="7" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="N343" s="7" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="O343" s="7" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="P343" s="7" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="Q343" s="7" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="R343" s="7" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="344" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A344" s="7" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B344" s="7" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C344" s="7" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D344" s="7" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E344" s="7" t="s">
         <v>1192</v>
       </c>
-      <c r="B344" s="7" t="s">
-        <v>1175</v>
-      </c>
-      <c r="C344" s="7" t="s">
-        <v>1072</v>
-      </c>
-      <c r="D344" s="7" t="s">
+      <c r="F344" s="7" t="s">
         <v>1193</v>
       </c>
-      <c r="E344" s="7" t="s">
+      <c r="G344" s="7" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H344" s="7" t="s">
         <v>1194</v>
       </c>
-      <c r="F344" s="7" t="s">
+      <c r="I344" s="7" t="s">
         <v>1195</v>
       </c>
-      <c r="G344" s="7" t="s">
-        <v>1185</v>
-      </c>
-      <c r="H344" s="7" t="s">
+      <c r="J344" s="7" t="s">
+        <v>1183</v>
+      </c>
+      <c r="K344" s="7" t="s">
         <v>1196</v>
       </c>
-      <c r="I344" s="7" t="s">
+      <c r="L344" s="7" t="s">
         <v>1197</v>
       </c>
-      <c r="J344" s="7" t="s">
-        <v>1185</v>
-      </c>
-      <c r="K344" s="7" t="s">
+      <c r="M344" s="7" t="s">
         <v>1198</v>
       </c>
-      <c r="L344" s="7" t="s">
+      <c r="N344" s="7" t="s">
         <v>1199</v>
       </c>
-      <c r="M344" s="7" t="s">
-        <v>1200</v>
-      </c>
-      <c r="N344" s="7" t="s">
-        <v>1201</v>
-      </c>
       <c r="O344" s="7" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="P344" s="7" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="Q344" s="7" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="R344" s="7" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
     </row>
   </sheetData>
@@ -30324,16 +30326,16 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
+        <v>938</v>
+      </c>
+      <c r="D2" t="s">
+        <v>939</v>
+      </c>
+      <c r="E2" t="s">
         <v>940</v>
       </c>
-      <c r="D2" t="s">
+      <c r="F2" t="s">
         <v>941</v>
-      </c>
-      <c r="E2" t="s">
-        <v>942</v>
-      </c>
-      <c r="F2" t="s">
-        <v>943</v>
       </c>
       <c r="G2">
         <v>50000</v>
@@ -30381,16 +30383,16 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
+        <v>938</v>
+      </c>
+      <c r="D3" t="s">
+        <v>942</v>
+      </c>
+      <c r="E3" t="s">
         <v>940</v>
       </c>
-      <c r="D3" t="s">
-        <v>944</v>
-      </c>
-      <c r="E3" t="s">
-        <v>942</v>
-      </c>
       <c r="F3" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
       <c r="G3">
         <v>500</v>
@@ -30438,16 +30440,16 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
+        <v>938</v>
+      </c>
+      <c r="D4" t="s">
+        <v>944</v>
+      </c>
+      <c r="E4" t="s">
         <v>940</v>
       </c>
-      <c r="D4" t="s">
-        <v>946</v>
-      </c>
-      <c r="E4" t="s">
-        <v>942</v>
-      </c>
       <c r="F4" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -30495,16 +30497,16 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
+        <v>833</v>
+      </c>
+      <c r="D5" t="s">
+        <v>834</v>
+      </c>
+      <c r="E5" t="s">
         <v>835</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>836</v>
-      </c>
-      <c r="E5" t="s">
-        <v>837</v>
-      </c>
-      <c r="F5" t="s">
-        <v>838</v>
       </c>
       <c r="G5">
         <v>24</v>
@@ -30552,16 +30554,16 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D6" t="s">
+        <v>837</v>
+      </c>
+      <c r="E6" t="s">
+        <v>838</v>
+      </c>
+      <c r="F6" t="s">
         <v>839</v>
-      </c>
-      <c r="E6" t="s">
-        <v>840</v>
-      </c>
-      <c r="F6" t="s">
-        <v>841</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -30609,16 +30611,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D7" t="s">
+        <v>840</v>
+      </c>
+      <c r="E7" t="s">
+        <v>841</v>
+      </c>
+      <c r="F7" t="s">
         <v>842</v>
-      </c>
-      <c r="E7" t="s">
-        <v>843</v>
-      </c>
-      <c r="F7" t="s">
-        <v>844</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -30666,16 +30668,16 @@
         <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D8" t="s">
+        <v>843</v>
+      </c>
+      <c r="E8" t="s">
+        <v>844</v>
+      </c>
+      <c r="F8" t="s">
         <v>845</v>
-      </c>
-      <c r="E8" t="s">
-        <v>846</v>
-      </c>
-      <c r="F8" t="s">
-        <v>847</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -31068,13 +31070,13 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
+        <v>912</v>
+      </c>
+      <c r="E15" t="s">
+        <v>913</v>
+      </c>
+      <c r="F15" t="s">
         <v>914</v>
-      </c>
-      <c r="E15" t="s">
-        <v>915</v>
-      </c>
-      <c r="F15" t="s">
-        <v>916</v>
       </c>
       <c r="G15">
         <v>30</v>
@@ -31125,13 +31127,13 @@
         <v>18</v>
       </c>
       <c r="D16" t="s">
+        <v>915</v>
+      </c>
+      <c r="E16" t="s">
+        <v>916</v>
+      </c>
+      <c r="F16" t="s">
         <v>917</v>
-      </c>
-      <c r="E16" t="s">
-        <v>918</v>
-      </c>
-      <c r="F16" t="s">
-        <v>919</v>
       </c>
       <c r="G16">
         <v>1000</v>
@@ -32670,7 +32672,7 @@
         <v>149</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -32727,7 +32729,7 @@
         <v>149</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -34092,10 +34094,10 @@
         <v>134</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G68">
         <v>0.86</v>
@@ -34320,10 +34322,10 @@
         <v>143</v>
       </c>
       <c r="E72" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="F72" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="G72">
         <v>5</v>
@@ -35175,10 +35177,10 @@
         <v>209</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="G87">
         <v>10</v>
@@ -35685,13 +35687,13 @@
         <v>188</v>
       </c>
       <c r="D96" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>947</v>
+      </c>
+      <c r="F96" s="2" t="s">
         <v>948</v>
-      </c>
-      <c r="E96" s="2" t="s">
-        <v>949</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>950</v>
       </c>
       <c r="G96">
         <v>0.75</v>
@@ -37401,7 +37403,7 @@
         <v>270</v>
       </c>
       <c r="F126" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="G126">
         <v>4</v>
@@ -37452,7 +37454,7 @@
         <v>245</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="E127" t="s">
         <v>271</v>
@@ -37509,7 +37511,7 @@
         <v>273</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="E128" t="s">
         <v>274</v>
@@ -37566,7 +37568,7 @@
         <v>273</v>
       </c>
       <c r="D129" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="E129" t="s">
         <v>274</v>
@@ -37623,7 +37625,7 @@
         <v>273</v>
       </c>
       <c r="D130" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="E130" t="s">
         <v>274</v>
@@ -37680,7 +37682,7 @@
         <v>273</v>
       </c>
       <c r="D131" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="E131" t="s">
         <v>274</v>
@@ -37737,7 +37739,7 @@
         <v>273</v>
       </c>
       <c r="D132" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="E132" t="s">
         <v>274</v>
@@ -37746,7 +37748,7 @@
         <v>275</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="H132" t="s">
         <v>287</v>
@@ -37755,7 +37757,7 @@
         <v>288</v>
       </c>
       <c r="J132" s="3" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
       <c r="K132">
         <v>0</v>
@@ -37794,7 +37796,7 @@
         <v>273</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="E133" t="s">
         <v>274</v>
@@ -37803,19 +37805,19 @@
         <v>275</v>
       </c>
       <c r="G133" s="3" t="s">
+        <v>994</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>995</v>
+      </c>
+      <c r="I133" s="3" t="s">
+        <v>993</v>
+      </c>
+      <c r="J133" s="3" t="s">
         <v>996</v>
       </c>
-      <c r="H133" s="3" t="s">
+      <c r="K133" s="3" t="s">
         <v>997</v>
-      </c>
-      <c r="I133" s="3" t="s">
-        <v>995</v>
-      </c>
-      <c r="J133" s="3" t="s">
-        <v>998</v>
-      </c>
-      <c r="K133" s="3" t="s">
-        <v>999</v>
       </c>
       <c r="L133">
         <v>0</v>
@@ -37851,7 +37853,7 @@
         <v>273</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="E134" t="s">
         <v>274</v>
@@ -37860,22 +37862,22 @@
         <v>275</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="J134" s="3" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="K134" s="3" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="L134" s="3" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M134">
         <v>0</v>
@@ -37908,13 +37910,13 @@
         <v>273</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="E135" t="s">
         <v>274</v>
       </c>
       <c r="F135" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="G135" t="s">
         <v>276</v>
@@ -37965,22 +37967,22 @@
         <v>273</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="E136" t="s">
         <v>274</v>
       </c>
       <c r="F136" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="J136">
         <v>0</v>
@@ -38022,28 +38024,28 @@
         <v>273</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="E137" t="s">
         <v>274</v>
       </c>
       <c r="F137" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="G137" s="3" t="s">
+        <v>961</v>
+      </c>
+      <c r="H137" s="3" t="s">
+        <v>962</v>
+      </c>
+      <c r="I137" s="3" t="s">
         <v>963</v>
       </c>
-      <c r="H137" s="3" t="s">
+      <c r="J137" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="K137" s="3" t="s">
         <v>964</v>
-      </c>
-      <c r="I137" s="3" t="s">
-        <v>965</v>
-      </c>
-      <c r="J137" s="3" t="s">
-        <v>967</v>
-      </c>
-      <c r="K137" s="3" t="s">
-        <v>966</v>
       </c>
       <c r="L137">
         <v>0</v>
@@ -38079,34 +38081,34 @@
         <v>273</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
       <c r="E138" t="s">
         <v>274</v>
       </c>
       <c r="F138" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="G138" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="I138" s="3" t="s">
         <v>978</v>
       </c>
-      <c r="H138" s="3" t="s">
+      <c r="J138" s="3" t="s">
         <v>979</v>
       </c>
-      <c r="I138" s="3" t="s">
+      <c r="K138" s="3" t="s">
         <v>980</v>
       </c>
-      <c r="J138" s="3" t="s">
+      <c r="L138" s="3" t="s">
         <v>981</v>
       </c>
-      <c r="K138" s="3" t="s">
+      <c r="M138" s="3" t="s">
         <v>982</v>
-      </c>
-      <c r="L138" s="3" t="s">
-        <v>983</v>
-      </c>
-      <c r="M138" s="3" t="s">
-        <v>984</v>
       </c>
       <c r="N138">
         <v>0</v>
@@ -38136,34 +38138,34 @@
         <v>273</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="E139" t="s">
         <v>274</v>
       </c>
       <c r="F139" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="G139" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="H139" s="3" t="s">
+        <v>970</v>
+      </c>
+      <c r="I139" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="J139" s="3" t="s">
         <v>971</v>
       </c>
-      <c r="H139" s="3" t="s">
+      <c r="K139" s="3" t="s">
         <v>972</v>
       </c>
-      <c r="I139" s="3" t="s">
-        <v>970</v>
-      </c>
-      <c r="J139" s="3" t="s">
+      <c r="L139" s="3" t="s">
         <v>973</v>
       </c>
-      <c r="K139" s="3" t="s">
+      <c r="M139" s="3" t="s">
         <v>974</v>
-      </c>
-      <c r="L139" s="3" t="s">
-        <v>975</v>
-      </c>
-      <c r="M139" s="3" t="s">
-        <v>976</v>
       </c>
       <c r="N139">
         <v>0</v>
@@ -40701,13 +40703,13 @@
         <v>530</v>
       </c>
       <c r="D184" t="s">
+        <v>935</v>
+      </c>
+      <c r="E184" t="s">
+        <v>936</v>
+      </c>
+      <c r="F184" t="s">
         <v>937</v>
-      </c>
-      <c r="E184" t="s">
-        <v>938</v>
-      </c>
-      <c r="F184" t="s">
-        <v>939</v>
       </c>
       <c r="G184">
         <v>0.1</v>
@@ -41385,13 +41387,13 @@
         <v>537</v>
       </c>
       <c r="D196" t="s">
+        <v>903</v>
+      </c>
+      <c r="E196" t="s">
+        <v>904</v>
+      </c>
+      <c r="F196" t="s">
         <v>905</v>
-      </c>
-      <c r="E196" t="s">
-        <v>906</v>
-      </c>
-      <c r="F196" t="s">
-        <v>907</v>
       </c>
       <c r="G196">
         <v>20</v>
@@ -41442,13 +41444,13 @@
         <v>537</v>
       </c>
       <c r="D197" t="s">
+        <v>906</v>
+      </c>
+      <c r="E197" t="s">
+        <v>907</v>
+      </c>
+      <c r="F197" t="s">
         <v>908</v>
-      </c>
-      <c r="E197" t="s">
-        <v>909</v>
-      </c>
-      <c r="F197" t="s">
-        <v>910</v>
       </c>
       <c r="G197">
         <v>500000000</v>
@@ -41499,13 +41501,13 @@
         <v>537</v>
       </c>
       <c r="D198" t="s">
+        <v>909</v>
+      </c>
+      <c r="E198" t="s">
+        <v>910</v>
+      </c>
+      <c r="F198" t="s">
         <v>911</v>
-      </c>
-      <c r="E198" t="s">
-        <v>912</v>
-      </c>
-      <c r="F198" t="s">
-        <v>913</v>
       </c>
       <c r="G198">
         <v>13</v>
@@ -42255,7 +42257,7 @@
         <v>607</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="F211" t="s">
         <v>608</v>
@@ -44237,10 +44239,10 @@
         <v>633</v>
       </c>
       <c r="E233" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="F233" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="G233">
         <v>3</v>
@@ -44294,10 +44296,10 @@
         <v>634</v>
       </c>
       <c r="E234" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="F234" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="G234">
         <v>100</v>
@@ -44351,10 +44353,10 @@
         <v>635</v>
       </c>
       <c r="E235" t="s">
-        <v>636</v>
+        <v>1223</v>
       </c>
       <c r="F235" t="s">
-        <v>637</v>
+        <v>1224</v>
       </c>
       <c r="G235">
         <v>9</v>
@@ -44405,13 +44407,13 @@
         <v>623</v>
       </c>
       <c r="D236" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E236" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="F236" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="G236">
         <v>0.7</v>
@@ -44462,13 +44464,13 @@
         <v>623</v>
       </c>
       <c r="D237" t="s">
+        <v>637</v>
+      </c>
+      <c r="E237" t="s">
+        <v>638</v>
+      </c>
+      <c r="F237" t="s">
         <v>639</v>
-      </c>
-      <c r="E237" t="s">
-        <v>640</v>
-      </c>
-      <c r="F237" t="s">
-        <v>641</v>
       </c>
       <c r="G237">
         <v>0.7</v>
@@ -44519,13 +44521,13 @@
         <v>623</v>
       </c>
       <c r="D238" t="s">
+        <v>640</v>
+      </c>
+      <c r="E238" t="s">
+        <v>641</v>
+      </c>
+      <c r="F238" t="s">
         <v>642</v>
-      </c>
-      <c r="E238" t="s">
-        <v>643</v>
-      </c>
-      <c r="F238" t="s">
-        <v>644</v>
       </c>
       <c r="G238">
         <v>10</v>
@@ -44576,13 +44578,13 @@
         <v>623</v>
       </c>
       <c r="D239" t="s">
+        <v>643</v>
+      </c>
+      <c r="E239" t="s">
+        <v>644</v>
+      </c>
+      <c r="F239" t="s">
         <v>645</v>
-      </c>
-      <c r="E239" t="s">
-        <v>646</v>
-      </c>
-      <c r="F239" t="s">
-        <v>647</v>
       </c>
       <c r="G239">
         <v>0</v>
@@ -44630,16 +44632,16 @@
         <v>0</v>
       </c>
       <c r="C240" t="s">
+        <v>646</v>
+      </c>
+      <c r="D240" t="s">
+        <v>647</v>
+      </c>
+      <c r="E240" t="s">
         <v>648</v>
       </c>
-      <c r="D240" t="s">
+      <c r="F240" t="s">
         <v>649</v>
-      </c>
-      <c r="E240" t="s">
-        <v>650</v>
-      </c>
-      <c r="F240" t="s">
-        <v>651</v>
       </c>
       <c r="G240">
         <v>100000</v>
@@ -44687,16 +44689,16 @@
         <v>0</v>
       </c>
       <c r="C241" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D241" t="s">
+        <v>650</v>
+      </c>
+      <c r="E241" t="s">
+        <v>651</v>
+      </c>
+      <c r="F241" t="s">
         <v>652</v>
-      </c>
-      <c r="E241" t="s">
-        <v>653</v>
-      </c>
-      <c r="F241" t="s">
-        <v>654</v>
       </c>
       <c r="G241">
         <v>5000</v>
@@ -44744,13 +44746,13 @@
         <v>0</v>
       </c>
       <c r="C242" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D242" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E242" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="F242">
         <v>0</v>
@@ -44801,16 +44803,16 @@
         <v>0</v>
       </c>
       <c r="C243" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D243" t="s">
+        <v>655</v>
+      </c>
+      <c r="E243" t="s">
+        <v>656</v>
+      </c>
+      <c r="F243" t="s">
         <v>657</v>
-      </c>
-      <c r="E243" t="s">
-        <v>658</v>
-      </c>
-      <c r="F243" t="s">
-        <v>659</v>
       </c>
       <c r="G243">
         <v>10000</v>
@@ -44858,28 +44860,28 @@
         <v>0</v>
       </c>
       <c r="C244" t="s">
+        <v>729</v>
+      </c>
+      <c r="D244" t="s">
+        <v>659</v>
+      </c>
+      <c r="E244" t="s">
+        <v>730</v>
+      </c>
+      <c r="F244" t="s">
         <v>731</v>
       </c>
-      <c r="D244" t="s">
-        <v>661</v>
-      </c>
-      <c r="E244" t="s">
+      <c r="G244" t="s">
         <v>732</v>
       </c>
-      <c r="F244" t="s">
+      <c r="H244" t="s">
         <v>733</v>
       </c>
-      <c r="G244" t="s">
+      <c r="I244" t="s">
         <v>734</v>
       </c>
-      <c r="H244" t="s">
+      <c r="J244" t="s">
         <v>735</v>
-      </c>
-      <c r="I244" t="s">
-        <v>736</v>
-      </c>
-      <c r="J244" t="s">
-        <v>737</v>
       </c>
       <c r="K244">
         <v>0</v>
@@ -44915,28 +44917,28 @@
         <v>0</v>
       </c>
       <c r="C245" t="s">
+        <v>729</v>
+      </c>
+      <c r="D245" t="s">
+        <v>664</v>
+      </c>
+      <c r="E245" t="s">
+        <v>730</v>
+      </c>
+      <c r="F245" t="s">
         <v>731</v>
       </c>
-      <c r="D245" t="s">
-        <v>666</v>
-      </c>
-      <c r="E245" t="s">
-        <v>732</v>
-      </c>
-      <c r="F245" t="s">
+      <c r="G245" t="s">
+        <v>736</v>
+      </c>
+      <c r="H245" t="s">
         <v>733</v>
       </c>
-      <c r="G245" t="s">
+      <c r="I245" t="s">
+        <v>737</v>
+      </c>
+      <c r="J245" t="s">
         <v>738</v>
-      </c>
-      <c r="H245" t="s">
-        <v>735</v>
-      </c>
-      <c r="I245" t="s">
-        <v>739</v>
-      </c>
-      <c r="J245" t="s">
-        <v>740</v>
       </c>
       <c r="K245">
         <v>0</v>
@@ -44972,28 +44974,28 @@
         <v>0</v>
       </c>
       <c r="C246" t="s">
+        <v>729</v>
+      </c>
+      <c r="D246" t="s">
+        <v>667</v>
+      </c>
+      <c r="E246" t="s">
+        <v>730</v>
+      </c>
+      <c r="F246" t="s">
         <v>731</v>
       </c>
-      <c r="D246" t="s">
-        <v>669</v>
-      </c>
-      <c r="E246" t="s">
-        <v>732</v>
-      </c>
-      <c r="F246" t="s">
+      <c r="G246" t="s">
+        <v>739</v>
+      </c>
+      <c r="H246" t="s">
         <v>733</v>
       </c>
-      <c r="G246" t="s">
+      <c r="I246" t="s">
+        <v>740</v>
+      </c>
+      <c r="J246" t="s">
         <v>741</v>
-      </c>
-      <c r="H246" t="s">
-        <v>735</v>
-      </c>
-      <c r="I246" t="s">
-        <v>742</v>
-      </c>
-      <c r="J246" t="s">
-        <v>743</v>
       </c>
       <c r="K246">
         <v>0</v>
@@ -45029,31 +45031,31 @@
         <v>0</v>
       </c>
       <c r="C247" t="s">
+        <v>729</v>
+      </c>
+      <c r="D247" t="s">
+        <v>670</v>
+      </c>
+      <c r="E247" t="s">
+        <v>730</v>
+      </c>
+      <c r="F247" t="s">
         <v>731</v>
       </c>
-      <c r="D247" t="s">
-        <v>672</v>
-      </c>
-      <c r="E247" t="s">
-        <v>732</v>
-      </c>
-      <c r="F247" t="s">
+      <c r="G247" t="s">
+        <v>742</v>
+      </c>
+      <c r="H247" t="s">
         <v>733</v>
       </c>
-      <c r="G247" t="s">
-        <v>744</v>
-      </c>
-      <c r="H247" t="s">
-        <v>735</v>
-      </c>
       <c r="I247" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="J247" t="s">
+        <v>741</v>
+      </c>
+      <c r="K247" t="s">
         <v>743</v>
-      </c>
-      <c r="K247" t="s">
-        <v>745</v>
       </c>
       <c r="L247">
         <v>0</v>
@@ -45086,31 +45088,31 @@
         <v>0</v>
       </c>
       <c r="C248" t="s">
+        <v>729</v>
+      </c>
+      <c r="D248" t="s">
+        <v>673</v>
+      </c>
+      <c r="E248" t="s">
+        <v>730</v>
+      </c>
+      <c r="F248" t="s">
         <v>731</v>
       </c>
-      <c r="D248" t="s">
-        <v>675</v>
-      </c>
-      <c r="E248" t="s">
-        <v>732</v>
-      </c>
-      <c r="F248" t="s">
+      <c r="G248" t="s">
+        <v>744</v>
+      </c>
+      <c r="H248" t="s">
         <v>733</v>
       </c>
-      <c r="G248" t="s">
+      <c r="I248" t="s">
+        <v>740</v>
+      </c>
+      <c r="J248" t="s">
+        <v>745</v>
+      </c>
+      <c r="K248" t="s">
         <v>746</v>
-      </c>
-      <c r="H248" t="s">
-        <v>735</v>
-      </c>
-      <c r="I248" t="s">
-        <v>742</v>
-      </c>
-      <c r="J248" t="s">
-        <v>747</v>
-      </c>
-      <c r="K248" t="s">
-        <v>748</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -45143,31 +45145,31 @@
         <v>0</v>
       </c>
       <c r="C249" t="s">
+        <v>729</v>
+      </c>
+      <c r="D249" t="s">
+        <v>676</v>
+      </c>
+      <c r="E249" t="s">
+        <v>730</v>
+      </c>
+      <c r="F249" t="s">
         <v>731</v>
       </c>
-      <c r="D249" t="s">
-        <v>678</v>
-      </c>
-      <c r="E249" t="s">
-        <v>732</v>
-      </c>
-      <c r="F249" t="s">
+      <c r="G249" t="s">
+        <v>747</v>
+      </c>
+      <c r="H249" t="s">
         <v>733</v>
       </c>
-      <c r="G249" t="s">
+      <c r="I249" t="s">
+        <v>740</v>
+      </c>
+      <c r="J249" t="s">
+        <v>748</v>
+      </c>
+      <c r="K249" t="s">
         <v>749</v>
-      </c>
-      <c r="H249" t="s">
-        <v>735</v>
-      </c>
-      <c r="I249" t="s">
-        <v>742</v>
-      </c>
-      <c r="J249" t="s">
-        <v>750</v>
-      </c>
-      <c r="K249" t="s">
-        <v>751</v>
       </c>
       <c r="L249">
         <v>0</v>
@@ -45200,31 +45202,31 @@
         <v>0</v>
       </c>
       <c r="C250" t="s">
+        <v>729</v>
+      </c>
+      <c r="D250" t="s">
+        <v>679</v>
+      </c>
+      <c r="E250" t="s">
+        <v>730</v>
+      </c>
+      <c r="F250" t="s">
         <v>731</v>
       </c>
-      <c r="D250" t="s">
-        <v>681</v>
-      </c>
-      <c r="E250" t="s">
-        <v>732</v>
-      </c>
-      <c r="F250" t="s">
+      <c r="G250" t="s">
+        <v>750</v>
+      </c>
+      <c r="H250" t="s">
         <v>733</v>
       </c>
-      <c r="G250" t="s">
+      <c r="I250" t="s">
+        <v>751</v>
+      </c>
+      <c r="J250" t="s">
         <v>752</v>
       </c>
-      <c r="H250" t="s">
-        <v>735</v>
-      </c>
-      <c r="I250" t="s">
+      <c r="K250" t="s">
         <v>753</v>
-      </c>
-      <c r="J250" t="s">
-        <v>754</v>
-      </c>
-      <c r="K250" t="s">
-        <v>755</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -45257,31 +45259,31 @@
         <v>0</v>
       </c>
       <c r="C251" t="s">
+        <v>729</v>
+      </c>
+      <c r="D251" t="s">
+        <v>684</v>
+      </c>
+      <c r="E251" t="s">
+        <v>730</v>
+      </c>
+      <c r="F251" t="s">
         <v>731</v>
       </c>
-      <c r="D251" t="s">
-        <v>686</v>
-      </c>
-      <c r="E251" t="s">
-        <v>732</v>
-      </c>
-      <c r="F251" t="s">
+      <c r="G251" t="s">
+        <v>754</v>
+      </c>
+      <c r="H251" t="s">
         <v>733</v>
       </c>
-      <c r="G251" t="s">
+      <c r="I251" t="s">
+        <v>755</v>
+      </c>
+      <c r="J251" t="s">
         <v>756</v>
       </c>
-      <c r="H251" t="s">
-        <v>735</v>
-      </c>
-      <c r="I251" t="s">
+      <c r="K251" t="s">
         <v>757</v>
-      </c>
-      <c r="J251" t="s">
-        <v>758</v>
-      </c>
-      <c r="K251" t="s">
-        <v>759</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -45314,31 +45316,31 @@
         <v>0</v>
       </c>
       <c r="C252" t="s">
+        <v>729</v>
+      </c>
+      <c r="D252" t="s">
+        <v>686</v>
+      </c>
+      <c r="E252" t="s">
+        <v>730</v>
+      </c>
+      <c r="F252" t="s">
         <v>731</v>
       </c>
-      <c r="D252" t="s">
-        <v>688</v>
-      </c>
-      <c r="E252" t="s">
-        <v>732</v>
-      </c>
-      <c r="F252" t="s">
+      <c r="G252" t="s">
+        <v>758</v>
+      </c>
+      <c r="H252" t="s">
         <v>733</v>
       </c>
-      <c r="G252" t="s">
+      <c r="I252" t="s">
+        <v>759</v>
+      </c>
+      <c r="J252" t="s">
         <v>760</v>
       </c>
-      <c r="H252" t="s">
-        <v>735</v>
-      </c>
-      <c r="I252" t="s">
+      <c r="K252" t="s">
         <v>761</v>
-      </c>
-      <c r="J252" t="s">
-        <v>762</v>
-      </c>
-      <c r="K252" t="s">
-        <v>763</v>
       </c>
       <c r="L252">
         <v>0</v>
@@ -45371,34 +45373,34 @@
         <v>0</v>
       </c>
       <c r="C253" t="s">
+        <v>729</v>
+      </c>
+      <c r="D253" t="s">
+        <v>690</v>
+      </c>
+      <c r="E253" t="s">
+        <v>730</v>
+      </c>
+      <c r="F253" t="s">
         <v>731</v>
       </c>
-      <c r="D253" t="s">
-        <v>692</v>
-      </c>
-      <c r="E253" t="s">
-        <v>732</v>
-      </c>
-      <c r="F253" t="s">
+      <c r="G253" t="s">
+        <v>762</v>
+      </c>
+      <c r="H253" t="s">
         <v>733</v>
       </c>
-      <c r="G253" t="s">
+      <c r="I253" t="s">
+        <v>759</v>
+      </c>
+      <c r="J253" t="s">
+        <v>760</v>
+      </c>
+      <c r="K253" t="s">
+        <v>763</v>
+      </c>
+      <c r="L253" t="s">
         <v>764</v>
-      </c>
-      <c r="H253" t="s">
-        <v>735</v>
-      </c>
-      <c r="I253" t="s">
-        <v>761</v>
-      </c>
-      <c r="J253" t="s">
-        <v>762</v>
-      </c>
-      <c r="K253" t="s">
-        <v>765</v>
-      </c>
-      <c r="L253" t="s">
-        <v>766</v>
       </c>
       <c r="M253">
         <v>0</v>
@@ -45428,34 +45430,34 @@
         <v>0</v>
       </c>
       <c r="C254" t="s">
+        <v>729</v>
+      </c>
+      <c r="D254" t="s">
+        <v>694</v>
+      </c>
+      <c r="E254" t="s">
+        <v>730</v>
+      </c>
+      <c r="F254" t="s">
         <v>731</v>
       </c>
-      <c r="D254" t="s">
-        <v>696</v>
-      </c>
-      <c r="E254" t="s">
-        <v>732</v>
-      </c>
-      <c r="F254" t="s">
+      <c r="G254" t="s">
+        <v>765</v>
+      </c>
+      <c r="H254" t="s">
         <v>733</v>
       </c>
-      <c r="G254" t="s">
+      <c r="I254" t="s">
+        <v>759</v>
+      </c>
+      <c r="J254" t="s">
+        <v>760</v>
+      </c>
+      <c r="K254" t="s">
+        <v>766</v>
+      </c>
+      <c r="L254" t="s">
         <v>767</v>
-      </c>
-      <c r="H254" t="s">
-        <v>735</v>
-      </c>
-      <c r="I254" t="s">
-        <v>761</v>
-      </c>
-      <c r="J254" t="s">
-        <v>762</v>
-      </c>
-      <c r="K254" t="s">
-        <v>768</v>
-      </c>
-      <c r="L254" t="s">
-        <v>769</v>
       </c>
       <c r="M254">
         <v>0</v>
@@ -45485,34 +45487,34 @@
         <v>0</v>
       </c>
       <c r="C255" t="s">
+        <v>729</v>
+      </c>
+      <c r="D255" t="s">
+        <v>698</v>
+      </c>
+      <c r="E255" t="s">
+        <v>730</v>
+      </c>
+      <c r="F255" t="s">
         <v>731</v>
       </c>
-      <c r="D255" t="s">
-        <v>700</v>
-      </c>
-      <c r="E255" t="s">
-        <v>732</v>
-      </c>
-      <c r="F255" t="s">
+      <c r="G255" t="s">
+        <v>768</v>
+      </c>
+      <c r="H255" t="s">
         <v>733</v>
       </c>
-      <c r="G255" t="s">
+      <c r="I255" t="s">
+        <v>769</v>
+      </c>
+      <c r="J255" t="s">
         <v>770</v>
       </c>
-      <c r="H255" t="s">
-        <v>735</v>
-      </c>
-      <c r="I255" t="s">
+      <c r="K255" t="s">
         <v>771</v>
       </c>
-      <c r="J255" t="s">
+      <c r="L255" t="s">
         <v>772</v>
-      </c>
-      <c r="K255" t="s">
-        <v>773</v>
-      </c>
-      <c r="L255" t="s">
-        <v>774</v>
       </c>
       <c r="M255">
         <v>0</v>
@@ -45542,34 +45544,34 @@
         <v>0</v>
       </c>
       <c r="C256" t="s">
+        <v>729</v>
+      </c>
+      <c r="D256" t="s">
+        <v>702</v>
+      </c>
+      <c r="E256" t="s">
+        <v>730</v>
+      </c>
+      <c r="F256" t="s">
         <v>731</v>
       </c>
-      <c r="D256" t="s">
-        <v>704</v>
-      </c>
-      <c r="E256" t="s">
-        <v>732</v>
-      </c>
-      <c r="F256" t="s">
+      <c r="G256" t="s">
+        <v>773</v>
+      </c>
+      <c r="H256" t="s">
         <v>733</v>
       </c>
-      <c r="G256" t="s">
-        <v>775</v>
-      </c>
-      <c r="H256" t="s">
-        <v>735</v>
-      </c>
       <c r="I256" t="s">
+        <v>769</v>
+      </c>
+      <c r="J256" t="s">
+        <v>770</v>
+      </c>
+      <c r="K256" t="s">
         <v>771</v>
       </c>
-      <c r="J256" t="s">
-        <v>772</v>
-      </c>
-      <c r="K256" t="s">
-        <v>773</v>
-      </c>
       <c r="L256" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="M256">
         <v>0</v>
@@ -45599,34 +45601,34 @@
         <v>0</v>
       </c>
       <c r="C257" t="s">
+        <v>729</v>
+      </c>
+      <c r="D257" t="s">
+        <v>706</v>
+      </c>
+      <c r="E257" t="s">
+        <v>730</v>
+      </c>
+      <c r="F257" t="s">
         <v>731</v>
       </c>
-      <c r="D257" t="s">
-        <v>708</v>
-      </c>
-      <c r="E257" t="s">
-        <v>732</v>
-      </c>
-      <c r="F257" t="s">
+      <c r="G257" t="s">
+        <v>775</v>
+      </c>
+      <c r="H257" t="s">
         <v>733</v>
       </c>
-      <c r="G257" t="s">
-        <v>777</v>
-      </c>
-      <c r="H257" t="s">
-        <v>735</v>
-      </c>
       <c r="I257" t="s">
+        <v>769</v>
+      </c>
+      <c r="J257" t="s">
+        <v>770</v>
+      </c>
+      <c r="K257" t="s">
         <v>771</v>
       </c>
-      <c r="J257" t="s">
-        <v>772</v>
-      </c>
-      <c r="K257" t="s">
-        <v>773</v>
-      </c>
       <c r="L257" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="M257">
         <v>0</v>
@@ -45656,37 +45658,37 @@
         <v>0</v>
       </c>
       <c r="C258" t="s">
+        <v>729</v>
+      </c>
+      <c r="D258" t="s">
+        <v>710</v>
+      </c>
+      <c r="E258" t="s">
+        <v>730</v>
+      </c>
+      <c r="F258" t="s">
         <v>731</v>
       </c>
-      <c r="D258" t="s">
-        <v>712</v>
-      </c>
-      <c r="E258" t="s">
-        <v>732</v>
-      </c>
-      <c r="F258" t="s">
+      <c r="G258" t="s">
+        <v>777</v>
+      </c>
+      <c r="H258" t="s">
         <v>733</v>
       </c>
-      <c r="G258" t="s">
+      <c r="I258" t="s">
+        <v>769</v>
+      </c>
+      <c r="J258" t="s">
+        <v>778</v>
+      </c>
+      <c r="K258" t="s">
         <v>779</v>
       </c>
-      <c r="H258" t="s">
-        <v>735</v>
-      </c>
-      <c r="I258" t="s">
-        <v>771</v>
-      </c>
-      <c r="J258" t="s">
+      <c r="L258" t="s">
+        <v>772</v>
+      </c>
+      <c r="M258" t="s">
         <v>780</v>
-      </c>
-      <c r="K258" t="s">
-        <v>781</v>
-      </c>
-      <c r="L258" t="s">
-        <v>774</v>
-      </c>
-      <c r="M258" t="s">
-        <v>782</v>
       </c>
       <c r="N258">
         <v>0</v>
@@ -45713,37 +45715,37 @@
         <v>0</v>
       </c>
       <c r="C259" t="s">
+        <v>729</v>
+      </c>
+      <c r="D259" t="s">
+        <v>714</v>
+      </c>
+      <c r="E259" t="s">
+        <v>730</v>
+      </c>
+      <c r="F259" t="s">
         <v>731</v>
       </c>
-      <c r="D259" t="s">
-        <v>716</v>
-      </c>
-      <c r="E259" t="s">
-        <v>732</v>
-      </c>
-      <c r="F259" t="s">
+      <c r="G259" t="s">
+        <v>781</v>
+      </c>
+      <c r="H259" t="s">
         <v>733</v>
       </c>
-      <c r="G259" t="s">
-        <v>783</v>
-      </c>
-      <c r="H259" t="s">
-        <v>735</v>
-      </c>
       <c r="I259" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="J259" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="K259" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="L259" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="M259" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="N259">
         <v>0</v>
@@ -45770,37 +45772,37 @@
         <v>0</v>
       </c>
       <c r="C260" t="s">
+        <v>729</v>
+      </c>
+      <c r="D260" t="s">
+        <v>718</v>
+      </c>
+      <c r="E260" t="s">
+        <v>730</v>
+      </c>
+      <c r="F260" t="s">
         <v>731</v>
       </c>
-      <c r="D260" t="s">
-        <v>720</v>
-      </c>
-      <c r="E260" t="s">
-        <v>732</v>
-      </c>
-      <c r="F260" t="s">
+      <c r="G260" t="s">
+        <v>783</v>
+      </c>
+      <c r="H260" t="s">
         <v>733</v>
       </c>
-      <c r="G260" t="s">
-        <v>785</v>
-      </c>
-      <c r="H260" t="s">
-        <v>735</v>
-      </c>
       <c r="I260" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="J260" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="K260" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="L260" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="M260" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="N260">
         <v>0</v>
@@ -45827,40 +45829,40 @@
         <v>0</v>
       </c>
       <c r="C261" t="s">
+        <v>729</v>
+      </c>
+      <c r="D261" t="s">
+        <v>722</v>
+      </c>
+      <c r="E261" t="s">
+        <v>730</v>
+      </c>
+      <c r="F261" t="s">
         <v>731</v>
       </c>
-      <c r="D261" t="s">
-        <v>724</v>
-      </c>
-      <c r="E261" t="s">
-        <v>732</v>
-      </c>
-      <c r="F261" t="s">
+      <c r="G261" t="s">
+        <v>785</v>
+      </c>
+      <c r="H261" t="s">
         <v>733</v>
       </c>
-      <c r="G261" t="s">
-        <v>787</v>
-      </c>
-      <c r="H261" t="s">
-        <v>735</v>
-      </c>
       <c r="I261" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="J261" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="K261" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="L261" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="M261" t="s">
+        <v>784</v>
+      </c>
+      <c r="N261" t="s">
         <v>786</v>
-      </c>
-      <c r="N261" t="s">
-        <v>788</v>
       </c>
       <c r="O261">
         <v>0</v>
@@ -45884,43 +45886,43 @@
         <v>0</v>
       </c>
       <c r="C262" t="s">
+        <v>729</v>
+      </c>
+      <c r="D262" t="s">
+        <v>727</v>
+      </c>
+      <c r="E262" t="s">
+        <v>730</v>
+      </c>
+      <c r="F262" t="s">
         <v>731</v>
       </c>
-      <c r="D262" t="s">
-        <v>729</v>
-      </c>
-      <c r="E262" t="s">
-        <v>732</v>
-      </c>
-      <c r="F262" t="s">
+      <c r="G262" t="s">
+        <v>787</v>
+      </c>
+      <c r="H262" t="s">
         <v>733</v>
       </c>
-      <c r="G262" t="s">
+      <c r="I262" t="s">
+        <v>769</v>
+      </c>
+      <c r="J262" t="s">
+        <v>778</v>
+      </c>
+      <c r="K262" t="s">
+        <v>779</v>
+      </c>
+      <c r="L262" t="s">
+        <v>774</v>
+      </c>
+      <c r="M262" t="s">
+        <v>784</v>
+      </c>
+      <c r="N262" t="s">
+        <v>788</v>
+      </c>
+      <c r="O262" t="s">
         <v>789</v>
-      </c>
-      <c r="H262" t="s">
-        <v>735</v>
-      </c>
-      <c r="I262" t="s">
-        <v>771</v>
-      </c>
-      <c r="J262" t="s">
-        <v>780</v>
-      </c>
-      <c r="K262" t="s">
-        <v>781</v>
-      </c>
-      <c r="L262" t="s">
-        <v>776</v>
-      </c>
-      <c r="M262" t="s">
-        <v>786</v>
-      </c>
-      <c r="N262" t="s">
-        <v>790</v>
-      </c>
-      <c r="O262" t="s">
-        <v>791</v>
       </c>
       <c r="P262">
         <v>0</v>
@@ -45941,46 +45943,46 @@
         <v>0</v>
       </c>
       <c r="C263" t="s">
+        <v>729</v>
+      </c>
+      <c r="D263" t="s">
+        <v>728</v>
+      </c>
+      <c r="E263" t="s">
+        <v>730</v>
+      </c>
+      <c r="F263" t="s">
         <v>731</v>
       </c>
-      <c r="D263" t="s">
-        <v>730</v>
-      </c>
-      <c r="E263" t="s">
-        <v>732</v>
-      </c>
-      <c r="F263" t="s">
+      <c r="G263" t="s">
+        <v>790</v>
+      </c>
+      <c r="H263" t="s">
         <v>733</v>
       </c>
-      <c r="G263" t="s">
+      <c r="I263" t="s">
+        <v>769</v>
+      </c>
+      <c r="J263" t="s">
+        <v>778</v>
+      </c>
+      <c r="K263" t="s">
+        <v>779</v>
+      </c>
+      <c r="L263" t="s">
+        <v>774</v>
+      </c>
+      <c r="M263" t="s">
+        <v>784</v>
+      </c>
+      <c r="N263" t="s">
+        <v>791</v>
+      </c>
+      <c r="O263" t="s">
         <v>792</v>
       </c>
-      <c r="H263" t="s">
-        <v>735</v>
-      </c>
-      <c r="I263" t="s">
-        <v>771</v>
-      </c>
-      <c r="J263" t="s">
-        <v>780</v>
-      </c>
-      <c r="K263" t="s">
-        <v>781</v>
-      </c>
-      <c r="L263" t="s">
-        <v>776</v>
-      </c>
-      <c r="M263" t="s">
-        <v>786</v>
-      </c>
-      <c r="N263" t="s">
+      <c r="P263" t="s">
         <v>793</v>
-      </c>
-      <c r="O263" t="s">
-        <v>794</v>
-      </c>
-      <c r="P263" t="s">
-        <v>795</v>
       </c>
       <c r="Q263">
         <v>0</v>
@@ -45998,22 +46000,22 @@
         <v>0</v>
       </c>
       <c r="C264" t="s">
+        <v>658</v>
+      </c>
+      <c r="D264" t="s">
+        <v>659</v>
+      </c>
+      <c r="E264" t="s">
         <v>660</v>
       </c>
-      <c r="D264" t="s">
+      <c r="F264" t="s">
         <v>661</v>
       </c>
-      <c r="E264" t="s">
+      <c r="G264" t="s">
         <v>662</v>
       </c>
-      <c r="F264" t="s">
+      <c r="H264" t="s">
         <v>663</v>
-      </c>
-      <c r="G264" t="s">
-        <v>664</v>
-      </c>
-      <c r="H264" t="s">
-        <v>665</v>
       </c>
       <c r="I264">
         <v>0</v>
@@ -46055,25 +46057,25 @@
         <v>0</v>
       </c>
       <c r="C265" t="s">
+        <v>658</v>
+      </c>
+      <c r="D265" t="s">
+        <v>664</v>
+      </c>
+      <c r="E265" t="s">
         <v>660</v>
       </c>
-      <c r="D265" t="s">
+      <c r="F265" t="s">
+        <v>661</v>
+      </c>
+      <c r="G265" t="s">
+        <v>662</v>
+      </c>
+      <c r="H265" t="s">
+        <v>665</v>
+      </c>
+      <c r="I265" t="s">
         <v>666</v>
-      </c>
-      <c r="E265" t="s">
-        <v>662</v>
-      </c>
-      <c r="F265" t="s">
-        <v>663</v>
-      </c>
-      <c r="G265" t="s">
-        <v>664</v>
-      </c>
-      <c r="H265" t="s">
-        <v>667</v>
-      </c>
-      <c r="I265" t="s">
-        <v>668</v>
       </c>
       <c r="J265">
         <v>0</v>
@@ -46112,28 +46114,28 @@
         <v>0</v>
       </c>
       <c r="C266" t="s">
+        <v>658</v>
+      </c>
+      <c r="D266" t="s">
+        <v>667</v>
+      </c>
+      <c r="E266" t="s">
         <v>660</v>
       </c>
-      <c r="D266" t="s">
+      <c r="F266" t="s">
+        <v>661</v>
+      </c>
+      <c r="G266" t="s">
+        <v>662</v>
+      </c>
+      <c r="H266" t="s">
+        <v>668</v>
+      </c>
+      <c r="I266" t="s">
+        <v>666</v>
+      </c>
+      <c r="J266" t="s">
         <v>669</v>
-      </c>
-      <c r="E266" t="s">
-        <v>662</v>
-      </c>
-      <c r="F266" t="s">
-        <v>663</v>
-      </c>
-      <c r="G266" t="s">
-        <v>664</v>
-      </c>
-      <c r="H266" t="s">
-        <v>670</v>
-      </c>
-      <c r="I266" t="s">
-        <v>668</v>
-      </c>
-      <c r="J266" t="s">
-        <v>671</v>
       </c>
       <c r="K266">
         <v>0</v>
@@ -46169,28 +46171,28 @@
         <v>0</v>
       </c>
       <c r="C267" t="s">
+        <v>658</v>
+      </c>
+      <c r="D267" t="s">
+        <v>670</v>
+      </c>
+      <c r="E267" t="s">
         <v>660</v>
       </c>
-      <c r="D267" t="s">
+      <c r="F267" t="s">
+        <v>661</v>
+      </c>
+      <c r="G267" t="s">
+        <v>671</v>
+      </c>
+      <c r="H267" t="s">
+        <v>668</v>
+      </c>
+      <c r="I267" t="s">
         <v>672</v>
       </c>
-      <c r="E267" t="s">
-        <v>662</v>
-      </c>
-      <c r="F267" t="s">
-        <v>663</v>
-      </c>
-      <c r="G267" t="s">
-        <v>673</v>
-      </c>
-      <c r="H267" t="s">
-        <v>670</v>
-      </c>
-      <c r="I267" t="s">
-        <v>674</v>
-      </c>
       <c r="J267" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="K267">
         <v>0</v>
@@ -46226,28 +46228,28 @@
         <v>0</v>
       </c>
       <c r="C268" t="s">
+        <v>658</v>
+      </c>
+      <c r="D268" t="s">
+        <v>673</v>
+      </c>
+      <c r="E268" t="s">
         <v>660</v>
       </c>
-      <c r="D268" t="s">
+      <c r="F268" t="s">
+        <v>661</v>
+      </c>
+      <c r="G268" t="s">
+        <v>674</v>
+      </c>
+      <c r="H268" t="s">
+        <v>668</v>
+      </c>
+      <c r="I268" t="s">
+        <v>672</v>
+      </c>
+      <c r="J268" t="s">
         <v>675</v>
-      </c>
-      <c r="E268" t="s">
-        <v>662</v>
-      </c>
-      <c r="F268" t="s">
-        <v>663</v>
-      </c>
-      <c r="G268" t="s">
-        <v>676</v>
-      </c>
-      <c r="H268" t="s">
-        <v>670</v>
-      </c>
-      <c r="I268" t="s">
-        <v>674</v>
-      </c>
-      <c r="J268" t="s">
-        <v>677</v>
       </c>
       <c r="K268">
         <v>0</v>
@@ -46283,31 +46285,31 @@
         <v>0</v>
       </c>
       <c r="C269" t="s">
+        <v>658</v>
+      </c>
+      <c r="D269" t="s">
+        <v>676</v>
+      </c>
+      <c r="E269" t="s">
         <v>660</v>
       </c>
-      <c r="D269" t="s">
+      <c r="F269" t="s">
+        <v>661</v>
+      </c>
+      <c r="G269" t="s">
+        <v>677</v>
+      </c>
+      <c r="H269" t="s">
+        <v>668</v>
+      </c>
+      <c r="I269" t="s">
+        <v>672</v>
+      </c>
+      <c r="J269" t="s">
+        <v>675</v>
+      </c>
+      <c r="K269" t="s">
         <v>678</v>
-      </c>
-      <c r="E269" t="s">
-        <v>662</v>
-      </c>
-      <c r="F269" t="s">
-        <v>663</v>
-      </c>
-      <c r="G269" t="s">
-        <v>679</v>
-      </c>
-      <c r="H269" t="s">
-        <v>670</v>
-      </c>
-      <c r="I269" t="s">
-        <v>674</v>
-      </c>
-      <c r="J269" t="s">
-        <v>677</v>
-      </c>
-      <c r="K269" t="s">
-        <v>680</v>
       </c>
       <c r="L269">
         <v>0</v>
@@ -46340,31 +46342,31 @@
         <v>0</v>
       </c>
       <c r="C270" t="s">
+        <v>658</v>
+      </c>
+      <c r="D270" t="s">
+        <v>679</v>
+      </c>
+      <c r="E270" t="s">
         <v>660</v>
       </c>
-      <c r="D270" t="s">
+      <c r="F270" t="s">
+        <v>661</v>
+      </c>
+      <c r="G270" t="s">
+        <v>680</v>
+      </c>
+      <c r="H270" t="s">
         <v>681</v>
       </c>
-      <c r="E270" t="s">
-        <v>662</v>
-      </c>
-      <c r="F270" t="s">
-        <v>663</v>
-      </c>
-      <c r="G270" t="s">
+      <c r="I270" t="s">
+        <v>675</v>
+      </c>
+      <c r="J270" t="s">
         <v>682</v>
       </c>
-      <c r="H270" t="s">
+      <c r="K270" t="s">
         <v>683</v>
-      </c>
-      <c r="I270" t="s">
-        <v>677</v>
-      </c>
-      <c r="J270" t="s">
-        <v>684</v>
-      </c>
-      <c r="K270" t="s">
-        <v>685</v>
       </c>
       <c r="L270">
         <v>0</v>
@@ -46397,31 +46399,31 @@
         <v>0</v>
       </c>
       <c r="C271" t="s">
+        <v>658</v>
+      </c>
+      <c r="D271" t="s">
+        <v>684</v>
+      </c>
+      <c r="E271" t="s">
         <v>660</v>
       </c>
-      <c r="D271" t="s">
-        <v>686</v>
-      </c>
-      <c r="E271" t="s">
-        <v>662</v>
-      </c>
       <c r="F271" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G271" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="H271" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="I271" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="J271" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="K271" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="L271">
         <v>0</v>
@@ -46454,31 +46456,31 @@
         <v>0</v>
       </c>
       <c r="C272" t="s">
+        <v>658</v>
+      </c>
+      <c r="D272" t="s">
+        <v>686</v>
+      </c>
+      <c r="E272" t="s">
         <v>660</v>
       </c>
-      <c r="D272" t="s">
+      <c r="F272" t="s">
+        <v>661</v>
+      </c>
+      <c r="G272" t="s">
+        <v>681</v>
+      </c>
+      <c r="H272" t="s">
+        <v>687</v>
+      </c>
+      <c r="I272" t="s">
+        <v>682</v>
+      </c>
+      <c r="J272" t="s">
         <v>688</v>
       </c>
-      <c r="E272" t="s">
-        <v>662</v>
-      </c>
-      <c r="F272" t="s">
-        <v>663</v>
-      </c>
-      <c r="G272" t="s">
-        <v>683</v>
-      </c>
-      <c r="H272" t="s">
+      <c r="K272" t="s">
         <v>689</v>
-      </c>
-      <c r="I272" t="s">
-        <v>684</v>
-      </c>
-      <c r="J272" t="s">
-        <v>690</v>
-      </c>
-      <c r="K272" t="s">
-        <v>691</v>
       </c>
       <c r="L272">
         <v>0</v>
@@ -46511,31 +46513,31 @@
         <v>0</v>
       </c>
       <c r="C273" t="s">
+        <v>658</v>
+      </c>
+      <c r="D273" t="s">
+        <v>690</v>
+      </c>
+      <c r="E273" t="s">
         <v>660</v>
       </c>
-      <c r="D273" t="s">
+      <c r="F273" t="s">
+        <v>661</v>
+      </c>
+      <c r="G273" t="s">
+        <v>687</v>
+      </c>
+      <c r="H273" t="s">
+        <v>691</v>
+      </c>
+      <c r="I273" t="s">
+        <v>688</v>
+      </c>
+      <c r="J273" t="s">
         <v>692</v>
       </c>
-      <c r="E273" t="s">
-        <v>662</v>
-      </c>
-      <c r="F273" t="s">
-        <v>663</v>
-      </c>
-      <c r="G273" t="s">
-        <v>689</v>
-      </c>
-      <c r="H273" t="s">
+      <c r="K273" t="s">
         <v>693</v>
-      </c>
-      <c r="I273" t="s">
-        <v>690</v>
-      </c>
-      <c r="J273" t="s">
-        <v>694</v>
-      </c>
-      <c r="K273" t="s">
-        <v>695</v>
       </c>
       <c r="L273">
         <v>0</v>
@@ -46568,31 +46570,31 @@
         <v>0</v>
       </c>
       <c r="C274" t="s">
+        <v>658</v>
+      </c>
+      <c r="D274" t="s">
+        <v>694</v>
+      </c>
+      <c r="E274" t="s">
         <v>660</v>
       </c>
-      <c r="D274" t="s">
+      <c r="F274" t="s">
+        <v>661</v>
+      </c>
+      <c r="G274" t="s">
+        <v>691</v>
+      </c>
+      <c r="H274" t="s">
+        <v>695</v>
+      </c>
+      <c r="I274" t="s">
+        <v>692</v>
+      </c>
+      <c r="J274" t="s">
         <v>696</v>
       </c>
-      <c r="E274" t="s">
-        <v>662</v>
-      </c>
-      <c r="F274" t="s">
-        <v>663</v>
-      </c>
-      <c r="G274" t="s">
-        <v>693</v>
-      </c>
-      <c r="H274" t="s">
+      <c r="K274" t="s">
         <v>697</v>
-      </c>
-      <c r="I274" t="s">
-        <v>694</v>
-      </c>
-      <c r="J274" t="s">
-        <v>698</v>
-      </c>
-      <c r="K274" t="s">
-        <v>699</v>
       </c>
       <c r="L274">
         <v>0</v>
@@ -46625,31 +46627,31 @@
         <v>0</v>
       </c>
       <c r="C275" t="s">
+        <v>658</v>
+      </c>
+      <c r="D275" t="s">
+        <v>698</v>
+      </c>
+      <c r="E275" t="s">
         <v>660</v>
       </c>
-      <c r="D275" t="s">
+      <c r="F275" t="s">
+        <v>661</v>
+      </c>
+      <c r="G275" t="s">
+        <v>695</v>
+      </c>
+      <c r="H275" t="s">
+        <v>699</v>
+      </c>
+      <c r="I275" t="s">
+        <v>696</v>
+      </c>
+      <c r="J275" t="s">
         <v>700</v>
       </c>
-      <c r="E275" t="s">
-        <v>662</v>
-      </c>
-      <c r="F275" t="s">
-        <v>663</v>
-      </c>
-      <c r="G275" t="s">
-        <v>697</v>
-      </c>
-      <c r="H275" t="s">
+      <c r="K275" t="s">
         <v>701</v>
-      </c>
-      <c r="I275" t="s">
-        <v>698</v>
-      </c>
-      <c r="J275" t="s">
-        <v>702</v>
-      </c>
-      <c r="K275" t="s">
-        <v>703</v>
       </c>
       <c r="L275">
         <v>0</v>
@@ -46682,31 +46684,31 @@
         <v>0</v>
       </c>
       <c r="C276" t="s">
+        <v>658</v>
+      </c>
+      <c r="D276" t="s">
+        <v>702</v>
+      </c>
+      <c r="E276" t="s">
         <v>660</v>
       </c>
-      <c r="D276" t="s">
+      <c r="F276" t="s">
+        <v>661</v>
+      </c>
+      <c r="G276" t="s">
+        <v>699</v>
+      </c>
+      <c r="H276" t="s">
+        <v>703</v>
+      </c>
+      <c r="I276" t="s">
+        <v>700</v>
+      </c>
+      <c r="J276" t="s">
         <v>704</v>
       </c>
-      <c r="E276" t="s">
-        <v>662</v>
-      </c>
-      <c r="F276" t="s">
-        <v>663</v>
-      </c>
-      <c r="G276" t="s">
-        <v>701</v>
-      </c>
-      <c r="H276" t="s">
+      <c r="K276" t="s">
         <v>705</v>
-      </c>
-      <c r="I276" t="s">
-        <v>702</v>
-      </c>
-      <c r="J276" t="s">
-        <v>706</v>
-      </c>
-      <c r="K276" t="s">
-        <v>707</v>
       </c>
       <c r="L276">
         <v>0</v>
@@ -46739,31 +46741,31 @@
         <v>0</v>
       </c>
       <c r="C277" t="s">
+        <v>658</v>
+      </c>
+      <c r="D277" t="s">
+        <v>706</v>
+      </c>
+      <c r="E277" t="s">
         <v>660</v>
       </c>
-      <c r="D277" t="s">
+      <c r="F277" t="s">
+        <v>661</v>
+      </c>
+      <c r="G277" t="s">
+        <v>703</v>
+      </c>
+      <c r="H277" t="s">
+        <v>707</v>
+      </c>
+      <c r="I277" t="s">
+        <v>704</v>
+      </c>
+      <c r="J277" t="s">
         <v>708</v>
       </c>
-      <c r="E277" t="s">
-        <v>662</v>
-      </c>
-      <c r="F277" t="s">
-        <v>663</v>
-      </c>
-      <c r="G277" t="s">
-        <v>705</v>
-      </c>
-      <c r="H277" t="s">
+      <c r="K277" t="s">
         <v>709</v>
-      </c>
-      <c r="I277" t="s">
-        <v>706</v>
-      </c>
-      <c r="J277" t="s">
-        <v>710</v>
-      </c>
-      <c r="K277" t="s">
-        <v>711</v>
       </c>
       <c r="L277">
         <v>0</v>
@@ -46796,31 +46798,31 @@
         <v>0</v>
       </c>
       <c r="C278" t="s">
+        <v>658</v>
+      </c>
+      <c r="D278" t="s">
+        <v>710</v>
+      </c>
+      <c r="E278" t="s">
         <v>660</v>
       </c>
-      <c r="D278" t="s">
+      <c r="F278" t="s">
+        <v>661</v>
+      </c>
+      <c r="G278" t="s">
+        <v>707</v>
+      </c>
+      <c r="H278" t="s">
+        <v>711</v>
+      </c>
+      <c r="I278" t="s">
+        <v>708</v>
+      </c>
+      <c r="J278" t="s">
         <v>712</v>
       </c>
-      <c r="E278" t="s">
-        <v>662</v>
-      </c>
-      <c r="F278" t="s">
-        <v>663</v>
-      </c>
-      <c r="G278" t="s">
-        <v>709</v>
-      </c>
-      <c r="H278" t="s">
+      <c r="K278" t="s">
         <v>713</v>
-      </c>
-      <c r="I278" t="s">
-        <v>710</v>
-      </c>
-      <c r="J278" t="s">
-        <v>714</v>
-      </c>
-      <c r="K278" t="s">
-        <v>715</v>
       </c>
       <c r="L278">
         <v>0</v>
@@ -46853,31 +46855,31 @@
         <v>0</v>
       </c>
       <c r="C279" t="s">
+        <v>658</v>
+      </c>
+      <c r="D279" t="s">
+        <v>714</v>
+      </c>
+      <c r="E279" t="s">
         <v>660</v>
       </c>
-      <c r="D279" t="s">
+      <c r="F279" t="s">
+        <v>661</v>
+      </c>
+      <c r="G279" t="s">
+        <v>711</v>
+      </c>
+      <c r="H279" t="s">
+        <v>715</v>
+      </c>
+      <c r="I279" t="s">
+        <v>712</v>
+      </c>
+      <c r="J279" t="s">
         <v>716</v>
       </c>
-      <c r="E279" t="s">
-        <v>662</v>
-      </c>
-      <c r="F279" t="s">
-        <v>663</v>
-      </c>
-      <c r="G279" t="s">
-        <v>713</v>
-      </c>
-      <c r="H279" t="s">
+      <c r="K279" t="s">
         <v>717</v>
-      </c>
-      <c r="I279" t="s">
-        <v>714</v>
-      </c>
-      <c r="J279" t="s">
-        <v>718</v>
-      </c>
-      <c r="K279" t="s">
-        <v>719</v>
       </c>
       <c r="L279">
         <v>0</v>
@@ -46910,31 +46912,31 @@
         <v>0</v>
       </c>
       <c r="C280" t="s">
+        <v>658</v>
+      </c>
+      <c r="D280" t="s">
+        <v>718</v>
+      </c>
+      <c r="E280" t="s">
         <v>660</v>
       </c>
-      <c r="D280" t="s">
+      <c r="F280" t="s">
+        <v>661</v>
+      </c>
+      <c r="G280" t="s">
+        <v>715</v>
+      </c>
+      <c r="H280" t="s">
+        <v>719</v>
+      </c>
+      <c r="I280" t="s">
+        <v>716</v>
+      </c>
+      <c r="J280" t="s">
         <v>720</v>
       </c>
-      <c r="E280" t="s">
-        <v>662</v>
-      </c>
-      <c r="F280" t="s">
-        <v>663</v>
-      </c>
-      <c r="G280" t="s">
-        <v>717</v>
-      </c>
-      <c r="H280" t="s">
+      <c r="K280" t="s">
         <v>721</v>
-      </c>
-      <c r="I280" t="s">
-        <v>718</v>
-      </c>
-      <c r="J280" t="s">
-        <v>722</v>
-      </c>
-      <c r="K280" t="s">
-        <v>723</v>
       </c>
       <c r="L280">
         <v>0</v>
@@ -46967,34 +46969,34 @@
         <v>0</v>
       </c>
       <c r="C281" t="s">
+        <v>658</v>
+      </c>
+      <c r="D281" t="s">
+        <v>722</v>
+      </c>
+      <c r="E281" t="s">
         <v>660</v>
       </c>
-      <c r="D281" t="s">
+      <c r="F281" t="s">
+        <v>661</v>
+      </c>
+      <c r="G281" t="s">
+        <v>705</v>
+      </c>
+      <c r="H281" t="s">
+        <v>723</v>
+      </c>
+      <c r="I281" t="s">
         <v>724</v>
       </c>
-      <c r="E281" t="s">
-        <v>662</v>
-      </c>
-      <c r="F281" t="s">
-        <v>663</v>
-      </c>
-      <c r="G281" t="s">
-        <v>707</v>
-      </c>
-      <c r="H281" t="s">
+      <c r="J281" t="s">
+        <v>720</v>
+      </c>
+      <c r="K281" t="s">
         <v>725</v>
       </c>
-      <c r="I281" t="s">
+      <c r="L281" t="s">
         <v>726</v>
-      </c>
-      <c r="J281" t="s">
-        <v>722</v>
-      </c>
-      <c r="K281" t="s">
-        <v>727</v>
-      </c>
-      <c r="L281" t="s">
-        <v>728</v>
       </c>
       <c r="M281">
         <v>0</v>
@@ -47024,34 +47026,34 @@
         <v>0</v>
       </c>
       <c r="C282" t="s">
+        <v>658</v>
+      </c>
+      <c r="D282" t="s">
+        <v>727</v>
+      </c>
+      <c r="E282" t="s">
         <v>660</v>
       </c>
-      <c r="D282" t="s">
-        <v>729</v>
-      </c>
-      <c r="E282" t="s">
-        <v>662</v>
-      </c>
       <c r="F282" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G282" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="H282" t="s">
+        <v>723</v>
+      </c>
+      <c r="I282" t="s">
+        <v>724</v>
+      </c>
+      <c r="J282" t="s">
+        <v>720</v>
+      </c>
+      <c r="K282" t="s">
         <v>725</v>
       </c>
-      <c r="I282" t="s">
+      <c r="L282" t="s">
         <v>726</v>
-      </c>
-      <c r="J282" t="s">
-        <v>722</v>
-      </c>
-      <c r="K282" t="s">
-        <v>727</v>
-      </c>
-      <c r="L282" t="s">
-        <v>728</v>
       </c>
       <c r="M282">
         <v>0</v>
@@ -47081,34 +47083,34 @@
         <v>0</v>
       </c>
       <c r="C283" t="s">
+        <v>658</v>
+      </c>
+      <c r="D283" t="s">
+        <v>728</v>
+      </c>
+      <c r="E283" t="s">
         <v>660</v>
       </c>
-      <c r="D283" t="s">
-        <v>730</v>
-      </c>
-      <c r="E283" t="s">
-        <v>662</v>
-      </c>
       <c r="F283" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G283" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="H283" t="s">
+        <v>723</v>
+      </c>
+      <c r="I283" t="s">
+        <v>724</v>
+      </c>
+      <c r="J283" t="s">
+        <v>720</v>
+      </c>
+      <c r="K283" t="s">
         <v>725</v>
       </c>
-      <c r="I283" t="s">
+      <c r="L283" t="s">
         <v>726</v>
-      </c>
-      <c r="J283" t="s">
-        <v>722</v>
-      </c>
-      <c r="K283" t="s">
-        <v>727</v>
-      </c>
-      <c r="L283" t="s">
-        <v>728</v>
       </c>
       <c r="M283">
         <v>0</v>
@@ -47138,16 +47140,16 @@
         <v>0</v>
       </c>
       <c r="C284" t="s">
+        <v>794</v>
+      </c>
+      <c r="D284" t="s">
+        <v>795</v>
+      </c>
+      <c r="E284" t="s">
         <v>796</v>
       </c>
-      <c r="D284" t="s">
+      <c r="F284" t="s">
         <v>797</v>
-      </c>
-      <c r="E284" t="s">
-        <v>798</v>
-      </c>
-      <c r="F284" t="s">
-        <v>799</v>
       </c>
       <c r="G284">
         <v>0</v>
@@ -47195,16 +47197,16 @@
         <v>0</v>
       </c>
       <c r="C285" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="D285" t="s">
+        <v>798</v>
+      </c>
+      <c r="E285" t="s">
+        <v>799</v>
+      </c>
+      <c r="F285" t="s">
         <v>800</v>
-      </c>
-      <c r="E285" t="s">
-        <v>801</v>
-      </c>
-      <c r="F285" t="s">
-        <v>802</v>
       </c>
       <c r="G285">
         <v>0.1</v>
@@ -47252,16 +47254,16 @@
         <v>0</v>
       </c>
       <c r="C286" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="D286" t="s">
+        <v>801</v>
+      </c>
+      <c r="E286" t="s">
+        <v>802</v>
+      </c>
+      <c r="F286" t="s">
         <v>803</v>
-      </c>
-      <c r="E286" t="s">
-        <v>804</v>
-      </c>
-      <c r="F286" t="s">
-        <v>805</v>
       </c>
       <c r="G286">
         <v>0</v>
@@ -47309,16 +47311,16 @@
         <v>0</v>
       </c>
       <c r="C287" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="D287" t="s">
+        <v>804</v>
+      </c>
+      <c r="E287" t="s">
+        <v>805</v>
+      </c>
+      <c r="F287" t="s">
         <v>806</v>
-      </c>
-      <c r="E287" t="s">
-        <v>807</v>
-      </c>
-      <c r="F287" t="s">
-        <v>808</v>
       </c>
       <c r="G287">
         <v>0</v>
@@ -47366,16 +47368,16 @@
         <v>0</v>
       </c>
       <c r="C288" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="D288" t="s">
+        <v>807</v>
+      </c>
+      <c r="E288" t="s">
+        <v>808</v>
+      </c>
+      <c r="F288" t="s">
         <v>809</v>
-      </c>
-      <c r="E288" t="s">
-        <v>810</v>
-      </c>
-      <c r="F288" t="s">
-        <v>811</v>
       </c>
       <c r="G288">
         <v>0.2</v>
@@ -47423,16 +47425,16 @@
         <v>0</v>
       </c>
       <c r="C289" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="E289" s="3" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="F289" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="G289">
         <v>0.5</v>
@@ -47480,16 +47482,16 @@
         <v>0</v>
       </c>
       <c r="C290" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="D290" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E290" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="F290" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="G290">
         <v>1000</v>
@@ -47537,16 +47539,16 @@
         <v>0</v>
       </c>
       <c r="C291" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="D291" t="s">
+        <v>813</v>
+      </c>
+      <c r="E291" t="s">
+        <v>814</v>
+      </c>
+      <c r="F291" t="s">
         <v>815</v>
-      </c>
-      <c r="E291" t="s">
-        <v>816</v>
-      </c>
-      <c r="F291" t="s">
-        <v>817</v>
       </c>
       <c r="G291">
         <v>0</v>
@@ -47594,16 +47596,16 @@
         <v>0</v>
       </c>
       <c r="C292" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="D292" t="s">
+        <v>816</v>
+      </c>
+      <c r="E292" t="s">
+        <v>817</v>
+      </c>
+      <c r="F292" t="s">
         <v>818</v>
-      </c>
-      <c r="E292" t="s">
-        <v>819</v>
-      </c>
-      <c r="F292" t="s">
-        <v>820</v>
       </c>
       <c r="G292">
         <v>30</v>
@@ -47651,16 +47653,16 @@
         <v>0</v>
       </c>
       <c r="C293" t="s">
+        <v>819</v>
+      </c>
+      <c r="D293" t="s">
+        <v>820</v>
+      </c>
+      <c r="E293" t="s">
         <v>821</v>
       </c>
-      <c r="D293" t="s">
+      <c r="F293" t="s">
         <v>822</v>
-      </c>
-      <c r="E293" t="s">
-        <v>823</v>
-      </c>
-      <c r="F293" t="s">
-        <v>824</v>
       </c>
       <c r="G293">
         <v>0.75</v>
@@ -47708,13 +47710,13 @@
         <v>0</v>
       </c>
       <c r="C294" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D294" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="E294" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="F294">
         <v>0</v>
@@ -47765,16 +47767,16 @@
         <v>0</v>
       </c>
       <c r="C295" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D295" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="E295" t="s">
         <v>592</v>
       </c>
       <c r="F295" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="G295">
         <v>45</v>
@@ -47822,16 +47824,16 @@
         <v>0</v>
       </c>
       <c r="C296" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D296" t="s">
+        <v>827</v>
+      </c>
+      <c r="E296" t="s">
+        <v>828</v>
+      </c>
+      <c r="F296" t="s">
         <v>829</v>
-      </c>
-      <c r="E296" t="s">
-        <v>830</v>
-      </c>
-      <c r="F296" t="s">
-        <v>831</v>
       </c>
       <c r="G296">
         <v>0</v>
@@ -47879,16 +47881,16 @@
         <v>0</v>
       </c>
       <c r="C297" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D297" t="s">
+        <v>830</v>
+      </c>
+      <c r="E297" t="s">
+        <v>831</v>
+      </c>
+      <c r="F297" t="s">
         <v>832</v>
-      </c>
-      <c r="E297" t="s">
-        <v>833</v>
-      </c>
-      <c r="F297" t="s">
-        <v>834</v>
       </c>
       <c r="G297">
         <v>0.1</v>
@@ -47936,16 +47938,16 @@
         <v>0</v>
       </c>
       <c r="C298" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D298" t="s">
+        <v>918</v>
+      </c>
+      <c r="E298" t="s">
+        <v>919</v>
+      </c>
+      <c r="F298" t="s">
         <v>920</v>
-      </c>
-      <c r="E298" t="s">
-        <v>921</v>
-      </c>
-      <c r="F298" t="s">
-        <v>922</v>
       </c>
       <c r="G298">
         <v>50000</v>
@@ -47993,16 +47995,16 @@
         <v>0</v>
       </c>
       <c r="C299" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D299" t="s">
+        <v>921</v>
+      </c>
+      <c r="E299" t="s">
+        <v>922</v>
+      </c>
+      <c r="F299" t="s">
         <v>923</v>
-      </c>
-      <c r="E299" t="s">
-        <v>924</v>
-      </c>
-      <c r="F299" t="s">
-        <v>925</v>
       </c>
       <c r="G299">
         <v>10</v>
@@ -48050,16 +48052,16 @@
         <v>0</v>
       </c>
       <c r="C300" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D300" t="s">
+        <v>924</v>
+      </c>
+      <c r="E300" t="s">
+        <v>925</v>
+      </c>
+      <c r="F300" t="s">
         <v>926</v>
-      </c>
-      <c r="E300" t="s">
-        <v>927</v>
-      </c>
-      <c r="F300" t="s">
-        <v>928</v>
       </c>
       <c r="G300">
         <v>75</v>
@@ -48107,16 +48109,16 @@
         <v>0</v>
       </c>
       <c r="C301" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D301" t="s">
+        <v>927</v>
+      </c>
+      <c r="E301" t="s">
+        <v>928</v>
+      </c>
+      <c r="F301" t="s">
         <v>929</v>
-      </c>
-      <c r="E301" t="s">
-        <v>930</v>
-      </c>
-      <c r="F301" t="s">
-        <v>931</v>
       </c>
       <c r="G301">
         <v>25</v>
@@ -48164,16 +48166,16 @@
         <v>0</v>
       </c>
       <c r="C302" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D302" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="E302" t="s">
         <v>592</v>
       </c>
       <c r="F302" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
       <c r="G302">
         <v>5</v>
@@ -48221,16 +48223,16 @@
         <v>0</v>
       </c>
       <c r="C303" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="D303" t="s">
+        <v>932</v>
+      </c>
+      <c r="E303" t="s">
+        <v>933</v>
+      </c>
+      <c r="F303" t="s">
         <v>934</v>
-      </c>
-      <c r="E303" t="s">
-        <v>935</v>
-      </c>
-      <c r="F303" t="s">
-        <v>936</v>
       </c>
       <c r="G303">
         <v>0.6</v>
@@ -48278,16 +48280,16 @@
         <v>0</v>
       </c>
       <c r="C304" t="s">
+        <v>856</v>
+      </c>
+      <c r="D304" t="s">
+        <v>857</v>
+      </c>
+      <c r="E304" t="s">
         <v>858</v>
       </c>
-      <c r="D304" t="s">
+      <c r="F304" t="s">
         <v>859</v>
-      </c>
-      <c r="E304" t="s">
-        <v>860</v>
-      </c>
-      <c r="F304" t="s">
-        <v>861</v>
       </c>
       <c r="G304">
         <v>25</v>
@@ -48296,7 +48298,7 @@
         <v>25</v>
       </c>
       <c r="I304" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="J304">
         <v>0</v>
@@ -48335,16 +48337,16 @@
         <v>0</v>
       </c>
       <c r="C305" t="s">
+        <v>856</v>
+      </c>
+      <c r="D305" t="s">
+        <v>861</v>
+      </c>
+      <c r="E305" t="s">
         <v>858</v>
       </c>
-      <c r="D305" t="s">
-        <v>863</v>
-      </c>
-      <c r="E305" t="s">
-        <v>860</v>
-      </c>
       <c r="F305" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="G305">
         <v>20</v>
@@ -48353,7 +48355,7 @@
         <v>20</v>
       </c>
       <c r="I305" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="J305">
         <v>0</v>
@@ -48392,16 +48394,16 @@
         <v>0</v>
       </c>
       <c r="C306" t="s">
+        <v>856</v>
+      </c>
+      <c r="D306" t="s">
+        <v>863</v>
+      </c>
+      <c r="E306" t="s">
         <v>858</v>
       </c>
-      <c r="D306" t="s">
-        <v>865</v>
-      </c>
-      <c r="E306" t="s">
-        <v>860</v>
-      </c>
       <c r="F306" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="G306">
         <v>3</v>
@@ -48410,7 +48412,7 @@
         <v>1.5</v>
       </c>
       <c r="I306" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="J306">
         <v>0</v>
@@ -48449,16 +48451,16 @@
         <v>0</v>
       </c>
       <c r="C307" t="s">
+        <v>856</v>
+      </c>
+      <c r="D307" t="s">
+        <v>865</v>
+      </c>
+      <c r="E307" t="s">
         <v>858</v>
       </c>
-      <c r="D307" t="s">
-        <v>867</v>
-      </c>
-      <c r="E307" t="s">
-        <v>860</v>
-      </c>
       <c r="F307" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="G307">
         <v>20</v>
@@ -48467,7 +48469,7 @@
         <v>20</v>
       </c>
       <c r="I307" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="J307">
         <v>0</v>
@@ -48506,16 +48508,16 @@
         <v>0</v>
       </c>
       <c r="C308" t="s">
+        <v>856</v>
+      </c>
+      <c r="D308" t="s">
+        <v>867</v>
+      </c>
+      <c r="E308" t="s">
         <v>858</v>
       </c>
-      <c r="D308" t="s">
-        <v>869</v>
-      </c>
-      <c r="E308" t="s">
-        <v>860</v>
-      </c>
       <c r="F308" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="G308">
         <v>3</v>
@@ -48524,7 +48526,7 @@
         <v>1.5</v>
       </c>
       <c r="I308" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="J308">
         <v>0</v>
@@ -48563,16 +48565,16 @@
         <v>0</v>
       </c>
       <c r="C309" t="s">
+        <v>856</v>
+      </c>
+      <c r="D309" t="s">
+        <v>869</v>
+      </c>
+      <c r="E309" t="s">
         <v>858</v>
       </c>
-      <c r="D309" t="s">
-        <v>871</v>
-      </c>
-      <c r="E309" t="s">
-        <v>860</v>
-      </c>
       <c r="F309" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G309">
         <v>3</v>
@@ -48581,7 +48583,7 @@
         <v>1.5</v>
       </c>
       <c r="I309" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="J309">
         <v>0</v>
@@ -48620,16 +48622,16 @@
         <v>0</v>
       </c>
       <c r="C310" t="s">
+        <v>856</v>
+      </c>
+      <c r="D310" t="s">
+        <v>871</v>
+      </c>
+      <c r="E310" t="s">
         <v>858</v>
       </c>
-      <c r="D310" t="s">
-        <v>873</v>
-      </c>
-      <c r="E310" t="s">
-        <v>860</v>
-      </c>
       <c r="F310" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="G310">
         <v>3</v>
@@ -48638,7 +48640,7 @@
         <v>1.5</v>
       </c>
       <c r="I310" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="J310">
         <v>0</v>
@@ -48677,16 +48679,16 @@
         <v>0</v>
       </c>
       <c r="C311" t="s">
+        <v>856</v>
+      </c>
+      <c r="D311" t="s">
+        <v>873</v>
+      </c>
+      <c r="E311" t="s">
         <v>858</v>
       </c>
-      <c r="D311" t="s">
-        <v>875</v>
-      </c>
-      <c r="E311" t="s">
-        <v>860</v>
-      </c>
       <c r="F311" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="G311">
         <v>25</v>
@@ -48695,7 +48697,7 @@
         <v>25</v>
       </c>
       <c r="I311" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="J311">
         <v>0</v>
@@ -48734,16 +48736,16 @@
         <v>0</v>
       </c>
       <c r="C312" t="s">
+        <v>856</v>
+      </c>
+      <c r="D312" t="s">
+        <v>875</v>
+      </c>
+      <c r="E312" t="s">
         <v>858</v>
       </c>
-      <c r="D312" t="s">
-        <v>877</v>
-      </c>
-      <c r="E312" t="s">
-        <v>860</v>
-      </c>
       <c r="F312" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="G312">
         <v>5</v>
@@ -48752,7 +48754,7 @@
         <v>2.5</v>
       </c>
       <c r="I312" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="J312">
         <v>0</v>
@@ -48791,19 +48793,19 @@
         <v>0</v>
       </c>
       <c r="C313" t="s">
+        <v>877</v>
+      </c>
+      <c r="D313" t="s">
+        <v>878</v>
+      </c>
+      <c r="E313" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="F313" t="s">
         <v>879</v>
       </c>
-      <c r="D313" t="s">
-        <v>880</v>
-      </c>
-      <c r="E313" s="3" t="s">
-        <v>985</v>
-      </c>
-      <c r="F313" t="s">
-        <v>881</v>
-      </c>
       <c r="G313" s="3" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="H313">
         <v>3</v>
@@ -48848,16 +48850,16 @@
         <v>0</v>
       </c>
       <c r="C314" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D314" t="s">
+        <v>880</v>
+      </c>
+      <c r="E314" t="s">
+        <v>881</v>
+      </c>
+      <c r="F314" t="s">
         <v>882</v>
-      </c>
-      <c r="E314" t="s">
-        <v>883</v>
-      </c>
-      <c r="F314" t="s">
-        <v>884</v>
       </c>
       <c r="G314">
         <v>5</v>
@@ -48905,16 +48907,16 @@
         <v>0</v>
       </c>
       <c r="C315" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D315" t="s">
+        <v>883</v>
+      </c>
+      <c r="E315" t="s">
+        <v>884</v>
+      </c>
+      <c r="F315" t="s">
         <v>885</v>
-      </c>
-      <c r="E315" t="s">
-        <v>886</v>
-      </c>
-      <c r="F315" t="s">
-        <v>887</v>
       </c>
       <c r="G315">
         <v>10</v>
@@ -48962,16 +48964,16 @@
         <v>0</v>
       </c>
       <c r="C316" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D316" t="s">
+        <v>886</v>
+      </c>
+      <c r="E316" t="s">
+        <v>887</v>
+      </c>
+      <c r="F316" t="s">
         <v>888</v>
-      </c>
-      <c r="E316" t="s">
-        <v>889</v>
-      </c>
-      <c r="F316" t="s">
-        <v>890</v>
       </c>
       <c r="G316">
         <v>10</v>
@@ -49019,16 +49021,16 @@
         <v>0</v>
       </c>
       <c r="C317" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D317" t="s">
+        <v>889</v>
+      </c>
+      <c r="E317" t="s">
+        <v>890</v>
+      </c>
+      <c r="F317" t="s">
         <v>891</v>
-      </c>
-      <c r="E317" t="s">
-        <v>892</v>
-      </c>
-      <c r="F317" t="s">
-        <v>893</v>
       </c>
       <c r="G317">
         <v>2</v>
@@ -49076,16 +49078,16 @@
         <v>0</v>
       </c>
       <c r="C318" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D318" t="s">
+        <v>892</v>
+      </c>
+      <c r="E318" t="s">
+        <v>893</v>
+      </c>
+      <c r="F318" t="s">
         <v>894</v>
-      </c>
-      <c r="E318" t="s">
-        <v>895</v>
-      </c>
-      <c r="F318" t="s">
-        <v>896</v>
       </c>
       <c r="G318">
         <v>5</v>
@@ -49133,16 +49135,16 @@
         <v>0</v>
       </c>
       <c r="C319" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D319" t="s">
+        <v>895</v>
+      </c>
+      <c r="E319" t="s">
+        <v>896</v>
+      </c>
+      <c r="F319" t="s">
         <v>897</v>
-      </c>
-      <c r="E319" t="s">
-        <v>898</v>
-      </c>
-      <c r="F319" t="s">
-        <v>899</v>
       </c>
       <c r="G319">
         <v>10</v>
@@ -49190,16 +49192,16 @@
         <v>0</v>
       </c>
       <c r="C320" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D320" t="s">
+        <v>898</v>
+      </c>
+      <c r="E320" t="s">
+        <v>899</v>
+      </c>
+      <c r="F320" t="s">
         <v>900</v>
-      </c>
-      <c r="E320" t="s">
-        <v>901</v>
-      </c>
-      <c r="F320" t="s">
-        <v>902</v>
       </c>
       <c r="G320">
         <v>20000</v>
@@ -49247,16 +49249,16 @@
         <v>0</v>
       </c>
       <c r="C321" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D321" t="s">
+        <v>984</v>
+      </c>
+      <c r="E321" t="s">
+        <v>985</v>
+      </c>
+      <c r="F321" s="5" t="s">
         <v>986</v>
-      </c>
-      <c r="E321" t="s">
-        <v>987</v>
-      </c>
-      <c r="F321" s="5" t="s">
-        <v>988</v>
       </c>
       <c r="G321">
         <v>0.35</v>
@@ -49304,16 +49306,16 @@
         <v>0</v>
       </c>
       <c r="C322" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D322" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="E322" t="s">
         <v>39</v>
       </c>
       <c r="F322" s="7" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G322">
         <v>1</v>
@@ -49361,16 +49363,16 @@
         <v>0</v>
       </c>
       <c r="C323" t="s">
+        <v>846</v>
+      </c>
+      <c r="D323" t="s">
         <v>848</v>
-      </c>
-      <c r="D323" t="s">
-        <v>850</v>
       </c>
       <c r="E323" t="s">
         <v>39</v>
       </c>
       <c r="F323" s="7" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G323">
         <v>1.35</v>
@@ -49418,16 +49420,16 @@
         <v>0</v>
       </c>
       <c r="C324" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D324" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="E324" t="s">
         <v>39</v>
       </c>
       <c r="F324" s="7" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G324">
         <v>1.75</v>
@@ -49475,16 +49477,16 @@
         <v>0</v>
       </c>
       <c r="C325" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D325" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="E325" t="s">
         <v>39</v>
       </c>
       <c r="F325" s="7" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G325">
         <v>2.2999999999999998</v>
@@ -49532,16 +49534,16 @@
         <v>0</v>
       </c>
       <c r="C326" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D326" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="E326" t="s">
         <v>39</v>
       </c>
       <c r="F326" s="7" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G326">
         <v>3</v>
@@ -49589,16 +49591,16 @@
         <v>0</v>
       </c>
       <c r="C327" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D327" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="E327" t="s">
         <v>39</v>
       </c>
       <c r="F327" s="7" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G327">
         <v>4</v>
@@ -49646,16 +49648,16 @@
         <v>0</v>
       </c>
       <c r="C328" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D328" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="E328" t="s">
         <v>39</v>
       </c>
       <c r="F328" s="7" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G328">
         <v>5.2</v>
@@ -49703,16 +49705,16 @@
         <v>0</v>
       </c>
       <c r="C329" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D329" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="E329" t="s">
         <v>39</v>
       </c>
       <c r="F329" s="7" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G329">
         <v>6.8</v>
@@ -49760,16 +49762,16 @@
         <v>0</v>
       </c>
       <c r="C330" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D330" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="E330" t="s">
         <v>39</v>
       </c>
       <c r="F330" s="7" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="G330">
         <v>10.199999999999999</v>
@@ -49817,16 +49819,16 @@
         <v>0</v>
       </c>
       <c r="C331" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D331" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="E331" t="s">
         <v>39</v>
       </c>
       <c r="F331" s="7" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="G331">
         <v>15.3</v>
@@ -49874,16 +49876,16 @@
         <v>0</v>
       </c>
       <c r="C332" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D332" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="E332" t="s">
         <v>39</v>
       </c>
       <c r="F332" s="7" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="G332">
         <v>22.95</v>
@@ -49931,22 +49933,22 @@
         <v>0</v>
       </c>
       <c r="C333" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D333" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E333" t="s">
         <v>1063</v>
       </c>
-      <c r="D333" t="s">
+      <c r="F333" t="s">
         <v>1064</v>
-      </c>
-      <c r="E333" t="s">
-        <v>1065</v>
-      </c>
-      <c r="F333" t="s">
-        <v>1066</v>
       </c>
       <c r="G333">
         <v>200</v>
       </c>
       <c r="H333" s="3" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="I333">
         <v>0</v>
@@ -49988,28 +49990,28 @@
         <v>0</v>
       </c>
       <c r="C334" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D334" s="2" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E334" t="s">
         <v>1072</v>
       </c>
-      <c r="D334" s="2" t="s">
+      <c r="F334" t="s">
         <v>1073</v>
       </c>
-      <c r="E334" t="s">
+      <c r="G334" s="7" t="s">
         <v>1074</v>
       </c>
-      <c r="F334" t="s">
+      <c r="H334" s="7" t="s">
         <v>1075</v>
       </c>
-      <c r="G334" s="7" t="s">
+      <c r="I334" s="7" t="s">
         <v>1076</v>
       </c>
-      <c r="H334" s="7" t="s">
+      <c r="J334" s="7" t="s">
         <v>1077</v>
-      </c>
-      <c r="I334" s="7" t="s">
-        <v>1078</v>
-      </c>
-      <c r="J334" s="7" t="s">
-        <v>1079</v>
       </c>
       <c r="K334">
         <v>0</v>
@@ -50045,22 +50047,22 @@
         <v>0</v>
       </c>
       <c r="C335" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D335" s="2" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E335" t="s">
         <v>1072</v>
       </c>
-      <c r="D335" s="2" t="s">
+      <c r="F335" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G335" s="7" t="s">
+        <v>1079</v>
+      </c>
+      <c r="H335" s="7" t="s">
         <v>1080</v>
-      </c>
-      <c r="E335" t="s">
-        <v>1074</v>
-      </c>
-      <c r="F335" t="s">
-        <v>1075</v>
-      </c>
-      <c r="G335" s="7" t="s">
-        <v>1081</v>
-      </c>
-      <c r="H335" s="7" t="s">
-        <v>1082</v>
       </c>
       <c r="I335">
         <v>0</v>
@@ -50102,22 +50104,22 @@
         <v>0</v>
       </c>
       <c r="C336" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D336" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E336" t="s">
         <v>1072</v>
       </c>
-      <c r="D336" s="2" t="s">
+      <c r="F336" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G336" s="7" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H336" s="7" t="s">
         <v>1083</v>
-      </c>
-      <c r="E336" t="s">
-        <v>1074</v>
-      </c>
-      <c r="F336" t="s">
-        <v>1075</v>
-      </c>
-      <c r="G336" s="7" t="s">
-        <v>1084</v>
-      </c>
-      <c r="H336" s="7" t="s">
-        <v>1085</v>
       </c>
       <c r="I336">
         <v>0</v>
@@ -50159,22 +50161,22 @@
         <v>0</v>
       </c>
       <c r="C337" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D337" s="2" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E337" t="s">
         <v>1072</v>
       </c>
-      <c r="D337" s="2" t="s">
+      <c r="F337" t="s">
+        <v>1073</v>
+      </c>
+      <c r="G337" s="7" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H337" s="7" t="s">
         <v>1086</v>
-      </c>
-      <c r="E337" t="s">
-        <v>1074</v>
-      </c>
-      <c r="F337" t="s">
-        <v>1075</v>
-      </c>
-      <c r="G337" s="7" t="s">
-        <v>1087</v>
-      </c>
-      <c r="H337" s="7" t="s">
-        <v>1088</v>
       </c>
       <c r="I337">
         <v>0</v>
@@ -50216,19 +50218,19 @@
         <v>0</v>
       </c>
       <c r="C338" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D338" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E338" t="s">
         <v>1072</v>
       </c>
-      <c r="D338" s="2" t="s">
-        <v>1089</v>
-      </c>
-      <c r="E338" t="s">
-        <v>1074</v>
-      </c>
       <c r="F338" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="G338" s="7" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="H338">
         <v>0</v>
@@ -50273,34 +50275,34 @@
         <v>0</v>
       </c>
       <c r="C339" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D339" s="2" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E339" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F339" t="s">
         <v>1091</v>
       </c>
-      <c r="E339" t="s">
+      <c r="G339" s="7" t="s">
         <v>1092</v>
       </c>
-      <c r="F339" t="s">
+      <c r="H339" s="7" t="s">
         <v>1093</v>
       </c>
-      <c r="G339" s="7" t="s">
+      <c r="I339" s="7" t="s">
         <v>1094</v>
       </c>
-      <c r="H339" s="7" t="s">
+      <c r="J339" s="7" t="s">
         <v>1095</v>
       </c>
-      <c r="I339" s="7" t="s">
+      <c r="K339" s="7" t="s">
         <v>1096</v>
       </c>
-      <c r="J339" s="7" t="s">
+      <c r="L339" s="7" t="s">
         <v>1097</v>
-      </c>
-      <c r="K339" s="7" t="s">
-        <v>1098</v>
-      </c>
-      <c r="L339" s="7" t="s">
-        <v>1099</v>
       </c>
       <c r="M339">
         <v>0</v>
@@ -50330,25 +50332,25 @@
         <v>0</v>
       </c>
       <c r="C340" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D340" s="2" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E340" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F340" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G340" s="7" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H340" s="7" t="s">
         <v>1100</v>
       </c>
-      <c r="E340" t="s">
-        <v>1092</v>
-      </c>
-      <c r="F340" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G340" s="7" t="s">
+      <c r="I340" s="7" t="s">
         <v>1101</v>
-      </c>
-      <c r="H340" s="7" t="s">
-        <v>1102</v>
-      </c>
-      <c r="I340" s="7" t="s">
-        <v>1103</v>
       </c>
       <c r="J340">
         <v>0</v>
@@ -50387,25 +50389,25 @@
         <v>0</v>
       </c>
       <c r="C341" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D341" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E341" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F341" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G341" s="7" t="s">
+        <v>1103</v>
+      </c>
+      <c r="H341" s="7" t="s">
         <v>1104</v>
       </c>
-      <c r="E341" t="s">
-        <v>1092</v>
-      </c>
-      <c r="F341" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G341" s="7" t="s">
+      <c r="I341" s="7" t="s">
         <v>1105</v>
-      </c>
-      <c r="H341" s="7" t="s">
-        <v>1106</v>
-      </c>
-      <c r="I341" s="7" t="s">
-        <v>1107</v>
       </c>
       <c r="J341">
         <v>0</v>
@@ -50444,25 +50446,25 @@
         <v>0</v>
       </c>
       <c r="C342" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D342" s="2" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E342" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F342" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G342" s="7" t="s">
+        <v>1107</v>
+      </c>
+      <c r="H342" s="7" t="s">
+        <v>1104</v>
+      </c>
+      <c r="I342" s="7" t="s">
         <v>1108</v>
-      </c>
-      <c r="E342" t="s">
-        <v>1092</v>
-      </c>
-      <c r="F342" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G342" s="7" t="s">
-        <v>1109</v>
-      </c>
-      <c r="H342" s="7" t="s">
-        <v>1106</v>
-      </c>
-      <c r="I342" s="7" t="s">
-        <v>1110</v>
       </c>
       <c r="J342">
         <v>0</v>
@@ -50501,25 +50503,25 @@
         <v>0</v>
       </c>
       <c r="C343" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D343" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E343" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F343" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G343" s="7" t="s">
+        <v>1110</v>
+      </c>
+      <c r="H343" s="7" t="s">
+        <v>1104</v>
+      </c>
+      <c r="I343" s="7" t="s">
         <v>1111</v>
-      </c>
-      <c r="E343" t="s">
-        <v>1092</v>
-      </c>
-      <c r="F343" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G343" s="7" t="s">
-        <v>1112</v>
-      </c>
-      <c r="H343" s="7" t="s">
-        <v>1106</v>
-      </c>
-      <c r="I343" s="7" t="s">
-        <v>1113</v>
       </c>
       <c r="J343">
         <v>0</v>
@@ -50558,22 +50560,22 @@
         <v>0</v>
       </c>
       <c r="C344" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D344" s="2" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E344" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F344" t="s">
         <v>1114</v>
       </c>
-      <c r="E344" t="s">
+      <c r="G344" s="7" t="s">
         <v>1115</v>
       </c>
-      <c r="F344" t="s">
+      <c r="H344" s="7" t="s">
         <v>1116</v>
-      </c>
-      <c r="G344" s="7" t="s">
-        <v>1117</v>
-      </c>
-      <c r="H344" s="7" t="s">
-        <v>1118</v>
       </c>
       <c r="I344">
         <v>0</v>
@@ -50615,22 +50617,22 @@
         <v>0</v>
       </c>
       <c r="C345" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D345" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E345" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F345" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G345" s="7" t="s">
+        <v>1118</v>
+      </c>
+      <c r="H345" s="7" t="s">
         <v>1119</v>
-      </c>
-      <c r="E345" t="s">
-        <v>1115</v>
-      </c>
-      <c r="F345" t="s">
-        <v>1116</v>
-      </c>
-      <c r="G345" s="7" t="s">
-        <v>1120</v>
-      </c>
-      <c r="H345" s="7" t="s">
-        <v>1121</v>
       </c>
       <c r="I345">
         <v>0</v>
@@ -50672,19 +50674,19 @@
         <v>0</v>
       </c>
       <c r="C346" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="E346" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="F346" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="G346" s="7" t="s">
-        <v>1123</v>
+        <v>1121</v>
       </c>
       <c r="H346">
         <v>0</v>
@@ -50729,19 +50731,19 @@
         <v>0</v>
       </c>
       <c r="C347" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="E347" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="F347" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="G347" s="7" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="H347">
         <v>0</v>
@@ -50786,19 +50788,19 @@
         <v>0</v>
       </c>
       <c r="C348" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="E348" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="F348" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="G348" s="7" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="H348">
         <v>0</v>
@@ -50843,25 +50845,25 @@
         <v>0</v>
       </c>
       <c r="C349" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D349" s="2" t="s">
+        <v>1126</v>
+      </c>
+      <c r="E349" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F349" t="s">
         <v>1128</v>
       </c>
-      <c r="E349" t="s">
+      <c r="G349" s="7" t="s">
         <v>1129</v>
       </c>
-      <c r="F349" t="s">
+      <c r="H349" s="7" t="s">
         <v>1130</v>
       </c>
-      <c r="G349" s="7" t="s">
+      <c r="I349" s="7" t="s">
         <v>1131</v>
-      </c>
-      <c r="H349" s="7" t="s">
-        <v>1132</v>
-      </c>
-      <c r="I349" s="7" t="s">
-        <v>1133</v>
       </c>
       <c r="J349">
         <v>0</v>
@@ -50900,25 +50902,25 @@
         <v>0</v>
       </c>
       <c r="C350" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D350" s="2" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E350" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F350" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G350" s="7" t="s">
         <v>1134</v>
       </c>
-      <c r="E350" t="s">
+      <c r="H350" s="7" t="s">
         <v>1135</v>
       </c>
-      <c r="F350" t="s">
-        <v>1162</v>
-      </c>
-      <c r="G350" s="7" t="s">
+      <c r="I350" s="7" t="s">
         <v>1136</v>
-      </c>
-      <c r="H350" s="7" t="s">
-        <v>1137</v>
-      </c>
-      <c r="I350" s="7" t="s">
-        <v>1138</v>
       </c>
       <c r="J350">
         <v>0</v>
@@ -50957,16 +50959,16 @@
         <v>0</v>
       </c>
       <c r="C351" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D351" s="2" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E351" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F351" t="s">
         <v>1139</v>
-      </c>
-      <c r="E351" t="s">
-        <v>1140</v>
-      </c>
-      <c r="F351" t="s">
-        <v>1141</v>
       </c>
       <c r="G351">
         <v>1</v>
@@ -51014,16 +51016,16 @@
         <v>0</v>
       </c>
       <c r="C352" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="E352" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="F352" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="G352">
         <v>100</v>
@@ -51070,16 +51072,16 @@
         <v>0</v>
       </c>
       <c r="C353" t="s">
+        <v>1144</v>
+      </c>
+      <c r="D353" s="2" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E353" t="s">
         <v>1146</v>
       </c>
-      <c r="D353" s="2" t="s">
+      <c r="F353" t="s">
         <v>1147</v>
-      </c>
-      <c r="E353" t="s">
-        <v>1148</v>
-      </c>
-      <c r="F353" t="s">
-        <v>1149</v>
       </c>
       <c r="G353">
         <v>125</v>
@@ -51127,16 +51129,16 @@
         <v>0</v>
       </c>
       <c r="C354" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D354" s="2" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E354" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F354" t="s">
         <v>1150</v>
-      </c>
-      <c r="E354" t="s">
-        <v>1151</v>
-      </c>
-      <c r="F354" t="s">
-        <v>1152</v>
       </c>
       <c r="G354">
         <v>6</v>
@@ -51184,16 +51186,16 @@
         <v>0</v>
       </c>
       <c r="C355" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D355" s="2" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E355" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F355" t="s">
         <v>1153</v>
-      </c>
-      <c r="E355" t="s">
-        <v>1154</v>
-      </c>
-      <c r="F355" t="s">
-        <v>1155</v>
       </c>
       <c r="G355">
         <v>8</v>
@@ -51241,16 +51243,16 @@
         <v>0</v>
       </c>
       <c r="C356" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D356" s="2" t="s">
+        <v>1154</v>
+      </c>
+      <c r="E356" t="s">
+        <v>1155</v>
+      </c>
+      <c r="F356" t="s">
         <v>1156</v>
-      </c>
-      <c r="E356" t="s">
-        <v>1157</v>
-      </c>
-      <c r="F356" t="s">
-        <v>1158</v>
       </c>
       <c r="G356">
         <v>1.6</v>
@@ -51298,16 +51300,16 @@
         <v>0</v>
       </c>
       <c r="C357" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="E357" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="F357" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="G357">
         <v>4</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\potential-remove-baseline-20261018\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\gem-workshop-merge\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0749A186-25A0-41D7-8557-CA73A8592363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0945DA2C-AF75-489F-9DB7-38BA8915E039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1939,9 +1939,6 @@
   </si>
   <si>
     <t>⌊81×leaves × a⌋ 顆 1 級（依屬性均分）</t>
-  </si>
-  <si>
-    <t>leaves=素材 5 階總數（融合時雙方相加）。　※與「寶石拆解(一般)」共用保留率，本列不生效。</t>
   </si>
   <si>
     <t>寶石融合成功率</t>
@@ -4449,14 +4446,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>⌊逐階合成成本連乘 × a⌋ 顆同種 1 級</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>a=保留比例；合成素材數見「寶石合成(手動)」，拆解依新合成成本換算。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>a 格；每格上限 b 顆；同階任意2顆換1顆指定寶石</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4477,6 +4466,18 @@
   </si>
   <si>
     <t>a=生命與四維最終倍率 b=升級經驗倍率 c=升級經驗基礎增加值 d=階級名稱。其餘欄位未使用。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1 顆 N 級 → gemComposeInputCount(N-1) 顆同種前一階寶石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>免費無損；2～5級回3顆、6～9級回4顆、10級回6顆9級。數量共用合成配方，無獨立參數，a～l不使用。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>leaves=素材 5 階總數（融合時雙方相加）。a=舊融合寶石拆解保留率，僅相容API使用，寶石頁無入口。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5977,7 +5978,7 @@
         <v>上限 a 級；擊殺技能經驗 = 怪物經驗 × b%</v>
       </c>
       <c r="F15" t="s">
-        <v>1211</v>
+        <v>1208</v>
       </c>
       <c r="G15">
         <f>計算表!G15</f>
@@ -6050,7 +6051,7 @@
         <v>（查表）</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G16">
         <f>計算表!G16</f>
@@ -6122,7 +6123,7 @@
         <v>（查表）</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G17">
         <f>計算表!G17</f>
@@ -6194,7 +6195,7 @@
         <v>（查表）</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G18">
         <f>計算表!G18</f>
@@ -6266,7 +6267,7 @@
         <v>（查表）</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G19">
         <f>計算表!G19</f>
@@ -6338,7 +6339,7 @@
         <v>（查表）</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G20">
         <f>計算表!G20</f>
@@ -6410,7 +6411,7 @@
         <v>（查表）</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G21">
         <f>計算表!G21</f>
@@ -6482,7 +6483,7 @@
         <v>（查表）</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G22">
         <f>計算表!G22</f>
@@ -6554,7 +6555,7 @@
         <v>（查表）</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G23">
         <f>計算表!G23</f>
@@ -6626,7 +6627,7 @@
         <v>（查表）</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G24">
         <f>計算表!G24</f>
@@ -6698,7 +6699,7 @@
         <v>（查表）</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G25">
         <f>計算表!G25</f>
@@ -6770,7 +6771,7 @@
         <v>（查表）</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G26">
         <f>計算表!G26</f>
@@ -6842,7 +6843,7 @@
         <v>（查表）</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G27">
         <f>計算表!G27</f>
@@ -6914,7 +6915,7 @@
         <v>（查表）</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G28">
         <f>計算表!G28</f>
@@ -6986,7 +6987,7 @@
         <v>（查表）</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G29">
         <f>計算表!G29</f>
@@ -7058,7 +7059,7 @@
         <v>（查表）</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G30">
         <f>計算表!G30</f>
@@ -7130,7 +7131,7 @@
         <v>（查表）</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G31">
         <f>計算表!G31</f>
@@ -7202,7 +7203,7 @@
         <v>（查表）</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G32">
         <f>計算表!G32</f>
@@ -7274,7 +7275,7 @@
         <v>（查表）</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G33">
         <f>計算表!G33</f>
@@ -7346,7 +7347,7 @@
         <v>（查表）</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G34">
         <f>計算表!G34</f>
@@ -7418,7 +7419,7 @@
         <v>（查表）</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G35">
         <f>計算表!G35</f>
@@ -7490,7 +7491,7 @@
         <v>（查表）</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>1212</v>
+        <v>1209</v>
       </c>
       <c r="G36">
         <f>計算表!G36</f>
@@ -9038,10 +9039,10 @@
         <v>生命上限</v>
       </c>
       <c r="E57" s="7" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F57" s="7" t="s">
         <v>1147</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>1148</v>
       </c>
       <c r="G57">
         <f>計算表!G57</f>
@@ -9184,20 +9185,20 @@
         <v>法力恢復/秒</v>
       </c>
       <c r="E59" s="7" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F59" s="7" t="s">
         <v>1149</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>1150</v>
       </c>
       <c r="G59">
         <f>計算表!G59</f>
         <v>1</v>
       </c>
       <c r="H59" s="7" t="s">
+        <v>1150</v>
+      </c>
+      <c r="I59" s="7" t="s">
         <v>1151</v>
-      </c>
-      <c r="I59" s="7" t="s">
-        <v>1152</v>
       </c>
       <c r="J59">
         <f>計算表!J59</f>
@@ -9402,10 +9403,10 @@
         <v>物理防禦</v>
       </c>
       <c r="E62" s="7" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F62" s="7" t="s">
         <v>1153</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>1154</v>
       </c>
       <c r="G62">
         <f>計算表!G62</f>
@@ -9420,10 +9421,10 @@
         <v>2.4</v>
       </c>
       <c r="J62" s="7" t="s">
+        <v>1154</v>
+      </c>
+      <c r="K62" s="7" t="s">
         <v>1155</v>
-      </c>
-      <c r="K62" s="7" t="s">
-        <v>1156</v>
       </c>
       <c r="L62">
         <f>計算表!L62</f>
@@ -9472,10 +9473,10 @@
         <v>魔法防禦</v>
       </c>
       <c r="E63" s="7" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F63" s="7" t="s">
         <v>1157</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>1158</v>
       </c>
       <c r="G63">
         <f>計算表!G63</f>
@@ -9490,10 +9491,10 @@
         <v>2.4</v>
       </c>
       <c r="J63" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="K63" s="7" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="L63">
         <f>計算表!L63</f>
@@ -9554,7 +9555,7 @@
         <v>5</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="I64">
         <f>計算表!I64</f>
@@ -9615,22 +9616,22 @@
         <v>連擊數</v>
       </c>
       <c r="E65" s="7" t="s">
+        <v>1172</v>
+      </c>
+      <c r="F65" s="7" t="s">
         <v>1173</v>
       </c>
-      <c r="F65" s="7" t="s">
-        <v>1174</v>
-      </c>
       <c r="G65" s="7" t="s">
+        <v>1168</v>
+      </c>
+      <c r="H65" s="7" t="s">
         <v>1169</v>
       </c>
-      <c r="H65" s="7" t="s">
+      <c r="I65" s="7" t="s">
         <v>1170</v>
       </c>
-      <c r="I65" s="7" t="s">
+      <c r="J65" s="7" t="s">
         <v>1171</v>
-      </c>
-      <c r="J65" s="7" t="s">
-        <v>1172</v>
       </c>
       <c r="K65">
         <f>計算表!K65</f>
@@ -9686,14 +9687,14 @@
         <v>122</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="G66">
         <f>計算表!G66</f>
         <v>150</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="I66">
         <f>計算表!I66</f>
@@ -9766,7 +9767,7 @@
         <v>0.86</v>
       </c>
       <c r="H67" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="I67">
         <f>計算表!I67</f>
@@ -9835,7 +9836,7 @@
         <v>a=每點敏捷%（減去敵方閃避後最低 5%）。</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>1152</v>
+        <v>1151</v>
       </c>
       <c r="H68">
         <f>計算表!H68</f>
@@ -9908,7 +9909,7 @@
         <v>a=每點敏捷%。</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H69">
         <f>計算表!H69</f>
@@ -9969,19 +9970,19 @@
         <v>2-屬性派生</v>
       </c>
       <c r="D70" s="7" t="s">
+        <v>1162</v>
+      </c>
+      <c r="E70" s="7" t="s">
         <v>1163</v>
       </c>
-      <c r="E70" s="7" t="s">
+      <c r="F70" s="7" t="s">
         <v>1164</v>
       </c>
-      <c r="F70" s="7" t="s">
+      <c r="G70" s="7" t="s">
         <v>1165</v>
       </c>
-      <c r="G70" s="7" t="s">
+      <c r="H70" s="7" t="s">
         <v>1166</v>
-      </c>
-      <c r="H70" s="7" t="s">
-        <v>1167</v>
       </c>
       <c r="I70">
         <f>計算表!I70</f>
@@ -11822,7 +11823,7 @@
         <v>忽略敵人防禦% = 穿透%/(穿透%+a)</v>
       </c>
       <c r="F95" s="7" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="G95">
         <f>計算表!G95</f>
@@ -13609,7 +13610,7 @@
         <v>0.5</v>
       </c>
       <c r="I119" s="7" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="J119">
         <f>計算表!J119</f>
@@ -15524,7 +15525,7 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條。</v>
       </c>
       <c r="G145" s="7" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H145">
         <f>計算表!H145</f>
@@ -15597,13 +15598,13 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條。</v>
       </c>
       <c r="G146" s="7" t="s">
+        <v>998</v>
+      </c>
+      <c r="H146" s="7" t="s">
         <v>999</v>
       </c>
-      <c r="H146" s="7" t="s">
+      <c r="I146" s="7" t="s">
         <v>1000</v>
-      </c>
-      <c r="I146" s="7" t="s">
-        <v>1001</v>
       </c>
       <c r="J146">
         <f>計算表!J146</f>
@@ -15668,20 +15669,20 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條。</v>
       </c>
       <c r="G147" s="7" t="s">
+        <v>1001</v>
+      </c>
+      <c r="H147" s="7" t="s">
         <v>1002</v>
-      </c>
-      <c r="H147" s="7" t="s">
-        <v>1003</v>
       </c>
       <c r="I147">
         <f>計算表!I147</f>
         <v>9.11754</v>
       </c>
       <c r="J147" s="7" t="s">
+        <v>1003</v>
+      </c>
+      <c r="K147" s="7" t="s">
         <v>1004</v>
-      </c>
-      <c r="K147" s="7" t="s">
-        <v>1005</v>
       </c>
       <c r="L147">
         <f>計算表!L147</f>
@@ -15738,22 +15739,22 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條。</v>
       </c>
       <c r="G148" s="7" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H148" s="7" t="s">
         <v>1006</v>
       </c>
-      <c r="H148" s="7" t="s">
+      <c r="I148" s="7" t="s">
         <v>1007</v>
       </c>
-      <c r="I148" s="7" t="s">
+      <c r="J148" s="7" t="s">
         <v>1008</v>
       </c>
-      <c r="J148" s="7" t="s">
+      <c r="K148" s="7" t="s">
         <v>1009</v>
       </c>
-      <c r="K148" s="7" t="s">
+      <c r="L148" s="7" t="s">
         <v>1010</v>
-      </c>
-      <c r="L148" s="7" t="s">
-        <v>1011</v>
       </c>
       <c r="M148">
         <f>計算表!M148</f>
@@ -15806,28 +15807,28 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條。</v>
       </c>
       <c r="G149" s="7" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H149" s="7" t="s">
         <v>1012</v>
       </c>
-      <c r="H149" s="7" t="s">
+      <c r="I149" s="7" t="s">
         <v>1013</v>
       </c>
-      <c r="I149" s="7" t="s">
+      <c r="J149" s="7" t="s">
         <v>1014</v>
       </c>
-      <c r="J149" s="7" t="s">
+      <c r="K149" s="7" t="s">
         <v>1015</v>
       </c>
-      <c r="K149" s="7" t="s">
+      <c r="L149" s="7" t="s">
         <v>1016</v>
       </c>
-      <c r="L149" s="7" t="s">
+      <c r="M149" s="7" t="s">
         <v>1017</v>
       </c>
-      <c r="M149" s="7" t="s">
+      <c r="N149" s="7" t="s">
         <v>1018</v>
-      </c>
-      <c r="N149" s="7" t="s">
-        <v>1019</v>
       </c>
       <c r="O149">
         <f>計算表!O149</f>
@@ -15872,28 +15873,28 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條。</v>
       </c>
       <c r="G150" s="7" t="s">
+        <v>1019</v>
+      </c>
+      <c r="H150" s="7" t="s">
         <v>1020</v>
       </c>
-      <c r="H150" s="7" t="s">
+      <c r="I150" s="7" t="s">
         <v>1021</v>
       </c>
-      <c r="I150" s="7" t="s">
+      <c r="J150" s="7" t="s">
         <v>1022</v>
       </c>
-      <c r="J150" s="7" t="s">
+      <c r="K150" s="7" t="s">
         <v>1023</v>
       </c>
-      <c r="K150" s="7" t="s">
+      <c r="L150" s="7" t="s">
         <v>1024</v>
       </c>
-      <c r="L150" s="7" t="s">
+      <c r="M150" s="7" t="s">
         <v>1025</v>
       </c>
-      <c r="M150" s="7" t="s">
+      <c r="N150" s="7" t="s">
         <v>1026</v>
-      </c>
-      <c r="N150" s="7" t="s">
-        <v>1027</v>
       </c>
       <c r="O150">
         <f>計算表!O150</f>
@@ -15938,31 +15939,31 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條 j=9條。</v>
       </c>
       <c r="G151" s="7" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H151" s="7" t="s">
         <v>1028</v>
       </c>
-      <c r="H151" s="7" t="s">
+      <c r="I151" s="7" t="s">
         <v>1029</v>
       </c>
-      <c r="I151" s="7" t="s">
+      <c r="J151" s="7" t="s">
         <v>1030</v>
       </c>
-      <c r="J151" s="7" t="s">
+      <c r="K151" s="7" t="s">
         <v>1031</v>
       </c>
-      <c r="K151" s="7" t="s">
+      <c r="L151" s="7" t="s">
         <v>1032</v>
       </c>
-      <c r="L151" s="7" t="s">
+      <c r="M151" s="7" t="s">
         <v>1033</v>
       </c>
-      <c r="M151" s="7" t="s">
+      <c r="N151" s="7" t="s">
         <v>1034</v>
       </c>
-      <c r="N151" s="7" t="s">
+      <c r="O151" s="7" t="s">
         <v>1035</v>
-      </c>
-      <c r="O151" s="7" t="s">
-        <v>1036</v>
       </c>
       <c r="P151">
         <f>計算表!P151</f>
@@ -16003,7 +16004,7 @@
         <v>裝備產出時依詞條數量決定太古條數與隨機位置（位置永久固定，洗煉不變）。a=0條 b=1條 c=2條 d=3條 e=4條 f=5條 g=6條 h=7條 i=8條 j=9條 k=10條。</v>
       </c>
       <c r="G152" s="7" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="H152">
         <f>計算表!H152</f>
@@ -17486,7 +17487,7 @@
         <v>200</v>
       </c>
       <c r="H172" s="7" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="I172">
         <f>計算表!I172</f>
@@ -18073,7 +18074,7 @@
         <v>a=基礎權重 b=權重加成 c=加成上限 d=出現門檻。普通無加成。神鑄創世不參與此擲骰。(裝備合成才有作用，目前功能關閉中)</v>
       </c>
       <c r="G180" s="7" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="H180" t="str">
         <f>計算表!H180</f>
@@ -20892,7 +20893,7 @@
         <v>1</v>
       </c>
       <c r="I218" s="7" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="J218">
         <f>計算表!J219</f>
@@ -21026,7 +21027,7 @@
         <v>607</v>
       </c>
       <c r="F220" s="7" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G220">
         <f>計算表!G221</f>
@@ -22058,15 +22059,15 @@
       </c>
       <c r="E234" t="str">
         <f>計算表!E235</f>
-        <v>⌊逐階合成成本連乘 × a⌋ 顆同種 1 級</v>
+        <v>1 顆 N 級 → gemComposeInputCount(N-1) 顆同種前一階寶石</v>
       </c>
       <c r="F234" t="str">
         <f>計算表!F235</f>
-        <v>a=保留比例；合成素材數見「寶石合成(手動)」，拆解依新合成成本換算。</v>
+        <v>免費無損；2～5級回3顆、6～9級回4顆、10級回6顆9級。數量共用合成配方，無獨立參數，a～l不使用。</v>
       </c>
       <c r="G234">
         <f>計算表!G235</f>
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="H234">
         <f>計算表!H235</f>
@@ -22136,7 +22137,7 @@
       </c>
       <c r="F235" t="str">
         <f>計算表!F236</f>
-        <v>leaves=素材 5 階總數（融合時雙方相加）。　※與「寶石拆解(一般)」共用保留率，本列不生效。</v>
+        <v>leaves=素材 5 階總數（融合時雙方相加）。a=舊融合寶石拆解保留率，僅相容API使用，寶石頁無入口。</v>
       </c>
       <c r="G235">
         <f>計算表!G236</f>
@@ -27393,7 +27394,7 @@
         <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）。</v>
       </c>
       <c r="G306" s="7" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H306">
         <f>計算表!H322</f>
@@ -27762,7 +27763,7 @@
         <v>a=詞條數值倍率 b=詞條數下限 c=詞條數上限 d=寶石插槽 e=附魔欄位 f=分解係數 g=符文孔數（0＝沒有符文孔；上限與雙手武器加成見 Runes 表）。</v>
       </c>
       <c r="G311" s="7" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H311">
         <f>計算表!H327</f>
@@ -29809,170 +29810,170 @@
     </row>
     <row r="339" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A339" s="7" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B339" s="7" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C339" s="7" t="s">
         <v>1186</v>
       </c>
-      <c r="B339" s="7" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C339" s="7" t="s">
+      <c r="D339" s="7" t="s">
         <v>1187</v>
       </c>
-      <c r="D339" s="7" t="s">
+      <c r="E339" s="7" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F339" s="7" t="s">
+        <v>1198</v>
+      </c>
+      <c r="G339" s="7" t="s">
         <v>1188</v>
       </c>
-      <c r="E339" s="7" t="s">
-        <v>1198</v>
-      </c>
-      <c r="F339" s="7" t="s">
+      <c r="H339" s="7" t="s">
+        <v>1189</v>
+      </c>
+      <c r="I339" s="7" t="s">
+        <v>1190</v>
+      </c>
+      <c r="J339" s="7" t="s">
         <v>1199</v>
       </c>
-      <c r="G339" s="7" t="s">
-        <v>1189</v>
-      </c>
-      <c r="H339" s="7" t="s">
-        <v>1190</v>
-      </c>
-      <c r="I339" s="7" t="s">
-        <v>1191</v>
-      </c>
-      <c r="J339" s="7" t="s">
+      <c r="K339" s="7" t="s">
+        <v>1184</v>
+      </c>
+      <c r="L339" s="7" t="s">
         <v>1200</v>
       </c>
-      <c r="K339" s="7" t="s">
-        <v>1185</v>
-      </c>
-      <c r="L339" s="7" t="s">
-        <v>1201</v>
-      </c>
       <c r="M339" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="N339" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O339" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="P339" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="Q339" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="R339" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="340" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A340" s="7" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B340" s="7" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C340" s="7" t="s">
+        <v>1186</v>
+      </c>
+      <c r="D340" s="7" t="s">
         <v>1192</v>
       </c>
-      <c r="B340" s="7" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C340" s="7" t="s">
-        <v>1187</v>
-      </c>
-      <c r="D340" s="7" t="s">
+      <c r="E340" s="7" t="s">
         <v>1193</v>
       </c>
-      <c r="E340" s="7" t="s">
+      <c r="F340" s="7" t="s">
+        <v>1201</v>
+      </c>
+      <c r="G340" s="7" t="s">
         <v>1194</v>
       </c>
-      <c r="F340" s="7" t="s">
-        <v>1202</v>
-      </c>
-      <c r="G340" s="7" t="s">
+      <c r="H340" s="7" t="s">
         <v>1195</v>
       </c>
-      <c r="H340" s="7" t="s">
+      <c r="I340" s="7" t="s">
+        <v>1171</v>
+      </c>
+      <c r="J340" s="7" t="s">
         <v>1196</v>
       </c>
-      <c r="I340" s="7" t="s">
-        <v>1172</v>
-      </c>
-      <c r="J340" s="7" t="s">
-        <v>1197</v>
-      </c>
       <c r="K340" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="L340" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="M340" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="N340" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="O340" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="P340" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="Q340" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="R340" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="341" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A341" s="7" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B341" s="7" t="s">
+        <v>1158</v>
+      </c>
+      <c r="C341" s="7" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D341" s="7" t="s">
         <v>1176</v>
       </c>
-      <c r="B341" s="7" t="s">
-        <v>1159</v>
-      </c>
-      <c r="C341" s="7" t="s">
-        <v>1056</v>
-      </c>
-      <c r="D341" s="7" t="s">
+      <c r="E341" s="7" t="s">
         <v>1177</v>
       </c>
-      <c r="E341" s="7" t="s">
+      <c r="F341" s="7" t="s">
         <v>1178</v>
       </c>
-      <c r="F341" s="7" t="s">
+      <c r="G341" s="7" t="s">
+        <v>1168</v>
+      </c>
+      <c r="H341" s="7" t="s">
         <v>1179</v>
       </c>
-      <c r="G341" s="7" t="s">
-        <v>1169</v>
-      </c>
-      <c r="H341" s="7" t="s">
+      <c r="I341" s="7" t="s">
         <v>1180</v>
       </c>
-      <c r="I341" s="7" t="s">
+      <c r="J341" s="7" t="s">
+        <v>1168</v>
+      </c>
+      <c r="K341" s="7" t="s">
         <v>1181</v>
       </c>
-      <c r="J341" s="7" t="s">
-        <v>1169</v>
-      </c>
-      <c r="K341" s="7" t="s">
+      <c r="L341" s="7" t="s">
         <v>1182</v>
       </c>
-      <c r="L341" s="7" t="s">
+      <c r="M341" s="7" t="s">
         <v>1183</v>
       </c>
-      <c r="M341" s="7" t="s">
+      <c r="N341" s="7" t="s">
         <v>1184</v>
       </c>
-      <c r="N341" s="7" t="s">
-        <v>1185</v>
-      </c>
       <c r="O341" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="P341" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="Q341" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="R341" s="7" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
     </row>
   </sheetData>
@@ -30058,16 +30059,16 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
+        <v>927</v>
+      </c>
+      <c r="D2" t="s">
         <v>928</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>929</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>930</v>
-      </c>
-      <c r="F2" t="s">
-        <v>931</v>
       </c>
       <c r="G2">
         <v>50000</v>
@@ -30115,16 +30116,16 @@
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D3" t="s">
+        <v>931</v>
+      </c>
+      <c r="E3" t="s">
+        <v>929</v>
+      </c>
+      <c r="F3" t="s">
         <v>932</v>
-      </c>
-      <c r="E3" t="s">
-        <v>930</v>
-      </c>
-      <c r="F3" t="s">
-        <v>933</v>
       </c>
       <c r="G3">
         <v>500</v>
@@ -30172,16 +30173,16 @@
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D4" t="s">
+        <v>933</v>
+      </c>
+      <c r="E4" t="s">
+        <v>929</v>
+      </c>
+      <c r="F4" t="s">
         <v>934</v>
-      </c>
-      <c r="E4" t="s">
-        <v>930</v>
-      </c>
-      <c r="F4" t="s">
-        <v>935</v>
       </c>
       <c r="G4">
         <v>100</v>
@@ -30229,16 +30230,16 @@
         <v>0</v>
       </c>
       <c r="C5" t="s">
+        <v>823</v>
+      </c>
+      <c r="D5" t="s">
         <v>824</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>825</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>826</v>
-      </c>
-      <c r="F5" t="s">
-        <v>827</v>
       </c>
       <c r="G5">
         <v>24</v>
@@ -30286,16 +30287,16 @@
         <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D6" t="s">
+        <v>827</v>
+      </c>
+      <c r="E6" t="s">
         <v>828</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>829</v>
-      </c>
-      <c r="F6" t="s">
-        <v>830</v>
       </c>
       <c r="G6">
         <v>10</v>
@@ -30343,16 +30344,16 @@
         <v>0</v>
       </c>
       <c r="C7" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D7" t="s">
+        <v>830</v>
+      </c>
+      <c r="E7" t="s">
         <v>831</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>832</v>
-      </c>
-      <c r="F7" t="s">
-        <v>833</v>
       </c>
       <c r="G7">
         <v>10</v>
@@ -30400,16 +30401,16 @@
         <v>0</v>
       </c>
       <c r="C8" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D8" t="s">
+        <v>833</v>
+      </c>
+      <c r="E8" t="s">
         <v>834</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>835</v>
-      </c>
-      <c r="F8" t="s">
-        <v>836</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -30745,13 +30746,13 @@
         <v>18</v>
       </c>
       <c r="D14" t="s">
+        <v>902</v>
+      </c>
+      <c r="E14" t="s">
         <v>903</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>904</v>
-      </c>
-      <c r="F14" t="s">
-        <v>905</v>
       </c>
       <c r="G14">
         <v>30</v>
@@ -30802,13 +30803,13 @@
         <v>18</v>
       </c>
       <c r="D15" t="s">
+        <v>905</v>
+      </c>
+      <c r="E15" t="s">
         <v>906</v>
       </c>
-      <c r="E15" t="s">
-        <v>907</v>
-      </c>
       <c r="F15" t="s">
-        <v>1213</v>
+        <v>1210</v>
       </c>
       <c r="G15">
         <v>1000</v>
@@ -30865,7 +30866,7 @@
         <v>36</v>
       </c>
       <c r="F16" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -30922,7 +30923,7 @@
         <v>36</v>
       </c>
       <c r="F17" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G17">
         <v>1.5</v>
@@ -30979,7 +30980,7 @@
         <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G18">
         <v>2.5</v>
@@ -31036,7 +31037,7 @@
         <v>36</v>
       </c>
       <c r="F19" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G19">
         <v>3.5</v>
@@ -31093,7 +31094,7 @@
         <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -31150,7 +31151,7 @@
         <v>36</v>
       </c>
       <c r="F21" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G21">
         <v>7</v>
@@ -31207,7 +31208,7 @@
         <v>36</v>
       </c>
       <c r="F22" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G22">
         <v>10</v>
@@ -31264,7 +31265,7 @@
         <v>36</v>
       </c>
       <c r="F23" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G23">
         <v>14</v>
@@ -31321,7 +31322,7 @@
         <v>36</v>
       </c>
       <c r="F24" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G24">
         <v>18</v>
@@ -31378,7 +31379,7 @@
         <v>36</v>
       </c>
       <c r="F25" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G25">
         <v>24</v>
@@ -31435,7 +31436,7 @@
         <v>36</v>
       </c>
       <c r="F26" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G26">
         <v>30</v>
@@ -31492,7 +31493,7 @@
         <v>36</v>
       </c>
       <c r="F27" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G27">
         <v>60</v>
@@ -31549,7 +31550,7 @@
         <v>36</v>
       </c>
       <c r="F28" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G28">
         <v>100</v>
@@ -31606,7 +31607,7 @@
         <v>36</v>
       </c>
       <c r="F29" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G29">
         <v>150</v>
@@ -31663,7 +31664,7 @@
         <v>36</v>
       </c>
       <c r="F30" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G30">
         <v>200</v>
@@ -31720,7 +31721,7 @@
         <v>36</v>
       </c>
       <c r="F31" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G31">
         <v>300</v>
@@ -31777,7 +31778,7 @@
         <v>36</v>
       </c>
       <c r="F32" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G32">
         <v>450</v>
@@ -31834,7 +31835,7 @@
         <v>36</v>
       </c>
       <c r="F33" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G33">
         <v>650</v>
@@ -31891,7 +31892,7 @@
         <v>36</v>
       </c>
       <c r="F34" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G34">
         <v>800</v>
@@ -31948,7 +31949,7 @@
         <v>36</v>
       </c>
       <c r="F35" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G35">
         <v>1200</v>
@@ -32005,7 +32006,7 @@
         <v>36</v>
       </c>
       <c r="F36" t="s">
-        <v>1214</v>
+        <v>1211</v>
       </c>
       <c r="G36">
         <v>2500</v>
@@ -32347,7 +32348,7 @@
         <v>145</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -32404,7 +32405,7 @@
         <v>145</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -33769,10 +33770,10 @@
         <v>130</v>
       </c>
       <c r="E67" s="6" t="s">
+        <v>993</v>
+      </c>
+      <c r="F67" s="3" t="s">
         <v>994</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>995</v>
       </c>
       <c r="G67">
         <v>0.86</v>
@@ -33997,10 +33998,10 @@
         <v>139</v>
       </c>
       <c r="E71" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F71" t="s">
         <v>1045</v>
-      </c>
-      <c r="F71" t="s">
-        <v>1046</v>
       </c>
       <c r="G71">
         <v>5</v>
@@ -34852,10 +34853,10 @@
         <v>205</v>
       </c>
       <c r="E86" s="7" t="s">
+        <v>1050</v>
+      </c>
+      <c r="F86" s="7" t="s">
         <v>1051</v>
-      </c>
-      <c r="F86" s="7" t="s">
-        <v>1052</v>
       </c>
       <c r="G86">
         <v>10</v>
@@ -35362,13 +35363,13 @@
         <v>184</v>
       </c>
       <c r="D95" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="E95" s="2" t="s">
         <v>936</v>
       </c>
-      <c r="E95" s="2" t="s">
+      <c r="F95" s="2" t="s">
         <v>937</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>938</v>
       </c>
       <c r="G95">
         <v>0.75</v>
@@ -37078,7 +37079,7 @@
         <v>266</v>
       </c>
       <c r="F125" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="G125">
         <v>4</v>
@@ -37129,7 +37130,7 @@
         <v>241</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E126" t="s">
         <v>267</v>
@@ -37186,7 +37187,7 @@
         <v>269</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="E127" t="s">
         <v>270</v>
@@ -37243,7 +37244,7 @@
         <v>269</v>
       </c>
       <c r="D128" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="E128" t="s">
         <v>270</v>
@@ -37300,7 +37301,7 @@
         <v>269</v>
       </c>
       <c r="D129" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="E129" t="s">
         <v>270</v>
@@ -37357,7 +37358,7 @@
         <v>269</v>
       </c>
       <c r="D130" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="E130" t="s">
         <v>270</v>
@@ -37414,7 +37415,7 @@
         <v>269</v>
       </c>
       <c r="D131" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="E131" t="s">
         <v>270</v>
@@ -37423,7 +37424,7 @@
         <v>271</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H131" t="s">
         <v>283</v>
@@ -37432,7 +37433,7 @@
         <v>284</v>
       </c>
       <c r="J131" s="3" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="K131">
         <v>0</v>
@@ -37471,7 +37472,7 @@
         <v>269</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="E132" t="s">
         <v>270</v>
@@ -37480,19 +37481,19 @@
         <v>271</v>
       </c>
       <c r="G132" s="3" t="s">
+        <v>983</v>
+      </c>
+      <c r="H132" s="3" t="s">
         <v>984</v>
       </c>
-      <c r="H132" s="3" t="s">
+      <c r="I132" s="3" t="s">
+        <v>982</v>
+      </c>
+      <c r="J132" s="3" t="s">
         <v>985</v>
       </c>
-      <c r="I132" s="3" t="s">
-        <v>983</v>
-      </c>
-      <c r="J132" s="3" t="s">
+      <c r="K132" s="3" t="s">
         <v>986</v>
-      </c>
-      <c r="K132" s="3" t="s">
-        <v>987</v>
       </c>
       <c r="L132">
         <v>0</v>
@@ -37528,7 +37529,7 @@
         <v>269</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E133" t="s">
         <v>270</v>
@@ -37537,22 +37538,22 @@
         <v>271</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="I133" s="3" t="s">
+        <v>989</v>
+      </c>
+      <c r="J133" s="3" t="s">
         <v>990</v>
       </c>
-      <c r="J133" s="3" t="s">
-        <v>991</v>
-      </c>
       <c r="K133" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="L133" s="3" t="s">
         <v>978</v>
-      </c>
-      <c r="L133" s="3" t="s">
-        <v>979</v>
       </c>
       <c r="M133">
         <v>0</v>
@@ -37585,13 +37586,13 @@
         <v>269</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="E134" t="s">
         <v>270</v>
       </c>
       <c r="F134" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G134" t="s">
         <v>272</v>
@@ -37642,22 +37643,22 @@
         <v>269</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="E135" t="s">
         <v>270</v>
       </c>
       <c r="F135" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H135" s="3" t="s">
+        <v>947</v>
+      </c>
+      <c r="I135" s="3" t="s">
         <v>948</v>
-      </c>
-      <c r="I135" s="3" t="s">
-        <v>949</v>
       </c>
       <c r="J135">
         <v>0</v>
@@ -37699,28 +37700,28 @@
         <v>269</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="E136" t="s">
         <v>270</v>
       </c>
       <c r="F136" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G136" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="H136" s="3" t="s">
         <v>951</v>
       </c>
-      <c r="H136" s="3" t="s">
+      <c r="I136" s="3" t="s">
         <v>952</v>
       </c>
-      <c r="I136" s="3" t="s">
+      <c r="J136" s="3" t="s">
+        <v>954</v>
+      </c>
+      <c r="K136" s="3" t="s">
         <v>953</v>
-      </c>
-      <c r="J136" s="3" t="s">
-        <v>955</v>
-      </c>
-      <c r="K136" s="3" t="s">
-        <v>954</v>
       </c>
       <c r="L136">
         <v>0</v>
@@ -37756,34 +37757,34 @@
         <v>269</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="E137" t="s">
         <v>270</v>
       </c>
       <c r="F137" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G137" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="H137" s="3" t="s">
         <v>966</v>
       </c>
-      <c r="H137" s="3" t="s">
+      <c r="I137" s="3" t="s">
         <v>967</v>
       </c>
-      <c r="I137" s="3" t="s">
+      <c r="J137" s="3" t="s">
         <v>968</v>
       </c>
-      <c r="J137" s="3" t="s">
+      <c r="K137" s="3" t="s">
         <v>969</v>
       </c>
-      <c r="K137" s="3" t="s">
+      <c r="L137" s="3" t="s">
         <v>970</v>
       </c>
-      <c r="L137" s="3" t="s">
+      <c r="M137" s="3" t="s">
         <v>971</v>
-      </c>
-      <c r="M137" s="3" t="s">
-        <v>972</v>
       </c>
       <c r="N137">
         <v>0</v>
@@ -37813,34 +37814,34 @@
         <v>269</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="E138" t="s">
         <v>270</v>
       </c>
       <c r="F138" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G138" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="H138" s="3" t="s">
         <v>959</v>
       </c>
-      <c r="H138" s="3" t="s">
+      <c r="I138" s="3" t="s">
+        <v>957</v>
+      </c>
+      <c r="J138" s="3" t="s">
         <v>960</v>
       </c>
-      <c r="I138" s="3" t="s">
-        <v>958</v>
-      </c>
-      <c r="J138" s="3" t="s">
+      <c r="K138" s="3" t="s">
         <v>961</v>
       </c>
-      <c r="K138" s="3" t="s">
+      <c r="L138" s="3" t="s">
         <v>962</v>
       </c>
-      <c r="L138" s="3" t="s">
+      <c r="M138" s="3" t="s">
         <v>963</v>
-      </c>
-      <c r="M138" s="3" t="s">
-        <v>964</v>
       </c>
       <c r="N138">
         <v>0</v>
@@ -40378,13 +40379,13 @@
         <v>526</v>
       </c>
       <c r="D183" t="s">
+        <v>924</v>
+      </c>
+      <c r="E183" t="s">
         <v>925</v>
       </c>
-      <c r="E183" t="s">
+      <c r="F183" t="s">
         <v>926</v>
-      </c>
-      <c r="F183" t="s">
-        <v>927</v>
       </c>
       <c r="G183">
         <v>0.1</v>
@@ -41062,13 +41063,13 @@
         <v>533</v>
       </c>
       <c r="D195" t="s">
+        <v>893</v>
+      </c>
+      <c r="E195" t="s">
         <v>894</v>
       </c>
-      <c r="E195" t="s">
+      <c r="F195" t="s">
         <v>895</v>
-      </c>
-      <c r="F195" t="s">
-        <v>896</v>
       </c>
       <c r="G195">
         <v>20</v>
@@ -41119,13 +41120,13 @@
         <v>533</v>
       </c>
       <c r="D196" t="s">
+        <v>896</v>
+      </c>
+      <c r="E196" t="s">
         <v>897</v>
       </c>
-      <c r="E196" t="s">
+      <c r="F196" t="s">
         <v>898</v>
-      </c>
-      <c r="F196" t="s">
-        <v>899</v>
       </c>
       <c r="G196">
         <v>500000000</v>
@@ -41176,13 +41177,13 @@
         <v>533</v>
       </c>
       <c r="D197" t="s">
+        <v>899</v>
+      </c>
+      <c r="E197" t="s">
         <v>900</v>
       </c>
-      <c r="E197" t="s">
+      <c r="F197" t="s">
         <v>901</v>
-      </c>
-      <c r="F197" t="s">
-        <v>902</v>
       </c>
       <c r="G197">
         <v>13</v>
@@ -41932,7 +41933,7 @@
         <v>603</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F210" t="s">
         <v>604</v>
@@ -43914,10 +43915,10 @@
         <v>629</v>
       </c>
       <c r="E232" t="s">
+        <v>1202</v>
+      </c>
+      <c r="F232" t="s">
         <v>1203</v>
-      </c>
-      <c r="F232" t="s">
-        <v>1204</v>
       </c>
       <c r="G232">
         <v>3</v>
@@ -43971,10 +43972,10 @@
         <v>630</v>
       </c>
       <c r="E233" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F233" t="s">
         <v>1205</v>
-      </c>
-      <c r="F233" t="s">
-        <v>1206</v>
       </c>
       <c r="G233">
         <v>100</v>
@@ -44028,10 +44029,10 @@
         <v>631</v>
       </c>
       <c r="E234" t="s">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="F234" t="s">
-        <v>1210</v>
+        <v>1207</v>
       </c>
       <c r="G234">
         <v>9</v>
@@ -44085,13 +44086,13 @@
         <v>632</v>
       </c>
       <c r="E235" t="s">
-        <v>1207</v>
+        <v>1212</v>
       </c>
       <c r="F235" t="s">
-        <v>1208</v>
+        <v>1213</v>
       </c>
       <c r="G235">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="H235">
         <v>0</v>
@@ -44145,7 +44146,7 @@
         <v>634</v>
       </c>
       <c r="F236" t="s">
-        <v>635</v>
+        <v>1214</v>
       </c>
       <c r="G236">
         <v>0.7</v>
@@ -44196,13 +44197,13 @@
         <v>619</v>
       </c>
       <c r="D237" t="s">
+        <v>635</v>
+      </c>
+      <c r="E237" t="s">
         <v>636</v>
       </c>
-      <c r="E237" t="s">
+      <c r="F237" t="s">
         <v>637</v>
-      </c>
-      <c r="F237" t="s">
-        <v>638</v>
       </c>
       <c r="G237">
         <v>10</v>
@@ -44253,13 +44254,13 @@
         <v>619</v>
       </c>
       <c r="D238" t="s">
+        <v>638</v>
+      </c>
+      <c r="E238" t="s">
         <v>639</v>
       </c>
-      <c r="E238" t="s">
+      <c r="F238" t="s">
         <v>640</v>
-      </c>
-      <c r="F238" t="s">
-        <v>641</v>
       </c>
       <c r="G238">
         <v>0</v>
@@ -44307,16 +44308,16 @@
         <v>0</v>
       </c>
       <c r="C239" t="s">
+        <v>641</v>
+      </c>
+      <c r="D239" t="s">
         <v>642</v>
       </c>
-      <c r="D239" t="s">
+      <c r="E239" t="s">
         <v>643</v>
       </c>
-      <c r="E239" t="s">
+      <c r="F239" t="s">
         <v>644</v>
-      </c>
-      <c r="F239" t="s">
-        <v>645</v>
       </c>
       <c r="G239">
         <v>100000</v>
@@ -44364,16 +44365,16 @@
         <v>0</v>
       </c>
       <c r="C240" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D240" t="s">
+        <v>645</v>
+      </c>
+      <c r="E240" t="s">
         <v>646</v>
       </c>
-      <c r="E240" t="s">
+      <c r="F240" t="s">
         <v>647</v>
-      </c>
-      <c r="F240" t="s">
-        <v>648</v>
       </c>
       <c r="G240">
         <v>5000</v>
@@ -44421,13 +44422,13 @@
         <v>0</v>
       </c>
       <c r="C241" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D241" t="s">
+        <v>648</v>
+      </c>
+      <c r="E241" t="s">
         <v>649</v>
-      </c>
-      <c r="E241" t="s">
-        <v>650</v>
       </c>
       <c r="F241">
         <v>0</v>
@@ -44478,16 +44479,16 @@
         <v>0</v>
       </c>
       <c r="C242" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D242" t="s">
+        <v>650</v>
+      </c>
+      <c r="E242" t="s">
         <v>651</v>
       </c>
-      <c r="E242" t="s">
+      <c r="F242" t="s">
         <v>652</v>
-      </c>
-      <c r="F242" t="s">
-        <v>653</v>
       </c>
       <c r="G242">
         <v>10000</v>
@@ -44535,28 +44536,28 @@
         <v>0</v>
       </c>
       <c r="C243" t="s">
+        <v>724</v>
+      </c>
+      <c r="D243" t="s">
+        <v>654</v>
+      </c>
+      <c r="E243" t="s">
         <v>725</v>
       </c>
-      <c r="D243" t="s">
-        <v>655</v>
-      </c>
-      <c r="E243" t="s">
+      <c r="F243" t="s">
         <v>726</v>
       </c>
-      <c r="F243" t="s">
+      <c r="G243" t="s">
         <v>727</v>
       </c>
-      <c r="G243" t="s">
+      <c r="H243" t="s">
         <v>728</v>
       </c>
-      <c r="H243" t="s">
+      <c r="I243" t="s">
         <v>729</v>
       </c>
-      <c r="I243" t="s">
+      <c r="J243" t="s">
         <v>730</v>
-      </c>
-      <c r="J243" t="s">
-        <v>731</v>
       </c>
       <c r="K243">
         <v>0</v>
@@ -44592,28 +44593,28 @@
         <v>0</v>
       </c>
       <c r="C244" t="s">
+        <v>724</v>
+      </c>
+      <c r="D244" t="s">
+        <v>659</v>
+      </c>
+      <c r="E244" t="s">
         <v>725</v>
       </c>
-      <c r="D244" t="s">
-        <v>660</v>
-      </c>
-      <c r="E244" t="s">
+      <c r="F244" t="s">
         <v>726</v>
       </c>
-      <c r="F244" t="s">
-        <v>727</v>
-      </c>
       <c r="G244" t="s">
+        <v>731</v>
+      </c>
+      <c r="H244" t="s">
+        <v>728</v>
+      </c>
+      <c r="I244" t="s">
         <v>732</v>
       </c>
-      <c r="H244" t="s">
-        <v>729</v>
-      </c>
-      <c r="I244" t="s">
+      <c r="J244" t="s">
         <v>733</v>
-      </c>
-      <c r="J244" t="s">
-        <v>734</v>
       </c>
       <c r="K244">
         <v>0</v>
@@ -44649,28 +44650,28 @@
         <v>0</v>
       </c>
       <c r="C245" t="s">
+        <v>724</v>
+      </c>
+      <c r="D245" t="s">
+        <v>662</v>
+      </c>
+      <c r="E245" t="s">
         <v>725</v>
       </c>
-      <c r="D245" t="s">
-        <v>663</v>
-      </c>
-      <c r="E245" t="s">
+      <c r="F245" t="s">
         <v>726</v>
       </c>
-      <c r="F245" t="s">
-        <v>727</v>
-      </c>
       <c r="G245" t="s">
+        <v>734</v>
+      </c>
+      <c r="H245" t="s">
+        <v>728</v>
+      </c>
+      <c r="I245" t="s">
         <v>735</v>
       </c>
-      <c r="H245" t="s">
-        <v>729</v>
-      </c>
-      <c r="I245" t="s">
+      <c r="J245" t="s">
         <v>736</v>
-      </c>
-      <c r="J245" t="s">
-        <v>737</v>
       </c>
       <c r="K245">
         <v>0</v>
@@ -44706,31 +44707,31 @@
         <v>0</v>
       </c>
       <c r="C246" t="s">
+        <v>724</v>
+      </c>
+      <c r="D246" t="s">
+        <v>665</v>
+      </c>
+      <c r="E246" t="s">
         <v>725</v>
       </c>
-      <c r="D246" t="s">
-        <v>666</v>
-      </c>
-      <c r="E246" t="s">
+      <c r="F246" t="s">
         <v>726</v>
       </c>
-      <c r="F246" t="s">
-        <v>727</v>
-      </c>
       <c r="G246" t="s">
+        <v>737</v>
+      </c>
+      <c r="H246" t="s">
+        <v>728</v>
+      </c>
+      <c r="I246" t="s">
+        <v>735</v>
+      </c>
+      <c r="J246" t="s">
+        <v>736</v>
+      </c>
+      <c r="K246" t="s">
         <v>738</v>
-      </c>
-      <c r="H246" t="s">
-        <v>729</v>
-      </c>
-      <c r="I246" t="s">
-        <v>736</v>
-      </c>
-      <c r="J246" t="s">
-        <v>737</v>
-      </c>
-      <c r="K246" t="s">
-        <v>739</v>
       </c>
       <c r="L246">
         <v>0</v>
@@ -44763,31 +44764,31 @@
         <v>0</v>
       </c>
       <c r="C247" t="s">
+        <v>724</v>
+      </c>
+      <c r="D247" t="s">
+        <v>668</v>
+      </c>
+      <c r="E247" t="s">
         <v>725</v>
       </c>
-      <c r="D247" t="s">
-        <v>669</v>
-      </c>
-      <c r="E247" t="s">
+      <c r="F247" t="s">
         <v>726</v>
       </c>
-      <c r="F247" t="s">
-        <v>727</v>
-      </c>
       <c r="G247" t="s">
+        <v>739</v>
+      </c>
+      <c r="H247" t="s">
+        <v>728</v>
+      </c>
+      <c r="I247" t="s">
+        <v>735</v>
+      </c>
+      <c r="J247" t="s">
         <v>740</v>
       </c>
-      <c r="H247" t="s">
-        <v>729</v>
-      </c>
-      <c r="I247" t="s">
-        <v>736</v>
-      </c>
-      <c r="J247" t="s">
+      <c r="K247" t="s">
         <v>741</v>
-      </c>
-      <c r="K247" t="s">
-        <v>742</v>
       </c>
       <c r="L247">
         <v>0</v>
@@ -44820,31 +44821,31 @@
         <v>0</v>
       </c>
       <c r="C248" t="s">
+        <v>724</v>
+      </c>
+      <c r="D248" t="s">
+        <v>671</v>
+      </c>
+      <c r="E248" t="s">
         <v>725</v>
       </c>
-      <c r="D248" t="s">
-        <v>672</v>
-      </c>
-      <c r="E248" t="s">
+      <c r="F248" t="s">
         <v>726</v>
       </c>
-      <c r="F248" t="s">
-        <v>727</v>
-      </c>
       <c r="G248" t="s">
+        <v>742</v>
+      </c>
+      <c r="H248" t="s">
+        <v>728</v>
+      </c>
+      <c r="I248" t="s">
+        <v>735</v>
+      </c>
+      <c r="J248" t="s">
         <v>743</v>
       </c>
-      <c r="H248" t="s">
-        <v>729</v>
-      </c>
-      <c r="I248" t="s">
-        <v>736</v>
-      </c>
-      <c r="J248" t="s">
+      <c r="K248" t="s">
         <v>744</v>
-      </c>
-      <c r="K248" t="s">
-        <v>745</v>
       </c>
       <c r="L248">
         <v>0</v>
@@ -44877,31 +44878,31 @@
         <v>0</v>
       </c>
       <c r="C249" t="s">
+        <v>724</v>
+      </c>
+      <c r="D249" t="s">
+        <v>674</v>
+      </c>
+      <c r="E249" t="s">
         <v>725</v>
       </c>
-      <c r="D249" t="s">
-        <v>675</v>
-      </c>
-      <c r="E249" t="s">
+      <c r="F249" t="s">
         <v>726</v>
       </c>
-      <c r="F249" t="s">
-        <v>727</v>
-      </c>
       <c r="G249" t="s">
+        <v>745</v>
+      </c>
+      <c r="H249" t="s">
+        <v>728</v>
+      </c>
+      <c r="I249" t="s">
         <v>746</v>
       </c>
-      <c r="H249" t="s">
-        <v>729</v>
-      </c>
-      <c r="I249" t="s">
+      <c r="J249" t="s">
         <v>747</v>
       </c>
-      <c r="J249" t="s">
+      <c r="K249" t="s">
         <v>748</v>
-      </c>
-      <c r="K249" t="s">
-        <v>749</v>
       </c>
       <c r="L249">
         <v>0</v>
@@ -44934,31 +44935,31 @@
         <v>0</v>
       </c>
       <c r="C250" t="s">
+        <v>724</v>
+      </c>
+      <c r="D250" t="s">
+        <v>679</v>
+      </c>
+      <c r="E250" t="s">
         <v>725</v>
       </c>
-      <c r="D250" t="s">
-        <v>680</v>
-      </c>
-      <c r="E250" t="s">
+      <c r="F250" t="s">
         <v>726</v>
       </c>
-      <c r="F250" t="s">
-        <v>727</v>
-      </c>
       <c r="G250" t="s">
+        <v>749</v>
+      </c>
+      <c r="H250" t="s">
+        <v>728</v>
+      </c>
+      <c r="I250" t="s">
         <v>750</v>
       </c>
-      <c r="H250" t="s">
-        <v>729</v>
-      </c>
-      <c r="I250" t="s">
+      <c r="J250" t="s">
         <v>751</v>
       </c>
-      <c r="J250" t="s">
+      <c r="K250" t="s">
         <v>752</v>
-      </c>
-      <c r="K250" t="s">
-        <v>753</v>
       </c>
       <c r="L250">
         <v>0</v>
@@ -44991,31 +44992,31 @@
         <v>0</v>
       </c>
       <c r="C251" t="s">
+        <v>724</v>
+      </c>
+      <c r="D251" t="s">
+        <v>681</v>
+      </c>
+      <c r="E251" t="s">
         <v>725</v>
       </c>
-      <c r="D251" t="s">
-        <v>682</v>
-      </c>
-      <c r="E251" t="s">
+      <c r="F251" t="s">
         <v>726</v>
       </c>
-      <c r="F251" t="s">
-        <v>727</v>
-      </c>
       <c r="G251" t="s">
+        <v>753</v>
+      </c>
+      <c r="H251" t="s">
+        <v>728</v>
+      </c>
+      <c r="I251" t="s">
         <v>754</v>
       </c>
-      <c r="H251" t="s">
-        <v>729</v>
-      </c>
-      <c r="I251" t="s">
+      <c r="J251" t="s">
         <v>755</v>
       </c>
-      <c r="J251" t="s">
+      <c r="K251" t="s">
         <v>756</v>
-      </c>
-      <c r="K251" t="s">
-        <v>757</v>
       </c>
       <c r="L251">
         <v>0</v>
@@ -45048,34 +45049,34 @@
         <v>0</v>
       </c>
       <c r="C252" t="s">
+        <v>724</v>
+      </c>
+      <c r="D252" t="s">
+        <v>685</v>
+      </c>
+      <c r="E252" t="s">
         <v>725</v>
       </c>
-      <c r="D252" t="s">
-        <v>686</v>
-      </c>
-      <c r="E252" t="s">
+      <c r="F252" t="s">
         <v>726</v>
       </c>
-      <c r="F252" t="s">
-        <v>727</v>
-      </c>
       <c r="G252" t="s">
+        <v>757</v>
+      </c>
+      <c r="H252" t="s">
+        <v>728</v>
+      </c>
+      <c r="I252" t="s">
+        <v>754</v>
+      </c>
+      <c r="J252" t="s">
+        <v>755</v>
+      </c>
+      <c r="K252" t="s">
         <v>758</v>
       </c>
-      <c r="H252" t="s">
-        <v>729</v>
-      </c>
-      <c r="I252" t="s">
-        <v>755</v>
-      </c>
-      <c r="J252" t="s">
-        <v>756</v>
-      </c>
-      <c r="K252" t="s">
+      <c r="L252" t="s">
         <v>759</v>
-      </c>
-      <c r="L252" t="s">
-        <v>760</v>
       </c>
       <c r="M252">
         <v>0</v>
@@ -45105,34 +45106,34 @@
         <v>0</v>
       </c>
       <c r="C253" t="s">
+        <v>724</v>
+      </c>
+      <c r="D253" t="s">
+        <v>689</v>
+      </c>
+      <c r="E253" t="s">
         <v>725</v>
       </c>
-      <c r="D253" t="s">
-        <v>690</v>
-      </c>
-      <c r="E253" t="s">
+      <c r="F253" t="s">
         <v>726</v>
       </c>
-      <c r="F253" t="s">
-        <v>727</v>
-      </c>
       <c r="G253" t="s">
+        <v>760</v>
+      </c>
+      <c r="H253" t="s">
+        <v>728</v>
+      </c>
+      <c r="I253" t="s">
+        <v>754</v>
+      </c>
+      <c r="J253" t="s">
+        <v>755</v>
+      </c>
+      <c r="K253" t="s">
         <v>761</v>
       </c>
-      <c r="H253" t="s">
-        <v>729</v>
-      </c>
-      <c r="I253" t="s">
-        <v>755</v>
-      </c>
-      <c r="J253" t="s">
-        <v>756</v>
-      </c>
-      <c r="K253" t="s">
+      <c r="L253" t="s">
         <v>762</v>
-      </c>
-      <c r="L253" t="s">
-        <v>763</v>
       </c>
       <c r="M253">
         <v>0</v>
@@ -45162,34 +45163,34 @@
         <v>0</v>
       </c>
       <c r="C254" t="s">
+        <v>724</v>
+      </c>
+      <c r="D254" t="s">
+        <v>693</v>
+      </c>
+      <c r="E254" t="s">
         <v>725</v>
       </c>
-      <c r="D254" t="s">
-        <v>694</v>
-      </c>
-      <c r="E254" t="s">
+      <c r="F254" t="s">
         <v>726</v>
       </c>
-      <c r="F254" t="s">
-        <v>727</v>
-      </c>
       <c r="G254" t="s">
+        <v>763</v>
+      </c>
+      <c r="H254" t="s">
+        <v>728</v>
+      </c>
+      <c r="I254" t="s">
         <v>764</v>
       </c>
-      <c r="H254" t="s">
-        <v>729</v>
-      </c>
-      <c r="I254" t="s">
+      <c r="J254" t="s">
         <v>765</v>
       </c>
-      <c r="J254" t="s">
+      <c r="K254" t="s">
         <v>766</v>
       </c>
-      <c r="K254" t="s">
+      <c r="L254" t="s">
         <v>767</v>
-      </c>
-      <c r="L254" t="s">
-        <v>768</v>
       </c>
       <c r="M254">
         <v>0</v>
@@ -45219,34 +45220,34 @@
         <v>0</v>
       </c>
       <c r="C255" t="s">
+        <v>724</v>
+      </c>
+      <c r="D255" t="s">
+        <v>697</v>
+      </c>
+      <c r="E255" t="s">
         <v>725</v>
       </c>
-      <c r="D255" t="s">
-        <v>698</v>
-      </c>
-      <c r="E255" t="s">
+      <c r="F255" t="s">
         <v>726</v>
       </c>
-      <c r="F255" t="s">
-        <v>727</v>
-      </c>
       <c r="G255" t="s">
+        <v>768</v>
+      </c>
+      <c r="H255" t="s">
+        <v>728</v>
+      </c>
+      <c r="I255" t="s">
+        <v>764</v>
+      </c>
+      <c r="J255" t="s">
+        <v>765</v>
+      </c>
+      <c r="K255" t="s">
+        <v>766</v>
+      </c>
+      <c r="L255" t="s">
         <v>769</v>
-      </c>
-      <c r="H255" t="s">
-        <v>729</v>
-      </c>
-      <c r="I255" t="s">
-        <v>765</v>
-      </c>
-      <c r="J255" t="s">
-        <v>766</v>
-      </c>
-      <c r="K255" t="s">
-        <v>767</v>
-      </c>
-      <c r="L255" t="s">
-        <v>770</v>
       </c>
       <c r="M255">
         <v>0</v>
@@ -45276,34 +45277,34 @@
         <v>0</v>
       </c>
       <c r="C256" t="s">
+        <v>724</v>
+      </c>
+      <c r="D256" t="s">
+        <v>701</v>
+      </c>
+      <c r="E256" t="s">
         <v>725</v>
       </c>
-      <c r="D256" t="s">
-        <v>702</v>
-      </c>
-      <c r="E256" t="s">
+      <c r="F256" t="s">
         <v>726</v>
       </c>
-      <c r="F256" t="s">
-        <v>727</v>
-      </c>
       <c r="G256" t="s">
+        <v>770</v>
+      </c>
+      <c r="H256" t="s">
+        <v>728</v>
+      </c>
+      <c r="I256" t="s">
+        <v>764</v>
+      </c>
+      <c r="J256" t="s">
+        <v>765</v>
+      </c>
+      <c r="K256" t="s">
+        <v>766</v>
+      </c>
+      <c r="L256" t="s">
         <v>771</v>
-      </c>
-      <c r="H256" t="s">
-        <v>729</v>
-      </c>
-      <c r="I256" t="s">
-        <v>765</v>
-      </c>
-      <c r="J256" t="s">
-        <v>766</v>
-      </c>
-      <c r="K256" t="s">
-        <v>767</v>
-      </c>
-      <c r="L256" t="s">
-        <v>772</v>
       </c>
       <c r="M256">
         <v>0</v>
@@ -45333,37 +45334,37 @@
         <v>0</v>
       </c>
       <c r="C257" t="s">
+        <v>724</v>
+      </c>
+      <c r="D257" t="s">
+        <v>705</v>
+      </c>
+      <c r="E257" t="s">
         <v>725</v>
       </c>
-      <c r="D257" t="s">
-        <v>706</v>
-      </c>
-      <c r="E257" t="s">
+      <c r="F257" t="s">
         <v>726</v>
       </c>
-      <c r="F257" t="s">
-        <v>727</v>
-      </c>
       <c r="G257" t="s">
+        <v>772</v>
+      </c>
+      <c r="H257" t="s">
+        <v>728</v>
+      </c>
+      <c r="I257" t="s">
+        <v>764</v>
+      </c>
+      <c r="J257" t="s">
         <v>773</v>
       </c>
-      <c r="H257" t="s">
-        <v>729</v>
-      </c>
-      <c r="I257" t="s">
-        <v>765</v>
-      </c>
-      <c r="J257" t="s">
+      <c r="K257" t="s">
         <v>774</v>
       </c>
-      <c r="K257" t="s">
+      <c r="L257" t="s">
+        <v>767</v>
+      </c>
+      <c r="M257" t="s">
         <v>775</v>
-      </c>
-      <c r="L257" t="s">
-        <v>768</v>
-      </c>
-      <c r="M257" t="s">
-        <v>776</v>
       </c>
       <c r="N257">
         <v>0</v>
@@ -45390,37 +45391,37 @@
         <v>0</v>
       </c>
       <c r="C258" t="s">
+        <v>724</v>
+      </c>
+      <c r="D258" t="s">
+        <v>709</v>
+      </c>
+      <c r="E258" t="s">
         <v>725</v>
       </c>
-      <c r="D258" t="s">
-        <v>710</v>
-      </c>
-      <c r="E258" t="s">
+      <c r="F258" t="s">
         <v>726</v>
       </c>
-      <c r="F258" t="s">
-        <v>727</v>
-      </c>
       <c r="G258" t="s">
+        <v>776</v>
+      </c>
+      <c r="H258" t="s">
+        <v>728</v>
+      </c>
+      <c r="I258" t="s">
+        <v>764</v>
+      </c>
+      <c r="J258" t="s">
+        <v>773</v>
+      </c>
+      <c r="K258" t="s">
+        <v>774</v>
+      </c>
+      <c r="L258" t="s">
+        <v>769</v>
+      </c>
+      <c r="M258" t="s">
         <v>777</v>
-      </c>
-      <c r="H258" t="s">
-        <v>729</v>
-      </c>
-      <c r="I258" t="s">
-        <v>765</v>
-      </c>
-      <c r="J258" t="s">
-        <v>774</v>
-      </c>
-      <c r="K258" t="s">
-        <v>775</v>
-      </c>
-      <c r="L258" t="s">
-        <v>770</v>
-      </c>
-      <c r="M258" t="s">
-        <v>778</v>
       </c>
       <c r="N258">
         <v>0</v>
@@ -45447,37 +45448,37 @@
         <v>0</v>
       </c>
       <c r="C259" t="s">
+        <v>724</v>
+      </c>
+      <c r="D259" t="s">
+        <v>713</v>
+      </c>
+      <c r="E259" t="s">
         <v>725</v>
       </c>
-      <c r="D259" t="s">
-        <v>714</v>
-      </c>
-      <c r="E259" t="s">
+      <c r="F259" t="s">
         <v>726</v>
       </c>
-      <c r="F259" t="s">
-        <v>727</v>
-      </c>
       <c r="G259" t="s">
+        <v>778</v>
+      </c>
+      <c r="H259" t="s">
+        <v>728</v>
+      </c>
+      <c r="I259" t="s">
+        <v>764</v>
+      </c>
+      <c r="J259" t="s">
+        <v>773</v>
+      </c>
+      <c r="K259" t="s">
+        <v>774</v>
+      </c>
+      <c r="L259" t="s">
+        <v>769</v>
+      </c>
+      <c r="M259" t="s">
         <v>779</v>
-      </c>
-      <c r="H259" t="s">
-        <v>729</v>
-      </c>
-      <c r="I259" t="s">
-        <v>765</v>
-      </c>
-      <c r="J259" t="s">
-        <v>774</v>
-      </c>
-      <c r="K259" t="s">
-        <v>775</v>
-      </c>
-      <c r="L259" t="s">
-        <v>770</v>
-      </c>
-      <c r="M259" t="s">
-        <v>780</v>
       </c>
       <c r="N259">
         <v>0</v>
@@ -45504,40 +45505,40 @@
         <v>0</v>
       </c>
       <c r="C260" t="s">
+        <v>724</v>
+      </c>
+      <c r="D260" t="s">
+        <v>717</v>
+      </c>
+      <c r="E260" t="s">
         <v>725</v>
       </c>
-      <c r="D260" t="s">
-        <v>718</v>
-      </c>
-      <c r="E260" t="s">
+      <c r="F260" t="s">
         <v>726</v>
       </c>
-      <c r="F260" t="s">
-        <v>727</v>
-      </c>
       <c r="G260" t="s">
+        <v>780</v>
+      </c>
+      <c r="H260" t="s">
+        <v>728</v>
+      </c>
+      <c r="I260" t="s">
+        <v>764</v>
+      </c>
+      <c r="J260" t="s">
+        <v>773</v>
+      </c>
+      <c r="K260" t="s">
+        <v>774</v>
+      </c>
+      <c r="L260" t="s">
+        <v>769</v>
+      </c>
+      <c r="M260" t="s">
+        <v>779</v>
+      </c>
+      <c r="N260" t="s">
         <v>781</v>
-      </c>
-      <c r="H260" t="s">
-        <v>729</v>
-      </c>
-      <c r="I260" t="s">
-        <v>765</v>
-      </c>
-      <c r="J260" t="s">
-        <v>774</v>
-      </c>
-      <c r="K260" t="s">
-        <v>775</v>
-      </c>
-      <c r="L260" t="s">
-        <v>770</v>
-      </c>
-      <c r="M260" t="s">
-        <v>780</v>
-      </c>
-      <c r="N260" t="s">
-        <v>782</v>
       </c>
       <c r="O260">
         <v>0</v>
@@ -45561,43 +45562,43 @@
         <v>0</v>
       </c>
       <c r="C261" t="s">
+        <v>724</v>
+      </c>
+      <c r="D261" t="s">
+        <v>722</v>
+      </c>
+      <c r="E261" t="s">
         <v>725</v>
       </c>
-      <c r="D261" t="s">
-        <v>723</v>
-      </c>
-      <c r="E261" t="s">
+      <c r="F261" t="s">
         <v>726</v>
       </c>
-      <c r="F261" t="s">
-        <v>727</v>
-      </c>
       <c r="G261" t="s">
+        <v>782</v>
+      </c>
+      <c r="H261" t="s">
+        <v>728</v>
+      </c>
+      <c r="I261" t="s">
+        <v>764</v>
+      </c>
+      <c r="J261" t="s">
+        <v>773</v>
+      </c>
+      <c r="K261" t="s">
+        <v>774</v>
+      </c>
+      <c r="L261" t="s">
+        <v>769</v>
+      </c>
+      <c r="M261" t="s">
+        <v>779</v>
+      </c>
+      <c r="N261" t="s">
         <v>783</v>
       </c>
-      <c r="H261" t="s">
-        <v>729</v>
-      </c>
-      <c r="I261" t="s">
-        <v>765</v>
-      </c>
-      <c r="J261" t="s">
-        <v>774</v>
-      </c>
-      <c r="K261" t="s">
-        <v>775</v>
-      </c>
-      <c r="L261" t="s">
-        <v>770</v>
-      </c>
-      <c r="M261" t="s">
-        <v>780</v>
-      </c>
-      <c r="N261" t="s">
+      <c r="O261" t="s">
         <v>784</v>
-      </c>
-      <c r="O261" t="s">
-        <v>785</v>
       </c>
       <c r="P261">
         <v>0</v>
@@ -45618,46 +45619,46 @@
         <v>0</v>
       </c>
       <c r="C262" t="s">
+        <v>724</v>
+      </c>
+      <c r="D262" t="s">
+        <v>723</v>
+      </c>
+      <c r="E262" t="s">
         <v>725</v>
       </c>
-      <c r="D262" t="s">
-        <v>724</v>
-      </c>
-      <c r="E262" t="s">
+      <c r="F262" t="s">
         <v>726</v>
       </c>
-      <c r="F262" t="s">
-        <v>727</v>
-      </c>
       <c r="G262" t="s">
+        <v>785</v>
+      </c>
+      <c r="H262" t="s">
+        <v>728</v>
+      </c>
+      <c r="I262" t="s">
+        <v>764</v>
+      </c>
+      <c r="J262" t="s">
+        <v>773</v>
+      </c>
+      <c r="K262" t="s">
+        <v>774</v>
+      </c>
+      <c r="L262" t="s">
+        <v>769</v>
+      </c>
+      <c r="M262" t="s">
+        <v>779</v>
+      </c>
+      <c r="N262" t="s">
         <v>786</v>
       </c>
-      <c r="H262" t="s">
-        <v>729</v>
-      </c>
-      <c r="I262" t="s">
-        <v>765</v>
-      </c>
-      <c r="J262" t="s">
-        <v>774</v>
-      </c>
-      <c r="K262" t="s">
-        <v>775</v>
-      </c>
-      <c r="L262" t="s">
-        <v>770</v>
-      </c>
-      <c r="M262" t="s">
-        <v>780</v>
-      </c>
-      <c r="N262" t="s">
+      <c r="O262" t="s">
         <v>787</v>
       </c>
-      <c r="O262" t="s">
+      <c r="P262" t="s">
         <v>788</v>
-      </c>
-      <c r="P262" t="s">
-        <v>789</v>
       </c>
       <c r="Q262">
         <v>0</v>
@@ -45675,22 +45676,22 @@
         <v>0</v>
       </c>
       <c r="C263" t="s">
+        <v>653</v>
+      </c>
+      <c r="D263" t="s">
         <v>654</v>
       </c>
-      <c r="D263" t="s">
+      <c r="E263" t="s">
         <v>655</v>
       </c>
-      <c r="E263" t="s">
+      <c r="F263" t="s">
         <v>656</v>
       </c>
-      <c r="F263" t="s">
+      <c r="G263" t="s">
         <v>657</v>
       </c>
-      <c r="G263" t="s">
+      <c r="H263" t="s">
         <v>658</v>
-      </c>
-      <c r="H263" t="s">
-        <v>659</v>
       </c>
       <c r="I263">
         <v>0</v>
@@ -45732,25 +45733,25 @@
         <v>0</v>
       </c>
       <c r="C264" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D264" t="s">
+        <v>659</v>
+      </c>
+      <c r="E264" t="s">
+        <v>655</v>
+      </c>
+      <c r="F264" t="s">
+        <v>656</v>
+      </c>
+      <c r="G264" t="s">
+        <v>657</v>
+      </c>
+      <c r="H264" t="s">
         <v>660</v>
       </c>
-      <c r="E264" t="s">
-        <v>656</v>
-      </c>
-      <c r="F264" t="s">
-        <v>657</v>
-      </c>
-      <c r="G264" t="s">
-        <v>658</v>
-      </c>
-      <c r="H264" t="s">
+      <c r="I264" t="s">
         <v>661</v>
-      </c>
-      <c r="I264" t="s">
-        <v>662</v>
       </c>
       <c r="J264">
         <v>0</v>
@@ -45789,28 +45790,28 @@
         <v>0</v>
       </c>
       <c r="C265" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D265" t="s">
+        <v>662</v>
+      </c>
+      <c r="E265" t="s">
+        <v>655</v>
+      </c>
+      <c r="F265" t="s">
+        <v>656</v>
+      </c>
+      <c r="G265" t="s">
+        <v>657</v>
+      </c>
+      <c r="H265" t="s">
         <v>663</v>
       </c>
-      <c r="E265" t="s">
-        <v>656</v>
-      </c>
-      <c r="F265" t="s">
-        <v>657</v>
-      </c>
-      <c r="G265" t="s">
-        <v>658</v>
-      </c>
-      <c r="H265" t="s">
+      <c r="I265" t="s">
+        <v>661</v>
+      </c>
+      <c r="J265" t="s">
         <v>664</v>
-      </c>
-      <c r="I265" t="s">
-        <v>662</v>
-      </c>
-      <c r="J265" t="s">
-        <v>665</v>
       </c>
       <c r="K265">
         <v>0</v>
@@ -45846,28 +45847,28 @@
         <v>0</v>
       </c>
       <c r="C266" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D266" t="s">
+        <v>665</v>
+      </c>
+      <c r="E266" t="s">
+        <v>655</v>
+      </c>
+      <c r="F266" t="s">
+        <v>656</v>
+      </c>
+      <c r="G266" t="s">
         <v>666</v>
       </c>
-      <c r="E266" t="s">
-        <v>656</v>
-      </c>
-      <c r="F266" t="s">
-        <v>657</v>
-      </c>
-      <c r="G266" t="s">
+      <c r="H266" t="s">
+        <v>663</v>
+      </c>
+      <c r="I266" t="s">
         <v>667</v>
       </c>
-      <c r="H266" t="s">
+      <c r="J266" t="s">
         <v>664</v>
-      </c>
-      <c r="I266" t="s">
-        <v>668</v>
-      </c>
-      <c r="J266" t="s">
-        <v>665</v>
       </c>
       <c r="K266">
         <v>0</v>
@@ -45903,28 +45904,28 @@
         <v>0</v>
       </c>
       <c r="C267" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D267" t="s">
+        <v>668</v>
+      </c>
+      <c r="E267" t="s">
+        <v>655</v>
+      </c>
+      <c r="F267" t="s">
+        <v>656</v>
+      </c>
+      <c r="G267" t="s">
         <v>669</v>
       </c>
-      <c r="E267" t="s">
-        <v>656</v>
-      </c>
-      <c r="F267" t="s">
-        <v>657</v>
-      </c>
-      <c r="G267" t="s">
+      <c r="H267" t="s">
+        <v>663</v>
+      </c>
+      <c r="I267" t="s">
+        <v>667</v>
+      </c>
+      <c r="J267" t="s">
         <v>670</v>
-      </c>
-      <c r="H267" t="s">
-        <v>664</v>
-      </c>
-      <c r="I267" t="s">
-        <v>668</v>
-      </c>
-      <c r="J267" t="s">
-        <v>671</v>
       </c>
       <c r="K267">
         <v>0</v>
@@ -45960,31 +45961,31 @@
         <v>0</v>
       </c>
       <c r="C268" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D268" t="s">
+        <v>671</v>
+      </c>
+      <c r="E268" t="s">
+        <v>655</v>
+      </c>
+      <c r="F268" t="s">
+        <v>656</v>
+      </c>
+      <c r="G268" t="s">
         <v>672</v>
       </c>
-      <c r="E268" t="s">
-        <v>656</v>
-      </c>
-      <c r="F268" t="s">
-        <v>657</v>
-      </c>
-      <c r="G268" t="s">
+      <c r="H268" t="s">
+        <v>663</v>
+      </c>
+      <c r="I268" t="s">
+        <v>667</v>
+      </c>
+      <c r="J268" t="s">
+        <v>670</v>
+      </c>
+      <c r="K268" t="s">
         <v>673</v>
-      </c>
-      <c r="H268" t="s">
-        <v>664</v>
-      </c>
-      <c r="I268" t="s">
-        <v>668</v>
-      </c>
-      <c r="J268" t="s">
-        <v>671</v>
-      </c>
-      <c r="K268" t="s">
-        <v>674</v>
       </c>
       <c r="L268">
         <v>0</v>
@@ -46017,31 +46018,31 @@
         <v>0</v>
       </c>
       <c r="C269" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D269" t="s">
+        <v>674</v>
+      </c>
+      <c r="E269" t="s">
+        <v>655</v>
+      </c>
+      <c r="F269" t="s">
+        <v>656</v>
+      </c>
+      <c r="G269" t="s">
         <v>675</v>
       </c>
-      <c r="E269" t="s">
-        <v>656</v>
-      </c>
-      <c r="F269" t="s">
-        <v>657</v>
-      </c>
-      <c r="G269" t="s">
+      <c r="H269" t="s">
         <v>676</v>
       </c>
-      <c r="H269" t="s">
+      <c r="I269" t="s">
+        <v>670</v>
+      </c>
+      <c r="J269" t="s">
         <v>677</v>
       </c>
-      <c r="I269" t="s">
-        <v>671</v>
-      </c>
-      <c r="J269" t="s">
+      <c r="K269" t="s">
         <v>678</v>
-      </c>
-      <c r="K269" t="s">
-        <v>679</v>
       </c>
       <c r="L269">
         <v>0</v>
@@ -46074,31 +46075,31 @@
         <v>0</v>
       </c>
       <c r="C270" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D270" t="s">
+        <v>679</v>
+      </c>
+      <c r="E270" t="s">
+        <v>655</v>
+      </c>
+      <c r="F270" t="s">
+        <v>656</v>
+      </c>
+      <c r="G270" t="s">
+        <v>663</v>
+      </c>
+      <c r="H270" t="s">
+        <v>676</v>
+      </c>
+      <c r="I270" t="s">
+        <v>670</v>
+      </c>
+      <c r="J270" t="s">
+        <v>677</v>
+      </c>
+      <c r="K270" t="s">
         <v>680</v>
-      </c>
-      <c r="E270" t="s">
-        <v>656</v>
-      </c>
-      <c r="F270" t="s">
-        <v>657</v>
-      </c>
-      <c r="G270" t="s">
-        <v>664</v>
-      </c>
-      <c r="H270" t="s">
-        <v>677</v>
-      </c>
-      <c r="I270" t="s">
-        <v>671</v>
-      </c>
-      <c r="J270" t="s">
-        <v>678</v>
-      </c>
-      <c r="K270" t="s">
-        <v>681</v>
       </c>
       <c r="L270">
         <v>0</v>
@@ -46131,31 +46132,31 @@
         <v>0</v>
       </c>
       <c r="C271" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D271" t="s">
+        <v>681</v>
+      </c>
+      <c r="E271" t="s">
+        <v>655</v>
+      </c>
+      <c r="F271" t="s">
+        <v>656</v>
+      </c>
+      <c r="G271" t="s">
+        <v>676</v>
+      </c>
+      <c r="H271" t="s">
         <v>682</v>
       </c>
-      <c r="E271" t="s">
-        <v>656</v>
-      </c>
-      <c r="F271" t="s">
-        <v>657</v>
-      </c>
-      <c r="G271" t="s">
+      <c r="I271" t="s">
         <v>677</v>
       </c>
-      <c r="H271" t="s">
+      <c r="J271" t="s">
         <v>683</v>
       </c>
-      <c r="I271" t="s">
-        <v>678</v>
-      </c>
-      <c r="J271" t="s">
+      <c r="K271" t="s">
         <v>684</v>
-      </c>
-      <c r="K271" t="s">
-        <v>685</v>
       </c>
       <c r="L271">
         <v>0</v>
@@ -46188,31 +46189,31 @@
         <v>0</v>
       </c>
       <c r="C272" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D272" t="s">
+        <v>685</v>
+      </c>
+      <c r="E272" t="s">
+        <v>655</v>
+      </c>
+      <c r="F272" t="s">
+        <v>656</v>
+      </c>
+      <c r="G272" t="s">
+        <v>682</v>
+      </c>
+      <c r="H272" t="s">
         <v>686</v>
       </c>
-      <c r="E272" t="s">
-        <v>656</v>
-      </c>
-      <c r="F272" t="s">
-        <v>657</v>
-      </c>
-      <c r="G272" t="s">
+      <c r="I272" t="s">
         <v>683</v>
       </c>
-      <c r="H272" t="s">
+      <c r="J272" t="s">
         <v>687</v>
       </c>
-      <c r="I272" t="s">
-        <v>684</v>
-      </c>
-      <c r="J272" t="s">
+      <c r="K272" t="s">
         <v>688</v>
-      </c>
-      <c r="K272" t="s">
-        <v>689</v>
       </c>
       <c r="L272">
         <v>0</v>
@@ -46245,31 +46246,31 @@
         <v>0</v>
       </c>
       <c r="C273" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D273" t="s">
+        <v>689</v>
+      </c>
+      <c r="E273" t="s">
+        <v>655</v>
+      </c>
+      <c r="F273" t="s">
+        <v>656</v>
+      </c>
+      <c r="G273" t="s">
+        <v>686</v>
+      </c>
+      <c r="H273" t="s">
         <v>690</v>
       </c>
-      <c r="E273" t="s">
-        <v>656</v>
-      </c>
-      <c r="F273" t="s">
-        <v>657</v>
-      </c>
-      <c r="G273" t="s">
+      <c r="I273" t="s">
         <v>687</v>
       </c>
-      <c r="H273" t="s">
+      <c r="J273" t="s">
         <v>691</v>
       </c>
-      <c r="I273" t="s">
-        <v>688</v>
-      </c>
-      <c r="J273" t="s">
+      <c r="K273" t="s">
         <v>692</v>
-      </c>
-      <c r="K273" t="s">
-        <v>693</v>
       </c>
       <c r="L273">
         <v>0</v>
@@ -46302,31 +46303,31 @@
         <v>0</v>
       </c>
       <c r="C274" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D274" t="s">
+        <v>693</v>
+      </c>
+      <c r="E274" t="s">
+        <v>655</v>
+      </c>
+      <c r="F274" t="s">
+        <v>656</v>
+      </c>
+      <c r="G274" t="s">
+        <v>690</v>
+      </c>
+      <c r="H274" t="s">
         <v>694</v>
       </c>
-      <c r="E274" t="s">
-        <v>656</v>
-      </c>
-      <c r="F274" t="s">
-        <v>657</v>
-      </c>
-      <c r="G274" t="s">
+      <c r="I274" t="s">
         <v>691</v>
       </c>
-      <c r="H274" t="s">
+      <c r="J274" t="s">
         <v>695</v>
       </c>
-      <c r="I274" t="s">
-        <v>692</v>
-      </c>
-      <c r="J274" t="s">
+      <c r="K274" t="s">
         <v>696</v>
-      </c>
-      <c r="K274" t="s">
-        <v>697</v>
       </c>
       <c r="L274">
         <v>0</v>
@@ -46359,31 +46360,31 @@
         <v>0</v>
       </c>
       <c r="C275" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D275" t="s">
+        <v>697</v>
+      </c>
+      <c r="E275" t="s">
+        <v>655</v>
+      </c>
+      <c r="F275" t="s">
+        <v>656</v>
+      </c>
+      <c r="G275" t="s">
+        <v>694</v>
+      </c>
+      <c r="H275" t="s">
         <v>698</v>
       </c>
-      <c r="E275" t="s">
-        <v>656</v>
-      </c>
-      <c r="F275" t="s">
-        <v>657</v>
-      </c>
-      <c r="G275" t="s">
+      <c r="I275" t="s">
         <v>695</v>
       </c>
-      <c r="H275" t="s">
+      <c r="J275" t="s">
         <v>699</v>
       </c>
-      <c r="I275" t="s">
-        <v>696</v>
-      </c>
-      <c r="J275" t="s">
+      <c r="K275" t="s">
         <v>700</v>
-      </c>
-      <c r="K275" t="s">
-        <v>701</v>
       </c>
       <c r="L275">
         <v>0</v>
@@ -46416,31 +46417,31 @@
         <v>0</v>
       </c>
       <c r="C276" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D276" t="s">
+        <v>701</v>
+      </c>
+      <c r="E276" t="s">
+        <v>655</v>
+      </c>
+      <c r="F276" t="s">
+        <v>656</v>
+      </c>
+      <c r="G276" t="s">
+        <v>698</v>
+      </c>
+      <c r="H276" t="s">
         <v>702</v>
       </c>
-      <c r="E276" t="s">
-        <v>656</v>
-      </c>
-      <c r="F276" t="s">
-        <v>657</v>
-      </c>
-      <c r="G276" t="s">
+      <c r="I276" t="s">
         <v>699</v>
       </c>
-      <c r="H276" t="s">
+      <c r="J276" t="s">
         <v>703</v>
       </c>
-      <c r="I276" t="s">
-        <v>700</v>
-      </c>
-      <c r="J276" t="s">
+      <c r="K276" t="s">
         <v>704</v>
-      </c>
-      <c r="K276" t="s">
-        <v>705</v>
       </c>
       <c r="L276">
         <v>0</v>
@@ -46473,31 +46474,31 @@
         <v>0</v>
       </c>
       <c r="C277" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D277" t="s">
+        <v>705</v>
+      </c>
+      <c r="E277" t="s">
+        <v>655</v>
+      </c>
+      <c r="F277" t="s">
+        <v>656</v>
+      </c>
+      <c r="G277" t="s">
+        <v>702</v>
+      </c>
+      <c r="H277" t="s">
         <v>706</v>
       </c>
-      <c r="E277" t="s">
-        <v>656</v>
-      </c>
-      <c r="F277" t="s">
-        <v>657</v>
-      </c>
-      <c r="G277" t="s">
+      <c r="I277" t="s">
         <v>703</v>
       </c>
-      <c r="H277" t="s">
+      <c r="J277" t="s">
         <v>707</v>
       </c>
-      <c r="I277" t="s">
-        <v>704</v>
-      </c>
-      <c r="J277" t="s">
+      <c r="K277" t="s">
         <v>708</v>
-      </c>
-      <c r="K277" t="s">
-        <v>709</v>
       </c>
       <c r="L277">
         <v>0</v>
@@ -46530,31 +46531,31 @@
         <v>0</v>
       </c>
       <c r="C278" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D278" t="s">
+        <v>709</v>
+      </c>
+      <c r="E278" t="s">
+        <v>655</v>
+      </c>
+      <c r="F278" t="s">
+        <v>656</v>
+      </c>
+      <c r="G278" t="s">
+        <v>706</v>
+      </c>
+      <c r="H278" t="s">
         <v>710</v>
       </c>
-      <c r="E278" t="s">
-        <v>656</v>
-      </c>
-      <c r="F278" t="s">
-        <v>657</v>
-      </c>
-      <c r="G278" t="s">
+      <c r="I278" t="s">
         <v>707</v>
       </c>
-      <c r="H278" t="s">
+      <c r="J278" t="s">
         <v>711</v>
       </c>
-      <c r="I278" t="s">
-        <v>708</v>
-      </c>
-      <c r="J278" t="s">
+      <c r="K278" t="s">
         <v>712</v>
-      </c>
-      <c r="K278" t="s">
-        <v>713</v>
       </c>
       <c r="L278">
         <v>0</v>
@@ -46587,31 +46588,31 @@
         <v>0</v>
       </c>
       <c r="C279" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D279" t="s">
+        <v>713</v>
+      </c>
+      <c r="E279" t="s">
+        <v>655</v>
+      </c>
+      <c r="F279" t="s">
+        <v>656</v>
+      </c>
+      <c r="G279" t="s">
+        <v>710</v>
+      </c>
+      <c r="H279" t="s">
         <v>714</v>
       </c>
-      <c r="E279" t="s">
-        <v>656</v>
-      </c>
-      <c r="F279" t="s">
-        <v>657</v>
-      </c>
-      <c r="G279" t="s">
+      <c r="I279" t="s">
         <v>711</v>
       </c>
-      <c r="H279" t="s">
+      <c r="J279" t="s">
         <v>715</v>
       </c>
-      <c r="I279" t="s">
-        <v>712</v>
-      </c>
-      <c r="J279" t="s">
+      <c r="K279" t="s">
         <v>716</v>
-      </c>
-      <c r="K279" t="s">
-        <v>717</v>
       </c>
       <c r="L279">
         <v>0</v>
@@ -46644,34 +46645,34 @@
         <v>0</v>
       </c>
       <c r="C280" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D280" t="s">
+        <v>717</v>
+      </c>
+      <c r="E280" t="s">
+        <v>655</v>
+      </c>
+      <c r="F280" t="s">
+        <v>656</v>
+      </c>
+      <c r="G280" t="s">
+        <v>700</v>
+      </c>
+      <c r="H280" t="s">
         <v>718</v>
       </c>
-      <c r="E280" t="s">
-        <v>656</v>
-      </c>
-      <c r="F280" t="s">
-        <v>657</v>
-      </c>
-      <c r="G280" t="s">
-        <v>701</v>
-      </c>
-      <c r="H280" t="s">
+      <c r="I280" t="s">
         <v>719</v>
       </c>
-      <c r="I280" t="s">
+      <c r="J280" t="s">
+        <v>715</v>
+      </c>
+      <c r="K280" t="s">
         <v>720</v>
       </c>
-      <c r="J280" t="s">
-        <v>716</v>
-      </c>
-      <c r="K280" t="s">
+      <c r="L280" t="s">
         <v>721</v>
-      </c>
-      <c r="L280" t="s">
-        <v>722</v>
       </c>
       <c r="M280">
         <v>0</v>
@@ -46701,34 +46702,34 @@
         <v>0</v>
       </c>
       <c r="C281" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D281" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E281" t="s">
+        <v>655</v>
+      </c>
+      <c r="F281" t="s">
         <v>656</v>
       </c>
-      <c r="F281" t="s">
-        <v>657</v>
-      </c>
       <c r="G281" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H281" t="s">
+        <v>718</v>
+      </c>
+      <c r="I281" t="s">
         <v>719</v>
       </c>
-      <c r="I281" t="s">
+      <c r="J281" t="s">
+        <v>715</v>
+      </c>
+      <c r="K281" t="s">
         <v>720</v>
       </c>
-      <c r="J281" t="s">
-        <v>716</v>
-      </c>
-      <c r="K281" t="s">
+      <c r="L281" t="s">
         <v>721</v>
-      </c>
-      <c r="L281" t="s">
-        <v>722</v>
       </c>
       <c r="M281">
         <v>0</v>
@@ -46758,34 +46759,34 @@
         <v>0</v>
       </c>
       <c r="C282" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D282" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E282" t="s">
+        <v>655</v>
+      </c>
+      <c r="F282" t="s">
         <v>656</v>
       </c>
-      <c r="F282" t="s">
-        <v>657</v>
-      </c>
       <c r="G282" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H282" t="s">
+        <v>718</v>
+      </c>
+      <c r="I282" t="s">
         <v>719</v>
       </c>
-      <c r="I282" t="s">
+      <c r="J282" t="s">
+        <v>715</v>
+      </c>
+      <c r="K282" t="s">
         <v>720</v>
       </c>
-      <c r="J282" t="s">
-        <v>716</v>
-      </c>
-      <c r="K282" t="s">
+      <c r="L282" t="s">
         <v>721</v>
-      </c>
-      <c r="L282" t="s">
-        <v>722</v>
       </c>
       <c r="M282">
         <v>0</v>
@@ -46815,16 +46816,16 @@
         <v>0</v>
       </c>
       <c r="C283" t="s">
+        <v>789</v>
+      </c>
+      <c r="D283" t="s">
         <v>790</v>
       </c>
-      <c r="D283" t="s">
+      <c r="E283" t="s">
         <v>791</v>
       </c>
-      <c r="E283" t="s">
+      <c r="F283" t="s">
         <v>792</v>
-      </c>
-      <c r="F283" t="s">
-        <v>793</v>
       </c>
       <c r="G283">
         <v>0</v>
@@ -46872,16 +46873,16 @@
         <v>0</v>
       </c>
       <c r="C284" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D284" t="s">
+        <v>793</v>
+      </c>
+      <c r="E284" t="s">
         <v>794</v>
       </c>
-      <c r="E284" t="s">
+      <c r="F284" t="s">
         <v>795</v>
-      </c>
-      <c r="F284" t="s">
-        <v>796</v>
       </c>
       <c r="G284">
         <v>0.1</v>
@@ -46929,16 +46930,16 @@
         <v>0</v>
       </c>
       <c r="C285" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D285" t="s">
+        <v>796</v>
+      </c>
+      <c r="E285" t="s">
         <v>797</v>
       </c>
-      <c r="E285" t="s">
+      <c r="F285" t="s">
         <v>798</v>
-      </c>
-      <c r="F285" t="s">
-        <v>799</v>
       </c>
       <c r="G285">
         <v>0</v>
@@ -46986,16 +46987,16 @@
         <v>0</v>
       </c>
       <c r="C286" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D286" t="s">
+        <v>799</v>
+      </c>
+      <c r="E286" t="s">
         <v>800</v>
       </c>
-      <c r="E286" t="s">
+      <c r="F286" t="s">
         <v>801</v>
-      </c>
-      <c r="F286" t="s">
-        <v>802</v>
       </c>
       <c r="G286">
         <v>0</v>
@@ -47043,16 +47044,16 @@
         <v>0</v>
       </c>
       <c r="C287" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D287" t="s">
+        <v>802</v>
+      </c>
+      <c r="E287" t="s">
         <v>803</v>
       </c>
-      <c r="E287" t="s">
+      <c r="F287" t="s">
         <v>804</v>
-      </c>
-      <c r="F287" t="s">
-        <v>805</v>
       </c>
       <c r="G287">
         <v>0.2</v>
@@ -47100,16 +47101,16 @@
         <v>0</v>
       </c>
       <c r="C288" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D288" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="E288" s="3" t="s">
         <v>992</v>
       </c>
-      <c r="E288" s="3" t="s">
-        <v>993</v>
-      </c>
       <c r="F288" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G288">
         <v>0.5</v>
@@ -47157,16 +47158,16 @@
         <v>0</v>
       </c>
       <c r="C289" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="D289" t="s">
+        <v>806</v>
+      </c>
+      <c r="E289" t="s">
         <v>807</v>
       </c>
-      <c r="E289" t="s">
+      <c r="F289" t="s">
         <v>808</v>
-      </c>
-      <c r="F289" t="s">
-        <v>809</v>
       </c>
       <c r="G289">
         <v>30</v>
@@ -47214,16 +47215,16 @@
         <v>0</v>
       </c>
       <c r="C290" t="s">
+        <v>809</v>
+      </c>
+      <c r="D290" t="s">
         <v>810</v>
       </c>
-      <c r="D290" t="s">
+      <c r="E290" t="s">
         <v>811</v>
       </c>
-      <c r="E290" t="s">
+      <c r="F290" t="s">
         <v>812</v>
-      </c>
-      <c r="F290" t="s">
-        <v>813</v>
       </c>
       <c r="G290">
         <v>0.75</v>
@@ -47271,13 +47272,13 @@
         <v>0</v>
       </c>
       <c r="C291" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D291" t="s">
+        <v>813</v>
+      </c>
+      <c r="E291" t="s">
         <v>814</v>
-      </c>
-      <c r="E291" t="s">
-        <v>815</v>
       </c>
       <c r="F291">
         <v>0</v>
@@ -47328,16 +47329,16 @@
         <v>0</v>
       </c>
       <c r="C292" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D292" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E292" t="s">
         <v>588</v>
       </c>
       <c r="F292" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="G292">
         <v>45</v>
@@ -47385,16 +47386,16 @@
         <v>0</v>
       </c>
       <c r="C293" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D293" t="s">
+        <v>817</v>
+      </c>
+      <c r="E293" t="s">
         <v>818</v>
       </c>
-      <c r="E293" t="s">
+      <c r="F293" t="s">
         <v>819</v>
-      </c>
-      <c r="F293" t="s">
-        <v>820</v>
       </c>
       <c r="G293">
         <v>0</v>
@@ -47442,16 +47443,16 @@
         <v>0</v>
       </c>
       <c r="C294" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D294" t="s">
+        <v>820</v>
+      </c>
+      <c r="E294" t="s">
         <v>821</v>
       </c>
-      <c r="E294" t="s">
+      <c r="F294" t="s">
         <v>822</v>
-      </c>
-      <c r="F294" t="s">
-        <v>823</v>
       </c>
       <c r="G294">
         <v>0.1</v>
@@ -47499,16 +47500,16 @@
         <v>0</v>
       </c>
       <c r="C295" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D295" t="s">
+        <v>907</v>
+      </c>
+      <c r="E295" t="s">
         <v>908</v>
       </c>
-      <c r="E295" t="s">
+      <c r="F295" t="s">
         <v>909</v>
-      </c>
-      <c r="F295" t="s">
-        <v>910</v>
       </c>
       <c r="G295">
         <v>50000</v>
@@ -47556,16 +47557,16 @@
         <v>0</v>
       </c>
       <c r="C296" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D296" t="s">
+        <v>910</v>
+      </c>
+      <c r="E296" t="s">
         <v>911</v>
       </c>
-      <c r="E296" t="s">
+      <c r="F296" t="s">
         <v>912</v>
-      </c>
-      <c r="F296" t="s">
-        <v>913</v>
       </c>
       <c r="G296">
         <v>10</v>
@@ -47613,16 +47614,16 @@
         <v>0</v>
       </c>
       <c r="C297" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D297" t="s">
+        <v>913</v>
+      </c>
+      <c r="E297" t="s">
         <v>914</v>
       </c>
-      <c r="E297" t="s">
+      <c r="F297" t="s">
         <v>915</v>
-      </c>
-      <c r="F297" t="s">
-        <v>916</v>
       </c>
       <c r="G297">
         <v>75</v>
@@ -47670,16 +47671,16 @@
         <v>0</v>
       </c>
       <c r="C298" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D298" t="s">
+        <v>916</v>
+      </c>
+      <c r="E298" t="s">
         <v>917</v>
       </c>
-      <c r="E298" t="s">
+      <c r="F298" t="s">
         <v>918</v>
-      </c>
-      <c r="F298" t="s">
-        <v>919</v>
       </c>
       <c r="G298">
         <v>25</v>
@@ -47727,16 +47728,16 @@
         <v>0</v>
       </c>
       <c r="C299" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D299" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E299" t="s">
         <v>588</v>
       </c>
       <c r="F299" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="G299">
         <v>5</v>
@@ -47784,16 +47785,16 @@
         <v>0</v>
       </c>
       <c r="C300" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D300" t="s">
+        <v>921</v>
+      </c>
+      <c r="E300" t="s">
         <v>922</v>
       </c>
-      <c r="E300" t="s">
+      <c r="F300" t="s">
         <v>923</v>
-      </c>
-      <c r="F300" t="s">
-        <v>924</v>
       </c>
       <c r="G300">
         <v>0.6</v>
@@ -47841,16 +47842,16 @@
         <v>0</v>
       </c>
       <c r="C301" t="s">
+        <v>846</v>
+      </c>
+      <c r="D301" t="s">
         <v>847</v>
       </c>
-      <c r="D301" t="s">
+      <c r="E301" t="s">
         <v>848</v>
       </c>
-      <c r="E301" t="s">
+      <c r="F301" t="s">
         <v>849</v>
-      </c>
-      <c r="F301" t="s">
-        <v>850</v>
       </c>
       <c r="G301">
         <v>25</v>
@@ -47859,7 +47860,7 @@
         <v>25</v>
       </c>
       <c r="I301" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="J301">
         <v>0</v>
@@ -47898,16 +47899,16 @@
         <v>0</v>
       </c>
       <c r="C302" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D302" t="s">
+        <v>851</v>
+      </c>
+      <c r="E302" t="s">
+        <v>848</v>
+      </c>
+      <c r="F302" t="s">
         <v>852</v>
-      </c>
-      <c r="E302" t="s">
-        <v>849</v>
-      </c>
-      <c r="F302" t="s">
-        <v>853</v>
       </c>
       <c r="G302">
         <v>20</v>
@@ -47916,7 +47917,7 @@
         <v>20</v>
       </c>
       <c r="I302" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="J302">
         <v>0</v>
@@ -47955,16 +47956,16 @@
         <v>0</v>
       </c>
       <c r="C303" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D303" t="s">
+        <v>853</v>
+      </c>
+      <c r="E303" t="s">
+        <v>848</v>
+      </c>
+      <c r="F303" t="s">
         <v>854</v>
-      </c>
-      <c r="E303" t="s">
-        <v>849</v>
-      </c>
-      <c r="F303" t="s">
-        <v>855</v>
       </c>
       <c r="G303">
         <v>3</v>
@@ -47973,7 +47974,7 @@
         <v>1.5</v>
       </c>
       <c r="I303" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="J303">
         <v>0</v>
@@ -48012,16 +48013,16 @@
         <v>0</v>
       </c>
       <c r="C304" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D304" t="s">
+        <v>855</v>
+      </c>
+      <c r="E304" t="s">
+        <v>848</v>
+      </c>
+      <c r="F304" t="s">
         <v>856</v>
-      </c>
-      <c r="E304" t="s">
-        <v>849</v>
-      </c>
-      <c r="F304" t="s">
-        <v>857</v>
       </c>
       <c r="G304">
         <v>20</v>
@@ -48030,7 +48031,7 @@
         <v>20</v>
       </c>
       <c r="I304" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="J304">
         <v>0</v>
@@ -48069,16 +48070,16 @@
         <v>0</v>
       </c>
       <c r="C305" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D305" t="s">
+        <v>857</v>
+      </c>
+      <c r="E305" t="s">
+        <v>848</v>
+      </c>
+      <c r="F305" t="s">
         <v>858</v>
-      </c>
-      <c r="E305" t="s">
-        <v>849</v>
-      </c>
-      <c r="F305" t="s">
-        <v>859</v>
       </c>
       <c r="G305">
         <v>3</v>
@@ -48087,7 +48088,7 @@
         <v>1.5</v>
       </c>
       <c r="I305" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="J305">
         <v>0</v>
@@ -48126,16 +48127,16 @@
         <v>0</v>
       </c>
       <c r="C306" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D306" t="s">
+        <v>859</v>
+      </c>
+      <c r="E306" t="s">
+        <v>848</v>
+      </c>
+      <c r="F306" t="s">
         <v>860</v>
-      </c>
-      <c r="E306" t="s">
-        <v>849</v>
-      </c>
-      <c r="F306" t="s">
-        <v>861</v>
       </c>
       <c r="G306">
         <v>3</v>
@@ -48144,7 +48145,7 @@
         <v>1.5</v>
       </c>
       <c r="I306" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="J306">
         <v>0</v>
@@ -48183,16 +48184,16 @@
         <v>0</v>
       </c>
       <c r="C307" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D307" t="s">
+        <v>861</v>
+      </c>
+      <c r="E307" t="s">
+        <v>848</v>
+      </c>
+      <c r="F307" t="s">
         <v>862</v>
-      </c>
-      <c r="E307" t="s">
-        <v>849</v>
-      </c>
-      <c r="F307" t="s">
-        <v>863</v>
       </c>
       <c r="G307">
         <v>3</v>
@@ -48201,7 +48202,7 @@
         <v>1.5</v>
       </c>
       <c r="I307" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="J307">
         <v>0</v>
@@ -48240,16 +48241,16 @@
         <v>0</v>
       </c>
       <c r="C308" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D308" t="s">
+        <v>863</v>
+      </c>
+      <c r="E308" t="s">
+        <v>848</v>
+      </c>
+      <c r="F308" t="s">
         <v>864</v>
-      </c>
-      <c r="E308" t="s">
-        <v>849</v>
-      </c>
-      <c r="F308" t="s">
-        <v>865</v>
       </c>
       <c r="G308">
         <v>25</v>
@@ -48258,7 +48259,7 @@
         <v>25</v>
       </c>
       <c r="I308" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="J308">
         <v>0</v>
@@ -48297,16 +48298,16 @@
         <v>0</v>
       </c>
       <c r="C309" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D309" t="s">
+        <v>865</v>
+      </c>
+      <c r="E309" t="s">
+        <v>848</v>
+      </c>
+      <c r="F309" t="s">
         <v>866</v>
-      </c>
-      <c r="E309" t="s">
-        <v>849</v>
-      </c>
-      <c r="F309" t="s">
-        <v>867</v>
       </c>
       <c r="G309">
         <v>5</v>
@@ -48315,7 +48316,7 @@
         <v>2.5</v>
       </c>
       <c r="I309" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="J309">
         <v>0</v>
@@ -48354,19 +48355,19 @@
         <v>0</v>
       </c>
       <c r="C310" t="s">
+        <v>867</v>
+      </c>
+      <c r="D310" t="s">
         <v>868</v>
       </c>
-      <c r="D310" t="s">
+      <c r="E310" s="3" t="s">
+        <v>972</v>
+      </c>
+      <c r="F310" t="s">
         <v>869</v>
       </c>
-      <c r="E310" s="3" t="s">
-        <v>973</v>
-      </c>
-      <c r="F310" t="s">
-        <v>870</v>
-      </c>
       <c r="G310" s="3" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H310">
         <v>3</v>
@@ -48411,16 +48412,16 @@
         <v>0</v>
       </c>
       <c r="C311" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D311" t="s">
+        <v>870</v>
+      </c>
+      <c r="E311" t="s">
         <v>871</v>
       </c>
-      <c r="E311" t="s">
+      <c r="F311" t="s">
         <v>872</v>
-      </c>
-      <c r="F311" t="s">
-        <v>873</v>
       </c>
       <c r="G311">
         <v>5</v>
@@ -48468,16 +48469,16 @@
         <v>0</v>
       </c>
       <c r="C312" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D312" t="s">
+        <v>873</v>
+      </c>
+      <c r="E312" t="s">
         <v>874</v>
       </c>
-      <c r="E312" t="s">
+      <c r="F312" t="s">
         <v>875</v>
-      </c>
-      <c r="F312" t="s">
-        <v>876</v>
       </c>
       <c r="G312">
         <v>10</v>
@@ -48525,16 +48526,16 @@
         <v>0</v>
       </c>
       <c r="C313" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D313" t="s">
+        <v>876</v>
+      </c>
+      <c r="E313" t="s">
         <v>877</v>
       </c>
-      <c r="E313" t="s">
+      <c r="F313" t="s">
         <v>878</v>
-      </c>
-      <c r="F313" t="s">
-        <v>879</v>
       </c>
       <c r="G313">
         <v>10</v>
@@ -48582,16 +48583,16 @@
         <v>0</v>
       </c>
       <c r="C314" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D314" t="s">
+        <v>879</v>
+      </c>
+      <c r="E314" t="s">
         <v>880</v>
       </c>
-      <c r="E314" t="s">
+      <c r="F314" t="s">
         <v>881</v>
-      </c>
-      <c r="F314" t="s">
-        <v>882</v>
       </c>
       <c r="G314">
         <v>2</v>
@@ -48639,16 +48640,16 @@
         <v>0</v>
       </c>
       <c r="C315" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D315" t="s">
+        <v>882</v>
+      </c>
+      <c r="E315" t="s">
         <v>883</v>
       </c>
-      <c r="E315" t="s">
+      <c r="F315" t="s">
         <v>884</v>
-      </c>
-      <c r="F315" t="s">
-        <v>885</v>
       </c>
       <c r="G315">
         <v>5</v>
@@ -48696,16 +48697,16 @@
         <v>0</v>
       </c>
       <c r="C316" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D316" t="s">
+        <v>885</v>
+      </c>
+      <c r="E316" t="s">
         <v>886</v>
       </c>
-      <c r="E316" t="s">
+      <c r="F316" t="s">
         <v>887</v>
-      </c>
-      <c r="F316" t="s">
-        <v>888</v>
       </c>
       <c r="G316">
         <v>10</v>
@@ -48753,16 +48754,16 @@
         <v>0</v>
       </c>
       <c r="C317" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D317" t="s">
+        <v>888</v>
+      </c>
+      <c r="E317" t="s">
         <v>889</v>
       </c>
-      <c r="E317" t="s">
+      <c r="F317" t="s">
         <v>890</v>
-      </c>
-      <c r="F317" t="s">
-        <v>891</v>
       </c>
       <c r="G317">
         <v>20000</v>
@@ -48810,16 +48811,16 @@
         <v>0</v>
       </c>
       <c r="C318" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="D318" t="s">
+        <v>973</v>
+      </c>
+      <c r="E318" t="s">
         <v>974</v>
       </c>
-      <c r="E318" t="s">
+      <c r="F318" s="5" t="s">
         <v>975</v>
-      </c>
-      <c r="F318" s="5" t="s">
-        <v>976</v>
       </c>
       <c r="G318">
         <v>0.35</v>
@@ -48867,16 +48868,16 @@
         <v>0</v>
       </c>
       <c r="C319" t="s">
+        <v>836</v>
+      </c>
+      <c r="D319" t="s">
         <v>837</v>
-      </c>
-      <c r="D319" t="s">
-        <v>838</v>
       </c>
       <c r="E319" t="s">
         <v>36</v>
       </c>
       <c r="F319" s="7" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G319">
         <v>1</v>
@@ -48924,16 +48925,16 @@
         <v>0</v>
       </c>
       <c r="C320" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D320" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E320" t="s">
         <v>36</v>
       </c>
       <c r="F320" s="7" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G320">
         <v>1.35</v>
@@ -48981,16 +48982,16 @@
         <v>0</v>
       </c>
       <c r="C321" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D321" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="E321" t="s">
         <v>36</v>
       </c>
       <c r="F321" s="7" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G321">
         <v>1.75</v>
@@ -49038,16 +49039,16 @@
         <v>0</v>
       </c>
       <c r="C322" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D322" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="E322" t="s">
         <v>36</v>
       </c>
       <c r="F322" s="7" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G322">
         <v>2.2999999999999998</v>
@@ -49095,16 +49096,16 @@
         <v>0</v>
       </c>
       <c r="C323" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D323" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="E323" t="s">
         <v>36</v>
       </c>
       <c r="F323" s="7" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G323">
         <v>3</v>
@@ -49152,16 +49153,16 @@
         <v>0</v>
       </c>
       <c r="C324" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D324" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="E324" t="s">
         <v>36</v>
       </c>
       <c r="F324" s="7" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G324">
         <v>4</v>
@@ -49209,16 +49210,16 @@
         <v>0</v>
       </c>
       <c r="C325" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D325" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="E325" t="s">
         <v>36</v>
       </c>
       <c r="F325" s="7" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G325">
         <v>5.2</v>
@@ -49266,16 +49267,16 @@
         <v>0</v>
       </c>
       <c r="C326" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D326" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="E326" t="s">
         <v>36</v>
       </c>
       <c r="F326" s="7" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G326">
         <v>6.8</v>
@@ -49323,16 +49324,16 @@
         <v>0</v>
       </c>
       <c r="C327" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D327" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E327" t="s">
         <v>36</v>
       </c>
       <c r="F327" s="7" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="G327">
         <v>10.199999999999999</v>
@@ -49380,16 +49381,16 @@
         <v>0</v>
       </c>
       <c r="C328" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D328" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E328" t="s">
         <v>36</v>
       </c>
       <c r="F328" s="7" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="G328">
         <v>15.3</v>
@@ -49437,16 +49438,16 @@
         <v>0</v>
       </c>
       <c r="C329" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D329" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="E329" t="s">
         <v>36</v>
       </c>
       <c r="F329" s="7" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="G329">
         <v>22.95</v>
@@ -49494,22 +49495,22 @@
         <v>0</v>
       </c>
       <c r="C330" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D330" t="s">
         <v>1047</v>
       </c>
-      <c r="D330" t="s">
+      <c r="E330" t="s">
         <v>1048</v>
       </c>
-      <c r="E330" t="s">
+      <c r="F330" t="s">
         <v>1049</v>
-      </c>
-      <c r="F330" t="s">
-        <v>1050</v>
       </c>
       <c r="G330">
         <v>200</v>
       </c>
       <c r="H330" s="3" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="I330">
         <v>0</v>
@@ -49551,28 +49552,28 @@
         <v>0</v>
       </c>
       <c r="C331" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D331" s="2" t="s">
         <v>1056</v>
       </c>
-      <c r="D331" s="2" t="s">
+      <c r="E331" t="s">
         <v>1057</v>
       </c>
-      <c r="E331" t="s">
+      <c r="F331" t="s">
         <v>1058</v>
       </c>
-      <c r="F331" t="s">
+      <c r="G331" s="7" t="s">
         <v>1059</v>
       </c>
-      <c r="G331" s="7" t="s">
+      <c r="H331" s="7" t="s">
         <v>1060</v>
       </c>
-      <c r="H331" s="7" t="s">
+      <c r="I331" s="7" t="s">
         <v>1061</v>
       </c>
-      <c r="I331" s="7" t="s">
+      <c r="J331" s="7" t="s">
         <v>1062</v>
-      </c>
-      <c r="J331" s="7" t="s">
-        <v>1063</v>
       </c>
       <c r="K331">
         <v>0</v>
@@ -49608,22 +49609,22 @@
         <v>0</v>
       </c>
       <c r="C332" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D332" s="2" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E332" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F332" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G332" s="7" t="s">
         <v>1064</v>
       </c>
-      <c r="E332" t="s">
-        <v>1058</v>
-      </c>
-      <c r="F332" t="s">
-        <v>1059</v>
-      </c>
-      <c r="G332" s="7" t="s">
+      <c r="H332" s="7" t="s">
         <v>1065</v>
-      </c>
-      <c r="H332" s="7" t="s">
-        <v>1066</v>
       </c>
       <c r="I332">
         <v>0</v>
@@ -49665,22 +49666,22 @@
         <v>0</v>
       </c>
       <c r="C333" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D333" s="2" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E333" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F333" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G333" s="7" t="s">
         <v>1067</v>
       </c>
-      <c r="E333" t="s">
-        <v>1058</v>
-      </c>
-      <c r="F333" t="s">
-        <v>1059</v>
-      </c>
-      <c r="G333" s="7" t="s">
+      <c r="H333" s="7" t="s">
         <v>1068</v>
-      </c>
-      <c r="H333" s="7" t="s">
-        <v>1069</v>
       </c>
       <c r="I333">
         <v>0</v>
@@ -49722,22 +49723,22 @@
         <v>0</v>
       </c>
       <c r="C334" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D334" s="2" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E334" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F334" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G334" s="7" t="s">
         <v>1070</v>
       </c>
-      <c r="E334" t="s">
-        <v>1058</v>
-      </c>
-      <c r="F334" t="s">
-        <v>1059</v>
-      </c>
-      <c r="G334" s="7" t="s">
+      <c r="H334" s="7" t="s">
         <v>1071</v>
-      </c>
-      <c r="H334" s="7" t="s">
-        <v>1072</v>
       </c>
       <c r="I334">
         <v>0</v>
@@ -49779,19 +49780,19 @@
         <v>0</v>
       </c>
       <c r="C335" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D335" s="2" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E335" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F335" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G335" s="7" t="s">
         <v>1073</v>
-      </c>
-      <c r="E335" t="s">
-        <v>1058</v>
-      </c>
-      <c r="F335" t="s">
-        <v>1059</v>
-      </c>
-      <c r="G335" s="7" t="s">
-        <v>1074</v>
       </c>
       <c r="H335">
         <v>0</v>
@@ -49836,34 +49837,34 @@
         <v>0</v>
       </c>
       <c r="C336" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D336" s="2" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E336" t="s">
         <v>1075</v>
       </c>
-      <c r="E336" t="s">
+      <c r="F336" t="s">
         <v>1076</v>
       </c>
-      <c r="F336" t="s">
+      <c r="G336" s="7" t="s">
         <v>1077</v>
       </c>
-      <c r="G336" s="7" t="s">
+      <c r="H336" s="7" t="s">
         <v>1078</v>
       </c>
-      <c r="H336" s="7" t="s">
+      <c r="I336" s="7" t="s">
         <v>1079</v>
       </c>
-      <c r="I336" s="7" t="s">
+      <c r="J336" s="7" t="s">
         <v>1080</v>
       </c>
-      <c r="J336" s="7" t="s">
+      <c r="K336" s="7" t="s">
         <v>1081</v>
       </c>
-      <c r="K336" s="7" t="s">
+      <c r="L336" s="7" t="s">
         <v>1082</v>
-      </c>
-      <c r="L336" s="7" t="s">
-        <v>1083</v>
       </c>
       <c r="M336">
         <v>0</v>
@@ -49893,25 +49894,25 @@
         <v>0</v>
       </c>
       <c r="C337" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D337" s="2" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E337" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F337" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G337" s="7" t="s">
         <v>1084</v>
       </c>
-      <c r="E337" t="s">
-        <v>1076</v>
-      </c>
-      <c r="F337" t="s">
-        <v>1077</v>
-      </c>
-      <c r="G337" s="7" t="s">
+      <c r="H337" s="7" t="s">
         <v>1085</v>
       </c>
-      <c r="H337" s="7" t="s">
+      <c r="I337" s="7" t="s">
         <v>1086</v>
-      </c>
-      <c r="I337" s="7" t="s">
-        <v>1087</v>
       </c>
       <c r="J337">
         <v>0</v>
@@ -49950,25 +49951,25 @@
         <v>0</v>
       </c>
       <c r="C338" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D338" s="2" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E338" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F338" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G338" s="7" t="s">
         <v>1088</v>
       </c>
-      <c r="E338" t="s">
-        <v>1076</v>
-      </c>
-      <c r="F338" t="s">
-        <v>1077</v>
-      </c>
-      <c r="G338" s="7" t="s">
+      <c r="H338" s="7" t="s">
         <v>1089</v>
       </c>
-      <c r="H338" s="7" t="s">
+      <c r="I338" s="7" t="s">
         <v>1090</v>
-      </c>
-      <c r="I338" s="7" t="s">
-        <v>1091</v>
       </c>
       <c r="J338">
         <v>0</v>
@@ -50007,25 +50008,25 @@
         <v>0</v>
       </c>
       <c r="C339" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D339" s="2" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E339" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F339" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G339" s="7" t="s">
         <v>1092</v>
       </c>
-      <c r="E339" t="s">
-        <v>1076</v>
-      </c>
-      <c r="F339" t="s">
-        <v>1077</v>
-      </c>
-      <c r="G339" s="7" t="s">
+      <c r="H339" s="7" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I339" s="7" t="s">
         <v>1093</v>
-      </c>
-      <c r="H339" s="7" t="s">
-        <v>1090</v>
-      </c>
-      <c r="I339" s="7" t="s">
-        <v>1094</v>
       </c>
       <c r="J339">
         <v>0</v>
@@ -50064,25 +50065,25 @@
         <v>0</v>
       </c>
       <c r="C340" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D340" s="2" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E340" t="s">
+        <v>1075</v>
+      </c>
+      <c r="F340" t="s">
+        <v>1076</v>
+      </c>
+      <c r="G340" s="7" t="s">
         <v>1095</v>
       </c>
-      <c r="E340" t="s">
-        <v>1076</v>
-      </c>
-      <c r="F340" t="s">
-        <v>1077</v>
-      </c>
-      <c r="G340" s="7" t="s">
+      <c r="H340" s="7" t="s">
+        <v>1089</v>
+      </c>
+      <c r="I340" s="7" t="s">
         <v>1096</v>
-      </c>
-      <c r="H340" s="7" t="s">
-        <v>1090</v>
-      </c>
-      <c r="I340" s="7" t="s">
-        <v>1097</v>
       </c>
       <c r="J340">
         <v>0</v>
@@ -50121,22 +50122,22 @@
         <v>0</v>
       </c>
       <c r="C341" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D341" s="2" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E341" t="s">
         <v>1098</v>
       </c>
-      <c r="E341" t="s">
+      <c r="F341" t="s">
         <v>1099</v>
       </c>
-      <c r="F341" t="s">
+      <c r="G341" s="7" t="s">
         <v>1100</v>
       </c>
-      <c r="G341" s="7" t="s">
+      <c r="H341" s="7" t="s">
         <v>1101</v>
-      </c>
-      <c r="H341" s="7" t="s">
-        <v>1102</v>
       </c>
       <c r="I341">
         <v>0</v>
@@ -50178,22 +50179,22 @@
         <v>0</v>
       </c>
       <c r="C342" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D342" s="2" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E342" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F342" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G342" s="7" t="s">
         <v>1103</v>
       </c>
-      <c r="E342" t="s">
-        <v>1099</v>
-      </c>
-      <c r="F342" t="s">
-        <v>1100</v>
-      </c>
-      <c r="G342" s="7" t="s">
+      <c r="H342" s="7" t="s">
         <v>1104</v>
-      </c>
-      <c r="H342" s="7" t="s">
-        <v>1105</v>
       </c>
       <c r="I342">
         <v>0</v>
@@ -50235,19 +50236,19 @@
         <v>0</v>
       </c>
       <c r="C343" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D343" s="2" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E343" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F343" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G343" s="7" t="s">
         <v>1106</v>
-      </c>
-      <c r="E343" t="s">
-        <v>1099</v>
-      </c>
-      <c r="F343" t="s">
-        <v>1100</v>
-      </c>
-      <c r="G343" s="7" t="s">
-        <v>1107</v>
       </c>
       <c r="H343">
         <v>0</v>
@@ -50292,19 +50293,19 @@
         <v>0</v>
       </c>
       <c r="C344" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D344" s="2" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E344" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F344" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G344" s="7" t="s">
         <v>1108</v>
-      </c>
-      <c r="E344" t="s">
-        <v>1099</v>
-      </c>
-      <c r="F344" t="s">
-        <v>1100</v>
-      </c>
-      <c r="G344" s="7" t="s">
-        <v>1109</v>
       </c>
       <c r="H344">
         <v>0</v>
@@ -50349,19 +50350,19 @@
         <v>0</v>
       </c>
       <c r="C345" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D345" s="2" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E345" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F345" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G345" s="7" t="s">
         <v>1110</v>
-      </c>
-      <c r="E345" t="s">
-        <v>1099</v>
-      </c>
-      <c r="F345" t="s">
-        <v>1100</v>
-      </c>
-      <c r="G345" s="7" t="s">
-        <v>1111</v>
       </c>
       <c r="H345">
         <v>0</v>
@@ -50406,25 +50407,25 @@
         <v>0</v>
       </c>
       <c r="C346" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D346" s="2" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E346" t="s">
         <v>1112</v>
       </c>
-      <c r="E346" t="s">
+      <c r="F346" t="s">
         <v>1113</v>
       </c>
-      <c r="F346" t="s">
+      <c r="G346" s="7" t="s">
         <v>1114</v>
       </c>
-      <c r="G346" s="7" t="s">
+      <c r="H346" s="7" t="s">
         <v>1115</v>
       </c>
-      <c r="H346" s="7" t="s">
+      <c r="I346" s="7" t="s">
         <v>1116</v>
-      </c>
-      <c r="I346" s="7" t="s">
-        <v>1117</v>
       </c>
       <c r="J346">
         <v>0</v>
@@ -50463,25 +50464,25 @@
         <v>0</v>
       </c>
       <c r="C347" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D347" s="2" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E347" t="s">
         <v>1118</v>
       </c>
-      <c r="E347" t="s">
+      <c r="F347" t="s">
+        <v>1145</v>
+      </c>
+      <c r="G347" s="7" t="s">
         <v>1119</v>
       </c>
-      <c r="F347" t="s">
-        <v>1146</v>
-      </c>
-      <c r="G347" s="7" t="s">
+      <c r="H347" s="7" t="s">
         <v>1120</v>
       </c>
-      <c r="H347" s="7" t="s">
+      <c r="I347" s="7" t="s">
         <v>1121</v>
-      </c>
-      <c r="I347" s="7" t="s">
-        <v>1122</v>
       </c>
       <c r="J347">
         <v>0</v>
@@ -50520,16 +50521,16 @@
         <v>0</v>
       </c>
       <c r="C348" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D348" s="2" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E348" t="s">
         <v>1123</v>
       </c>
-      <c r="E348" t="s">
+      <c r="F348" t="s">
         <v>1124</v>
-      </c>
-      <c r="F348" t="s">
-        <v>1125</v>
       </c>
       <c r="G348">
         <v>1</v>
@@ -50577,16 +50578,16 @@
         <v>0</v>
       </c>
       <c r="C349" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D349" s="2" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E349" t="s">
         <v>1126</v>
       </c>
-      <c r="E349" t="s">
-        <v>1127</v>
-      </c>
       <c r="F349" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="G349">
         <v>100</v>
@@ -50633,16 +50634,16 @@
         <v>0</v>
       </c>
       <c r="C350" t="s">
+        <v>1129</v>
+      </c>
+      <c r="D350" s="2" t="s">
         <v>1130</v>
       </c>
-      <c r="D350" s="2" t="s">
+      <c r="E350" t="s">
         <v>1131</v>
       </c>
-      <c r="E350" t="s">
+      <c r="F350" t="s">
         <v>1132</v>
-      </c>
-      <c r="F350" t="s">
-        <v>1133</v>
       </c>
       <c r="G350">
         <v>125</v>
@@ -50690,16 +50691,16 @@
         <v>0</v>
       </c>
       <c r="C351" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D351" s="2" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E351" t="s">
         <v>1134</v>
       </c>
-      <c r="E351" t="s">
+      <c r="F351" t="s">
         <v>1135</v>
-      </c>
-      <c r="F351" t="s">
-        <v>1136</v>
       </c>
       <c r="G351">
         <v>6</v>
@@ -50747,16 +50748,16 @@
         <v>0</v>
       </c>
       <c r="C352" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D352" s="2" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E352" t="s">
         <v>1137</v>
       </c>
-      <c r="E352" t="s">
+      <c r="F352" t="s">
         <v>1138</v>
-      </c>
-      <c r="F352" t="s">
-        <v>1139</v>
       </c>
       <c r="G352">
         <v>8</v>
@@ -50804,16 +50805,16 @@
         <v>0</v>
       </c>
       <c r="C353" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D353" s="2" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E353" t="s">
         <v>1140</v>
       </c>
-      <c r="E353" t="s">
+      <c r="F353" t="s">
         <v>1141</v>
-      </c>
-      <c r="F353" t="s">
-        <v>1142</v>
       </c>
       <c r="G353">
         <v>1.6</v>
@@ -50861,16 +50862,16 @@
         <v>0</v>
       </c>
       <c r="C354" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D354" s="2" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E354" t="s">
         <v>1143</v>
       </c>
-      <c r="E354" t="s">
-        <v>1144</v>
-      </c>
       <c r="F354" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="G354">
         <v>4</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\gem-workshop-merge\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0945DA2C-AF75-489F-9DB7-38BA8915E039}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CB26AC-DCFF-49BF-85CD-A7A6E4340139}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3090" yWindow="2310" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="1215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2049" uniqueCount="1215">
   <si>
     <t>編號</t>
   </si>
@@ -29401,9 +29401,8 @@
         <f>計算表!I349</f>
         <v>3.5</v>
       </c>
-      <c r="J333">
-        <f>計算表!J349</f>
-        <v>48</v>
+      <c r="J333" s="7" t="s">
+        <v>1188</v>
       </c>
       <c r="K333">
         <f>計算表!K349</f>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.codex\visualizations\2026\10\27\01a17caf-1be0-79f0-b690-dc09a7e73373\speed-gear\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A74D117-3051-40E3-8452-37549878E022}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CF4EDD-7DFC-4E3E-ADD7-2F0F5188A65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30615" yWindow="2280" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2052" uniqueCount="1216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2010" uniqueCount="1201">
   <si>
     <t>編號</t>
   </si>
@@ -4329,9 +4329,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>357</t>
-  </si>
-  <si>
     <t>封魔塔BOSS玩家技能</t>
   </si>
   <si>
@@ -4341,27 +4338,9 @@
     <t>封魔塔 BOSS 施放的玩家超神進化技能（Skills2 超神列的封魔塔層級＝該層 BOSS 固定使用；規則與對照表見 docs/BOSS_PLAYER_SKILLS.md）的整體強度。a＝技能傷害倍率（%）：技能 pct% 乘 a% 就是 BOSS 攻擊力的倍數；b＝持續場域與領域每次跳動的再折扣（%）；c＝範圍半徑倍率（%，玩家技能的範圍是為打一群怪設計的）；d＝玩家式增益（攻擊提高％、疊層）轉成 BOSS 增益的強度（%）；e＝控場（暈眩、緩速）秒數倍率（%）；f＝護盾量倍率（%）；g＝復活類技能復活後的生命倍率（%）；h＝被動反應技能（神聖之體、天穹崩裂）兩次觸發的最短間隔（秒）。單一技能要個別調整時，在 Skills2 該列的效果參數(JSON) 補 bossMul（傷害倍率）、bossCd 與 bossCdMax（冷卻秒數）。</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>50</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>358</t>
-  </si>
-  <si>
     <t>4-遠方怪群</t>
   </si>
   <si>
@@ -4371,48 +4350,10 @@
     <t>100</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>70</t>
-  </si>
-  <si>
-    <t>359</t>
-  </si>
-  <si>
     <t>未警戒遊走</t>
   </si>
   <si>
     <t>出生點半徑a米內；跑速×b；到點停留c~d秒</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>0.25</t>
-  </si>
-  <si>
-    <t>2.5</t>
-  </si>
-  <si>
-    <t>格點間距a米；預載b米內／c米外；隨機f～d群，每群最多e隻</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>初次隨機抽定群數，整群死亡後在遠方隨機空位補回。存活群保留，部分死亡不補單隻；與近身波次獨立，共用戰場總容量。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>僅遠方預置怪群未發現玩家時生效。以各隻出生世界座標為固定中心隨機走停；玩家進入NPC視野或怪物受擊後停止遊走並追擊。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>依成品階級消耗 a/b/c 顆同種同級寶石</t>
@@ -4484,6 +4425,15 @@
   <si>
     <t>a=基礎值 b=每級增加值；節點為 salvage。</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>格點間距a米；預載b米內／c米外；隨機f～d群，每群最多e隻</t>
+  </si>
+  <si>
+    <t>初次隨機抽定群數，整群死亡後在遠方隨機空位補回。存活群保留，部分死亡不補單隻；與近身波次獨立，共用戰場總容量。</t>
+  </si>
+  <si>
+    <t>僅遠方預置怪群未發現玩家時生效。以各隻出生世界座標為固定中心隨機走停；玩家進入NPC視野或怪物受擊後停止遊走並追擊。</t>
   </si>
 </sst>
 </file>
@@ -4577,7 +4527,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -4600,6 +4550,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5691,10 +5644,10 @@
         <v>每 a 級 +1 格，最少 b、最多 c。</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>1183</v>
+        <v>1176</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>1211</v>
+        <v>1193</v>
       </c>
       <c r="I11">
         <f>計算表!I11</f>
@@ -5759,13 +5712,13 @@
         <v>達到a級可轉生；最高b轉</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>1210</v>
+        <v>1192</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>1153</v>
       </c>
       <c r="H12" s="7" t="s">
-        <v>1212</v>
+        <v>1194</v>
       </c>
       <c r="I12">
         <f>計算表!I12</f>
@@ -5904,13 +5857,13 @@
         <v>上限 a 級；擊殺技能經驗 = 怪物經驗 × b%</v>
       </c>
       <c r="F14" t="s">
-        <v>1203</v>
+        <v>1185</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>1213</v>
+        <v>1195</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="I14">
         <f>計算表!I15</f>
@@ -5975,7 +5928,7 @@
         <v>（查表）</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>1204</v>
+        <v>1186</v>
       </c>
       <c r="G15">
         <f>計算表!G16</f>
@@ -6047,7 +6000,7 @@
         <v>（查表）</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>1204</v>
+        <v>1186</v>
       </c>
       <c r="G16">
         <f>計算表!G17</f>
@@ -6119,7 +6072,7 @@
         <v>（查表）</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>1204</v>
+        <v>1186</v>
       </c>
       <c r="G17">
         <f>計算表!G18</f>
@@ -6191,7 +6144,7 @@
         <v>（查表）</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>1204</v>
+        <v>1186</v>
       </c>
       <c r="G18">
         <f>計算表!G19</f>
@@ -6263,7 +6216,7 @@
         <v>（查表）</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>1204</v>
+        <v>1186</v>
       </c>
       <c r="G19">
         <f>計算表!G20</f>
@@ -6335,7 +6288,7 @@
         <v>（查表）</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>1204</v>
+        <v>1186</v>
       </c>
       <c r="G20">
         <f>計算表!G21</f>
@@ -6407,7 +6360,7 @@
         <v>（查表）</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>1204</v>
+        <v>1186</v>
       </c>
       <c r="G21">
         <f>計算表!G22</f>
@@ -6479,7 +6432,7 @@
         <v>（查表）</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>1204</v>
+        <v>1186</v>
       </c>
       <c r="G22">
         <f>計算表!G23</f>
@@ -6551,7 +6504,7 @@
         <v>（查表）</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>1204</v>
+        <v>1186</v>
       </c>
       <c r="G23">
         <f>計算表!G24</f>
@@ -6623,7 +6576,7 @@
         <v>（查表）</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>1204</v>
+        <v>1186</v>
       </c>
       <c r="G24">
         <f>計算表!G25</f>
@@ -6695,7 +6648,7 @@
         <v>（查表）</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>1204</v>
+        <v>1186</v>
       </c>
       <c r="G25">
         <f>計算表!G26</f>
@@ -6767,7 +6720,7 @@
         <v>（查表）</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>1204</v>
+        <v>1186</v>
       </c>
       <c r="G26">
         <f>計算表!G27</f>
@@ -6839,7 +6792,7 @@
         <v>（查表）</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>1204</v>
+        <v>1186</v>
       </c>
       <c r="G27">
         <f>計算表!G28</f>
@@ -6911,7 +6864,7 @@
         <v>（查表）</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>1204</v>
+        <v>1186</v>
       </c>
       <c r="G28">
         <f>計算表!G29</f>
@@ -6983,7 +6936,7 @@
         <v>（查表）</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>1204</v>
+        <v>1186</v>
       </c>
       <c r="G29">
         <f>計算表!G30</f>
@@ -7055,7 +7008,7 @@
         <v>（查表）</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>1204</v>
+        <v>1186</v>
       </c>
       <c r="G30">
         <f>計算表!G31</f>
@@ -7127,7 +7080,7 @@
         <v>（查表）</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>1204</v>
+        <v>1186</v>
       </c>
       <c r="G31">
         <f>計算表!G32</f>
@@ -7199,7 +7152,7 @@
         <v>（查表）</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>1204</v>
+        <v>1186</v>
       </c>
       <c r="G32">
         <f>計算表!G33</f>
@@ -7271,7 +7224,7 @@
         <v>（查表）</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>1204</v>
+        <v>1186</v>
       </c>
       <c r="G33">
         <f>計算表!G34</f>
@@ -7343,7 +7296,7 @@
         <v>（查表）</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>1204</v>
+        <v>1186</v>
       </c>
       <c r="G34">
         <f>計算表!G35</f>
@@ -7415,7 +7368,7 @@
         <v>（查表）</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>1204</v>
+        <v>1186</v>
       </c>
       <c r="G35">
         <f>計算表!G36</f>
@@ -29252,7 +29205,7 @@
         <v>3.5</v>
       </c>
       <c r="J331" s="7" t="s">
-        <v>1183</v>
+        <v>1176</v>
       </c>
       <c r="K331">
         <f>計算表!K348</f>
@@ -29658,171 +29611,225 @@
       </c>
     </row>
     <row r="337" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A337" s="7" t="s">
-        <v>1180</v>
-      </c>
-      <c r="B337" s="7" t="s">
-        <v>1153</v>
-      </c>
-      <c r="C337" s="7" t="s">
-        <v>1181</v>
-      </c>
-      <c r="D337" s="7" t="s">
-        <v>1182</v>
-      </c>
-      <c r="E337" s="7" t="s">
-        <v>1192</v>
-      </c>
-      <c r="F337" s="7" t="s">
-        <v>1193</v>
-      </c>
-      <c r="G337" s="7" t="s">
-        <v>1183</v>
-      </c>
-      <c r="H337" s="7" t="s">
-        <v>1184</v>
-      </c>
-      <c r="I337" s="7" t="s">
-        <v>1185</v>
-      </c>
-      <c r="J337" s="7" t="s">
-        <v>1194</v>
-      </c>
-      <c r="K337" s="7" t="s">
-        <v>1179</v>
-      </c>
-      <c r="L337" s="7" t="s">
-        <v>1195</v>
-      </c>
-      <c r="M337" s="7" t="s">
-        <v>1153</v>
-      </c>
-      <c r="N337" s="7" t="s">
-        <v>1153</v>
-      </c>
-      <c r="O337" s="7" t="s">
-        <v>1153</v>
-      </c>
-      <c r="P337" s="7" t="s">
-        <v>1153</v>
-      </c>
-      <c r="Q337" s="7" t="s">
-        <v>1153</v>
-      </c>
-      <c r="R337" s="7" t="s">
-        <v>1153</v>
+      <c r="A337">
+        <f>計算表!A354</f>
+        <v>357</v>
+      </c>
+      <c r="B337">
+        <f>計算表!B354</f>
+        <v>0</v>
+      </c>
+      <c r="C337" t="str">
+        <f>計算表!C354</f>
+        <v>4-遠方怪群</v>
+      </c>
+      <c r="D337" t="str">
+        <f>計算表!D354</f>
+        <v>預先生成</v>
+      </c>
+      <c r="E337" t="str">
+        <f>計算表!E354</f>
+        <v>格點間距a米；預載b米內／c米外；隨機f～d群，每群最多e隻</v>
+      </c>
+      <c r="F337" t="str">
+        <f>計算表!F354</f>
+        <v>初次隨機抽定群數，整群死亡後在遠方隨機空位補回。存活群保留，部分死亡不補單隻；與近身波次獨立，共用戰場總容量。</v>
+      </c>
+      <c r="G337">
+        <f>計算表!G354</f>
+        <v>100</v>
+      </c>
+      <c r="H337">
+        <f>計算表!H354</f>
+        <v>160</v>
+      </c>
+      <c r="I337">
+        <f>計算表!I354</f>
+        <v>70</v>
+      </c>
+      <c r="J337">
+        <f>計算表!J354</f>
+        <v>8</v>
+      </c>
+      <c r="K337">
+        <f>計算表!K354</f>
+        <v>4</v>
+      </c>
+      <c r="L337">
+        <f>計算表!L354</f>
+        <v>4</v>
+      </c>
+      <c r="M337">
+        <f>計算表!M354</f>
+        <v>0</v>
+      </c>
+      <c r="N337">
+        <f>計算表!N354</f>
+        <v>0</v>
+      </c>
+      <c r="O337">
+        <f>計算表!O354</f>
+        <v>0</v>
+      </c>
+      <c r="P337">
+        <f>計算表!P354</f>
+        <v>0</v>
+      </c>
+      <c r="Q337">
+        <f>計算表!Q354</f>
+        <v>0</v>
+      </c>
+      <c r="R337">
+        <f>計算表!R354</f>
+        <v>0</v>
       </c>
     </row>
     <row r="338" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A338" s="7" t="s">
-        <v>1186</v>
-      </c>
-      <c r="B338" s="7" t="s">
-        <v>1153</v>
-      </c>
-      <c r="C338" s="7" t="s">
-        <v>1181</v>
-      </c>
-      <c r="D338" s="7" t="s">
-        <v>1187</v>
-      </c>
-      <c r="E338" s="7" t="s">
-        <v>1188</v>
-      </c>
-      <c r="F338" s="7" t="s">
-        <v>1196</v>
-      </c>
-      <c r="G338" s="7" t="s">
-        <v>1189</v>
-      </c>
-      <c r="H338" s="7" t="s">
-        <v>1190</v>
-      </c>
-      <c r="I338" s="7" t="s">
-        <v>1166</v>
-      </c>
-      <c r="J338" s="7" t="s">
-        <v>1191</v>
-      </c>
-      <c r="K338" s="7" t="s">
-        <v>1153</v>
-      </c>
-      <c r="L338" s="7" t="s">
-        <v>1153</v>
-      </c>
-      <c r="M338" s="7" t="s">
-        <v>1153</v>
-      </c>
-      <c r="N338" s="7" t="s">
-        <v>1153</v>
-      </c>
-      <c r="O338" s="7" t="s">
-        <v>1153</v>
-      </c>
-      <c r="P338" s="7" t="s">
-        <v>1153</v>
-      </c>
-      <c r="Q338" s="7" t="s">
-        <v>1153</v>
-      </c>
-      <c r="R338" s="7" t="s">
-        <v>1153</v>
+      <c r="A338">
+        <f>計算表!A355</f>
+        <v>358</v>
+      </c>
+      <c r="B338">
+        <f>計算表!B355</f>
+        <v>0</v>
+      </c>
+      <c r="C338" t="str">
+        <f>計算表!C355</f>
+        <v>4-遠方怪群</v>
+      </c>
+      <c r="D338" t="str">
+        <f>計算表!D355</f>
+        <v>未警戒遊走</v>
+      </c>
+      <c r="E338" t="str">
+        <f>計算表!E355</f>
+        <v>出生點半徑a米內；跑速×b；到點停留c~d秒</v>
+      </c>
+      <c r="F338" t="str">
+        <f>計算表!F355</f>
+        <v>僅遠方預置怪群未發現玩家時生效。以各隻出生世界座標為固定中心隨機走停；玩家進入NPC視野或怪物受擊後停止遊走並追擊。</v>
+      </c>
+      <c r="G338">
+        <f>計算表!G355</f>
+        <v>8</v>
+      </c>
+      <c r="H338">
+        <f>計算表!H355</f>
+        <v>0.25</v>
+      </c>
+      <c r="I338">
+        <f>計算表!I355</f>
+        <v>0.8</v>
+      </c>
+      <c r="J338">
+        <f>計算表!J355</f>
+        <v>2.5</v>
+      </c>
+      <c r="K338">
+        <f>計算表!K355</f>
+        <v>0</v>
+      </c>
+      <c r="L338">
+        <f>計算表!L355</f>
+        <v>0</v>
+      </c>
+      <c r="M338">
+        <f>計算表!M355</f>
+        <v>0</v>
+      </c>
+      <c r="N338">
+        <f>計算表!N355</f>
+        <v>0</v>
+      </c>
+      <c r="O338">
+        <f>計算表!O355</f>
+        <v>0</v>
+      </c>
+      <c r="P338">
+        <f>計算表!P355</f>
+        <v>0</v>
+      </c>
+      <c r="Q338">
+        <f>計算表!Q355</f>
+        <v>0</v>
+      </c>
+      <c r="R338">
+        <f>計算表!R355</f>
+        <v>0</v>
       </c>
     </row>
     <row r="339" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A339" s="7" t="s">
-        <v>1170</v>
-      </c>
-      <c r="B339" s="7" t="s">
-        <v>1153</v>
-      </c>
-      <c r="C339" s="7" t="s">
-        <v>1050</v>
-      </c>
-      <c r="D339" s="7" t="s">
-        <v>1171</v>
-      </c>
-      <c r="E339" s="7" t="s">
-        <v>1172</v>
-      </c>
-      <c r="F339" s="7" t="s">
-        <v>1173</v>
-      </c>
-      <c r="G339" s="7" t="s">
-        <v>1163</v>
-      </c>
-      <c r="H339" s="7" t="s">
-        <v>1174</v>
-      </c>
-      <c r="I339" s="7" t="s">
-        <v>1175</v>
-      </c>
-      <c r="J339" s="7" t="s">
-        <v>1163</v>
-      </c>
-      <c r="K339" s="7" t="s">
-        <v>1176</v>
-      </c>
-      <c r="L339" s="7" t="s">
-        <v>1177</v>
-      </c>
-      <c r="M339" s="7" t="s">
-        <v>1178</v>
-      </c>
-      <c r="N339" s="7" t="s">
-        <v>1179</v>
-      </c>
-      <c r="O339" s="7" t="s">
-        <v>1153</v>
-      </c>
-      <c r="P339" s="7" t="s">
-        <v>1153</v>
-      </c>
-      <c r="Q339" s="7" t="s">
-        <v>1153</v>
-      </c>
-      <c r="R339" s="7" t="s">
-        <v>1153</v>
+      <c r="A339">
+        <f>計算表!A356</f>
+        <v>359</v>
+      </c>
+      <c r="B339">
+        <f>計算表!B356</f>
+        <v>0</v>
+      </c>
+      <c r="C339" t="str">
+        <f>計算表!C356</f>
+        <v>4-菁英群組</v>
+      </c>
+      <c r="D339" t="str">
+        <f>計算表!D356</f>
+        <v>封魔塔BOSS玩家技能</v>
+      </c>
+      <c r="E339" t="str">
+        <f>計算表!E356</f>
+        <v>傷害×a% 跳動×b% 範圍×c% 增益×d% 控場×e% 護盾×f% 復活生命×g%；被動最短間隔 h 秒</v>
+      </c>
+      <c r="F339" t="str">
+        <f>計算表!F356</f>
+        <v>封魔塔 BOSS 施放的玩家超神進化技能（Skills2 超神列的封魔塔層級＝該層 BOSS 固定使用；規則與對照表見 docs/BOSS_PLAYER_SKILLS.md）的整體強度。a＝技能傷害倍率（%）：技能 pct% 乘 a% 就是 BOSS 攻擊力的倍數；b＝持續場域與領域每次跳動的再折扣（%）；c＝範圍半徑倍率（%，玩家技能的範圍是為打一群怪設計的）；d＝玩家式增益（攻擊提高％、疊層）轉成 BOSS 增益的強度（%）；e＝控場（暈眩、緩速）秒數倍率（%）；f＝護盾量倍率（%）；g＝復活類技能復活後的生命倍率（%）；h＝被動反應技能（神聖之體、天穹崩裂）兩次觸發的最短間隔（秒）。單一技能要個別調整時，在 Skills2 該列的效果參數(JSON) 補 bossMul（傷害倍率）、bossCd 與 bossCdMax（冷卻秒數）。</v>
+      </c>
+      <c r="G339">
+        <f>計算表!G356</f>
+        <v>25</v>
+      </c>
+      <c r="H339">
+        <f>計算表!H356</f>
+        <v>20</v>
+      </c>
+      <c r="I339">
+        <f>計算表!I356</f>
+        <v>60</v>
+      </c>
+      <c r="J339">
+        <f>計算表!J356</f>
+        <v>25</v>
+      </c>
+      <c r="K339">
+        <f>計算表!K356</f>
+        <v>50</v>
+      </c>
+      <c r="L339">
+        <f>計算表!L356</f>
+        <v>15</v>
+      </c>
+      <c r="M339">
+        <f>計算表!M356</f>
+        <v>40</v>
+      </c>
+      <c r="N339">
+        <f>計算表!N356</f>
+        <v>4</v>
+      </c>
+      <c r="O339">
+        <f>計算表!O356</f>
+        <v>0</v>
+      </c>
+      <c r="P339">
+        <f>計算表!P356</f>
+        <v>0</v>
+      </c>
+      <c r="Q339">
+        <f>計算表!Q356</f>
+        <v>0</v>
+      </c>
+      <c r="R339">
+        <f>計算表!R356</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -29833,7 +29840,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AB353"/>
+  <dimension ref="A1:AB356"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="23.42578125" customWidth="1"/>
@@ -30658,7 +30665,7 @@
         <v>901</v>
       </c>
       <c r="F15" t="s">
-        <v>1205</v>
+        <v>1187</v>
       </c>
       <c r="G15">
         <v>1000</v>
@@ -30715,7 +30722,7 @@
         <v>36</v>
       </c>
       <c r="F16" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -30772,7 +30779,7 @@
         <v>36</v>
       </c>
       <c r="F17" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="G17">
         <v>1.5</v>
@@ -30829,7 +30836,7 @@
         <v>36</v>
       </c>
       <c r="F18" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="G18">
         <v>2.5</v>
@@ -30886,7 +30893,7 @@
         <v>36</v>
       </c>
       <c r="F19" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="G19">
         <v>3.5</v>
@@ -30943,7 +30950,7 @@
         <v>36</v>
       </c>
       <c r="F20" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="G20">
         <v>5</v>
@@ -31000,7 +31007,7 @@
         <v>36</v>
       </c>
       <c r="F21" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="G21">
         <v>7</v>
@@ -31057,7 +31064,7 @@
         <v>36</v>
       </c>
       <c r="F22" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="G22">
         <v>10</v>
@@ -31114,7 +31121,7 @@
         <v>36</v>
       </c>
       <c r="F23" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="G23">
         <v>14</v>
@@ -31171,7 +31178,7 @@
         <v>36</v>
       </c>
       <c r="F24" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="G24">
         <v>18</v>
@@ -31228,7 +31235,7 @@
         <v>36</v>
       </c>
       <c r="F25" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="G25">
         <v>24</v>
@@ -31285,7 +31292,7 @@
         <v>36</v>
       </c>
       <c r="F26" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="G26">
         <v>30</v>
@@ -31342,7 +31349,7 @@
         <v>36</v>
       </c>
       <c r="F27" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="G27">
         <v>60</v>
@@ -31399,7 +31406,7 @@
         <v>36</v>
       </c>
       <c r="F28" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="G28">
         <v>100</v>
@@ -31456,7 +31463,7 @@
         <v>36</v>
       </c>
       <c r="F29" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="G29">
         <v>150</v>
@@ -31513,7 +31520,7 @@
         <v>36</v>
       </c>
       <c r="F30" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="G30">
         <v>200</v>
@@ -31570,7 +31577,7 @@
         <v>36</v>
       </c>
       <c r="F31" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="G31">
         <v>300</v>
@@ -31627,7 +31634,7 @@
         <v>36</v>
       </c>
       <c r="F32" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="G32">
         <v>450</v>
@@ -31684,7 +31691,7 @@
         <v>36</v>
       </c>
       <c r="F33" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="G33">
         <v>650</v>
@@ -31741,7 +31748,7 @@
         <v>36</v>
       </c>
       <c r="F34" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="G34">
         <v>800</v>
@@ -31798,7 +31805,7 @@
         <v>36</v>
       </c>
       <c r="F35" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="G35">
         <v>1200</v>
@@ -31855,7 +31862,7 @@
         <v>36</v>
       </c>
       <c r="F36" t="s">
-        <v>1206</v>
+        <v>1188</v>
       </c>
       <c r="G36">
         <v>2500</v>
@@ -41659,7 +41666,7 @@
         <v>597</v>
       </c>
       <c r="F208" t="s">
-        <v>1214</v>
+        <v>1196</v>
       </c>
       <c r="G208">
         <v>2</v>
@@ -43707,10 +43714,10 @@
         <v>625</v>
       </c>
       <c r="E231" t="s">
-        <v>1197</v>
+        <v>1179</v>
       </c>
       <c r="F231" t="s">
-        <v>1198</v>
+        <v>1180</v>
       </c>
       <c r="G231">
         <v>3</v>
@@ -43764,10 +43771,10 @@
         <v>626</v>
       </c>
       <c r="E232" t="s">
-        <v>1199</v>
+        <v>1181</v>
       </c>
       <c r="F232" t="s">
-        <v>1200</v>
+        <v>1182</v>
       </c>
       <c r="G232">
         <v>100</v>
@@ -43821,10 +43828,10 @@
         <v>627</v>
       </c>
       <c r="E233" t="s">
-        <v>1201</v>
+        <v>1183</v>
       </c>
       <c r="F233" t="s">
-        <v>1202</v>
+        <v>1184</v>
       </c>
       <c r="G233">
         <v>9</v>
@@ -43878,10 +43885,10 @@
         <v>628</v>
       </c>
       <c r="E234" t="s">
-        <v>1207</v>
+        <v>1189</v>
       </c>
       <c r="F234" t="s">
-        <v>1208</v>
+        <v>1190</v>
       </c>
       <c r="G234">
         <v>0</v>
@@ -43938,7 +43945,7 @@
         <v>630</v>
       </c>
       <c r="F235" t="s">
-        <v>1209</v>
+        <v>1191</v>
       </c>
       <c r="G235">
         <v>0.7</v>
@@ -47643,7 +47650,7 @@
         <v>844</v>
       </c>
       <c r="F300" t="s">
-        <v>1215</v>
+        <v>1197</v>
       </c>
       <c r="G300">
         <v>25</v>
@@ -50699,6 +50706,177 @@
         <v>0</v>
       </c>
       <c r="R353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A354">
+        <f t="shared" ref="A354:A356" si="11">A353+1</f>
+        <v>357</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D354" t="s">
+        <v>1175</v>
+      </c>
+      <c r="E354" t="s">
+        <v>1198</v>
+      </c>
+      <c r="F354" t="s">
+        <v>1199</v>
+      </c>
+      <c r="G354" s="8">
+        <v>100</v>
+      </c>
+      <c r="H354" s="8">
+        <v>160</v>
+      </c>
+      <c r="I354" s="8">
+        <v>70</v>
+      </c>
+      <c r="J354" s="8">
+        <v>8</v>
+      </c>
+      <c r="K354" s="8">
+        <v>4</v>
+      </c>
+      <c r="L354" s="8">
+        <v>4</v>
+      </c>
+      <c r="M354" s="8">
+        <v>0</v>
+      </c>
+      <c r="N354" s="8">
+        <v>0</v>
+      </c>
+      <c r="O354" s="8">
+        <v>0</v>
+      </c>
+      <c r="P354" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q354" s="8">
+        <v>0</v>
+      </c>
+      <c r="R354" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A355">
+        <f t="shared" si="11"/>
+        <v>358</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355" t="s">
+        <v>1174</v>
+      </c>
+      <c r="D355" t="s">
+        <v>1177</v>
+      </c>
+      <c r="E355" t="s">
+        <v>1178</v>
+      </c>
+      <c r="F355" t="s">
+        <v>1200</v>
+      </c>
+      <c r="G355" s="8">
+        <v>8</v>
+      </c>
+      <c r="H355" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="I355" s="8">
+        <v>0.8</v>
+      </c>
+      <c r="J355" s="8">
+        <v>2.5</v>
+      </c>
+      <c r="K355" s="8">
+        <v>0</v>
+      </c>
+      <c r="L355" s="8">
+        <v>0</v>
+      </c>
+      <c r="M355" s="8">
+        <v>0</v>
+      </c>
+      <c r="N355" s="8">
+        <v>0</v>
+      </c>
+      <c r="O355" s="8">
+        <v>0</v>
+      </c>
+      <c r="P355" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q355" s="8">
+        <v>0</v>
+      </c>
+      <c r="R355" s="8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A356">
+        <f t="shared" si="11"/>
+        <v>359</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D356" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E356" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F356" t="s">
+        <v>1172</v>
+      </c>
+      <c r="G356" s="8">
+        <v>25</v>
+      </c>
+      <c r="H356" s="8">
+        <v>20</v>
+      </c>
+      <c r="I356" s="8">
+        <v>60</v>
+      </c>
+      <c r="J356" s="8">
+        <v>25</v>
+      </c>
+      <c r="K356" s="8">
+        <v>50</v>
+      </c>
+      <c r="L356" s="8">
+        <v>15</v>
+      </c>
+      <c r="M356" s="8">
+        <v>40</v>
+      </c>
+      <c r="N356" s="8">
+        <v>4</v>
+      </c>
+      <c r="O356" s="8">
+        <v>0</v>
+      </c>
+      <c r="P356" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q356" s="8">
+        <v>0</v>
+      </c>
+      <c r="R356" s="8">
         <v>0</v>
       </c>
     </row>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.codex\visualizations\2026\10\28\01a180f1-c923-7602-8f0f-e80d1ccc6e78\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\codex\config\param-patches\archive\2026-10-29T11-26-02-803Z-20204697-bfee-4d5d-9300-76352337712b\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A43013B-C95B-49C1-9BB3-64D8A3BA1FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A166EEC4-F6CA-4F9E-BA07-CC3CC0C73F40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3015" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -24705,7 +24705,7 @@
       </c>
       <c r="H267">
         <f>計算表!H286</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I267">
         <f>計算表!I286</f>
@@ -48303,7 +48303,7 @@
         <v>0.2</v>
       </c>
       <c r="H286">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I286">
         <v>0</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.codex\visualizations\2026\10\28\01a180f1-c923-7602-8f0f-e80d1ccc6e78\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\claude\config\param-patches\archive\2026-10-29T11-25-54-214Z-4ee11e04-ddb3-4bfc-8366-523db214a548\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A43013B-C95B-49C1-9BB3-64D8A3BA1FB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A5AA6DA-5997-4C1F-9117-3DEDBAB26938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3015" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -24705,7 +24705,7 @@
       </c>
       <c r="H267">
         <f>計算表!H286</f>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I267">
         <f>計算表!I286</f>
@@ -48303,7 +48303,7 @@
         <v>0.2</v>
       </c>
       <c r="H286">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="I286">
         <v>0</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyGame\Idle-RPG\claude\config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33719C6B-FD07-43AA-91F6-3FE0CC75A924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A4A26CA-527B-4FCA-9659-C4268563987C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3015" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="game_parameters" sheetId="1" r:id="rId1"/>
@@ -5147,12 +5147,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R365"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5208,7 +5208,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2">
         <f>計算表!A2</f>
         <v>1</v>
@@ -5282,7 +5282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>計算表!A3</f>
         <v>2</v>
@@ -5356,7 +5356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4">
         <f>計算表!A4</f>
         <v>3</v>
@@ -5430,7 +5430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5">
         <f>計算表!A5</f>
         <v>4</v>
@@ -5504,7 +5504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6">
         <f>計算表!A6</f>
         <v>5</v>
@@ -5578,7 +5578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7">
         <f>計算表!A7</f>
         <v>6</v>
@@ -5652,7 +5652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8">
         <f>計算表!A8</f>
         <v>7</v>
@@ -5726,7 +5726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9">
         <f>計算表!A9</f>
         <v>8</v>
@@ -5800,7 +5800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10">
         <f>計算表!A10</f>
         <v>9</v>
@@ -5874,7 +5874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>計算表!A11</f>
         <v>11</v>
@@ -5946,7 +5946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12">
         <f>計算表!A12</f>
         <v>12</v>
@@ -6017,7 +6017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13">
         <f>計算表!A14</f>
         <v>14</v>
@@ -6091,7 +6091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14">
         <f>計算表!A15</f>
         <v>15</v>
@@ -6162,7 +6162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15">
         <f>計算表!A16</f>
         <v>16</v>
@@ -6234,7 +6234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16">
         <f>計算表!A17</f>
         <v>17</v>
@@ -6306,7 +6306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17">
         <f>計算表!A18</f>
         <v>18</v>
@@ -6378,7 +6378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18">
         <f>計算表!A19</f>
         <v>19</v>
@@ -6450,7 +6450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19">
         <f>計算表!A20</f>
         <v>20</v>
@@ -6522,7 +6522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20">
         <f>計算表!A21</f>
         <v>21</v>
@@ -6594,7 +6594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21">
         <f>計算表!A22</f>
         <v>22</v>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22">
         <f>計算表!A23</f>
         <v>23</v>
@@ -6738,7 +6738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23">
         <f>計算表!A24</f>
         <v>24</v>
@@ -6810,7 +6810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24">
         <f>計算表!A25</f>
         <v>25</v>
@@ -6882,7 +6882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25">
         <f>計算表!A26</f>
         <v>26</v>
@@ -6954,7 +6954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26">
         <f>計算表!A27</f>
         <v>27</v>
@@ -7026,7 +7026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27">
         <f>計算表!A28</f>
         <v>28</v>
@@ -7098,7 +7098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28">
         <f>計算表!A29</f>
         <v>29</v>
@@ -7170,7 +7170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29">
         <f>計算表!A30</f>
         <v>30</v>
@@ -7242,7 +7242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30">
         <f>計算表!A31</f>
         <v>31</v>
@@ -7314,7 +7314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31">
         <f>計算表!A32</f>
         <v>32</v>
@@ -7386,7 +7386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32">
         <f>計算表!A33</f>
         <v>33</v>
@@ -7458,7 +7458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33">
         <f>計算表!A34</f>
         <v>34</v>
@@ -7530,7 +7530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34">
         <f>計算表!A35</f>
         <v>35</v>
@@ -7602,7 +7602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35">
         <f>計算表!A36</f>
         <v>36</v>
@@ -7674,7 +7674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36">
         <f>計算表!A37</f>
         <v>37</v>
@@ -7748,7 +7748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37">
         <f>計算表!A38</f>
         <v>38</v>
@@ -7822,7 +7822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38">
         <f>計算表!A39</f>
         <v>39</v>
@@ -7896,7 +7896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39">
         <f>計算表!A40</f>
         <v>40</v>
@@ -7970,7 +7970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40">
         <f>計算表!A41</f>
         <v>41</v>
@@ -8044,7 +8044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41">
         <f>計算表!A42</f>
         <v>42</v>
@@ -8118,7 +8118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42">
         <f>計算表!A43</f>
         <v>43</v>
@@ -8192,7 +8192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43">
         <f>計算表!A44</f>
         <v>44</v>
@@ -8266,7 +8266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44">
         <f>計算表!A45</f>
         <v>45</v>
@@ -8340,7 +8340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45">
         <f>計算表!A46</f>
         <v>46</v>
@@ -8414,7 +8414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46">
         <f>計算表!A47</f>
         <v>47</v>
@@ -8488,7 +8488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47">
         <f>計算表!A48</f>
         <v>48</v>
@@ -8562,7 +8562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48">
         <f>計算表!A49</f>
         <v>49</v>
@@ -8636,7 +8636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49">
         <f>計算表!A50</f>
         <v>50</v>
@@ -8710,7 +8710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50">
         <f>計算表!A51</f>
         <v>51</v>
@@ -8784,7 +8784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51">
         <f>計算表!A52</f>
         <v>52</v>
@@ -8858,7 +8858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52">
         <f>計算表!A53</f>
         <v>53</v>
@@ -8932,7 +8932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53">
         <f>計算表!A54</f>
         <v>54</v>
@@ -9006,7 +9006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54">
         <f>計算表!A55</f>
         <v>55</v>
@@ -9080,7 +9080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55">
         <f>計算表!A56</f>
         <v>56</v>
@@ -9154,7 +9154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56">
         <f>計算表!A57</f>
         <v>57</v>
@@ -9226,7 +9226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57">
         <f>計算表!A58</f>
         <v>58</v>
@@ -9300,7 +9300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58">
         <f>計算表!A59</f>
         <v>59</v>
@@ -9370,7 +9370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59">
         <f>計算表!A60</f>
         <v>60</v>
@@ -9444,7 +9444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60">
         <f>計算表!A61</f>
         <v>61</v>
@@ -9518,7 +9518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61">
         <f>計算表!A62</f>
         <v>62</v>
@@ -9588,7 +9588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62">
         <f>計算表!A63</f>
         <v>63</v>
@@ -9658,7 +9658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63">
         <f>計算表!A64</f>
         <v>64</v>
@@ -9731,7 +9731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64">
         <f>計算表!A65</f>
         <v>65</v>
@@ -9799,7 +9799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65">
         <f>計算表!A66</f>
         <v>66</v>
@@ -9870,7 +9870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66">
         <f>計算表!A67</f>
         <v>67</v>
@@ -9943,7 +9943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A67">
         <f>計算表!A68</f>
         <v>68</v>
@@ -10016,7 +10016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68">
         <f>計算表!A69</f>
         <v>69</v>
@@ -10089,7 +10089,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69">
         <f>計算表!A70</f>
         <v>70</v>
@@ -10158,7 +10158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70">
         <f>計算表!A71</f>
         <v>71</v>
@@ -10232,7 +10232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A71">
         <f>計算表!A72</f>
         <v>72</v>
@@ -10306,7 +10306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72">
         <f>計算表!A73</f>
         <v>73</v>
@@ -10380,7 +10380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A73">
         <f>計算表!A74</f>
         <v>74</v>
@@ -10454,7 +10454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74">
         <f>計算表!A75</f>
         <v>75</v>
@@ -10528,7 +10528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75">
         <f>計算表!A76</f>
         <v>76</v>
@@ -10602,7 +10602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76">
         <f>計算表!A77</f>
         <v>77</v>
@@ -10676,7 +10676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77">
         <f>計算表!A78</f>
         <v>78</v>
@@ -10750,7 +10750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78">
         <f>計算表!A79</f>
         <v>79</v>
@@ -10824,7 +10824,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79">
         <f>計算表!A80</f>
         <v>80</v>
@@ -10898,7 +10898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80">
         <f>計算表!A81</f>
         <v>81</v>
@@ -10972,7 +10972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81">
         <f>計算表!A82</f>
         <v>82</v>
@@ -11046,7 +11046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82">
         <f>計算表!A83</f>
         <v>83</v>
@@ -11120,7 +11120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83">
         <f>計算表!A84</f>
         <v>84</v>
@@ -11194,7 +11194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84">
         <f>計算表!A85</f>
         <v>85</v>
@@ -11268,7 +11268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85">
         <f>計算表!A86</f>
         <v>86</v>
@@ -11342,7 +11342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86">
         <f>計算表!A87</f>
         <v>87</v>
@@ -11416,7 +11416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87">
         <f>計算表!A88</f>
         <v>88</v>
@@ -11490,7 +11490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88">
         <f>計算表!A89</f>
         <v>89</v>
@@ -11564,7 +11564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89">
         <f>計算表!A90</f>
         <v>90</v>
@@ -11638,7 +11638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90">
         <f>計算表!A91</f>
         <v>91</v>
@@ -11712,7 +11712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91">
         <f>計算表!A92</f>
         <v>92</v>
@@ -11786,7 +11786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92">
         <f>計算表!A93</f>
         <v>93</v>
@@ -11860,7 +11860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93">
         <f>計算表!A94</f>
         <v>94</v>
@@ -11934,7 +11934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94">
         <f>計算表!A95</f>
         <v>95</v>
@@ -12007,7 +12007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95">
         <f>計算表!A96</f>
         <v>96</v>
@@ -12081,7 +12081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96">
         <f>計算表!A97</f>
         <v>97</v>
@@ -12155,7 +12155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97">
         <f>計算表!A98</f>
         <v>98</v>
@@ -12229,7 +12229,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98">
         <f>計算表!A99</f>
         <v>99</v>
@@ -12303,7 +12303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A99">
         <f>計算表!A100</f>
         <v>100</v>
@@ -12377,7 +12377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100">
         <f>計算表!A101</f>
         <v>101</v>
@@ -12451,7 +12451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101">
         <f>計算表!A102</f>
         <v>102</v>
@@ -12525,7 +12525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102">
         <f>計算表!A103</f>
         <v>103</v>
@@ -12599,7 +12599,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103">
         <f>計算表!A104</f>
         <v>104</v>
@@ -12673,7 +12673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A104">
         <f>計算表!A105</f>
         <v>105</v>
@@ -12747,7 +12747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A105">
         <f>計算表!A106</f>
         <v>106</v>
@@ -12821,7 +12821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A106">
         <f>計算表!A107</f>
         <v>107</v>
@@ -12895,7 +12895,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A107">
         <f>計算表!A108</f>
         <v>108</v>
@@ -12969,7 +12969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A108">
         <f>計算表!A109</f>
         <v>109</v>
@@ -13043,7 +13043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A109">
         <f>計算表!A110</f>
         <v>110</v>
@@ -13117,7 +13117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A110">
         <f>計算表!A111</f>
         <v>111</v>
@@ -13191,7 +13191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A111">
         <f>計算表!A112</f>
         <v>112</v>
@@ -13265,7 +13265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A112">
         <f>計算表!A113</f>
         <v>113</v>
@@ -13339,7 +13339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A113">
         <f>計算表!A114</f>
         <v>114</v>
@@ -13413,7 +13413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A114">
         <f>計算表!A115</f>
         <v>115</v>
@@ -13487,7 +13487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A115">
         <f>計算表!A116</f>
         <v>116</v>
@@ -13561,7 +13561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A116">
         <f>計算表!A117</f>
         <v>117</v>
@@ -13635,7 +13635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A117">
         <f>計算表!A118</f>
         <v>118</v>
@@ -13709,7 +13709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A118">
         <f>計算表!A119</f>
         <v>119</v>
@@ -13782,7 +13782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A119">
         <f>計算表!A120</f>
         <v>120</v>
@@ -13856,7 +13856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A120">
         <f>計算表!A121</f>
         <v>121</v>
@@ -13930,7 +13930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A121">
         <f>計算表!A122</f>
         <v>122</v>
@@ -14004,7 +14004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A122">
         <f>計算表!A123</f>
         <v>123</v>
@@ -14078,7 +14078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A123">
         <f>計算表!A124</f>
         <v>124</v>
@@ -14152,7 +14152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A124">
         <f>計算表!A125</f>
         <v>125</v>
@@ -14226,7 +14226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A125">
         <f>計算表!A126</f>
         <v>126</v>
@@ -14300,7 +14300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A126">
         <f>計算表!A127</f>
         <v>127</v>
@@ -14374,7 +14374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A127">
         <f>計算表!A128</f>
         <v>128</v>
@@ -14448,7 +14448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A128">
         <f>計算表!A129</f>
         <v>129</v>
@@ -14522,7 +14522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A129">
         <f>計算表!A130</f>
         <v>130</v>
@@ -14596,7 +14596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A130">
         <f>計算表!A131</f>
         <v>131</v>
@@ -14670,7 +14670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A131">
         <f>計算表!A132</f>
         <v>132</v>
@@ -14744,7 +14744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A132">
         <f>計算表!A133</f>
         <v>133</v>
@@ -14818,7 +14818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A133">
         <f>計算表!A134</f>
         <v>134</v>
@@ -14892,7 +14892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A134">
         <f>計算表!A135</f>
         <v>135</v>
@@ -14966,7 +14966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A135">
         <f>計算表!A136</f>
         <v>136</v>
@@ -15040,7 +15040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A136">
         <f>計算表!A137</f>
         <v>137</v>
@@ -15114,7 +15114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A137">
         <f>計算表!A138</f>
         <v>138</v>
@@ -15188,7 +15188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A138">
         <f>計算表!A139</f>
         <v>139</v>
@@ -15262,7 +15262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A139">
         <f>計算表!A140</f>
         <v>140</v>
@@ -15336,7 +15336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A140">
         <f>計算表!A141</f>
         <v>141</v>
@@ -15410,7 +15410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A141">
         <f>計算表!A142</f>
         <v>142</v>
@@ -15484,7 +15484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A142">
         <f>計算表!A143</f>
         <v>143</v>
@@ -15558,7 +15558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A143">
         <f>計算表!A144</f>
         <v>144</v>
@@ -15632,7 +15632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A144">
         <f>計算表!A145</f>
         <v>145</v>
@@ -15705,7 +15705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A145">
         <f>計算表!A146</f>
         <v>146</v>
@@ -15776,7 +15776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A146">
         <f>計算表!A147</f>
         <v>147</v>
@@ -15846,7 +15846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A147">
         <f>計算表!A148</f>
         <v>148</v>
@@ -15914,7 +15914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A148">
         <f>計算表!A149</f>
         <v>149</v>
@@ -15980,7 +15980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A149">
         <f>計算表!A150</f>
         <v>150</v>
@@ -16046,7 +16046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A150">
         <f>計算表!A151</f>
         <v>151</v>
@@ -16111,7 +16111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A151">
         <f>計算表!A152</f>
         <v>152</v>
@@ -16184,7 +16184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A152">
         <f>計算表!A153</f>
         <v>153</v>
@@ -16258,7 +16258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A153">
         <f>計算表!A154</f>
         <v>154</v>
@@ -16332,7 +16332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A154">
         <f>計算表!A155</f>
         <v>155</v>
@@ -16406,7 +16406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A155">
         <f>計算表!A156</f>
         <v>156</v>
@@ -16480,7 +16480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A156">
         <f>計算表!A157</f>
         <v>157</v>
@@ -16554,7 +16554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A157">
         <f>計算表!A158</f>
         <v>158</v>
@@ -16628,7 +16628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A158">
         <f>計算表!A159</f>
         <v>159</v>
@@ -16702,7 +16702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A159">
         <f>計算表!A160</f>
         <v>160</v>
@@ -16776,7 +16776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A160">
         <f>計算表!A161</f>
         <v>161</v>
@@ -16850,7 +16850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A161">
         <f>計算表!A162</f>
         <v>162</v>
@@ -16924,7 +16924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A162">
         <f>計算表!A163</f>
         <v>163</v>
@@ -16998,7 +16998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A163">
         <f>計算表!A164</f>
         <v>164</v>
@@ -17072,7 +17072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A164">
         <f>計算表!A165</f>
         <v>165</v>
@@ -17146,7 +17146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A165">
         <f>計算表!A166</f>
         <v>166</v>
@@ -17220,7 +17220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A166">
         <f>計算表!A167</f>
         <v>167</v>
@@ -17294,7 +17294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A167">
         <f>計算表!A168</f>
         <v>168</v>
@@ -17368,7 +17368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A168">
         <f>計算表!A169</f>
         <v>169</v>
@@ -17442,7 +17442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A169">
         <f>計算表!A170</f>
         <v>171</v>
@@ -17516,7 +17516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A170">
         <f>計算表!A171</f>
         <v>172</v>
@@ -17589,7 +17589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A171">
         <f>計算表!A172</f>
         <v>173</v>
@@ -17663,7 +17663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A172">
         <f>計算表!A173</f>
         <v>174</v>
@@ -17737,7 +17737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A173">
         <f>計算表!A174</f>
         <v>175</v>
@@ -17811,7 +17811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A174">
         <f>計算表!A175</f>
         <v>176</v>
@@ -17885,7 +17885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A175">
         <f>計算表!A176</f>
         <v>177</v>
@@ -17959,7 +17959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A176">
         <f>計算表!A177</f>
         <v>178</v>
@@ -18033,7 +18033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A177">
         <f>計算表!A178</f>
         <v>179</v>
@@ -18107,7 +18107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A178">
         <f>計算表!A179</f>
         <v>180</v>
@@ -18180,7 +18180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A179">
         <f>計算表!A180</f>
         <v>181</v>
@@ -18254,7 +18254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A180">
         <f>計算表!A181</f>
         <v>182</v>
@@ -18328,7 +18328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A181">
         <f>計算表!A197</f>
         <v>198</v>
@@ -18402,7 +18402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A182">
         <f>計算表!A198</f>
         <v>199</v>
@@ -18476,7 +18476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A183">
         <f>計算表!A199</f>
         <v>200</v>
@@ -18550,7 +18550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A184">
         <f>計算表!A200</f>
         <v>201</v>
@@ -18624,7 +18624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A185">
         <f>計算表!A201</f>
         <v>202</v>
@@ -18698,7 +18698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A186">
         <f>計算表!A202</f>
         <v>203</v>
@@ -18772,7 +18772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A187">
         <f>計算表!A203</f>
         <v>204</v>
@@ -18846,7 +18846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A188">
         <f>計算表!A204</f>
         <v>205</v>
@@ -18920,7 +18920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A189">
         <f>計算表!A205</f>
         <v>206</v>
@@ -18994,7 +18994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A190">
         <f>計算表!A206</f>
         <v>207</v>
@@ -19068,7 +19068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A191">
         <f>計算表!A207</f>
         <v>208</v>
@@ -19142,7 +19142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A192">
         <f>計算表!A208</f>
         <v>209</v>
@@ -19216,7 +19216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A193">
         <f>計算表!A209</f>
         <v>210</v>
@@ -19290,7 +19290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A194">
         <f>計算表!A210</f>
         <v>211</v>
@@ -19364,7 +19364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A195">
         <f>計算表!A211</f>
         <v>212</v>
@@ -19438,7 +19438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A196">
         <f>計算表!A212</f>
         <v>213</v>
@@ -19512,7 +19512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A197">
         <f>計算表!A213</f>
         <v>214</v>
@@ -19586,7 +19586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A198">
         <f>計算表!A214</f>
         <v>215</v>
@@ -19660,7 +19660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A199">
         <f>計算表!A215</f>
         <v>216</v>
@@ -19734,7 +19734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A200">
         <f>計算表!A216</f>
         <v>217</v>
@@ -19808,7 +19808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A201">
         <f>計算表!A217</f>
         <v>218</v>
@@ -19882,7 +19882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A202">
         <f>計算表!A218</f>
         <v>219</v>
@@ -19955,7 +19955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A203">
         <f>計算表!A219</f>
         <v>220</v>
@@ -20029,7 +20029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A204">
         <f>計算表!A220</f>
         <v>221</v>
@@ -20101,7 +20101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A205">
         <f>計算表!A221</f>
         <v>222</v>
@@ -20175,7 +20175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A206">
         <f>計算表!A222</f>
         <v>223</v>
@@ -20249,7 +20249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A207">
         <f>計算表!A223</f>
         <v>224</v>
@@ -20323,7 +20323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A208">
         <f>計算表!A224</f>
         <v>225</v>
@@ -20397,7 +20397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A209">
         <f>計算表!A225</f>
         <v>226</v>
@@ -20471,7 +20471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A210">
         <f>計算表!A226</f>
         <v>227</v>
@@ -20545,7 +20545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A211">
         <f>計算表!A227</f>
         <v>228</v>
@@ -20619,7 +20619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A212">
         <f>計算表!A228</f>
         <v>229</v>
@@ -20693,7 +20693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A213">
         <f>計算表!A229</f>
         <v>230</v>
@@ -20767,7 +20767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A214">
         <f>計算表!A230</f>
         <v>231</v>
@@ -20841,7 +20841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A215">
         <f>計算表!A231</f>
         <v>232</v>
@@ -20915,7 +20915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A216">
         <f>計算表!A232</f>
         <v>233</v>
@@ -20989,7 +20989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A217">
         <f>計算表!A233</f>
         <v>234</v>
@@ -21063,7 +21063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A218">
         <f>計算表!A234</f>
         <v>235</v>
@@ -21137,7 +21137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A219">
         <f>計算表!A235</f>
         <v>236</v>
@@ -21211,7 +21211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A220">
         <f>計算表!A236</f>
         <v>237</v>
@@ -21285,7 +21285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A221">
         <f>計算表!A237</f>
         <v>238</v>
@@ -21359,7 +21359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A222">
         <f>計算表!A238</f>
         <v>239</v>
@@ -21433,7 +21433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A223">
         <f>計算表!A239</f>
         <v>240</v>
@@ -21507,7 +21507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A224">
         <f>計算表!A240</f>
         <v>241</v>
@@ -21581,7 +21581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A225">
         <f>計算表!A241</f>
         <v>242</v>
@@ -21655,7 +21655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A226">
         <f>計算表!A242</f>
         <v>243</v>
@@ -21729,7 +21729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A227">
         <f>計算表!A243</f>
         <v>244</v>
@@ -21803,7 +21803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A228">
         <f>計算表!A244</f>
         <v>245</v>
@@ -21877,7 +21877,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A229">
         <f>計算表!A245</f>
         <v>246</v>
@@ -21951,7 +21951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A230">
         <f>計算表!A246</f>
         <v>247</v>
@@ -22025,7 +22025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A231">
         <f>計算表!A247</f>
         <v>248</v>
@@ -22099,7 +22099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A232">
         <f>計算表!A248</f>
         <v>249</v>
@@ -22173,7 +22173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A233">
         <f>計算表!A249</f>
         <v>250</v>
@@ -22247,7 +22247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A234">
         <f>計算表!A250</f>
         <v>251</v>
@@ -22321,7 +22321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A235">
         <f>計算表!A251</f>
         <v>252</v>
@@ -22395,7 +22395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A236">
         <f>計算表!A252</f>
         <v>253</v>
@@ -22469,7 +22469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A237">
         <f>計算表!A253</f>
         <v>254</v>
@@ -22543,7 +22543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A238">
         <f>計算表!A254</f>
         <v>255</v>
@@ -22617,7 +22617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A239">
         <f>計算表!A255</f>
         <v>256</v>
@@ -22691,7 +22691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A240">
         <f>計算表!A256</f>
         <v>257</v>
@@ -22765,7 +22765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A241">
         <f>計算表!A257</f>
         <v>258</v>
@@ -22839,7 +22839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A242">
         <f>計算表!A258</f>
         <v>259</v>
@@ -22913,7 +22913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A243">
         <f>計算表!A259</f>
         <v>260</v>
@@ -22987,7 +22987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A244">
         <f>計算表!A260</f>
         <v>261</v>
@@ -23061,7 +23061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A245">
         <f>計算表!A261</f>
         <v>262</v>
@@ -23135,7 +23135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A246">
         <f>計算表!A262</f>
         <v>263</v>
@@ -23209,7 +23209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A247">
         <f>計算表!A263</f>
         <v>264</v>
@@ -23283,7 +23283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A248">
         <f>計算表!A264</f>
         <v>265</v>
@@ -23357,7 +23357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A249">
         <f>計算表!A265</f>
         <v>266</v>
@@ -23431,7 +23431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A250">
         <f>計算表!A266</f>
         <v>267</v>
@@ -23505,7 +23505,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A251">
         <f>計算表!A267</f>
         <v>268</v>
@@ -23579,7 +23579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A252">
         <f>計算表!A268</f>
         <v>269</v>
@@ -23653,7 +23653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A253">
         <f>計算表!A269</f>
         <v>270</v>
@@ -23727,7 +23727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A254">
         <f>計算表!A270</f>
         <v>271</v>
@@ -23801,7 +23801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A255">
         <f>計算表!A271</f>
         <v>272</v>
@@ -23875,7 +23875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A256">
         <f>計算表!A272</f>
         <v>273</v>
@@ -23949,7 +23949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A257">
         <f>計算表!A273</f>
         <v>274</v>
@@ -24023,7 +24023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A258">
         <f>計算表!A274</f>
         <v>275</v>
@@ -24097,7 +24097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A259">
         <f>計算表!A275</f>
         <v>276</v>
@@ -24171,7 +24171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A260">
         <f>計算表!A276</f>
         <v>277</v>
@@ -24245,7 +24245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A261">
         <f>計算表!A277</f>
         <v>278</v>
@@ -24319,7 +24319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A262">
         <f>計算表!A278</f>
         <v>279</v>
@@ -24393,7 +24393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A263">
         <f>計算表!A279</f>
         <v>280</v>
@@ -24467,7 +24467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A264">
         <f>計算表!A280</f>
         <v>281</v>
@@ -24541,7 +24541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A265">
         <f>計算表!A281</f>
         <v>282</v>
@@ -24615,7 +24615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A266">
         <f>計算表!A285</f>
         <v>286</v>
@@ -24689,7 +24689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A267">
         <f>計算表!A286</f>
         <v>287</v>
@@ -24763,7 +24763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A268">
         <f>計算表!A287</f>
         <v>288</v>
@@ -24837,7 +24837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A269">
         <f>計算表!A300</f>
         <v>303</v>
@@ -24911,7 +24911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A270">
         <f>計算表!A301</f>
         <v>304</v>
@@ -24985,7 +24985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A271">
         <f>計算表!A302</f>
         <v>305</v>
@@ -25059,7 +25059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A272">
         <f>計算表!A303</f>
         <v>306</v>
@@ -25133,7 +25133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A273">
         <f>計算表!A304</f>
         <v>307</v>
@@ -25207,7 +25207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A274">
         <f>計算表!A305</f>
         <v>308</v>
@@ -25281,7 +25281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A275">
         <f>計算表!A306</f>
         <v>309</v>
@@ -25355,7 +25355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A276">
         <f>計算表!A307</f>
         <v>310</v>
@@ -25429,7 +25429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A277">
         <f>計算表!A308</f>
         <v>311</v>
@@ -25503,7 +25503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A278">
         <f>計算表!A309</f>
         <v>312</v>
@@ -25577,7 +25577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A279">
         <f>計算表!A310</f>
         <v>313</v>
@@ -25651,7 +25651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A280">
         <f>計算表!A311</f>
         <v>314</v>
@@ -25725,7 +25725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A281">
         <f>計算表!A312</f>
         <v>315</v>
@@ -25799,7 +25799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A282">
         <f>計算表!A313</f>
         <v>316</v>
@@ -25873,7 +25873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A283">
         <f>計算表!A314</f>
         <v>317</v>
@@ -25947,7 +25947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A284">
         <f>計算表!A315</f>
         <v>318</v>
@@ -26021,7 +26021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A285">
         <f>計算表!A316</f>
         <v>319</v>
@@ -26095,7 +26095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A286">
         <f>計算表!A317</f>
         <v>320</v>
@@ -26169,7 +26169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A287">
         <f>計算表!A318</f>
         <v>321</v>
@@ -26243,7 +26243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A288">
         <f>計算表!A319</f>
         <v>322</v>
@@ -26317,7 +26317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A289">
         <f>計算表!A320</f>
         <v>323</v>
@@ -26391,7 +26391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A290">
         <f>計算表!A321</f>
         <v>324</v>
@@ -26464,7 +26464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A291">
         <f>計算表!A322</f>
         <v>325</v>
@@ -26538,7 +26538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A292">
         <f>計算表!A323</f>
         <v>326</v>
@@ -26612,7 +26612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A293">
         <f>計算表!A324</f>
         <v>327</v>
@@ -26686,7 +26686,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A294">
         <f>計算表!A325</f>
         <v>328</v>
@@ -26760,7 +26760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A295">
         <f>計算表!A326</f>
         <v>329</v>
@@ -26833,7 +26833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A296">
         <f>計算表!A327</f>
         <v>330</v>
@@ -26907,7 +26907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A297">
         <f>計算表!A328</f>
         <v>331</v>
@@ -26981,7 +26981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A298">
         <f>計算表!A329</f>
         <v>332</v>
@@ -27055,7 +27055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A299">
         <f>計算表!A330</f>
         <v>333</v>
@@ -27129,7 +27129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A300">
         <f>計算表!A331</f>
         <v>334</v>
@@ -27203,7 +27203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A301">
         <f>計算表!A332</f>
         <v>335</v>
@@ -27277,7 +27277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A302">
         <f>計算表!A333</f>
         <v>336</v>
@@ -27351,7 +27351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A303">
         <f>計算表!A334</f>
         <v>337</v>
@@ -27425,7 +27425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A304">
         <f>計算表!A335</f>
         <v>338</v>
@@ -27499,7 +27499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A305">
         <f>計算表!A336</f>
         <v>339</v>
@@ -27573,7 +27573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A306">
         <f>計算表!A337</f>
         <v>340</v>
@@ -27647,7 +27647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A307">
         <f>計算表!A338</f>
         <v>341</v>
@@ -27721,7 +27721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A308">
         <f>計算表!A339</f>
         <v>342</v>
@@ -27795,7 +27795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A309">
         <f>計算表!A340</f>
         <v>343</v>
@@ -27869,7 +27869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A310">
         <f>計算表!A341</f>
         <v>344</v>
@@ -27943,7 +27943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A311">
         <f>計算表!A342</f>
         <v>345</v>
@@ -28017,7 +28017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A312">
         <f>計算表!A343</f>
         <v>346</v>
@@ -28091,7 +28091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A313">
         <f>計算表!A344</f>
         <v>347</v>
@@ -28165,7 +28165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A314">
         <f>計算表!A345</f>
         <v>348</v>
@@ -28239,7 +28239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A315">
         <f>計算表!A346</f>
         <v>349</v>
@@ -28313,7 +28313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A316">
         <f>計算表!A347</f>
         <v>350</v>
@@ -28387,7 +28387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A317">
         <f>計算表!A348</f>
         <v>351</v>
@@ -28460,7 +28460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A318">
         <f>計算表!A349</f>
         <v>352</v>
@@ -28487,7 +28487,7 @@
       </c>
       <c r="G318">
         <f>計算表!G349</f>
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="H318">
         <f>計算表!H349</f>
@@ -28534,7 +28534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A319">
         <f>計算表!A350</f>
         <v>353</v>
@@ -28608,7 +28608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A320">
         <f>計算表!A351</f>
         <v>354</v>
@@ -28682,7 +28682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A321">
         <f>計算表!A352</f>
         <v>355</v>
@@ -28756,7 +28756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A322">
         <f>計算表!A353</f>
         <v>356</v>
@@ -28830,7 +28830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A323">
         <f>計算表!A354</f>
         <v>357</v>
@@ -28904,7 +28904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A324">
         <f>計算表!A355</f>
         <v>358</v>
@@ -28978,7 +28978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A325">
         <f>計算表!A356</f>
         <v>359</v>
@@ -29052,7 +29052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A326" s="7">
         <v>360</v>
       </c>
@@ -29108,7 +29108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A327" s="7">
         <v>361</v>
       </c>
@@ -29164,7 +29164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A328" s="7">
         <v>362</v>
       </c>
@@ -29220,7 +29220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A329" s="7">
         <v>363</v>
       </c>
@@ -29276,7 +29276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A330" s="7">
         <v>364</v>
       </c>
@@ -29332,7 +29332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A331" s="7">
         <v>365</v>
       </c>
@@ -29388,7 +29388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A332" s="7">
         <v>366</v>
       </c>
@@ -29444,7 +29444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A333" s="7">
         <v>367</v>
       </c>
@@ -29500,7 +29500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A334" s="7">
         <v>368</v>
       </c>
@@ -29556,7 +29556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A335" s="7">
         <v>369</v>
       </c>
@@ -29612,7 +29612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A336" s="7">
         <v>370</v>
       </c>
@@ -29668,7 +29668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A337" s="7">
         <v>371</v>
       </c>
@@ -29724,7 +29724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A338" s="7">
         <v>372</v>
       </c>
@@ -29780,7 +29780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A339" s="7">
         <v>373</v>
       </c>
@@ -29836,7 +29836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A340" s="7">
         <v>374</v>
       </c>
@@ -29892,7 +29892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A341" s="7">
         <v>375</v>
       </c>
@@ -29948,7 +29948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A342" s="7">
         <v>376</v>
       </c>
@@ -30004,7 +30004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A343" s="7">
         <v>377</v>
       </c>
@@ -30060,7 +30060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A344" s="7">
         <v>378</v>
       </c>
@@ -30116,7 +30116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A345" s="7">
         <v>379</v>
       </c>
@@ -30172,7 +30172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A346" s="7">
         <v>380</v>
       </c>
@@ -30228,7 +30228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A347" s="7">
         <v>381</v>
       </c>
@@ -30284,7 +30284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A348" s="7">
         <v>382</v>
       </c>
@@ -30340,7 +30340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A349" s="7">
         <v>383</v>
       </c>
@@ -30396,7 +30396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A350" s="7">
         <v>384</v>
       </c>
@@ -30452,7 +30452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A351" s="7">
         <v>385</v>
       </c>
@@ -30508,7 +30508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A352" s="7">
         <v>386</v>
       </c>
@@ -30564,7 +30564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A353" s="7">
         <v>387</v>
       </c>
@@ -30620,7 +30620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A354" s="7">
         <v>388</v>
       </c>
@@ -30676,7 +30676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A355" s="7">
         <v>389</v>
       </c>
@@ -30732,7 +30732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A356" s="7">
         <v>390</v>
       </c>
@@ -30788,7 +30788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A357" s="7">
         <v>391</v>
       </c>
@@ -30844,7 +30844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A358" s="7">
         <v>392</v>
       </c>
@@ -30900,7 +30900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A359" s="7">
         <v>393</v>
       </c>
@@ -30956,7 +30956,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A360" s="7">
         <v>394</v>
       </c>
@@ -31012,7 +31012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A361" s="7">
         <v>395</v>
       </c>
@@ -31068,7 +31068,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A362" s="7">
         <v>396</v>
       </c>
@@ -31124,7 +31124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A363" s="7">
         <v>397</v>
       </c>
@@ -31180,7 +31180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A364" s="7">
         <v>398</v>
       </c>
@@ -31236,7 +31236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="365" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A365" s="7">
         <v>399</v>
       </c>
@@ -31301,17 +31301,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AB356"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="23.42578125" customWidth="1"/>
+    <col min="3" max="3" width="23.44140625" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="25.140625" customWidth="1"/>
-    <col min="6" max="6" width="23.42578125" customWidth="1"/>
-    <col min="21" max="21" width="17.7109375" customWidth="1"/>
-    <col min="22" max="28" width="14.5703125" customWidth="1"/>
+    <col min="5" max="5" width="25.109375" customWidth="1"/>
+    <col min="6" max="6" width="23.44140625" customWidth="1"/>
+    <col min="21" max="21" width="17.6640625" customWidth="1"/>
+    <col min="22" max="28" width="14.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -31367,7 +31367,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -31423,7 +31423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -31480,7 +31480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4">
         <f t="shared" ref="A4:A66" si="0">A3+1</f>
         <v>3</v>
@@ -31537,7 +31537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -31594,7 +31594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -31651,7 +31651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -31708,7 +31708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -31765,7 +31765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -31822,7 +31822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -31879,7 +31879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11">
         <f>A10+2</f>
         <v>11</v>
@@ -31936,7 +31936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -31993,7 +31993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -32050,7 +32050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -32107,7 +32107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -32164,7 +32164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -32221,7 +32221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -32278,7 +32278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -32335,7 +32335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -32392,7 +32392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -32449,7 +32449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A21">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -32506,7 +32506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A22">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -32563,7 +32563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A23">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -32620,7 +32620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A24">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -32677,7 +32677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -32734,7 +32734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -32791,7 +32791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -32848,7 +32848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -32905,7 +32905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -32962,7 +32962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -33019,7 +33019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -33076,7 +33076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -33133,7 +33133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -33190,7 +33190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -33247,7 +33247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -33304,7 +33304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -33361,7 +33361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -33418,7 +33418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -33475,7 +33475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -33532,7 +33532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -33589,7 +33589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -33646,7 +33646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -33703,7 +33703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -33760,7 +33760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -33817,7 +33817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -33874,7 +33874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -33931,7 +33931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -33988,7 +33988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -34045,7 +34045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -34102,7 +34102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -34159,7 +34159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51">
         <f t="shared" si="0"/>
         <v>51</v>
@@ -34216,7 +34216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52">
         <f t="shared" si="0"/>
         <v>52</v>
@@ -34273,7 +34273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53">
         <f t="shared" si="0"/>
         <v>53</v>
@@ -34330,7 +34330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54">
         <f t="shared" si="0"/>
         <v>54</v>
@@ -34387,7 +34387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55">
         <f t="shared" si="0"/>
         <v>55</v>
@@ -34444,7 +34444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56">
         <f t="shared" si="0"/>
         <v>56</v>
@@ -34501,7 +34501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57">
         <f t="shared" si="0"/>
         <v>57</v>
@@ -34558,7 +34558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58">
         <f t="shared" si="0"/>
         <v>58</v>
@@ -34615,7 +34615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59">
         <f t="shared" si="0"/>
         <v>59</v>
@@ -34672,7 +34672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60">
         <f t="shared" si="0"/>
         <v>60</v>
@@ -34729,7 +34729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61">
         <f t="shared" si="0"/>
         <v>61</v>
@@ -34786,7 +34786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62">
         <f t="shared" si="0"/>
         <v>62</v>
@@ -34843,7 +34843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63">
         <f t="shared" si="0"/>
         <v>63</v>
@@ -34900,7 +34900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64">
         <f t="shared" si="0"/>
         <v>64</v>
@@ -34957,7 +34957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A65">
         <f t="shared" si="0"/>
         <v>65</v>
@@ -35014,7 +35014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A66">
         <f t="shared" si="0"/>
         <v>66</v>
@@ -35071,7 +35071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" ht="15" x14ac:dyDescent="0.3">
       <c r="A67">
         <f t="shared" ref="A67:A132" si="1">A66+1</f>
         <v>67</v>
@@ -35128,7 +35128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A68">
         <f t="shared" si="1"/>
         <v>68</v>
@@ -35185,7 +35185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A69">
         <f t="shared" si="1"/>
         <v>69</v>
@@ -35242,7 +35242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A70">
         <f t="shared" si="1"/>
         <v>70</v>
@@ -35299,7 +35299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A71">
         <f t="shared" si="1"/>
         <v>71</v>
@@ -35356,7 +35356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A72">
         <f t="shared" si="1"/>
         <v>72</v>
@@ -35413,7 +35413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A73">
         <f t="shared" si="1"/>
         <v>73</v>
@@ -35470,7 +35470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A74">
         <f t="shared" si="1"/>
         <v>74</v>
@@ -35527,7 +35527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A75">
         <f t="shared" si="1"/>
         <v>75</v>
@@ -35584,7 +35584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A76">
         <f t="shared" si="1"/>
         <v>76</v>
@@ -35641,7 +35641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A77">
         <f t="shared" si="1"/>
         <v>77</v>
@@ -35698,7 +35698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A78">
         <f t="shared" si="1"/>
         <v>78</v>
@@ -35755,7 +35755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A79">
         <f t="shared" si="1"/>
         <v>79</v>
@@ -35812,7 +35812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A80">
         <f t="shared" si="1"/>
         <v>80</v>
@@ -35869,7 +35869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81">
         <f t="shared" si="1"/>
         <v>81</v>
@@ -35926,7 +35926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82">
         <f t="shared" si="1"/>
         <v>82</v>
@@ -35983,7 +35983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83">
         <f t="shared" si="1"/>
         <v>83</v>
@@ -36040,7 +36040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84">
         <f t="shared" si="1"/>
         <v>84</v>
@@ -36097,7 +36097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85">
         <f t="shared" si="1"/>
         <v>85</v>
@@ -36154,7 +36154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86">
         <f t="shared" si="1"/>
         <v>86</v>
@@ -36211,7 +36211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87">
         <f t="shared" si="1"/>
         <v>87</v>
@@ -36268,7 +36268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88">
         <f t="shared" si="1"/>
         <v>88</v>
@@ -36325,7 +36325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89">
         <f t="shared" si="1"/>
         <v>89</v>
@@ -36382,7 +36382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90">
         <f t="shared" si="1"/>
         <v>90</v>
@@ -36439,7 +36439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91">
         <f t="shared" si="1"/>
         <v>91</v>
@@ -36496,7 +36496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92">
         <f t="shared" si="1"/>
         <v>92</v>
@@ -36553,7 +36553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93">
         <f t="shared" si="1"/>
         <v>93</v>
@@ -36610,7 +36610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94">
         <f t="shared" si="1"/>
         <v>94</v>
@@ -36667,7 +36667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" ht="15" x14ac:dyDescent="0.3">
       <c r="A95">
         <f t="shared" si="1"/>
         <v>95</v>
@@ -36724,7 +36724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96">
         <f t="shared" si="1"/>
         <v>96</v>
@@ -36781,7 +36781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97">
         <f t="shared" si="1"/>
         <v>97</v>
@@ -36838,7 +36838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98">
         <f t="shared" si="1"/>
         <v>98</v>
@@ -36895,7 +36895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A99">
         <f t="shared" si="1"/>
         <v>99</v>
@@ -36952,7 +36952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100">
         <f t="shared" si="1"/>
         <v>100</v>
@@ -37009,7 +37009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101">
         <f t="shared" si="1"/>
         <v>101</v>
@@ -37066,7 +37066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102">
         <f t="shared" si="1"/>
         <v>102</v>
@@ -37123,7 +37123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103">
         <f t="shared" si="1"/>
         <v>103</v>
@@ -37180,7 +37180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A104">
         <f t="shared" si="1"/>
         <v>104</v>
@@ -37237,7 +37237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A105">
         <f t="shared" si="1"/>
         <v>105</v>
@@ -37294,7 +37294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A106">
         <f t="shared" si="1"/>
         <v>106</v>
@@ -37351,7 +37351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A107">
         <f t="shared" si="1"/>
         <v>107</v>
@@ -37408,7 +37408,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A108">
         <f t="shared" si="1"/>
         <v>108</v>
@@ -37465,7 +37465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A109">
         <f t="shared" si="1"/>
         <v>109</v>
@@ -37522,7 +37522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A110">
         <f t="shared" si="1"/>
         <v>110</v>
@@ -37579,7 +37579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A111">
         <f t="shared" si="1"/>
         <v>111</v>
@@ -37636,7 +37636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A112">
         <f t="shared" si="1"/>
         <v>112</v>
@@ -37693,7 +37693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A113">
         <f t="shared" si="1"/>
         <v>113</v>
@@ -37750,7 +37750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A114">
         <f t="shared" si="1"/>
         <v>114</v>
@@ -37807,7 +37807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A115">
         <f t="shared" si="1"/>
         <v>115</v>
@@ -37864,7 +37864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A116">
         <f t="shared" si="1"/>
         <v>116</v>
@@ -37921,7 +37921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A117">
         <f t="shared" si="1"/>
         <v>117</v>
@@ -37978,7 +37978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A118">
         <f t="shared" si="1"/>
         <v>118</v>
@@ -38035,7 +38035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A119">
         <f t="shared" si="1"/>
         <v>119</v>
@@ -38092,7 +38092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A120">
         <f t="shared" si="1"/>
         <v>120</v>
@@ -38149,7 +38149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A121">
         <f t="shared" si="1"/>
         <v>121</v>
@@ -38206,7 +38206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A122">
         <f t="shared" si="1"/>
         <v>122</v>
@@ -38263,7 +38263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A123">
         <f t="shared" si="1"/>
         <v>123</v>
@@ -38320,7 +38320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A124">
         <f t="shared" si="1"/>
         <v>124</v>
@@ -38377,7 +38377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A125">
         <f t="shared" si="1"/>
         <v>125</v>
@@ -38434,7 +38434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A126">
         <f t="shared" si="1"/>
         <v>126</v>
@@ -38491,7 +38491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A127">
         <f t="shared" si="1"/>
         <v>127</v>
@@ -38548,7 +38548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A128">
         <f t="shared" si="1"/>
         <v>128</v>
@@ -38605,7 +38605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A129">
         <f t="shared" si="1"/>
         <v>129</v>
@@ -38662,7 +38662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A130">
         <f t="shared" si="1"/>
         <v>130</v>
@@ -38719,7 +38719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A131">
         <f t="shared" ref="A131:A194" si="2">A130+1</f>
         <v>131</v>
@@ -38776,7 +38776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A132">
         <f t="shared" si="1"/>
         <v>132</v>
@@ -38833,7 +38833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" ht="15" x14ac:dyDescent="0.3">
       <c r="A133">
         <f t="shared" si="2"/>
         <v>133</v>
@@ -38890,7 +38890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A134">
         <f t="shared" si="2"/>
         <v>134</v>
@@ -38947,7 +38947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A135">
         <f t="shared" si="2"/>
         <v>135</v>
@@ -39004,7 +39004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A136">
         <f t="shared" si="2"/>
         <v>136</v>
@@ -39061,7 +39061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A137">
         <f t="shared" si="2"/>
         <v>137</v>
@@ -39118,7 +39118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" ht="15" x14ac:dyDescent="0.3">
       <c r="A138">
         <f t="shared" si="2"/>
         <v>138</v>
@@ -39175,7 +39175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A139">
         <f t="shared" si="2"/>
         <v>139</v>
@@ -39232,7 +39232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A140">
         <f t="shared" si="2"/>
         <v>140</v>
@@ -39289,7 +39289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A141">
         <f t="shared" si="2"/>
         <v>141</v>
@@ -39346,7 +39346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A142">
         <f t="shared" si="2"/>
         <v>142</v>
@@ -39403,7 +39403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A143">
         <f t="shared" si="2"/>
         <v>143</v>
@@ -39460,7 +39460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A144">
         <f t="shared" si="2"/>
         <v>144</v>
@@ -39517,7 +39517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A145">
         <f t="shared" si="2"/>
         <v>145</v>
@@ -39574,7 +39574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A146">
         <f t="shared" si="2"/>
         <v>146</v>
@@ -39631,7 +39631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A147">
         <f t="shared" si="2"/>
         <v>147</v>
@@ -39688,7 +39688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A148">
         <f t="shared" si="2"/>
         <v>148</v>
@@ -39745,7 +39745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A149">
         <f t="shared" si="2"/>
         <v>149</v>
@@ -39802,7 +39802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A150">
         <f t="shared" si="2"/>
         <v>150</v>
@@ -39859,7 +39859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A151">
         <f t="shared" si="2"/>
         <v>151</v>
@@ -39916,7 +39916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A152">
         <f t="shared" si="2"/>
         <v>152</v>
@@ -39973,7 +39973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A153">
         <f t="shared" si="2"/>
         <v>153</v>
@@ -40030,7 +40030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A154">
         <f t="shared" si="2"/>
         <v>154</v>
@@ -40087,7 +40087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A155">
         <f t="shared" si="2"/>
         <v>155</v>
@@ -40144,7 +40144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A156">
         <f t="shared" si="2"/>
         <v>156</v>
@@ -40201,7 +40201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A157">
         <f t="shared" si="2"/>
         <v>157</v>
@@ -40258,7 +40258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A158">
         <f t="shared" si="2"/>
         <v>158</v>
@@ -40315,7 +40315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A159">
         <f t="shared" si="2"/>
         <v>159</v>
@@ -40372,7 +40372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A160">
         <f t="shared" si="2"/>
         <v>160</v>
@@ -40429,7 +40429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A161">
         <f t="shared" si="2"/>
         <v>161</v>
@@ -40486,7 +40486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A162">
         <f t="shared" si="2"/>
         <v>162</v>
@@ -40543,7 +40543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A163">
         <f t="shared" si="2"/>
         <v>163</v>
@@ -40600,7 +40600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A164">
         <f t="shared" si="2"/>
         <v>164</v>
@@ -40657,7 +40657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A165">
         <f t="shared" si="2"/>
         <v>165</v>
@@ -40714,7 +40714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A166">
         <f t="shared" si="2"/>
         <v>166</v>
@@ -40771,7 +40771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A167">
         <f t="shared" si="2"/>
         <v>167</v>
@@ -40828,7 +40828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A168">
         <f t="shared" si="2"/>
         <v>168</v>
@@ -40885,7 +40885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A169">
         <f t="shared" si="2"/>
         <v>169</v>
@@ -40942,7 +40942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A170">
         <f>A169+2</f>
         <v>171</v>
@@ -40999,7 +40999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A171">
         <f t="shared" si="2"/>
         <v>172</v>
@@ -41056,7 +41056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A172">
         <f t="shared" si="2"/>
         <v>173</v>
@@ -41113,7 +41113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A173">
         <f t="shared" si="2"/>
         <v>174</v>
@@ -41170,7 +41170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A174">
         <f t="shared" si="2"/>
         <v>175</v>
@@ -41227,7 +41227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A175">
         <f t="shared" si="2"/>
         <v>176</v>
@@ -41284,7 +41284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A176">
         <f t="shared" si="2"/>
         <v>177</v>
@@ -41341,7 +41341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A177">
         <f t="shared" si="2"/>
         <v>178</v>
@@ -41398,7 +41398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A178">
         <f t="shared" si="2"/>
         <v>179</v>
@@ -41455,7 +41455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A179">
         <f t="shared" si="2"/>
         <v>180</v>
@@ -41512,7 +41512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A180">
         <f t="shared" si="2"/>
         <v>181</v>
@@ -41569,7 +41569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A181">
         <f t="shared" si="2"/>
         <v>182</v>
@@ -41626,7 +41626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A182">
         <f t="shared" si="2"/>
         <v>183</v>
@@ -41683,7 +41683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A183">
         <f t="shared" si="2"/>
         <v>184</v>
@@ -41740,7 +41740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A184">
         <f t="shared" si="2"/>
         <v>185</v>
@@ -41797,7 +41797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A185">
         <f t="shared" si="2"/>
         <v>186</v>
@@ -41854,7 +41854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A186">
         <f t="shared" si="2"/>
         <v>187</v>
@@ -41911,7 +41911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A187">
         <f t="shared" si="2"/>
         <v>188</v>
@@ -41968,7 +41968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A188">
         <f t="shared" si="2"/>
         <v>189</v>
@@ -42025,7 +42025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A189">
         <f t="shared" si="2"/>
         <v>190</v>
@@ -42082,7 +42082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A190">
         <f t="shared" si="2"/>
         <v>191</v>
@@ -42139,7 +42139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A191">
         <f t="shared" si="2"/>
         <v>192</v>
@@ -42196,7 +42196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A192">
         <f t="shared" si="2"/>
         <v>193</v>
@@ -42253,7 +42253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A193">
         <f t="shared" si="2"/>
         <v>194</v>
@@ -42310,7 +42310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A194">
         <f t="shared" si="2"/>
         <v>195</v>
@@ -42367,7 +42367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A195">
         <f t="shared" ref="A195:A258" si="3">A194+1</f>
         <v>196</v>
@@ -42424,7 +42424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A196">
         <f t="shared" si="3"/>
         <v>197</v>
@@ -42481,7 +42481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A197">
         <f t="shared" si="3"/>
         <v>198</v>
@@ -42538,7 +42538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A198">
         <f t="shared" si="3"/>
         <v>199</v>
@@ -42595,7 +42595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A199">
         <f t="shared" si="3"/>
         <v>200</v>
@@ -42652,7 +42652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A200">
         <f t="shared" si="3"/>
         <v>201</v>
@@ -42709,7 +42709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A201">
         <f t="shared" si="3"/>
         <v>202</v>
@@ -42766,7 +42766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A202">
         <f t="shared" si="3"/>
         <v>203</v>
@@ -42823,7 +42823,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A203">
         <f t="shared" si="3"/>
         <v>204</v>
@@ -42880,7 +42880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A204">
         <f t="shared" si="3"/>
         <v>205</v>
@@ -42937,7 +42937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A205">
         <f t="shared" si="3"/>
         <v>206</v>
@@ -42994,7 +42994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A206">
         <f t="shared" si="3"/>
         <v>207</v>
@@ -43051,7 +43051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A207">
         <f t="shared" si="3"/>
         <v>208</v>
@@ -43108,7 +43108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A208">
         <f t="shared" si="3"/>
         <v>209</v>
@@ -43177,7 +43177,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="209" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A209">
         <f t="shared" si="3"/>
         <v>210</v>
@@ -43258,7 +43258,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="210" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A210">
         <f t="shared" si="3"/>
         <v>211</v>
@@ -43350,7 +43350,7 @@
         <v>500000</v>
       </c>
     </row>
-    <row r="211" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A211">
         <f t="shared" si="3"/>
         <v>212</v>
@@ -43442,7 +43442,7 @@
         <v>4000000</v>
       </c>
     </row>
-    <row r="212" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A212">
         <f t="shared" si="3"/>
         <v>213</v>
@@ -43534,7 +43534,7 @@
         <v>13500000</v>
       </c>
     </row>
-    <row r="213" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A213">
         <f t="shared" si="3"/>
         <v>214</v>
@@ -43626,7 +43626,7 @@
         <v>32000000</v>
       </c>
     </row>
-    <row r="214" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A214">
         <f t="shared" si="3"/>
         <v>215</v>
@@ -43718,7 +43718,7 @@
         <v>62500000</v>
       </c>
     </row>
-    <row r="215" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A215">
         <f t="shared" si="3"/>
         <v>216</v>
@@ -43810,7 +43810,7 @@
         <v>108000000</v>
       </c>
     </row>
-    <row r="216" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A216">
         <f t="shared" si="3"/>
         <v>217</v>
@@ -43902,7 +43902,7 @@
         <v>171500000</v>
       </c>
     </row>
-    <row r="217" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A217">
         <f t="shared" si="3"/>
         <v>218</v>
@@ -43994,7 +43994,7 @@
         <v>256000000</v>
       </c>
     </row>
-    <row r="218" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A218">
         <f t="shared" si="3"/>
         <v>219</v>
@@ -44086,7 +44086,7 @@
         <v>364500000</v>
       </c>
     </row>
-    <row r="219" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A219">
         <f t="shared" si="3"/>
         <v>220</v>
@@ -44178,7 +44178,7 @@
         <v>500000000</v>
       </c>
     </row>
-    <row r="220" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A220">
         <f t="shared" si="3"/>
         <v>221</v>
@@ -44270,7 +44270,7 @@
         <v>665500000</v>
       </c>
     </row>
-    <row r="221" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A221">
         <f t="shared" si="3"/>
         <v>222</v>
@@ -44362,7 +44362,7 @@
         <v>864000000</v>
       </c>
     </row>
-    <row r="222" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A222">
         <f t="shared" si="3"/>
         <v>223</v>
@@ -44454,7 +44454,7 @@
         <v>1098500000</v>
       </c>
     </row>
-    <row r="223" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A223">
         <f t="shared" si="3"/>
         <v>224</v>
@@ -44546,7 +44546,7 @@
         <v>1372000000</v>
       </c>
     </row>
-    <row r="224" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A224">
         <f t="shared" si="3"/>
         <v>225</v>
@@ -44638,7 +44638,7 @@
         <v>1687500000</v>
       </c>
     </row>
-    <row r="225" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A225">
         <f t="shared" si="3"/>
         <v>226</v>
@@ -44730,7 +44730,7 @@
         <v>2048000000</v>
       </c>
     </row>
-    <row r="226" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A226">
         <f t="shared" si="3"/>
         <v>227</v>
@@ -44822,7 +44822,7 @@
         <v>2456500000</v>
       </c>
     </row>
-    <row r="227" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A227">
         <f t="shared" si="3"/>
         <v>228</v>
@@ -44914,7 +44914,7 @@
         <v>2916000000</v>
       </c>
     </row>
-    <row r="228" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A228">
         <f t="shared" si="3"/>
         <v>229</v>
@@ -45006,7 +45006,7 @@
         <v>3429500000</v>
       </c>
     </row>
-    <row r="229" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A229">
         <f t="shared" si="3"/>
         <v>230</v>
@@ -45098,7 +45098,7 @@
         <v>4000000000</v>
       </c>
     </row>
-    <row r="230" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A230">
         <f t="shared" si="3"/>
         <v>231</v>
@@ -45159,7 +45159,7 @@
         <v>65268000000</v>
       </c>
     </row>
-    <row r="231" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A231">
         <f t="shared" si="3"/>
         <v>232</v>
@@ -45216,7 +45216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A232">
         <f t="shared" si="3"/>
         <v>233</v>
@@ -45273,7 +45273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A233">
         <f t="shared" si="3"/>
         <v>234</v>
@@ -45330,7 +45330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A234">
         <f t="shared" si="3"/>
         <v>235</v>
@@ -45387,7 +45387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A235">
         <f t="shared" si="3"/>
         <v>236</v>
@@ -45444,7 +45444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A236">
         <f t="shared" si="3"/>
         <v>237</v>
@@ -45501,7 +45501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A237">
         <f t="shared" si="3"/>
         <v>238</v>
@@ -45558,7 +45558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A238">
         <f t="shared" si="3"/>
         <v>239</v>
@@ -45615,7 +45615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="239" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A239">
         <f t="shared" si="3"/>
         <v>240</v>
@@ -45672,7 +45672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A240">
         <f t="shared" si="3"/>
         <v>241</v>
@@ -45729,7 +45729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A241">
         <f t="shared" si="3"/>
         <v>242</v>
@@ -45786,7 +45786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A242">
         <f t="shared" si="3"/>
         <v>243</v>
@@ -45843,7 +45843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A243">
         <f t="shared" si="3"/>
         <v>244</v>
@@ -45900,7 +45900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A244">
         <f t="shared" si="3"/>
         <v>245</v>
@@ -45957,7 +45957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A245">
         <f t="shared" si="3"/>
         <v>246</v>
@@ -46014,7 +46014,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A246">
         <f t="shared" si="3"/>
         <v>247</v>
@@ -46071,7 +46071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A247">
         <f t="shared" si="3"/>
         <v>248</v>
@@ -46128,7 +46128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A248">
         <f t="shared" si="3"/>
         <v>249</v>
@@ -46185,7 +46185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A249">
         <f t="shared" si="3"/>
         <v>250</v>
@@ -46242,7 +46242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A250">
         <f t="shared" si="3"/>
         <v>251</v>
@@ -46299,7 +46299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A251">
         <f t="shared" si="3"/>
         <v>252</v>
@@ -46356,7 +46356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A252">
         <f t="shared" si="3"/>
         <v>253</v>
@@ -46413,7 +46413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A253">
         <f t="shared" si="3"/>
         <v>254</v>
@@ -46470,7 +46470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A254">
         <f t="shared" si="3"/>
         <v>255</v>
@@ -46527,7 +46527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A255">
         <f t="shared" si="3"/>
         <v>256</v>
@@ -46584,7 +46584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A256">
         <f t="shared" si="3"/>
         <v>257</v>
@@ -46641,7 +46641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="257" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A257">
         <f t="shared" si="3"/>
         <v>258</v>
@@ -46698,7 +46698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A258">
         <f t="shared" si="3"/>
         <v>259</v>
@@ -46755,7 +46755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A259">
         <f t="shared" ref="A259:A320" si="8">A258+1</f>
         <v>260</v>
@@ -46812,7 +46812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A260">
         <f t="shared" si="8"/>
         <v>261</v>
@@ -46869,7 +46869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A261">
         <f t="shared" si="8"/>
         <v>262</v>
@@ -46926,7 +46926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A262">
         <f t="shared" si="8"/>
         <v>263</v>
@@ -46983,7 +46983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A263">
         <f t="shared" si="8"/>
         <v>264</v>
@@ -47040,7 +47040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A264">
         <f t="shared" si="8"/>
         <v>265</v>
@@ -47097,7 +47097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A265">
         <f t="shared" si="8"/>
         <v>266</v>
@@ -47154,7 +47154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A266">
         <f t="shared" si="8"/>
         <v>267</v>
@@ -47211,7 +47211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A267">
         <f t="shared" si="8"/>
         <v>268</v>
@@ -47268,7 +47268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A268">
         <f t="shared" si="8"/>
         <v>269</v>
@@ -47325,7 +47325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A269">
         <f t="shared" si="8"/>
         <v>270</v>
@@ -47382,7 +47382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A270">
         <f t="shared" si="8"/>
         <v>271</v>
@@ -47439,7 +47439,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A271">
         <f t="shared" si="8"/>
         <v>272</v>
@@ -47496,7 +47496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A272">
         <f t="shared" si="8"/>
         <v>273</v>
@@ -47553,7 +47553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A273">
         <f t="shared" si="8"/>
         <v>274</v>
@@ -47610,7 +47610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A274">
         <f t="shared" si="8"/>
         <v>275</v>
@@ -47667,7 +47667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A275">
         <f t="shared" si="8"/>
         <v>276</v>
@@ -47724,7 +47724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A276">
         <f t="shared" si="8"/>
         <v>277</v>
@@ -47781,7 +47781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A277">
         <f t="shared" si="8"/>
         <v>278</v>
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A278">
         <f t="shared" si="8"/>
         <v>279</v>
@@ -47895,7 +47895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A279">
         <f t="shared" si="8"/>
         <v>280</v>
@@ -47952,7 +47952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A280">
         <f t="shared" si="8"/>
         <v>281</v>
@@ -48009,7 +48009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A281">
         <f t="shared" si="8"/>
         <v>282</v>
@@ -48066,7 +48066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A282">
         <f t="shared" si="8"/>
         <v>283</v>
@@ -48123,7 +48123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A283">
         <f t="shared" si="8"/>
         <v>284</v>
@@ -48180,7 +48180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="284" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A284">
         <f t="shared" si="8"/>
         <v>285</v>
@@ -48237,7 +48237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A285">
         <f t="shared" si="8"/>
         <v>286</v>
@@ -48294,7 +48294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A286">
         <f t="shared" si="8"/>
         <v>287</v>
@@ -48351,7 +48351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A287">
         <f t="shared" si="8"/>
         <v>288</v>
@@ -48408,7 +48408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A288">
         <f>A287+3</f>
         <v>291</v>
@@ -48465,7 +48465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A289">
         <f t="shared" si="8"/>
         <v>292</v>
@@ -48522,7 +48522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A290">
         <f t="shared" si="8"/>
         <v>293</v>
@@ -48579,7 +48579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A291">
         <f t="shared" si="8"/>
         <v>294</v>
@@ -48636,7 +48636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A292">
         <f t="shared" si="8"/>
         <v>295</v>
@@ -48693,7 +48693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="293" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A293">
         <f t="shared" si="8"/>
         <v>296</v>
@@ -48750,7 +48750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A294">
         <f t="shared" si="8"/>
         <v>297</v>
@@ -48807,7 +48807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A295">
         <f t="shared" si="8"/>
         <v>298</v>
@@ -48864,7 +48864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A296">
         <f t="shared" si="8"/>
         <v>299</v>
@@ -48921,7 +48921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A297">
         <f t="shared" si="8"/>
         <v>300</v>
@@ -48978,7 +48978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A298">
         <f t="shared" si="8"/>
         <v>301</v>
@@ -49035,7 +49035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A299">
         <f t="shared" si="8"/>
         <v>302</v>
@@ -49092,7 +49092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A300">
         <f t="shared" si="8"/>
         <v>303</v>
@@ -49149,7 +49149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A301">
         <f t="shared" si="8"/>
         <v>304</v>
@@ -49206,7 +49206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="302" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A302">
         <f t="shared" si="8"/>
         <v>305</v>
@@ -49263,7 +49263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A303">
         <f t="shared" si="8"/>
         <v>306</v>
@@ -49320,7 +49320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A304">
         <f t="shared" si="8"/>
         <v>307</v>
@@ -49377,7 +49377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A305">
         <f t="shared" si="8"/>
         <v>308</v>
@@ -49434,7 +49434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A306">
         <f t="shared" si="8"/>
         <v>309</v>
@@ -49491,7 +49491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A307">
         <f t="shared" si="8"/>
         <v>310</v>
@@ -49548,7 +49548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A308">
         <f t="shared" si="8"/>
         <v>311</v>
@@ -49605,7 +49605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A309">
         <f t="shared" si="8"/>
         <v>312</v>
@@ -49662,7 +49662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A310">
         <f t="shared" si="8"/>
         <v>313</v>
@@ -49719,7 +49719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A311">
         <f t="shared" si="8"/>
         <v>314</v>
@@ -49776,7 +49776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A312">
         <f t="shared" si="8"/>
         <v>315</v>
@@ -49833,7 +49833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A313">
         <f t="shared" si="8"/>
         <v>316</v>
@@ -49890,7 +49890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A314">
         <f t="shared" si="8"/>
         <v>317</v>
@@ -49947,7 +49947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A315">
         <f t="shared" si="8"/>
         <v>318</v>
@@ -50004,7 +50004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A316">
         <f t="shared" si="8"/>
         <v>319</v>
@@ -50061,7 +50061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:18" ht="15" x14ac:dyDescent="0.3">
       <c r="A317">
         <f t="shared" si="8"/>
         <v>320</v>
@@ -50118,7 +50118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A318">
         <f t="shared" si="8"/>
         <v>321</v>
@@ -50175,7 +50175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A319">
         <f t="shared" si="8"/>
         <v>322</v>
@@ -50232,7 +50232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A320">
         <f t="shared" si="8"/>
         <v>323</v>
@@ -50289,7 +50289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A321">
         <f t="shared" ref="A321:A329" si="9">A320+1</f>
         <v>324</v>
@@ -50346,7 +50346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A322">
         <f t="shared" si="9"/>
         <v>325</v>
@@ -50403,7 +50403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A323">
         <f t="shared" si="9"/>
         <v>326</v>
@@ -50460,7 +50460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A324">
         <f t="shared" si="9"/>
         <v>327</v>
@@ -50517,7 +50517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A325">
         <f t="shared" si="9"/>
         <v>328</v>
@@ -50574,7 +50574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A326">
         <f t="shared" si="9"/>
         <v>329</v>
@@ -50631,7 +50631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A327">
         <f t="shared" si="9"/>
         <v>330</v>
@@ -50688,7 +50688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A328">
         <f t="shared" si="9"/>
         <v>331</v>
@@ -50745,7 +50745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A329">
         <f t="shared" si="9"/>
         <v>332</v>
@@ -50802,7 +50802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A330">
         <f t="shared" ref="A330:A348" si="10">A329+1</f>
         <v>333</v>
@@ -50859,7 +50859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A331">
         <f t="shared" si="10"/>
         <v>334</v>
@@ -50916,7 +50916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A332">
         <f t="shared" si="10"/>
         <v>335</v>
@@ -50973,7 +50973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A333">
         <f t="shared" si="10"/>
         <v>336</v>
@@ -51030,7 +51030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A334">
         <f t="shared" si="10"/>
         <v>337</v>
@@ -51087,7 +51087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A335">
         <f t="shared" si="10"/>
         <v>338</v>
@@ -51144,7 +51144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A336">
         <f t="shared" si="10"/>
         <v>339</v>
@@ -51201,7 +51201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A337">
         <f t="shared" si="10"/>
         <v>340</v>
@@ -51258,7 +51258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A338">
         <f t="shared" si="10"/>
         <v>341</v>
@@ -51315,7 +51315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A339">
         <f t="shared" si="10"/>
         <v>342</v>
@@ -51372,7 +51372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A340">
         <f t="shared" si="10"/>
         <v>343</v>
@@ -51429,7 +51429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A341">
         <f t="shared" si="10"/>
         <v>344</v>
@@ -51486,7 +51486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A342">
         <f t="shared" si="10"/>
         <v>345</v>
@@ -51543,7 +51543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A343">
         <f t="shared" si="10"/>
         <v>346</v>
@@ -51600,7 +51600,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A344">
         <f t="shared" si="10"/>
         <v>347</v>
@@ -51657,7 +51657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A345">
         <f t="shared" si="10"/>
         <v>348</v>
@@ -51714,7 +51714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A346">
         <f t="shared" si="10"/>
         <v>349</v>
@@ -51771,7 +51771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="347" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A347">
         <f t="shared" si="10"/>
         <v>350</v>
@@ -51828,7 +51828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A348">
         <f t="shared" si="10"/>
         <v>351</v>
@@ -51885,7 +51885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>352</v>
       </c>
@@ -51905,7 +51905,7 @@
         <v>1127</v>
       </c>
       <c r="G349">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="H349">
         <v>0</v>
@@ -51941,7 +51941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A350">
         <f>A349+1</f>
         <v>353</v>
@@ -51998,7 +51998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A351">
         <f>A350+1</f>
         <v>354</v>
@@ -52055,7 +52055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A352">
         <f>A351+1</f>
         <v>355</v>
@@ -52112,7 +52112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A353">
         <f>A352+1</f>
         <v>356</v>
@@ -52169,7 +52169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A354">
         <f t="shared" ref="A354:A356" si="11">A353+1</f>
         <v>357</v>
@@ -52226,7 +52226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A355">
         <f t="shared" si="11"/>
         <v>358</v>
@@ -52283,7 +52283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="356" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A356">
         <f t="shared" si="11"/>
         <v>359</v>

--- a/config/Excel/game_parameters.xlsx
+++ b/config/Excel/game_parameters.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\AppData\Local\Temp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\.codex\visualizations\2026\10\31\01a190e4-e970-79e0-9abb-28460a792bba\mastery-300\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F508ABB8-D7EF-446B-9A93-ADE9633EA194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA23A95F-8BB4-4AE0-A082-376F396AE729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3015" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6050,8 +6050,7 @@
         <v>技能熟練度升 1 級所需經驗（沿用玩家升級公式未轉生版；L=目前熟練度等級）。</v>
       </c>
       <c r="G13">
-        <f>計算表!G14</f>
-        <v>30</v>
+        <v>1240</v>
       </c>
       <c r="H13">
         <f>計算表!H14</f>
